--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-06.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-06.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="100">
   <si>
     <t>League</t>
   </si>
@@ -254,6 +254,66 @@
   </si>
   <si>
     <t>SnapshotTS</t>
+  </si>
+  <si>
+    <t>Argentinian Primera Division</t>
+  </si>
+  <si>
+    <t>US United Soccer League</t>
+  </si>
+  <si>
+    <t>Colombian Primera A</t>
+  </si>
+  <si>
+    <t>2026-08-06</t>
+  </si>
+  <si>
+    <t>00:15:00</t>
+  </si>
+  <si>
+    <t>00:30:00</t>
+  </si>
+  <si>
+    <t>01:00:00</t>
+  </si>
+  <si>
+    <t>01:30:00</t>
+  </si>
+  <si>
+    <t>02:30:00</t>
+  </si>
+  <si>
+    <t>Tigre</t>
+  </si>
+  <si>
+    <t>Tulsa Roughnecks FC</t>
+  </si>
+  <si>
+    <t>El Paso Locomotive FC</t>
+  </si>
+  <si>
+    <t>Once Caldas</t>
+  </si>
+  <si>
+    <t>Las Vegas Lights FC</t>
+  </si>
+  <si>
+    <t>Belgrano</t>
+  </si>
+  <si>
+    <t>Sacramento Republic</t>
+  </si>
+  <si>
+    <t>Monterey Bay FC</t>
+  </si>
+  <si>
+    <t>America de Cali S.A</t>
+  </si>
+  <si>
+    <t>Oakland Roots</t>
+  </si>
+  <si>
+    <t>2026-08-04 00:34:08</t>
   </si>
 </sst>
 </file>
@@ -585,7 +645,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB1"/>
+  <dimension ref="A1:CB6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -830,6 +890,1216 @@
         <v>79</v>
       </c>
     </row>
+    <row r="2" spans="1:80">
+      <c r="A2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D2" t="s">
+        <v>89</v>
+      </c>
+      <c r="E2" t="s">
+        <v>94</v>
+      </c>
+      <c r="F2">
+        <v>2.62</v>
+      </c>
+      <c r="G2">
+        <v>2.78</v>
+      </c>
+      <c r="H2">
+        <v>3.3</v>
+      </c>
+      <c r="I2">
+        <v>3.55</v>
+      </c>
+      <c r="J2">
+        <v>2.96</v>
+      </c>
+      <c r="K2">
+        <v>3.05</v>
+      </c>
+      <c r="L2">
+        <v>1.01</v>
+      </c>
+      <c r="M2">
+        <v>1.16</v>
+      </c>
+      <c r="N2">
+        <v>2.26</v>
+      </c>
+      <c r="O2">
+        <v>1.71</v>
+      </c>
+      <c r="P2">
+        <v>1.42</v>
+      </c>
+      <c r="Q2">
+        <v>3.15</v>
+      </c>
+      <c r="R2">
+        <v>1.14</v>
+      </c>
+      <c r="S2">
+        <v>7.2</v>
+      </c>
+      <c r="T2">
+        <v>2.32</v>
+      </c>
+      <c r="U2">
+        <v>1.61</v>
+      </c>
+      <c r="V2">
+        <v>1.4</v>
+      </c>
+      <c r="W2">
+        <v>1.56</v>
+      </c>
+      <c r="X2">
+        <v>7.6</v>
+      </c>
+      <c r="Y2">
+        <v>9.4</v>
+      </c>
+      <c r="Z2">
+        <v>22</v>
+      </c>
+      <c r="AA2">
+        <v>90</v>
+      </c>
+      <c r="AB2">
+        <v>7.2</v>
+      </c>
+      <c r="AC2">
+        <v>7.8</v>
+      </c>
+      <c r="AD2">
+        <v>17</v>
+      </c>
+      <c r="AE2">
+        <v>75</v>
+      </c>
+      <c r="AF2">
+        <v>16.5</v>
+      </c>
+      <c r="AG2">
+        <v>14.5</v>
+      </c>
+      <c r="AH2">
+        <v>32</v>
+      </c>
+      <c r="AI2">
+        <v>120</v>
+      </c>
+      <c r="AJ2">
+        <v>60</v>
+      </c>
+      <c r="AK2">
+        <v>55</v>
+      </c>
+      <c r="AL2">
+        <v>100</v>
+      </c>
+      <c r="AM2">
+        <v>310</v>
+      </c>
+      <c r="AN2">
+        <v>65</v>
+      </c>
+      <c r="AO2">
+        <v>120</v>
+      </c>
+      <c r="AP2">
+        <v>6.2</v>
+      </c>
+      <c r="AQ2">
+        <v>7</v>
+      </c>
+      <c r="AR2">
+        <v>17.5</v>
+      </c>
+      <c r="AS2">
+        <v>7.2</v>
+      </c>
+      <c r="AT2">
+        <v>6</v>
+      </c>
+      <c r="AU2">
+        <v>6.2</v>
+      </c>
+      <c r="AV2">
+        <v>14</v>
+      </c>
+      <c r="AW2">
+        <v>7.2</v>
+      </c>
+      <c r="AX2">
+        <v>13</v>
+      </c>
+      <c r="AY2">
+        <v>11.5</v>
+      </c>
+      <c r="AZ2">
+        <v>6.2</v>
+      </c>
+      <c r="BA2">
+        <v>7.4</v>
+      </c>
+      <c r="BB2">
+        <v>7</v>
+      </c>
+      <c r="BC2">
+        <v>6.8</v>
+      </c>
+      <c r="BD2">
+        <v>7.2</v>
+      </c>
+      <c r="BE2">
+        <v>7.6</v>
+      </c>
+      <c r="BF2">
+        <v>7</v>
+      </c>
+      <c r="BG2">
+        <v>7.4</v>
+      </c>
+      <c r="BH2">
+        <v>1000</v>
+      </c>
+      <c r="BI2">
+        <v>1.63</v>
+      </c>
+      <c r="BJ2">
+        <v>17.5</v>
+      </c>
+      <c r="BK2">
+        <v>1.49</v>
+      </c>
+      <c r="BL2">
+        <v>1000</v>
+      </c>
+      <c r="BM2">
+        <v>1.63</v>
+      </c>
+      <c r="BN2">
+        <v>7.4</v>
+      </c>
+      <c r="BO2">
+        <v>3.7</v>
+      </c>
+      <c r="BP2">
+        <v>38</v>
+      </c>
+      <c r="BQ2">
+        <v>1.57</v>
+      </c>
+      <c r="BR2">
+        <v>1000</v>
+      </c>
+      <c r="BS2">
+        <v>1.6</v>
+      </c>
+      <c r="BT2">
+        <v>8.6</v>
+      </c>
+      <c r="BU2">
+        <v>4.2</v>
+      </c>
+      <c r="BV2">
+        <v>50</v>
+      </c>
+      <c r="BW2">
+        <v>1.58</v>
+      </c>
+      <c r="BX2">
+        <v>1000</v>
+      </c>
+      <c r="BY2">
+        <v>1.61</v>
+      </c>
+      <c r="BZ2">
+        <v>1000</v>
+      </c>
+      <c r="CA2">
+        <v>1.61</v>
+      </c>
+      <c r="CB2" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="3" spans="1:80">
+      <c r="A3" t="s">
+        <v>81</v>
+      </c>
+      <c r="B3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C3" t="s">
+        <v>85</v>
+      </c>
+      <c r="D3" t="s">
+        <v>90</v>
+      </c>
+      <c r="E3" t="s">
+        <v>95</v>
+      </c>
+      <c r="F3">
+        <v>2.76</v>
+      </c>
+      <c r="G3">
+        <v>3.2</v>
+      </c>
+      <c r="H3">
+        <v>2.58</v>
+      </c>
+      <c r="I3">
+        <v>2.94</v>
+      </c>
+      <c r="J3">
+        <v>3.1</v>
+      </c>
+      <c r="K3">
+        <v>3.6</v>
+      </c>
+      <c r="L3">
+        <v>1.35</v>
+      </c>
+      <c r="M3">
+        <v>1.01</v>
+      </c>
+      <c r="N3">
+        <v>2.76</v>
+      </c>
+      <c r="O3">
+        <v>1.36</v>
+      </c>
+      <c r="P3">
+        <v>1.74</v>
+      </c>
+      <c r="Q3">
+        <v>2.08</v>
+      </c>
+      <c r="R3">
+        <v>1.22</v>
+      </c>
+      <c r="S3">
+        <v>3.3</v>
+      </c>
+      <c r="T3">
+        <v>1.11</v>
+      </c>
+      <c r="U3">
+        <v>1.11</v>
+      </c>
+      <c r="V3">
+        <v>1.51</v>
+      </c>
+      <c r="W3">
+        <v>1.45</v>
+      </c>
+      <c r="X3">
+        <v>1000</v>
+      </c>
+      <c r="Y3">
+        <v>1000</v>
+      </c>
+      <c r="Z3">
+        <v>1000</v>
+      </c>
+      <c r="AA3">
+        <v>1000</v>
+      </c>
+      <c r="AB3">
+        <v>1000</v>
+      </c>
+      <c r="AC3">
+        <v>1000</v>
+      </c>
+      <c r="AD3">
+        <v>1000</v>
+      </c>
+      <c r="AE3">
+        <v>1000</v>
+      </c>
+      <c r="AF3">
+        <v>1000</v>
+      </c>
+      <c r="AG3">
+        <v>1000</v>
+      </c>
+      <c r="AH3">
+        <v>1000</v>
+      </c>
+      <c r="AI3">
+        <v>1000</v>
+      </c>
+      <c r="AJ3">
+        <v>1000</v>
+      </c>
+      <c r="AK3">
+        <v>1000</v>
+      </c>
+      <c r="AL3">
+        <v>1000</v>
+      </c>
+      <c r="AM3">
+        <v>1000</v>
+      </c>
+      <c r="AN3">
+        <v>1000</v>
+      </c>
+      <c r="AO3">
+        <v>1000</v>
+      </c>
+      <c r="AP3">
+        <v>1.01</v>
+      </c>
+      <c r="AQ3">
+        <v>1.01</v>
+      </c>
+      <c r="AR3">
+        <v>1.01</v>
+      </c>
+      <c r="AS3">
+        <v>1.01</v>
+      </c>
+      <c r="AT3">
+        <v>1.01</v>
+      </c>
+      <c r="AU3">
+        <v>1.01</v>
+      </c>
+      <c r="AV3">
+        <v>1.01</v>
+      </c>
+      <c r="AW3">
+        <v>1.01</v>
+      </c>
+      <c r="AX3">
+        <v>1.01</v>
+      </c>
+      <c r="AY3">
+        <v>1.01</v>
+      </c>
+      <c r="AZ3">
+        <v>1.01</v>
+      </c>
+      <c r="BA3">
+        <v>1.01</v>
+      </c>
+      <c r="BB3">
+        <v>1.01</v>
+      </c>
+      <c r="BC3">
+        <v>1.01</v>
+      </c>
+      <c r="BD3">
+        <v>1.01</v>
+      </c>
+      <c r="BE3">
+        <v>1.01</v>
+      </c>
+      <c r="BF3">
+        <v>1.01</v>
+      </c>
+      <c r="BG3">
+        <v>1.01</v>
+      </c>
+      <c r="BH3">
+        <v>1000</v>
+      </c>
+      <c r="BI3">
+        <v>1.04</v>
+      </c>
+      <c r="BJ3">
+        <v>1000</v>
+      </c>
+      <c r="BK3">
+        <v>1.04</v>
+      </c>
+      <c r="BL3">
+        <v>1000</v>
+      </c>
+      <c r="BM3">
+        <v>1.04</v>
+      </c>
+      <c r="BN3">
+        <v>1000</v>
+      </c>
+      <c r="BO3">
+        <v>1.04</v>
+      </c>
+      <c r="BP3">
+        <v>1000</v>
+      </c>
+      <c r="BQ3">
+        <v>1.04</v>
+      </c>
+      <c r="BR3">
+        <v>1000</v>
+      </c>
+      <c r="BS3">
+        <v>1.04</v>
+      </c>
+      <c r="BT3">
+        <v>1000</v>
+      </c>
+      <c r="BU3">
+        <v>1.04</v>
+      </c>
+      <c r="BV3">
+        <v>1000</v>
+      </c>
+      <c r="BW3">
+        <v>1.04</v>
+      </c>
+      <c r="BX3">
+        <v>1000</v>
+      </c>
+      <c r="BY3">
+        <v>1.04</v>
+      </c>
+      <c r="BZ3">
+        <v>1000</v>
+      </c>
+      <c r="CA3">
+        <v>1.04</v>
+      </c>
+      <c r="CB3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="4" spans="1:80">
+      <c r="A4" t="s">
+        <v>81</v>
+      </c>
+      <c r="B4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C4" t="s">
+        <v>86</v>
+      </c>
+      <c r="D4" t="s">
+        <v>91</v>
+      </c>
+      <c r="E4" t="s">
+        <v>96</v>
+      </c>
+      <c r="F4">
+        <v>1.7</v>
+      </c>
+      <c r="G4">
+        <v>1.86</v>
+      </c>
+      <c r="H4">
+        <v>4.6</v>
+      </c>
+      <c r="I4">
+        <v>5.6</v>
+      </c>
+      <c r="J4">
+        <v>4</v>
+      </c>
+      <c r="K4">
+        <v>4.6</v>
+      </c>
+      <c r="L4">
+        <v>1.01</v>
+      </c>
+      <c r="M4">
+        <v>1.01</v>
+      </c>
+      <c r="N4">
+        <v>1.1</v>
+      </c>
+      <c r="O4">
+        <v>1.24</v>
+      </c>
+      <c r="P4">
+        <v>2.1</v>
+      </c>
+      <c r="Q4">
+        <v>1.72</v>
+      </c>
+      <c r="R4">
+        <v>1.41</v>
+      </c>
+      <c r="S4">
+        <v>2.74</v>
+      </c>
+      <c r="T4">
+        <v>1.11</v>
+      </c>
+      <c r="U4">
+        <v>1.11</v>
+      </c>
+      <c r="V4">
+        <v>1.21</v>
+      </c>
+      <c r="W4">
+        <v>2.16</v>
+      </c>
+      <c r="X4">
+        <v>1000</v>
+      </c>
+      <c r="Y4">
+        <v>1000</v>
+      </c>
+      <c r="Z4">
+        <v>1000</v>
+      </c>
+      <c r="AA4">
+        <v>1000</v>
+      </c>
+      <c r="AB4">
+        <v>1000</v>
+      </c>
+      <c r="AC4">
+        <v>1000</v>
+      </c>
+      <c r="AD4">
+        <v>1000</v>
+      </c>
+      <c r="AE4">
+        <v>1000</v>
+      </c>
+      <c r="AF4">
+        <v>1000</v>
+      </c>
+      <c r="AG4">
+        <v>1000</v>
+      </c>
+      <c r="AH4">
+        <v>1000</v>
+      </c>
+      <c r="AI4">
+        <v>1000</v>
+      </c>
+      <c r="AJ4">
+        <v>1000</v>
+      </c>
+      <c r="AK4">
+        <v>1000</v>
+      </c>
+      <c r="AL4">
+        <v>1000</v>
+      </c>
+      <c r="AM4">
+        <v>1000</v>
+      </c>
+      <c r="AN4">
+        <v>1000</v>
+      </c>
+      <c r="AO4">
+        <v>1000</v>
+      </c>
+      <c r="AP4">
+        <v>1.01</v>
+      </c>
+      <c r="AQ4">
+        <v>1.01</v>
+      </c>
+      <c r="AR4">
+        <v>1.01</v>
+      </c>
+      <c r="AS4">
+        <v>1.01</v>
+      </c>
+      <c r="AT4">
+        <v>1.01</v>
+      </c>
+      <c r="AU4">
+        <v>1.01</v>
+      </c>
+      <c r="AV4">
+        <v>1.01</v>
+      </c>
+      <c r="AW4">
+        <v>1.01</v>
+      </c>
+      <c r="AX4">
+        <v>1.01</v>
+      </c>
+      <c r="AY4">
+        <v>1.01</v>
+      </c>
+      <c r="AZ4">
+        <v>1.01</v>
+      </c>
+      <c r="BA4">
+        <v>1.01</v>
+      </c>
+      <c r="BB4">
+        <v>1.01</v>
+      </c>
+      <c r="BC4">
+        <v>1.01</v>
+      </c>
+      <c r="BD4">
+        <v>1.01</v>
+      </c>
+      <c r="BE4">
+        <v>1.01</v>
+      </c>
+      <c r="BF4">
+        <v>1.01</v>
+      </c>
+      <c r="BG4">
+        <v>1.01</v>
+      </c>
+      <c r="BH4">
+        <v>1000</v>
+      </c>
+      <c r="BI4">
+        <v>1.04</v>
+      </c>
+      <c r="BJ4">
+        <v>1000</v>
+      </c>
+      <c r="BK4">
+        <v>1.04</v>
+      </c>
+      <c r="BL4">
+        <v>1000</v>
+      </c>
+      <c r="BM4">
+        <v>1.04</v>
+      </c>
+      <c r="BN4">
+        <v>1000</v>
+      </c>
+      <c r="BO4">
+        <v>1.04</v>
+      </c>
+      <c r="BP4">
+        <v>1000</v>
+      </c>
+      <c r="BQ4">
+        <v>1.04</v>
+      </c>
+      <c r="BR4">
+        <v>1000</v>
+      </c>
+      <c r="BS4">
+        <v>1.04</v>
+      </c>
+      <c r="BT4">
+        <v>1000</v>
+      </c>
+      <c r="BU4">
+        <v>1.04</v>
+      </c>
+      <c r="BV4">
+        <v>1000</v>
+      </c>
+      <c r="BW4">
+        <v>1.04</v>
+      </c>
+      <c r="BX4">
+        <v>1000</v>
+      </c>
+      <c r="BY4">
+        <v>1.04</v>
+      </c>
+      <c r="BZ4">
+        <v>1000</v>
+      </c>
+      <c r="CA4">
+        <v>1.04</v>
+      </c>
+      <c r="CB4" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="5" spans="1:80">
+      <c r="A5" t="s">
+        <v>82</v>
+      </c>
+      <c r="B5" t="s">
+        <v>83</v>
+      </c>
+      <c r="C5" t="s">
+        <v>87</v>
+      </c>
+      <c r="D5" t="s">
+        <v>92</v>
+      </c>
+      <c r="E5" t="s">
+        <v>97</v>
+      </c>
+      <c r="F5">
+        <v>2.12</v>
+      </c>
+      <c r="G5">
+        <v>2.36</v>
+      </c>
+      <c r="H5">
+        <v>3.6</v>
+      </c>
+      <c r="I5">
+        <v>4.1</v>
+      </c>
+      <c r="J5">
+        <v>3.15</v>
+      </c>
+      <c r="K5">
+        <v>3.6</v>
+      </c>
+      <c r="L5">
+        <v>1.01</v>
+      </c>
+      <c r="M5">
+        <v>1.08</v>
+      </c>
+      <c r="N5">
+        <v>3.1</v>
+      </c>
+      <c r="O5">
+        <v>1.39</v>
+      </c>
+      <c r="P5">
+        <v>1.73</v>
+      </c>
+      <c r="Q5">
+        <v>2.14</v>
+      </c>
+      <c r="R5">
+        <v>1.27</v>
+      </c>
+      <c r="S5">
+        <v>4</v>
+      </c>
+      <c r="T5">
+        <v>1.87</v>
+      </c>
+      <c r="U5">
+        <v>1.93</v>
+      </c>
+      <c r="V5">
+        <v>1.32</v>
+      </c>
+      <c r="W5">
+        <v>1.74</v>
+      </c>
+      <c r="X5">
+        <v>14</v>
+      </c>
+      <c r="Y5">
+        <v>15</v>
+      </c>
+      <c r="Z5">
+        <v>34</v>
+      </c>
+      <c r="AA5">
+        <v>100</v>
+      </c>
+      <c r="AB5">
+        <v>10.5</v>
+      </c>
+      <c r="AC5">
+        <v>8</v>
+      </c>
+      <c r="AD5">
+        <v>19.5</v>
+      </c>
+      <c r="AE5">
+        <v>65</v>
+      </c>
+      <c r="AF5">
+        <v>16</v>
+      </c>
+      <c r="AG5">
+        <v>13.5</v>
+      </c>
+      <c r="AH5">
+        <v>21</v>
+      </c>
+      <c r="AI5">
+        <v>80</v>
+      </c>
+      <c r="AJ5">
+        <v>32</v>
+      </c>
+      <c r="AK5">
+        <v>32</v>
+      </c>
+      <c r="AL5">
+        <v>55</v>
+      </c>
+      <c r="AM5">
+        <v>150</v>
+      </c>
+      <c r="AN5">
+        <v>27</v>
+      </c>
+      <c r="AO5">
+        <v>80</v>
+      </c>
+      <c r="AP5">
+        <v>8.6</v>
+      </c>
+      <c r="AQ5">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AR5">
+        <v>19.5</v>
+      </c>
+      <c r="AS5">
+        <v>5.1</v>
+      </c>
+      <c r="AT5">
+        <v>7.2</v>
+      </c>
+      <c r="AU5">
+        <v>6.6</v>
+      </c>
+      <c r="AV5">
+        <v>11.5</v>
+      </c>
+      <c r="AW5">
+        <v>4.9</v>
+      </c>
+      <c r="AX5">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AY5">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AZ5">
+        <v>16.5</v>
+      </c>
+      <c r="BA5">
+        <v>5</v>
+      </c>
+      <c r="BB5">
+        <v>21</v>
+      </c>
+      <c r="BC5">
+        <v>19</v>
+      </c>
+      <c r="BD5">
+        <v>4.8</v>
+      </c>
+      <c r="BE5">
+        <v>5.2</v>
+      </c>
+      <c r="BF5">
+        <v>15.5</v>
+      </c>
+      <c r="BG5">
+        <v>5</v>
+      </c>
+      <c r="BH5">
+        <v>1000</v>
+      </c>
+      <c r="BI5">
+        <v>2.22</v>
+      </c>
+      <c r="BJ5">
+        <v>15</v>
+      </c>
+      <c r="BK5">
+        <v>1.58</v>
+      </c>
+      <c r="BL5">
+        <v>1000</v>
+      </c>
+      <c r="BM5">
+        <v>1.76</v>
+      </c>
+      <c r="BN5">
+        <v>6.6</v>
+      </c>
+      <c r="BO5">
+        <v>3.25</v>
+      </c>
+      <c r="BP5">
+        <v>25</v>
+      </c>
+      <c r="BQ5">
+        <v>1.65</v>
+      </c>
+      <c r="BR5">
+        <v>50</v>
+      </c>
+      <c r="BS5">
+        <v>1.71</v>
+      </c>
+      <c r="BT5">
+        <v>10</v>
+      </c>
+      <c r="BU5">
+        <v>4.5</v>
+      </c>
+      <c r="BV5">
+        <v>50</v>
+      </c>
+      <c r="BW5">
+        <v>1.71</v>
+      </c>
+      <c r="BX5">
+        <v>1000</v>
+      </c>
+      <c r="BY5">
+        <v>1.72</v>
+      </c>
+      <c r="BZ5">
+        <v>48</v>
+      </c>
+      <c r="CA5">
+        <v>1.7</v>
+      </c>
+      <c r="CB5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="6" spans="1:80">
+      <c r="A6" t="s">
+        <v>81</v>
+      </c>
+      <c r="B6" t="s">
+        <v>83</v>
+      </c>
+      <c r="C6" t="s">
+        <v>88</v>
+      </c>
+      <c r="D6" t="s">
+        <v>93</v>
+      </c>
+      <c r="E6" t="s">
+        <v>98</v>
+      </c>
+      <c r="F6">
+        <v>2.42</v>
+      </c>
+      <c r="G6">
+        <v>2.84</v>
+      </c>
+      <c r="H6">
+        <v>2.8</v>
+      </c>
+      <c r="I6">
+        <v>3.2</v>
+      </c>
+      <c r="J6">
+        <v>3.45</v>
+      </c>
+      <c r="K6">
+        <v>4.4</v>
+      </c>
+      <c r="L6">
+        <v>1.01</v>
+      </c>
+      <c r="M6">
+        <v>1.01</v>
+      </c>
+      <c r="N6">
+        <v>2.08</v>
+      </c>
+      <c r="O6">
+        <v>1.23</v>
+      </c>
+      <c r="P6">
+        <v>2.08</v>
+      </c>
+      <c r="Q6">
+        <v>1.74</v>
+      </c>
+      <c r="R6">
+        <v>1.36</v>
+      </c>
+      <c r="S6">
+        <v>2.5</v>
+      </c>
+      <c r="T6">
+        <v>1.01</v>
+      </c>
+      <c r="U6">
+        <v>1.01</v>
+      </c>
+      <c r="V6">
+        <v>1.4</v>
+      </c>
+      <c r="W6">
+        <v>1.48</v>
+      </c>
+      <c r="X6">
+        <v>1000</v>
+      </c>
+      <c r="Y6">
+        <v>1000</v>
+      </c>
+      <c r="Z6">
+        <v>1000</v>
+      </c>
+      <c r="AA6">
+        <v>1000</v>
+      </c>
+      <c r="AB6">
+        <v>1000</v>
+      </c>
+      <c r="AC6">
+        <v>1000</v>
+      </c>
+      <c r="AD6">
+        <v>1000</v>
+      </c>
+      <c r="AE6">
+        <v>1000</v>
+      </c>
+      <c r="AF6">
+        <v>1000</v>
+      </c>
+      <c r="AG6">
+        <v>1000</v>
+      </c>
+      <c r="AH6">
+        <v>1000</v>
+      </c>
+      <c r="AI6">
+        <v>1000</v>
+      </c>
+      <c r="AJ6">
+        <v>1000</v>
+      </c>
+      <c r="AK6">
+        <v>1000</v>
+      </c>
+      <c r="AL6">
+        <v>1000</v>
+      </c>
+      <c r="AM6">
+        <v>1000</v>
+      </c>
+      <c r="AN6">
+        <v>1000</v>
+      </c>
+      <c r="AO6">
+        <v>1000</v>
+      </c>
+      <c r="AP6">
+        <v>1.03</v>
+      </c>
+      <c r="AQ6">
+        <v>1.03</v>
+      </c>
+      <c r="AR6">
+        <v>1.03</v>
+      </c>
+      <c r="AS6">
+        <v>1.03</v>
+      </c>
+      <c r="AT6">
+        <v>1.03</v>
+      </c>
+      <c r="AU6">
+        <v>1.03</v>
+      </c>
+      <c r="AV6">
+        <v>1.03</v>
+      </c>
+      <c r="AW6">
+        <v>1.03</v>
+      </c>
+      <c r="AX6">
+        <v>1.03</v>
+      </c>
+      <c r="AY6">
+        <v>1.03</v>
+      </c>
+      <c r="AZ6">
+        <v>1.03</v>
+      </c>
+      <c r="BA6">
+        <v>1.03</v>
+      </c>
+      <c r="BB6">
+        <v>1.03</v>
+      </c>
+      <c r="BC6">
+        <v>1.03</v>
+      </c>
+      <c r="BD6">
+        <v>1.03</v>
+      </c>
+      <c r="BE6">
+        <v>1.03</v>
+      </c>
+      <c r="BF6">
+        <v>1.01</v>
+      </c>
+      <c r="BG6">
+        <v>1.01</v>
+      </c>
+      <c r="BH6">
+        <v>1000</v>
+      </c>
+      <c r="BI6">
+        <v>1.01</v>
+      </c>
+      <c r="BJ6">
+        <v>1000</v>
+      </c>
+      <c r="BK6">
+        <v>1.01</v>
+      </c>
+      <c r="BL6">
+        <v>1000</v>
+      </c>
+      <c r="BM6">
+        <v>1.01</v>
+      </c>
+      <c r="BN6">
+        <v>1000</v>
+      </c>
+      <c r="BO6">
+        <v>1.01</v>
+      </c>
+      <c r="BP6">
+        <v>1000</v>
+      </c>
+      <c r="BQ6">
+        <v>1.01</v>
+      </c>
+      <c r="BR6">
+        <v>1000</v>
+      </c>
+      <c r="BS6">
+        <v>1.01</v>
+      </c>
+      <c r="BT6">
+        <v>1000</v>
+      </c>
+      <c r="BU6">
+        <v>1.01</v>
+      </c>
+      <c r="BV6">
+        <v>1000</v>
+      </c>
+      <c r="BW6">
+        <v>1.01</v>
+      </c>
+      <c r="BX6">
+        <v>1000</v>
+      </c>
+      <c r="BY6">
+        <v>1.01</v>
+      </c>
+      <c r="BZ6">
+        <v>1000</v>
+      </c>
+      <c r="CA6">
+        <v>1.01</v>
+      </c>
+      <c r="CB6" t="s">
+        <v>99</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-06.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-06.xlsx
@@ -313,7 +313,7 @@
     <t>Oakland Roots</t>
   </si>
   <si>
-    <t>2026-08-04 00:34:08</t>
+    <t>2026-08-04 02:41:30</t>
   </si>
 </sst>
 </file>
@@ -907,16 +907,16 @@
         <v>94</v>
       </c>
       <c r="F2">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="G2">
-        <v>2.78</v>
+        <v>2.82</v>
       </c>
       <c r="H2">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="I2">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="J2">
         <v>2.96</v>
@@ -931,7 +931,7 @@
         <v>1.16</v>
       </c>
       <c r="N2">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="O2">
         <v>1.71</v>
@@ -943,28 +943,28 @@
         <v>3.15</v>
       </c>
       <c r="R2">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="S2">
         <v>7.2</v>
       </c>
       <c r="T2">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="U2">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="V2">
         <v>1.4</v>
       </c>
       <c r="W2">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="X2">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="Y2">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Z2">
         <v>22</v>
@@ -976,7 +976,7 @@
         <v>7.2</v>
       </c>
       <c r="AC2">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="AD2">
         <v>17</v>
@@ -991,13 +991,13 @@
         <v>14.5</v>
       </c>
       <c r="AH2">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AI2">
         <v>120</v>
       </c>
       <c r="AJ2">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AK2">
         <v>55</v>
@@ -1006,7 +1006,7 @@
         <v>100</v>
       </c>
       <c r="AM2">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="AN2">
         <v>65</v>
@@ -1015,58 +1015,58 @@
         <v>120</v>
       </c>
       <c r="AP2">
+        <v>5.9</v>
+      </c>
+      <c r="AQ2">
+        <v>7.2</v>
+      </c>
+      <c r="AR2">
+        <v>18</v>
+      </c>
+      <c r="AS2">
+        <v>6.8</v>
+      </c>
+      <c r="AT2">
         <v>6.2</v>
       </c>
-      <c r="AQ2">
-        <v>7</v>
-      </c>
-      <c r="AR2">
-        <v>17.5</v>
-      </c>
-      <c r="AS2">
-        <v>7.2</v>
-      </c>
-      <c r="AT2">
-        <v>6</v>
-      </c>
       <c r="AU2">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="AV2">
         <v>14</v>
       </c>
       <c r="AW2">
+        <v>6.8</v>
+      </c>
+      <c r="AX2">
+        <v>13.5</v>
+      </c>
+      <c r="AY2">
+        <v>12</v>
+      </c>
+      <c r="AZ2">
+        <v>5.9</v>
+      </c>
+      <c r="BA2">
+        <v>7</v>
+      </c>
+      <c r="BB2">
+        <v>36</v>
+      </c>
+      <c r="BC2">
+        <v>34</v>
+      </c>
+      <c r="BD2">
+        <v>7</v>
+      </c>
+      <c r="BE2">
         <v>7.2</v>
       </c>
-      <c r="AX2">
-        <v>13</v>
-      </c>
-      <c r="AY2">
-        <v>11.5</v>
-      </c>
-      <c r="AZ2">
-        <v>6.2</v>
-      </c>
-      <c r="BA2">
-        <v>7.4</v>
-      </c>
-      <c r="BB2">
+      <c r="BF2">
+        <v>6.6</v>
+      </c>
+      <c r="BG2">
         <v>7</v>
-      </c>
-      <c r="BC2">
-        <v>6.8</v>
-      </c>
-      <c r="BD2">
-        <v>7.2</v>
-      </c>
-      <c r="BE2">
-        <v>7.6</v>
-      </c>
-      <c r="BF2">
-        <v>7</v>
-      </c>
-      <c r="BG2">
-        <v>7.4</v>
       </c>
       <c r="BH2">
         <v>1000</v>
@@ -1090,7 +1090,7 @@
         <v>7.4</v>
       </c>
       <c r="BO2">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="BP2">
         <v>38</v>
@@ -1108,7 +1108,7 @@
         <v>8.6</v>
       </c>
       <c r="BU2">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="BV2">
         <v>50</v>
@@ -1149,13 +1149,13 @@
         <v>95</v>
       </c>
       <c r="F3">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="G3">
         <v>3.2</v>
       </c>
       <c r="H3">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="I3">
         <v>2.94</v>
@@ -1164,130 +1164,130 @@
         <v>3.1</v>
       </c>
       <c r="K3">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="L3">
         <v>1.35</v>
       </c>
       <c r="M3">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N3">
-        <v>2.76</v>
+        <v>3.15</v>
       </c>
       <c r="O3">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="P3">
         <v>1.74</v>
       </c>
       <c r="Q3">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="R3">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="S3">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="T3">
-        <v>1.11</v>
+        <v>1.79</v>
       </c>
       <c r="U3">
-        <v>1.11</v>
+        <v>2</v>
       </c>
       <c r="V3">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="W3">
         <v>1.45</v>
       </c>
       <c r="X3">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="Y3">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="Z3">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AA3">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AB3">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AC3">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="AD3">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AE3">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AF3">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AG3">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AH3">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AI3">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AJ3">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AK3">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AL3">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AM3">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AN3">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AO3">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AP3">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="AQ3">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AR3">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="AS3">
         <v>1.01</v>
       </c>
       <c r="AT3">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="AU3">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="AV3">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW3">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="AX3">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="AY3">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="AZ3">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="BA3">
         <v>1.01</v>
@@ -1296,7 +1296,7 @@
         <v>1.01</v>
       </c>
       <c r="BC3">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD3">
         <v>1.01</v>
@@ -1305,7 +1305,7 @@
         <v>1.01</v>
       </c>
       <c r="BF3">
-        <v>1.01</v>
+        <v>25</v>
       </c>
       <c r="BG3">
         <v>1.01</v>
@@ -1391,226 +1391,226 @@
         <v>96</v>
       </c>
       <c r="F4">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="G4">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="H4">
         <v>4.6</v>
       </c>
       <c r="I4">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="J4">
         <v>4</v>
       </c>
       <c r="K4">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="L4">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="M4">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N4">
-        <v>1.1</v>
+        <v>4.2</v>
       </c>
       <c r="O4">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="P4">
         <v>2.1</v>
       </c>
       <c r="Q4">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="R4">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="S4">
-        <v>2.74</v>
+        <v>2.84</v>
       </c>
       <c r="T4">
-        <v>1.11</v>
+        <v>1.73</v>
       </c>
       <c r="U4">
-        <v>1.11</v>
+        <v>2.12</v>
       </c>
       <c r="V4">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="W4">
         <v>2.16</v>
       </c>
       <c r="X4">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="Y4">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="Z4">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AA4">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AB4">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AC4">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AD4">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AE4">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AF4">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AG4">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AH4">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AI4">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AJ4">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AK4">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AL4">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AM4">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AN4">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AO4">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AP4">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="AQ4">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="AR4">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="AS4">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="AT4">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AU4">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="AV4">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="AW4">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="AX4">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AY4">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="AZ4">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="BA4">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BB4">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="BC4">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="BD4">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BE4">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BF4">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG4">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BH4">
-        <v>1000</v>
+        <v>3.95</v>
       </c>
       <c r="BI4">
-        <v>1.04</v>
+        <v>3.1</v>
       </c>
       <c r="BJ4">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="BK4">
-        <v>1.04</v>
+        <v>5.2</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>1.04</v>
+        <v>10</v>
       </c>
       <c r="BN4">
-        <v>1000</v>
+        <v>4.7</v>
       </c>
       <c r="BO4">
-        <v>1.04</v>
+        <v>3.65</v>
       </c>
       <c r="BP4">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BQ4">
-        <v>1.04</v>
+        <v>5.7</v>
       </c>
       <c r="BR4">
         <v>1000</v>
       </c>
       <c r="BS4">
-        <v>1.04</v>
+        <v>7.6</v>
       </c>
       <c r="BT4">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BU4">
-        <v>1.04</v>
+        <v>4.9</v>
       </c>
       <c r="BV4">
         <v>1000</v>
       </c>
       <c r="BW4">
-        <v>1.04</v>
+        <v>8.6</v>
       </c>
       <c r="BX4">
         <v>1000</v>
       </c>
       <c r="BY4">
-        <v>1.04</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ4">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="CA4">
-        <v>1.04</v>
+        <v>7</v>
       </c>
       <c r="CB4" t="s">
         <v>99</v>
@@ -1633,34 +1633,34 @@
         <v>97</v>
       </c>
       <c r="F5">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="G5">
         <v>2.36</v>
       </c>
       <c r="H5">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="I5">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="J5">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="K5">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="L5">
-        <v>1.01</v>
+        <v>1.39</v>
       </c>
       <c r="M5">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N5">
         <v>3.1</v>
       </c>
       <c r="O5">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="P5">
         <v>1.73</v>
@@ -1678,7 +1678,7 @@
         <v>1.87</v>
       </c>
       <c r="U5">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="V5">
         <v>1.32</v>
@@ -1690,169 +1690,169 @@
         <v>14</v>
       </c>
       <c r="Y5">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="Z5">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="AA5">
         <v>100</v>
       </c>
       <c r="AB5">
-        <v>10.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC5">
         <v>8</v>
       </c>
       <c r="AD5">
-        <v>19.5</v>
+        <v>16.5</v>
       </c>
       <c r="AE5">
+        <v>55</v>
+      </c>
+      <c r="AF5">
+        <v>14</v>
+      </c>
+      <c r="AG5">
+        <v>12</v>
+      </c>
+      <c r="AH5">
+        <v>20</v>
+      </c>
+      <c r="AI5">
         <v>65</v>
-      </c>
-      <c r="AF5">
-        <v>16</v>
-      </c>
-      <c r="AG5">
-        <v>13.5</v>
-      </c>
-      <c r="AH5">
-        <v>21</v>
-      </c>
-      <c r="AI5">
-        <v>80</v>
       </c>
       <c r="AJ5">
         <v>32</v>
       </c>
       <c r="AK5">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="AL5">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="AM5">
         <v>150</v>
       </c>
       <c r="AN5">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="AO5">
         <v>80</v>
       </c>
       <c r="AP5">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ5">
         <v>9.199999999999999</v>
       </c>
       <c r="AR5">
-        <v>19.5</v>
+        <v>6.4</v>
       </c>
       <c r="AS5">
-        <v>5.1</v>
+        <v>8</v>
       </c>
       <c r="AT5">
-        <v>7.2</v>
+        <v>6.4</v>
       </c>
       <c r="AU5">
         <v>6.6</v>
       </c>
       <c r="AV5">
-        <v>11.5</v>
+        <v>5.6</v>
       </c>
       <c r="AW5">
-        <v>4.9</v>
+        <v>7.4</v>
       </c>
       <c r="AX5">
-        <v>9.800000000000001</v>
+        <v>5.3</v>
       </c>
       <c r="AY5">
         <v>8.199999999999999</v>
       </c>
       <c r="AZ5">
+        <v>17</v>
+      </c>
+      <c r="BA5">
+        <v>7.6</v>
+      </c>
+      <c r="BB5">
+        <v>18</v>
+      </c>
+      <c r="BC5">
         <v>16.5</v>
       </c>
-      <c r="BA5">
-        <v>5</v>
-      </c>
-      <c r="BB5">
-        <v>21</v>
-      </c>
-      <c r="BC5">
-        <v>19</v>
-      </c>
       <c r="BD5">
-        <v>4.8</v>
+        <v>27</v>
       </c>
       <c r="BE5">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BF5">
+        <v>6.2</v>
+      </c>
+      <c r="BG5">
+        <v>7.8</v>
+      </c>
+      <c r="BH5">
+        <v>3.2</v>
+      </c>
+      <c r="BI5">
+        <v>2.5</v>
+      </c>
+      <c r="BJ5">
+        <v>10.5</v>
+      </c>
+      <c r="BK5">
         <v>5.2</v>
       </c>
-      <c r="BF5">
-        <v>15.5</v>
-      </c>
-      <c r="BG5">
-        <v>5</v>
-      </c>
-      <c r="BH5">
-        <v>1000</v>
-      </c>
-      <c r="BI5">
-        <v>2.22</v>
-      </c>
-      <c r="BJ5">
-        <v>15</v>
-      </c>
-      <c r="BK5">
-        <v>1.58</v>
-      </c>
       <c r="BL5">
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>1.76</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN5">
+        <v>5.1</v>
+      </c>
+      <c r="BO5">
+        <v>4.2</v>
+      </c>
+      <c r="BP5">
+        <v>17.5</v>
+      </c>
+      <c r="BQ5">
         <v>6.6</v>
       </c>
-      <c r="BO5">
-        <v>3.25</v>
-      </c>
-      <c r="BP5">
-        <v>25</v>
-      </c>
-      <c r="BQ5">
-        <v>1.65</v>
-      </c>
       <c r="BR5">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="BS5">
-        <v>1.71</v>
+        <v>8</v>
       </c>
       <c r="BT5">
-        <v>10</v>
+        <v>7.4</v>
       </c>
       <c r="BU5">
-        <v>4.5</v>
+        <v>5.4</v>
       </c>
       <c r="BV5">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="BW5">
-        <v>1.71</v>
+        <v>8</v>
       </c>
       <c r="BX5">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="BY5">
-        <v>1.72</v>
+        <v>8.6</v>
       </c>
       <c r="BZ5">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="CA5">
-        <v>1.7</v>
+        <v>8</v>
       </c>
       <c r="CB5" t="s">
         <v>99</v>
@@ -1878,16 +1878,16 @@
         <v>2.42</v>
       </c>
       <c r="G6">
-        <v>2.84</v>
+        <v>2.96</v>
       </c>
       <c r="H6">
         <v>2.8</v>
       </c>
       <c r="I6">
+        <v>3.5</v>
+      </c>
+      <c r="J6">
         <v>3.2</v>
-      </c>
-      <c r="J6">
-        <v>3.45</v>
       </c>
       <c r="K6">
         <v>4.4</v>
@@ -1899,7 +1899,7 @@
         <v>1.01</v>
       </c>
       <c r="N6">
-        <v>2.08</v>
+        <v>2.24</v>
       </c>
       <c r="O6">
         <v>1.23</v>
@@ -1908,7 +1908,7 @@
         <v>2.08</v>
       </c>
       <c r="Q6">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="R6">
         <v>1.36</v>
@@ -1917,16 +1917,16 @@
         <v>2.5</v>
       </c>
       <c r="T6">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U6">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V6">
         <v>1.4</v>
       </c>
       <c r="W6">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="X6">
         <v>1000</v>
@@ -1983,52 +1983,52 @@
         <v>1000</v>
       </c>
       <c r="AP6">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ6">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR6">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS6">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT6">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU6">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV6">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW6">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX6">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY6">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ6">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA6">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB6">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC6">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD6">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE6">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF6">
         <v>1.01</v>
@@ -2037,64 +2037,64 @@
         <v>1.01</v>
       </c>
       <c r="BH6">
-        <v>1000</v>
+        <v>3.9</v>
       </c>
       <c r="BI6">
-        <v>1.01</v>
+        <v>3</v>
       </c>
       <c r="BJ6">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="BK6">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL6">
         <v>1000</v>
       </c>
       <c r="BM6">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN6">
-        <v>1000</v>
+        <v>5.9</v>
       </c>
       <c r="BO6">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BP6">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="BQ6">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR6">
         <v>1000</v>
       </c>
       <c r="BS6">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT6">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="BU6">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BV6">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BW6">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX6">
         <v>1000</v>
       </c>
       <c r="BY6">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ6">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="CA6">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB6" t="s">
         <v>99</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-06.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-06.xlsx
@@ -313,7 +313,7 @@
     <t>Oakland Roots</t>
   </si>
   <si>
-    <t>2026-08-04 02:41:30</t>
+    <t>2026-08-04 04:48:38</t>
   </si>
 </sst>
 </file>
@@ -907,13 +907,13 @@
         <v>94</v>
       </c>
       <c r="F2">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="G2">
-        <v>2.82</v>
+        <v>2.76</v>
       </c>
       <c r="H2">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="I2">
         <v>3.5</v>
@@ -922,7 +922,7 @@
         <v>2.96</v>
       </c>
       <c r="K2">
-        <v>3.05</v>
+        <v>2.98</v>
       </c>
       <c r="L2">
         <v>1.01</v>
@@ -958,13 +958,13 @@
         <v>1.4</v>
       </c>
       <c r="W2">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="X2">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="Y2">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="Z2">
         <v>22</v>
@@ -976,7 +976,7 @@
         <v>7.2</v>
       </c>
       <c r="AC2">
-        <v>8.4</v>
+        <v>7.2</v>
       </c>
       <c r="AD2">
         <v>17</v>
@@ -985,7 +985,7 @@
         <v>75</v>
       </c>
       <c r="AF2">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AG2">
         <v>14.5</v>
@@ -1012,7 +1012,7 @@
         <v>65</v>
       </c>
       <c r="AO2">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AP2">
         <v>5.9</v>
@@ -1024,7 +1024,7 @@
         <v>18</v>
       </c>
       <c r="AS2">
-        <v>6.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT2">
         <v>6.2</v>
@@ -1036,7 +1036,7 @@
         <v>14</v>
       </c>
       <c r="AW2">
-        <v>6.8</v>
+        <v>9</v>
       </c>
       <c r="AX2">
         <v>13.5</v>
@@ -1045,10 +1045,10 @@
         <v>12</v>
       </c>
       <c r="AZ2">
-        <v>5.9</v>
+        <v>7.4</v>
       </c>
       <c r="BA2">
-        <v>7</v>
+        <v>9.4</v>
       </c>
       <c r="BB2">
         <v>36</v>
@@ -1057,16 +1057,16 @@
         <v>34</v>
       </c>
       <c r="BD2">
-        <v>7</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE2">
-        <v>7.2</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF2">
-        <v>6.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG2">
-        <v>7</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH2">
         <v>1000</v>
@@ -1155,10 +1155,10 @@
         <v>3.2</v>
       </c>
       <c r="H3">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="I3">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="J3">
         <v>3.1</v>
@@ -1167,7 +1167,7 @@
         <v>3.65</v>
       </c>
       <c r="L3">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
       <c r="M3">
         <v>1.08</v>
@@ -1191,7 +1191,7 @@
         <v>3.8</v>
       </c>
       <c r="T3">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="U3">
         <v>2</v>
@@ -1263,13 +1263,13 @@
         <v>7.4</v>
       </c>
       <c r="AR3">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AS3">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AT3">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU3">
         <v>5.7</v>
@@ -1290,85 +1290,85 @@
         <v>13</v>
       </c>
       <c r="BA3">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BB3">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BC3">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="BD3">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BE3">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BF3">
-        <v>25</v>
+        <v>4.1</v>
       </c>
       <c r="BG3">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BH3">
-        <v>1000</v>
+        <v>3.25</v>
       </c>
       <c r="BI3">
-        <v>1.04</v>
+        <v>2.54</v>
       </c>
       <c r="BJ3">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BK3">
-        <v>1.04</v>
+        <v>5.3</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>1.04</v>
+        <v>10</v>
       </c>
       <c r="BN3">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="BO3">
-        <v>1.04</v>
+        <v>4.5</v>
       </c>
       <c r="BP3">
         <v>1000</v>
       </c>
       <c r="BQ3">
-        <v>1.04</v>
+        <v>7.4</v>
       </c>
       <c r="BR3">
         <v>1000</v>
       </c>
       <c r="BS3">
-        <v>1.04</v>
+        <v>8.4</v>
       </c>
       <c r="BT3">
-        <v>1000</v>
+        <v>5.8</v>
       </c>
       <c r="BU3">
-        <v>1.04</v>
+        <v>4.3</v>
       </c>
       <c r="BV3">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BW3">
-        <v>1.04</v>
+        <v>7.2</v>
       </c>
       <c r="BX3">
         <v>1000</v>
       </c>
       <c r="BY3">
-        <v>1.04</v>
+        <v>8.4</v>
       </c>
       <c r="BZ3">
         <v>1000</v>
       </c>
       <c r="CA3">
-        <v>1.04</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CB3" t="s">
         <v>99</v>
@@ -1409,7 +1409,7 @@
         <v>4.4</v>
       </c>
       <c r="L4">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="M4">
         <v>1.05</v>
@@ -1636,7 +1636,7 @@
         <v>2.18</v>
       </c>
       <c r="G5">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="H5">
         <v>3.7</v>
@@ -1645,10 +1645,10 @@
         <v>4.2</v>
       </c>
       <c r="J5">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="K5">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="L5">
         <v>1.39</v>
@@ -1657,7 +1657,7 @@
         <v>1.09</v>
       </c>
       <c r="N5">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="O5">
         <v>1.4</v>
@@ -1684,7 +1684,7 @@
         <v>1.32</v>
       </c>
       <c r="W5">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="X5">
         <v>14</v>
@@ -1738,7 +1738,7 @@
         <v>23</v>
       </c>
       <c r="AO5">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AP5">
         <v>8.800000000000001</v>
@@ -1747,7 +1747,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AR5">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AS5">
         <v>8</v>
@@ -1759,7 +1759,7 @@
         <v>6.6</v>
       </c>
       <c r="AV5">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="AW5">
         <v>7.4</v>
@@ -1789,28 +1789,28 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BF5">
-        <v>6.2</v>
+        <v>18.5</v>
       </c>
       <c r="BG5">
-        <v>7.8</v>
+        <v>42</v>
       </c>
       <c r="BH5">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="BI5">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="BJ5">
         <v>10.5</v>
       </c>
       <c r="BK5">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BL5">
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BN5">
         <v>5.1</v>
@@ -1822,10 +1822,10 @@
         <v>17.5</v>
       </c>
       <c r="BQ5">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BR5">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BS5">
         <v>8</v>
@@ -1834,7 +1834,7 @@
         <v>7.4</v>
       </c>
       <c r="BU5">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BV5">
         <v>1000</v>
@@ -1843,16 +1843,16 @@
         <v>8</v>
       </c>
       <c r="BX5">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="BY5">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BZ5">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="CA5">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="CB5" t="s">
         <v>99</v>
@@ -1878,31 +1878,31 @@
         <v>2.42</v>
       </c>
       <c r="G6">
-        <v>2.96</v>
+        <v>2.72</v>
       </c>
       <c r="H6">
         <v>2.8</v>
       </c>
       <c r="I6">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="J6">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="K6">
         <v>4.4</v>
       </c>
       <c r="L6">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="M6">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N6">
-        <v>2.24</v>
+        <v>4.1</v>
       </c>
       <c r="O6">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="P6">
         <v>2.08</v>
@@ -1911,109 +1911,109 @@
         <v>1.73</v>
       </c>
       <c r="R6">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="S6">
-        <v>2.5</v>
+        <v>2.84</v>
       </c>
       <c r="T6">
-        <v>1.11</v>
+        <v>1.62</v>
       </c>
       <c r="U6">
-        <v>1.11</v>
+        <v>2.28</v>
       </c>
       <c r="V6">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="W6">
-        <v>1.51</v>
+        <v>1.58</v>
       </c>
       <c r="X6">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="Y6">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="Z6">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AA6">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AB6">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AC6">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AD6">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AE6">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AF6">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AG6">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AH6">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AI6">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AJ6">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AK6">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AL6">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AM6">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AN6">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AO6">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AP6">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="AQ6">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AR6">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="AS6">
         <v>1.01</v>
       </c>
       <c r="AT6">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AU6">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AV6">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="AW6">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX6">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="AY6">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ6">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="BA6">
         <v>1.01</v>
@@ -2022,7 +2022,7 @@
         <v>1.01</v>
       </c>
       <c r="BC6">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BD6">
         <v>1.01</v>
@@ -2031,28 +2031,28 @@
         <v>1.01</v>
       </c>
       <c r="BF6">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="BG6">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="BH6">
         <v>3.9</v>
       </c>
       <c r="BI6">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="BJ6">
         <v>9.4</v>
       </c>
       <c r="BK6">
-        <v>1.04</v>
+        <v>4.8</v>
       </c>
       <c r="BL6">
         <v>1000</v>
       </c>
       <c r="BM6">
-        <v>1.04</v>
+        <v>9</v>
       </c>
       <c r="BN6">
         <v>5.9</v>
@@ -2064,13 +2064,13 @@
         <v>18.5</v>
       </c>
       <c r="BQ6">
-        <v>1.04</v>
+        <v>6.4</v>
       </c>
       <c r="BR6">
         <v>1000</v>
       </c>
       <c r="BS6">
-        <v>1.04</v>
+        <v>7.4</v>
       </c>
       <c r="BT6">
         <v>6.6</v>
@@ -2082,19 +2082,19 @@
         <v>23</v>
       </c>
       <c r="BW6">
-        <v>1.04</v>
+        <v>7</v>
       </c>
       <c r="BX6">
         <v>1000</v>
       </c>
       <c r="BY6">
-        <v>1.04</v>
+        <v>7.6</v>
       </c>
       <c r="BZ6">
         <v>23</v>
       </c>
       <c r="CA6">
-        <v>1.04</v>
+        <v>7</v>
       </c>
       <c r="CB6" t="s">
         <v>99</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-06.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-06.xlsx
@@ -313,7 +313,7 @@
     <t>Oakland Roots</t>
   </si>
   <si>
-    <t>2026-08-04 04:48:38</t>
+    <t>2026-08-04 06:55:09</t>
   </si>
 </sst>
 </file>
@@ -907,16 +907,16 @@
         <v>94</v>
       </c>
       <c r="F2">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="G2">
         <v>2.76</v>
       </c>
       <c r="H2">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="I2">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="J2">
         <v>2.96</v>
@@ -925,37 +925,37 @@
         <v>2.98</v>
       </c>
       <c r="L2">
-        <v>1.01</v>
+        <v>1.66</v>
       </c>
       <c r="M2">
         <v>1.16</v>
       </c>
       <c r="N2">
-        <v>2.28</v>
+        <v>2.22</v>
       </c>
       <c r="O2">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="P2">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="Q2">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="R2">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="S2">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="T2">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="U2">
-        <v>1.63</v>
+        <v>1.57</v>
       </c>
       <c r="V2">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W2">
         <v>1.57</v>
@@ -970,16 +970,16 @@
         <v>22</v>
       </c>
       <c r="AA2">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AB2">
         <v>7.2</v>
       </c>
       <c r="AC2">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AD2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AE2">
         <v>75</v>
@@ -988,34 +988,34 @@
         <v>16</v>
       </c>
       <c r="AG2">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AH2">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="AI2">
         <v>120</v>
       </c>
       <c r="AJ2">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AK2">
         <v>55</v>
       </c>
       <c r="AL2">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AM2">
-        <v>300</v>
+        <v>310</v>
       </c>
       <c r="AN2">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="AO2">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AP2">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AQ2">
         <v>7.2</v>
@@ -1024,109 +1024,109 @@
         <v>18</v>
       </c>
       <c r="AS2">
-        <v>9.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="AT2">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AU2">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AV2">
         <v>14</v>
       </c>
       <c r="AW2">
-        <v>9</v>
+        <v>7.4</v>
       </c>
       <c r="AX2">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AY2">
         <v>12</v>
       </c>
       <c r="AZ2">
+        <v>6.4</v>
+      </c>
+      <c r="BA2">
+        <v>7.6</v>
+      </c>
+      <c r="BB2">
+        <v>7.2</v>
+      </c>
+      <c r="BC2">
+        <v>7.2</v>
+      </c>
+      <c r="BD2">
+        <v>7.6</v>
+      </c>
+      <c r="BE2">
+        <v>8</v>
+      </c>
+      <c r="BF2">
         <v>7.4</v>
       </c>
-      <c r="BA2">
-        <v>9.4</v>
-      </c>
-      <c r="BB2">
-        <v>36</v>
-      </c>
-      <c r="BC2">
-        <v>34</v>
-      </c>
-      <c r="BD2">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BE2">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BF2">
-        <v>8.800000000000001</v>
-      </c>
       <c r="BG2">
-        <v>9.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="BH2">
-        <v>1000</v>
+        <v>2.52</v>
       </c>
       <c r="BI2">
-        <v>1.63</v>
+        <v>2.2</v>
       </c>
       <c r="BJ2">
-        <v>17.5</v>
+        <v>13</v>
       </c>
       <c r="BK2">
-        <v>1.49</v>
+        <v>6</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>1.63</v>
+        <v>10.5</v>
       </c>
       <c r="BN2">
-        <v>7.4</v>
+        <v>5.6</v>
       </c>
       <c r="BO2">
-        <v>3.8</v>
+        <v>4.7</v>
       </c>
       <c r="BP2">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="BQ2">
-        <v>1.57</v>
+        <v>8</v>
       </c>
       <c r="BR2">
         <v>1000</v>
       </c>
       <c r="BS2">
-        <v>1.6</v>
+        <v>9.4</v>
       </c>
       <c r="BT2">
+        <v>6.6</v>
+      </c>
+      <c r="BU2">
+        <v>4.9</v>
+      </c>
+      <c r="BV2">
+        <v>38</v>
+      </c>
+      <c r="BW2">
         <v>8.6</v>
-      </c>
-      <c r="BU2">
-        <v>4.4</v>
-      </c>
-      <c r="BV2">
-        <v>50</v>
-      </c>
-      <c r="BW2">
-        <v>1.58</v>
       </c>
       <c r="BX2">
         <v>1000</v>
       </c>
       <c r="BY2">
-        <v>1.61</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ2">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="CA2">
-        <v>1.61</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="CB2" t="s">
         <v>99</v>
@@ -1152,7 +1152,7 @@
         <v>2.78</v>
       </c>
       <c r="G3">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="H3">
         <v>2.54</v>
@@ -1161,7 +1161,7 @@
         <v>2.92</v>
       </c>
       <c r="J3">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="K3">
         <v>3.65</v>
@@ -1188,7 +1188,7 @@
         <v>1.28</v>
       </c>
       <c r="S3">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="T3">
         <v>1.8</v>
@@ -1203,13 +1203,13 @@
         <v>1.45</v>
       </c>
       <c r="X3">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="Y3">
         <v>12.5</v>
       </c>
       <c r="Z3">
-        <v>18.5</v>
+        <v>22</v>
       </c>
       <c r="AA3">
         <v>55</v>
@@ -1221,10 +1221,10 @@
         <v>9</v>
       </c>
       <c r="AD3">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AE3">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="AF3">
         <v>24</v>
@@ -1233,7 +1233,7 @@
         <v>16</v>
       </c>
       <c r="AH3">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AI3">
         <v>60</v>
@@ -1254,22 +1254,22 @@
         <v>44</v>
       </c>
       <c r="AO3">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AP3">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ3">
         <v>7.4</v>
       </c>
       <c r="AR3">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="AS3">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="AT3">
-        <v>9.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AU3">
         <v>5.7</v>
@@ -1278,37 +1278,37 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AW3">
-        <v>9</v>
+        <v>3.9</v>
       </c>
       <c r="AX3">
         <v>14</v>
       </c>
       <c r="AY3">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ3">
         <v>13</v>
       </c>
       <c r="BA3">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="BB3">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="BC3">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="BD3">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="BE3">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="BF3">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="BG3">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="BH3">
         <v>3.25</v>
@@ -1391,10 +1391,10 @@
         <v>96</v>
       </c>
       <c r="F4">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="G4">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="H4">
         <v>4.6</v>
@@ -1403,55 +1403,55 @@
         <v>5.5</v>
       </c>
       <c r="J4">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K4">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="L4">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="M4">
         <v>1.05</v>
       </c>
       <c r="N4">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="O4">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="P4">
-        <v>2.1</v>
+        <v>2.26</v>
       </c>
       <c r="Q4">
-        <v>1.73</v>
+        <v>1.64</v>
       </c>
       <c r="R4">
-        <v>1.43</v>
+        <v>1.49</v>
       </c>
       <c r="S4">
-        <v>2.84</v>
+        <v>2.6</v>
       </c>
       <c r="T4">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="U4">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="V4">
         <v>1.22</v>
       </c>
       <c r="W4">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="X4">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Y4">
         <v>23</v>
       </c>
       <c r="Z4">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AA4">
         <v>130</v>
@@ -1466,112 +1466,112 @@
         <v>23</v>
       </c>
       <c r="AE4">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AF4">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="AG4">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AH4">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AI4">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AJ4">
         <v>21</v>
       </c>
       <c r="AK4">
-        <v>21</v>
+        <v>17.5</v>
       </c>
       <c r="AL4">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AM4">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="AN4">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AO4">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AP4">
         <v>14</v>
       </c>
       <c r="AQ4">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="AR4">
-        <v>4.9</v>
+        <v>5.5</v>
       </c>
       <c r="AS4">
-        <v>5.2</v>
+        <v>5.9</v>
       </c>
       <c r="AT4">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="AU4">
         <v>8</v>
       </c>
       <c r="AV4">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="AW4">
-        <v>5.1</v>
+        <v>5.7</v>
       </c>
       <c r="AX4">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY4">
         <v>8.6</v>
       </c>
       <c r="AZ4">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BA4">
-        <v>5.1</v>
+        <v>5.7</v>
       </c>
       <c r="BB4">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="BC4">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BD4">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="BE4">
-        <v>5.2</v>
+        <v>5.8</v>
       </c>
       <c r="BF4">
-        <v>8.199999999999999</v>
+        <v>6.6</v>
       </c>
       <c r="BG4">
-        <v>5.1</v>
+        <v>5.7</v>
       </c>
       <c r="BH4">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="BI4">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="BJ4">
         <v>10</v>
       </c>
       <c r="BK4">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>10</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN4">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BO4">
         <v>3.65</v>
@@ -1580,37 +1580,37 @@
         <v>12</v>
       </c>
       <c r="BQ4">
-        <v>5.7</v>
+        <v>5.3</v>
       </c>
       <c r="BR4">
         <v>1000</v>
       </c>
       <c r="BS4">
-        <v>7.6</v>
+        <v>6.8</v>
       </c>
       <c r="BT4">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BU4">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="BV4">
         <v>1000</v>
       </c>
       <c r="BW4">
-        <v>8.6</v>
+        <v>7.6</v>
       </c>
       <c r="BX4">
         <v>1000</v>
       </c>
       <c r="BY4">
-        <v>8.800000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="BZ4">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="CA4">
-        <v>7</v>
+        <v>6.2</v>
       </c>
       <c r="CB4" t="s">
         <v>99</v>
@@ -1633,7 +1633,7 @@
         <v>97</v>
       </c>
       <c r="F5">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="G5">
         <v>2.32</v>
@@ -1651,40 +1651,40 @@
         <v>3.65</v>
       </c>
       <c r="L5">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="M5">
         <v>1.09</v>
       </c>
       <c r="N5">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="O5">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="P5">
         <v>1.73</v>
       </c>
       <c r="Q5">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="R5">
         <v>1.27</v>
       </c>
       <c r="S5">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="T5">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="U5">
-        <v>1.94</v>
+        <v>1.97</v>
       </c>
       <c r="V5">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="W5">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="X5">
         <v>14</v>
@@ -1693,10 +1693,10 @@
         <v>13</v>
       </c>
       <c r="Z5">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="AA5">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="AB5">
         <v>8.800000000000001</v>
@@ -1714,7 +1714,7 @@
         <v>14</v>
       </c>
       <c r="AG5">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AH5">
         <v>20</v>
@@ -1723,10 +1723,10 @@
         <v>65</v>
       </c>
       <c r="AJ5">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AK5">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="AL5">
         <v>46</v>
@@ -1738,7 +1738,7 @@
         <v>23</v>
       </c>
       <c r="AO5">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AP5">
         <v>8.800000000000001</v>
@@ -1747,25 +1747,25 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AR5">
-        <v>6.6</v>
+        <v>20</v>
       </c>
       <c r="AS5">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AT5">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="AU5">
         <v>6.6</v>
       </c>
       <c r="AV5">
-        <v>5.7</v>
+        <v>11.5</v>
       </c>
       <c r="AW5">
-        <v>7.4</v>
+        <v>36</v>
       </c>
       <c r="AX5">
-        <v>5.3</v>
+        <v>11.5</v>
       </c>
       <c r="AY5">
         <v>8.199999999999999</v>
@@ -1774,25 +1774,25 @@
         <v>17</v>
       </c>
       <c r="BA5">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB5">
-        <v>18</v>
+        <v>7.2</v>
       </c>
       <c r="BC5">
-        <v>16.5</v>
+        <v>7</v>
       </c>
       <c r="BD5">
-        <v>27</v>
+        <v>7.8</v>
       </c>
       <c r="BE5">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF5">
         <v>18.5</v>
       </c>
       <c r="BG5">
-        <v>42</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH5">
         <v>3.25</v>
@@ -1804,7 +1804,7 @@
         <v>10.5</v>
       </c>
       <c r="BK5">
-        <v>5.1</v>
+        <v>7.6</v>
       </c>
       <c r="BL5">
         <v>1000</v>
@@ -1875,22 +1875,22 @@
         <v>98</v>
       </c>
       <c r="F6">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="G6">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="H6">
-        <v>2.8</v>
+        <v>2.76</v>
       </c>
       <c r="I6">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="J6">
         <v>3.45</v>
       </c>
       <c r="K6">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="L6">
         <v>1.29</v>
@@ -1923,7 +1923,7 @@
         <v>2.28</v>
       </c>
       <c r="V6">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="W6">
         <v>1.58</v>
@@ -1935,7 +1935,7 @@
         <v>17</v>
       </c>
       <c r="Z6">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AA6">
         <v>55</v>
@@ -1965,7 +1965,7 @@
         <v>46</v>
       </c>
       <c r="AJ6">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AK6">
         <v>32</v>
@@ -1989,13 +1989,13 @@
         <v>10</v>
       </c>
       <c r="AR6">
-        <v>18</v>
+        <v>15.5</v>
       </c>
       <c r="AS6">
         <v>1.01</v>
       </c>
       <c r="AT6">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU6">
         <v>6.4</v>
@@ -2007,25 +2007,25 @@
         <v>1.03</v>
       </c>
       <c r="AX6">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AY6">
         <v>8.800000000000001</v>
       </c>
       <c r="AZ6">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="BA6">
         <v>1.01</v>
       </c>
       <c r="BB6">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC6">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="BD6">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE6">
         <v>1.01</v>
@@ -2040,7 +2040,7 @@
         <v>3.9</v>
       </c>
       <c r="BI6">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="BJ6">
         <v>9.4</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-06.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-06.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="97">
   <si>
     <t>League</t>
   </si>
@@ -280,9 +280,6 @@
     <t>01:30:00</t>
   </si>
   <si>
-    <t>02:30:00</t>
-  </si>
-  <si>
     <t>Tigre</t>
   </si>
   <si>
@@ -295,9 +292,6 @@
     <t>Once Caldas</t>
   </si>
   <si>
-    <t>Las Vegas Lights FC</t>
-  </si>
-  <si>
     <t>Belgrano</t>
   </si>
   <si>
@@ -310,10 +304,7 @@
     <t>America de Cali S.A</t>
   </si>
   <si>
-    <t>Oakland Roots</t>
-  </si>
-  <si>
-    <t>2026-08-04 06:55:09</t>
+    <t>2026-08-04 09:01:53</t>
   </si>
 </sst>
 </file>
@@ -645,7 +636,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB6"/>
+  <dimension ref="A1:CB5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -901,22 +892,22 @@
         <v>84</v>
       </c>
       <c r="D2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E2" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="F2">
-        <v>2.68</v>
+        <v>2.64</v>
       </c>
       <c r="G2">
-        <v>2.76</v>
+        <v>2.7</v>
       </c>
       <c r="H2">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="I2">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="J2">
         <v>2.96</v>
@@ -925,19 +916,19 @@
         <v>2.98</v>
       </c>
       <c r="L2">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="M2">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="N2">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="O2">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="P2">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="Q2">
         <v>3.25</v>
@@ -946,22 +937,22 @@
         <v>1.14</v>
       </c>
       <c r="S2">
+        <v>7.6</v>
+      </c>
+      <c r="T2">
+        <v>2.46</v>
+      </c>
+      <c r="U2">
+        <v>1.6</v>
+      </c>
+      <c r="V2">
+        <v>1.4</v>
+      </c>
+      <c r="W2">
+        <v>1.58</v>
+      </c>
+      <c r="X2">
         <v>7.4</v>
-      </c>
-      <c r="T2">
-        <v>2.4</v>
-      </c>
-      <c r="U2">
-        <v>1.57</v>
-      </c>
-      <c r="V2">
-        <v>1.41</v>
-      </c>
-      <c r="W2">
-        <v>1.57</v>
-      </c>
-      <c r="X2">
-        <v>7.8</v>
       </c>
       <c r="Y2">
         <v>8.6</v>
@@ -976,16 +967,16 @@
         <v>7.2</v>
       </c>
       <c r="AC2">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AD2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AE2">
         <v>75</v>
       </c>
       <c r="AF2">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AG2">
         <v>15.5</v>
@@ -1009,13 +1000,13 @@
         <v>310</v>
       </c>
       <c r="AN2">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AO2">
         <v>120</v>
       </c>
       <c r="AP2">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="AQ2">
         <v>7.2</v>
@@ -1024,7 +1015,7 @@
         <v>18</v>
       </c>
       <c r="AS2">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AT2">
         <v>6</v>
@@ -1036,7 +1027,7 @@
         <v>14</v>
       </c>
       <c r="AW2">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AX2">
         <v>12</v>
@@ -1045,34 +1036,34 @@
         <v>12</v>
       </c>
       <c r="AZ2">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BA2">
+        <v>8</v>
+      </c>
+      <c r="BB2">
+        <v>7.4</v>
+      </c>
+      <c r="BC2">
+        <v>7.4</v>
+      </c>
+      <c r="BD2">
+        <v>7.8</v>
+      </c>
+      <c r="BE2">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BF2">
         <v>7.6</v>
       </c>
-      <c r="BB2">
-        <v>7.2</v>
-      </c>
-      <c r="BC2">
-        <v>7.2</v>
-      </c>
-      <c r="BD2">
-        <v>7.6</v>
-      </c>
-      <c r="BE2">
+      <c r="BG2">
         <v>8</v>
-      </c>
-      <c r="BF2">
-        <v>7.4</v>
-      </c>
-      <c r="BG2">
-        <v>7.6</v>
       </c>
       <c r="BH2">
         <v>2.52</v>
       </c>
       <c r="BI2">
-        <v>2.2</v>
+        <v>2.08</v>
       </c>
       <c r="BJ2">
         <v>13</v>
@@ -1084,16 +1075,16 @@
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BN2">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BO2">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BP2">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="BQ2">
         <v>8</v>
@@ -1102,19 +1093,19 @@
         <v>1000</v>
       </c>
       <c r="BS2">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BT2">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BU2">
-        <v>4.9</v>
+        <v>5.5</v>
       </c>
       <c r="BV2">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BW2">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX2">
         <v>1000</v>
@@ -1123,13 +1114,13 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BZ2">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="CA2">
         <v>9.800000000000001</v>
       </c>
       <c r="CB2" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1143,70 +1134,70 @@
         <v>85</v>
       </c>
       <c r="D3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E3" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="F3">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="G3">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="H3">
-        <v>2.54</v>
+        <v>2.58</v>
       </c>
       <c r="I3">
-        <v>2.92</v>
+        <v>2.98</v>
       </c>
       <c r="J3">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="K3">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="L3">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="M3">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N3">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="O3">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="P3">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="Q3">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="R3">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="S3">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="T3">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="U3">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="V3">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="W3">
         <v>1.45</v>
       </c>
       <c r="X3">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="Y3">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Z3">
         <v>22</v>
@@ -1215,118 +1206,118 @@
         <v>55</v>
       </c>
       <c r="AB3">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AC3">
         <v>9</v>
       </c>
       <c r="AD3">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AE3">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AF3">
         <v>24</v>
       </c>
       <c r="AG3">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AH3">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AI3">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AJ3">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AK3">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AL3">
         <v>65</v>
       </c>
       <c r="AM3">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="AN3">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AO3">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="AP3">
+        <v>8.4</v>
+      </c>
+      <c r="AQ3">
+        <v>8.4</v>
+      </c>
+      <c r="AR3">
+        <v>13</v>
+      </c>
+      <c r="AS3">
+        <v>4.3</v>
+      </c>
+      <c r="AT3">
         <v>8.800000000000001</v>
       </c>
-      <c r="AQ3">
-        <v>7.4</v>
-      </c>
-      <c r="AR3">
-        <v>12.5</v>
-      </c>
-      <c r="AS3">
-        <v>4</v>
-      </c>
-      <c r="AT3">
-        <v>8</v>
-      </c>
       <c r="AU3">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="AV3">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="AW3">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="AX3">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AY3">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="AZ3">
-        <v>13</v>
+        <v>15.5</v>
       </c>
       <c r="BA3">
-        <v>4</v>
+        <v>34</v>
       </c>
       <c r="BB3">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="BC3">
-        <v>3.95</v>
+        <v>26</v>
       </c>
       <c r="BD3">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="BE3">
+        <v>4.5</v>
+      </c>
+      <c r="BF3">
         <v>4.2</v>
       </c>
-      <c r="BF3">
-        <v>3.95</v>
-      </c>
       <c r="BG3">
-        <v>3.9</v>
+        <v>19.5</v>
       </c>
       <c r="BH3">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="BI3">
-        <v>2.54</v>
+        <v>2.48</v>
       </c>
       <c r="BJ3">
         <v>10.5</v>
       </c>
       <c r="BK3">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN3">
         <v>6.2</v>
@@ -1335,7 +1326,7 @@
         <v>4.5</v>
       </c>
       <c r="BP3">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="BQ3">
         <v>7.4</v>
@@ -1353,7 +1344,7 @@
         <v>4.3</v>
       </c>
       <c r="BV3">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BW3">
         <v>7.2</v>
@@ -1362,16 +1353,16 @@
         <v>1000</v>
       </c>
       <c r="BY3">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ3">
         <v>1000</v>
       </c>
       <c r="CA3">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="CB3" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1385,34 +1376,34 @@
         <v>86</v>
       </c>
       <c r="D4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E4" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="F4">
         <v>1.69</v>
       </c>
       <c r="G4">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="H4">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="I4">
         <v>5.5</v>
       </c>
       <c r="J4">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="K4">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="L4">
         <v>1.29</v>
       </c>
       <c r="M4">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N4">
         <v>4.6</v>
@@ -1421,16 +1412,16 @@
         <v>1.22</v>
       </c>
       <c r="P4">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="Q4">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="R4">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="S4">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="T4">
         <v>1.67</v>
@@ -1442,7 +1433,7 @@
         <v>1.22</v>
       </c>
       <c r="W4">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="X4">
         <v>22</v>
@@ -1493,7 +1484,7 @@
         <v>95</v>
       </c>
       <c r="AN4">
-        <v>10</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AO4">
         <v>65</v>
@@ -1505,22 +1496,22 @@
         <v>16.5</v>
       </c>
       <c r="AR4">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="AS4">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="AT4">
         <v>8.4</v>
       </c>
       <c r="AU4">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="AV4">
         <v>16.5</v>
       </c>
       <c r="AW4">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="AX4">
         <v>9.800000000000001</v>
@@ -1532,7 +1523,7 @@
         <v>13</v>
       </c>
       <c r="BA4">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="BB4">
         <v>15.5</v>
@@ -1541,16 +1532,16 @@
         <v>13</v>
       </c>
       <c r="BD4">
-        <v>5.2</v>
+        <v>5.7</v>
       </c>
       <c r="BE4">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="BF4">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BG4">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="BH4">
         <v>4.1</v>
@@ -1568,7 +1559,7 @@
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BN4">
         <v>4.8</v>
@@ -1583,10 +1574,10 @@
         <v>5.3</v>
       </c>
       <c r="BR4">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BS4">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BT4">
         <v>9</v>
@@ -1598,22 +1589,22 @@
         <v>1000</v>
       </c>
       <c r="BW4">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BX4">
         <v>1000</v>
       </c>
       <c r="BY4">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BZ4">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="CA4">
         <v>6.2</v>
       </c>
       <c r="CB4" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1627,28 +1618,28 @@
         <v>87</v>
       </c>
       <c r="D5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E5" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F5">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="G5">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="H5">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="I5">
         <v>4.2</v>
       </c>
       <c r="J5">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K5">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="L5">
         <v>1.38</v>
@@ -1663,7 +1654,7 @@
         <v>1.39</v>
       </c>
       <c r="P5">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="Q5">
         <v>2.12</v>
@@ -1672,19 +1663,19 @@
         <v>1.27</v>
       </c>
       <c r="S5">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="T5">
         <v>1.86</v>
       </c>
       <c r="U5">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="V5">
         <v>1.31</v>
       </c>
       <c r="W5">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="X5">
         <v>14</v>
@@ -1747,7 +1738,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AR5">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AS5">
         <v>8.4</v>
@@ -1783,7 +1774,7 @@
         <v>7</v>
       </c>
       <c r="BD5">
-        <v>7.8</v>
+        <v>36</v>
       </c>
       <c r="BE5">
         <v>8.800000000000001</v>
@@ -1804,7 +1795,7 @@
         <v>10.5</v>
       </c>
       <c r="BK5">
-        <v>7.6</v>
+        <v>5.1</v>
       </c>
       <c r="BL5">
         <v>1000</v>
@@ -1816,7 +1807,7 @@
         <v>5.1</v>
       </c>
       <c r="BO5">
-        <v>4.2</v>
+        <v>3.75</v>
       </c>
       <c r="BP5">
         <v>17.5</v>
@@ -1855,249 +1846,7 @@
         <v>7.8</v>
       </c>
       <c r="CB5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="6" spans="1:80">
-      <c r="A6" t="s">
-        <v>81</v>
-      </c>
-      <c r="B6" t="s">
-        <v>83</v>
-      </c>
-      <c r="C6" t="s">
-        <v>88</v>
-      </c>
-      <c r="D6" t="s">
-        <v>93</v>
-      </c>
-      <c r="E6" t="s">
-        <v>98</v>
-      </c>
-      <c r="F6">
-        <v>2.4</v>
-      </c>
-      <c r="G6">
-        <v>2.74</v>
-      </c>
-      <c r="H6">
-        <v>2.76</v>
-      </c>
-      <c r="I6">
-        <v>3.3</v>
-      </c>
-      <c r="J6">
-        <v>3.45</v>
-      </c>
-      <c r="K6">
-        <v>4.2</v>
-      </c>
-      <c r="L6">
-        <v>1.29</v>
-      </c>
-      <c r="M6">
-        <v>1.05</v>
-      </c>
-      <c r="N6">
-        <v>4.1</v>
-      </c>
-      <c r="O6">
-        <v>1.25</v>
-      </c>
-      <c r="P6">
-        <v>2.08</v>
-      </c>
-      <c r="Q6">
-        <v>1.73</v>
-      </c>
-      <c r="R6">
-        <v>1.43</v>
-      </c>
-      <c r="S6">
-        <v>2.84</v>
-      </c>
-      <c r="T6">
-        <v>1.62</v>
-      </c>
-      <c r="U6">
-        <v>2.28</v>
-      </c>
-      <c r="V6">
-        <v>1.44</v>
-      </c>
-      <c r="W6">
-        <v>1.58</v>
-      </c>
-      <c r="X6">
-        <v>22</v>
-      </c>
-      <c r="Y6">
-        <v>17</v>
-      </c>
-      <c r="Z6">
-        <v>26</v>
-      </c>
-      <c r="AA6">
-        <v>55</v>
-      </c>
-      <c r="AB6">
-        <v>15.5</v>
-      </c>
-      <c r="AC6">
-        <v>10.5</v>
-      </c>
-      <c r="AD6">
-        <v>16</v>
-      </c>
-      <c r="AE6">
-        <v>38</v>
-      </c>
-      <c r="AF6">
-        <v>22</v>
-      </c>
-      <c r="AG6">
-        <v>14.5</v>
-      </c>
-      <c r="AH6">
-        <v>19.5</v>
-      </c>
-      <c r="AI6">
-        <v>46</v>
-      </c>
-      <c r="AJ6">
-        <v>44</v>
-      </c>
-      <c r="AK6">
-        <v>32</v>
-      </c>
-      <c r="AL6">
-        <v>42</v>
-      </c>
-      <c r="AM6">
-        <v>90</v>
-      </c>
-      <c r="AN6">
-        <v>22</v>
-      </c>
-      <c r="AO6">
-        <v>29</v>
-      </c>
-      <c r="AP6">
-        <v>13</v>
-      </c>
-      <c r="AQ6">
-        <v>10</v>
-      </c>
-      <c r="AR6">
-        <v>15.5</v>
-      </c>
-      <c r="AS6">
-        <v>1.01</v>
-      </c>
-      <c r="AT6">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AU6">
-        <v>6.4</v>
-      </c>
-      <c r="AV6">
-        <v>9.6</v>
-      </c>
-      <c r="AW6">
-        <v>1.03</v>
-      </c>
-      <c r="AX6">
-        <v>13</v>
-      </c>
-      <c r="AY6">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AZ6">
-        <v>11.5</v>
-      </c>
-      <c r="BA6">
-        <v>1.01</v>
-      </c>
-      <c r="BB6">
-        <v>1.03</v>
-      </c>
-      <c r="BC6">
-        <v>18.5</v>
-      </c>
-      <c r="BD6">
-        <v>1.03</v>
-      </c>
-      <c r="BE6">
-        <v>1.01</v>
-      </c>
-      <c r="BF6">
-        <v>13</v>
-      </c>
-      <c r="BG6">
-        <v>17</v>
-      </c>
-      <c r="BH6">
-        <v>3.9</v>
-      </c>
-      <c r="BI6">
-        <v>3</v>
-      </c>
-      <c r="BJ6">
-        <v>9.4</v>
-      </c>
-      <c r="BK6">
-        <v>4.8</v>
-      </c>
-      <c r="BL6">
-        <v>1000</v>
-      </c>
-      <c r="BM6">
-        <v>9</v>
-      </c>
-      <c r="BN6">
-        <v>5.9</v>
-      </c>
-      <c r="BO6">
-        <v>4.3</v>
-      </c>
-      <c r="BP6">
-        <v>18.5</v>
-      </c>
-      <c r="BQ6">
-        <v>6.4</v>
-      </c>
-      <c r="BR6">
-        <v>1000</v>
-      </c>
-      <c r="BS6">
-        <v>7.4</v>
-      </c>
-      <c r="BT6">
-        <v>6.6</v>
-      </c>
-      <c r="BU6">
-        <v>4.7</v>
-      </c>
-      <c r="BV6">
-        <v>23</v>
-      </c>
-      <c r="BW6">
-        <v>7</v>
-      </c>
-      <c r="BX6">
-        <v>1000</v>
-      </c>
-      <c r="BY6">
-        <v>7.6</v>
-      </c>
-      <c r="BZ6">
-        <v>23</v>
-      </c>
-      <c r="CA6">
-        <v>7</v>
-      </c>
-      <c r="CB6" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-06.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-06.xlsx
@@ -304,7 +304,7 @@
     <t>America de Cali S.A</t>
   </si>
   <si>
-    <t>2026-08-04 09:01:53</t>
+    <t>2026-08-04 11:09:02</t>
   </si>
 </sst>
 </file>
@@ -901,10 +901,10 @@
         <v>2.64</v>
       </c>
       <c r="G2">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="H2">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="I2">
         <v>3.55</v>
@@ -916,22 +916,22 @@
         <v>2.98</v>
       </c>
       <c r="L2">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="M2">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="N2">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="O2">
         <v>1.74</v>
       </c>
       <c r="P2">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="Q2">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="R2">
         <v>1.14</v>
@@ -940,34 +940,34 @@
         <v>7.6</v>
       </c>
       <c r="T2">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="U2">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="V2">
         <v>1.4</v>
       </c>
       <c r="W2">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="X2">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="Y2">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="Z2">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AA2">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AB2">
+        <v>6.8</v>
+      </c>
+      <c r="AC2">
         <v>7.2</v>
-      </c>
-      <c r="AC2">
-        <v>7.8</v>
       </c>
       <c r="AD2">
         <v>19</v>
@@ -976,7 +976,7 @@
         <v>75</v>
       </c>
       <c r="AF2">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AG2">
         <v>15.5</v>
@@ -985,79 +985,79 @@
         <v>32</v>
       </c>
       <c r="AI2">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AJ2">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AK2">
         <v>55</v>
       </c>
       <c r="AL2">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AM2">
         <v>310</v>
       </c>
       <c r="AN2">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AO2">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AP2">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="AQ2">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AR2">
         <v>18</v>
       </c>
       <c r="AS2">
-        <v>7.8</v>
+        <v>32</v>
       </c>
       <c r="AT2">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AU2">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="AV2">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="AW2">
-        <v>7.6</v>
+        <v>30</v>
       </c>
       <c r="AX2">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AY2">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AZ2">
-        <v>6.6</v>
+        <v>21</v>
       </c>
       <c r="BA2">
-        <v>8</v>
+        <v>42</v>
       </c>
       <c r="BB2">
-        <v>7.4</v>
+        <v>25</v>
       </c>
       <c r="BC2">
-        <v>7.4</v>
+        <v>26</v>
       </c>
       <c r="BD2">
-        <v>7.8</v>
+        <v>38</v>
       </c>
       <c r="BE2">
-        <v>8.199999999999999</v>
+        <v>55</v>
       </c>
       <c r="BF2">
-        <v>7.6</v>
+        <v>30</v>
       </c>
       <c r="BG2">
-        <v>8</v>
+        <v>36</v>
       </c>
       <c r="BH2">
         <v>2.52</v>
@@ -1078,16 +1078,16 @@
         <v>11</v>
       </c>
       <c r="BN2">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BO2">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="BP2">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BQ2">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR2">
         <v>1000</v>
@@ -1096,13 +1096,13 @@
         <v>9.6</v>
       </c>
       <c r="BT2">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BU2">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BV2">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BW2">
         <v>8.800000000000001</v>
@@ -1111,13 +1111,13 @@
         <v>1000</v>
       </c>
       <c r="BY2">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BZ2">
         <v>1000</v>
       </c>
       <c r="CA2">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="CB2" t="s">
         <v>96</v>
@@ -1140,58 +1140,58 @@
         <v>93</v>
       </c>
       <c r="F3">
-        <v>2.76</v>
+        <v>2.82</v>
       </c>
       <c r="G3">
+        <v>3.15</v>
+      </c>
+      <c r="H3">
+        <v>2.6</v>
+      </c>
+      <c r="I3">
+        <v>2.92</v>
+      </c>
+      <c r="J3">
         <v>3.2</v>
       </c>
-      <c r="H3">
-        <v>2.58</v>
-      </c>
-      <c r="I3">
-        <v>2.98</v>
-      </c>
-      <c r="J3">
-        <v>3.05</v>
-      </c>
       <c r="K3">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="L3">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="M3">
         <v>1.09</v>
       </c>
       <c r="N3">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="O3">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="P3">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="Q3">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="R3">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="S3">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="T3">
         <v>1.83</v>
       </c>
       <c r="U3">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="V3">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="W3">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="X3">
         <v>14</v>
@@ -1200,7 +1200,7 @@
         <v>12</v>
       </c>
       <c r="Z3">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="AA3">
         <v>55</v>
@@ -1212,112 +1212,112 @@
         <v>9</v>
       </c>
       <c r="AD3">
-        <v>15.5</v>
+        <v>13</v>
       </c>
       <c r="AE3">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="AF3">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AG3">
         <v>14</v>
       </c>
       <c r="AH3">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI3">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="AJ3">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AK3">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AL3">
         <v>65</v>
       </c>
       <c r="AM3">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AN3">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AO3">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="AP3">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="AQ3">
-        <v>8.4</v>
+        <v>7.2</v>
       </c>
       <c r="AR3">
         <v>13</v>
       </c>
       <c r="AS3">
-        <v>4.3</v>
+        <v>5.3</v>
       </c>
       <c r="AT3">
-        <v>8.800000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="AU3">
+        <v>5.7</v>
+      </c>
+      <c r="AV3">
+        <v>9.4</v>
+      </c>
+      <c r="AW3">
+        <v>5</v>
+      </c>
+      <c r="AX3">
+        <v>14</v>
+      </c>
+      <c r="AY3">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ3">
+        <v>13.5</v>
+      </c>
+      <c r="BA3">
+        <v>5.3</v>
+      </c>
+      <c r="BB3">
+        <v>5.4</v>
+      </c>
+      <c r="BC3">
+        <v>5.2</v>
+      </c>
+      <c r="BD3">
+        <v>5.4</v>
+      </c>
+      <c r="BE3">
         <v>5.6</v>
       </c>
-      <c r="AV3">
-        <v>10.5</v>
-      </c>
-      <c r="AW3">
-        <v>4.2</v>
-      </c>
-      <c r="AX3">
-        <v>16</v>
-      </c>
-      <c r="AY3">
-        <v>11</v>
-      </c>
-      <c r="AZ3">
-        <v>15.5</v>
-      </c>
-      <c r="BA3">
-        <v>34</v>
-      </c>
-      <c r="BB3">
-        <v>4.3</v>
-      </c>
-      <c r="BC3">
-        <v>26</v>
-      </c>
-      <c r="BD3">
-        <v>4.3</v>
-      </c>
-      <c r="BE3">
-        <v>4.5</v>
-      </c>
       <c r="BF3">
-        <v>4.2</v>
+        <v>5.2</v>
       </c>
       <c r="BG3">
-        <v>19.5</v>
+        <v>5</v>
       </c>
       <c r="BH3">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="BI3">
-        <v>2.48</v>
+        <v>2.54</v>
       </c>
       <c r="BJ3">
         <v>10.5</v>
       </c>
       <c r="BK3">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BN3">
         <v>6.2</v>
@@ -1326,16 +1326,16 @@
         <v>4.5</v>
       </c>
       <c r="BP3">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="BQ3">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BR3">
         <v>1000</v>
       </c>
       <c r="BS3">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BT3">
         <v>5.8</v>
@@ -1344,7 +1344,7 @@
         <v>4.3</v>
       </c>
       <c r="BV3">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="BW3">
         <v>7.2</v>
@@ -1353,13 +1353,13 @@
         <v>1000</v>
       </c>
       <c r="BY3">
+        <v>8.4</v>
+      </c>
+      <c r="BZ3">
+        <v>1000</v>
+      </c>
+      <c r="CA3">
         <v>8.199999999999999</v>
-      </c>
-      <c r="BZ3">
-        <v>1000</v>
-      </c>
-      <c r="CA3">
-        <v>8</v>
       </c>
       <c r="CB3" t="s">
         <v>96</v>
@@ -1382,7 +1382,7 @@
         <v>94</v>
       </c>
       <c r="F4">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="G4">
         <v>1.82</v>
@@ -1394,10 +1394,10 @@
         <v>5.5</v>
       </c>
       <c r="J4">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K4">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="L4">
         <v>1.29</v>
@@ -1415,10 +1415,10 @@
         <v>2.3</v>
       </c>
       <c r="Q4">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="R4">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="S4">
         <v>2.62</v>
@@ -1475,7 +1475,7 @@
         <v>21</v>
       </c>
       <c r="AK4">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AL4">
         <v>34</v>
@@ -1490,7 +1490,7 @@
         <v>65</v>
       </c>
       <c r="AP4">
-        <v>14</v>
+        <v>17.5</v>
       </c>
       <c r="AQ4">
         <v>16.5</v>
@@ -1505,19 +1505,19 @@
         <v>8.4</v>
       </c>
       <c r="AU4">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="AV4">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="AW4">
         <v>6.2</v>
       </c>
       <c r="AX4">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AY4">
-        <v>8.6</v>
+        <v>7.8</v>
       </c>
       <c r="AZ4">
         <v>13</v>
@@ -1526,10 +1526,10 @@
         <v>6.2</v>
       </c>
       <c r="BB4">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="BC4">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BD4">
         <v>5.7</v>
@@ -1553,16 +1553,16 @@
         <v>10</v>
       </c>
       <c r="BK4">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BN4">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BO4">
         <v>3.65</v>
@@ -1571,37 +1571,37 @@
         <v>12</v>
       </c>
       <c r="BQ4">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="BR4">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="BS4">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BT4">
         <v>9</v>
       </c>
       <c r="BU4">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BV4">
         <v>1000</v>
       </c>
       <c r="BW4">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX4">
         <v>1000</v>
       </c>
       <c r="BY4">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BZ4">
         <v>18</v>
       </c>
       <c r="CA4">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="CB4" t="s">
         <v>96</v>
@@ -1630,13 +1630,13 @@
         <v>2.34</v>
       </c>
       <c r="H5">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="I5">
         <v>4.2</v>
       </c>
       <c r="J5">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="K5">
         <v>3.6</v>
@@ -1651,16 +1651,16 @@
         <v>3.2</v>
       </c>
       <c r="O5">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="P5">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="Q5">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="R5">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="S5">
         <v>4</v>
@@ -1675,7 +1675,7 @@
         <v>1.31</v>
       </c>
       <c r="W5">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="X5">
         <v>14</v>
@@ -1732,19 +1732,19 @@
         <v>65</v>
       </c>
       <c r="AP5">
-        <v>8.800000000000001</v>
+        <v>5.6</v>
       </c>
       <c r="AQ5">
         <v>9.199999999999999</v>
       </c>
       <c r="AR5">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="AS5">
         <v>8.4</v>
       </c>
       <c r="AT5">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AU5">
         <v>6.6</v>
@@ -1756,31 +1756,31 @@
         <v>36</v>
       </c>
       <c r="AX5">
-        <v>11.5</v>
+        <v>5.6</v>
       </c>
       <c r="AY5">
         <v>8.199999999999999</v>
       </c>
       <c r="AZ5">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BA5">
         <v>8.199999999999999</v>
       </c>
       <c r="BB5">
-        <v>7.2</v>
+        <v>21</v>
       </c>
       <c r="BC5">
         <v>7</v>
       </c>
       <c r="BD5">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="BE5">
         <v>8.800000000000001</v>
       </c>
       <c r="BF5">
-        <v>18.5</v>
+        <v>6.6</v>
       </c>
       <c r="BG5">
         <v>8.199999999999999</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-06.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-06.xlsx
@@ -304,7 +304,7 @@
     <t>America de Cali S.A</t>
   </si>
   <si>
-    <t>2026-08-04 11:09:02</t>
+    <t>2026-08-04 13:15:54</t>
   </si>
 </sst>
 </file>
@@ -898,16 +898,16 @@
         <v>92</v>
       </c>
       <c r="F2">
-        <v>2.64</v>
+        <v>2.68</v>
       </c>
       <c r="G2">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="H2">
         <v>3.35</v>
       </c>
       <c r="I2">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="J2">
         <v>2.96</v>
@@ -916,28 +916,28 @@
         <v>2.98</v>
       </c>
       <c r="L2">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="M2">
         <v>1.18</v>
       </c>
       <c r="N2">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="O2">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="P2">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="Q2">
         <v>3.3</v>
       </c>
       <c r="R2">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="S2">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="T2">
         <v>2.48</v>
@@ -955,10 +955,10 @@
         <v>6.8</v>
       </c>
       <c r="Y2">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Z2">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AA2">
         <v>80</v>
@@ -970,7 +970,7 @@
         <v>7.2</v>
       </c>
       <c r="AD2">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AE2">
         <v>75</v>
@@ -982,7 +982,7 @@
         <v>15.5</v>
       </c>
       <c r="AH2">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AI2">
         <v>1000</v>
@@ -1006,10 +1006,10 @@
         <v>1000</v>
       </c>
       <c r="AP2">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="AQ2">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AR2">
         <v>18</v>
@@ -1018,7 +1018,7 @@
         <v>32</v>
       </c>
       <c r="AT2">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AU2">
         <v>6.6</v>
@@ -1087,7 +1087,7 @@
         <v>28</v>
       </c>
       <c r="BQ2">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BR2">
         <v>1000</v>
@@ -1111,10 +1111,10 @@
         <v>1000</v>
       </c>
       <c r="BY2">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ2">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="CA2">
         <v>10</v>
@@ -1149,7 +1149,7 @@
         <v>2.6</v>
       </c>
       <c r="I3">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="J3">
         <v>3.2</v>
@@ -1236,7 +1236,7 @@
         <v>44</v>
       </c>
       <c r="AL3">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AM3">
         <v>130</v>
@@ -1251,16 +1251,16 @@
         <v>9</v>
       </c>
       <c r="AQ3">
-        <v>7.2</v>
+        <v>8.6</v>
       </c>
       <c r="AR3">
         <v>13</v>
       </c>
       <c r="AS3">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AT3">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AU3">
         <v>5.7</v>
@@ -1269,7 +1269,7 @@
         <v>9.4</v>
       </c>
       <c r="AW3">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AX3">
         <v>14</v>
@@ -1287,19 +1287,19 @@
         <v>5.4</v>
       </c>
       <c r="BC3">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BD3">
         <v>5.4</v>
       </c>
       <c r="BE3">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BF3">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BG3">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BH3">
         <v>3.25</v>
@@ -1382,22 +1382,22 @@
         <v>94</v>
       </c>
       <c r="F4">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="G4">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="H4">
         <v>4.7</v>
       </c>
       <c r="I4">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="J4">
         <v>4.1</v>
       </c>
       <c r="K4">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="L4">
         <v>1.29</v>
@@ -1406,7 +1406,7 @@
         <v>1.04</v>
       </c>
       <c r="N4">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="O4">
         <v>1.22</v>
@@ -1415,13 +1415,13 @@
         <v>2.3</v>
       </c>
       <c r="Q4">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="R4">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="S4">
-        <v>2.62</v>
+        <v>2.58</v>
       </c>
       <c r="T4">
         <v>1.67</v>
@@ -1624,25 +1624,25 @@
         <v>95</v>
       </c>
       <c r="F5">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="G5">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="H5">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="I5">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="J5">
         <v>3.25</v>
       </c>
       <c r="K5">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="L5">
-        <v>1.38</v>
+        <v>1.45</v>
       </c>
       <c r="M5">
         <v>1.09</v>
@@ -1672,10 +1672,10 @@
         <v>1.96</v>
       </c>
       <c r="V5">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="W5">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="X5">
         <v>14</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-06.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-06.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="101">
   <si>
     <t>League</t>
   </si>
@@ -256,6 +256,9 @@
     <t>SnapshotTS</t>
   </si>
   <si>
+    <t>Bolivian Liga de Futbol Profesional</t>
+  </si>
+  <si>
     <t>Argentinian Primera Division</t>
   </si>
   <si>
@@ -268,6 +271,9 @@
     <t>2026-08-06</t>
   </si>
   <si>
+    <t>00:00:00</t>
+  </si>
+  <si>
     <t>00:15:00</t>
   </si>
   <si>
@@ -280,6 +286,9 @@
     <t>01:30:00</t>
   </si>
   <si>
+    <t>Bolivar</t>
+  </si>
+  <si>
     <t>Tigre</t>
   </si>
   <si>
@@ -292,6 +301,9 @@
     <t>Once Caldas</t>
   </si>
   <si>
+    <t>Oriente Petrolero</t>
+  </si>
+  <si>
     <t>Belgrano</t>
   </si>
   <si>
@@ -304,7 +316,7 @@
     <t>America de Cali S.A</t>
   </si>
   <si>
-    <t>2026-08-04 13:15:54</t>
+    <t>2026-08-04 15:22:38</t>
   </si>
 </sst>
 </file>
@@ -636,7 +648,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB5"/>
+  <dimension ref="A1:CB6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -886,241 +898,241 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D2" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="E2" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="F2">
-        <v>2.68</v>
+        <v>1.04</v>
       </c>
       <c r="G2">
-        <v>2.76</v>
+        <v>1.26</v>
       </c>
       <c r="H2">
-        <v>3.35</v>
+        <v>1.04</v>
       </c>
       <c r="I2">
-        <v>3.5</v>
+        <v>1000</v>
       </c>
       <c r="J2">
-        <v>2.96</v>
+        <v>1.01</v>
       </c>
       <c r="K2">
-        <v>2.98</v>
+        <v>950</v>
       </c>
       <c r="L2">
-        <v>1.7</v>
+        <v>1.01</v>
       </c>
       <c r="M2">
-        <v>1.18</v>
+        <v>1.01</v>
       </c>
       <c r="N2">
-        <v>2.26</v>
+        <v>1.71</v>
       </c>
       <c r="O2">
-        <v>1.75</v>
+        <v>1.03</v>
       </c>
       <c r="P2">
-        <v>1.39</v>
+        <v>1.71</v>
       </c>
       <c r="Q2">
-        <v>3.3</v>
+        <v>1.03</v>
       </c>
       <c r="R2">
-        <v>1.13</v>
+        <v>1.71</v>
       </c>
       <c r="S2">
-        <v>8</v>
+        <v>1.02</v>
       </c>
       <c r="T2">
-        <v>2.48</v>
+        <v>1.01</v>
       </c>
       <c r="U2">
-        <v>1.61</v>
+        <v>1.01</v>
       </c>
       <c r="V2">
-        <v>1.4</v>
+        <v>1.01</v>
       </c>
       <c r="W2">
-        <v>1.57</v>
+        <v>1.01</v>
       </c>
       <c r="X2">
-        <v>6.8</v>
+        <v>1000</v>
       </c>
       <c r="Y2">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="Z2">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AA2">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AB2">
-        <v>6.8</v>
+        <v>1000</v>
       </c>
       <c r="AC2">
-        <v>7.2</v>
+        <v>1000</v>
       </c>
       <c r="AD2">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AE2">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AF2">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AG2">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AH2">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AI2">
         <v>1000</v>
       </c>
       <c r="AJ2">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AK2">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AL2">
         <v>1000</v>
       </c>
       <c r="AM2">
-        <v>310</v>
+        <v>1000</v>
       </c>
       <c r="AN2">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AO2">
         <v>1000</v>
       </c>
       <c r="AP2">
-        <v>5.9</v>
+        <v>1.01</v>
       </c>
       <c r="AQ2">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="AR2">
-        <v>18</v>
+        <v>1.01</v>
       </c>
       <c r="AS2">
-        <v>32</v>
+        <v>1.01</v>
       </c>
       <c r="AT2">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="AU2">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="AV2">
-        <v>15.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW2">
-        <v>30</v>
+        <v>1.01</v>
       </c>
       <c r="AX2">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="AY2">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="AZ2">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BA2">
-        <v>42</v>
+        <v>1.01</v>
       </c>
       <c r="BB2">
-        <v>25</v>
+        <v>1.01</v>
       </c>
       <c r="BC2">
-        <v>26</v>
+        <v>1.01</v>
       </c>
       <c r="BD2">
-        <v>38</v>
+        <v>1.01</v>
       </c>
       <c r="BE2">
-        <v>55</v>
+        <v>1.01</v>
       </c>
       <c r="BF2">
-        <v>30</v>
+        <v>1.01</v>
       </c>
       <c r="BG2">
-        <v>36</v>
+        <v>1.01</v>
       </c>
       <c r="BH2">
-        <v>2.52</v>
+        <v>1000</v>
       </c>
       <c r="BI2">
-        <v>2.08</v>
+        <v>1.01</v>
       </c>
       <c r="BJ2">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="BK2">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="BN2">
-        <v>5.6</v>
+        <v>1000</v>
       </c>
       <c r="BO2">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="BP2">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="BQ2">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="BR2">
         <v>1000</v>
       </c>
       <c r="BS2">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="BT2">
-        <v>6.6</v>
+        <v>1000</v>
       </c>
       <c r="BU2">
-        <v>5.4</v>
+        <v>1.01</v>
       </c>
       <c r="BV2">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="BW2">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BX2">
         <v>1000</v>
       </c>
       <c r="BY2">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BZ2">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="CA2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="CB2" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1128,468 +1140,468 @@
         <v>81</v>
       </c>
       <c r="B3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D3" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E3" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="F3">
-        <v>2.82</v>
+        <v>2.68</v>
       </c>
       <c r="G3">
-        <v>3.15</v>
+        <v>2.72</v>
       </c>
       <c r="H3">
-        <v>2.6</v>
+        <v>3.4</v>
       </c>
       <c r="I3">
-        <v>2.94</v>
+        <v>3.5</v>
       </c>
       <c r="J3">
-        <v>3.2</v>
+        <v>2.96</v>
       </c>
       <c r="K3">
-        <v>3.55</v>
+        <v>2.98</v>
       </c>
       <c r="L3">
-        <v>1.44</v>
+        <v>1.67</v>
       </c>
       <c r="M3">
-        <v>1.09</v>
+        <v>1.18</v>
       </c>
       <c r="N3">
-        <v>3.2</v>
+        <v>2.24</v>
       </c>
       <c r="O3">
-        <v>1.38</v>
+        <v>1.75</v>
       </c>
       <c r="P3">
-        <v>1.75</v>
+        <v>1.39</v>
       </c>
       <c r="Q3">
-        <v>2.12</v>
+        <v>3.3</v>
       </c>
       <c r="R3">
-        <v>1.28</v>
+        <v>1.13</v>
       </c>
       <c r="S3">
-        <v>3.9</v>
+        <v>7.6</v>
       </c>
       <c r="T3">
-        <v>1.83</v>
+        <v>2.48</v>
       </c>
       <c r="U3">
-        <v>2</v>
+        <v>1.61</v>
       </c>
       <c r="V3">
-        <v>1.52</v>
+        <v>1.4</v>
       </c>
       <c r="W3">
-        <v>1.46</v>
+        <v>1.58</v>
       </c>
       <c r="X3">
-        <v>14</v>
+        <v>6.8</v>
       </c>
       <c r="Y3">
-        <v>12</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Z3">
+        <v>21</v>
+      </c>
+      <c r="AA3">
+        <v>80</v>
+      </c>
+      <c r="AB3">
+        <v>6.8</v>
+      </c>
+      <c r="AC3">
+        <v>7.2</v>
+      </c>
+      <c r="AD3">
+        <v>18.5</v>
+      </c>
+      <c r="AE3">
+        <v>75</v>
+      </c>
+      <c r="AF3">
+        <v>15</v>
+      </c>
+      <c r="AG3">
+        <v>15.5</v>
+      </c>
+      <c r="AH3">
+        <v>30</v>
+      </c>
+      <c r="AI3">
+        <v>1000</v>
+      </c>
+      <c r="AJ3">
+        <v>48</v>
+      </c>
+      <c r="AK3">
+        <v>55</v>
+      </c>
+      <c r="AL3">
+        <v>1000</v>
+      </c>
+      <c r="AM3">
+        <v>310</v>
+      </c>
+      <c r="AN3">
+        <v>65</v>
+      </c>
+      <c r="AO3">
+        <v>1000</v>
+      </c>
+      <c r="AP3">
+        <v>5.9</v>
+      </c>
+      <c r="AQ3">
+        <v>7.6</v>
+      </c>
+      <c r="AR3">
         <v>18</v>
       </c>
-      <c r="AA3">
+      <c r="AS3">
+        <v>32</v>
+      </c>
+      <c r="AT3">
+        <v>6.4</v>
+      </c>
+      <c r="AU3">
+        <v>6.6</v>
+      </c>
+      <c r="AV3">
+        <v>15.5</v>
+      </c>
+      <c r="AW3">
+        <v>32</v>
+      </c>
+      <c r="AX3">
+        <v>13</v>
+      </c>
+      <c r="AY3">
+        <v>13</v>
+      </c>
+      <c r="AZ3">
+        <v>25</v>
+      </c>
+      <c r="BA3">
+        <v>42</v>
+      </c>
+      <c r="BB3">
+        <v>25</v>
+      </c>
+      <c r="BC3">
+        <v>26</v>
+      </c>
+      <c r="BD3">
+        <v>38</v>
+      </c>
+      <c r="BE3">
         <v>55</v>
       </c>
-      <c r="AB3">
+      <c r="BF3">
+        <v>30</v>
+      </c>
+      <c r="BG3">
+        <v>36</v>
+      </c>
+      <c r="BH3">
+        <v>2.52</v>
+      </c>
+      <c r="BI3">
+        <v>2.08</v>
+      </c>
+      <c r="BJ3">
+        <v>13</v>
+      </c>
+      <c r="BK3">
+        <v>9.6</v>
+      </c>
+      <c r="BL3">
+        <v>1000</v>
+      </c>
+      <c r="BM3">
         <v>11</v>
       </c>
-      <c r="AC3">
-        <v>9</v>
-      </c>
-      <c r="AD3">
-        <v>13</v>
-      </c>
-      <c r="AE3">
-        <v>34</v>
-      </c>
-      <c r="AF3">
-        <v>23</v>
-      </c>
-      <c r="AG3">
-        <v>14</v>
-      </c>
-      <c r="AH3">
-        <v>22</v>
-      </c>
-      <c r="AI3">
-        <v>50</v>
-      </c>
-      <c r="AJ3">
-        <v>60</v>
-      </c>
-      <c r="AK3">
-        <v>44</v>
-      </c>
-      <c r="AL3">
-        <v>55</v>
-      </c>
-      <c r="AM3">
-        <v>130</v>
-      </c>
-      <c r="AN3">
-        <v>44</v>
-      </c>
-      <c r="AO3">
-        <v>34</v>
-      </c>
-      <c r="AP3">
-        <v>9</v>
-      </c>
-      <c r="AQ3">
-        <v>8.6</v>
-      </c>
-      <c r="AR3">
-        <v>13</v>
-      </c>
-      <c r="AS3">
+      <c r="BN3">
+        <v>5.6</v>
+      </c>
+      <c r="BO3">
+        <v>4.3</v>
+      </c>
+      <c r="BP3">
+        <v>28</v>
+      </c>
+      <c r="BQ3">
+        <v>8</v>
+      </c>
+      <c r="BR3">
+        <v>1000</v>
+      </c>
+      <c r="BS3">
+        <v>9.6</v>
+      </c>
+      <c r="BT3">
+        <v>6.6</v>
+      </c>
+      <c r="BU3">
         <v>5.4</v>
       </c>
-      <c r="AT3">
-        <v>8</v>
-      </c>
-      <c r="AU3">
-        <v>5.7</v>
-      </c>
-      <c r="AV3">
-        <v>9.4</v>
-      </c>
-      <c r="AW3">
-        <v>5.1</v>
-      </c>
-      <c r="AX3">
-        <v>14</v>
-      </c>
-      <c r="AY3">
+      <c r="BV3">
+        <v>38</v>
+      </c>
+      <c r="BW3">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BX3">
+        <v>1000</v>
+      </c>
+      <c r="BY3">
         <v>9.800000000000001</v>
       </c>
-      <c r="AZ3">
-        <v>13.5</v>
-      </c>
-      <c r="BA3">
-        <v>5.3</v>
-      </c>
-      <c r="BB3">
-        <v>5.4</v>
-      </c>
-      <c r="BC3">
-        <v>5.3</v>
-      </c>
-      <c r="BD3">
-        <v>5.4</v>
-      </c>
-      <c r="BE3">
-        <v>5.7</v>
-      </c>
-      <c r="BF3">
-        <v>5.3</v>
-      </c>
-      <c r="BG3">
-        <v>5.1</v>
-      </c>
-      <c r="BH3">
-        <v>3.25</v>
-      </c>
-      <c r="BI3">
-        <v>2.54</v>
-      </c>
-      <c r="BJ3">
-        <v>10.5</v>
-      </c>
-      <c r="BK3">
-        <v>5.3</v>
-      </c>
-      <c r="BL3">
-        <v>1000</v>
-      </c>
-      <c r="BM3">
+      <c r="BZ3">
+        <v>75</v>
+      </c>
+      <c r="CA3">
         <v>10</v>
       </c>
-      <c r="BN3">
-        <v>6.2</v>
-      </c>
-      <c r="BO3">
-        <v>4.5</v>
-      </c>
-      <c r="BP3">
-        <v>1000</v>
-      </c>
-      <c r="BQ3">
-        <v>7.6</v>
-      </c>
-      <c r="BR3">
-        <v>1000</v>
-      </c>
-      <c r="BS3">
-        <v>8.6</v>
-      </c>
-      <c r="BT3">
-        <v>5.8</v>
-      </c>
-      <c r="BU3">
-        <v>4.3</v>
-      </c>
-      <c r="BV3">
-        <v>1000</v>
-      </c>
-      <c r="BW3">
-        <v>7.2</v>
-      </c>
-      <c r="BX3">
-        <v>1000</v>
-      </c>
-      <c r="BY3">
-        <v>8.4</v>
-      </c>
-      <c r="BZ3">
-        <v>1000</v>
-      </c>
-      <c r="CA3">
-        <v>8.199999999999999</v>
-      </c>
       <c r="CB3" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
     </row>
     <row r="4" spans="1:80">
       <c r="A4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D4" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E4" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="F4">
-        <v>1.68</v>
+        <v>2.82</v>
       </c>
       <c r="G4">
-        <v>1.81</v>
+        <v>3.15</v>
       </c>
       <c r="H4">
-        <v>4.7</v>
+        <v>2.6</v>
       </c>
       <c r="I4">
-        <v>5.6</v>
+        <v>2.94</v>
       </c>
       <c r="J4">
-        <v>4.1</v>
+        <v>3.2</v>
       </c>
       <c r="K4">
-        <v>4.8</v>
+        <v>3.55</v>
       </c>
       <c r="L4">
-        <v>1.29</v>
+        <v>1.44</v>
       </c>
       <c r="M4">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="N4">
-        <v>4.7</v>
+        <v>3.2</v>
       </c>
       <c r="O4">
-        <v>1.22</v>
+        <v>1.38</v>
       </c>
       <c r="P4">
-        <v>2.3</v>
+        <v>1.75</v>
       </c>
       <c r="Q4">
-        <v>1.63</v>
+        <v>2.14</v>
       </c>
       <c r="R4">
-        <v>1.51</v>
+        <v>1.28</v>
       </c>
       <c r="S4">
-        <v>2.58</v>
+        <v>3.9</v>
       </c>
       <c r="T4">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="U4">
-        <v>2.2</v>
+        <v>2.02</v>
       </c>
       <c r="V4">
-        <v>1.22</v>
+        <v>1.52</v>
       </c>
       <c r="W4">
-        <v>2.22</v>
+        <v>1.46</v>
       </c>
       <c r="X4">
+        <v>14</v>
+      </c>
+      <c r="Y4">
+        <v>12</v>
+      </c>
+      <c r="Z4">
+        <v>18</v>
+      </c>
+      <c r="AA4">
+        <v>55</v>
+      </c>
+      <c r="AB4">
+        <v>11</v>
+      </c>
+      <c r="AC4">
+        <v>9</v>
+      </c>
+      <c r="AD4">
+        <v>13</v>
+      </c>
+      <c r="AE4">
+        <v>34</v>
+      </c>
+      <c r="AF4">
+        <v>23</v>
+      </c>
+      <c r="AG4">
+        <v>13.5</v>
+      </c>
+      <c r="AH4">
         <v>22</v>
       </c>
-      <c r="Y4">
-        <v>23</v>
-      </c>
-      <c r="Z4">
-        <v>48</v>
-      </c>
-      <c r="AA4">
+      <c r="AI4">
+        <v>50</v>
+      </c>
+      <c r="AJ4">
+        <v>60</v>
+      </c>
+      <c r="AK4">
+        <v>44</v>
+      </c>
+      <c r="AL4">
+        <v>55</v>
+      </c>
+      <c r="AM4">
         <v>130</v>
       </c>
-      <c r="AB4">
-        <v>11.5</v>
-      </c>
-      <c r="AC4">
-        <v>11</v>
-      </c>
-      <c r="AD4">
-        <v>23</v>
-      </c>
-      <c r="AE4">
-        <v>65</v>
-      </c>
-      <c r="AF4">
+      <c r="AN4">
+        <v>44</v>
+      </c>
+      <c r="AO4">
+        <v>34</v>
+      </c>
+      <c r="AP4">
+        <v>9</v>
+      </c>
+      <c r="AQ4">
+        <v>8.6</v>
+      </c>
+      <c r="AR4">
+        <v>13</v>
+      </c>
+      <c r="AS4">
+        <v>5.5</v>
+      </c>
+      <c r="AT4">
+        <v>8</v>
+      </c>
+      <c r="AU4">
+        <v>5.7</v>
+      </c>
+      <c r="AV4">
+        <v>9.4</v>
+      </c>
+      <c r="AW4">
+        <v>5.2</v>
+      </c>
+      <c r="AX4">
+        <v>14</v>
+      </c>
+      <c r="AY4">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ4">
         <v>13.5</v>
       </c>
-      <c r="AG4">
-        <v>11.5</v>
-      </c>
-      <c r="AH4">
-        <v>20</v>
-      </c>
-      <c r="AI4">
-        <v>65</v>
-      </c>
-      <c r="AJ4">
-        <v>21</v>
-      </c>
-      <c r="AK4">
-        <v>17</v>
-      </c>
-      <c r="AL4">
-        <v>34</v>
-      </c>
-      <c r="AM4">
-        <v>95</v>
-      </c>
-      <c r="AN4">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AO4">
-        <v>65</v>
-      </c>
-      <c r="AP4">
-        <v>17.5</v>
-      </c>
-      <c r="AQ4">
-        <v>16.5</v>
-      </c>
-      <c r="AR4">
-        <v>6</v>
-      </c>
-      <c r="AS4">
-        <v>6.4</v>
-      </c>
-      <c r="AT4">
-        <v>8.4</v>
-      </c>
-      <c r="AU4">
-        <v>8</v>
-      </c>
-      <c r="AV4">
-        <v>14.5</v>
-      </c>
-      <c r="AW4">
+      <c r="BA4">
+        <v>5.4</v>
+      </c>
+      <c r="BB4">
+        <v>5.5</v>
+      </c>
+      <c r="BC4">
+        <v>5.3</v>
+      </c>
+      <c r="BD4">
+        <v>5.5</v>
+      </c>
+      <c r="BE4">
+        <v>5.8</v>
+      </c>
+      <c r="BF4">
+        <v>5.3</v>
+      </c>
+      <c r="BG4">
+        <v>5.2</v>
+      </c>
+      <c r="BH4">
+        <v>3.25</v>
+      </c>
+      <c r="BI4">
+        <v>2.54</v>
+      </c>
+      <c r="BJ4">
+        <v>10.5</v>
+      </c>
+      <c r="BK4">
+        <v>5.3</v>
+      </c>
+      <c r="BL4">
+        <v>1000</v>
+      </c>
+      <c r="BM4">
+        <v>10</v>
+      </c>
+      <c r="BN4">
         <v>6.2</v>
       </c>
-      <c r="AX4">
-        <v>9.6</v>
-      </c>
-      <c r="AY4">
-        <v>7.8</v>
-      </c>
-      <c r="AZ4">
-        <v>13</v>
-      </c>
-      <c r="BA4">
-        <v>6.2</v>
-      </c>
-      <c r="BB4">
-        <v>13.5</v>
-      </c>
-      <c r="BC4">
-        <v>12.5</v>
-      </c>
-      <c r="BD4">
-        <v>5.7</v>
-      </c>
-      <c r="BE4">
-        <v>6.4</v>
-      </c>
-      <c r="BF4">
-        <v>6.8</v>
-      </c>
-      <c r="BG4">
-        <v>6.2</v>
-      </c>
-      <c r="BH4">
-        <v>4.1</v>
-      </c>
-      <c r="BI4">
-        <v>3.2</v>
-      </c>
-      <c r="BJ4">
-        <v>10</v>
-      </c>
-      <c r="BK4">
-        <v>5</v>
-      </c>
-      <c r="BL4">
-        <v>1000</v>
-      </c>
-      <c r="BM4">
-        <v>9.4</v>
-      </c>
-      <c r="BN4">
-        <v>4.7</v>
-      </c>
       <c r="BO4">
-        <v>3.65</v>
+        <v>4.5</v>
       </c>
       <c r="BP4">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="BQ4">
-        <v>5.5</v>
+        <v>7.6</v>
       </c>
       <c r="BR4">
         <v>1000</v>
       </c>
       <c r="BS4">
+        <v>8.6</v>
+      </c>
+      <c r="BT4">
+        <v>5.8</v>
+      </c>
+      <c r="BU4">
+        <v>4.3</v>
+      </c>
+      <c r="BV4">
+        <v>1000</v>
+      </c>
+      <c r="BW4">
         <v>7.2</v>
-      </c>
-      <c r="BT4">
-        <v>9</v>
-      </c>
-      <c r="BU4">
-        <v>4.8</v>
-      </c>
-      <c r="BV4">
-        <v>1000</v>
-      </c>
-      <c r="BW4">
-        <v>8.199999999999999</v>
       </c>
       <c r="BX4">
         <v>1000</v>
@@ -1598,13 +1610,13 @@
         <v>8.4</v>
       </c>
       <c r="BZ4">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="CA4">
-        <v>6.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CB4" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1612,97 +1624,97 @@
         <v>82</v>
       </c>
       <c r="B5" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D5" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E5" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="F5">
-        <v>2.16</v>
+        <v>1.68</v>
       </c>
       <c r="G5">
+        <v>1.81</v>
+      </c>
+      <c r="H5">
+        <v>4.7</v>
+      </c>
+      <c r="I5">
+        <v>5.6</v>
+      </c>
+      <c r="J5">
+        <v>4.1</v>
+      </c>
+      <c r="K5">
+        <v>4.8</v>
+      </c>
+      <c r="L5">
+        <v>1.29</v>
+      </c>
+      <c r="M5">
+        <v>1.04</v>
+      </c>
+      <c r="N5">
+        <v>4.7</v>
+      </c>
+      <c r="O5">
+        <v>1.22</v>
+      </c>
+      <c r="P5">
         <v>2.32</v>
       </c>
-      <c r="H5">
-        <v>3.6</v>
-      </c>
-      <c r="I5">
-        <v>4.1</v>
-      </c>
-      <c r="J5">
-        <v>3.25</v>
-      </c>
-      <c r="K5">
-        <v>3.55</v>
-      </c>
-      <c r="L5">
-        <v>1.45</v>
-      </c>
-      <c r="M5">
-        <v>1.09</v>
-      </c>
-      <c r="N5">
-        <v>3.2</v>
-      </c>
-      <c r="O5">
-        <v>1.4</v>
-      </c>
-      <c r="P5">
-        <v>1.74</v>
-      </c>
       <c r="Q5">
-        <v>2.14</v>
+        <v>1.63</v>
       </c>
       <c r="R5">
-        <v>1.28</v>
+        <v>1.52</v>
       </c>
       <c r="S5">
-        <v>4</v>
+        <v>2.58</v>
       </c>
       <c r="T5">
-        <v>1.86</v>
+        <v>1.67</v>
       </c>
       <c r="U5">
-        <v>1.96</v>
+        <v>2.24</v>
       </c>
       <c r="V5">
-        <v>1.32</v>
+        <v>1.22</v>
       </c>
       <c r="W5">
-        <v>1.75</v>
+        <v>2.22</v>
       </c>
       <c r="X5">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="Y5">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="Z5">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="AA5">
-        <v>85</v>
+        <v>130</v>
       </c>
       <c r="AB5">
-        <v>8.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="AC5">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AD5">
-        <v>16.5</v>
+        <v>23</v>
       </c>
       <c r="AE5">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AF5">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AG5">
         <v>11.5</v>
@@ -1714,124 +1726,124 @@
         <v>65</v>
       </c>
       <c r="AJ5">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="AK5">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="AL5">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="AM5">
-        <v>150</v>
+        <v>90</v>
       </c>
       <c r="AN5">
-        <v>23</v>
+        <v>8.6</v>
       </c>
       <c r="AO5">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AP5">
-        <v>5.6</v>
+        <v>17.5</v>
       </c>
       <c r="AQ5">
-        <v>9.199999999999999</v>
+        <v>16.5</v>
       </c>
       <c r="AR5">
-        <v>7</v>
+        <v>6.2</v>
       </c>
       <c r="AS5">
+        <v>6.6</v>
+      </c>
+      <c r="AT5">
         <v>8.4</v>
       </c>
-      <c r="AT5">
-        <v>7.4</v>
-      </c>
       <c r="AU5">
+        <v>8</v>
+      </c>
+      <c r="AV5">
+        <v>14.5</v>
+      </c>
+      <c r="AW5">
+        <v>6.4</v>
+      </c>
+      <c r="AX5">
+        <v>9.6</v>
+      </c>
+      <c r="AY5">
+        <v>7.8</v>
+      </c>
+      <c r="AZ5">
+        <v>13</v>
+      </c>
+      <c r="BA5">
+        <v>6.4</v>
+      </c>
+      <c r="BB5">
+        <v>13.5</v>
+      </c>
+      <c r="BC5">
+        <v>12.5</v>
+      </c>
+      <c r="BD5">
+        <v>5.9</v>
+      </c>
+      <c r="BE5">
         <v>6.6</v>
       </c>
-      <c r="AV5">
-        <v>11.5</v>
-      </c>
-      <c r="AW5">
-        <v>36</v>
-      </c>
-      <c r="AX5">
-        <v>5.6</v>
-      </c>
-      <c r="AY5">
+      <c r="BF5">
+        <v>6.8</v>
+      </c>
+      <c r="BG5">
+        <v>6.4</v>
+      </c>
+      <c r="BH5">
+        <v>4.1</v>
+      </c>
+      <c r="BI5">
+        <v>3.2</v>
+      </c>
+      <c r="BJ5">
+        <v>10</v>
+      </c>
+      <c r="BK5">
+        <v>5</v>
+      </c>
+      <c r="BL5">
+        <v>1000</v>
+      </c>
+      <c r="BM5">
+        <v>9.4</v>
+      </c>
+      <c r="BN5">
+        <v>4.7</v>
+      </c>
+      <c r="BO5">
+        <v>3.65</v>
+      </c>
+      <c r="BP5">
+        <v>12</v>
+      </c>
+      <c r="BQ5">
+        <v>5.5</v>
+      </c>
+      <c r="BR5">
+        <v>1000</v>
+      </c>
+      <c r="BS5">
+        <v>7.2</v>
+      </c>
+      <c r="BT5">
+        <v>9</v>
+      </c>
+      <c r="BU5">
+        <v>4.8</v>
+      </c>
+      <c r="BV5">
+        <v>1000</v>
+      </c>
+      <c r="BW5">
         <v>8.199999999999999</v>
-      </c>
-      <c r="AZ5">
-        <v>16.5</v>
-      </c>
-      <c r="BA5">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BB5">
-        <v>21</v>
-      </c>
-      <c r="BC5">
-        <v>7</v>
-      </c>
-      <c r="BD5">
-        <v>30</v>
-      </c>
-      <c r="BE5">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BF5">
-        <v>6.6</v>
-      </c>
-      <c r="BG5">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BH5">
-        <v>3.25</v>
-      </c>
-      <c r="BI5">
-        <v>2.52</v>
-      </c>
-      <c r="BJ5">
-        <v>10.5</v>
-      </c>
-      <c r="BK5">
-        <v>5.1</v>
-      </c>
-      <c r="BL5">
-        <v>1000</v>
-      </c>
-      <c r="BM5">
-        <v>9.6</v>
-      </c>
-      <c r="BN5">
-        <v>5.1</v>
-      </c>
-      <c r="BO5">
-        <v>3.75</v>
-      </c>
-      <c r="BP5">
-        <v>17.5</v>
-      </c>
-      <c r="BQ5">
-        <v>6.4</v>
-      </c>
-      <c r="BR5">
-        <v>36</v>
-      </c>
-      <c r="BS5">
-        <v>8</v>
-      </c>
-      <c r="BT5">
-        <v>7.4</v>
-      </c>
-      <c r="BU5">
-        <v>5.3</v>
-      </c>
-      <c r="BV5">
-        <v>1000</v>
-      </c>
-      <c r="BW5">
-        <v>8</v>
       </c>
       <c r="BX5">
         <v>1000</v>
@@ -1840,13 +1852,255 @@
         <v>8.4</v>
       </c>
       <c r="BZ5">
+        <v>18</v>
+      </c>
+      <c r="CA5">
+        <v>6.4</v>
+      </c>
+      <c r="CB5" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="6" spans="1:80">
+      <c r="A6" t="s">
+        <v>83</v>
+      </c>
+      <c r="B6" t="s">
+        <v>84</v>
+      </c>
+      <c r="C6" t="s">
+        <v>89</v>
+      </c>
+      <c r="D6" t="s">
+        <v>94</v>
+      </c>
+      <c r="E6" t="s">
+        <v>99</v>
+      </c>
+      <c r="F6">
+        <v>2.14</v>
+      </c>
+      <c r="G6">
+        <v>2.32</v>
+      </c>
+      <c r="H6">
+        <v>3.6</v>
+      </c>
+      <c r="I6">
+        <v>4.1</v>
+      </c>
+      <c r="J6">
+        <v>3.25</v>
+      </c>
+      <c r="K6">
+        <v>3.55</v>
+      </c>
+      <c r="L6">
+        <v>1.45</v>
+      </c>
+      <c r="M6">
+        <v>1.09</v>
+      </c>
+      <c r="N6">
+        <v>3.2</v>
+      </c>
+      <c r="O6">
+        <v>1.4</v>
+      </c>
+      <c r="P6">
+        <v>1.74</v>
+      </c>
+      <c r="Q6">
+        <v>2.14</v>
+      </c>
+      <c r="R6">
+        <v>1.28</v>
+      </c>
+      <c r="S6">
+        <v>4</v>
+      </c>
+      <c r="T6">
+        <v>1.87</v>
+      </c>
+      <c r="U6">
+        <v>1.96</v>
+      </c>
+      <c r="V6">
+        <v>1.32</v>
+      </c>
+      <c r="W6">
+        <v>1.75</v>
+      </c>
+      <c r="X6">
+        <v>14</v>
+      </c>
+      <c r="Y6">
+        <v>13</v>
+      </c>
+      <c r="Z6">
+        <v>28</v>
+      </c>
+      <c r="AA6">
+        <v>85</v>
+      </c>
+      <c r="AB6">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AC6">
+        <v>8</v>
+      </c>
+      <c r="AD6">
+        <v>16.5</v>
+      </c>
+      <c r="AE6">
+        <v>55</v>
+      </c>
+      <c r="AF6">
+        <v>14</v>
+      </c>
+      <c r="AG6">
+        <v>11.5</v>
+      </c>
+      <c r="AH6">
+        <v>20</v>
+      </c>
+      <c r="AI6">
+        <v>65</v>
+      </c>
+      <c r="AJ6">
+        <v>30</v>
+      </c>
+      <c r="AK6">
+        <v>27</v>
+      </c>
+      <c r="AL6">
+        <v>46</v>
+      </c>
+      <c r="AM6">
+        <v>150</v>
+      </c>
+      <c r="AN6">
+        <v>23</v>
+      </c>
+      <c r="AO6">
+        <v>65</v>
+      </c>
+      <c r="AP6">
+        <v>5.6</v>
+      </c>
+      <c r="AQ6">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AR6">
+        <v>7</v>
+      </c>
+      <c r="AS6">
+        <v>8.4</v>
+      </c>
+      <c r="AT6">
+        <v>7.4</v>
+      </c>
+      <c r="AU6">
+        <v>6.6</v>
+      </c>
+      <c r="AV6">
+        <v>11.5</v>
+      </c>
+      <c r="AW6">
+        <v>36</v>
+      </c>
+      <c r="AX6">
+        <v>5.6</v>
+      </c>
+      <c r="AY6">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AZ6">
+        <v>16.5</v>
+      </c>
+      <c r="BA6">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BB6">
+        <v>21</v>
+      </c>
+      <c r="BC6">
+        <v>7</v>
+      </c>
+      <c r="BD6">
+        <v>30</v>
+      </c>
+      <c r="BE6">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BF6">
+        <v>6.6</v>
+      </c>
+      <c r="BG6">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BH6">
+        <v>3.25</v>
+      </c>
+      <c r="BI6">
+        <v>2.52</v>
+      </c>
+      <c r="BJ6">
+        <v>10.5</v>
+      </c>
+      <c r="BK6">
+        <v>5.1</v>
+      </c>
+      <c r="BL6">
+        <v>1000</v>
+      </c>
+      <c r="BM6">
+        <v>9.6</v>
+      </c>
+      <c r="BN6">
+        <v>5.1</v>
+      </c>
+      <c r="BO6">
+        <v>4.2</v>
+      </c>
+      <c r="BP6">
+        <v>17.5</v>
+      </c>
+      <c r="BQ6">
+        <v>6.4</v>
+      </c>
+      <c r="BR6">
+        <v>36</v>
+      </c>
+      <c r="BS6">
+        <v>8</v>
+      </c>
+      <c r="BT6">
+        <v>7.4</v>
+      </c>
+      <c r="BU6">
+        <v>5.3</v>
+      </c>
+      <c r="BV6">
+        <v>1000</v>
+      </c>
+      <c r="BW6">
+        <v>8</v>
+      </c>
+      <c r="BX6">
+        <v>1000</v>
+      </c>
+      <c r="BY6">
+        <v>8.4</v>
+      </c>
+      <c r="BZ6">
         <v>34</v>
       </c>
-      <c r="CA5">
+      <c r="CA6">
         <v>7.8</v>
       </c>
-      <c r="CB5" t="s">
-        <v>96</v>
+      <c r="CB6" t="s">
+        <v>100</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-06.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-06.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="109">
   <si>
     <t>League</t>
   </si>
@@ -268,6 +268,12 @@
     <t>Colombian Primera A</t>
   </si>
   <si>
+    <t>Colombian Primera B</t>
+  </si>
+  <si>
+    <t>Icelandic 1 Deild</t>
+  </si>
+  <si>
     <t>2026-08-06</t>
   </si>
   <si>
@@ -286,6 +292,12 @@
     <t>01:30:00</t>
   </si>
   <si>
+    <t>19:00:00</t>
+  </si>
+  <si>
+    <t>19:15:00</t>
+  </si>
+  <si>
     <t>Bolivar</t>
   </si>
   <si>
@@ -301,6 +313,12 @@
     <t>Once Caldas</t>
   </si>
   <si>
+    <t>Real Soacha Cundinamarca FC</t>
+  </si>
+  <si>
+    <t>IR Reykjavik</t>
+  </si>
+  <si>
     <t>Oriente Petrolero</t>
   </si>
   <si>
@@ -316,7 +334,13 @@
     <t>America de Cali S.A</t>
   </si>
   <si>
-    <t>2026-08-04 15:22:38</t>
+    <t>Boca Juniors de Cali</t>
+  </si>
+  <si>
+    <t>Aegir</t>
+  </si>
+  <si>
+    <t>2026-08-04 17:29:57</t>
   </si>
 </sst>
 </file>
@@ -648,7 +672,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB6"/>
+  <dimension ref="A1:CB8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -898,16 +922,16 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C2" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D2" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="E2" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="F2">
         <v>1.04</v>
@@ -919,7 +943,7 @@
         <v>1.04</v>
       </c>
       <c r="I2">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="J2">
         <v>1.01</v>
@@ -934,28 +958,28 @@
         <v>1.01</v>
       </c>
       <c r="N2">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="O2">
         <v>1.03</v>
       </c>
       <c r="P2">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="Q2">
         <v>1.03</v>
       </c>
       <c r="R2">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="S2">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="T2">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U2">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V2">
         <v>1.01</v>
@@ -1132,7 +1156,7 @@
         <v>0</v>
       </c>
       <c r="CB2" t="s">
-        <v>100</v>
+        <v>108</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1140,16 +1164,16 @@
         <v>81</v>
       </c>
       <c r="B3" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C3" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D3" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="E3" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="F3">
         <v>2.68</v>
@@ -1158,7 +1182,7 @@
         <v>2.72</v>
       </c>
       <c r="H3">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="I3">
         <v>3.5</v>
@@ -1176,19 +1200,19 @@
         <v>1.18</v>
       </c>
       <c r="N3">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="O3">
         <v>1.75</v>
       </c>
       <c r="P3">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="Q3">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="R3">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="S3">
         <v>7.6</v>
@@ -1221,7 +1245,7 @@
         <v>6.8</v>
       </c>
       <c r="AC3">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AD3">
         <v>18.5</v>
@@ -1263,7 +1287,7 @@
         <v>5.9</v>
       </c>
       <c r="AQ3">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AR3">
         <v>18</v>
@@ -1272,7 +1296,7 @@
         <v>32</v>
       </c>
       <c r="AT3">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AU3">
         <v>6.6</v>
@@ -1314,7 +1338,7 @@
         <v>36</v>
       </c>
       <c r="BH3">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="BI3">
         <v>2.08</v>
@@ -1338,16 +1362,16 @@
         <v>4.3</v>
       </c>
       <c r="BP3">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BQ3">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BR3">
         <v>1000</v>
       </c>
       <c r="BS3">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BT3">
         <v>6.6</v>
@@ -1359,13 +1383,13 @@
         <v>38</v>
       </c>
       <c r="BW3">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BX3">
         <v>1000</v>
       </c>
       <c r="BY3">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BZ3">
         <v>75</v>
@@ -1374,7 +1398,7 @@
         <v>10</v>
       </c>
       <c r="CB3" t="s">
-        <v>100</v>
+        <v>108</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1382,16 +1406,16 @@
         <v>82</v>
       </c>
       <c r="B4" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C4" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D4" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="E4" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="F4">
         <v>2.82</v>
@@ -1403,7 +1427,7 @@
         <v>2.6</v>
       </c>
       <c r="I4">
-        <v>2.94</v>
+        <v>2.9</v>
       </c>
       <c r="J4">
         <v>3.2</v>
@@ -1427,7 +1451,7 @@
         <v>1.75</v>
       </c>
       <c r="Q4">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="R4">
         <v>1.28</v>
@@ -1442,7 +1466,7 @@
         <v>2.02</v>
       </c>
       <c r="V4">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="W4">
         <v>1.46</v>
@@ -1556,22 +1580,22 @@
         <v>5.2</v>
       </c>
       <c r="BH4">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="BI4">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="BJ4">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BK4">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="BN4">
         <v>6.2</v>
@@ -1583,16 +1607,16 @@
         <v>1000</v>
       </c>
       <c r="BQ4">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="BR4">
         <v>1000</v>
       </c>
       <c r="BS4">
-        <v>8.6</v>
+        <v>9.6</v>
       </c>
       <c r="BT4">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BU4">
         <v>4.3</v>
@@ -1601,22 +1625,22 @@
         <v>1000</v>
       </c>
       <c r="BW4">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="BX4">
         <v>1000</v>
       </c>
       <c r="BY4">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="BZ4">
         <v>1000</v>
       </c>
       <c r="CA4">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CB4" t="s">
-        <v>100</v>
+        <v>108</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1624,19 +1648,19 @@
         <v>82</v>
       </c>
       <c r="B5" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C5" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D5" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="E5" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="F5">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="G5">
         <v>1.81</v>
@@ -1858,7 +1882,7 @@
         <v>6.4</v>
       </c>
       <c r="CB5" t="s">
-        <v>100</v>
+        <v>108</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -1866,19 +1890,19 @@
         <v>83</v>
       </c>
       <c r="B6" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C6" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D6" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="E6" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="F6">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="G6">
         <v>2.32</v>
@@ -1896,7 +1920,7 @@
         <v>3.55</v>
       </c>
       <c r="L6">
-        <v>1.45</v>
+        <v>1.38</v>
       </c>
       <c r="M6">
         <v>1.09</v>
@@ -1905,10 +1929,10 @@
         <v>3.2</v>
       </c>
       <c r="O6">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="P6">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="Q6">
         <v>2.14</v>
@@ -2010,7 +2034,7 @@
         <v>36</v>
       </c>
       <c r="AX6">
-        <v>5.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY6">
         <v>8.199999999999999</v>
@@ -2034,7 +2058,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BF6">
-        <v>6.6</v>
+        <v>15.5</v>
       </c>
       <c r="BG6">
         <v>8.199999999999999</v>
@@ -2049,13 +2073,13 @@
         <v>10.5</v>
       </c>
       <c r="BK6">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BL6">
         <v>1000</v>
       </c>
       <c r="BM6">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BN6">
         <v>5.1</v>
@@ -2067,40 +2091,524 @@
         <v>17.5</v>
       </c>
       <c r="BQ6">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BR6">
         <v>36</v>
       </c>
       <c r="BS6">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT6">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BU6">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BV6">
         <v>1000</v>
       </c>
       <c r="BW6">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX6">
         <v>1000</v>
       </c>
       <c r="BY6">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ6">
         <v>34</v>
       </c>
       <c r="CA6">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="CB6" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="7" spans="1:80">
+      <c r="A7" t="s">
+        <v>84</v>
+      </c>
+      <c r="B7" t="s">
+        <v>86</v>
+      </c>
+      <c r="C7" t="s">
+        <v>92</v>
+      </c>
+      <c r="D7" t="s">
+        <v>99</v>
+      </c>
+      <c r="E7" t="s">
+        <v>106</v>
+      </c>
+      <c r="F7">
+        <v>1.04</v>
+      </c>
+      <c r="G7">
+        <v>600</v>
+      </c>
+      <c r="H7">
+        <v>1.04</v>
+      </c>
+      <c r="I7">
+        <v>870</v>
+      </c>
+      <c r="J7">
+        <v>1.01</v>
+      </c>
+      <c r="K7">
+        <v>950</v>
+      </c>
+      <c r="L7">
+        <v>1.01</v>
+      </c>
+      <c r="M7">
+        <v>1.01</v>
+      </c>
+      <c r="N7">
+        <v>1.24</v>
+      </c>
+      <c r="O7">
+        <v>1.01</v>
+      </c>
+      <c r="P7">
+        <v>1.24</v>
+      </c>
+      <c r="Q7">
+        <v>1.02</v>
+      </c>
+      <c r="R7">
+        <v>1.13</v>
+      </c>
+      <c r="S7">
+        <v>1.02</v>
+      </c>
+      <c r="T7">
+        <v>1.01</v>
+      </c>
+      <c r="U7">
+        <v>1.01</v>
+      </c>
+      <c r="V7">
+        <v>1.01</v>
+      </c>
+      <c r="W7">
+        <v>1.01</v>
+      </c>
+      <c r="X7">
+        <v>1000</v>
+      </c>
+      <c r="Y7">
+        <v>1000</v>
+      </c>
+      <c r="Z7">
+        <v>1000</v>
+      </c>
+      <c r="AA7">
+        <v>1000</v>
+      </c>
+      <c r="AB7">
+        <v>1000</v>
+      </c>
+      <c r="AC7">
+        <v>1000</v>
+      </c>
+      <c r="AD7">
+        <v>1000</v>
+      </c>
+      <c r="AE7">
+        <v>1000</v>
+      </c>
+      <c r="AF7">
+        <v>1000</v>
+      </c>
+      <c r="AG7">
+        <v>1000</v>
+      </c>
+      <c r="AH7">
+        <v>1000</v>
+      </c>
+      <c r="AI7">
+        <v>1000</v>
+      </c>
+      <c r="AJ7">
+        <v>1000</v>
+      </c>
+      <c r="AK7">
+        <v>1000</v>
+      </c>
+      <c r="AL7">
+        <v>1000</v>
+      </c>
+      <c r="AM7">
+        <v>1000</v>
+      </c>
+      <c r="AN7">
+        <v>1000</v>
+      </c>
+      <c r="AO7">
+        <v>1000</v>
+      </c>
+      <c r="AP7">
+        <v>1.03</v>
+      </c>
+      <c r="AQ7">
+        <v>1.03</v>
+      </c>
+      <c r="AR7">
+        <v>1.03</v>
+      </c>
+      <c r="AS7">
+        <v>1.03</v>
+      </c>
+      <c r="AT7">
+        <v>1.03</v>
+      </c>
+      <c r="AU7">
+        <v>1.03</v>
+      </c>
+      <c r="AV7">
+        <v>1.03</v>
+      </c>
+      <c r="AW7">
+        <v>1.03</v>
+      </c>
+      <c r="AX7">
+        <v>1.03</v>
+      </c>
+      <c r="AY7">
+        <v>1.03</v>
+      </c>
+      <c r="AZ7">
+        <v>1.03</v>
+      </c>
+      <c r="BA7">
+        <v>1.03</v>
+      </c>
+      <c r="BB7">
+        <v>1.03</v>
+      </c>
+      <c r="BC7">
+        <v>1.03</v>
+      </c>
+      <c r="BD7">
+        <v>1.03</v>
+      </c>
+      <c r="BE7">
+        <v>1.03</v>
+      </c>
+      <c r="BF7">
+        <v>1.01</v>
+      </c>
+      <c r="BG7">
+        <v>1.01</v>
+      </c>
+      <c r="BH7">
+        <v>1000</v>
+      </c>
+      <c r="BI7">
+        <v>1.01</v>
+      </c>
+      <c r="BJ7">
+        <v>1000</v>
+      </c>
+      <c r="BK7">
+        <v>1.01</v>
+      </c>
+      <c r="BL7">
+        <v>1000</v>
+      </c>
+      <c r="BM7">
+        <v>1.01</v>
+      </c>
+      <c r="BN7">
+        <v>1000</v>
+      </c>
+      <c r="BO7">
+        <v>1.01</v>
+      </c>
+      <c r="BP7">
+        <v>1000</v>
+      </c>
+      <c r="BQ7">
+        <v>1.01</v>
+      </c>
+      <c r="BR7">
+        <v>1000</v>
+      </c>
+      <c r="BS7">
+        <v>1.01</v>
+      </c>
+      <c r="BT7">
+        <v>1000</v>
+      </c>
+      <c r="BU7">
+        <v>1.01</v>
+      </c>
+      <c r="BV7">
+        <v>1000</v>
+      </c>
+      <c r="BW7">
+        <v>1.01</v>
+      </c>
+      <c r="BX7">
+        <v>1000</v>
+      </c>
+      <c r="BY7">
+        <v>1.01</v>
+      </c>
+      <c r="BZ7">
+        <v>0</v>
+      </c>
+      <c r="CA7">
+        <v>0</v>
+      </c>
+      <c r="CB7" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="8" spans="1:80">
+      <c r="A8" t="s">
+        <v>85</v>
+      </c>
+      <c r="B8" t="s">
+        <v>86</v>
+      </c>
+      <c r="C8" t="s">
+        <v>93</v>
+      </c>
+      <c r="D8" t="s">
         <v>100</v>
+      </c>
+      <c r="E8" t="s">
+        <v>107</v>
+      </c>
+      <c r="F8">
+        <v>1.46</v>
+      </c>
+      <c r="G8">
+        <v>1.62</v>
+      </c>
+      <c r="H8">
+        <v>4.6</v>
+      </c>
+      <c r="I8">
+        <v>7.4</v>
+      </c>
+      <c r="J8">
+        <v>4</v>
+      </c>
+      <c r="K8">
+        <v>6.8</v>
+      </c>
+      <c r="L8">
+        <v>1.01</v>
+      </c>
+      <c r="M8">
+        <v>1.01</v>
+      </c>
+      <c r="N8">
+        <v>3.35</v>
+      </c>
+      <c r="O8">
+        <v>1.07</v>
+      </c>
+      <c r="P8">
+        <v>3.35</v>
+      </c>
+      <c r="Q8">
+        <v>1.28</v>
+      </c>
+      <c r="R8">
+        <v>1.81</v>
+      </c>
+      <c r="S8">
+        <v>1.64</v>
+      </c>
+      <c r="T8">
+        <v>1.35</v>
+      </c>
+      <c r="U8">
+        <v>2.22</v>
+      </c>
+      <c r="V8">
+        <v>1.16</v>
+      </c>
+      <c r="W8">
+        <v>2.6</v>
+      </c>
+      <c r="X8">
+        <v>1000</v>
+      </c>
+      <c r="Y8">
+        <v>1000</v>
+      </c>
+      <c r="Z8">
+        <v>1000</v>
+      </c>
+      <c r="AA8">
+        <v>1000</v>
+      </c>
+      <c r="AB8">
+        <v>26</v>
+      </c>
+      <c r="AC8">
+        <v>20</v>
+      </c>
+      <c r="AD8">
+        <v>32</v>
+      </c>
+      <c r="AE8">
+        <v>1000</v>
+      </c>
+      <c r="AF8">
+        <v>21</v>
+      </c>
+      <c r="AG8">
+        <v>16</v>
+      </c>
+      <c r="AH8">
+        <v>24</v>
+      </c>
+      <c r="AI8">
+        <v>1000</v>
+      </c>
+      <c r="AJ8">
+        <v>23</v>
+      </c>
+      <c r="AK8">
+        <v>20</v>
+      </c>
+      <c r="AL8">
+        <v>30</v>
+      </c>
+      <c r="AM8">
+        <v>1000</v>
+      </c>
+      <c r="AN8">
+        <v>1000</v>
+      </c>
+      <c r="AO8">
+        <v>1000</v>
+      </c>
+      <c r="AP8">
+        <v>1.03</v>
+      </c>
+      <c r="AQ8">
+        <v>1.03</v>
+      </c>
+      <c r="AR8">
+        <v>1.03</v>
+      </c>
+      <c r="AS8">
+        <v>1.03</v>
+      </c>
+      <c r="AT8">
+        <v>1.03</v>
+      </c>
+      <c r="AU8">
+        <v>1.03</v>
+      </c>
+      <c r="AV8">
+        <v>1.03</v>
+      </c>
+      <c r="AW8">
+        <v>1.03</v>
+      </c>
+      <c r="AX8">
+        <v>1.03</v>
+      </c>
+      <c r="AY8">
+        <v>1.03</v>
+      </c>
+      <c r="AZ8">
+        <v>1.03</v>
+      </c>
+      <c r="BA8">
+        <v>1.03</v>
+      </c>
+      <c r="BB8">
+        <v>1.03</v>
+      </c>
+      <c r="BC8">
+        <v>1.03</v>
+      </c>
+      <c r="BD8">
+        <v>1.03</v>
+      </c>
+      <c r="BE8">
+        <v>1.03</v>
+      </c>
+      <c r="BF8">
+        <v>1.01</v>
+      </c>
+      <c r="BG8">
+        <v>1.01</v>
+      </c>
+      <c r="BH8">
+        <v>1000</v>
+      </c>
+      <c r="BI8">
+        <v>1.01</v>
+      </c>
+      <c r="BJ8">
+        <v>1000</v>
+      </c>
+      <c r="BK8">
+        <v>1.01</v>
+      </c>
+      <c r="BL8">
+        <v>1000</v>
+      </c>
+      <c r="BM8">
+        <v>1.01</v>
+      </c>
+      <c r="BN8">
+        <v>1000</v>
+      </c>
+      <c r="BO8">
+        <v>1.01</v>
+      </c>
+      <c r="BP8">
+        <v>1000</v>
+      </c>
+      <c r="BQ8">
+        <v>1.01</v>
+      </c>
+      <c r="BR8">
+        <v>1000</v>
+      </c>
+      <c r="BS8">
+        <v>1.01</v>
+      </c>
+      <c r="BT8">
+        <v>1000</v>
+      </c>
+      <c r="BU8">
+        <v>1.01</v>
+      </c>
+      <c r="BV8">
+        <v>1000</v>
+      </c>
+      <c r="BW8">
+        <v>1.01</v>
+      </c>
+      <c r="BX8">
+        <v>1000</v>
+      </c>
+      <c r="BY8">
+        <v>1.01</v>
+      </c>
+      <c r="BZ8">
+        <v>1000</v>
+      </c>
+      <c r="CA8">
+        <v>1.01</v>
+      </c>
+      <c r="CB8" t="s">
+        <v>108</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-06.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-06.xlsx
@@ -340,7 +340,7 @@
     <t>Aegir</t>
   </si>
   <si>
-    <t>2026-08-04 17:29:57</t>
+    <t>2026-08-04 19:37:07</t>
   </si>
 </sst>
 </file>
@@ -946,7 +946,7 @@
         <v>990</v>
       </c>
       <c r="J2">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="K2">
         <v>950</v>
@@ -964,7 +964,7 @@
         <v>1.03</v>
       </c>
       <c r="P2">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="Q2">
         <v>1.03</v>
@@ -1099,55 +1099,55 @@
         <v>1000</v>
       </c>
       <c r="BI2">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ2">
         <v>1000</v>
       </c>
       <c r="BK2">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN2">
         <v>1000</v>
       </c>
       <c r="BO2">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP2">
         <v>1000</v>
       </c>
       <c r="BQ2">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR2">
         <v>1000</v>
       </c>
       <c r="BS2">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT2">
         <v>1000</v>
       </c>
       <c r="BU2">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV2">
         <v>1000</v>
       </c>
       <c r="BW2">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX2">
         <v>1000</v>
       </c>
       <c r="BY2">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ2">
         <v>0</v>
@@ -1176,7 +1176,7 @@
         <v>102</v>
       </c>
       <c r="F3">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="G3">
         <v>2.72</v>
@@ -1191,16 +1191,16 @@
         <v>2.96</v>
       </c>
       <c r="K3">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="L3">
         <v>1.67</v>
       </c>
       <c r="M3">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="N3">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="O3">
         <v>1.75</v>
@@ -1338,7 +1338,7 @@
         <v>36</v>
       </c>
       <c r="BH3">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="BI3">
         <v>2.08</v>
@@ -1362,16 +1362,16 @@
         <v>4.3</v>
       </c>
       <c r="BP3">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BQ3">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="BR3">
         <v>1000</v>
       </c>
       <c r="BS3">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BT3">
         <v>6.6</v>
@@ -1383,13 +1383,13 @@
         <v>38</v>
       </c>
       <c r="BW3">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX3">
         <v>1000</v>
       </c>
       <c r="BY3">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ3">
         <v>75</v>
@@ -1580,22 +1580,22 @@
         <v>5.2</v>
       </c>
       <c r="BH4">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="BI4">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="BJ4">
+        <v>10.5</v>
+      </c>
+      <c r="BK4">
+        <v>5.3</v>
+      </c>
+      <c r="BL4">
+        <v>1000</v>
+      </c>
+      <c r="BM4">
         <v>10</v>
-      </c>
-      <c r="BK4">
-        <v>5.6</v>
-      </c>
-      <c r="BL4">
-        <v>1000</v>
-      </c>
-      <c r="BM4">
-        <v>11.5</v>
       </c>
       <c r="BN4">
         <v>6.2</v>
@@ -1607,16 +1607,16 @@
         <v>1000</v>
       </c>
       <c r="BQ4">
-        <v>8.4</v>
+        <v>7.6</v>
       </c>
       <c r="BR4">
         <v>1000</v>
       </c>
       <c r="BS4">
-        <v>9.6</v>
+        <v>8.6</v>
       </c>
       <c r="BT4">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BU4">
         <v>4.3</v>
@@ -1625,19 +1625,19 @@
         <v>1000</v>
       </c>
       <c r="BW4">
-        <v>8</v>
+        <v>7.2</v>
       </c>
       <c r="BX4">
         <v>1000</v>
       </c>
       <c r="BY4">
-        <v>9.6</v>
+        <v>8.4</v>
       </c>
       <c r="BZ4">
         <v>1000</v>
       </c>
       <c r="CA4">
-        <v>9.199999999999999</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CB4" t="s">
         <v>108</v>
@@ -1792,7 +1792,7 @@
         <v>6.4</v>
       </c>
       <c r="AX5">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="AY5">
         <v>7.8</v>
@@ -1902,13 +1902,13 @@
         <v>105</v>
       </c>
       <c r="F6">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="G6">
         <v>2.32</v>
       </c>
       <c r="H6">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="I6">
         <v>4.1</v>
@@ -2073,13 +2073,13 @@
         <v>10.5</v>
       </c>
       <c r="BK6">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="BL6">
         <v>1000</v>
       </c>
       <c r="BM6">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BN6">
         <v>5.1</v>
@@ -2091,37 +2091,37 @@
         <v>17.5</v>
       </c>
       <c r="BQ6">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BR6">
         <v>36</v>
       </c>
       <c r="BS6">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BT6">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BU6">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BV6">
         <v>1000</v>
       </c>
       <c r="BW6">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BX6">
         <v>1000</v>
       </c>
       <c r="BY6">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="BZ6">
         <v>34</v>
       </c>
       <c r="CA6">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="CB6" t="s">
         <v>108</v>
@@ -2144,22 +2144,22 @@
         <v>106</v>
       </c>
       <c r="F7">
-        <v>1.04</v>
+        <v>1.8</v>
       </c>
       <c r="G7">
-        <v>600</v>
+        <v>2.12</v>
       </c>
       <c r="H7">
-        <v>1.04</v>
+        <v>4.6</v>
       </c>
       <c r="I7">
-        <v>870</v>
+        <v>7.2</v>
       </c>
       <c r="J7">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="K7">
-        <v>950</v>
+        <v>3.65</v>
       </c>
       <c r="L7">
         <v>1.01</v>
@@ -2168,34 +2168,34 @@
         <v>1.01</v>
       </c>
       <c r="N7">
-        <v>1.24</v>
+        <v>2.66</v>
       </c>
       <c r="O7">
-        <v>1.01</v>
+        <v>1.47</v>
       </c>
       <c r="P7">
-        <v>1.24</v>
+        <v>1.4</v>
       </c>
       <c r="Q7">
-        <v>1.02</v>
+        <v>2.22</v>
       </c>
       <c r="R7">
         <v>1.13</v>
       </c>
       <c r="S7">
-        <v>1.02</v>
+        <v>2.68</v>
       </c>
       <c r="T7">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U7">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V7">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="W7">
-        <v>1.01</v>
+        <v>1.89</v>
       </c>
       <c r="X7">
         <v>1000</v>
@@ -2252,52 +2252,52 @@
         <v>1000</v>
       </c>
       <c r="AP7">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ7">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR7">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS7">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT7">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU7">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV7">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW7">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX7">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY7">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ7">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA7">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB7">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC7">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD7">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE7">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF7">
         <v>1.01</v>
@@ -2309,55 +2309,55 @@
         <v>1000</v>
       </c>
       <c r="BI7">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ7">
         <v>1000</v>
       </c>
       <c r="BK7">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL7">
         <v>1000</v>
       </c>
       <c r="BM7">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN7">
         <v>1000</v>
       </c>
       <c r="BO7">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP7">
         <v>1000</v>
       </c>
       <c r="BQ7">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR7">
         <v>1000</v>
       </c>
       <c r="BS7">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT7">
         <v>1000</v>
       </c>
       <c r="BU7">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV7">
         <v>1000</v>
       </c>
       <c r="BW7">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX7">
         <v>1000</v>
       </c>
       <c r="BY7">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ7">
         <v>0</v>
@@ -2386,22 +2386,22 @@
         <v>107</v>
       </c>
       <c r="F8">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="G8">
-        <v>1.62</v>
+        <v>1.68</v>
       </c>
       <c r="H8">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="I8">
         <v>7.4</v>
       </c>
       <c r="J8">
-        <v>4</v>
+        <v>4.9</v>
       </c>
       <c r="K8">
-        <v>6.8</v>
+        <v>5.8</v>
       </c>
       <c r="L8">
         <v>1.01</v>
@@ -2437,7 +2437,7 @@
         <v>1.16</v>
       </c>
       <c r="W8">
-        <v>2.6</v>
+        <v>2.46</v>
       </c>
       <c r="X8">
         <v>1000</v>
@@ -2458,7 +2458,7 @@
         <v>20</v>
       </c>
       <c r="AD8">
-        <v>32</v>
+        <v>950</v>
       </c>
       <c r="AE8">
         <v>1000</v>
@@ -2470,7 +2470,7 @@
         <v>16</v>
       </c>
       <c r="AH8">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI8">
         <v>1000</v>
@@ -2488,124 +2488,124 @@
         <v>1000</v>
       </c>
       <c r="AN8">
-        <v>1000</v>
+        <v>6</v>
       </c>
       <c r="AO8">
         <v>1000</v>
       </c>
       <c r="AP8">
-        <v>1.03</v>
+        <v>2.32</v>
       </c>
       <c r="AQ8">
-        <v>1.03</v>
+        <v>2.32</v>
       </c>
       <c r="AR8">
-        <v>1.03</v>
+        <v>2.32</v>
       </c>
       <c r="AS8">
-        <v>1.03</v>
+        <v>2.32</v>
       </c>
       <c r="AT8">
-        <v>1.03</v>
+        <v>2.12</v>
       </c>
       <c r="AU8">
-        <v>1.03</v>
+        <v>2.08</v>
       </c>
       <c r="AV8">
-        <v>1.03</v>
+        <v>2.16</v>
       </c>
       <c r="AW8">
-        <v>1.03</v>
+        <v>2.32</v>
       </c>
       <c r="AX8">
-        <v>1.03</v>
+        <v>2.08</v>
       </c>
       <c r="AY8">
-        <v>1.03</v>
+        <v>2.02</v>
       </c>
       <c r="AZ8">
-        <v>1.03</v>
+        <v>2.1</v>
       </c>
       <c r="BA8">
-        <v>1.03</v>
+        <v>2.32</v>
       </c>
       <c r="BB8">
-        <v>1.03</v>
+        <v>2.1</v>
       </c>
       <c r="BC8">
-        <v>1.03</v>
+        <v>2.08</v>
       </c>
       <c r="BD8">
-        <v>1.03</v>
+        <v>2.16</v>
       </c>
       <c r="BE8">
-        <v>1.03</v>
+        <v>2.32</v>
       </c>
       <c r="BF8">
-        <v>1.01</v>
+        <v>1.67</v>
       </c>
       <c r="BG8">
-        <v>1.01</v>
+        <v>2.32</v>
       </c>
       <c r="BH8">
         <v>1000</v>
       </c>
       <c r="BI8">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ8">
         <v>1000</v>
       </c>
       <c r="BK8">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL8">
         <v>1000</v>
       </c>
       <c r="BM8">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN8">
         <v>1000</v>
       </c>
       <c r="BO8">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP8">
         <v>1000</v>
       </c>
       <c r="BQ8">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR8">
         <v>1000</v>
       </c>
       <c r="BS8">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT8">
         <v>1000</v>
       </c>
       <c r="BU8">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV8">
         <v>1000</v>
       </c>
       <c r="BW8">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX8">
         <v>1000</v>
       </c>
       <c r="BY8">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ8">
         <v>1000</v>
       </c>
       <c r="CA8">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB8" t="s">
         <v>108</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-06.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-06.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="113">
   <si>
     <t>League</t>
   </si>
@@ -274,6 +274,9 @@
     <t>Icelandic 1 Deild</t>
   </si>
   <si>
+    <t>Venezuelan Primera Division</t>
+  </si>
+  <si>
     <t>2026-08-06</t>
   </si>
   <si>
@@ -298,6 +301,9 @@
     <t>19:15:00</t>
   </si>
   <si>
+    <t>20:00:00</t>
+  </si>
+  <si>
     <t>Bolivar</t>
   </si>
   <si>
@@ -319,6 +325,9 @@
     <t>IR Reykjavik</t>
   </si>
   <si>
+    <t>Estudiantes de Merida</t>
+  </si>
+  <si>
     <t>Oriente Petrolero</t>
   </si>
   <si>
@@ -340,7 +349,10 @@
     <t>Aegir</t>
   </si>
   <si>
-    <t>2026-08-04 19:37:07</t>
+    <t>Zamora FC</t>
+  </si>
+  <si>
+    <t>2026-08-04 21:44:26</t>
   </si>
 </sst>
 </file>
@@ -672,7 +684,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB8"/>
+  <dimension ref="A1:CB9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -922,31 +934,31 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E2" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="F2">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="G2">
         <v>1.26</v>
       </c>
       <c r="H2">
-        <v>1.04</v>
+        <v>5.6</v>
       </c>
       <c r="I2">
         <v>990</v>
       </c>
       <c r="J2">
-        <v>1.1</v>
+        <v>4.3</v>
       </c>
       <c r="K2">
         <v>950</v>
@@ -958,34 +970,34 @@
         <v>1.01</v>
       </c>
       <c r="N2">
-        <v>1.72</v>
+        <v>3.35</v>
       </c>
       <c r="O2">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="P2">
-        <v>1.71</v>
+        <v>3.3</v>
       </c>
       <c r="Q2">
-        <v>1.03</v>
+        <v>1.17</v>
       </c>
       <c r="R2">
-        <v>1.7</v>
+        <v>2.3</v>
       </c>
       <c r="S2">
-        <v>1.05</v>
+        <v>1.66</v>
       </c>
       <c r="T2">
-        <v>1.11</v>
+        <v>1.8</v>
       </c>
       <c r="U2">
-        <v>1.11</v>
+        <v>1.95</v>
       </c>
       <c r="V2">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="W2">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="X2">
         <v>1000</v>
@@ -1156,7 +1168,7 @@
         <v>0</v>
       </c>
       <c r="CB2" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1164,43 +1176,43 @@
         <v>81</v>
       </c>
       <c r="B3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D3" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E3" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="F3">
         <v>2.66</v>
       </c>
       <c r="G3">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="H3">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="I3">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="J3">
-        <v>2.96</v>
+        <v>2.9</v>
       </c>
       <c r="K3">
         <v>3</v>
       </c>
       <c r="L3">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="M3">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="N3">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="O3">
         <v>1.75</v>
@@ -1212,7 +1224,7 @@
         <v>3.25</v>
       </c>
       <c r="R3">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="S3">
         <v>7.6</v>
@@ -1224,13 +1236,13 @@
         <v>1.61</v>
       </c>
       <c r="V3">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="W3">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="X3">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="Y3">
         <v>8.199999999999999</v>
@@ -1245,58 +1257,58 @@
         <v>6.8</v>
       </c>
       <c r="AC3">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AD3">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AE3">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AF3">
+        <v>14.5</v>
+      </c>
+      <c r="AG3">
         <v>15</v>
-      </c>
-      <c r="AG3">
-        <v>15.5</v>
       </c>
       <c r="AH3">
         <v>30</v>
       </c>
       <c r="AI3">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AJ3">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AK3">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AL3">
         <v>1000</v>
       </c>
       <c r="AM3">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="AN3">
         <v>65</v>
       </c>
       <c r="AO3">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AP3">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="AQ3">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AR3">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AS3">
         <v>32</v>
       </c>
       <c r="AT3">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AU3">
         <v>6.6</v>
@@ -1305,7 +1317,7 @@
         <v>15.5</v>
       </c>
       <c r="AW3">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="AX3">
         <v>13</v>
@@ -1314,7 +1326,7 @@
         <v>13</v>
       </c>
       <c r="AZ3">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BA3">
         <v>42</v>
@@ -1323,7 +1335,7 @@
         <v>25</v>
       </c>
       <c r="BC3">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="BD3">
         <v>38</v>
@@ -1332,13 +1344,13 @@
         <v>55</v>
       </c>
       <c r="BF3">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="BG3">
         <v>36</v>
       </c>
       <c r="BH3">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="BI3">
         <v>2.08</v>
@@ -1353,7 +1365,7 @@
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BN3">
         <v>5.6</v>
@@ -1365,13 +1377,13 @@
         <v>28</v>
       </c>
       <c r="BQ3">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BR3">
         <v>1000</v>
       </c>
       <c r="BS3">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BT3">
         <v>6.6</v>
@@ -1383,13 +1395,13 @@
         <v>38</v>
       </c>
       <c r="BW3">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BX3">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="BY3">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BZ3">
         <v>75</v>
@@ -1398,7 +1410,7 @@
         <v>10</v>
       </c>
       <c r="CB3" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1406,19 +1418,19 @@
         <v>82</v>
       </c>
       <c r="B4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C4" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D4" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="E4" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="F4">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="G4">
         <v>3.15</v>
@@ -1436,7 +1448,7 @@
         <v>3.55</v>
       </c>
       <c r="L4">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="M4">
         <v>1.09</v>
@@ -1448,13 +1460,13 @@
         <v>1.38</v>
       </c>
       <c r="P4">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="Q4">
         <v>2.12</v>
       </c>
       <c r="R4">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="S4">
         <v>3.9</v>
@@ -1583,19 +1595,19 @@
         <v>3.25</v>
       </c>
       <c r="BI4">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="BJ4">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BK4">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BN4">
         <v>6.2</v>
@@ -1607,16 +1619,16 @@
         <v>1000</v>
       </c>
       <c r="BQ4">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BR4">
         <v>1000</v>
       </c>
       <c r="BS4">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT4">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BU4">
         <v>4.3</v>
@@ -1625,22 +1637,22 @@
         <v>1000</v>
       </c>
       <c r="BW4">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BX4">
         <v>1000</v>
       </c>
       <c r="BY4">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ4">
         <v>1000</v>
       </c>
       <c r="CA4">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB4" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1648,16 +1660,16 @@
         <v>82</v>
       </c>
       <c r="B5" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C5" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D5" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="E5" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="F5">
         <v>1.67</v>
@@ -1669,7 +1681,7 @@
         <v>4.7</v>
       </c>
       <c r="I5">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="J5">
         <v>4.1</v>
@@ -1690,7 +1702,7 @@
         <v>1.22</v>
       </c>
       <c r="P5">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="Q5">
         <v>1.63</v>
@@ -1882,7 +1894,7 @@
         <v>6.4</v>
       </c>
       <c r="CB5" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -1890,16 +1902,16 @@
         <v>83</v>
       </c>
       <c r="B6" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D6" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E6" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="F6">
         <v>2.14</v>
@@ -1920,7 +1932,7 @@
         <v>3.55</v>
       </c>
       <c r="L6">
-        <v>1.38</v>
+        <v>1.01</v>
       </c>
       <c r="M6">
         <v>1.09</v>
@@ -2124,7 +2136,7 @@
         <v>7.8</v>
       </c>
       <c r="CB6" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
     </row>
     <row r="7" spans="1:80">
@@ -2132,28 +2144,28 @@
         <v>84</v>
       </c>
       <c r="B7" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C7" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D7" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E7" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="F7">
         <v>1.8</v>
       </c>
       <c r="G7">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="H7">
-        <v>4.6</v>
+        <v>4</v>
       </c>
       <c r="I7">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="J7">
         <v>3.15</v>
@@ -2168,7 +2180,7 @@
         <v>1.01</v>
       </c>
       <c r="N7">
-        <v>2.66</v>
+        <v>2.06</v>
       </c>
       <c r="O7">
         <v>1.47</v>
@@ -2195,7 +2207,7 @@
         <v>1.16</v>
       </c>
       <c r="W7">
-        <v>1.89</v>
+        <v>1.83</v>
       </c>
       <c r="X7">
         <v>1000</v>
@@ -2366,7 +2378,7 @@
         <v>0</v>
       </c>
       <c r="CB7" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
     </row>
     <row r="8" spans="1:80">
@@ -2374,25 +2386,25 @@
         <v>85</v>
       </c>
       <c r="B8" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C8" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D8" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E8" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="F8">
         <v>1.47</v>
       </c>
       <c r="G8">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="H8">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="I8">
         <v>7.4</v>
@@ -2401,7 +2413,7 @@
         <v>4.9</v>
       </c>
       <c r="K8">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="L8">
         <v>1.01</v>
@@ -2437,7 +2449,7 @@
         <v>1.16</v>
       </c>
       <c r="W8">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="X8">
         <v>1000</v>
@@ -2608,7 +2620,249 @@
         <v>1.04</v>
       </c>
       <c r="CB8" t="s">
-        <v>108</v>
+        <v>112</v>
+      </c>
+    </row>
+    <row r="9" spans="1:80">
+      <c r="A9" t="s">
+        <v>86</v>
+      </c>
+      <c r="B9" t="s">
+        <v>87</v>
+      </c>
+      <c r="C9" t="s">
+        <v>95</v>
+      </c>
+      <c r="D9" t="s">
+        <v>103</v>
+      </c>
+      <c r="E9" t="s">
+        <v>111</v>
+      </c>
+      <c r="F9">
+        <v>1.04</v>
+      </c>
+      <c r="G9">
+        <v>1000</v>
+      </c>
+      <c r="H9">
+        <v>1.04</v>
+      </c>
+      <c r="I9">
+        <v>1000</v>
+      </c>
+      <c r="J9">
+        <v>1.01</v>
+      </c>
+      <c r="K9">
+        <v>1000</v>
+      </c>
+      <c r="L9">
+        <v>1.01</v>
+      </c>
+      <c r="M9">
+        <v>1.01</v>
+      </c>
+      <c r="N9">
+        <v>1.24</v>
+      </c>
+      <c r="O9">
+        <v>1.01</v>
+      </c>
+      <c r="P9">
+        <v>1.24</v>
+      </c>
+      <c r="Q9">
+        <v>1.01</v>
+      </c>
+      <c r="R9">
+        <v>1.18</v>
+      </c>
+      <c r="S9">
+        <v>1.46</v>
+      </c>
+      <c r="T9">
+        <v>1.01</v>
+      </c>
+      <c r="U9">
+        <v>1.01</v>
+      </c>
+      <c r="V9">
+        <v>1.01</v>
+      </c>
+      <c r="W9">
+        <v>1.01</v>
+      </c>
+      <c r="X9">
+        <v>1000</v>
+      </c>
+      <c r="Y9">
+        <v>1000</v>
+      </c>
+      <c r="Z9">
+        <v>1000</v>
+      </c>
+      <c r="AA9">
+        <v>1000</v>
+      </c>
+      <c r="AB9">
+        <v>1000</v>
+      </c>
+      <c r="AC9">
+        <v>1000</v>
+      </c>
+      <c r="AD9">
+        <v>1000</v>
+      </c>
+      <c r="AE9">
+        <v>1000</v>
+      </c>
+      <c r="AF9">
+        <v>1000</v>
+      </c>
+      <c r="AG9">
+        <v>1000</v>
+      </c>
+      <c r="AH9">
+        <v>1000</v>
+      </c>
+      <c r="AI9">
+        <v>1000</v>
+      </c>
+      <c r="AJ9">
+        <v>1000</v>
+      </c>
+      <c r="AK9">
+        <v>1000</v>
+      </c>
+      <c r="AL9">
+        <v>1000</v>
+      </c>
+      <c r="AM9">
+        <v>1000</v>
+      </c>
+      <c r="AN9">
+        <v>1000</v>
+      </c>
+      <c r="AO9">
+        <v>1000</v>
+      </c>
+      <c r="AP9">
+        <v>1.01</v>
+      </c>
+      <c r="AQ9">
+        <v>1.01</v>
+      </c>
+      <c r="AR9">
+        <v>1.01</v>
+      </c>
+      <c r="AS9">
+        <v>1.01</v>
+      </c>
+      <c r="AT9">
+        <v>1.01</v>
+      </c>
+      <c r="AU9">
+        <v>1.01</v>
+      </c>
+      <c r="AV9">
+        <v>1.01</v>
+      </c>
+      <c r="AW9">
+        <v>1.01</v>
+      </c>
+      <c r="AX9">
+        <v>1.01</v>
+      </c>
+      <c r="AY9">
+        <v>1.01</v>
+      </c>
+      <c r="AZ9">
+        <v>1.01</v>
+      </c>
+      <c r="BA9">
+        <v>1.01</v>
+      </c>
+      <c r="BB9">
+        <v>1.01</v>
+      </c>
+      <c r="BC9">
+        <v>1.01</v>
+      </c>
+      <c r="BD9">
+        <v>1.01</v>
+      </c>
+      <c r="BE9">
+        <v>1.01</v>
+      </c>
+      <c r="BF9">
+        <v>1.01</v>
+      </c>
+      <c r="BG9">
+        <v>1.01</v>
+      </c>
+      <c r="BH9">
+        <v>1000</v>
+      </c>
+      <c r="BI9">
+        <v>1.01</v>
+      </c>
+      <c r="BJ9">
+        <v>1000</v>
+      </c>
+      <c r="BK9">
+        <v>1.01</v>
+      </c>
+      <c r="BL9">
+        <v>1000</v>
+      </c>
+      <c r="BM9">
+        <v>1.01</v>
+      </c>
+      <c r="BN9">
+        <v>1000</v>
+      </c>
+      <c r="BO9">
+        <v>1.01</v>
+      </c>
+      <c r="BP9">
+        <v>1000</v>
+      </c>
+      <c r="BQ9">
+        <v>1.01</v>
+      </c>
+      <c r="BR9">
+        <v>1000</v>
+      </c>
+      <c r="BS9">
+        <v>1.01</v>
+      </c>
+      <c r="BT9">
+        <v>1000</v>
+      </c>
+      <c r="BU9">
+        <v>1.01</v>
+      </c>
+      <c r="BV9">
+        <v>1000</v>
+      </c>
+      <c r="BW9">
+        <v>1.01</v>
+      </c>
+      <c r="BX9">
+        <v>1000</v>
+      </c>
+      <c r="BY9">
+        <v>1.01</v>
+      </c>
+      <c r="BZ9">
+        <v>1000</v>
+      </c>
+      <c r="CA9">
+        <v>1.01</v>
+      </c>
+      <c r="CB9" t="s">
+        <v>112</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-06.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-06.xlsx
@@ -352,7 +352,7 @@
     <t>Zamora FC</t>
   </si>
   <si>
-    <t>2026-08-04 21:44:26</t>
+    <t>2026-08-04 23:50:59</t>
   </si>
 </sst>
 </file>
@@ -946,22 +946,22 @@
         <v>104</v>
       </c>
       <c r="F2">
-        <v>1.08</v>
+        <v>1.18</v>
       </c>
       <c r="G2">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="H2">
-        <v>5.6</v>
+        <v>11</v>
       </c>
       <c r="I2">
-        <v>990</v>
+        <v>19.5</v>
       </c>
       <c r="J2">
-        <v>4.3</v>
+        <v>7.8</v>
       </c>
       <c r="K2">
-        <v>950</v>
+        <v>10</v>
       </c>
       <c r="L2">
         <v>1.01</v>
@@ -970,142 +970,142 @@
         <v>1.01</v>
       </c>
       <c r="N2">
-        <v>3.35</v>
+        <v>1.1</v>
       </c>
       <c r="O2">
         <v>1.09</v>
       </c>
       <c r="P2">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="Q2">
-        <v>1.17</v>
+        <v>1.28</v>
       </c>
       <c r="R2">
-        <v>2.3</v>
+        <v>2.12</v>
       </c>
       <c r="S2">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="T2">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="U2">
-        <v>1.95</v>
+        <v>2.02</v>
       </c>
       <c r="V2">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="W2">
-        <v>4.2</v>
+        <v>5.2</v>
       </c>
       <c r="X2">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="Y2">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="Z2">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AA2">
-        <v>1000</v>
+        <v>610</v>
       </c>
       <c r="AB2">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AC2">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AD2">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AE2">
-        <v>1000</v>
+        <v>230</v>
       </c>
       <c r="AF2">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AG2">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AH2">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AI2">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AJ2">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AK2">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AL2">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AM2">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AN2">
-        <v>1000</v>
+        <v>2.82</v>
       </c>
       <c r="AO2">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AP2">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="AQ2">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AR2">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AS2">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AT2">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="AU2">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="AV2">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AW2">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AX2">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AY2">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="AZ2">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BA2">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BB2">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BC2">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BD2">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BE2">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BF2">
-        <v>1.01</v>
+        <v>2.4</v>
       </c>
       <c r="BG2">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BH2">
         <v>1000</v>
@@ -1203,22 +1203,22 @@
         <v>2.9</v>
       </c>
       <c r="K3">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="L3">
         <v>1.7</v>
       </c>
       <c r="M3">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="N3">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="O3">
         <v>1.75</v>
       </c>
       <c r="P3">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="Q3">
         <v>3.25</v>
@@ -1233,16 +1233,16 @@
         <v>2.48</v>
       </c>
       <c r="U3">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="V3">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W3">
         <v>1.57</v>
       </c>
       <c r="X3">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="Y3">
         <v>8.199999999999999</v>
@@ -1266,7 +1266,7 @@
         <v>70</v>
       </c>
       <c r="AF3">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AG3">
         <v>15</v>
@@ -1287,7 +1287,7 @@
         <v>1000</v>
       </c>
       <c r="AM3">
-        <v>300</v>
+        <v>310</v>
       </c>
       <c r="AN3">
         <v>65</v>
@@ -1299,7 +1299,7 @@
         <v>6.2</v>
       </c>
       <c r="AQ3">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AR3">
         <v>18.5</v>
@@ -1329,7 +1329,7 @@
         <v>26</v>
       </c>
       <c r="BA3">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BB3">
         <v>25</v>
@@ -1466,7 +1466,7 @@
         <v>2.12</v>
       </c>
       <c r="R4">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="S4">
         <v>3.9</v>
@@ -1544,7 +1544,7 @@
         <v>8.6</v>
       </c>
       <c r="AR4">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AS4">
         <v>5.5</v>
@@ -1556,7 +1556,7 @@
         <v>5.7</v>
       </c>
       <c r="AV4">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="AW4">
         <v>5.2</v>
@@ -1672,7 +1672,7 @@
         <v>107</v>
       </c>
       <c r="F5">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="G5">
         <v>1.81</v>
@@ -1687,7 +1687,7 @@
         <v>4.1</v>
       </c>
       <c r="K5">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="L5">
         <v>1.29</v>
@@ -1696,22 +1696,22 @@
         <v>1.04</v>
       </c>
       <c r="N5">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="O5">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="P5">
         <v>2.34</v>
       </c>
       <c r="Q5">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="R5">
         <v>1.52</v>
       </c>
       <c r="S5">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="T5">
         <v>1.67</v>
@@ -1720,7 +1720,7 @@
         <v>2.24</v>
       </c>
       <c r="V5">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="W5">
         <v>2.22</v>
@@ -1753,7 +1753,7 @@
         <v>13.5</v>
       </c>
       <c r="AG5">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AH5">
         <v>20</v>
@@ -1786,10 +1786,10 @@
         <v>16.5</v>
       </c>
       <c r="AR5">
-        <v>6.2</v>
+        <v>32</v>
       </c>
       <c r="AS5">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="AT5">
         <v>8.4</v>
@@ -1798,22 +1798,22 @@
         <v>8</v>
       </c>
       <c r="AV5">
-        <v>14.5</v>
+        <v>16.5</v>
       </c>
       <c r="AW5">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="AX5">
         <v>10.5</v>
       </c>
       <c r="AY5">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="AZ5">
         <v>13</v>
       </c>
       <c r="BA5">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="BB5">
         <v>13.5</v>
@@ -1822,22 +1822,22 @@
         <v>12.5</v>
       </c>
       <c r="BD5">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="BE5">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="BF5">
         <v>6.8</v>
       </c>
       <c r="BG5">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BH5">
         <v>4.1</v>
       </c>
       <c r="BI5">
-        <v>3.2</v>
+        <v>3.55</v>
       </c>
       <c r="BJ5">
         <v>10</v>
@@ -1849,10 +1849,10 @@
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN5">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BO5">
         <v>3.65</v>
@@ -1861,31 +1861,31 @@
         <v>12</v>
       </c>
       <c r="BQ5">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BR5">
         <v>1000</v>
       </c>
       <c r="BS5">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BT5">
         <v>9</v>
       </c>
       <c r="BU5">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BV5">
         <v>1000</v>
       </c>
       <c r="BW5">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BX5">
         <v>1000</v>
       </c>
       <c r="BY5">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="BZ5">
         <v>18</v>
@@ -1914,13 +1914,13 @@
         <v>108</v>
       </c>
       <c r="F6">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="G6">
         <v>2.32</v>
       </c>
       <c r="H6">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="I6">
         <v>4.1</v>
@@ -1929,25 +1929,25 @@
         <v>3.25</v>
       </c>
       <c r="K6">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="L6">
         <v>1.01</v>
       </c>
       <c r="M6">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N6">
         <v>3.2</v>
       </c>
       <c r="O6">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="P6">
         <v>1.75</v>
       </c>
       <c r="Q6">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="R6">
         <v>1.28</v>
@@ -1956,7 +1956,7 @@
         <v>4</v>
       </c>
       <c r="T6">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="U6">
         <v>1.96</v>
@@ -2040,7 +2040,7 @@
         <v>6.6</v>
       </c>
       <c r="AV6">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="AW6">
         <v>36</v>
@@ -2049,7 +2049,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AY6">
-        <v>8.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AZ6">
         <v>16.5</v>
@@ -2058,7 +2058,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BB6">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BC6">
         <v>7</v>
@@ -2156,7 +2156,7 @@
         <v>109</v>
       </c>
       <c r="F7">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="G7">
         <v>2.2</v>
@@ -2165,10 +2165,10 @@
         <v>4</v>
       </c>
       <c r="I7">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="J7">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="K7">
         <v>3.65</v>
@@ -2404,7 +2404,7 @@
         <v>1.69</v>
       </c>
       <c r="H8">
-        <v>4.4</v>
+        <v>3.8</v>
       </c>
       <c r="I8">
         <v>7.4</v>
@@ -2413,7 +2413,7 @@
         <v>4.9</v>
       </c>
       <c r="K8">
-        <v>5.7</v>
+        <v>6.8</v>
       </c>
       <c r="L8">
         <v>1.01</v>
@@ -2422,10 +2422,10 @@
         <v>1.01</v>
       </c>
       <c r="N8">
-        <v>3.35</v>
+        <v>1.1</v>
       </c>
       <c r="O8">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="P8">
         <v>3.35</v>
@@ -2440,10 +2440,10 @@
         <v>1.64</v>
       </c>
       <c r="T8">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="U8">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="V8">
         <v>1.16</v>
@@ -2640,22 +2640,22 @@
         <v>111</v>
       </c>
       <c r="F9">
-        <v>1.04</v>
+        <v>2.32</v>
       </c>
       <c r="G9">
-        <v>1000</v>
+        <v>3.55</v>
       </c>
       <c r="H9">
-        <v>1.04</v>
+        <v>2.46</v>
       </c>
       <c r="I9">
-        <v>1000</v>
+        <v>3.65</v>
       </c>
       <c r="J9">
-        <v>1.01</v>
+        <v>2.52</v>
       </c>
       <c r="K9">
-        <v>1000</v>
+        <v>6</v>
       </c>
       <c r="L9">
         <v>1.01</v>
@@ -2664,22 +2664,22 @@
         <v>1.01</v>
       </c>
       <c r="N9">
-        <v>1.24</v>
+        <v>2.92</v>
       </c>
       <c r="O9">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P9">
-        <v>1.24</v>
+        <v>1.61</v>
       </c>
       <c r="Q9">
-        <v>1.01</v>
+        <v>1.66</v>
       </c>
       <c r="R9">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="S9">
-        <v>1.46</v>
+        <v>3.1</v>
       </c>
       <c r="T9">
         <v>1.01</v>
@@ -2688,10 +2688,10 @@
         <v>1.01</v>
       </c>
       <c r="V9">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="W9">
-        <v>1.01</v>
+        <v>1.39</v>
       </c>
       <c r="X9">
         <v>1000</v>
@@ -2748,52 +2748,52 @@
         <v>1000</v>
       </c>
       <c r="AP9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF9">
         <v>1.01</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-06.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-06.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="128">
   <si>
     <t>League</t>
   </si>
@@ -304,6 +304,21 @@
     <t>20:00:00</t>
   </si>
   <si>
+    <t>21:00:00</t>
+  </si>
+  <si>
+    <t>21:30:00</t>
+  </si>
+  <si>
+    <t>22:00:00</t>
+  </si>
+  <si>
+    <t>23:00:00</t>
+  </si>
+  <si>
+    <t>23:30:00</t>
+  </si>
+  <si>
     <t>Bolivar</t>
   </si>
   <si>
@@ -328,6 +343,21 @@
     <t>Estudiantes de Merida</t>
   </si>
   <si>
+    <t>Atletico FC Cali</t>
+  </si>
+  <si>
+    <t>Bogota</t>
+  </si>
+  <si>
+    <t>Union Santa Fe</t>
+  </si>
+  <si>
+    <t>Orsomarso</t>
+  </si>
+  <si>
+    <t>Blooming Santa Cruz</t>
+  </si>
+  <si>
     <t>Oriente Petrolero</t>
   </si>
   <si>
@@ -352,7 +382,22 @@
     <t>Zamora FC</t>
   </si>
   <si>
-    <t>2026-08-04 23:50:59</t>
+    <t>Real Santander</t>
+  </si>
+  <si>
+    <t>Leones FC</t>
+  </si>
+  <si>
+    <t>Lanus</t>
+  </si>
+  <si>
+    <t>Tigres FC Zipaquira</t>
+  </si>
+  <si>
+    <t>Always Ready</t>
+  </si>
+  <si>
+    <t>2026-08-05 01:57:35</t>
   </si>
 </sst>
 </file>
@@ -684,7 +729,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB9"/>
+  <dimension ref="A1:CB14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -940,19 +985,19 @@
         <v>88</v>
       </c>
       <c r="D2" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="E2" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="F2">
         <v>1.18</v>
       </c>
       <c r="G2">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="H2">
-        <v>11</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I2">
         <v>19.5</v>
@@ -964,7 +1009,7 @@
         <v>10</v>
       </c>
       <c r="L2">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="M2">
         <v>1.01</v>
@@ -982,22 +1027,22 @@
         <v>1.28</v>
       </c>
       <c r="R2">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="S2">
         <v>1.69</v>
       </c>
       <c r="T2">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="U2">
-        <v>2.02</v>
+        <v>1.95</v>
       </c>
       <c r="V2">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="W2">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
       <c r="X2">
         <v>65</v>
@@ -1054,7 +1099,7 @@
         <v>200</v>
       </c>
       <c r="AP2">
-        <v>13.5</v>
+        <v>6.8</v>
       </c>
       <c r="AQ2">
         <v>7</v>
@@ -1168,7 +1213,7 @@
         <v>0</v>
       </c>
       <c r="CB2" t="s">
-        <v>112</v>
+        <v>127</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1182,10 +1227,10 @@
         <v>89</v>
       </c>
       <c r="D3" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="E3" t="s">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="F3">
         <v>2.66</v>
@@ -1197,22 +1242,22 @@
         <v>3.4</v>
       </c>
       <c r="I3">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="J3">
         <v>2.9</v>
       </c>
       <c r="K3">
-        <v>2.98</v>
+        <v>2.94</v>
       </c>
       <c r="L3">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="M3">
         <v>1.17</v>
       </c>
       <c r="N3">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="O3">
         <v>1.75</v>
@@ -1221,10 +1266,10 @@
         <v>1.41</v>
       </c>
       <c r="Q3">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="R3">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="S3">
         <v>7.6</v>
@@ -1242,7 +1287,7 @@
         <v>1.57</v>
       </c>
       <c r="X3">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="Y3">
         <v>8.199999999999999</v>
@@ -1410,7 +1455,7 @@
         <v>10</v>
       </c>
       <c r="CB3" t="s">
-        <v>112</v>
+        <v>127</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1424,64 +1469,64 @@
         <v>90</v>
       </c>
       <c r="D4" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="E4" t="s">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="F4">
-        <v>2.8</v>
+        <v>2.86</v>
       </c>
       <c r="G4">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="H4">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="I4">
-        <v>2.9</v>
+        <v>2.78</v>
       </c>
       <c r="J4">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="K4">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="L4">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="M4">
         <v>1.09</v>
       </c>
       <c r="N4">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="O4">
         <v>1.38</v>
       </c>
       <c r="P4">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="Q4">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="R4">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="S4">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="T4">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="U4">
         <v>2.02</v>
       </c>
       <c r="V4">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="W4">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="X4">
         <v>14</v>
@@ -1652,7 +1697,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="CB4" t="s">
-        <v>112</v>
+        <v>127</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1666,67 +1711,67 @@
         <v>91</v>
       </c>
       <c r="D5" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="E5" t="s">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="F5">
-        <v>1.69</v>
+        <v>1.74</v>
       </c>
       <c r="G5">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="H5">
         <v>4.7</v>
       </c>
       <c r="I5">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="J5">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="K5">
         <v>4.5</v>
       </c>
       <c r="L5">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="M5">
         <v>1.04</v>
       </c>
       <c r="N5">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="O5">
         <v>1.21</v>
       </c>
       <c r="P5">
-        <v>2.34</v>
+        <v>2.44</v>
       </c>
       <c r="Q5">
         <v>1.65</v>
       </c>
       <c r="R5">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="S5">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="T5">
         <v>1.67</v>
       </c>
       <c r="U5">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="V5">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="W5">
-        <v>2.22</v>
+        <v>2.28</v>
       </c>
       <c r="X5">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="Y5">
         <v>23</v>
@@ -1762,13 +1807,13 @@
         <v>65</v>
       </c>
       <c r="AJ5">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AK5">
         <v>17</v>
       </c>
       <c r="AL5">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AM5">
         <v>90</v>
@@ -1780,7 +1825,7 @@
         <v>60</v>
       </c>
       <c r="AP5">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="AQ5">
         <v>16.5</v>
@@ -1792,10 +1837,10 @@
         <v>7.4</v>
       </c>
       <c r="AT5">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="AU5">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV5">
         <v>16.5</v>
@@ -1834,13 +1879,13 @@
         <v>6.8</v>
       </c>
       <c r="BH5">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BI5">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="BJ5">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK5">
         <v>5</v>
@@ -1855,13 +1900,13 @@
         <v>4.8</v>
       </c>
       <c r="BO5">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="BP5">
         <v>12</v>
       </c>
       <c r="BQ5">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BR5">
         <v>1000</v>
@@ -1885,16 +1930,16 @@
         <v>1000</v>
       </c>
       <c r="BY5">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ5">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="CA5">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="CB5" t="s">
-        <v>112</v>
+        <v>127</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -1908,64 +1953,64 @@
         <v>92</v>
       </c>
       <c r="D6" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="E6" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="F6">
+        <v>2.18</v>
+      </c>
+      <c r="G6">
+        <v>2.28</v>
+      </c>
+      <c r="H6">
+        <v>3.7</v>
+      </c>
+      <c r="I6">
+        <v>4</v>
+      </c>
+      <c r="J6">
+        <v>3.3</v>
+      </c>
+      <c r="K6">
+        <v>3.5</v>
+      </c>
+      <c r="L6">
+        <v>1.46</v>
+      </c>
+      <c r="M6">
+        <v>1.09</v>
+      </c>
+      <c r="N6">
+        <v>3.35</v>
+      </c>
+      <c r="O6">
+        <v>1.39</v>
+      </c>
+      <c r="P6">
+        <v>1.78</v>
+      </c>
+      <c r="Q6">
         <v>2.2</v>
       </c>
-      <c r="G6">
-        <v>2.32</v>
-      </c>
-      <c r="H6">
-        <v>3.75</v>
-      </c>
-      <c r="I6">
+      <c r="R6">
+        <v>1.29</v>
+      </c>
+      <c r="S6">
         <v>4.1</v>
       </c>
-      <c r="J6">
-        <v>3.25</v>
-      </c>
-      <c r="K6">
-        <v>3.3</v>
-      </c>
-      <c r="L6">
-        <v>1.01</v>
-      </c>
-      <c r="M6">
-        <v>1.1</v>
-      </c>
-      <c r="N6">
-        <v>3.2</v>
-      </c>
-      <c r="O6">
-        <v>1.4</v>
-      </c>
-      <c r="P6">
-        <v>1.75</v>
-      </c>
-      <c r="Q6">
-        <v>2.16</v>
-      </c>
-      <c r="R6">
-        <v>1.28</v>
-      </c>
-      <c r="S6">
-        <v>4</v>
-      </c>
       <c r="T6">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="U6">
         <v>1.96</v>
       </c>
       <c r="V6">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W6">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="X6">
         <v>14</v>
@@ -1983,7 +2028,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AC6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AD6">
         <v>16.5</v>
@@ -2022,16 +2067,16 @@
         <v>65</v>
       </c>
       <c r="AP6">
-        <v>5.6</v>
+        <v>5.2</v>
       </c>
       <c r="AQ6">
         <v>9.199999999999999</v>
       </c>
       <c r="AR6">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="AS6">
-        <v>8.4</v>
+        <v>7.6</v>
       </c>
       <c r="AT6">
         <v>7.4</v>
@@ -2043,7 +2088,7 @@
         <v>13.5</v>
       </c>
       <c r="AW6">
-        <v>36</v>
+        <v>7.2</v>
       </c>
       <c r="AX6">
         <v>9.800000000000001</v>
@@ -2055,25 +2100,25 @@
         <v>16.5</v>
       </c>
       <c r="BA6">
-        <v>8.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="BB6">
         <v>22</v>
       </c>
       <c r="BC6">
-        <v>7</v>
+        <v>6.2</v>
       </c>
       <c r="BD6">
         <v>30</v>
       </c>
       <c r="BE6">
-        <v>8.800000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="BF6">
         <v>15.5</v>
       </c>
       <c r="BG6">
-        <v>8.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="BH6">
         <v>3.25</v>
@@ -2085,13 +2130,13 @@
         <v>10.5</v>
       </c>
       <c r="BK6">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BL6">
         <v>1000</v>
       </c>
       <c r="BM6">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BN6">
         <v>5.1</v>
@@ -2103,16 +2148,16 @@
         <v>17.5</v>
       </c>
       <c r="BQ6">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BR6">
         <v>36</v>
       </c>
       <c r="BS6">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT6">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BU6">
         <v>5.3</v>
@@ -2121,22 +2166,22 @@
         <v>1000</v>
       </c>
       <c r="BW6">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX6">
         <v>1000</v>
       </c>
       <c r="BY6">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ6">
         <v>34</v>
       </c>
       <c r="CA6">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="CB6" t="s">
-        <v>112</v>
+        <v>127</v>
       </c>
     </row>
     <row r="7" spans="1:80">
@@ -2150,10 +2195,10 @@
         <v>93</v>
       </c>
       <c r="D7" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E7" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="F7">
         <v>1.73</v>
@@ -2378,7 +2423,7 @@
         <v>0</v>
       </c>
       <c r="CB7" t="s">
-        <v>112</v>
+        <v>127</v>
       </c>
     </row>
     <row r="8" spans="1:80">
@@ -2392,172 +2437,172 @@
         <v>94</v>
       </c>
       <c r="D8" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="E8" t="s">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="F8">
-        <v>1.47</v>
+        <v>1.52</v>
       </c>
       <c r="G8">
         <v>1.69</v>
       </c>
       <c r="H8">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="I8">
-        <v>7.4</v>
+        <v>6.2</v>
       </c>
       <c r="J8">
         <v>4.9</v>
       </c>
       <c r="K8">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="L8">
         <v>1.01</v>
       </c>
       <c r="M8">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N8">
-        <v>1.1</v>
+        <v>7.2</v>
       </c>
       <c r="O8">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="P8">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="Q8">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="R8">
-        <v>1.81</v>
+        <v>1.96</v>
       </c>
       <c r="S8">
-        <v>1.64</v>
+        <v>1.82</v>
       </c>
       <c r="T8">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="U8">
-        <v>2.3</v>
+        <v>2.78</v>
       </c>
       <c r="V8">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="W8">
         <v>2.44</v>
       </c>
       <c r="X8">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="Y8">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="Z8">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AA8">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AB8">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="AC8">
+        <v>15</v>
+      </c>
+      <c r="AD8">
+        <v>23</v>
+      </c>
+      <c r="AE8">
+        <v>55</v>
+      </c>
+      <c r="AF8">
+        <v>17.5</v>
+      </c>
+      <c r="AG8">
+        <v>12.5</v>
+      </c>
+      <c r="AH8">
+        <v>17.5</v>
+      </c>
+      <c r="AI8">
+        <v>46</v>
+      </c>
+      <c r="AJ8">
         <v>20</v>
       </c>
-      <c r="AD8">
-        <v>950</v>
-      </c>
-      <c r="AE8">
-        <v>1000</v>
-      </c>
-      <c r="AF8">
-        <v>21</v>
-      </c>
-      <c r="AG8">
+      <c r="AK8">
         <v>16</v>
       </c>
-      <c r="AH8">
+      <c r="AL8">
         <v>23</v>
       </c>
-      <c r="AI8">
-        <v>1000</v>
-      </c>
-      <c r="AJ8">
-        <v>23</v>
-      </c>
-      <c r="AK8">
-        <v>20</v>
-      </c>
-      <c r="AL8">
-        <v>30</v>
-      </c>
       <c r="AM8">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AN8">
+        <v>5</v>
+      </c>
+      <c r="AO8">
+        <v>38</v>
+      </c>
+      <c r="AP8">
+        <v>7</v>
+      </c>
+      <c r="AQ8">
+        <v>6.6</v>
+      </c>
+      <c r="AR8">
+        <v>7.2</v>
+      </c>
+      <c r="AS8">
+        <v>7.6</v>
+      </c>
+      <c r="AT8">
+        <v>5.8</v>
+      </c>
+      <c r="AU8">
+        <v>5.3</v>
+      </c>
+      <c r="AV8">
         <v>6</v>
       </c>
-      <c r="AO8">
-        <v>1000</v>
-      </c>
-      <c r="AP8">
-        <v>2.32</v>
-      </c>
-      <c r="AQ8">
-        <v>2.32</v>
-      </c>
-      <c r="AR8">
-        <v>2.32</v>
-      </c>
-      <c r="AS8">
-        <v>2.32</v>
-      </c>
-      <c r="AT8">
-        <v>2.12</v>
-      </c>
-      <c r="AU8">
-        <v>2.08</v>
-      </c>
-      <c r="AV8">
-        <v>2.16</v>
-      </c>
       <c r="AW8">
-        <v>2.32</v>
+        <v>7</v>
       </c>
       <c r="AX8">
-        <v>2.08</v>
+        <v>5.5</v>
       </c>
       <c r="AY8">
-        <v>2.02</v>
+        <v>4.9</v>
       </c>
       <c r="AZ8">
-        <v>2.1</v>
+        <v>5.5</v>
       </c>
       <c r="BA8">
-        <v>2.32</v>
+        <v>6.8</v>
       </c>
       <c r="BB8">
-        <v>2.1</v>
+        <v>5.8</v>
       </c>
       <c r="BC8">
-        <v>2.08</v>
+        <v>5.4</v>
       </c>
       <c r="BD8">
-        <v>2.16</v>
+        <v>6</v>
       </c>
       <c r="BE8">
-        <v>2.32</v>
+        <v>7</v>
       </c>
       <c r="BF8">
-        <v>1.67</v>
+        <v>3.25</v>
       </c>
       <c r="BG8">
-        <v>2.32</v>
+        <v>6.2</v>
       </c>
       <c r="BH8">
         <v>1000</v>
@@ -2620,7 +2665,7 @@
         <v>1.04</v>
       </c>
       <c r="CB8" t="s">
-        <v>112</v>
+        <v>127</v>
       </c>
     </row>
     <row r="9" spans="1:80">
@@ -2634,31 +2679,31 @@
         <v>95</v>
       </c>
       <c r="D9" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="E9" t="s">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="F9">
         <v>2.32</v>
       </c>
       <c r="G9">
-        <v>3.55</v>
+        <v>3.1</v>
       </c>
       <c r="H9">
         <v>2.46</v>
       </c>
       <c r="I9">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="J9">
         <v>2.52</v>
       </c>
       <c r="K9">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="L9">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="M9">
         <v>1.01</v>
@@ -2667,19 +2712,19 @@
         <v>2.92</v>
       </c>
       <c r="O9">
-        <v>1.02</v>
+        <v>1.37</v>
       </c>
       <c r="P9">
         <v>1.61</v>
       </c>
       <c r="Q9">
-        <v>1.66</v>
+        <v>2.06</v>
       </c>
       <c r="R9">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="S9">
-        <v>3.1</v>
+        <v>2.56</v>
       </c>
       <c r="T9">
         <v>1.01</v>
@@ -2688,10 +2733,10 @@
         <v>1.01</v>
       </c>
       <c r="V9">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="W9">
-        <v>1.39</v>
+        <v>1.48</v>
       </c>
       <c r="X9">
         <v>1000</v>
@@ -2862,7 +2907,1217 @@
         <v>1.01</v>
       </c>
       <c r="CB9" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="10" spans="1:80">
+      <c r="A10" t="s">
+        <v>84</v>
+      </c>
+      <c r="B10" t="s">
+        <v>87</v>
+      </c>
+      <c r="C10" t="s">
+        <v>96</v>
+      </c>
+      <c r="D10" t="s">
+        <v>109</v>
+      </c>
+      <c r="E10" t="s">
+        <v>122</v>
+      </c>
+      <c r="F10">
+        <v>2.36</v>
+      </c>
+      <c r="G10">
+        <v>2.52</v>
+      </c>
+      <c r="H10">
+        <v>3.15</v>
+      </c>
+      <c r="I10">
+        <v>3.35</v>
+      </c>
+      <c r="J10">
+        <v>3.5</v>
+      </c>
+      <c r="K10">
+        <v>3.85</v>
+      </c>
+      <c r="L10">
+        <v>1.01</v>
+      </c>
+      <c r="M10">
+        <v>1.07</v>
+      </c>
+      <c r="N10">
+        <v>3.3</v>
+      </c>
+      <c r="O10">
+        <v>1.36</v>
+      </c>
+      <c r="P10">
+        <v>1.85</v>
+      </c>
+      <c r="Q10">
+        <v>1.85</v>
+      </c>
+      <c r="R10">
+        <v>1.33</v>
+      </c>
+      <c r="S10">
+        <v>3.3</v>
+      </c>
+      <c r="T10">
+        <v>1.75</v>
+      </c>
+      <c r="U10">
+        <v>2.1</v>
+      </c>
+      <c r="V10">
+        <v>1.42</v>
+      </c>
+      <c r="W10">
+        <v>1.65</v>
+      </c>
+      <c r="X10">
+        <v>17</v>
+      </c>
+      <c r="Y10">
+        <v>15</v>
+      </c>
+      <c r="Z10">
+        <v>27</v>
+      </c>
+      <c r="AA10">
+        <v>70</v>
+      </c>
+      <c r="AB10">
+        <v>13</v>
+      </c>
+      <c r="AC10">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD10">
+        <v>17</v>
+      </c>
+      <c r="AE10">
+        <v>46</v>
+      </c>
+      <c r="AF10">
+        <v>20</v>
+      </c>
+      <c r="AG10">
+        <v>14.5</v>
+      </c>
+      <c r="AH10">
+        <v>21</v>
+      </c>
+      <c r="AI10">
+        <v>60</v>
+      </c>
+      <c r="AJ10">
+        <v>42</v>
+      </c>
+      <c r="AK10">
+        <v>34</v>
+      </c>
+      <c r="AL10">
+        <v>48</v>
+      </c>
+      <c r="AM10">
+        <v>120</v>
+      </c>
+      <c r="AN10">
+        <v>27</v>
+      </c>
+      <c r="AO10">
+        <v>42</v>
+      </c>
+      <c r="AP10">
+        <v>3.6</v>
+      </c>
+      <c r="AQ10">
+        <v>3.5</v>
+      </c>
+      <c r="AR10">
+        <v>3.9</v>
+      </c>
+      <c r="AS10">
+        <v>4.3</v>
+      </c>
+      <c r="AT10">
+        <v>3.35</v>
+      </c>
+      <c r="AU10">
+        <v>2.94</v>
+      </c>
+      <c r="AV10">
+        <v>3.6</v>
+      </c>
+      <c r="AW10">
+        <v>4.1</v>
+      </c>
+      <c r="AX10">
+        <v>3.7</v>
+      </c>
+      <c r="AY10">
+        <v>3.45</v>
+      </c>
+      <c r="AZ10">
+        <v>3.75</v>
+      </c>
+      <c r="BA10">
+        <v>4.2</v>
+      </c>
+      <c r="BB10">
+        <v>4.1</v>
+      </c>
+      <c r="BC10">
+        <v>4</v>
+      </c>
+      <c r="BD10">
+        <v>4.1</v>
+      </c>
+      <c r="BE10">
+        <v>4.4</v>
+      </c>
+      <c r="BF10">
+        <v>3.9</v>
+      </c>
+      <c r="BG10">
+        <v>4.1</v>
+      </c>
+      <c r="BH10">
+        <v>1000</v>
+      </c>
+      <c r="BI10">
+        <v>1.04</v>
+      </c>
+      <c r="BJ10">
+        <v>1000</v>
+      </c>
+      <c r="BK10">
+        <v>1.04</v>
+      </c>
+      <c r="BL10">
+        <v>1000</v>
+      </c>
+      <c r="BM10">
+        <v>1.04</v>
+      </c>
+      <c r="BN10">
+        <v>1000</v>
+      </c>
+      <c r="BO10">
+        <v>1.04</v>
+      </c>
+      <c r="BP10">
+        <v>1000</v>
+      </c>
+      <c r="BQ10">
+        <v>1.04</v>
+      </c>
+      <c r="BR10">
+        <v>1000</v>
+      </c>
+      <c r="BS10">
+        <v>1.04</v>
+      </c>
+      <c r="BT10">
+        <v>1000</v>
+      </c>
+      <c r="BU10">
+        <v>1.04</v>
+      </c>
+      <c r="BV10">
+        <v>1000</v>
+      </c>
+      <c r="BW10">
+        <v>1.04</v>
+      </c>
+      <c r="BX10">
+        <v>1000</v>
+      </c>
+      <c r="BY10">
+        <v>1.04</v>
+      </c>
+      <c r="BZ10">
+        <v>0</v>
+      </c>
+      <c r="CA10">
+        <v>0</v>
+      </c>
+      <c r="CB10" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="11" spans="1:80">
+      <c r="A11" t="s">
+        <v>84</v>
+      </c>
+      <c r="B11" t="s">
+        <v>87</v>
+      </c>
+      <c r="C11" t="s">
+        <v>97</v>
+      </c>
+      <c r="D11" t="s">
+        <v>110</v>
+      </c>
+      <c r="E11" t="s">
+        <v>123</v>
+      </c>
+      <c r="F11">
+        <v>1.77</v>
+      </c>
+      <c r="G11">
+        <v>1.98</v>
+      </c>
+      <c r="H11">
+        <v>4.4</v>
+      </c>
+      <c r="I11">
+        <v>6.2</v>
+      </c>
+      <c r="J11">
+        <v>3.25</v>
+      </c>
+      <c r="K11">
+        <v>3.75</v>
+      </c>
+      <c r="L11">
+        <v>1.01</v>
+      </c>
+      <c r="M11">
+        <v>1.01</v>
+      </c>
+      <c r="N11">
+        <v>2.9</v>
+      </c>
+      <c r="O11">
+        <v>1.36</v>
+      </c>
+      <c r="P11">
+        <v>1.7</v>
+      </c>
+      <c r="Q11">
+        <v>2.12</v>
+      </c>
+      <c r="R11">
+        <v>1.25</v>
+      </c>
+      <c r="S11">
+        <v>3.5</v>
+      </c>
+      <c r="T11">
+        <v>1.11</v>
+      </c>
+      <c r="U11">
+        <v>1.11</v>
+      </c>
+      <c r="V11">
+        <v>1.19</v>
+      </c>
+      <c r="W11">
+        <v>2.02</v>
+      </c>
+      <c r="X11">
+        <v>1000</v>
+      </c>
+      <c r="Y11">
+        <v>1000</v>
+      </c>
+      <c r="Z11">
+        <v>1000</v>
+      </c>
+      <c r="AA11">
+        <v>1000</v>
+      </c>
+      <c r="AB11">
+        <v>1000</v>
+      </c>
+      <c r="AC11">
+        <v>1000</v>
+      </c>
+      <c r="AD11">
+        <v>1000</v>
+      </c>
+      <c r="AE11">
+        <v>1000</v>
+      </c>
+      <c r="AF11">
+        <v>1000</v>
+      </c>
+      <c r="AG11">
+        <v>1000</v>
+      </c>
+      <c r="AH11">
+        <v>1000</v>
+      </c>
+      <c r="AI11">
+        <v>1000</v>
+      </c>
+      <c r="AJ11">
+        <v>1000</v>
+      </c>
+      <c r="AK11">
+        <v>1000</v>
+      </c>
+      <c r="AL11">
+        <v>1000</v>
+      </c>
+      <c r="AM11">
+        <v>1000</v>
+      </c>
+      <c r="AN11">
+        <v>1000</v>
+      </c>
+      <c r="AO11">
+        <v>1000</v>
+      </c>
+      <c r="AP11">
+        <v>1.01</v>
+      </c>
+      <c r="AQ11">
+        <v>1.01</v>
+      </c>
+      <c r="AR11">
+        <v>1.01</v>
+      </c>
+      <c r="AS11">
+        <v>1.01</v>
+      </c>
+      <c r="AT11">
+        <v>1.01</v>
+      </c>
+      <c r="AU11">
+        <v>1.01</v>
+      </c>
+      <c r="AV11">
+        <v>1.01</v>
+      </c>
+      <c r="AW11">
+        <v>1.01</v>
+      </c>
+      <c r="AX11">
+        <v>1.01</v>
+      </c>
+      <c r="AY11">
+        <v>1.01</v>
+      </c>
+      <c r="AZ11">
+        <v>1.01</v>
+      </c>
+      <c r="BA11">
+        <v>1.01</v>
+      </c>
+      <c r="BB11">
+        <v>1.01</v>
+      </c>
+      <c r="BC11">
+        <v>1.01</v>
+      </c>
+      <c r="BD11">
+        <v>1.01</v>
+      </c>
+      <c r="BE11">
+        <v>1.01</v>
+      </c>
+      <c r="BF11">
+        <v>1.01</v>
+      </c>
+      <c r="BG11">
+        <v>1.01</v>
+      </c>
+      <c r="BH11">
+        <v>1000</v>
+      </c>
+      <c r="BI11">
+        <v>1.04</v>
+      </c>
+      <c r="BJ11">
+        <v>1000</v>
+      </c>
+      <c r="BK11">
+        <v>1.04</v>
+      </c>
+      <c r="BL11">
+        <v>1000</v>
+      </c>
+      <c r="BM11">
+        <v>1.04</v>
+      </c>
+      <c r="BN11">
+        <v>1000</v>
+      </c>
+      <c r="BO11">
+        <v>1.04</v>
+      </c>
+      <c r="BP11">
+        <v>1000</v>
+      </c>
+      <c r="BQ11">
+        <v>1.04</v>
+      </c>
+      <c r="BR11">
+        <v>1000</v>
+      </c>
+      <c r="BS11">
+        <v>1.04</v>
+      </c>
+      <c r="BT11">
+        <v>1000</v>
+      </c>
+      <c r="BU11">
+        <v>1.04</v>
+      </c>
+      <c r="BV11">
+        <v>1000</v>
+      </c>
+      <c r="BW11">
+        <v>1.04</v>
+      </c>
+      <c r="BX11">
+        <v>1000</v>
+      </c>
+      <c r="BY11">
+        <v>1.04</v>
+      </c>
+      <c r="BZ11">
+        <v>1000</v>
+      </c>
+      <c r="CA11">
+        <v>1.04</v>
+      </c>
+      <c r="CB11" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="12" spans="1:80">
+      <c r="A12" t="s">
+        <v>81</v>
+      </c>
+      <c r="B12" t="s">
+        <v>87</v>
+      </c>
+      <c r="C12" t="s">
+        <v>98</v>
+      </c>
+      <c r="D12" t="s">
+        <v>111</v>
+      </c>
+      <c r="E12" t="s">
+        <v>124</v>
+      </c>
+      <c r="F12">
+        <v>2.38</v>
+      </c>
+      <c r="G12">
+        <v>2.52</v>
+      </c>
+      <c r="H12">
+        <v>3.55</v>
+      </c>
+      <c r="I12">
+        <v>3.85</v>
+      </c>
+      <c r="J12">
+        <v>3.05</v>
+      </c>
+      <c r="K12">
+        <v>3.15</v>
+      </c>
+      <c r="L12">
+        <v>1.01</v>
+      </c>
+      <c r="M12">
+        <v>1.12</v>
+      </c>
+      <c r="N12">
+        <v>2.62</v>
+      </c>
+      <c r="O12">
+        <v>1.54</v>
+      </c>
+      <c r="P12">
+        <v>1.56</v>
+      </c>
+      <c r="Q12">
+        <v>2.6</v>
+      </c>
+      <c r="R12">
+        <v>1.2</v>
+      </c>
+      <c r="S12">
+        <v>5.4</v>
+      </c>
+      <c r="T12">
+        <v>2.12</v>
+      </c>
+      <c r="U12">
+        <v>1.8</v>
+      </c>
+      <c r="V12">
+        <v>1.35</v>
+      </c>
+      <c r="W12">
+        <v>1.66</v>
+      </c>
+      <c r="X12">
+        <v>10.5</v>
+      </c>
+      <c r="Y12">
+        <v>12</v>
+      </c>
+      <c r="Z12">
+        <v>30</v>
+      </c>
+      <c r="AA12">
+        <v>100</v>
+      </c>
+      <c r="AB12">
+        <v>7.4</v>
+      </c>
+      <c r="AC12">
+        <v>7.4</v>
+      </c>
+      <c r="AD12">
+        <v>17</v>
+      </c>
+      <c r="AE12">
+        <v>75</v>
+      </c>
+      <c r="AF12">
+        <v>14.5</v>
+      </c>
+      <c r="AG12">
+        <v>13</v>
+      </c>
+      <c r="AH12">
+        <v>24</v>
+      </c>
+      <c r="AI12">
+        <v>100</v>
+      </c>
+      <c r="AJ12">
+        <v>46</v>
+      </c>
+      <c r="AK12">
+        <v>42</v>
+      </c>
+      <c r="AL12">
+        <v>75</v>
+      </c>
+      <c r="AM12">
+        <v>220</v>
+      </c>
+      <c r="AN12">
+        <v>44</v>
+      </c>
+      <c r="AO12">
+        <v>100</v>
+      </c>
+      <c r="AP12">
+        <v>7.8</v>
+      </c>
+      <c r="AQ12">
+        <v>9</v>
+      </c>
+      <c r="AR12">
+        <v>5.7</v>
+      </c>
+      <c r="AS12">
+        <v>6.8</v>
+      </c>
+      <c r="AT12">
+        <v>6.6</v>
+      </c>
+      <c r="AU12">
+        <v>6.4</v>
+      </c>
+      <c r="AV12">
+        <v>14</v>
+      </c>
+      <c r="AW12">
+        <v>6.6</v>
+      </c>
+      <c r="AX12">
+        <v>12</v>
+      </c>
+      <c r="AY12">
+        <v>10.5</v>
+      </c>
+      <c r="AZ12">
+        <v>5.6</v>
+      </c>
+      <c r="BA12">
+        <v>6.8</v>
+      </c>
+      <c r="BB12">
+        <v>6.2</v>
+      </c>
+      <c r="BC12">
+        <v>6.2</v>
+      </c>
+      <c r="BD12">
+        <v>6.6</v>
+      </c>
+      <c r="BE12">
+        <v>7</v>
+      </c>
+      <c r="BF12">
+        <v>6.2</v>
+      </c>
+      <c r="BG12">
+        <v>6.8</v>
+      </c>
+      <c r="BH12">
+        <v>3.15</v>
+      </c>
+      <c r="BI12">
+        <v>2.22</v>
+      </c>
+      <c r="BJ12">
+        <v>16</v>
+      </c>
+      <c r="BK12">
+        <v>2.98</v>
+      </c>
+      <c r="BL12">
+        <v>1000</v>
+      </c>
+      <c r="BM12">
+        <v>3.65</v>
+      </c>
+      <c r="BN12">
+        <v>7</v>
+      </c>
+      <c r="BO12">
+        <v>3.4</v>
+      </c>
+      <c r="BP12">
+        <v>30</v>
+      </c>
+      <c r="BQ12">
+        <v>3.25</v>
+      </c>
+      <c r="BR12">
+        <v>1000</v>
+      </c>
+      <c r="BS12">
+        <v>3.45</v>
+      </c>
+      <c r="BT12">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BU12">
+        <v>4.3</v>
+      </c>
+      <c r="BV12">
+        <v>50</v>
+      </c>
+      <c r="BW12">
+        <v>3.4</v>
+      </c>
+      <c r="BX12">
+        <v>1000</v>
+      </c>
+      <c r="BY12">
+        <v>3.5</v>
+      </c>
+      <c r="BZ12">
+        <v>1000</v>
+      </c>
+      <c r="CA12">
+        <v>3.45</v>
+      </c>
+      <c r="CB12" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="13" spans="1:80">
+      <c r="A13" t="s">
+        <v>84</v>
+      </c>
+      <c r="B13" t="s">
+        <v>87</v>
+      </c>
+      <c r="C13" t="s">
+        <v>99</v>
+      </c>
+      <c r="D13" t="s">
         <v>112</v>
+      </c>
+      <c r="E13" t="s">
+        <v>125</v>
+      </c>
+      <c r="F13">
+        <v>2.08</v>
+      </c>
+      <c r="G13">
+        <v>2.44</v>
+      </c>
+      <c r="H13">
+        <v>3.7</v>
+      </c>
+      <c r="I13">
+        <v>5.4</v>
+      </c>
+      <c r="J13">
+        <v>2.8</v>
+      </c>
+      <c r="K13">
+        <v>4.1</v>
+      </c>
+      <c r="L13">
+        <v>1.01</v>
+      </c>
+      <c r="M13">
+        <v>1.01</v>
+      </c>
+      <c r="N13">
+        <v>1.97</v>
+      </c>
+      <c r="O13">
+        <v>1.51</v>
+      </c>
+      <c r="P13">
+        <v>1.35</v>
+      </c>
+      <c r="Q13">
+        <v>2.44</v>
+      </c>
+      <c r="R13">
+        <v>1.13</v>
+      </c>
+      <c r="S13">
+        <v>2.96</v>
+      </c>
+      <c r="T13">
+        <v>1.11</v>
+      </c>
+      <c r="U13">
+        <v>1.11</v>
+      </c>
+      <c r="V13">
+        <v>1.26</v>
+      </c>
+      <c r="W13">
+        <v>1.69</v>
+      </c>
+      <c r="X13">
+        <v>1000</v>
+      </c>
+      <c r="Y13">
+        <v>1000</v>
+      </c>
+      <c r="Z13">
+        <v>1000</v>
+      </c>
+      <c r="AA13">
+        <v>1000</v>
+      </c>
+      <c r="AB13">
+        <v>1000</v>
+      </c>
+      <c r="AC13">
+        <v>1000</v>
+      </c>
+      <c r="AD13">
+        <v>1000</v>
+      </c>
+      <c r="AE13">
+        <v>1000</v>
+      </c>
+      <c r="AF13">
+        <v>1000</v>
+      </c>
+      <c r="AG13">
+        <v>1000</v>
+      </c>
+      <c r="AH13">
+        <v>1000</v>
+      </c>
+      <c r="AI13">
+        <v>1000</v>
+      </c>
+      <c r="AJ13">
+        <v>1000</v>
+      </c>
+      <c r="AK13">
+        <v>1000</v>
+      </c>
+      <c r="AL13">
+        <v>1000</v>
+      </c>
+      <c r="AM13">
+        <v>1000</v>
+      </c>
+      <c r="AN13">
+        <v>1000</v>
+      </c>
+      <c r="AO13">
+        <v>1000</v>
+      </c>
+      <c r="AP13">
+        <v>1.01</v>
+      </c>
+      <c r="AQ13">
+        <v>1.01</v>
+      </c>
+      <c r="AR13">
+        <v>1.01</v>
+      </c>
+      <c r="AS13">
+        <v>1.01</v>
+      </c>
+      <c r="AT13">
+        <v>1.01</v>
+      </c>
+      <c r="AU13">
+        <v>1.01</v>
+      </c>
+      <c r="AV13">
+        <v>1.01</v>
+      </c>
+      <c r="AW13">
+        <v>1.01</v>
+      </c>
+      <c r="AX13">
+        <v>1.01</v>
+      </c>
+      <c r="AY13">
+        <v>1.01</v>
+      </c>
+      <c r="AZ13">
+        <v>1.01</v>
+      </c>
+      <c r="BA13">
+        <v>1.01</v>
+      </c>
+      <c r="BB13">
+        <v>1.01</v>
+      </c>
+      <c r="BC13">
+        <v>1.01</v>
+      </c>
+      <c r="BD13">
+        <v>1.01</v>
+      </c>
+      <c r="BE13">
+        <v>1.01</v>
+      </c>
+      <c r="BF13">
+        <v>1.01</v>
+      </c>
+      <c r="BG13">
+        <v>1.01</v>
+      </c>
+      <c r="BH13">
+        <v>1000</v>
+      </c>
+      <c r="BI13">
+        <v>1.04</v>
+      </c>
+      <c r="BJ13">
+        <v>1000</v>
+      </c>
+      <c r="BK13">
+        <v>1.04</v>
+      </c>
+      <c r="BL13">
+        <v>1000</v>
+      </c>
+      <c r="BM13">
+        <v>1.04</v>
+      </c>
+      <c r="BN13">
+        <v>1000</v>
+      </c>
+      <c r="BO13">
+        <v>1.04</v>
+      </c>
+      <c r="BP13">
+        <v>1000</v>
+      </c>
+      <c r="BQ13">
+        <v>1.04</v>
+      </c>
+      <c r="BR13">
+        <v>1000</v>
+      </c>
+      <c r="BS13">
+        <v>1.04</v>
+      </c>
+      <c r="BT13">
+        <v>1000</v>
+      </c>
+      <c r="BU13">
+        <v>1.04</v>
+      </c>
+      <c r="BV13">
+        <v>1000</v>
+      </c>
+      <c r="BW13">
+        <v>1.04</v>
+      </c>
+      <c r="BX13">
+        <v>1000</v>
+      </c>
+      <c r="BY13">
+        <v>1.04</v>
+      </c>
+      <c r="BZ13">
+        <v>1000</v>
+      </c>
+      <c r="CA13">
+        <v>1.04</v>
+      </c>
+      <c r="CB13" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="14" spans="1:80">
+      <c r="A14" t="s">
+        <v>80</v>
+      </c>
+      <c r="B14" t="s">
+        <v>87</v>
+      </c>
+      <c r="C14" t="s">
+        <v>100</v>
+      </c>
+      <c r="D14" t="s">
+        <v>113</v>
+      </c>
+      <c r="E14" t="s">
+        <v>126</v>
+      </c>
+      <c r="F14">
+        <v>1.5</v>
+      </c>
+      <c r="G14">
+        <v>110</v>
+      </c>
+      <c r="H14">
+        <v>1.32</v>
+      </c>
+      <c r="I14">
+        <v>110</v>
+      </c>
+      <c r="J14">
+        <v>1.72</v>
+      </c>
+      <c r="K14">
+        <v>4.2</v>
+      </c>
+      <c r="L14">
+        <v>1.01</v>
+      </c>
+      <c r="M14">
+        <v>1.01</v>
+      </c>
+      <c r="N14">
+        <v>1.31</v>
+      </c>
+      <c r="O14">
+        <v>1.14</v>
+      </c>
+      <c r="P14">
+        <v>1.31</v>
+      </c>
+      <c r="Q14">
+        <v>1.14</v>
+      </c>
+      <c r="R14">
+        <v>1.27</v>
+      </c>
+      <c r="S14">
+        <v>1.14</v>
+      </c>
+      <c r="T14">
+        <v>1.01</v>
+      </c>
+      <c r="U14">
+        <v>1.01</v>
+      </c>
+      <c r="V14">
+        <v>1.66</v>
+      </c>
+      <c r="W14">
+        <v>1.01</v>
+      </c>
+      <c r="X14">
+        <v>1000</v>
+      </c>
+      <c r="Y14">
+        <v>1000</v>
+      </c>
+      <c r="Z14">
+        <v>1000</v>
+      </c>
+      <c r="AA14">
+        <v>1000</v>
+      </c>
+      <c r="AB14">
+        <v>1000</v>
+      </c>
+      <c r="AC14">
+        <v>1000</v>
+      </c>
+      <c r="AD14">
+        <v>1000</v>
+      </c>
+      <c r="AE14">
+        <v>1000</v>
+      </c>
+      <c r="AF14">
+        <v>1000</v>
+      </c>
+      <c r="AG14">
+        <v>1000</v>
+      </c>
+      <c r="AH14">
+        <v>1000</v>
+      </c>
+      <c r="AI14">
+        <v>1000</v>
+      </c>
+      <c r="AJ14">
+        <v>1000</v>
+      </c>
+      <c r="AK14">
+        <v>1000</v>
+      </c>
+      <c r="AL14">
+        <v>1000</v>
+      </c>
+      <c r="AM14">
+        <v>1000</v>
+      </c>
+      <c r="AN14">
+        <v>1000</v>
+      </c>
+      <c r="AO14">
+        <v>1000</v>
+      </c>
+      <c r="AP14">
+        <v>1.01</v>
+      </c>
+      <c r="AQ14">
+        <v>1.01</v>
+      </c>
+      <c r="AR14">
+        <v>1.01</v>
+      </c>
+      <c r="AS14">
+        <v>1.01</v>
+      </c>
+      <c r="AT14">
+        <v>1.01</v>
+      </c>
+      <c r="AU14">
+        <v>1.01</v>
+      </c>
+      <c r="AV14">
+        <v>1.01</v>
+      </c>
+      <c r="AW14">
+        <v>1.01</v>
+      </c>
+      <c r="AX14">
+        <v>1.01</v>
+      </c>
+      <c r="AY14">
+        <v>1.01</v>
+      </c>
+      <c r="AZ14">
+        <v>1.01</v>
+      </c>
+      <c r="BA14">
+        <v>1.01</v>
+      </c>
+      <c r="BB14">
+        <v>1.01</v>
+      </c>
+      <c r="BC14">
+        <v>1.01</v>
+      </c>
+      <c r="BD14">
+        <v>1.01</v>
+      </c>
+      <c r="BE14">
+        <v>1.01</v>
+      </c>
+      <c r="BF14">
+        <v>1.01</v>
+      </c>
+      <c r="BG14">
+        <v>1.01</v>
+      </c>
+      <c r="BH14">
+        <v>1000</v>
+      </c>
+      <c r="BI14">
+        <v>1.01</v>
+      </c>
+      <c r="BJ14">
+        <v>1000</v>
+      </c>
+      <c r="BK14">
+        <v>1.01</v>
+      </c>
+      <c r="BL14">
+        <v>1000</v>
+      </c>
+      <c r="BM14">
+        <v>1.01</v>
+      </c>
+      <c r="BN14">
+        <v>1000</v>
+      </c>
+      <c r="BO14">
+        <v>1.01</v>
+      </c>
+      <c r="BP14">
+        <v>1000</v>
+      </c>
+      <c r="BQ14">
+        <v>1.01</v>
+      </c>
+      <c r="BR14">
+        <v>1000</v>
+      </c>
+      <c r="BS14">
+        <v>1.01</v>
+      </c>
+      <c r="BT14">
+        <v>1000</v>
+      </c>
+      <c r="BU14">
+        <v>1.01</v>
+      </c>
+      <c r="BV14">
+        <v>1000</v>
+      </c>
+      <c r="BW14">
+        <v>1.01</v>
+      </c>
+      <c r="BX14">
+        <v>1000</v>
+      </c>
+      <c r="BY14">
+        <v>1.01</v>
+      </c>
+      <c r="BZ14">
+        <v>0</v>
+      </c>
+      <c r="CA14">
+        <v>0</v>
+      </c>
+      <c r="CB14" t="s">
+        <v>127</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-06.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-06.xlsx
@@ -397,7 +397,7 @@
     <t>Always Ready</t>
   </si>
   <si>
-    <t>2026-08-05 01:57:35</t>
+    <t>2026-08-05 04:04:30</t>
   </si>
 </sst>
 </file>
@@ -994,70 +994,70 @@
         <v>1.18</v>
       </c>
       <c r="G2">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="H2">
-        <v>8.800000000000001</v>
+        <v>12.5</v>
       </c>
       <c r="I2">
         <v>19.5</v>
       </c>
       <c r="J2">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="K2">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="L2">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="M2">
         <v>1.01</v>
       </c>
       <c r="N2">
-        <v>1.1</v>
+        <v>3.45</v>
       </c>
       <c r="O2">
         <v>1.09</v>
       </c>
       <c r="P2">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="Q2">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="R2">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="S2">
         <v>1.69</v>
       </c>
       <c r="T2">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="U2">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="V2">
         <v>1.06</v>
       </c>
       <c r="W2">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="X2">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="Y2">
-        <v>85</v>
+        <v>950</v>
       </c>
       <c r="Z2">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="AA2">
         <v>610</v>
       </c>
       <c r="AB2">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AC2">
         <v>24</v>
@@ -1066,7 +1066,7 @@
         <v>65</v>
       </c>
       <c r="AE2">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="AF2">
         <v>13</v>
@@ -1075,7 +1075,7 @@
         <v>15</v>
       </c>
       <c r="AH2">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AI2">
         <v>150</v>
@@ -1087,124 +1087,124 @@
         <v>15</v>
       </c>
       <c r="AL2">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AM2">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AN2">
         <v>2.82</v>
       </c>
       <c r="AO2">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="AP2">
+        <v>2.02</v>
+      </c>
+      <c r="AQ2">
+        <v>7.2</v>
+      </c>
+      <c r="AR2">
+        <v>24</v>
+      </c>
+      <c r="AS2">
+        <v>2.06</v>
+      </c>
+      <c r="AT2">
+        <v>5.6</v>
+      </c>
+      <c r="AU2">
+        <v>5.9</v>
+      </c>
+      <c r="AV2">
+        <v>2.02</v>
+      </c>
+      <c r="AW2">
+        <v>19.5</v>
+      </c>
+      <c r="AX2">
+        <v>4.9</v>
+      </c>
+      <c r="AY2">
+        <v>5.1</v>
+      </c>
+      <c r="AZ2">
+        <v>14</v>
+      </c>
+      <c r="BA2">
+        <v>18.5</v>
+      </c>
+      <c r="BB2">
+        <v>4.7</v>
+      </c>
+      <c r="BC2">
+        <v>5.1</v>
+      </c>
+      <c r="BD2">
+        <v>6.4</v>
+      </c>
+      <c r="BE2">
+        <v>7.4</v>
+      </c>
+      <c r="BF2">
+        <v>2.36</v>
+      </c>
+      <c r="BG2">
+        <v>2.06</v>
+      </c>
+      <c r="BH2">
+        <v>7</v>
+      </c>
+      <c r="BI2">
+        <v>3.75</v>
+      </c>
+      <c r="BJ2">
+        <v>13</v>
+      </c>
+      <c r="BK2">
+        <v>4.9</v>
+      </c>
+      <c r="BL2">
+        <v>1000</v>
+      </c>
+      <c r="BM2">
+        <v>7.4</v>
+      </c>
+      <c r="BN2">
+        <v>4.7</v>
+      </c>
+      <c r="BO2">
+        <v>2.96</v>
+      </c>
+      <c r="BP2">
         <v>6.8</v>
       </c>
-      <c r="AQ2">
-        <v>7</v>
-      </c>
-      <c r="AR2">
+      <c r="BQ2">
+        <v>3.65</v>
+      </c>
+      <c r="BR2">
+        <v>18.5</v>
+      </c>
+      <c r="BS2">
+        <v>5.6</v>
+      </c>
+      <c r="BT2">
+        <v>18.5</v>
+      </c>
+      <c r="BU2">
+        <v>5.6</v>
+      </c>
+      <c r="BV2">
+        <v>1000</v>
+      </c>
+      <c r="BW2">
+        <v>7.4</v>
+      </c>
+      <c r="BX2">
+        <v>75</v>
+      </c>
+      <c r="BY2">
         <v>7.2</v>
-      </c>
-      <c r="AS2">
-        <v>7.4</v>
-      </c>
-      <c r="AT2">
-        <v>5.4</v>
-      </c>
-      <c r="AU2">
-        <v>5.7</v>
-      </c>
-      <c r="AV2">
-        <v>6.8</v>
-      </c>
-      <c r="AW2">
-        <v>7.2</v>
-      </c>
-      <c r="AX2">
-        <v>4.8</v>
-      </c>
-      <c r="AY2">
-        <v>5</v>
-      </c>
-      <c r="AZ2">
-        <v>6.2</v>
-      </c>
-      <c r="BA2">
-        <v>7.2</v>
-      </c>
-      <c r="BB2">
-        <v>4.6</v>
-      </c>
-      <c r="BC2">
-        <v>5</v>
-      </c>
-      <c r="BD2">
-        <v>6.2</v>
-      </c>
-      <c r="BE2">
-        <v>7.2</v>
-      </c>
-      <c r="BF2">
-        <v>2.4</v>
-      </c>
-      <c r="BG2">
-        <v>7.2</v>
-      </c>
-      <c r="BH2">
-        <v>1000</v>
-      </c>
-      <c r="BI2">
-        <v>1.04</v>
-      </c>
-      <c r="BJ2">
-        <v>1000</v>
-      </c>
-      <c r="BK2">
-        <v>1.04</v>
-      </c>
-      <c r="BL2">
-        <v>1000</v>
-      </c>
-      <c r="BM2">
-        <v>1.04</v>
-      </c>
-      <c r="BN2">
-        <v>1000</v>
-      </c>
-      <c r="BO2">
-        <v>1.04</v>
-      </c>
-      <c r="BP2">
-        <v>1000</v>
-      </c>
-      <c r="BQ2">
-        <v>1.04</v>
-      </c>
-      <c r="BR2">
-        <v>1000</v>
-      </c>
-      <c r="BS2">
-        <v>1.04</v>
-      </c>
-      <c r="BT2">
-        <v>1000</v>
-      </c>
-      <c r="BU2">
-        <v>1.04</v>
-      </c>
-      <c r="BV2">
-        <v>1000</v>
-      </c>
-      <c r="BW2">
-        <v>1.04</v>
-      </c>
-      <c r="BX2">
-        <v>1000</v>
-      </c>
-      <c r="BY2">
-        <v>1.04</v>
       </c>
       <c r="BZ2">
         <v>0</v>
@@ -1236,37 +1236,37 @@
         <v>2.66</v>
       </c>
       <c r="G3">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="H3">
         <v>3.4</v>
       </c>
       <c r="I3">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="J3">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="K3">
         <v>2.94</v>
       </c>
       <c r="L3">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="M3">
         <v>1.17</v>
       </c>
       <c r="N3">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="O3">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="P3">
         <v>1.41</v>
       </c>
       <c r="Q3">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="R3">
         <v>1.14</v>
@@ -1278,16 +1278,16 @@
         <v>2.48</v>
       </c>
       <c r="U3">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="V3">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="W3">
         <v>1.57</v>
       </c>
       <c r="X3">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="Y3">
         <v>8.199999999999999</v>
@@ -1296,13 +1296,13 @@
         <v>21</v>
       </c>
       <c r="AA3">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AB3">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AC3">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AD3">
         <v>18</v>
@@ -1311,7 +1311,7 @@
         <v>70</v>
       </c>
       <c r="AF3">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AG3">
         <v>15</v>
@@ -1332,25 +1332,25 @@
         <v>1000</v>
       </c>
       <c r="AM3">
-        <v>310</v>
+        <v>280</v>
       </c>
       <c r="AN3">
         <v>65</v>
       </c>
       <c r="AO3">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AP3">
         <v>6.2</v>
       </c>
       <c r="AQ3">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AR3">
         <v>18.5</v>
       </c>
       <c r="AS3">
-        <v>32</v>
+        <v>60</v>
       </c>
       <c r="AT3">
         <v>6.4</v>
@@ -1359,7 +1359,7 @@
         <v>6.6</v>
       </c>
       <c r="AV3">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AW3">
         <v>55</v>
@@ -1374,7 +1374,7 @@
         <v>26</v>
       </c>
       <c r="BA3">
-        <v>40</v>
+        <v>95</v>
       </c>
       <c r="BB3">
         <v>25</v>
@@ -1398,7 +1398,7 @@
         <v>2.5</v>
       </c>
       <c r="BI3">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="BJ3">
         <v>13</v>
@@ -1410,28 +1410,28 @@
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BN3">
         <v>5.6</v>
       </c>
       <c r="BO3">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="BP3">
         <v>28</v>
       </c>
       <c r="BQ3">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR3">
         <v>1000</v>
       </c>
       <c r="BS3">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BT3">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BU3">
         <v>5.4</v>
@@ -1440,19 +1440,19 @@
         <v>38</v>
       </c>
       <c r="BW3">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="BX3">
         <v>75</v>
       </c>
       <c r="BY3">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BZ3">
         <v>75</v>
       </c>
       <c r="CA3">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="CB3" t="s">
         <v>127</v>
@@ -1475,25 +1475,25 @@
         <v>116</v>
       </c>
       <c r="F4">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="G4">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="H4">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="I4">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="J4">
         <v>3.25</v>
       </c>
       <c r="K4">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="L4">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="M4">
         <v>1.09</v>
@@ -1508,19 +1508,19 @@
         <v>1.79</v>
       </c>
       <c r="Q4">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="R4">
         <v>1.3</v>
       </c>
       <c r="S4">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="T4">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="U4">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="V4">
         <v>1.56</v>
@@ -1538,13 +1538,13 @@
         <v>18</v>
       </c>
       <c r="AA4">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AB4">
         <v>11</v>
       </c>
       <c r="AC4">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD4">
         <v>13</v>
@@ -1592,10 +1592,10 @@
         <v>15</v>
       </c>
       <c r="AS4">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="AT4">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU4">
         <v>5.7</v>
@@ -1604,7 +1604,7 @@
         <v>10.5</v>
       </c>
       <c r="AW4">
-        <v>5.2</v>
+        <v>24</v>
       </c>
       <c r="AX4">
         <v>14</v>
@@ -1616,46 +1616,46 @@
         <v>13.5</v>
       </c>
       <c r="BA4">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BB4">
+        <v>5.7</v>
+      </c>
+      <c r="BC4">
         <v>5.5</v>
       </c>
-      <c r="BC4">
+      <c r="BD4">
+        <v>5.6</v>
+      </c>
+      <c r="BE4">
+        <v>6</v>
+      </c>
+      <c r="BF4">
+        <v>5.5</v>
+      </c>
+      <c r="BG4">
         <v>5.3</v>
       </c>
-      <c r="BD4">
-        <v>5.5</v>
-      </c>
-      <c r="BE4">
-        <v>5.8</v>
-      </c>
-      <c r="BF4">
-        <v>5.3</v>
-      </c>
-      <c r="BG4">
-        <v>5.2</v>
-      </c>
       <c r="BH4">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="BI4">
-        <v>2.56</v>
+        <v>2.66</v>
       </c>
       <c r="BJ4">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK4">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>11</v>
+        <v>4.2</v>
       </c>
       <c r="BN4">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BO4">
         <v>4.5</v>
@@ -1664,37 +1664,37 @@
         <v>1000</v>
       </c>
       <c r="BQ4">
-        <v>8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BR4">
         <v>1000</v>
       </c>
       <c r="BS4">
-        <v>9.199999999999999</v>
+        <v>11.5</v>
       </c>
       <c r="BT4">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BU4">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BV4">
         <v>1000</v>
       </c>
       <c r="BW4">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="BX4">
         <v>1000</v>
       </c>
       <c r="BY4">
-        <v>9.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="BZ4">
         <v>1000</v>
       </c>
       <c r="CA4">
-        <v>8.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="CB4" t="s">
         <v>127</v>
@@ -1723,10 +1723,10 @@
         <v>1.79</v>
       </c>
       <c r="H5">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="I5">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J5">
         <v>4.2</v>
@@ -1741,34 +1741,34 @@
         <v>1.04</v>
       </c>
       <c r="N5">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="O5">
         <v>1.21</v>
       </c>
       <c r="P5">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="Q5">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="R5">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="S5">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="T5">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="U5">
+        <v>2.36</v>
+      </c>
+      <c r="V5">
+        <v>1.25</v>
+      </c>
+      <c r="W5">
         <v>2.26</v>
-      </c>
-      <c r="V5">
-        <v>1.24</v>
-      </c>
-      <c r="W5">
-        <v>2.28</v>
       </c>
       <c r="X5">
         <v>26</v>
@@ -1777,22 +1777,22 @@
         <v>23</v>
       </c>
       <c r="Z5">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AA5">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AB5">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AC5">
         <v>11</v>
       </c>
       <c r="AD5">
-        <v>23</v>
+        <v>19.5</v>
       </c>
       <c r="AE5">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AF5">
         <v>13.5</v>
@@ -1801,10 +1801,10 @@
         <v>10.5</v>
       </c>
       <c r="AH5">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AI5">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AJ5">
         <v>19</v>
@@ -1816,13 +1816,13 @@
         <v>32</v>
       </c>
       <c r="AM5">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AN5">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="AO5">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="AP5">
         <v>18.5</v>
@@ -1834,7 +1834,7 @@
         <v>32</v>
       </c>
       <c r="AS5">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="AT5">
         <v>9.6</v>
@@ -1846,7 +1846,7 @@
         <v>16.5</v>
       </c>
       <c r="AW5">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="AX5">
         <v>10.5</v>
@@ -1858,49 +1858,49 @@
         <v>13</v>
       </c>
       <c r="BA5">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="BB5">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="BC5">
         <v>12.5</v>
       </c>
       <c r="BD5">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="BE5">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="BF5">
         <v>6.8</v>
       </c>
       <c r="BG5">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="BH5">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="BI5">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="BJ5">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BK5">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BL5">
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BN5">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BO5">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="BP5">
         <v>12</v>
@@ -1909,13 +1909,13 @@
         <v>5.5</v>
       </c>
       <c r="BR5">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BS5">
         <v>7</v>
       </c>
       <c r="BT5">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BU5">
         <v>4.7</v>
@@ -1924,16 +1924,16 @@
         <v>1000</v>
       </c>
       <c r="BW5">
+        <v>7.8</v>
+      </c>
+      <c r="BX5">
+        <v>1000</v>
+      </c>
+      <c r="BY5">
         <v>8</v>
       </c>
-      <c r="BX5">
-        <v>1000</v>
-      </c>
-      <c r="BY5">
-        <v>8.199999999999999</v>
-      </c>
       <c r="BZ5">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="CA5">
         <v>6.2</v>
@@ -1959,7 +1959,7 @@
         <v>118</v>
       </c>
       <c r="F6">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="G6">
         <v>2.28</v>
@@ -2130,13 +2130,13 @@
         <v>10.5</v>
       </c>
       <c r="BK6">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="BL6">
         <v>1000</v>
       </c>
       <c r="BM6">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BN6">
         <v>5.1</v>
@@ -2148,37 +2148,37 @@
         <v>17.5</v>
       </c>
       <c r="BQ6">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BR6">
         <v>36</v>
       </c>
       <c r="BS6">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BT6">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BU6">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="BV6">
         <v>1000</v>
       </c>
       <c r="BW6">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BX6">
         <v>1000</v>
       </c>
       <c r="BY6">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="BZ6">
         <v>34</v>
       </c>
       <c r="CA6">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="CB6" t="s">
         <v>127</v>
@@ -2201,166 +2201,166 @@
         <v>119</v>
       </c>
       <c r="F7">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="G7">
-        <v>2.2</v>
+        <v>2.04</v>
       </c>
       <c r="H7">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="I7">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="J7">
         <v>3.2</v>
       </c>
       <c r="K7">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="L7">
         <v>1.01</v>
       </c>
       <c r="M7">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="N7">
-        <v>2.06</v>
+        <v>2.58</v>
       </c>
       <c r="O7">
-        <v>1.47</v>
+        <v>1.54</v>
       </c>
       <c r="P7">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="Q7">
-        <v>2.22</v>
+        <v>2.6</v>
       </c>
       <c r="R7">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="S7">
-        <v>2.68</v>
+        <v>3.45</v>
       </c>
       <c r="T7">
-        <v>1.11</v>
+        <v>2.28</v>
       </c>
       <c r="U7">
-        <v>1.11</v>
+        <v>1.58</v>
       </c>
       <c r="V7">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="W7">
-        <v>1.83</v>
+        <v>1.96</v>
       </c>
       <c r="X7">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Y7">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="Z7">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AA7">
-        <v>1000</v>
+        <v>220</v>
       </c>
       <c r="AB7">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="AC7">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="AD7">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AE7">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AF7">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AG7">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AH7">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AI7">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AJ7">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AK7">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AL7">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AM7">
-        <v>1000</v>
+        <v>290</v>
       </c>
       <c r="AN7">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AO7">
-        <v>1000</v>
+        <v>240</v>
       </c>
       <c r="AP7">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="AQ7">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="AR7">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AS7">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="AT7">
-        <v>1.01</v>
+        <v>3</v>
       </c>
       <c r="AU7">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="AV7">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AW7">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="AX7">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="AY7">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="AZ7">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BA7">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BB7">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BC7">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BD7">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BE7">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BF7">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BG7">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BH7">
         <v>1000</v>
@@ -2446,7 +2446,7 @@
         <v>1.52</v>
       </c>
       <c r="G8">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="H8">
         <v>4.3</v>
@@ -2455,46 +2455,46 @@
         <v>6.2</v>
       </c>
       <c r="J8">
-        <v>4.9</v>
+        <v>4</v>
       </c>
       <c r="K8">
         <v>6.4</v>
       </c>
       <c r="L8">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="M8">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="N8">
-        <v>7.2</v>
+        <v>1.1</v>
       </c>
       <c r="O8">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="P8">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="Q8">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="R8">
-        <v>1.96</v>
+        <v>2.02</v>
       </c>
       <c r="S8">
-        <v>1.82</v>
+        <v>1.77</v>
       </c>
       <c r="T8">
         <v>1.44</v>
       </c>
       <c r="U8">
-        <v>2.78</v>
+        <v>2.84</v>
       </c>
       <c r="V8">
         <v>1.21</v>
       </c>
       <c r="W8">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="X8">
         <v>55</v>
@@ -2509,7 +2509,7 @@
         <v>120</v>
       </c>
       <c r="AB8">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AC8">
         <v>15</v>
@@ -2530,7 +2530,7 @@
         <v>17.5</v>
       </c>
       <c r="AI8">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AJ8">
         <v>20</v>
@@ -2539,70 +2539,70 @@
         <v>16</v>
       </c>
       <c r="AL8">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AM8">
         <v>55</v>
       </c>
       <c r="AN8">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="AO8">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="AP8">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="AQ8">
+        <v>7.2</v>
+      </c>
+      <c r="AR8">
+        <v>7.8</v>
+      </c>
+      <c r="AS8">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AT8">
+        <v>6.2</v>
+      </c>
+      <c r="AU8">
+        <v>5.6</v>
+      </c>
+      <c r="AV8">
+        <v>6.4</v>
+      </c>
+      <c r="AW8">
+        <v>7.6</v>
+      </c>
+      <c r="AX8">
+        <v>5.9</v>
+      </c>
+      <c r="AY8">
+        <v>5.2</v>
+      </c>
+      <c r="AZ8">
+        <v>5.9</v>
+      </c>
+      <c r="BA8">
+        <v>7.4</v>
+      </c>
+      <c r="BB8">
+        <v>6.2</v>
+      </c>
+      <c r="BC8">
+        <v>5.7</v>
+      </c>
+      <c r="BD8">
+        <v>6.2</v>
+      </c>
+      <c r="BE8">
+        <v>7.6</v>
+      </c>
+      <c r="BF8">
+        <v>3.3</v>
+      </c>
+      <c r="BG8">
         <v>6.6</v>
-      </c>
-      <c r="AR8">
-        <v>7.2</v>
-      </c>
-      <c r="AS8">
-        <v>7.6</v>
-      </c>
-      <c r="AT8">
-        <v>5.8</v>
-      </c>
-      <c r="AU8">
-        <v>5.3</v>
-      </c>
-      <c r="AV8">
-        <v>6</v>
-      </c>
-      <c r="AW8">
-        <v>7</v>
-      </c>
-      <c r="AX8">
-        <v>5.5</v>
-      </c>
-      <c r="AY8">
-        <v>4.9</v>
-      </c>
-      <c r="AZ8">
-        <v>5.5</v>
-      </c>
-      <c r="BA8">
-        <v>6.8</v>
-      </c>
-      <c r="BB8">
-        <v>5.8</v>
-      </c>
-      <c r="BC8">
-        <v>5.4</v>
-      </c>
-      <c r="BD8">
-        <v>6</v>
-      </c>
-      <c r="BE8">
-        <v>7</v>
-      </c>
-      <c r="BF8">
-        <v>3.25</v>
-      </c>
-      <c r="BG8">
-        <v>6.2</v>
       </c>
       <c r="BH8">
         <v>1000</v>
@@ -2685,226 +2685,226 @@
         <v>121</v>
       </c>
       <c r="F9">
-        <v>2.32</v>
+        <v>2.48</v>
       </c>
       <c r="G9">
-        <v>3.1</v>
+        <v>2.86</v>
       </c>
       <c r="H9">
-        <v>2.46</v>
+        <v>2.78</v>
       </c>
       <c r="I9">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="J9">
-        <v>2.52</v>
+        <v>2.88</v>
       </c>
       <c r="K9">
+        <v>3.75</v>
+      </c>
+      <c r="L9">
+        <v>1.41</v>
+      </c>
+      <c r="M9">
+        <v>1.07</v>
+      </c>
+      <c r="N9">
+        <v>3.05</v>
+      </c>
+      <c r="O9">
+        <v>1.34</v>
+      </c>
+      <c r="P9">
+        <v>1.81</v>
+      </c>
+      <c r="Q9">
+        <v>1.98</v>
+      </c>
+      <c r="R9">
+        <v>1.31</v>
+      </c>
+      <c r="S9">
+        <v>3.4</v>
+      </c>
+      <c r="T9">
+        <v>1.74</v>
+      </c>
+      <c r="U9">
+        <v>2.06</v>
+      </c>
+      <c r="V9">
+        <v>1.38</v>
+      </c>
+      <c r="W9">
+        <v>1.53</v>
+      </c>
+      <c r="X9">
+        <v>16</v>
+      </c>
+      <c r="Y9">
+        <v>12</v>
+      </c>
+      <c r="Z9">
+        <v>21</v>
+      </c>
+      <c r="AA9">
+        <v>60</v>
+      </c>
+      <c r="AB9">
+        <v>11.5</v>
+      </c>
+      <c r="AC9">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD9">
+        <v>14</v>
+      </c>
+      <c r="AE9">
+        <v>50</v>
+      </c>
+      <c r="AF9">
+        <v>18.5</v>
+      </c>
+      <c r="AG9">
+        <v>13</v>
+      </c>
+      <c r="AH9">
+        <v>18.5</v>
+      </c>
+      <c r="AI9">
+        <v>60</v>
+      </c>
+      <c r="AJ9">
+        <v>48</v>
+      </c>
+      <c r="AK9">
+        <v>44</v>
+      </c>
+      <c r="AL9">
+        <v>55</v>
+      </c>
+      <c r="AM9">
+        <v>120</v>
+      </c>
+      <c r="AN9">
+        <v>32</v>
+      </c>
+      <c r="AO9">
+        <v>40</v>
+      </c>
+      <c r="AP9">
+        <v>1.01</v>
+      </c>
+      <c r="AQ9">
+        <v>1.01</v>
+      </c>
+      <c r="AR9">
+        <v>1.01</v>
+      </c>
+      <c r="AS9">
+        <v>1.01</v>
+      </c>
+      <c r="AT9">
+        <v>1.01</v>
+      </c>
+      <c r="AU9">
+        <v>5</v>
+      </c>
+      <c r="AV9">
+        <v>1.01</v>
+      </c>
+      <c r="AW9">
+        <v>1.01</v>
+      </c>
+      <c r="AX9">
+        <v>1.01</v>
+      </c>
+      <c r="AY9">
+        <v>1.01</v>
+      </c>
+      <c r="AZ9">
+        <v>1.01</v>
+      </c>
+      <c r="BA9">
+        <v>1.01</v>
+      </c>
+      <c r="BB9">
+        <v>1.01</v>
+      </c>
+      <c r="BC9">
+        <v>1.01</v>
+      </c>
+      <c r="BD9">
+        <v>1.01</v>
+      </c>
+      <c r="BE9">
+        <v>1.01</v>
+      </c>
+      <c r="BF9">
+        <v>1.01</v>
+      </c>
+      <c r="BG9">
+        <v>1.01</v>
+      </c>
+      <c r="BH9">
+        <v>3.4</v>
+      </c>
+      <c r="BI9">
+        <v>2.64</v>
+      </c>
+      <c r="BJ9">
+        <v>10</v>
+      </c>
+      <c r="BK9">
+        <v>5.2</v>
+      </c>
+      <c r="BL9">
+        <v>1000</v>
+      </c>
+      <c r="BM9">
+        <v>2.54</v>
+      </c>
+      <c r="BN9">
+        <v>5.8</v>
+      </c>
+      <c r="BO9">
+        <v>3.75</v>
+      </c>
+      <c r="BP9">
+        <v>21</v>
+      </c>
+      <c r="BQ9">
+        <v>7</v>
+      </c>
+      <c r="BR9">
+        <v>1000</v>
+      </c>
+      <c r="BS9">
+        <v>2.42</v>
+      </c>
+      <c r="BT9">
         <v>6.2</v>
       </c>
-      <c r="L9">
-        <v>1.33</v>
-      </c>
-      <c r="M9">
-        <v>1.01</v>
-      </c>
-      <c r="N9">
-        <v>2.92</v>
-      </c>
-      <c r="O9">
-        <v>1.37</v>
-      </c>
-      <c r="P9">
-        <v>1.61</v>
-      </c>
-      <c r="Q9">
-        <v>2.06</v>
-      </c>
-      <c r="R9">
-        <v>1.2</v>
-      </c>
-      <c r="S9">
-        <v>2.56</v>
-      </c>
-      <c r="T9">
-        <v>1.01</v>
-      </c>
-      <c r="U9">
-        <v>1.01</v>
-      </c>
-      <c r="V9">
-        <v>1.36</v>
-      </c>
-      <c r="W9">
-        <v>1.48</v>
-      </c>
-      <c r="X9">
-        <v>1000</v>
-      </c>
-      <c r="Y9">
-        <v>1000</v>
-      </c>
-      <c r="Z9">
-        <v>1000</v>
-      </c>
-      <c r="AA9">
-        <v>1000</v>
-      </c>
-      <c r="AB9">
-        <v>1000</v>
-      </c>
-      <c r="AC9">
-        <v>1000</v>
-      </c>
-      <c r="AD9">
-        <v>1000</v>
-      </c>
-      <c r="AE9">
-        <v>1000</v>
-      </c>
-      <c r="AF9">
-        <v>1000</v>
-      </c>
-      <c r="AG9">
-        <v>1000</v>
-      </c>
-      <c r="AH9">
-        <v>1000</v>
-      </c>
-      <c r="AI9">
-        <v>1000</v>
-      </c>
-      <c r="AJ9">
-        <v>1000</v>
-      </c>
-      <c r="AK9">
-        <v>1000</v>
-      </c>
-      <c r="AL9">
-        <v>1000</v>
-      </c>
-      <c r="AM9">
-        <v>1000</v>
-      </c>
-      <c r="AN9">
-        <v>1000</v>
-      </c>
-      <c r="AO9">
-        <v>1000</v>
-      </c>
-      <c r="AP9">
-        <v>1.03</v>
-      </c>
-      <c r="AQ9">
-        <v>1.03</v>
-      </c>
-      <c r="AR9">
-        <v>1.03</v>
-      </c>
-      <c r="AS9">
-        <v>1.03</v>
-      </c>
-      <c r="AT9">
-        <v>1.03</v>
-      </c>
-      <c r="AU9">
-        <v>1.03</v>
-      </c>
-      <c r="AV9">
-        <v>1.03</v>
-      </c>
-      <c r="AW9">
-        <v>1.03</v>
-      </c>
-      <c r="AX9">
-        <v>1.03</v>
-      </c>
-      <c r="AY9">
-        <v>1.03</v>
-      </c>
-      <c r="AZ9">
-        <v>1.03</v>
-      </c>
-      <c r="BA9">
-        <v>1.03</v>
-      </c>
-      <c r="BB9">
-        <v>1.03</v>
-      </c>
-      <c r="BC9">
-        <v>1.03</v>
-      </c>
-      <c r="BD9">
-        <v>1.03</v>
-      </c>
-      <c r="BE9">
-        <v>1.03</v>
-      </c>
-      <c r="BF9">
-        <v>1.01</v>
-      </c>
-      <c r="BG9">
-        <v>1.01</v>
-      </c>
-      <c r="BH9">
-        <v>1000</v>
-      </c>
-      <c r="BI9">
-        <v>1.01</v>
-      </c>
-      <c r="BJ9">
-        <v>1000</v>
-      </c>
-      <c r="BK9">
-        <v>1.01</v>
-      </c>
-      <c r="BL9">
-        <v>1000</v>
-      </c>
-      <c r="BM9">
-        <v>1.01</v>
-      </c>
-      <c r="BN9">
-        <v>1000</v>
-      </c>
-      <c r="BO9">
-        <v>1.01</v>
-      </c>
-      <c r="BP9">
-        <v>1000</v>
-      </c>
-      <c r="BQ9">
-        <v>1.01</v>
-      </c>
-      <c r="BR9">
-        <v>1000</v>
-      </c>
-      <c r="BS9">
-        <v>1.01</v>
-      </c>
-      <c r="BT9">
-        <v>1000</v>
-      </c>
       <c r="BU9">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BV9">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BW9">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BX9">
         <v>1000</v>
       </c>
       <c r="BY9">
-        <v>1.01</v>
+        <v>2.42</v>
       </c>
       <c r="BZ9">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="CA9">
-        <v>1.01</v>
+        <v>2.4</v>
       </c>
       <c r="CB9" t="s">
         <v>127</v>
@@ -2945,19 +2945,19 @@
         <v>3.85</v>
       </c>
       <c r="L10">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="M10">
         <v>1.07</v>
       </c>
       <c r="N10">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="O10">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="P10">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="Q10">
         <v>1.85</v>
@@ -2966,7 +2966,7 @@
         <v>1.33</v>
       </c>
       <c r="S10">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="T10">
         <v>1.75</v>
@@ -3089,58 +3089,58 @@
         <v>4.1</v>
       </c>
       <c r="BH10">
-        <v>1000</v>
+        <v>3.5</v>
       </c>
       <c r="BI10">
-        <v>1.04</v>
+        <v>2.72</v>
       </c>
       <c r="BJ10">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK10">
-        <v>1.04</v>
+        <v>5.1</v>
       </c>
       <c r="BL10">
         <v>1000</v>
       </c>
       <c r="BM10">
-        <v>1.04</v>
+        <v>2.58</v>
       </c>
       <c r="BN10">
-        <v>1000</v>
+        <v>5.6</v>
       </c>
       <c r="BO10">
-        <v>1.04</v>
+        <v>3.65</v>
       </c>
       <c r="BP10">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="BQ10">
-        <v>1.04</v>
+        <v>6.8</v>
       </c>
       <c r="BR10">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BS10">
-        <v>1.04</v>
+        <v>2.44</v>
       </c>
       <c r="BT10">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="BU10">
-        <v>1.04</v>
+        <v>4</v>
       </c>
       <c r="BV10">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="BW10">
-        <v>1.04</v>
+        <v>7.4</v>
       </c>
       <c r="BX10">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BY10">
-        <v>1.04</v>
+        <v>2.46</v>
       </c>
       <c r="BZ10">
         <v>0</v>
@@ -3169,166 +3169,166 @@
         <v>123</v>
       </c>
       <c r="F11">
-        <v>1.77</v>
+        <v>1.83</v>
       </c>
       <c r="G11">
-        <v>1.98</v>
+        <v>1.89</v>
       </c>
       <c r="H11">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="I11">
+        <v>5</v>
+      </c>
+      <c r="J11">
+        <v>3.65</v>
+      </c>
+      <c r="K11">
+        <v>4.3</v>
+      </c>
+      <c r="L11">
+        <v>1.01</v>
+      </c>
+      <c r="M11">
+        <v>1.09</v>
+      </c>
+      <c r="N11">
+        <v>2.84</v>
+      </c>
+      <c r="O11">
+        <v>1.45</v>
+      </c>
+      <c r="P11">
+        <v>1.68</v>
+      </c>
+      <c r="Q11">
+        <v>2.28</v>
+      </c>
+      <c r="R11">
+        <v>1.24</v>
+      </c>
+      <c r="S11">
+        <v>4</v>
+      </c>
+      <c r="T11">
+        <v>2.16</v>
+      </c>
+      <c r="U11">
+        <v>1.73</v>
+      </c>
+      <c r="V11">
+        <v>1.25</v>
+      </c>
+      <c r="W11">
+        <v>2.12</v>
+      </c>
+      <c r="X11">
+        <v>14.5</v>
+      </c>
+      <c r="Y11">
+        <v>13</v>
+      </c>
+      <c r="Z11">
+        <v>38</v>
+      </c>
+      <c r="AA11">
+        <v>180</v>
+      </c>
+      <c r="AB11">
+        <v>6.8</v>
+      </c>
+      <c r="AC11">
+        <v>9.4</v>
+      </c>
+      <c r="AD11">
+        <v>20</v>
+      </c>
+      <c r="AE11">
+        <v>110</v>
+      </c>
+      <c r="AF11">
+        <v>10</v>
+      </c>
+      <c r="AG11">
+        <v>11</v>
+      </c>
+      <c r="AH11">
+        <v>29</v>
+      </c>
+      <c r="AI11">
+        <v>120</v>
+      </c>
+      <c r="AJ11">
+        <v>21</v>
+      </c>
+      <c r="AK11">
+        <v>24</v>
+      </c>
+      <c r="AL11">
+        <v>55</v>
+      </c>
+      <c r="AM11">
+        <v>260</v>
+      </c>
+      <c r="AN11">
+        <v>18</v>
+      </c>
+      <c r="AO11">
+        <v>170</v>
+      </c>
+      <c r="AP11">
+        <v>5.8</v>
+      </c>
+      <c r="AQ11">
+        <v>5.5</v>
+      </c>
+      <c r="AR11">
+        <v>7.6</v>
+      </c>
+      <c r="AS11">
+        <v>9</v>
+      </c>
+      <c r="AT11">
+        <v>3.95</v>
+      </c>
+      <c r="AU11">
+        <v>4.7</v>
+      </c>
+      <c r="AV11">
+        <v>6.4</v>
+      </c>
+      <c r="AW11">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AX11">
+        <v>4.9</v>
+      </c>
+      <c r="AY11">
+        <v>5.1</v>
+      </c>
+      <c r="AZ11">
+        <v>7.2</v>
+      </c>
+      <c r="BA11">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BB11">
+        <v>6.6</v>
+      </c>
+      <c r="BC11">
+        <v>6.8</v>
+      </c>
+      <c r="BD11">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BE11">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BF11">
         <v>6.2</v>
       </c>
-      <c r="J11">
-        <v>3.25</v>
-      </c>
-      <c r="K11">
-        <v>3.75</v>
-      </c>
-      <c r="L11">
-        <v>1.01</v>
-      </c>
-      <c r="M11">
-        <v>1.01</v>
-      </c>
-      <c r="N11">
-        <v>2.9</v>
-      </c>
-      <c r="O11">
-        <v>1.36</v>
-      </c>
-      <c r="P11">
-        <v>1.7</v>
-      </c>
-      <c r="Q11">
-        <v>2.12</v>
-      </c>
-      <c r="R11">
-        <v>1.25</v>
-      </c>
-      <c r="S11">
-        <v>3.5</v>
-      </c>
-      <c r="T11">
-        <v>1.11</v>
-      </c>
-      <c r="U11">
-        <v>1.11</v>
-      </c>
-      <c r="V11">
-        <v>1.19</v>
-      </c>
-      <c r="W11">
-        <v>2.02</v>
-      </c>
-      <c r="X11">
-        <v>1000</v>
-      </c>
-      <c r="Y11">
-        <v>1000</v>
-      </c>
-      <c r="Z11">
-        <v>1000</v>
-      </c>
-      <c r="AA11">
-        <v>1000</v>
-      </c>
-      <c r="AB11">
-        <v>1000</v>
-      </c>
-      <c r="AC11">
-        <v>1000</v>
-      </c>
-      <c r="AD11">
-        <v>1000</v>
-      </c>
-      <c r="AE11">
-        <v>1000</v>
-      </c>
-      <c r="AF11">
-        <v>1000</v>
-      </c>
-      <c r="AG11">
-        <v>1000</v>
-      </c>
-      <c r="AH11">
-        <v>1000</v>
-      </c>
-      <c r="AI11">
-        <v>1000</v>
-      </c>
-      <c r="AJ11">
-        <v>1000</v>
-      </c>
-      <c r="AK11">
-        <v>1000</v>
-      </c>
-      <c r="AL11">
-        <v>1000</v>
-      </c>
-      <c r="AM11">
-        <v>1000</v>
-      </c>
-      <c r="AN11">
-        <v>1000</v>
-      </c>
-      <c r="AO11">
-        <v>1000</v>
-      </c>
-      <c r="AP11">
-        <v>1.01</v>
-      </c>
-      <c r="AQ11">
-        <v>1.01</v>
-      </c>
-      <c r="AR11">
-        <v>1.01</v>
-      </c>
-      <c r="AS11">
-        <v>1.01</v>
-      </c>
-      <c r="AT11">
-        <v>1.01</v>
-      </c>
-      <c r="AU11">
-        <v>1.01</v>
-      </c>
-      <c r="AV11">
-        <v>1.01</v>
-      </c>
-      <c r="AW11">
-        <v>1.01</v>
-      </c>
-      <c r="AX11">
-        <v>1.01</v>
-      </c>
-      <c r="AY11">
-        <v>1.01</v>
-      </c>
-      <c r="AZ11">
-        <v>1.01</v>
-      </c>
-      <c r="BA11">
-        <v>1.01</v>
-      </c>
-      <c r="BB11">
-        <v>1.01</v>
-      </c>
-      <c r="BC11">
-        <v>1.01</v>
-      </c>
-      <c r="BD11">
-        <v>1.01</v>
-      </c>
-      <c r="BE11">
-        <v>1.01</v>
-      </c>
-      <c r="BF11">
-        <v>1.01</v>
-      </c>
       <c r="BG11">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="BH11">
         <v>1000</v>
@@ -3414,7 +3414,7 @@
         <v>2.38</v>
       </c>
       <c r="G12">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="H12">
         <v>3.55</v>
@@ -3429,7 +3429,7 @@
         <v>3.15</v>
       </c>
       <c r="L12">
-        <v>1.01</v>
+        <v>1.47</v>
       </c>
       <c r="M12">
         <v>1.12</v>
@@ -3519,7 +3519,7 @@
         <v>100</v>
       </c>
       <c r="AP12">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AQ12">
         <v>9</v>
@@ -3573,64 +3573,64 @@
         <v>6.8</v>
       </c>
       <c r="BH12">
-        <v>3.15</v>
+        <v>2.74</v>
       </c>
       <c r="BI12">
-        <v>2.22</v>
+        <v>2.52</v>
       </c>
       <c r="BJ12">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="BK12">
-        <v>2.98</v>
+        <v>5.6</v>
       </c>
       <c r="BL12">
         <v>1000</v>
       </c>
       <c r="BM12">
-        <v>3.65</v>
+        <v>10.5</v>
       </c>
       <c r="BN12">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BO12">
-        <v>3.4</v>
+        <v>4.5</v>
       </c>
       <c r="BP12">
         <v>30</v>
       </c>
       <c r="BQ12">
-        <v>3.25</v>
+        <v>7.4</v>
       </c>
       <c r="BR12">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BS12">
-        <v>3.45</v>
+        <v>9</v>
       </c>
       <c r="BT12">
-        <v>9.199999999999999</v>
+        <v>6.6</v>
       </c>
       <c r="BU12">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="BV12">
         <v>50</v>
       </c>
       <c r="BW12">
-        <v>3.4</v>
+        <v>8.6</v>
       </c>
       <c r="BX12">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="BY12">
-        <v>3.5</v>
+        <v>9.6</v>
       </c>
       <c r="BZ12">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="CA12">
-        <v>3.45</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CB12" t="s">
         <v>127</v>
@@ -3653,226 +3653,226 @@
         <v>125</v>
       </c>
       <c r="F13">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="G13">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="H13">
         <v>3.7</v>
       </c>
       <c r="I13">
-        <v>5.4</v>
+        <v>4.9</v>
       </c>
       <c r="J13">
         <v>2.8</v>
       </c>
       <c r="K13">
-        <v>4.1</v>
+        <v>3.25</v>
       </c>
       <c r="L13">
-        <v>1.01</v>
+        <v>1.54</v>
       </c>
       <c r="M13">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="N13">
-        <v>1.97</v>
+        <v>2.22</v>
       </c>
       <c r="O13">
-        <v>1.51</v>
+        <v>1.55</v>
       </c>
       <c r="P13">
-        <v>1.35</v>
+        <v>1.45</v>
       </c>
       <c r="Q13">
         <v>2.44</v>
       </c>
       <c r="R13">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="S13">
-        <v>2.96</v>
+        <v>1.05</v>
       </c>
       <c r="T13">
-        <v>1.11</v>
+        <v>2.2</v>
       </c>
       <c r="U13">
-        <v>1.11</v>
+        <v>1.67</v>
       </c>
       <c r="V13">
         <v>1.26</v>
       </c>
       <c r="W13">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="X13">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="Y13">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="Z13">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AA13">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AB13">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="AC13">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD13">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AE13">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AF13">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AG13">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AH13">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AI13">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AJ13">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AK13">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AL13">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AM13">
-        <v>1000</v>
+        <v>270</v>
       </c>
       <c r="AN13">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AO13">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AP13">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="AQ13">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="AR13">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AS13">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="AT13">
-        <v>1.01</v>
+        <v>3.1</v>
       </c>
       <c r="AU13">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="AV13">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AW13">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="AX13">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="AY13">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="AZ13">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BA13">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BB13">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BC13">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BD13">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BE13">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BF13">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BG13">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BH13">
-        <v>1000</v>
+        <v>2.84</v>
       </c>
       <c r="BI13">
-        <v>1.04</v>
+        <v>2.18</v>
       </c>
       <c r="BJ13">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="BK13">
-        <v>1.04</v>
+        <v>4.3</v>
       </c>
       <c r="BL13">
         <v>1000</v>
       </c>
       <c r="BM13">
-        <v>1.04</v>
+        <v>1.94</v>
       </c>
       <c r="BN13">
-        <v>1000</v>
+        <v>5.4</v>
       </c>
       <c r="BO13">
-        <v>1.04</v>
+        <v>2.9</v>
       </c>
       <c r="BP13">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BQ13">
-        <v>1.04</v>
+        <v>4.9</v>
       </c>
       <c r="BR13">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BS13">
-        <v>1.04</v>
+        <v>5.6</v>
       </c>
       <c r="BT13">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BU13">
-        <v>1.04</v>
+        <v>3.55</v>
       </c>
       <c r="BV13">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BW13">
-        <v>1.04</v>
+        <v>5.6</v>
       </c>
       <c r="BX13">
         <v>1000</v>
       </c>
       <c r="BY13">
-        <v>1.04</v>
+        <v>5.8</v>
       </c>
       <c r="BZ13">
         <v>1000</v>
       </c>
       <c r="CA13">
-        <v>1.04</v>
+        <v>5.7</v>
       </c>
       <c r="CB13" t="s">
         <v>127</v>
@@ -3907,7 +3907,7 @@
         <v>110</v>
       </c>
       <c r="J14">
-        <v>1.72</v>
+        <v>1.11</v>
       </c>
       <c r="K14">
         <v>4.2</v>
@@ -3943,7 +3943,7 @@
         <v>1.01</v>
       </c>
       <c r="V14">
-        <v>1.66</v>
+        <v>1.1</v>
       </c>
       <c r="W14">
         <v>1.01</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-06.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-06.xlsx
@@ -397,7 +397,7 @@
     <t>Always Ready</t>
   </si>
   <si>
-    <t>2026-08-05 04:04:30</t>
+    <t>2026-08-05 06:11:50</t>
   </si>
 </sst>
 </file>
@@ -991,220 +991,220 @@
         <v>114</v>
       </c>
       <c r="F2">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="G2">
-        <v>1.23</v>
+        <v>1.17</v>
       </c>
       <c r="H2">
-        <v>12.5</v>
+        <v>21</v>
       </c>
       <c r="I2">
-        <v>19.5</v>
+        <v>26</v>
       </c>
       <c r="J2">
-        <v>8</v>
+        <v>9.6</v>
       </c>
       <c r="K2">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="L2">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="M2">
         <v>1.01</v>
       </c>
       <c r="N2">
-        <v>3.45</v>
+        <v>9</v>
       </c>
       <c r="O2">
         <v>1.09</v>
       </c>
       <c r="P2">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="Q2">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="R2">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="S2">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="T2">
-        <v>1.77</v>
+        <v>2</v>
       </c>
       <c r="U2">
-        <v>1.97</v>
+        <v>1.76</v>
       </c>
       <c r="V2">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="W2">
-        <v>5</v>
+        <v>6.8</v>
       </c>
       <c r="X2">
-        <v>70</v>
+        <v>950</v>
       </c>
       <c r="Y2">
         <v>950</v>
       </c>
       <c r="Z2">
+        <v>280</v>
+      </c>
+      <c r="AA2">
+        <v>1000</v>
+      </c>
+      <c r="AB2">
+        <v>18</v>
+      </c>
+      <c r="AC2">
+        <v>27</v>
+      </c>
+      <c r="AD2">
+        <v>90</v>
+      </c>
+      <c r="AE2">
+        <v>380</v>
+      </c>
+      <c r="AF2">
+        <v>11</v>
+      </c>
+      <c r="AG2">
+        <v>16</v>
+      </c>
+      <c r="AH2">
+        <v>48</v>
+      </c>
+      <c r="AI2">
+        <v>230</v>
+      </c>
+      <c r="AJ2">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AK2">
+        <v>16.5</v>
+      </c>
+      <c r="AL2">
+        <v>48</v>
+      </c>
+      <c r="AM2">
         <v>200</v>
       </c>
-      <c r="AA2">
-        <v>610</v>
-      </c>
-      <c r="AB2">
-        <v>19</v>
-      </c>
-      <c r="AC2">
-        <v>24</v>
-      </c>
-      <c r="AD2">
-        <v>65</v>
-      </c>
-      <c r="AE2">
-        <v>220</v>
-      </c>
-      <c r="AF2">
+      <c r="AN2">
+        <v>2.62</v>
+      </c>
+      <c r="AO2">
+        <v>390</v>
+      </c>
+      <c r="AP2">
+        <v>7.6</v>
+      </c>
+      <c r="AQ2">
+        <v>8</v>
+      </c>
+      <c r="AR2">
+        <v>8.6</v>
+      </c>
+      <c r="AS2">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AT2">
         <v>13</v>
       </c>
-      <c r="AG2">
-        <v>15</v>
-      </c>
-      <c r="AH2">
-        <v>34</v>
-      </c>
-      <c r="AI2">
-        <v>150</v>
-      </c>
-      <c r="AJ2">
-        <v>12</v>
-      </c>
-      <c r="AK2">
-        <v>15</v>
-      </c>
-      <c r="AL2">
-        <v>34</v>
-      </c>
-      <c r="AM2">
-        <v>130</v>
-      </c>
-      <c r="AN2">
-        <v>2.82</v>
-      </c>
-      <c r="AO2">
-        <v>190</v>
-      </c>
-      <c r="AP2">
-        <v>2.02</v>
-      </c>
-      <c r="AQ2">
-        <v>7.2</v>
-      </c>
-      <c r="AR2">
-        <v>24</v>
-      </c>
-      <c r="AS2">
-        <v>2.06</v>
-      </c>
-      <c r="AT2">
-        <v>5.6</v>
-      </c>
       <c r="AU2">
-        <v>5.9</v>
+        <v>20</v>
       </c>
       <c r="AV2">
-        <v>2.02</v>
+        <v>8</v>
       </c>
       <c r="AW2">
-        <v>19.5</v>
+        <v>8.6</v>
       </c>
       <c r="AX2">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AY2">
+        <v>12.5</v>
+      </c>
+      <c r="AZ2">
+        <v>7.4</v>
+      </c>
+      <c r="BA2">
+        <v>8.4</v>
+      </c>
+      <c r="BB2">
+        <v>7.6</v>
+      </c>
+      <c r="BC2">
+        <v>11</v>
+      </c>
+      <c r="BD2">
+        <v>32</v>
+      </c>
+      <c r="BE2">
+        <v>8.4</v>
+      </c>
+      <c r="BF2">
+        <v>2.24</v>
+      </c>
+      <c r="BG2">
+        <v>8.6</v>
+      </c>
+      <c r="BH2">
+        <v>6.6</v>
+      </c>
+      <c r="BI2">
         <v>4.9</v>
       </c>
-      <c r="AY2">
-        <v>5.1</v>
-      </c>
-      <c r="AZ2">
-        <v>14</v>
-      </c>
-      <c r="BA2">
-        <v>18.5</v>
-      </c>
-      <c r="BB2">
-        <v>4.7</v>
-      </c>
-      <c r="BC2">
-        <v>5.1</v>
-      </c>
-      <c r="BD2">
+      <c r="BJ2">
+        <v>15.5</v>
+      </c>
+      <c r="BK2">
+        <v>5.7</v>
+      </c>
+      <c r="BL2">
+        <v>1000</v>
+      </c>
+      <c r="BM2">
+        <v>8.4</v>
+      </c>
+      <c r="BN2">
+        <v>4.3</v>
+      </c>
+      <c r="BO2">
+        <v>3.3</v>
+      </c>
+      <c r="BP2">
+        <v>6.2</v>
+      </c>
+      <c r="BQ2">
+        <v>4.5</v>
+      </c>
+      <c r="BR2">
+        <v>21</v>
+      </c>
+      <c r="BS2">
+        <v>6.2</v>
+      </c>
+      <c r="BT2">
+        <v>23</v>
+      </c>
+      <c r="BU2">
         <v>6.4</v>
       </c>
-      <c r="BE2">
-        <v>7.4</v>
-      </c>
-      <c r="BF2">
-        <v>2.36</v>
-      </c>
-      <c r="BG2">
-        <v>2.06</v>
-      </c>
-      <c r="BH2">
-        <v>7</v>
-      </c>
-      <c r="BI2">
-        <v>3.75</v>
-      </c>
-      <c r="BJ2">
-        <v>13</v>
-      </c>
-      <c r="BK2">
-        <v>4.9</v>
-      </c>
-      <c r="BL2">
-        <v>1000</v>
-      </c>
-      <c r="BM2">
-        <v>7.4</v>
-      </c>
-      <c r="BN2">
-        <v>4.7</v>
-      </c>
-      <c r="BO2">
-        <v>2.96</v>
-      </c>
-      <c r="BP2">
-        <v>6.8</v>
-      </c>
-      <c r="BQ2">
-        <v>3.65</v>
-      </c>
-      <c r="BR2">
-        <v>18.5</v>
-      </c>
-      <c r="BS2">
-        <v>5.6</v>
-      </c>
-      <c r="BT2">
-        <v>18.5</v>
-      </c>
-      <c r="BU2">
-        <v>5.6</v>
-      </c>
       <c r="BV2">
         <v>1000</v>
       </c>
       <c r="BW2">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="BX2">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="BY2">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ2">
         <v>0</v>
@@ -1236,28 +1236,28 @@
         <v>2.66</v>
       </c>
       <c r="G3">
-        <v>2.76</v>
+        <v>2.72</v>
       </c>
       <c r="H3">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="I3">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="J3">
         <v>2.88</v>
       </c>
       <c r="K3">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="L3">
         <v>1.72</v>
       </c>
       <c r="M3">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="N3">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="O3">
         <v>1.73</v>
@@ -1275,34 +1275,34 @@
         <v>7.6</v>
       </c>
       <c r="T3">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="U3">
         <v>1.64</v>
       </c>
       <c r="V3">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="W3">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="X3">
         <v>6.8</v>
       </c>
       <c r="Y3">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="Z3">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AA3">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AB3">
+        <v>6.8</v>
+      </c>
+      <c r="AC3">
         <v>7</v>
-      </c>
-      <c r="AC3">
-        <v>7.2</v>
       </c>
       <c r="AD3">
         <v>18</v>
@@ -1332,19 +1332,19 @@
         <v>1000</v>
       </c>
       <c r="AM3">
-        <v>280</v>
+        <v>330</v>
       </c>
       <c r="AN3">
         <v>65</v>
       </c>
       <c r="AO3">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AP3">
         <v>6.2</v>
       </c>
       <c r="AQ3">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AR3">
         <v>18.5</v>
@@ -1359,7 +1359,7 @@
         <v>6.6</v>
       </c>
       <c r="AV3">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AW3">
         <v>55</v>
@@ -1377,10 +1377,10 @@
         <v>95</v>
       </c>
       <c r="BB3">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="BC3">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="BD3">
         <v>38</v>
@@ -1392,7 +1392,7 @@
         <v>50</v>
       </c>
       <c r="BG3">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BH3">
         <v>2.5</v>
@@ -1404,16 +1404,16 @@
         <v>13</v>
       </c>
       <c r="BK3">
-        <v>9.6</v>
+        <v>6.6</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BN3">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BO3">
         <v>4.7</v>
@@ -1422,13 +1422,13 @@
         <v>28</v>
       </c>
       <c r="BQ3">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BR3">
         <v>1000</v>
       </c>
       <c r="BS3">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BT3">
         <v>6.4</v>
@@ -1440,19 +1440,19 @@
         <v>38</v>
       </c>
       <c r="BW3">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BX3">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="BY3">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BZ3">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="CA3">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="CB3" t="s">
         <v>127</v>
@@ -1475,184 +1475,184 @@
         <v>116</v>
       </c>
       <c r="F4">
+        <v>2.96</v>
+      </c>
+      <c r="G4">
+        <v>3.2</v>
+      </c>
+      <c r="H4">
+        <v>2.72</v>
+      </c>
+      <c r="I4">
         <v>2.88</v>
       </c>
-      <c r="G4">
-        <v>3.1</v>
-      </c>
-      <c r="H4">
-        <v>2.62</v>
-      </c>
-      <c r="I4">
+      <c r="J4">
+        <v>3.05</v>
+      </c>
+      <c r="K4">
+        <v>3.3</v>
+      </c>
+      <c r="L4">
+        <v>1.59</v>
+      </c>
+      <c r="M4">
+        <v>1.12</v>
+      </c>
+      <c r="N4">
         <v>2.8</v>
       </c>
-      <c r="J4">
-        <v>3.25</v>
-      </c>
-      <c r="K4">
-        <v>3.55</v>
-      </c>
-      <c r="L4">
-        <v>1.45</v>
-      </c>
-      <c r="M4">
-        <v>1.09</v>
-      </c>
-      <c r="N4">
-        <v>3.4</v>
-      </c>
       <c r="O4">
-        <v>1.38</v>
+        <v>1.51</v>
       </c>
       <c r="P4">
-        <v>1.79</v>
+        <v>1.6</v>
       </c>
       <c r="Q4">
-        <v>2.16</v>
+        <v>2.6</v>
       </c>
       <c r="R4">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="S4">
-        <v>4</v>
+        <v>5.1</v>
       </c>
       <c r="T4">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="U4">
-        <v>2.04</v>
+        <v>1.84</v>
       </c>
       <c r="V4">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="W4">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="X4">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="Y4">
+        <v>9</v>
+      </c>
+      <c r="Z4">
+        <v>17</v>
+      </c>
+      <c r="AA4">
+        <v>60</v>
+      </c>
+      <c r="AB4">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AC4">
+        <v>7</v>
+      </c>
+      <c r="AD4">
+        <v>13.5</v>
+      </c>
+      <c r="AE4">
+        <v>60</v>
+      </c>
+      <c r="AF4">
+        <v>19.5</v>
+      </c>
+      <c r="AG4">
+        <v>20</v>
+      </c>
+      <c r="AH4">
+        <v>29</v>
+      </c>
+      <c r="AI4">
+        <v>75</v>
+      </c>
+      <c r="AJ4">
+        <v>70</v>
+      </c>
+      <c r="AK4">
+        <v>60</v>
+      </c>
+      <c r="AL4">
+        <v>80</v>
+      </c>
+      <c r="AM4">
+        <v>180</v>
+      </c>
+      <c r="AN4">
+        <v>65</v>
+      </c>
+      <c r="AO4">
+        <v>55</v>
+      </c>
+      <c r="AP4">
+        <v>7.2</v>
+      </c>
+      <c r="AQ4">
+        <v>7.6</v>
+      </c>
+      <c r="AR4">
         <v>12</v>
       </c>
-      <c r="Z4">
-        <v>18</v>
-      </c>
-      <c r="AA4">
-        <v>50</v>
-      </c>
-      <c r="AB4">
+      <c r="AS4">
+        <v>7.6</v>
+      </c>
+      <c r="AT4">
+        <v>8</v>
+      </c>
+      <c r="AU4">
+        <v>6.2</v>
+      </c>
+      <c r="AV4">
         <v>11</v>
       </c>
-      <c r="AC4">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AD4">
-        <v>13</v>
-      </c>
-      <c r="AE4">
-        <v>34</v>
-      </c>
-      <c r="AF4">
-        <v>23</v>
-      </c>
-      <c r="AG4">
-        <v>13.5</v>
-      </c>
-      <c r="AH4">
-        <v>22</v>
-      </c>
-      <c r="AI4">
-        <v>50</v>
-      </c>
-      <c r="AJ4">
-        <v>60</v>
-      </c>
-      <c r="AK4">
-        <v>44</v>
-      </c>
-      <c r="AL4">
-        <v>55</v>
-      </c>
-      <c r="AM4">
-        <v>130</v>
-      </c>
-      <c r="AN4">
-        <v>44</v>
-      </c>
-      <c r="AO4">
-        <v>34</v>
-      </c>
-      <c r="AP4">
-        <v>9</v>
-      </c>
-      <c r="AQ4">
-        <v>8.6</v>
-      </c>
-      <c r="AR4">
-        <v>15</v>
-      </c>
-      <c r="AS4">
-        <v>5.6</v>
-      </c>
-      <c r="AT4">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AU4">
-        <v>5.7</v>
-      </c>
-      <c r="AV4">
+      <c r="AW4">
+        <v>28</v>
+      </c>
+      <c r="AX4">
         <v>10.5</v>
       </c>
-      <c r="AW4">
-        <v>24</v>
-      </c>
-      <c r="AX4">
-        <v>14</v>
-      </c>
       <c r="AY4">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AZ4">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="BA4">
-        <v>5.6</v>
+        <v>7.8</v>
       </c>
       <c r="BB4">
-        <v>5.7</v>
+        <v>7.8</v>
       </c>
       <c r="BC4">
-        <v>5.5</v>
+        <v>32</v>
       </c>
       <c r="BD4">
-        <v>5.6</v>
+        <v>8</v>
       </c>
       <c r="BE4">
-        <v>6</v>
+        <v>8.4</v>
       </c>
       <c r="BF4">
-        <v>5.5</v>
+        <v>7.8</v>
       </c>
       <c r="BG4">
-        <v>5.3</v>
+        <v>7.6</v>
       </c>
       <c r="BH4">
-        <v>3.2</v>
+        <v>2.78</v>
       </c>
       <c r="BI4">
-        <v>2.66</v>
+        <v>2.36</v>
       </c>
       <c r="BJ4">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="BK4">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>4.2</v>
+        <v>2.34</v>
       </c>
       <c r="BN4">
         <v>6</v>
@@ -1664,13 +1664,13 @@
         <v>1000</v>
       </c>
       <c r="BQ4">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BR4">
         <v>1000</v>
       </c>
       <c r="BS4">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BT4">
         <v>5.6</v>
@@ -1682,19 +1682,19 @@
         <v>1000</v>
       </c>
       <c r="BW4">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="BX4">
         <v>1000</v>
       </c>
       <c r="BY4">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BZ4">
         <v>1000</v>
       </c>
       <c r="CA4">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="CB4" t="s">
         <v>127</v>
@@ -1720,13 +1720,13 @@
         <v>1.74</v>
       </c>
       <c r="G5">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="H5">
         <v>4.6</v>
       </c>
       <c r="I5">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J5">
         <v>4.2</v>
@@ -1744,7 +1744,7 @@
         <v>5.3</v>
       </c>
       <c r="O5">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="P5">
         <v>2.46</v>
@@ -1753,16 +1753,16 @@
         <v>1.64</v>
       </c>
       <c r="R5">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="S5">
         <v>2.62</v>
       </c>
       <c r="T5">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="U5">
-        <v>2.36</v>
+        <v>2.3</v>
       </c>
       <c r="V5">
         <v>1.25</v>
@@ -1789,7 +1789,7 @@
         <v>11</v>
       </c>
       <c r="AD5">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AE5">
         <v>60</v>
@@ -1819,7 +1819,7 @@
         <v>80</v>
       </c>
       <c r="AN5">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AO5">
         <v>48</v>
@@ -1834,7 +1834,7 @@
         <v>32</v>
       </c>
       <c r="AS5">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="AT5">
         <v>9.6</v>
@@ -1846,7 +1846,7 @@
         <v>16.5</v>
       </c>
       <c r="AW5">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="AX5">
         <v>10.5</v>
@@ -1858,7 +1858,7 @@
         <v>13</v>
       </c>
       <c r="BA5">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="BB5">
         <v>14.5</v>
@@ -1867,43 +1867,43 @@
         <v>12.5</v>
       </c>
       <c r="BD5">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="BE5">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="BF5">
         <v>6.8</v>
       </c>
       <c r="BG5">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="BH5">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BI5">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="BJ5">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK5">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BL5">
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BN5">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BO5">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="BP5">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BQ5">
         <v>5.5</v>
@@ -1912,31 +1912,31 @@
         <v>23</v>
       </c>
       <c r="BS5">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BT5">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BU5">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BV5">
         <v>1000</v>
       </c>
       <c r="BW5">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX5">
         <v>1000</v>
       </c>
       <c r="BY5">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BZ5">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="CA5">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="CB5" t="s">
         <v>127</v>
@@ -1962,7 +1962,7 @@
         <v>2.16</v>
       </c>
       <c r="G6">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="H6">
         <v>3.7</v>
@@ -1971,7 +1971,7 @@
         <v>4</v>
       </c>
       <c r="J6">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K6">
         <v>3.5</v>
@@ -1989,19 +1989,19 @@
         <v>1.39</v>
       </c>
       <c r="P6">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="Q6">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="R6">
         <v>1.29</v>
       </c>
       <c r="S6">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="T6">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="U6">
         <v>1.96</v>
@@ -2028,7 +2028,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AC6">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD6">
         <v>16.5</v>
@@ -2067,16 +2067,16 @@
         <v>65</v>
       </c>
       <c r="AP6">
-        <v>5.2</v>
+        <v>10</v>
       </c>
       <c r="AQ6">
         <v>9.199999999999999</v>
       </c>
       <c r="AR6">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AS6">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AT6">
         <v>7.4</v>
@@ -2088,10 +2088,10 @@
         <v>13.5</v>
       </c>
       <c r="AW6">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AX6">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="AY6">
         <v>9.4</v>
@@ -2100,25 +2100,25 @@
         <v>16.5</v>
       </c>
       <c r="BA6">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BB6">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="BC6">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BD6">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BE6">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BF6">
         <v>15.5</v>
       </c>
       <c r="BG6">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BH6">
         <v>3.25</v>
@@ -2204,58 +2204,58 @@
         <v>1.85</v>
       </c>
       <c r="G7">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="H7">
         <v>4.8</v>
       </c>
       <c r="I7">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="J7">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="K7">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="L7">
         <v>1.01</v>
       </c>
       <c r="M7">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="N7">
-        <v>2.58</v>
+        <v>2.52</v>
       </c>
       <c r="O7">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="P7">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="Q7">
-        <v>2.6</v>
+        <v>2.54</v>
       </c>
       <c r="R7">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="S7">
-        <v>3.45</v>
+        <v>1.05</v>
       </c>
       <c r="T7">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="U7">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="V7">
         <v>1.19</v>
       </c>
       <c r="W7">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="X7">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="Y7">
         <v>15.5</v>
@@ -2288,28 +2288,28 @@
         <v>34</v>
       </c>
       <c r="AI7">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="AJ7">
         <v>27</v>
       </c>
       <c r="AK7">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AL7">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AM7">
-        <v>290</v>
+        <v>310</v>
       </c>
       <c r="AN7">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AO7">
-        <v>240</v>
+        <v>260</v>
       </c>
       <c r="AP7">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="AQ7">
         <v>3.95</v>
@@ -2318,7 +2318,7 @@
         <v>4.8</v>
       </c>
       <c r="AS7">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="AT7">
         <v>3</v>
@@ -2339,7 +2339,7 @@
         <v>3.75</v>
       </c>
       <c r="AZ7">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BA7">
         <v>5.1</v>
@@ -2455,13 +2455,13 @@
         <v>6.2</v>
       </c>
       <c r="J8">
-        <v>4</v>
+        <v>1.1</v>
       </c>
       <c r="K8">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="L8">
-        <v>1.17</v>
+        <v>1.01</v>
       </c>
       <c r="M8">
         <v>1.01</v>
@@ -2500,7 +2500,7 @@
         <v>55</v>
       </c>
       <c r="Y8">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="Z8">
         <v>60</v>
@@ -2530,7 +2530,7 @@
         <v>17.5</v>
       </c>
       <c r="AI8">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AJ8">
         <v>20</v>
@@ -2548,7 +2548,7 @@
         <v>4.8</v>
       </c>
       <c r="AO8">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AP8">
         <v>7.6</v>
@@ -2599,7 +2599,7 @@
         <v>7.6</v>
       </c>
       <c r="BF8">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="BG8">
         <v>6.6</v>
@@ -2694,28 +2694,28 @@
         <v>2.78</v>
       </c>
       <c r="I9">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="J9">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="K9">
         <v>3.75</v>
       </c>
       <c r="L9">
-        <v>1.41</v>
+        <v>1.35</v>
       </c>
       <c r="M9">
         <v>1.07</v>
       </c>
       <c r="N9">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="O9">
         <v>1.34</v>
       </c>
       <c r="P9">
-        <v>1.81</v>
+        <v>1.78</v>
       </c>
       <c r="Q9">
         <v>1.98</v>
@@ -2724,7 +2724,7 @@
         <v>1.31</v>
       </c>
       <c r="S9">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="T9">
         <v>1.74</v>
@@ -2733,7 +2733,7 @@
         <v>2.06</v>
       </c>
       <c r="V9">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="W9">
         <v>1.53</v>
@@ -2760,7 +2760,7 @@
         <v>14</v>
       </c>
       <c r="AE9">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="AF9">
         <v>18.5</v>
@@ -2778,7 +2778,7 @@
         <v>48</v>
       </c>
       <c r="AK9">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AL9">
         <v>55</v>
@@ -2793,64 +2793,64 @@
         <v>40</v>
       </c>
       <c r="AP9">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AQ9">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AR9">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="AS9">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="AT9">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AU9">
-        <v>5</v>
+        <v>5.9</v>
       </c>
       <c r="AV9">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AW9">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="AX9">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AY9">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AZ9">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BA9">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="BB9">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BC9">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BD9">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BE9">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BF9">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BG9">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BH9">
         <v>3.4</v>
       </c>
       <c r="BI9">
-        <v>2.64</v>
+        <v>2.92</v>
       </c>
       <c r="BJ9">
         <v>10</v>
@@ -2927,7 +2927,7 @@
         <v>122</v>
       </c>
       <c r="F10">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="G10">
         <v>2.52</v>
@@ -2936,13 +2936,13 @@
         <v>3.15</v>
       </c>
       <c r="I10">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="J10">
         <v>3.5</v>
       </c>
       <c r="K10">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="L10">
         <v>1.41</v>
@@ -2951,19 +2951,19 @@
         <v>1.07</v>
       </c>
       <c r="N10">
-        <v>3.4</v>
+        <v>3.15</v>
       </c>
       <c r="O10">
         <v>1.32</v>
       </c>
       <c r="P10">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="Q10">
         <v>1.85</v>
       </c>
       <c r="R10">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="S10">
         <v>3.2</v>
@@ -2972,10 +2972,10 @@
         <v>1.75</v>
       </c>
       <c r="U10">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="V10">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="W10">
         <v>1.65</v>
@@ -2993,10 +2993,10 @@
         <v>70</v>
       </c>
       <c r="AB10">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AC10">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AD10">
         <v>17</v>
@@ -3005,10 +3005,10 @@
         <v>46</v>
       </c>
       <c r="AF10">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AG10">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AH10">
         <v>21</v>
@@ -3017,79 +3017,79 @@
         <v>60</v>
       </c>
       <c r="AJ10">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AK10">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AL10">
         <v>48</v>
       </c>
       <c r="AM10">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AN10">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AO10">
         <v>42</v>
       </c>
       <c r="AP10">
+        <v>3.75</v>
+      </c>
+      <c r="AQ10">
+        <v>3.65</v>
+      </c>
+      <c r="AR10">
+        <v>4.1</v>
+      </c>
+      <c r="AS10">
+        <v>4.5</v>
+      </c>
+      <c r="AT10">
+        <v>3.5</v>
+      </c>
+      <c r="AU10">
+        <v>3.05</v>
+      </c>
+      <c r="AV10">
+        <v>3.75</v>
+      </c>
+      <c r="AW10">
+        <v>4.4</v>
+      </c>
+      <c r="AX10">
+        <v>3.85</v>
+      </c>
+      <c r="AY10">
         <v>3.6</v>
       </c>
-      <c r="AQ10">
-        <v>3.5</v>
-      </c>
-      <c r="AR10">
-        <v>3.9</v>
-      </c>
-      <c r="AS10">
+      <c r="AZ10">
+        <v>3.95</v>
+      </c>
+      <c r="BA10">
+        <v>4.5</v>
+      </c>
+      <c r="BB10">
         <v>4.3</v>
       </c>
-      <c r="AT10">
-        <v>3.35</v>
-      </c>
-      <c r="AU10">
-        <v>2.94</v>
-      </c>
-      <c r="AV10">
-        <v>3.6</v>
-      </c>
-      <c r="AW10">
-        <v>4.1</v>
-      </c>
-      <c r="AX10">
-        <v>3.7</v>
-      </c>
-      <c r="AY10">
-        <v>3.45</v>
-      </c>
-      <c r="AZ10">
-        <v>3.75</v>
-      </c>
-      <c r="BA10">
+      <c r="BC10">
         <v>4.2</v>
       </c>
-      <c r="BB10">
-        <v>4.1</v>
-      </c>
-      <c r="BC10">
+      <c r="BD10">
+        <v>4.4</v>
+      </c>
+      <c r="BE10">
+        <v>4.6</v>
+      </c>
+      <c r="BF10">
         <v>4</v>
       </c>
-      <c r="BD10">
-        <v>4.1</v>
-      </c>
-      <c r="BE10">
-        <v>4.4</v>
-      </c>
-      <c r="BF10">
-        <v>3.9</v>
-      </c>
       <c r="BG10">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="BH10">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="BI10">
         <v>2.72</v>
@@ -3098,7 +3098,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BK10">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BL10">
         <v>1000</v>
@@ -3107,40 +3107,40 @@
         <v>2.58</v>
       </c>
       <c r="BN10">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BO10">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="BP10">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="BQ10">
+        <v>6.6</v>
+      </c>
+      <c r="BR10">
+        <v>32</v>
+      </c>
+      <c r="BS10">
+        <v>7.8</v>
+      </c>
+      <c r="BT10">
         <v>6.8</v>
       </c>
-      <c r="BR10">
-        <v>34</v>
-      </c>
-      <c r="BS10">
-        <v>2.44</v>
-      </c>
-      <c r="BT10">
-        <v>6.6</v>
-      </c>
       <c r="BU10">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BV10">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BW10">
         <v>7.4</v>
       </c>
       <c r="BX10">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BY10">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="BZ10">
         <v>0</v>
@@ -3169,13 +3169,13 @@
         <v>123</v>
       </c>
       <c r="F11">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="G11">
         <v>1.89</v>
       </c>
       <c r="H11">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="I11">
         <v>5</v>
@@ -3184,7 +3184,7 @@
         <v>3.65</v>
       </c>
       <c r="K11">
-        <v>4.3</v>
+        <v>3.75</v>
       </c>
       <c r="L11">
         <v>1.01</v>
@@ -3193,7 +3193,7 @@
         <v>1.09</v>
       </c>
       <c r="N11">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="O11">
         <v>1.45</v>
@@ -3205,16 +3205,16 @@
         <v>2.28</v>
       </c>
       <c r="R11">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="S11">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="T11">
         <v>2.16</v>
       </c>
       <c r="U11">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="V11">
         <v>1.25</v>
@@ -3417,7 +3417,7 @@
         <v>2.5</v>
       </c>
       <c r="H12">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="I12">
         <v>3.85</v>
@@ -3429,10 +3429,10 @@
         <v>3.15</v>
       </c>
       <c r="L12">
-        <v>1.47</v>
+        <v>1.57</v>
       </c>
       <c r="M12">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="N12">
         <v>2.62</v>
@@ -3441,7 +3441,7 @@
         <v>1.54</v>
       </c>
       <c r="P12">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="Q12">
         <v>2.6</v>
@@ -3453,7 +3453,7 @@
         <v>5.4</v>
       </c>
       <c r="T12">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="U12">
         <v>1.8</v>
@@ -3462,7 +3462,7 @@
         <v>1.35</v>
       </c>
       <c r="W12">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="X12">
         <v>10.5</v>
@@ -3471,7 +3471,7 @@
         <v>12</v>
       </c>
       <c r="Z12">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AA12">
         <v>100</v>
@@ -3483,19 +3483,19 @@
         <v>7.4</v>
       </c>
       <c r="AD12">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AE12">
         <v>75</v>
       </c>
       <c r="AF12">
-        <v>14.5</v>
+        <v>17</v>
       </c>
       <c r="AG12">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AH12">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="AI12">
         <v>100</v>
@@ -3525,10 +3525,10 @@
         <v>9</v>
       </c>
       <c r="AR12">
-        <v>5.7</v>
+        <v>17.5</v>
       </c>
       <c r="AS12">
-        <v>6.8</v>
+        <v>5.3</v>
       </c>
       <c r="AT12">
         <v>6.6</v>
@@ -3540,7 +3540,7 @@
         <v>14</v>
       </c>
       <c r="AW12">
-        <v>6.6</v>
+        <v>5.2</v>
       </c>
       <c r="AX12">
         <v>12</v>
@@ -3549,46 +3549,46 @@
         <v>10.5</v>
       </c>
       <c r="AZ12">
-        <v>5.6</v>
+        <v>19.5</v>
       </c>
       <c r="BA12">
-        <v>6.8</v>
+        <v>5.3</v>
       </c>
       <c r="BB12">
-        <v>6.2</v>
+        <v>5</v>
       </c>
       <c r="BC12">
-        <v>6.2</v>
+        <v>5</v>
       </c>
       <c r="BD12">
-        <v>6.6</v>
+        <v>5.2</v>
       </c>
       <c r="BE12">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="BF12">
-        <v>6.2</v>
+        <v>5</v>
       </c>
       <c r="BG12">
-        <v>6.8</v>
+        <v>5.3</v>
       </c>
       <c r="BH12">
-        <v>2.74</v>
+        <v>3.15</v>
       </c>
       <c r="BI12">
-        <v>2.52</v>
+        <v>2.24</v>
       </c>
       <c r="BJ12">
-        <v>11</v>
+        <v>13.5</v>
       </c>
       <c r="BK12">
-        <v>5.6</v>
+        <v>3.6</v>
       </c>
       <c r="BL12">
         <v>1000</v>
       </c>
       <c r="BM12">
-        <v>10.5</v>
+        <v>4.8</v>
       </c>
       <c r="BN12">
         <v>6</v>
@@ -3597,40 +3597,40 @@
         <v>4.5</v>
       </c>
       <c r="BP12">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="BQ12">
-        <v>7.4</v>
+        <v>4.1</v>
       </c>
       <c r="BR12">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="BS12">
-        <v>9</v>
+        <v>4.5</v>
       </c>
       <c r="BT12">
-        <v>6.6</v>
+        <v>8</v>
       </c>
       <c r="BU12">
         <v>5</v>
       </c>
       <c r="BV12">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="BW12">
-        <v>8.6</v>
+        <v>4.4</v>
       </c>
       <c r="BX12">
         <v>70</v>
       </c>
       <c r="BY12">
-        <v>9.6</v>
+        <v>4.6</v>
       </c>
       <c r="BZ12">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="CA12">
-        <v>9.199999999999999</v>
+        <v>4.5</v>
       </c>
       <c r="CB12" t="s">
         <v>127</v>
@@ -3656,16 +3656,16 @@
         <v>2.14</v>
       </c>
       <c r="G13">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="H13">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="I13">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="J13">
-        <v>2.8</v>
+        <v>2.86</v>
       </c>
       <c r="K13">
         <v>3.25</v>
@@ -3677,16 +3677,16 @@
         <v>1.14</v>
       </c>
       <c r="N13">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="O13">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="P13">
         <v>1.45</v>
       </c>
       <c r="Q13">
-        <v>2.44</v>
+        <v>2.64</v>
       </c>
       <c r="R13">
         <v>1.16</v>
@@ -3704,7 +3704,7 @@
         <v>1.26</v>
       </c>
       <c r="W13">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="X13">
         <v>9</v>
@@ -3734,7 +3734,7 @@
         <v>14.5</v>
       </c>
       <c r="AG13">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AH13">
         <v>32</v>
@@ -3743,82 +3743,82 @@
         <v>130</v>
       </c>
       <c r="AJ13">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AK13">
         <v>40</v>
       </c>
       <c r="AL13">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AM13">
         <v>270</v>
       </c>
       <c r="AN13">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AO13">
         <v>150</v>
       </c>
       <c r="AP13">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="AQ13">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="AR13">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AS13">
+        <v>5.1</v>
+      </c>
+      <c r="AT13">
+        <v>3.15</v>
+      </c>
+      <c r="AU13">
+        <v>3.25</v>
+      </c>
+      <c r="AV13">
+        <v>4.3</v>
+      </c>
+      <c r="AW13">
+        <v>5.1</v>
+      </c>
+      <c r="AX13">
+        <v>3.9</v>
+      </c>
+      <c r="AY13">
+        <v>3.9</v>
+      </c>
+      <c r="AZ13">
+        <v>4.6</v>
+      </c>
+      <c r="BA13">
+        <v>5.1</v>
+      </c>
+      <c r="BB13">
+        <v>4.7</v>
+      </c>
+      <c r="BC13">
+        <v>4.7</v>
+      </c>
+      <c r="BD13">
         <v>5</v>
       </c>
-      <c r="AT13">
-        <v>3.1</v>
-      </c>
-      <c r="AU13">
-        <v>3.2</v>
-      </c>
-      <c r="AV13">
-        <v>4.2</v>
-      </c>
-      <c r="AW13">
-        <v>4.9</v>
-      </c>
-      <c r="AX13">
-        <v>3.85</v>
-      </c>
-      <c r="AY13">
-        <v>3.85</v>
-      </c>
-      <c r="AZ13">
-        <v>4.5</v>
-      </c>
-      <c r="BA13">
-        <v>5</v>
-      </c>
-      <c r="BB13">
-        <v>4.6</v>
-      </c>
-      <c r="BC13">
-        <v>4.6</v>
-      </c>
-      <c r="BD13">
-        <v>4.9</v>
-      </c>
       <c r="BE13">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BF13">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BG13">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BH13">
         <v>2.84</v>
       </c>
       <c r="BI13">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="BJ13">
         <v>14</v>
@@ -3830,13 +3830,13 @@
         <v>1000</v>
       </c>
       <c r="BM13">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="BN13">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BO13">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="BP13">
         <v>23</v>
@@ -3851,10 +3851,10 @@
         <v>5.6</v>
       </c>
       <c r="BT13">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BU13">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="BV13">
         <v>55</v>
@@ -3895,19 +3895,19 @@
         <v>126</v>
       </c>
       <c r="F14">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="G14">
-        <v>110</v>
+        <v>990</v>
       </c>
       <c r="H14">
         <v>1.32</v>
       </c>
       <c r="I14">
-        <v>110</v>
+        <v>990</v>
       </c>
       <c r="J14">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="K14">
         <v>4.2</v>
@@ -3931,19 +3931,19 @@
         <v>1.14</v>
       </c>
       <c r="R14">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="S14">
-        <v>1.14</v>
+        <v>1.05</v>
       </c>
       <c r="T14">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U14">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V14">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="W14">
         <v>1.01</v>
@@ -4060,55 +4060,55 @@
         <v>1000</v>
       </c>
       <c r="BI14">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ14">
         <v>1000</v>
       </c>
       <c r="BK14">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL14">
         <v>1000</v>
       </c>
       <c r="BM14">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN14">
         <v>1000</v>
       </c>
       <c r="BO14">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP14">
         <v>1000</v>
       </c>
       <c r="BQ14">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR14">
         <v>1000</v>
       </c>
       <c r="BS14">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT14">
         <v>1000</v>
       </c>
       <c r="BU14">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV14">
         <v>1000</v>
       </c>
       <c r="BW14">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX14">
         <v>1000</v>
       </c>
       <c r="BY14">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ14">
         <v>0</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-06.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-06.xlsx
@@ -397,7 +397,7 @@
     <t>Always Ready</t>
   </si>
   <si>
-    <t>2026-08-05 06:11:50</t>
+    <t>2026-08-05 08:18:51</t>
   </si>
 </sst>
 </file>
@@ -997,49 +997,49 @@
         <v>1.17</v>
       </c>
       <c r="H2">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I2">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="J2">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="K2">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="L2">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="M2">
         <v>1.01</v>
       </c>
       <c r="N2">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="O2">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="P2">
-        <v>3.9</v>
+        <v>4.7</v>
       </c>
       <c r="Q2">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="R2">
-        <v>2.2</v>
+        <v>2.58</v>
       </c>
       <c r="S2">
-        <v>1.72</v>
+        <v>1.51</v>
       </c>
       <c r="T2">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="U2">
-        <v>1.76</v>
+        <v>1.95</v>
       </c>
       <c r="V2">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="W2">
         <v>6.8</v>
@@ -1051,160 +1051,160 @@
         <v>950</v>
       </c>
       <c r="Z2">
-        <v>280</v>
+        <v>330</v>
       </c>
       <c r="AA2">
         <v>1000</v>
       </c>
       <c r="AB2">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="AC2">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="AD2">
         <v>90</v>
       </c>
       <c r="AE2">
-        <v>380</v>
+        <v>350</v>
       </c>
       <c r="AF2">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AG2">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="AH2">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AI2">
-        <v>230</v>
+        <v>180</v>
       </c>
       <c r="AJ2">
-        <v>9.800000000000001</v>
+        <v>12</v>
       </c>
       <c r="AK2">
         <v>16.5</v>
       </c>
       <c r="AL2">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="AM2">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="AN2">
-        <v>2.62</v>
+        <v>2.22</v>
       </c>
       <c r="AO2">
-        <v>390</v>
+        <v>250</v>
       </c>
       <c r="AP2">
-        <v>7.6</v>
+        <v>9</v>
       </c>
       <c r="AQ2">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR2">
-        <v>8.6</v>
+        <v>9.6</v>
       </c>
       <c r="AS2">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AT2">
+        <v>19</v>
+      </c>
+      <c r="AU2">
+        <v>21</v>
+      </c>
+      <c r="AV2">
         <v>8.800000000000001</v>
       </c>
-      <c r="AT2">
-        <v>13</v>
-      </c>
-      <c r="AU2">
-        <v>20</v>
-      </c>
-      <c r="AV2">
-        <v>8</v>
-      </c>
       <c r="AW2">
-        <v>8.6</v>
+        <v>9.6</v>
       </c>
       <c r="AX2">
-        <v>8.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="AY2">
         <v>12.5</v>
       </c>
       <c r="AZ2">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BA2">
+        <v>9.4</v>
+      </c>
+      <c r="BB2">
+        <v>8.6</v>
+      </c>
+      <c r="BC2">
+        <v>11.5</v>
+      </c>
+      <c r="BD2">
+        <v>8</v>
+      </c>
+      <c r="BE2">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BF2">
+        <v>1.91</v>
+      </c>
+      <c r="BG2">
+        <v>9.4</v>
+      </c>
+      <c r="BH2">
         <v>8.4</v>
       </c>
-      <c r="BB2">
-        <v>7.6</v>
-      </c>
-      <c r="BC2">
-        <v>11</v>
-      </c>
-      <c r="BD2">
-        <v>32</v>
-      </c>
-      <c r="BE2">
-        <v>8.4</v>
-      </c>
-      <c r="BF2">
-        <v>2.24</v>
-      </c>
-      <c r="BG2">
-        <v>8.6</v>
-      </c>
-      <c r="BH2">
+      <c r="BI2">
+        <v>6</v>
+      </c>
+      <c r="BJ2">
+        <v>14.5</v>
+      </c>
+      <c r="BK2">
+        <v>4.9</v>
+      </c>
+      <c r="BL2">
+        <v>1000</v>
+      </c>
+      <c r="BM2">
+        <v>6.8</v>
+      </c>
+      <c r="BN2">
+        <v>5</v>
+      </c>
+      <c r="BO2">
+        <v>3.7</v>
+      </c>
+      <c r="BP2">
+        <v>6.4</v>
+      </c>
+      <c r="BQ2">
+        <v>4.7</v>
+      </c>
+      <c r="BR2">
+        <v>18</v>
+      </c>
+      <c r="BS2">
+        <v>5.2</v>
+      </c>
+      <c r="BT2">
+        <v>25</v>
+      </c>
+      <c r="BU2">
+        <v>5.7</v>
+      </c>
+      <c r="BV2">
+        <v>1000</v>
+      </c>
+      <c r="BW2">
+        <v>7</v>
+      </c>
+      <c r="BX2">
+        <v>1000</v>
+      </c>
+      <c r="BY2">
         <v>6.6</v>
-      </c>
-      <c r="BI2">
-        <v>4.9</v>
-      </c>
-      <c r="BJ2">
-        <v>15.5</v>
-      </c>
-      <c r="BK2">
-        <v>5.7</v>
-      </c>
-      <c r="BL2">
-        <v>1000</v>
-      </c>
-      <c r="BM2">
-        <v>8.4</v>
-      </c>
-      <c r="BN2">
-        <v>4.3</v>
-      </c>
-      <c r="BO2">
-        <v>3.3</v>
-      </c>
-      <c r="BP2">
-        <v>6.2</v>
-      </c>
-      <c r="BQ2">
-        <v>4.5</v>
-      </c>
-      <c r="BR2">
-        <v>21</v>
-      </c>
-      <c r="BS2">
-        <v>6.2</v>
-      </c>
-      <c r="BT2">
-        <v>23</v>
-      </c>
-      <c r="BU2">
-        <v>6.4</v>
-      </c>
-      <c r="BV2">
-        <v>1000</v>
-      </c>
-      <c r="BW2">
-        <v>8.4</v>
-      </c>
-      <c r="BX2">
-        <v>1000</v>
-      </c>
-      <c r="BY2">
-        <v>8.199999999999999</v>
       </c>
       <c r="BZ2">
         <v>0</v>
@@ -1233,61 +1233,61 @@
         <v>115</v>
       </c>
       <c r="F3">
+        <v>2.62</v>
+      </c>
+      <c r="G3">
         <v>2.66</v>
       </c>
-      <c r="G3">
-        <v>2.72</v>
-      </c>
       <c r="H3">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="I3">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="J3">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="K3">
         <v>2.92</v>
       </c>
       <c r="L3">
-        <v>1.72</v>
+        <v>1.8</v>
       </c>
       <c r="M3">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="N3">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="O3">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="P3">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="Q3">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="R3">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="S3">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="T3">
-        <v>2.46</v>
+        <v>2.6</v>
       </c>
       <c r="U3">
-        <v>1.64</v>
+        <v>1.59</v>
       </c>
       <c r="V3">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="W3">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="X3">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="Y3">
         <v>8.4</v>
@@ -1299,28 +1299,28 @@
         <v>1000</v>
       </c>
       <c r="AB3">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="AC3">
         <v>7</v>
       </c>
       <c r="AD3">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AE3">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="AF3">
         <v>14.5</v>
       </c>
       <c r="AG3">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AH3">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AI3">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AJ3">
         <v>46</v>
@@ -1329,43 +1329,43 @@
         <v>50</v>
       </c>
       <c r="AL3">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AM3">
-        <v>330</v>
+        <v>340</v>
       </c>
       <c r="AN3">
         <v>65</v>
       </c>
       <c r="AO3">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AP3">
-        <v>6.2</v>
+        <v>5.8</v>
       </c>
       <c r="AQ3">
         <v>7.8</v>
       </c>
       <c r="AR3">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AS3">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="AT3">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="AU3">
         <v>6.6</v>
       </c>
       <c r="AV3">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AW3">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AX3">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AY3">
         <v>13</v>
@@ -1380,7 +1380,7 @@
         <v>38</v>
       </c>
       <c r="BC3">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="BD3">
         <v>38</v>
@@ -1392,10 +1392,10 @@
         <v>50</v>
       </c>
       <c r="BG3">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BH3">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="BI3">
         <v>2.1</v>
@@ -1404,55 +1404,55 @@
         <v>13</v>
       </c>
       <c r="BK3">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="BN3">
         <v>5.5</v>
       </c>
       <c r="BO3">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="BP3">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BQ3">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BR3">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="BS3">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="BT3">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BU3">
         <v>5.4</v>
       </c>
       <c r="BV3">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BW3">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="BX3">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="BY3">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="BZ3">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="CA3">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="CB3" t="s">
         <v>127</v>
@@ -1475,55 +1475,55 @@
         <v>116</v>
       </c>
       <c r="F4">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="G4">
         <v>3.2</v>
       </c>
       <c r="H4">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="I4">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="J4">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="K4">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="L4">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="M4">
         <v>1.12</v>
       </c>
       <c r="N4">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="O4">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="P4">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="Q4">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="R4">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="S4">
         <v>5.1</v>
       </c>
       <c r="T4">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="U4">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="V4">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="W4">
         <v>1.46</v>
@@ -1532,127 +1532,127 @@
         <v>11</v>
       </c>
       <c r="Y4">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="Z4">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AA4">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AB4">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AC4">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AD4">
         <v>13.5</v>
       </c>
       <c r="AE4">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="AF4">
         <v>19.5</v>
       </c>
       <c r="AG4">
-        <v>20</v>
+        <v>14.5</v>
       </c>
       <c r="AH4">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="AI4">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AJ4">
+        <v>60</v>
+      </c>
+      <c r="AK4">
+        <v>46</v>
+      </c>
+      <c r="AL4">
         <v>70</v>
       </c>
-      <c r="AK4">
-        <v>60</v>
-      </c>
-      <c r="AL4">
-        <v>80</v>
-      </c>
       <c r="AM4">
-        <v>180</v>
+        <v>210</v>
       </c>
       <c r="AN4">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AO4">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AP4">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="AQ4">
         <v>7.6</v>
       </c>
       <c r="AR4">
+        <v>14.5</v>
+      </c>
+      <c r="AS4">
+        <v>6.8</v>
+      </c>
+      <c r="AT4">
+        <v>6.8</v>
+      </c>
+      <c r="AU4">
+        <v>6</v>
+      </c>
+      <c r="AV4">
+        <v>11.5</v>
+      </c>
+      <c r="AW4">
+        <v>30</v>
+      </c>
+      <c r="AX4">
+        <v>13.5</v>
+      </c>
+      <c r="AY4">
         <v>12</v>
       </c>
-      <c r="AS4">
-        <v>7.6</v>
-      </c>
-      <c r="AT4">
-        <v>8</v>
-      </c>
-      <c r="AU4">
-        <v>6.2</v>
-      </c>
-      <c r="AV4">
-        <v>11</v>
-      </c>
-      <c r="AW4">
-        <v>28</v>
-      </c>
-      <c r="AX4">
-        <v>10.5</v>
-      </c>
-      <c r="AY4">
-        <v>10.5</v>
-      </c>
       <c r="AZ4">
-        <v>15.5</v>
+        <v>18.5</v>
       </c>
       <c r="BA4">
-        <v>7.8</v>
+        <v>7</v>
       </c>
       <c r="BB4">
-        <v>7.8</v>
+        <v>7</v>
       </c>
       <c r="BC4">
         <v>32</v>
       </c>
       <c r="BD4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BE4">
-        <v>8.4</v>
+        <v>7.6</v>
       </c>
       <c r="BF4">
-        <v>7.8</v>
+        <v>7</v>
       </c>
       <c r="BG4">
-        <v>7.6</v>
+        <v>6.8</v>
       </c>
       <c r="BH4">
         <v>2.78</v>
       </c>
       <c r="BI4">
-        <v>2.36</v>
+        <v>2.3</v>
       </c>
       <c r="BJ4">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BK4">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>2.34</v>
+        <v>12.5</v>
       </c>
       <c r="BN4">
         <v>6</v>
@@ -1664,16 +1664,16 @@
         <v>1000</v>
       </c>
       <c r="BQ4">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BR4">
         <v>1000</v>
       </c>
       <c r="BS4">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="BT4">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BU4">
         <v>4.2</v>
@@ -1682,19 +1682,19 @@
         <v>1000</v>
       </c>
       <c r="BW4">
-        <v>9.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX4">
         <v>1000</v>
       </c>
       <c r="BY4">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="BZ4">
         <v>1000</v>
       </c>
       <c r="CA4">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="CB4" t="s">
         <v>127</v>
@@ -1717,10 +1717,10 @@
         <v>117</v>
       </c>
       <c r="F5">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="G5">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="H5">
         <v>4.6</v>
@@ -1732,7 +1732,7 @@
         <v>4.2</v>
       </c>
       <c r="K5">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="L5">
         <v>1.31</v>
@@ -1753,16 +1753,16 @@
         <v>1.64</v>
       </c>
       <c r="R5">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="S5">
         <v>2.62</v>
       </c>
       <c r="T5">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="U5">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="V5">
         <v>1.25</v>
@@ -1774,130 +1774,130 @@
         <v>26</v>
       </c>
       <c r="Y5">
-        <v>23</v>
+        <v>950</v>
       </c>
       <c r="Z5">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AA5">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AB5">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AC5">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AD5">
         <v>21</v>
       </c>
       <c r="AE5">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AF5">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AG5">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AH5">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AI5">
         <v>60</v>
       </c>
       <c r="AJ5">
+        <v>22</v>
+      </c>
+      <c r="AK5">
         <v>19</v>
-      </c>
-      <c r="AK5">
-        <v>17</v>
       </c>
       <c r="AL5">
         <v>32</v>
       </c>
       <c r="AM5">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AN5">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AO5">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AP5">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="AQ5">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AR5">
         <v>32</v>
       </c>
       <c r="AS5">
-        <v>7.8</v>
+        <v>5.9</v>
       </c>
       <c r="AT5">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU5">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="AV5">
         <v>16.5</v>
       </c>
       <c r="AW5">
-        <v>7.2</v>
+        <v>5.6</v>
       </c>
       <c r="AX5">
         <v>10.5</v>
       </c>
       <c r="AY5">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AZ5">
         <v>13</v>
       </c>
       <c r="BA5">
-        <v>7.2</v>
+        <v>5.6</v>
       </c>
       <c r="BB5">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BC5">
         <v>12.5</v>
       </c>
       <c r="BD5">
-        <v>6.6</v>
+        <v>21</v>
       </c>
       <c r="BE5">
-        <v>7.4</v>
+        <v>5.7</v>
       </c>
       <c r="BF5">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="BG5">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="BH5">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BI5">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="BJ5">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BK5">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BL5">
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="BN5">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BO5">
         <v>3.75</v>
@@ -1906,37 +1906,37 @@
         <v>11.5</v>
       </c>
       <c r="BQ5">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="BR5">
         <v>23</v>
       </c>
       <c r="BS5">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="BT5">
         <v>9</v>
       </c>
       <c r="BU5">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BV5">
         <v>1000</v>
       </c>
       <c r="BW5">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="BX5">
         <v>1000</v>
       </c>
       <c r="BY5">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="BZ5">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="CA5">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="CB5" t="s">
         <v>127</v>
@@ -1959,19 +1959,19 @@
         <v>118</v>
       </c>
       <c r="F6">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="G6">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="H6">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="I6">
         <v>4</v>
       </c>
       <c r="J6">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="K6">
         <v>3.5</v>
@@ -1992,61 +1992,61 @@
         <v>1.76</v>
       </c>
       <c r="Q6">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="R6">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="S6">
         <v>4.2</v>
       </c>
       <c r="T6">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="U6">
-        <v>1.96</v>
+        <v>1.99</v>
       </c>
       <c r="V6">
         <v>1.33</v>
       </c>
       <c r="W6">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="X6">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="Y6">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="Z6">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AA6">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="AB6">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC6">
         <v>9.199999999999999</v>
       </c>
       <c r="AD6">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AE6">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AF6">
         <v>14</v>
       </c>
       <c r="AG6">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="AH6">
         <v>20</v>
       </c>
       <c r="AI6">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="AJ6">
         <v>30</v>
@@ -2055,7 +2055,7 @@
         <v>27</v>
       </c>
       <c r="AL6">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="AM6">
         <v>150</v>
@@ -2064,19 +2064,19 @@
         <v>23</v>
       </c>
       <c r="AO6">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AP6">
-        <v>10</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ6">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="AR6">
-        <v>6.8</v>
+        <v>5.8</v>
       </c>
       <c r="AS6">
-        <v>7.4</v>
+        <v>5.9</v>
       </c>
       <c r="AT6">
         <v>7.4</v>
@@ -2088,7 +2088,7 @@
         <v>13.5</v>
       </c>
       <c r="AW6">
-        <v>7</v>
+        <v>5.7</v>
       </c>
       <c r="AX6">
         <v>11</v>
@@ -2100,25 +2100,25 @@
         <v>16.5</v>
       </c>
       <c r="BA6">
-        <v>7.2</v>
+        <v>5.8</v>
       </c>
       <c r="BB6">
         <v>24</v>
       </c>
       <c r="BC6">
-        <v>6.6</v>
+        <v>21</v>
       </c>
       <c r="BD6">
         <v>32</v>
       </c>
       <c r="BE6">
-        <v>7.6</v>
+        <v>6</v>
       </c>
       <c r="BF6">
         <v>15.5</v>
       </c>
       <c r="BG6">
-        <v>7.2</v>
+        <v>5.7</v>
       </c>
       <c r="BH6">
         <v>3.25</v>
@@ -2142,7 +2142,7 @@
         <v>5.1</v>
       </c>
       <c r="BO6">
-        <v>4.2</v>
+        <v>3.75</v>
       </c>
       <c r="BP6">
         <v>17.5</v>
@@ -2151,7 +2151,7 @@
         <v>6.4</v>
       </c>
       <c r="BR6">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="BS6">
         <v>8</v>
@@ -2160,7 +2160,7 @@
         <v>7.4</v>
       </c>
       <c r="BU6">
-        <v>6</v>
+        <v>5.3</v>
       </c>
       <c r="BV6">
         <v>1000</v>
@@ -2175,7 +2175,7 @@
         <v>8.4</v>
       </c>
       <c r="BZ6">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="CA6">
         <v>7.8</v>
@@ -2204,43 +2204,43 @@
         <v>1.85</v>
       </c>
       <c r="G7">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="H7">
         <v>4.8</v>
       </c>
       <c r="I7">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="J7">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="K7">
         <v>3.45</v>
       </c>
       <c r="L7">
-        <v>1.01</v>
+        <v>1.52</v>
       </c>
       <c r="M7">
         <v>1.13</v>
       </c>
       <c r="N7">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="O7">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="P7">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="Q7">
-        <v>2.54</v>
+        <v>2.66</v>
       </c>
       <c r="R7">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="S7">
-        <v>1.05</v>
+        <v>2.88</v>
       </c>
       <c r="T7">
         <v>2.32</v>
@@ -2252,7 +2252,7 @@
         <v>1.19</v>
       </c>
       <c r="W7">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="X7">
         <v>9.4</v>
@@ -2363,58 +2363,58 @@
         <v>5.2</v>
       </c>
       <c r="BH7">
-        <v>1000</v>
+        <v>2.92</v>
       </c>
       <c r="BI7">
-        <v>1.04</v>
+        <v>2.24</v>
       </c>
       <c r="BJ7">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="BK7">
-        <v>1.04</v>
+        <v>4.3</v>
       </c>
       <c r="BL7">
         <v>1000</v>
       </c>
       <c r="BM7">
-        <v>1.04</v>
+        <v>6</v>
       </c>
       <c r="BN7">
-        <v>1000</v>
+        <v>4.8</v>
       </c>
       <c r="BO7">
-        <v>1.04</v>
+        <v>2.7</v>
       </c>
       <c r="BP7">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="BQ7">
-        <v>1.04</v>
+        <v>4.6</v>
       </c>
       <c r="BR7">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="BS7">
-        <v>1.04</v>
+        <v>5.5</v>
       </c>
       <c r="BT7">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="BU7">
-        <v>1.04</v>
+        <v>3.8</v>
       </c>
       <c r="BV7">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="BW7">
-        <v>1.04</v>
+        <v>5.7</v>
       </c>
       <c r="BX7">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="BY7">
-        <v>1.04</v>
+        <v>5.8</v>
       </c>
       <c r="BZ7">
         <v>0</v>
@@ -2443,100 +2443,100 @@
         <v>120</v>
       </c>
       <c r="F8">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="G8">
         <v>1.71</v>
       </c>
       <c r="H8">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="I8">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="J8">
         <v>1.1</v>
       </c>
       <c r="K8">
-        <v>6.8</v>
+        <v>5.6</v>
       </c>
       <c r="L8">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="M8">
         <v>1.01</v>
       </c>
       <c r="N8">
-        <v>1.1</v>
+        <v>7.2</v>
       </c>
       <c r="O8">
         <v>1.1</v>
       </c>
       <c r="P8">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="Q8">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="R8">
         <v>2.02</v>
       </c>
       <c r="S8">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="T8">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="U8">
         <v>2.84</v>
       </c>
       <c r="V8">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="W8">
         <v>2.4</v>
       </c>
       <c r="X8">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="Y8">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="Z8">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AA8">
         <v>120</v>
       </c>
       <c r="AB8">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AC8">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AD8">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AE8">
         <v>55</v>
       </c>
       <c r="AF8">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AG8">
         <v>12.5</v>
       </c>
       <c r="AH8">
+        <v>19</v>
+      </c>
+      <c r="AI8">
+        <v>46</v>
+      </c>
+      <c r="AJ8">
+        <v>23</v>
+      </c>
+      <c r="AK8">
         <v>17.5</v>
-      </c>
-      <c r="AI8">
-        <v>42</v>
-      </c>
-      <c r="AJ8">
-        <v>20</v>
-      </c>
-      <c r="AK8">
-        <v>16</v>
       </c>
       <c r="AL8">
         <v>22</v>
@@ -2545,124 +2545,124 @@
         <v>55</v>
       </c>
       <c r="AN8">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="AO8">
         <v>27</v>
       </c>
       <c r="AP8">
-        <v>7.6</v>
+        <v>5.3</v>
       </c>
       <c r="AQ8">
-        <v>7.2</v>
+        <v>5.1</v>
       </c>
       <c r="AR8">
-        <v>7.8</v>
+        <v>5.3</v>
       </c>
       <c r="AS8">
-        <v>8.199999999999999</v>
+        <v>5.5</v>
       </c>
       <c r="AT8">
-        <v>6.2</v>
+        <v>4.6</v>
       </c>
       <c r="AU8">
-        <v>5.6</v>
+        <v>4.3</v>
       </c>
       <c r="AV8">
-        <v>6.4</v>
+        <v>4.7</v>
       </c>
       <c r="AW8">
-        <v>7.6</v>
+        <v>5.2</v>
       </c>
       <c r="AX8">
-        <v>5.9</v>
+        <v>4.4</v>
       </c>
       <c r="AY8">
+        <v>3.95</v>
+      </c>
+      <c r="AZ8">
+        <v>4.4</v>
+      </c>
+      <c r="BA8">
         <v>5.2</v>
       </c>
-      <c r="AZ8">
-        <v>5.9</v>
-      </c>
-      <c r="BA8">
-        <v>7.4</v>
-      </c>
       <c r="BB8">
-        <v>6.2</v>
+        <v>4.6</v>
       </c>
       <c r="BC8">
-        <v>5.7</v>
+        <v>4.3</v>
       </c>
       <c r="BD8">
-        <v>6.2</v>
+        <v>4.6</v>
       </c>
       <c r="BE8">
-        <v>7.6</v>
+        <v>5.2</v>
       </c>
       <c r="BF8">
-        <v>3.1</v>
+        <v>2.74</v>
       </c>
       <c r="BG8">
-        <v>6.6</v>
+        <v>4.8</v>
       </c>
       <c r="BH8">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="BI8">
-        <v>1.04</v>
+        <v>3</v>
       </c>
       <c r="BJ8">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="BK8">
-        <v>1.04</v>
+        <v>3.5</v>
       </c>
       <c r="BL8">
         <v>1000</v>
       </c>
       <c r="BM8">
-        <v>1.04</v>
+        <v>5</v>
       </c>
       <c r="BN8">
-        <v>1000</v>
+        <v>6</v>
       </c>
       <c r="BO8">
-        <v>1.04</v>
+        <v>2.86</v>
       </c>
       <c r="BP8">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BQ8">
-        <v>1.04</v>
+        <v>3.7</v>
       </c>
       <c r="BR8">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="BS8">
-        <v>1.04</v>
+        <v>4.2</v>
       </c>
       <c r="BT8">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BU8">
-        <v>1.04</v>
+        <v>3.65</v>
       </c>
       <c r="BV8">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BW8">
-        <v>1.04</v>
+        <v>4.7</v>
       </c>
       <c r="BX8">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BY8">
-        <v>1.04</v>
+        <v>4.7</v>
       </c>
       <c r="BZ8">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="CA8">
-        <v>1.04</v>
+        <v>3.5</v>
       </c>
       <c r="CB8" t="s">
         <v>127</v>
@@ -2694,10 +2694,10 @@
         <v>2.78</v>
       </c>
       <c r="I9">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="J9">
-        <v>2.9</v>
+        <v>2.94</v>
       </c>
       <c r="K9">
         <v>3.75</v>
@@ -2724,16 +2724,16 @@
         <v>1.31</v>
       </c>
       <c r="S9">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="T9">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="U9">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="V9">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="W9">
         <v>1.53</v>
@@ -2751,7 +2751,7 @@
         <v>60</v>
       </c>
       <c r="AB9">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AC9">
         <v>8.199999999999999</v>
@@ -2766,10 +2766,10 @@
         <v>18.5</v>
       </c>
       <c r="AG9">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AH9">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="AI9">
         <v>60</v>
@@ -2793,64 +2793,64 @@
         <v>40</v>
       </c>
       <c r="AP9">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
       <c r="AQ9">
-        <v>4.2</v>
+        <v>7.4</v>
       </c>
       <c r="AR9">
+        <v>4.4</v>
+      </c>
+      <c r="AS9">
+        <v>5.1</v>
+      </c>
+      <c r="AT9">
+        <v>3.9</v>
+      </c>
+      <c r="AU9">
         <v>5</v>
       </c>
-      <c r="AS9">
-        <v>5.9</v>
-      </c>
-      <c r="AT9">
+      <c r="AV9">
+        <v>4</v>
+      </c>
+      <c r="AW9">
+        <v>4.9</v>
+      </c>
+      <c r="AX9">
+        <v>4.3</v>
+      </c>
+      <c r="AY9">
         <v>4.1</v>
       </c>
-      <c r="AU9">
-        <v>5.9</v>
-      </c>
-      <c r="AV9">
+      <c r="AZ9">
         <v>4.4</v>
       </c>
-      <c r="AW9">
-        <v>5.6</v>
-      </c>
-      <c r="AX9">
+      <c r="BA9">
+        <v>5.1</v>
+      </c>
+      <c r="BB9">
+        <v>5</v>
+      </c>
+      <c r="BC9">
+        <v>4.9</v>
+      </c>
+      <c r="BD9">
+        <v>5.1</v>
+      </c>
+      <c r="BE9">
+        <v>5.3</v>
+      </c>
+      <c r="BF9">
         <v>4.8</v>
       </c>
-      <c r="AY9">
-        <v>4.3</v>
-      </c>
-      <c r="AZ9">
-        <v>4.8</v>
-      </c>
-      <c r="BA9">
-        <v>5.9</v>
-      </c>
-      <c r="BB9">
-        <v>5.7</v>
-      </c>
-      <c r="BC9">
-        <v>5.6</v>
-      </c>
-      <c r="BD9">
-        <v>5.8</v>
-      </c>
-      <c r="BE9">
-        <v>6.2</v>
-      </c>
-      <c r="BF9">
-        <v>5.4</v>
-      </c>
       <c r="BG9">
-        <v>5.6</v>
+        <v>4.9</v>
       </c>
       <c r="BH9">
         <v>3.4</v>
       </c>
       <c r="BI9">
-        <v>2.92</v>
+        <v>2.64</v>
       </c>
       <c r="BJ9">
         <v>10</v>
@@ -2927,19 +2927,19 @@
         <v>122</v>
       </c>
       <c r="F10">
-        <v>2.32</v>
+        <v>2.22</v>
       </c>
       <c r="G10">
-        <v>2.52</v>
+        <v>2.46</v>
       </c>
       <c r="H10">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="I10">
+        <v>3.65</v>
+      </c>
+      <c r="J10">
         <v>3.45</v>
-      </c>
-      <c r="J10">
-        <v>3.5</v>
       </c>
       <c r="K10">
         <v>3.75</v>
@@ -2951,43 +2951,43 @@
         <v>1.07</v>
       </c>
       <c r="N10">
-        <v>3.15</v>
+        <v>3.5</v>
       </c>
       <c r="O10">
         <v>1.32</v>
       </c>
       <c r="P10">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="Q10">
-        <v>1.85</v>
+        <v>1.92</v>
       </c>
       <c r="R10">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="S10">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="T10">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="U10">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="V10">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="W10">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="X10">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="Y10">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="Z10">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AA10">
         <v>70</v>
@@ -2996,7 +2996,7 @@
         <v>12.5</v>
       </c>
       <c r="AC10">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="AD10">
         <v>17</v>
@@ -3005,7 +3005,7 @@
         <v>46</v>
       </c>
       <c r="AF10">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AG10">
         <v>14</v>
@@ -3017,79 +3017,79 @@
         <v>60</v>
       </c>
       <c r="AJ10">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AK10">
         <v>32</v>
       </c>
       <c r="AL10">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AM10">
         <v>110</v>
       </c>
       <c r="AN10">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AO10">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AP10">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="AQ10">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="AR10">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="AS10">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="AT10">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="AU10">
         <v>3.05</v>
       </c>
       <c r="AV10">
-        <v>3.75</v>
+        <v>3.55</v>
       </c>
       <c r="AW10">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="AX10">
-        <v>3.85</v>
+        <v>3.65</v>
       </c>
       <c r="AY10">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="AZ10">
+        <v>3.7</v>
+      </c>
+      <c r="BA10">
+        <v>4.2</v>
+      </c>
+      <c r="BB10">
+        <v>4</v>
+      </c>
+      <c r="BC10">
         <v>3.95</v>
       </c>
-      <c r="BA10">
-        <v>4.5</v>
-      </c>
-      <c r="BB10">
+      <c r="BD10">
+        <v>4.1</v>
+      </c>
+      <c r="BE10">
         <v>4.3</v>
       </c>
-      <c r="BC10">
-        <v>4.2</v>
-      </c>
-      <c r="BD10">
-        <v>4.4</v>
-      </c>
-      <c r="BE10">
-        <v>4.6</v>
-      </c>
       <c r="BF10">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="BG10">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="BH10">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="BI10">
         <v>2.72</v>
@@ -3098,49 +3098,49 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BK10">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BL10">
         <v>1000</v>
       </c>
       <c r="BM10">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="BN10">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BO10">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="BP10">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BQ10">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BR10">
         <v>32</v>
       </c>
       <c r="BS10">
-        <v>7.8</v>
+        <v>2.46</v>
       </c>
       <c r="BT10">
         <v>6.8</v>
       </c>
       <c r="BU10">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BV10">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BW10">
-        <v>7.4</v>
+        <v>2.44</v>
       </c>
       <c r="BX10">
         <v>40</v>
       </c>
       <c r="BY10">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="BZ10">
         <v>0</v>
@@ -3169,13 +3169,13 @@
         <v>123</v>
       </c>
       <c r="F11">
-        <v>1.87</v>
+        <v>1.77</v>
       </c>
       <c r="G11">
         <v>1.89</v>
       </c>
       <c r="H11">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="I11">
         <v>5</v>
@@ -3184,16 +3184,16 @@
         <v>3.65</v>
       </c>
       <c r="K11">
-        <v>3.75</v>
+        <v>4.3</v>
       </c>
       <c r="L11">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="M11">
         <v>1.09</v>
       </c>
       <c r="N11">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="O11">
         <v>1.45</v>
@@ -3205,10 +3205,10 @@
         <v>2.28</v>
       </c>
       <c r="R11">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="S11">
-        <v>4.5</v>
+        <v>3.85</v>
       </c>
       <c r="T11">
         <v>2.16</v>
@@ -3229,7 +3229,7 @@
         <v>13</v>
       </c>
       <c r="Z11">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="AA11">
         <v>180</v>
@@ -3265,7 +3265,7 @@
         <v>24</v>
       </c>
       <c r="AL11">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AM11">
         <v>260</v>
@@ -3277,118 +3277,118 @@
         <v>170</v>
       </c>
       <c r="AP11">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="AQ11">
+        <v>5.3</v>
+      </c>
+      <c r="AR11">
+        <v>7.4</v>
+      </c>
+      <c r="AS11">
+        <v>8.6</v>
+      </c>
+      <c r="AT11">
+        <v>5.1</v>
+      </c>
+      <c r="AU11">
+        <v>4.6</v>
+      </c>
+      <c r="AV11">
+        <v>6.2</v>
+      </c>
+      <c r="AW11">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AX11">
+        <v>4.7</v>
+      </c>
+      <c r="AY11">
+        <v>4.9</v>
+      </c>
+      <c r="AZ11">
+        <v>6.8</v>
+      </c>
+      <c r="BA11">
+        <v>8.4</v>
+      </c>
+      <c r="BB11">
+        <v>6.2</v>
+      </c>
+      <c r="BC11">
+        <v>6.4</v>
+      </c>
+      <c r="BD11">
+        <v>7.8</v>
+      </c>
+      <c r="BE11">
+        <v>8.6</v>
+      </c>
+      <c r="BF11">
+        <v>6</v>
+      </c>
+      <c r="BG11">
+        <v>8.4</v>
+      </c>
+      <c r="BH11">
+        <v>2.94</v>
+      </c>
+      <c r="BI11">
+        <v>2.44</v>
+      </c>
+      <c r="BJ11">
+        <v>12</v>
+      </c>
+      <c r="BK11">
+        <v>6.4</v>
+      </c>
+      <c r="BL11">
+        <v>1000</v>
+      </c>
+      <c r="BM11">
+        <v>2.4</v>
+      </c>
+      <c r="BN11">
+        <v>4.3</v>
+      </c>
+      <c r="BO11">
+        <v>3.3</v>
+      </c>
+      <c r="BP11">
+        <v>14</v>
+      </c>
+      <c r="BQ11">
+        <v>7</v>
+      </c>
+      <c r="BR11">
+        <v>36</v>
+      </c>
+      <c r="BS11">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BT11">
+        <v>9</v>
+      </c>
+      <c r="BU11">
         <v>5.5</v>
       </c>
-      <c r="AR11">
-        <v>7.6</v>
-      </c>
-      <c r="AS11">
-        <v>9</v>
-      </c>
-      <c r="AT11">
-        <v>3.95</v>
-      </c>
-      <c r="AU11">
-        <v>4.7</v>
-      </c>
-      <c r="AV11">
-        <v>6.4</v>
-      </c>
-      <c r="AW11">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AX11">
-        <v>4.9</v>
-      </c>
-      <c r="AY11">
-        <v>5.1</v>
-      </c>
-      <c r="AZ11">
-        <v>7.2</v>
-      </c>
-      <c r="BA11">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BB11">
-        <v>6.6</v>
-      </c>
-      <c r="BC11">
-        <v>6.8</v>
-      </c>
-      <c r="BD11">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BE11">
+      <c r="BV11">
+        <v>1000</v>
+      </c>
+      <c r="BW11">
         <v>9.199999999999999</v>
       </c>
-      <c r="BF11">
-        <v>6.2</v>
-      </c>
-      <c r="BG11">
-        <v>9</v>
-      </c>
-      <c r="BH11">
-        <v>1000</v>
-      </c>
-      <c r="BI11">
-        <v>1.04</v>
-      </c>
-      <c r="BJ11">
-        <v>1000</v>
-      </c>
-      <c r="BK11">
-        <v>1.04</v>
-      </c>
-      <c r="BL11">
-        <v>1000</v>
-      </c>
-      <c r="BM11">
-        <v>1.04</v>
-      </c>
-      <c r="BN11">
-        <v>1000</v>
-      </c>
-      <c r="BO11">
-        <v>1.04</v>
-      </c>
-      <c r="BP11">
-        <v>1000</v>
-      </c>
-      <c r="BQ11">
-        <v>1.04</v>
-      </c>
-      <c r="BR11">
-        <v>1000</v>
-      </c>
-      <c r="BS11">
-        <v>1.04</v>
-      </c>
-      <c r="BT11">
-        <v>1000</v>
-      </c>
-      <c r="BU11">
-        <v>1.04</v>
-      </c>
-      <c r="BV11">
-        <v>1000</v>
-      </c>
-      <c r="BW11">
-        <v>1.04</v>
-      </c>
       <c r="BX11">
         <v>1000</v>
       </c>
       <c r="BY11">
-        <v>1.04</v>
+        <v>2.36</v>
       </c>
       <c r="BZ11">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="CA11">
-        <v>1.04</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CB11" t="s">
         <v>127</v>
@@ -3417,10 +3417,10 @@
         <v>2.5</v>
       </c>
       <c r="H12">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="I12">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="J12">
         <v>3.05</v>
@@ -3432,19 +3432,19 @@
         <v>1.57</v>
       </c>
       <c r="M12">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="N12">
         <v>2.62</v>
       </c>
       <c r="O12">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="P12">
         <v>1.55</v>
       </c>
       <c r="Q12">
-        <v>2.6</v>
+        <v>2.66</v>
       </c>
       <c r="R12">
         <v>1.2</v>
@@ -3453,7 +3453,7 @@
         <v>5.4</v>
       </c>
       <c r="T12">
-        <v>2.1</v>
+        <v>1.89</v>
       </c>
       <c r="U12">
         <v>1.8</v>
@@ -3462,22 +3462,22 @@
         <v>1.35</v>
       </c>
       <c r="W12">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="X12">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="Y12">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="Z12">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AA12">
         <v>100</v>
       </c>
       <c r="AB12">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AC12">
         <v>7.4</v>
@@ -3489,13 +3489,13 @@
         <v>75</v>
       </c>
       <c r="AF12">
-        <v>17</v>
+        <v>14.5</v>
       </c>
       <c r="AG12">
-        <v>15</v>
+        <v>12.5</v>
       </c>
       <c r="AH12">
-        <v>28</v>
+        <v>950</v>
       </c>
       <c r="AI12">
         <v>100</v>
@@ -3525,10 +3525,10 @@
         <v>9</v>
       </c>
       <c r="AR12">
-        <v>17.5</v>
+        <v>5.2</v>
       </c>
       <c r="AS12">
-        <v>5.3</v>
+        <v>5.9</v>
       </c>
       <c r="AT12">
         <v>6.6</v>
@@ -3540,37 +3540,37 @@
         <v>14</v>
       </c>
       <c r="AW12">
-        <v>5.2</v>
+        <v>5.8</v>
       </c>
       <c r="AX12">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AY12">
         <v>10.5</v>
       </c>
       <c r="AZ12">
-        <v>19.5</v>
+        <v>4.9</v>
       </c>
       <c r="BA12">
-        <v>5.3</v>
+        <v>5.9</v>
       </c>
       <c r="BB12">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="BC12">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="BD12">
-        <v>5.2</v>
+        <v>5.8</v>
       </c>
       <c r="BE12">
+        <v>6</v>
+      </c>
+      <c r="BF12">
         <v>5.5</v>
       </c>
-      <c r="BF12">
-        <v>5</v>
-      </c>
       <c r="BG12">
-        <v>5.3</v>
+        <v>5.9</v>
       </c>
       <c r="BH12">
         <v>3.15</v>
@@ -3594,7 +3594,7 @@
         <v>6</v>
       </c>
       <c r="BO12">
-        <v>4.5</v>
+        <v>3.9</v>
       </c>
       <c r="BP12">
         <v>26</v>
@@ -3653,64 +3653,64 @@
         <v>125</v>
       </c>
       <c r="F13">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="G13">
-        <v>2.4</v>
+        <v>2.48</v>
       </c>
       <c r="H13">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="I13">
-        <v>5.2</v>
+        <v>4.6</v>
       </c>
       <c r="J13">
-        <v>2.86</v>
+        <v>2.82</v>
       </c>
       <c r="K13">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="L13">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="M13">
         <v>1.14</v>
       </c>
       <c r="N13">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="O13">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="P13">
         <v>1.45</v>
       </c>
       <c r="Q13">
-        <v>2.64</v>
+        <v>2.78</v>
       </c>
       <c r="R13">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="S13">
-        <v>1.05</v>
+        <v>5.3</v>
       </c>
       <c r="T13">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="U13">
+        <v>1.66</v>
+      </c>
+      <c r="V13">
+        <v>1.27</v>
+      </c>
+      <c r="W13">
         <v>1.67</v>
       </c>
-      <c r="V13">
-        <v>1.26</v>
-      </c>
-      <c r="W13">
-        <v>1.71</v>
-      </c>
       <c r="X13">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="Y13">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="Z13">
         <v>34</v>
@@ -3719,13 +3719,13 @@
         <v>130</v>
       </c>
       <c r="AB13">
+        <v>7.4</v>
+      </c>
+      <c r="AC13">
         <v>7.6</v>
       </c>
-      <c r="AC13">
-        <v>8.199999999999999</v>
-      </c>
       <c r="AD13">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AE13">
         <v>95</v>
@@ -3758,100 +3758,100 @@
         <v>42</v>
       </c>
       <c r="AO13">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="AP13">
-        <v>3.35</v>
+        <v>3.7</v>
       </c>
       <c r="AQ13">
-        <v>3.75</v>
+        <v>4.1</v>
       </c>
       <c r="AR13">
-        <v>4.6</v>
+        <v>5.5</v>
       </c>
       <c r="AS13">
-        <v>5.1</v>
+        <v>6.2</v>
       </c>
       <c r="AT13">
-        <v>3.15</v>
+        <v>3.45</v>
       </c>
       <c r="AU13">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="AV13">
-        <v>4.3</v>
+        <v>4.9</v>
       </c>
       <c r="AW13">
-        <v>5.1</v>
+        <v>6</v>
       </c>
       <c r="AX13">
-        <v>3.9</v>
+        <v>4.5</v>
       </c>
       <c r="AY13">
-        <v>3.9</v>
+        <v>4.4</v>
       </c>
       <c r="AZ13">
-        <v>4.6</v>
+        <v>5.4</v>
       </c>
       <c r="BA13">
-        <v>5.1</v>
+        <v>6.2</v>
       </c>
       <c r="BB13">
-        <v>4.7</v>
+        <v>5.6</v>
       </c>
       <c r="BC13">
-        <v>4.7</v>
+        <v>5.6</v>
       </c>
       <c r="BD13">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BE13">
-        <v>5.3</v>
+        <v>6.4</v>
       </c>
       <c r="BF13">
-        <v>4.7</v>
+        <v>5.7</v>
       </c>
       <c r="BG13">
-        <v>5.2</v>
+        <v>6.2</v>
       </c>
       <c r="BH13">
-        <v>2.84</v>
+        <v>2.78</v>
       </c>
       <c r="BI13">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="BJ13">
         <v>14</v>
       </c>
       <c r="BK13">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BL13">
         <v>1000</v>
       </c>
       <c r="BM13">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="BN13">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BO13">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="BP13">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BQ13">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BR13">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="BS13">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BT13">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BU13">
         <v>3.6</v>
@@ -3860,19 +3860,19 @@
         <v>55</v>
       </c>
       <c r="BW13">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BX13">
         <v>1000</v>
       </c>
       <c r="BY13">
+        <v>5.9</v>
+      </c>
+      <c r="BZ13">
+        <v>1000</v>
+      </c>
+      <c r="CA13">
         <v>5.8</v>
-      </c>
-      <c r="BZ13">
-        <v>1000</v>
-      </c>
-      <c r="CA13">
-        <v>5.7</v>
       </c>
       <c r="CB13" t="s">
         <v>127</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-06.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-06.xlsx
@@ -397,7 +397,7 @@
     <t>Always Ready</t>
   </si>
   <si>
-    <t>2026-08-05 08:18:51</t>
+    <t>2026-08-05 10:26:28</t>
   </si>
 </sst>
 </file>
@@ -991,16 +991,16 @@
         <v>114</v>
       </c>
       <c r="F2">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="G2">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="H2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J2">
         <v>10.5</v>
@@ -1015,19 +1015,19 @@
         <v>1.01</v>
       </c>
       <c r="N2">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="O2">
         <v>1.05</v>
       </c>
       <c r="P2">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="Q2">
         <v>1.2</v>
       </c>
       <c r="R2">
-        <v>2.58</v>
+        <v>2.64</v>
       </c>
       <c r="S2">
         <v>1.51</v>
@@ -1036,13 +1036,13 @@
         <v>1.92</v>
       </c>
       <c r="U2">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="V2">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="W2">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="X2">
         <v>950</v>
@@ -1057,154 +1057,154 @@
         <v>1000</v>
       </c>
       <c r="AB2">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AC2">
         <v>34</v>
       </c>
       <c r="AD2">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="AE2">
-        <v>350</v>
+        <v>390</v>
       </c>
       <c r="AF2">
-        <v>11.5</v>
+        <v>15</v>
       </c>
       <c r="AG2">
-        <v>17.5</v>
+        <v>19.5</v>
       </c>
       <c r="AH2">
         <v>44</v>
       </c>
       <c r="AI2">
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="AJ2">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AK2">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AL2">
         <v>42</v>
       </c>
       <c r="AM2">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="AN2">
-        <v>2.22</v>
+        <v>2.14</v>
       </c>
       <c r="AO2">
-        <v>250</v>
+        <v>290</v>
       </c>
       <c r="AP2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AQ2">
-        <v>9.199999999999999</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR2">
-        <v>9.6</v>
+        <v>8.4</v>
       </c>
       <c r="AS2">
-        <v>9.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AT2">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AU2">
-        <v>21</v>
+        <v>7.4</v>
       </c>
       <c r="AV2">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="AW2">
-        <v>9.6</v>
+        <v>8.4</v>
       </c>
       <c r="AX2">
         <v>11</v>
       </c>
       <c r="AY2">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="AZ2">
-        <v>8</v>
+        <v>7.2</v>
       </c>
       <c r="BA2">
-        <v>9.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB2">
         <v>8.6</v>
       </c>
       <c r="BC2">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BD2">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="BE2">
-        <v>9.199999999999999</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF2">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="BG2">
-        <v>9.4</v>
+        <v>8.4</v>
       </c>
       <c r="BH2">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BI2">
-        <v>6</v>
+        <v>4.2</v>
       </c>
       <c r="BJ2">
         <v>14.5</v>
       </c>
       <c r="BK2">
+        <v>5.4</v>
+      </c>
+      <c r="BL2">
+        <v>1000</v>
+      </c>
+      <c r="BM2">
+        <v>7.8</v>
+      </c>
+      <c r="BN2">
         <v>4.9</v>
       </c>
-      <c r="BL2">
-        <v>1000</v>
-      </c>
-      <c r="BM2">
-        <v>6.8</v>
-      </c>
-      <c r="BN2">
-        <v>5</v>
-      </c>
       <c r="BO2">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="BP2">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BQ2">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BR2">
         <v>18</v>
       </c>
       <c r="BS2">
-        <v>5.2</v>
+        <v>5.8</v>
       </c>
       <c r="BT2">
         <v>25</v>
       </c>
       <c r="BU2">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="BV2">
         <v>1000</v>
       </c>
       <c r="BW2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BX2">
         <v>1000</v>
       </c>
       <c r="BY2">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="BZ2">
         <v>0</v>
@@ -1239,220 +1239,220 @@
         <v>2.66</v>
       </c>
       <c r="H3">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="I3">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="J3">
-        <v>2.84</v>
+        <v>2.78</v>
       </c>
       <c r="K3">
-        <v>2.92</v>
+        <v>2.82</v>
       </c>
       <c r="L3">
-        <v>1.8</v>
+        <v>1.88</v>
       </c>
       <c r="M3">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="N3">
-        <v>2.18</v>
+        <v>2.04</v>
       </c>
       <c r="O3">
-        <v>1.81</v>
+        <v>1.94</v>
       </c>
       <c r="P3">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="Q3">
-        <v>3.55</v>
+        <v>3.9</v>
       </c>
       <c r="R3">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="S3">
-        <v>8.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="T3">
-        <v>2.6</v>
+        <v>2.74</v>
       </c>
       <c r="U3">
-        <v>1.59</v>
+        <v>1.5</v>
       </c>
       <c r="V3">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W3">
         <v>1.6</v>
       </c>
       <c r="X3">
-        <v>6.4</v>
+        <v>5.9</v>
       </c>
       <c r="Y3">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="Z3">
+        <v>34</v>
+      </c>
+      <c r="AA3">
+        <v>110</v>
+      </c>
+      <c r="AB3">
+        <v>6</v>
+      </c>
+      <c r="AC3">
+        <v>7.8</v>
+      </c>
+      <c r="AD3">
         <v>22</v>
       </c>
-      <c r="AA3">
-        <v>1000</v>
-      </c>
-      <c r="AB3">
-        <v>6.4</v>
-      </c>
-      <c r="AC3">
-        <v>7</v>
-      </c>
-      <c r="AD3">
-        <v>18.5</v>
-      </c>
       <c r="AE3">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AF3">
         <v>14.5</v>
       </c>
       <c r="AG3">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AH3">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="AI3">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AJ3">
         <v>46</v>
       </c>
       <c r="AK3">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AL3">
-        <v>110</v>
+        <v>150</v>
       </c>
       <c r="AM3">
-        <v>340</v>
+        <v>490</v>
       </c>
       <c r="AN3">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="AO3">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AP3">
-        <v>5.8</v>
+        <v>5.3</v>
       </c>
       <c r="AQ3">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="AR3">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AS3">
-        <v>70</v>
+        <v>48</v>
       </c>
       <c r="AT3">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="AU3">
         <v>6.6</v>
       </c>
       <c r="AV3">
-        <v>16.5</v>
+        <v>18.5</v>
       </c>
       <c r="AW3">
         <v>60</v>
       </c>
       <c r="AX3">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AY3">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AZ3">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="BA3">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="BB3">
         <v>38</v>
       </c>
       <c r="BC3">
+        <v>32</v>
+      </c>
+      <c r="BD3">
+        <v>55</v>
+      </c>
+      <c r="BE3">
+        <v>85</v>
+      </c>
+      <c r="BF3">
+        <v>34</v>
+      </c>
+      <c r="BG3">
         <v>42</v>
       </c>
-      <c r="BD3">
-        <v>38</v>
-      </c>
-      <c r="BE3">
-        <v>55</v>
-      </c>
-      <c r="BF3">
-        <v>50</v>
-      </c>
-      <c r="BG3">
-        <v>40</v>
-      </c>
       <c r="BH3">
-        <v>2.38</v>
+        <v>1000</v>
       </c>
       <c r="BI3">
-        <v>2.1</v>
+        <v>1.04</v>
       </c>
       <c r="BJ3">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="BK3">
-        <v>7</v>
+        <v>1.04</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>15</v>
+        <v>1.04</v>
       </c>
       <c r="BN3">
-        <v>5.5</v>
+        <v>1000</v>
       </c>
       <c r="BO3">
-        <v>4.3</v>
+        <v>1.04</v>
       </c>
       <c r="BP3">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="BQ3">
-        <v>9.800000000000001</v>
+        <v>1.04</v>
       </c>
       <c r="BR3">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="BS3">
-        <v>12.5</v>
+        <v>1.04</v>
       </c>
       <c r="BT3">
-        <v>6.6</v>
+        <v>1000</v>
       </c>
       <c r="BU3">
-        <v>5.4</v>
+        <v>1.04</v>
       </c>
       <c r="BV3">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="BW3">
-        <v>11</v>
+        <v>1.04</v>
       </c>
       <c r="BX3">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="BY3">
-        <v>13</v>
+        <v>1.04</v>
       </c>
       <c r="BZ3">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="CA3">
-        <v>13</v>
+        <v>1.04</v>
       </c>
       <c r="CB3" t="s">
         <v>127</v>
@@ -1475,19 +1475,19 @@
         <v>116</v>
       </c>
       <c r="F4">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="G4">
         <v>3.2</v>
       </c>
       <c r="H4">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="I4">
         <v>2.92</v>
       </c>
       <c r="J4">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="K4">
         <v>3.25</v>
@@ -1499,28 +1499,28 @@
         <v>1.12</v>
       </c>
       <c r="N4">
-        <v>2.78</v>
+        <v>2.7</v>
       </c>
       <c r="O4">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="P4">
-        <v>1.59</v>
+        <v>1.56</v>
       </c>
       <c r="Q4">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="R4">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="S4">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="T4">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="U4">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="V4">
         <v>1.52</v>
@@ -1529,7 +1529,7 @@
         <v>1.46</v>
       </c>
       <c r="X4">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Y4">
         <v>10.5</v>
@@ -1544,7 +1544,7 @@
         <v>9.6</v>
       </c>
       <c r="AC4">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AD4">
         <v>13.5</v>
@@ -1568,22 +1568,22 @@
         <v>60</v>
       </c>
       <c r="AK4">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="AL4">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="AM4">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="AN4">
         <v>70</v>
       </c>
       <c r="AO4">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="AP4">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="AQ4">
         <v>7.6</v>
@@ -1592,10 +1592,10 @@
         <v>14.5</v>
       </c>
       <c r="AS4">
-        <v>6.8</v>
+        <v>34</v>
       </c>
       <c r="AT4">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="AU4">
         <v>6</v>
@@ -1607,52 +1607,52 @@
         <v>30</v>
       </c>
       <c r="AX4">
-        <v>13.5</v>
+        <v>16</v>
       </c>
       <c r="AY4">
         <v>12</v>
       </c>
       <c r="AZ4">
-        <v>18.5</v>
+        <v>6.2</v>
       </c>
       <c r="BA4">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="BB4">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="BC4">
         <v>32</v>
       </c>
       <c r="BD4">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="BE4">
+        <v>8</v>
+      </c>
+      <c r="BF4">
         <v>7.6</v>
       </c>
-      <c r="BF4">
-        <v>7</v>
-      </c>
       <c r="BG4">
-        <v>6.8</v>
+        <v>34</v>
       </c>
       <c r="BH4">
-        <v>2.78</v>
+        <v>2.72</v>
       </c>
       <c r="BI4">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="BJ4">
         <v>11.5</v>
       </c>
       <c r="BK4">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BN4">
         <v>6</v>
@@ -1664,37 +1664,37 @@
         <v>1000</v>
       </c>
       <c r="BQ4">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="BR4">
         <v>1000</v>
       </c>
       <c r="BS4">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BT4">
         <v>5.7</v>
       </c>
       <c r="BU4">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BV4">
         <v>1000</v>
       </c>
       <c r="BW4">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX4">
         <v>1000</v>
       </c>
       <c r="BY4">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BZ4">
         <v>1000</v>
       </c>
       <c r="CA4">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="CB4" t="s">
         <v>127</v>
@@ -1726,43 +1726,43 @@
         <v>4.6</v>
       </c>
       <c r="I5">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="J5">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="K5">
         <v>4.6</v>
       </c>
       <c r="L5">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="M5">
         <v>1.04</v>
       </c>
       <c r="N5">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="O5">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="P5">
-        <v>2.46</v>
+        <v>2.52</v>
       </c>
       <c r="Q5">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="R5">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="S5">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="T5">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="U5">
-        <v>2.28</v>
+        <v>2.36</v>
       </c>
       <c r="V5">
         <v>1.25</v>
@@ -1774,166 +1774,166 @@
         <v>26</v>
       </c>
       <c r="Y5">
-        <v>950</v>
+        <v>30</v>
       </c>
       <c r="Z5">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AA5">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AB5">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AC5">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AD5">
         <v>21</v>
       </c>
       <c r="AE5">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="AF5">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AG5">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AH5">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AI5">
         <v>60</v>
       </c>
       <c r="AJ5">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="AK5">
-        <v>19</v>
+        <v>16.5</v>
       </c>
       <c r="AL5">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AM5">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AN5">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="AO5">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="AP5">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AQ5">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AR5">
         <v>32</v>
       </c>
       <c r="AS5">
-        <v>5.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT5">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AU5">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV5">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AW5">
-        <v>5.6</v>
+        <v>36</v>
       </c>
       <c r="AX5">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AY5">
         <v>9</v>
       </c>
       <c r="AZ5">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="BA5">
-        <v>5.6</v>
+        <v>32</v>
       </c>
       <c r="BB5">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="BC5">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BD5">
         <v>21</v>
       </c>
       <c r="BE5">
-        <v>5.7</v>
+        <v>55</v>
       </c>
       <c r="BF5">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BG5">
-        <v>5.5</v>
+        <v>27</v>
       </c>
       <c r="BH5">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BI5">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="BJ5">
         <v>9.6</v>
       </c>
       <c r="BK5">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BL5">
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN5">
         <v>4.9</v>
       </c>
       <c r="BO5">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="BP5">
         <v>11.5</v>
       </c>
       <c r="BQ5">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BR5">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="BS5">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BT5">
         <v>9</v>
       </c>
       <c r="BU5">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BV5">
         <v>1000</v>
       </c>
       <c r="BW5">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BX5">
         <v>1000</v>
       </c>
       <c r="BY5">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ5">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="CA5">
         <v>6</v>
@@ -1959,19 +1959,19 @@
         <v>118</v>
       </c>
       <c r="F6">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="G6">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="H6">
         <v>3.75</v>
       </c>
       <c r="I6">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="J6">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K6">
         <v>3.5</v>
@@ -1983,25 +1983,25 @@
         <v>1.09</v>
       </c>
       <c r="N6">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="O6">
         <v>1.39</v>
       </c>
       <c r="P6">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="Q6">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="R6">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="S6">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="T6">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="U6">
         <v>1.99</v>
@@ -2010,7 +2010,7 @@
         <v>1.33</v>
       </c>
       <c r="W6">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="X6">
         <v>14.5</v>
@@ -2019,19 +2019,19 @@
         <v>13.5</v>
       </c>
       <c r="Z6">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AA6">
         <v>100</v>
       </c>
       <c r="AB6">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AC6">
         <v>9.199999999999999</v>
       </c>
       <c r="AD6">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AE6">
         <v>65</v>
@@ -2046,7 +2046,7 @@
         <v>20</v>
       </c>
       <c r="AI6">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="AJ6">
         <v>30</v>
@@ -2055,7 +2055,7 @@
         <v>27</v>
       </c>
       <c r="AL6">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="AM6">
         <v>150</v>
@@ -2073,10 +2073,10 @@
         <v>10.5</v>
       </c>
       <c r="AR6">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="AS6">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="AT6">
         <v>7.4</v>
@@ -2088,7 +2088,7 @@
         <v>13.5</v>
       </c>
       <c r="AW6">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="AX6">
         <v>11</v>
@@ -2100,7 +2100,7 @@
         <v>16.5</v>
       </c>
       <c r="BA6">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="BB6">
         <v>24</v>
@@ -2112,19 +2112,19 @@
         <v>32</v>
       </c>
       <c r="BE6">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BF6">
         <v>15.5</v>
       </c>
       <c r="BG6">
-        <v>5.7</v>
+        <v>7</v>
       </c>
       <c r="BH6">
         <v>3.25</v>
       </c>
       <c r="BI6">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="BJ6">
         <v>10.5</v>
@@ -2142,7 +2142,7 @@
         <v>5.1</v>
       </c>
       <c r="BO6">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="BP6">
         <v>17.5</v>
@@ -2151,7 +2151,7 @@
         <v>6.4</v>
       </c>
       <c r="BR6">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BS6">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>5.3</v>
       </c>
       <c r="BV6">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BW6">
         <v>8</v>
@@ -2201,16 +2201,16 @@
         <v>119</v>
       </c>
       <c r="F7">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="G7">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="H7">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="I7">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="J7">
         <v>3.1</v>
@@ -2222,25 +2222,25 @@
         <v>1.52</v>
       </c>
       <c r="M7">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="N7">
-        <v>2.5</v>
+        <v>2.32</v>
       </c>
       <c r="O7">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="P7">
-        <v>1.52</v>
+        <v>1.47</v>
       </c>
       <c r="Q7">
-        <v>2.66</v>
+        <v>2.56</v>
       </c>
       <c r="R7">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="S7">
-        <v>2.88</v>
+        <v>3.45</v>
       </c>
       <c r="T7">
         <v>2.32</v>
@@ -2252,25 +2252,25 @@
         <v>1.19</v>
       </c>
       <c r="W7">
-        <v>1.96</v>
+        <v>1.92</v>
       </c>
       <c r="X7">
         <v>9.4</v>
       </c>
       <c r="Y7">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="Z7">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AA7">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="AB7">
         <v>7</v>
       </c>
       <c r="AC7">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD7">
         <v>28</v>
@@ -2279,19 +2279,19 @@
         <v>140</v>
       </c>
       <c r="AF7">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AG7">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AH7">
         <v>34</v>
       </c>
       <c r="AI7">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="AJ7">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AK7">
         <v>34</v>
@@ -2300,37 +2300,37 @@
         <v>80</v>
       </c>
       <c r="AM7">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="AN7">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AO7">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="AP7">
         <v>3.35</v>
       </c>
       <c r="AQ7">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="AR7">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="AS7">
         <v>5.1</v>
       </c>
       <c r="AT7">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="AU7">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="AV7">
         <v>4.4</v>
       </c>
       <c r="AW7">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="AX7">
         <v>3.6</v>
@@ -2342,7 +2342,7 @@
         <v>4.5</v>
       </c>
       <c r="BA7">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BB7">
         <v>4.4</v>
@@ -2354,16 +2354,16 @@
         <v>4.9</v>
       </c>
       <c r="BE7">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BF7">
         <v>4.4</v>
       </c>
       <c r="BG7">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BH7">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="BI7">
         <v>2.24</v>
@@ -2372,49 +2372,49 @@
         <v>14.5</v>
       </c>
       <c r="BK7">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BL7">
         <v>1000</v>
       </c>
       <c r="BM7">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BN7">
         <v>4.8</v>
       </c>
       <c r="BO7">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="BP7">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BQ7">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BR7">
         <v>50</v>
       </c>
       <c r="BS7">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BT7">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BU7">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="BV7">
         <v>75</v>
       </c>
       <c r="BW7">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BX7">
         <v>100</v>
       </c>
       <c r="BY7">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BZ7">
         <v>0</v>
@@ -2449,16 +2449,16 @@
         <v>1.71</v>
       </c>
       <c r="H8">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="I8">
         <v>6</v>
       </c>
       <c r="J8">
-        <v>1.1</v>
+        <v>4</v>
       </c>
       <c r="K8">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="L8">
         <v>1.17</v>
@@ -2491,7 +2491,7 @@
         <v>2.84</v>
       </c>
       <c r="V8">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="W8">
         <v>2.4</v>
@@ -2500,7 +2500,7 @@
         <v>60</v>
       </c>
       <c r="Y8">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="Z8">
         <v>65</v>
@@ -2515,7 +2515,7 @@
         <v>17</v>
       </c>
       <c r="AD8">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AE8">
         <v>55</v>
@@ -2533,7 +2533,7 @@
         <v>46</v>
       </c>
       <c r="AJ8">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AK8">
         <v>17.5</v>
@@ -2551,58 +2551,58 @@
         <v>27</v>
       </c>
       <c r="AP8">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="AQ8">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="AR8">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="AS8">
+        <v>5.9</v>
+      </c>
+      <c r="AT8">
+        <v>4.9</v>
+      </c>
+      <c r="AU8">
+        <v>4.5</v>
+      </c>
+      <c r="AV8">
+        <v>4.9</v>
+      </c>
+      <c r="AW8">
+        <v>5.6</v>
+      </c>
+      <c r="AX8">
+        <v>4.6</v>
+      </c>
+      <c r="AY8">
+        <v>4.1</v>
+      </c>
+      <c r="AZ8">
+        <v>4.7</v>
+      </c>
+      <c r="BA8">
         <v>5.5</v>
       </c>
-      <c r="AT8">
+      <c r="BB8">
+        <v>4.8</v>
+      </c>
+      <c r="BC8">
         <v>4.6</v>
       </c>
-      <c r="AU8">
-        <v>4.3</v>
-      </c>
-      <c r="AV8">
-        <v>4.7</v>
-      </c>
-      <c r="AW8">
-        <v>5.2</v>
-      </c>
-      <c r="AX8">
-        <v>4.4</v>
-      </c>
-      <c r="AY8">
-        <v>3.95</v>
-      </c>
-      <c r="AZ8">
-        <v>4.4</v>
-      </c>
-      <c r="BA8">
-        <v>5.2</v>
-      </c>
-      <c r="BB8">
-        <v>4.6</v>
-      </c>
-      <c r="BC8">
-        <v>4.3</v>
-      </c>
       <c r="BD8">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BE8">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="BF8">
-        <v>2.74</v>
+        <v>2.84</v>
       </c>
       <c r="BG8">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BH8">
         <v>6.8</v>
@@ -2694,10 +2694,10 @@
         <v>2.78</v>
       </c>
       <c r="I9">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="J9">
-        <v>2.94</v>
+        <v>2.9</v>
       </c>
       <c r="K9">
         <v>3.75</v>
@@ -2727,13 +2727,13 @@
         <v>3.35</v>
       </c>
       <c r="T9">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="U9">
         <v>2.08</v>
       </c>
       <c r="V9">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="W9">
         <v>1.53</v>
@@ -2757,10 +2757,10 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AD9">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AE9">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AF9">
         <v>18.5</v>
@@ -2793,64 +2793,64 @@
         <v>40</v>
       </c>
       <c r="AP9">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="AQ9">
         <v>7.4</v>
       </c>
       <c r="AR9">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="AS9">
-        <v>5.1</v>
+        <v>4.8</v>
       </c>
       <c r="AT9">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="AU9">
         <v>5</v>
       </c>
       <c r="AV9">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="AW9">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="AX9">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="AY9">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="AZ9">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="BA9">
-        <v>5.1</v>
+        <v>4.8</v>
       </c>
       <c r="BB9">
+        <v>4.7</v>
+      </c>
+      <c r="BC9">
+        <v>4.6</v>
+      </c>
+      <c r="BD9">
+        <v>4.8</v>
+      </c>
+      <c r="BE9">
         <v>5</v>
       </c>
-      <c r="BC9">
-        <v>4.9</v>
-      </c>
-      <c r="BD9">
-        <v>5.1</v>
-      </c>
-      <c r="BE9">
-        <v>5.3</v>
-      </c>
       <c r="BF9">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="BG9">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="BH9">
         <v>3.4</v>
       </c>
       <c r="BI9">
-        <v>2.64</v>
+        <v>2.92</v>
       </c>
       <c r="BJ9">
         <v>10</v>
@@ -2966,7 +2966,7 @@
         <v>1.35</v>
       </c>
       <c r="S10">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="T10">
         <v>1.74</v>
@@ -3411,7 +3411,7 @@
         <v>124</v>
       </c>
       <c r="F12">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="G12">
         <v>2.5</v>
@@ -3420,7 +3420,7 @@
         <v>3.5</v>
       </c>
       <c r="I12">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="J12">
         <v>3.05</v>
@@ -3429,7 +3429,7 @@
         <v>3.15</v>
       </c>
       <c r="L12">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="M12">
         <v>1.12</v>
@@ -3438,7 +3438,7 @@
         <v>2.62</v>
       </c>
       <c r="O12">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="P12">
         <v>1.55</v>
@@ -3453,25 +3453,25 @@
         <v>5.4</v>
       </c>
       <c r="T12">
-        <v>1.89</v>
+        <v>2.1</v>
       </c>
       <c r="U12">
         <v>1.8</v>
       </c>
       <c r="V12">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W12">
         <v>1.66</v>
       </c>
       <c r="X12">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Y12">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Z12">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="AA12">
         <v>100</v>
@@ -3483,19 +3483,19 @@
         <v>7.4</v>
       </c>
       <c r="AD12">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AE12">
         <v>75</v>
       </c>
       <c r="AF12">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AG12">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AH12">
-        <v>950</v>
+        <v>25</v>
       </c>
       <c r="AI12">
         <v>100</v>
@@ -3519,16 +3519,16 @@
         <v>100</v>
       </c>
       <c r="AP12">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AQ12">
         <v>9</v>
       </c>
       <c r="AR12">
-        <v>5.2</v>
+        <v>17.5</v>
       </c>
       <c r="AS12">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="AT12">
         <v>6.6</v>
@@ -3540,37 +3540,37 @@
         <v>14</v>
       </c>
       <c r="AW12">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="AX12">
-        <v>12.5</v>
+        <v>10</v>
       </c>
       <c r="AY12">
         <v>10.5</v>
       </c>
       <c r="AZ12">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="BA12">
+        <v>6.4</v>
+      </c>
+      <c r="BB12">
+        <v>6</v>
+      </c>
+      <c r="BC12">
+        <v>24</v>
+      </c>
+      <c r="BD12">
+        <v>6.2</v>
+      </c>
+      <c r="BE12">
+        <v>6.6</v>
+      </c>
+      <c r="BF12">
         <v>5.9</v>
       </c>
-      <c r="BB12">
-        <v>5.5</v>
-      </c>
-      <c r="BC12">
-        <v>5.4</v>
-      </c>
-      <c r="BD12">
-        <v>5.8</v>
-      </c>
-      <c r="BE12">
-        <v>6</v>
-      </c>
-      <c r="BF12">
-        <v>5.5</v>
-      </c>
       <c r="BG12">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="BH12">
         <v>3.15</v>
@@ -3582,13 +3582,13 @@
         <v>13.5</v>
       </c>
       <c r="BK12">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="BL12">
         <v>1000</v>
       </c>
       <c r="BM12">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BN12">
         <v>6</v>
@@ -3600,16 +3600,16 @@
         <v>26</v>
       </c>
       <c r="BQ12">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BR12">
         <v>55</v>
       </c>
       <c r="BS12">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BT12">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BU12">
         <v>5</v>
@@ -3618,7 +3618,7 @@
         <v>44</v>
       </c>
       <c r="BW12">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BX12">
         <v>70</v>
@@ -3630,7 +3630,7 @@
         <v>60</v>
       </c>
       <c r="CA12">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="CB12" t="s">
         <v>127</v>
@@ -3653,16 +3653,16 @@
         <v>125</v>
       </c>
       <c r="F13">
-        <v>2.18</v>
+        <v>2.24</v>
       </c>
       <c r="G13">
-        <v>2.48</v>
+        <v>2.54</v>
       </c>
       <c r="H13">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="I13">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="J13">
         <v>2.82</v>
@@ -3671,19 +3671,19 @@
         <v>3.2</v>
       </c>
       <c r="L13">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="M13">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="N13">
         <v>2.22</v>
       </c>
       <c r="O13">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="P13">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="Q13">
         <v>2.78</v>
@@ -3692,34 +3692,34 @@
         <v>1.15</v>
       </c>
       <c r="S13">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="T13">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="U13">
-        <v>1.66</v>
+        <v>1.58</v>
       </c>
       <c r="V13">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="W13">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="X13">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Y13">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Z13">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="AA13">
         <v>130</v>
       </c>
       <c r="AB13">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="AC13">
         <v>7.6</v>
@@ -3728,13 +3728,13 @@
         <v>20</v>
       </c>
       <c r="AE13">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AF13">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AG13">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AH13">
         <v>32</v>
@@ -3755,70 +3755,70 @@
         <v>270</v>
       </c>
       <c r="AN13">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="AO13">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AP13">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="AQ13">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="AR13">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="AS13">
+        <v>7.4</v>
+      </c>
+      <c r="AT13">
+        <v>5.2</v>
+      </c>
+      <c r="AU13">
+        <v>3.85</v>
+      </c>
+      <c r="AV13">
+        <v>5.6</v>
+      </c>
+      <c r="AW13">
+        <v>7.2</v>
+      </c>
+      <c r="AX13">
+        <v>11</v>
+      </c>
+      <c r="AY13">
+        <v>10.5</v>
+      </c>
+      <c r="AZ13">
         <v>6.2</v>
       </c>
-      <c r="AT13">
-        <v>3.45</v>
-      </c>
-      <c r="AU13">
-        <v>3.5</v>
-      </c>
-      <c r="AV13">
-        <v>4.9</v>
-      </c>
-      <c r="AW13">
-        <v>6</v>
-      </c>
-      <c r="AX13">
-        <v>4.5</v>
-      </c>
-      <c r="AY13">
-        <v>4.4</v>
-      </c>
-      <c r="AZ13">
-        <v>5.4</v>
-      </c>
       <c r="BA13">
-        <v>6.2</v>
+        <v>7.4</v>
       </c>
       <c r="BB13">
-        <v>5.6</v>
+        <v>6.4</v>
       </c>
       <c r="BC13">
-        <v>5.6</v>
+        <v>6.6</v>
       </c>
       <c r="BD13">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BE13">
-        <v>6.4</v>
+        <v>7.6</v>
       </c>
       <c r="BF13">
-        <v>5.7</v>
+        <v>6.8</v>
       </c>
       <c r="BG13">
-        <v>6.2</v>
+        <v>7.4</v>
       </c>
       <c r="BH13">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="BI13">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="BJ13">
         <v>14</v>
@@ -3830,31 +3830,31 @@
         <v>1000</v>
       </c>
       <c r="BM13">
-        <v>1.93</v>
+        <v>6.2</v>
       </c>
       <c r="BN13">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BO13">
-        <v>2.92</v>
+        <v>3.9</v>
       </c>
       <c r="BP13">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BQ13">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BR13">
         <v>60</v>
       </c>
       <c r="BS13">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BT13">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BU13">
-        <v>3.6</v>
+        <v>5.5</v>
       </c>
       <c r="BV13">
         <v>55</v>
@@ -3872,7 +3872,7 @@
         <v>1000</v>
       </c>
       <c r="CA13">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="CB13" t="s">
         <v>127</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-06.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-06.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="134">
   <si>
     <t>League</t>
   </si>
@@ -301,6 +301,9 @@
     <t>19:15:00</t>
   </si>
   <si>
+    <t>19:30:00</t>
+  </si>
+  <si>
     <t>20:00:00</t>
   </si>
   <si>
@@ -313,6 +316,9 @@
     <t>22:00:00</t>
   </si>
   <si>
+    <t>22:30:00</t>
+  </si>
+  <si>
     <t>23:00:00</t>
   </si>
   <si>
@@ -340,6 +346,9 @@
     <t>IR Reykjavik</t>
   </si>
   <si>
+    <t>Rayo Zuliano</t>
+  </si>
+  <si>
     <t>Estudiantes de Merida</t>
   </si>
   <si>
@@ -352,6 +361,9 @@
     <t>Union Santa Fe</t>
   </si>
   <si>
+    <t>Puerto Cabello</t>
+  </si>
+  <si>
     <t>Orsomarso</t>
   </si>
   <si>
@@ -379,6 +391,9 @@
     <t>Aegir</t>
   </si>
   <si>
+    <t>Academia Anzoategui FC</t>
+  </si>
+  <si>
     <t>Zamora FC</t>
   </si>
   <si>
@@ -391,13 +406,16 @@
     <t>Lanus</t>
   </si>
   <si>
+    <t>Caracas</t>
+  </si>
+  <si>
     <t>Tigres FC Zipaquira</t>
   </si>
   <si>
     <t>Always Ready</t>
   </si>
   <si>
-    <t>2026-08-05 10:26:28</t>
+    <t>2026-08-05 12:33:42</t>
   </si>
 </sst>
 </file>
@@ -729,7 +747,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB14"/>
+  <dimension ref="A1:CB16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -985,19 +1003,19 @@
         <v>88</v>
       </c>
       <c r="D2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E2" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="F2">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="G2">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="H2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I2">
         <v>30</v>
@@ -1006,52 +1024,52 @@
         <v>10.5</v>
       </c>
       <c r="K2">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="L2">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="M2">
         <v>1.01</v>
       </c>
       <c r="N2">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="O2">
         <v>1.05</v>
       </c>
       <c r="P2">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="Q2">
         <v>1.2</v>
       </c>
       <c r="R2">
-        <v>2.64</v>
+        <v>2.7</v>
       </c>
       <c r="S2">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="T2">
-        <v>1.92</v>
+        <v>1.86</v>
       </c>
       <c r="U2">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="V2">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="W2">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="X2">
-        <v>950</v>
+        <v>110</v>
       </c>
       <c r="Y2">
         <v>950</v>
       </c>
       <c r="Z2">
-        <v>330</v>
+        <v>350</v>
       </c>
       <c r="AA2">
         <v>1000</v>
@@ -1060,10 +1078,10 @@
         <v>27</v>
       </c>
       <c r="AC2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AD2">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AE2">
         <v>390</v>
@@ -1072,19 +1090,19 @@
         <v>15</v>
       </c>
       <c r="AG2">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AH2">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AI2">
         <v>200</v>
       </c>
       <c r="AJ2">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AK2">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="AL2">
         <v>42</v>
@@ -1099,112 +1117,112 @@
         <v>290</v>
       </c>
       <c r="AP2">
-        <v>8</v>
+        <v>7.2</v>
       </c>
       <c r="AQ2">
-        <v>8.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="AR2">
-        <v>8.4</v>
+        <v>7.6</v>
       </c>
       <c r="AS2">
-        <v>8.6</v>
+        <v>7.8</v>
       </c>
       <c r="AT2">
         <v>20</v>
       </c>
       <c r="AU2">
+        <v>6.6</v>
+      </c>
+      <c r="AV2">
+        <v>7.2</v>
+      </c>
+      <c r="AW2">
+        <v>7.6</v>
+      </c>
+      <c r="AX2">
+        <v>11.5</v>
+      </c>
+      <c r="AY2">
+        <v>14.5</v>
+      </c>
+      <c r="AZ2">
+        <v>32</v>
+      </c>
+      <c r="BA2">
         <v>7.4</v>
       </c>
-      <c r="AV2">
-        <v>8</v>
-      </c>
-      <c r="AW2">
-        <v>8.4</v>
-      </c>
-      <c r="AX2">
-        <v>11</v>
-      </c>
-      <c r="AY2">
-        <v>14</v>
-      </c>
-      <c r="AZ2">
-        <v>7.2</v>
-      </c>
-      <c r="BA2">
-        <v>8.199999999999999</v>
-      </c>
       <c r="BB2">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BC2">
+        <v>13</v>
+      </c>
+      <c r="BD2">
+        <v>6.8</v>
+      </c>
+      <c r="BE2">
+        <v>7.4</v>
+      </c>
+      <c r="BF2">
+        <v>1.82</v>
+      </c>
+      <c r="BG2">
+        <v>7.6</v>
+      </c>
+      <c r="BH2">
         <v>8.6</v>
       </c>
-      <c r="BC2">
-        <v>12.5</v>
-      </c>
-      <c r="BD2">
-        <v>7.6</v>
-      </c>
-      <c r="BE2">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BF2">
-        <v>1.85</v>
-      </c>
-      <c r="BG2">
-        <v>8.4</v>
-      </c>
-      <c r="BH2">
-        <v>8.199999999999999</v>
-      </c>
       <c r="BI2">
-        <v>4.2</v>
+        <v>3.95</v>
       </c>
       <c r="BJ2">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BK2">
-        <v>5.4</v>
+        <v>4.9</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>7.8</v>
+        <v>6.8</v>
       </c>
       <c r="BN2">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BO2">
         <v>3.75</v>
       </c>
       <c r="BP2">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BQ2">
         <v>4.6</v>
       </c>
       <c r="BR2">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BS2">
-        <v>5.8</v>
+        <v>5.2</v>
       </c>
       <c r="BT2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BU2">
-        <v>6.4</v>
+        <v>5.7</v>
       </c>
       <c r="BV2">
         <v>1000</v>
       </c>
       <c r="BW2">
-        <v>8</v>
+        <v>6.8</v>
       </c>
       <c r="BX2">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="BY2">
-        <v>7.8</v>
+        <v>6.6</v>
       </c>
       <c r="BZ2">
         <v>0</v>
@@ -1213,7 +1231,7 @@
         <v>0</v>
       </c>
       <c r="CB2" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1227,16 +1245,16 @@
         <v>89</v>
       </c>
       <c r="D3" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E3" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="F3">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="G3">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="H3">
         <v>3.7</v>
@@ -1251,64 +1269,64 @@
         <v>2.82</v>
       </c>
       <c r="L3">
-        <v>1.88</v>
+        <v>1.82</v>
       </c>
       <c r="M3">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="N3">
-        <v>2.04</v>
+        <v>2.12</v>
       </c>
       <c r="O3">
-        <v>1.94</v>
+        <v>1.87</v>
       </c>
       <c r="P3">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="Q3">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="R3">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="S3">
-        <v>9.800000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="T3">
-        <v>2.74</v>
+        <v>2.66</v>
       </c>
       <c r="U3">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="V3">
         <v>1.35</v>
       </c>
       <c r="W3">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="X3">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="Y3">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z3">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AA3">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AB3">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AC3">
-        <v>7.8</v>
+        <v>7</v>
       </c>
       <c r="AD3">
         <v>22</v>
       </c>
       <c r="AE3">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AF3">
         <v>14.5</v>
@@ -1341,31 +1359,31 @@
         <v>180</v>
       </c>
       <c r="AP3">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="AQ3">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AR3">
         <v>20</v>
       </c>
       <c r="AS3">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="AT3">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="AU3">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AV3">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AW3">
         <v>60</v>
       </c>
       <c r="AX3">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AY3">
         <v>14</v>
@@ -1374,25 +1392,25 @@
         <v>32</v>
       </c>
       <c r="BA3">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="BB3">
         <v>38</v>
       </c>
       <c r="BC3">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="BD3">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="BE3">
         <v>85</v>
       </c>
       <c r="BF3">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BG3">
-        <v>42</v>
+        <v>80</v>
       </c>
       <c r="BH3">
         <v>1000</v>
@@ -1455,7 +1473,7 @@
         <v>1.04</v>
       </c>
       <c r="CB3" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1469,70 +1487,70 @@
         <v>90</v>
       </c>
       <c r="D4" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="E4" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="F4">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="G4">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="H4">
+        <v>2.78</v>
+      </c>
+      <c r="I4">
+        <v>2.94</v>
+      </c>
+      <c r="J4">
+        <v>2.94</v>
+      </c>
+      <c r="K4">
+        <v>3.15</v>
+      </c>
+      <c r="L4">
+        <v>1.64</v>
+      </c>
+      <c r="M4">
+        <v>1.13</v>
+      </c>
+      <c r="N4">
+        <v>2.64</v>
+      </c>
+      <c r="O4">
+        <v>1.56</v>
+      </c>
+      <c r="P4">
+        <v>1.53</v>
+      </c>
+      <c r="Q4">
         <v>2.72</v>
       </c>
-      <c r="I4">
-        <v>2.92</v>
-      </c>
-      <c r="J4">
-        <v>2.98</v>
-      </c>
-      <c r="K4">
-        <v>3.25</v>
-      </c>
-      <c r="L4">
-        <v>1.61</v>
-      </c>
-      <c r="M4">
-        <v>1.12</v>
-      </c>
-      <c r="N4">
-        <v>2.7</v>
-      </c>
-      <c r="O4">
-        <v>1.54</v>
-      </c>
-      <c r="P4">
-        <v>1.56</v>
-      </c>
-      <c r="Q4">
-        <v>2.62</v>
-      </c>
       <c r="R4">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="S4">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="T4">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="U4">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="V4">
         <v>1.52</v>
       </c>
       <c r="W4">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="X4">
-        <v>10.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Y4">
-        <v>10.5</v>
+        <v>8.6</v>
       </c>
       <c r="Z4">
         <v>17.5</v>
@@ -1541,25 +1559,25 @@
         <v>50</v>
       </c>
       <c r="AB4">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC4">
         <v>7</v>
       </c>
       <c r="AD4">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AE4">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AF4">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AG4">
         <v>14.5</v>
       </c>
       <c r="AH4">
-        <v>23</v>
+        <v>950</v>
       </c>
       <c r="AI4">
         <v>70</v>
@@ -1568,16 +1586,16 @@
         <v>60</v>
       </c>
       <c r="AK4">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AL4">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AM4">
-        <v>200</v>
+        <v>220</v>
       </c>
       <c r="AN4">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AO4">
         <v>65</v>
@@ -1592,7 +1610,7 @@
         <v>14.5</v>
       </c>
       <c r="AS4">
-        <v>34</v>
+        <v>9.6</v>
       </c>
       <c r="AT4">
         <v>8</v>
@@ -1604,7 +1622,7 @@
         <v>11.5</v>
       </c>
       <c r="AW4">
-        <v>30</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AX4">
         <v>16</v>
@@ -1613,31 +1631,31 @@
         <v>12</v>
       </c>
       <c r="AZ4">
-        <v>6.2</v>
+        <v>19</v>
       </c>
       <c r="BA4">
-        <v>7.8</v>
+        <v>10</v>
       </c>
       <c r="BB4">
-        <v>7.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BC4">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="BD4">
-        <v>7.8</v>
+        <v>10</v>
       </c>
       <c r="BE4">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="BF4">
-        <v>7.6</v>
+        <v>10</v>
       </c>
       <c r="BG4">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="BH4">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="BI4">
         <v>2.28</v>
@@ -1652,7 +1670,7 @@
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>13.5</v>
+        <v>2.26</v>
       </c>
       <c r="BN4">
         <v>6</v>
@@ -1664,7 +1682,7 @@
         <v>1000</v>
       </c>
       <c r="BQ4">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BR4">
         <v>1000</v>
@@ -1682,13 +1700,13 @@
         <v>1000</v>
       </c>
       <c r="BW4">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BX4">
         <v>1000</v>
       </c>
       <c r="BY4">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BZ4">
         <v>1000</v>
@@ -1697,7 +1715,7 @@
         <v>11.5</v>
       </c>
       <c r="CB4" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1711,22 +1729,22 @@
         <v>91</v>
       </c>
       <c r="D5" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E5" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="F5">
         <v>1.72</v>
       </c>
       <c r="G5">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="H5">
         <v>4.6</v>
       </c>
       <c r="I5">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="J5">
         <v>4.3</v>
@@ -1744,7 +1762,7 @@
         <v>5.4</v>
       </c>
       <c r="O5">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="P5">
         <v>2.52</v>
@@ -1753,31 +1771,31 @@
         <v>1.61</v>
       </c>
       <c r="R5">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="S5">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="T5">
         <v>1.63</v>
       </c>
       <c r="U5">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="V5">
         <v>1.25</v>
       </c>
       <c r="W5">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="X5">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="Y5">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="Z5">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="AA5">
         <v>120</v>
@@ -1786,19 +1804,19 @@
         <v>13</v>
       </c>
       <c r="AC5">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AD5">
-        <v>21</v>
+        <v>950</v>
       </c>
       <c r="AE5">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="AF5">
         <v>13.5</v>
       </c>
       <c r="AG5">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AH5">
         <v>18</v>
@@ -1810,16 +1828,16 @@
         <v>19.5</v>
       </c>
       <c r="AK5">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AL5">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AM5">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AN5">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AO5">
         <v>46</v>
@@ -1831,22 +1849,22 @@
         <v>20</v>
       </c>
       <c r="AR5">
-        <v>32</v>
+        <v>6.2</v>
       </c>
       <c r="AS5">
-        <v>8.800000000000001</v>
+        <v>7</v>
       </c>
       <c r="AT5">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AU5">
         <v>9.199999999999999</v>
       </c>
       <c r="AV5">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AW5">
-        <v>36</v>
+        <v>6.6</v>
       </c>
       <c r="AX5">
         <v>11</v>
@@ -1858,7 +1876,7 @@
         <v>14.5</v>
       </c>
       <c r="BA5">
-        <v>32</v>
+        <v>6.6</v>
       </c>
       <c r="BB5">
         <v>16</v>
@@ -1867,28 +1885,28 @@
         <v>13.5</v>
       </c>
       <c r="BD5">
-        <v>21</v>
+        <v>6.2</v>
       </c>
       <c r="BE5">
-        <v>55</v>
+        <v>6.8</v>
       </c>
       <c r="BF5">
         <v>6.6</v>
       </c>
       <c r="BG5">
-        <v>27</v>
+        <v>6.2</v>
       </c>
       <c r="BH5">
         <v>4.5</v>
       </c>
       <c r="BI5">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="BJ5">
         <v>9.6</v>
       </c>
       <c r="BK5">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BL5">
         <v>1000</v>
@@ -1909,7 +1927,7 @@
         <v>5.4</v>
       </c>
       <c r="BR5">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="BS5">
         <v>7</v>
@@ -1939,7 +1957,7 @@
         <v>6</v>
       </c>
       <c r="CB5" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -1953,13 +1971,13 @@
         <v>92</v>
       </c>
       <c r="D6" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E6" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="F6">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="G6">
         <v>2.26</v>
@@ -1989,22 +2007,22 @@
         <v>1.39</v>
       </c>
       <c r="P6">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="Q6">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="R6">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="S6">
         <v>4.1</v>
       </c>
       <c r="T6">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="U6">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="V6">
         <v>1.33</v>
@@ -2013,34 +2031,34 @@
         <v>1.79</v>
       </c>
       <c r="X6">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="Y6">
         <v>13.5</v>
       </c>
       <c r="Z6">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AA6">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="AB6">
         <v>9</v>
       </c>
       <c r="AC6">
-        <v>9.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AD6">
         <v>16.5</v>
       </c>
       <c r="AE6">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AF6">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AG6">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="AH6">
         <v>20</v>
@@ -2049,7 +2067,7 @@
         <v>70</v>
       </c>
       <c r="AJ6">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AK6">
         <v>27</v>
@@ -2064,43 +2082,43 @@
         <v>23</v>
       </c>
       <c r="AO6">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AP6">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AQ6">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AR6">
-        <v>6.2</v>
+        <v>22</v>
       </c>
       <c r="AS6">
-        <v>6.2</v>
+        <v>55</v>
       </c>
       <c r="AT6">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AU6">
         <v>6.6</v>
       </c>
       <c r="AV6">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AW6">
-        <v>6</v>
+        <v>38</v>
       </c>
       <c r="AX6">
         <v>11</v>
       </c>
       <c r="AY6">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ6">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BA6">
-        <v>6.2</v>
+        <v>48</v>
       </c>
       <c r="BB6">
         <v>24</v>
@@ -2112,13 +2130,13 @@
         <v>32</v>
       </c>
       <c r="BE6">
-        <v>6.4</v>
+        <v>9.4</v>
       </c>
       <c r="BF6">
-        <v>15.5</v>
+        <v>18</v>
       </c>
       <c r="BG6">
-        <v>7</v>
+        <v>38</v>
       </c>
       <c r="BH6">
         <v>3.25</v>
@@ -2130,7 +2148,7 @@
         <v>10.5</v>
       </c>
       <c r="BK6">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BL6">
         <v>1000</v>
@@ -2169,19 +2187,19 @@
         <v>8</v>
       </c>
       <c r="BX6">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="BY6">
         <v>8.4</v>
       </c>
       <c r="BZ6">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="CA6">
         <v>7.8</v>
       </c>
       <c r="CB6" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
     </row>
     <row r="7" spans="1:80">
@@ -2195,52 +2213,52 @@
         <v>93</v>
       </c>
       <c r="D7" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E7" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="F7">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="G7">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="H7">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="I7">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="J7">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="K7">
         <v>3.45</v>
       </c>
       <c r="L7">
-        <v>1.52</v>
+        <v>1.01</v>
       </c>
       <c r="M7">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="N7">
-        <v>2.32</v>
+        <v>2.52</v>
       </c>
       <c r="O7">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="P7">
         <v>1.47</v>
       </c>
       <c r="Q7">
-        <v>2.56</v>
+        <v>2.68</v>
       </c>
       <c r="R7">
         <v>1.15</v>
       </c>
       <c r="S7">
-        <v>3.45</v>
+        <v>5.7</v>
       </c>
       <c r="T7">
         <v>2.32</v>
@@ -2252,25 +2270,25 @@
         <v>1.19</v>
       </c>
       <c r="W7">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
       <c r="X7">
         <v>9.4</v>
       </c>
       <c r="Y7">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="Z7">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AA7">
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="AB7">
         <v>7</v>
       </c>
       <c r="AC7">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AD7">
         <v>28</v>
@@ -2279,19 +2297,19 @@
         <v>140</v>
       </c>
       <c r="AF7">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AG7">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AH7">
         <v>34</v>
       </c>
       <c r="AI7">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="AJ7">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AK7">
         <v>34</v>
@@ -2300,70 +2318,70 @@
         <v>80</v>
       </c>
       <c r="AM7">
-        <v>300</v>
+        <v>310</v>
       </c>
       <c r="AN7">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AO7">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="AP7">
-        <v>3.35</v>
+        <v>6.4</v>
       </c>
       <c r="AQ7">
-        <v>3.85</v>
+        <v>10</v>
       </c>
       <c r="AR7">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AS7">
         <v>5.1</v>
       </c>
       <c r="AT7">
-        <v>2.98</v>
+        <v>4.8</v>
       </c>
       <c r="AU7">
-        <v>3.25</v>
+        <v>6</v>
       </c>
       <c r="AV7">
-        <v>4.4</v>
+        <v>18.5</v>
       </c>
       <c r="AW7">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AX7">
-        <v>3.6</v>
+        <v>7.8</v>
       </c>
       <c r="AY7">
-        <v>3.75</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ7">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="BA7">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BB7">
-        <v>4.4</v>
+        <v>17.5</v>
       </c>
       <c r="BC7">
-        <v>4.5</v>
+        <v>21</v>
       </c>
       <c r="BD7">
         <v>4.9</v>
       </c>
       <c r="BE7">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BF7">
-        <v>4.4</v>
+        <v>19</v>
       </c>
       <c r="BG7">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BH7">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="BI7">
         <v>2.24</v>
@@ -2372,49 +2390,49 @@
         <v>14.5</v>
       </c>
       <c r="BK7">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BL7">
         <v>1000</v>
       </c>
       <c r="BM7">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BN7">
         <v>4.8</v>
       </c>
       <c r="BO7">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="BP7">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BQ7">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BR7">
         <v>50</v>
       </c>
       <c r="BS7">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BT7">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BU7">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="BV7">
         <v>75</v>
       </c>
       <c r="BW7">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BX7">
         <v>100</v>
       </c>
       <c r="BY7">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="BZ7">
         <v>0</v>
@@ -2423,7 +2441,7 @@
         <v>0</v>
       </c>
       <c r="CB7" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
     </row>
     <row r="8" spans="1:80">
@@ -2437,43 +2455,43 @@
         <v>94</v>
       </c>
       <c r="D8" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E8" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="F8">
         <v>1.57</v>
       </c>
       <c r="G8">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="H8">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="I8">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="J8">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K8">
         <v>5.8</v>
       </c>
       <c r="L8">
-        <v>1.17</v>
+        <v>1.01</v>
       </c>
       <c r="M8">
         <v>1.01</v>
       </c>
       <c r="N8">
-        <v>7.2</v>
+        <v>8.6</v>
       </c>
       <c r="O8">
         <v>1.1</v>
       </c>
       <c r="P8">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="Q8">
         <v>1.31</v>
@@ -2494,13 +2512,13 @@
         <v>1.21</v>
       </c>
       <c r="W8">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="X8">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="Y8">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="Z8">
         <v>65</v>
@@ -2509,10 +2527,10 @@
         <v>120</v>
       </c>
       <c r="AB8">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AC8">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="AD8">
         <v>23</v>
@@ -2521,22 +2539,22 @@
         <v>55</v>
       </c>
       <c r="AF8">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AG8">
         <v>12.5</v>
       </c>
       <c r="AH8">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="AI8">
         <v>46</v>
       </c>
       <c r="AJ8">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AK8">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="AL8">
         <v>22</v>
@@ -2545,91 +2563,91 @@
         <v>55</v>
       </c>
       <c r="AN8">
-        <v>5.2</v>
+        <v>4.8</v>
       </c>
       <c r="AO8">
         <v>27</v>
       </c>
       <c r="AP8">
+        <v>7.2</v>
+      </c>
+      <c r="AQ8">
+        <v>6.8</v>
+      </c>
+      <c r="AR8">
+        <v>7.2</v>
+      </c>
+      <c r="AS8">
+        <v>7.6</v>
+      </c>
+      <c r="AT8">
+        <v>16.5</v>
+      </c>
+      <c r="AU8">
+        <v>11</v>
+      </c>
+      <c r="AV8">
+        <v>18.5</v>
+      </c>
+      <c r="AW8">
+        <v>7.2</v>
+      </c>
+      <c r="AX8">
         <v>5.6</v>
       </c>
-      <c r="AQ8">
-        <v>5.4</v>
-      </c>
-      <c r="AR8">
-        <v>5.7</v>
-      </c>
-      <c r="AS8">
-        <v>5.9</v>
-      </c>
-      <c r="AT8">
-        <v>4.9</v>
-      </c>
-      <c r="AU8">
-        <v>4.5</v>
-      </c>
-      <c r="AV8">
-        <v>4.9</v>
-      </c>
-      <c r="AW8">
-        <v>5.6</v>
-      </c>
-      <c r="AX8">
-        <v>4.6</v>
-      </c>
       <c r="AY8">
-        <v>4.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ8">
-        <v>4.7</v>
+        <v>12.5</v>
       </c>
       <c r="BA8">
-        <v>5.5</v>
+        <v>7</v>
       </c>
       <c r="BB8">
-        <v>4.8</v>
+        <v>16</v>
       </c>
       <c r="BC8">
-        <v>4.6</v>
+        <v>11.5</v>
       </c>
       <c r="BD8">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="BE8">
-        <v>5.6</v>
+        <v>7.2</v>
       </c>
       <c r="BF8">
-        <v>2.84</v>
+        <v>3.7</v>
       </c>
       <c r="BG8">
-        <v>5</v>
+        <v>6.2</v>
       </c>
       <c r="BH8">
         <v>6.8</v>
       </c>
       <c r="BI8">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="BJ8">
         <v>10</v>
       </c>
       <c r="BK8">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="BL8">
         <v>1000</v>
       </c>
       <c r="BM8">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BN8">
         <v>6</v>
       </c>
       <c r="BO8">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="BP8">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BQ8">
         <v>3.7</v>
@@ -2644,13 +2662,13 @@
         <v>11</v>
       </c>
       <c r="BU8">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="BV8">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BW8">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BX8">
         <v>34</v>
@@ -2662,10 +2680,10 @@
         <v>10</v>
       </c>
       <c r="CA8">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="CB8" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
     </row>
     <row r="9" spans="1:80">
@@ -2679,240 +2697,240 @@
         <v>95</v>
       </c>
       <c r="D9" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E9" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="F9">
-        <v>2.48</v>
+        <v>2.12</v>
       </c>
       <c r="G9">
-        <v>2.86</v>
+        <v>2.44</v>
       </c>
       <c r="H9">
-        <v>2.78</v>
+        <v>3.15</v>
       </c>
       <c r="I9">
-        <v>3.25</v>
+        <v>4.8</v>
       </c>
       <c r="J9">
-        <v>2.9</v>
+        <v>3.05</v>
       </c>
       <c r="K9">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="L9">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="M9">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="N9">
-        <v>3.1</v>
+        <v>2.5</v>
       </c>
       <c r="O9">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="P9">
-        <v>1.78</v>
+        <v>1.57</v>
       </c>
       <c r="Q9">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="R9">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="S9">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="T9">
+        <v>1.77</v>
+      </c>
+      <c r="U9">
         <v>1.76</v>
       </c>
-      <c r="U9">
-        <v>2.08</v>
-      </c>
       <c r="V9">
-        <v>1.44</v>
+        <v>1.26</v>
       </c>
       <c r="W9">
-        <v>1.53</v>
+        <v>1.69</v>
       </c>
       <c r="X9">
-        <v>16</v>
+        <v>13.5</v>
       </c>
       <c r="Y9">
-        <v>12</v>
+        <v>14.5</v>
       </c>
       <c r="Z9">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="AA9">
+        <v>100</v>
+      </c>
+      <c r="AB9">
+        <v>10</v>
+      </c>
+      <c r="AC9">
+        <v>9</v>
+      </c>
+      <c r="AD9">
+        <v>19.5</v>
+      </c>
+      <c r="AE9">
+        <v>70</v>
+      </c>
+      <c r="AF9">
+        <v>16.5</v>
+      </c>
+      <c r="AG9">
+        <v>14</v>
+      </c>
+      <c r="AH9">
+        <v>25</v>
+      </c>
+      <c r="AI9">
+        <v>85</v>
+      </c>
+      <c r="AJ9">
+        <v>38</v>
+      </c>
+      <c r="AK9">
+        <v>34</v>
+      </c>
+      <c r="AL9">
         <v>60</v>
       </c>
-      <c r="AB9">
-        <v>13</v>
-      </c>
-      <c r="AC9">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AD9">
-        <v>16</v>
-      </c>
-      <c r="AE9">
-        <v>42</v>
-      </c>
-      <c r="AF9">
-        <v>18.5</v>
-      </c>
-      <c r="AG9">
-        <v>15</v>
-      </c>
-      <c r="AH9">
-        <v>21</v>
-      </c>
-      <c r="AI9">
+      <c r="AM9">
+        <v>170</v>
+      </c>
+      <c r="AN9">
+        <v>30</v>
+      </c>
+      <c r="AO9">
+        <v>85</v>
+      </c>
+      <c r="AP9">
+        <v>1.03</v>
+      </c>
+      <c r="AQ9">
+        <v>1.03</v>
+      </c>
+      <c r="AR9">
+        <v>1.03</v>
+      </c>
+      <c r="AS9">
+        <v>1.03</v>
+      </c>
+      <c r="AT9">
+        <v>1.03</v>
+      </c>
+      <c r="AU9">
+        <v>1.03</v>
+      </c>
+      <c r="AV9">
+        <v>1.03</v>
+      </c>
+      <c r="AW9">
+        <v>1.03</v>
+      </c>
+      <c r="AX9">
+        <v>1.03</v>
+      </c>
+      <c r="AY9">
+        <v>1.03</v>
+      </c>
+      <c r="AZ9">
+        <v>1.03</v>
+      </c>
+      <c r="BA9">
+        <v>1.03</v>
+      </c>
+      <c r="BB9">
+        <v>1.03</v>
+      </c>
+      <c r="BC9">
+        <v>1.03</v>
+      </c>
+      <c r="BD9">
+        <v>1.03</v>
+      </c>
+      <c r="BE9">
+        <v>1.03</v>
+      </c>
+      <c r="BF9">
+        <v>17.5</v>
+      </c>
+      <c r="BG9">
+        <v>1.01</v>
+      </c>
+      <c r="BH9">
+        <v>3.15</v>
+      </c>
+      <c r="BI9">
+        <v>2.44</v>
+      </c>
+      <c r="BJ9">
+        <v>12.5</v>
+      </c>
+      <c r="BK9">
+        <v>4.9</v>
+      </c>
+      <c r="BL9">
+        <v>1000</v>
+      </c>
+      <c r="BM9">
+        <v>7.8</v>
+      </c>
+      <c r="BN9">
+        <v>5.2</v>
+      </c>
+      <c r="BO9">
+        <v>3.4</v>
+      </c>
+      <c r="BP9">
+        <v>19</v>
+      </c>
+      <c r="BQ9">
+        <v>5.7</v>
+      </c>
+      <c r="BR9">
+        <v>38</v>
+      </c>
+      <c r="BS9">
+        <v>6.8</v>
+      </c>
+      <c r="BT9">
+        <v>7.4</v>
+      </c>
+      <c r="BU9">
+        <v>3.9</v>
+      </c>
+      <c r="BV9">
+        <v>36</v>
+      </c>
+      <c r="BW9">
+        <v>6.6</v>
+      </c>
+      <c r="BX9">
         <v>60</v>
       </c>
-      <c r="AJ9">
-        <v>48</v>
-      </c>
-      <c r="AK9">
+      <c r="BY9">
+        <v>7.2</v>
+      </c>
+      <c r="BZ9">
         <v>38</v>
       </c>
-      <c r="AL9">
-        <v>55</v>
-      </c>
-      <c r="AM9">
-        <v>120</v>
-      </c>
-      <c r="AN9">
-        <v>32</v>
-      </c>
-      <c r="AO9">
-        <v>40</v>
-      </c>
-      <c r="AP9">
-        <v>3.95</v>
-      </c>
-      <c r="AQ9">
-        <v>7.4</v>
-      </c>
-      <c r="AR9">
-        <v>4.2</v>
-      </c>
-      <c r="AS9">
-        <v>4.8</v>
-      </c>
-      <c r="AT9">
-        <v>3.75</v>
-      </c>
-      <c r="AU9">
-        <v>5</v>
-      </c>
-      <c r="AV9">
-        <v>3.95</v>
-      </c>
-      <c r="AW9">
-        <v>4.6</v>
-      </c>
-      <c r="AX9">
-        <v>4.1</v>
-      </c>
-      <c r="AY9">
-        <v>3.9</v>
-      </c>
-      <c r="AZ9">
-        <v>4.2</v>
-      </c>
-      <c r="BA9">
-        <v>4.8</v>
-      </c>
-      <c r="BB9">
-        <v>4.7</v>
-      </c>
-      <c r="BC9">
-        <v>4.6</v>
-      </c>
-      <c r="BD9">
-        <v>4.8</v>
-      </c>
-      <c r="BE9">
-        <v>5</v>
-      </c>
-      <c r="BF9">
-        <v>4.5</v>
-      </c>
-      <c r="BG9">
-        <v>4.6</v>
-      </c>
-      <c r="BH9">
-        <v>3.4</v>
-      </c>
-      <c r="BI9">
-        <v>2.92</v>
-      </c>
-      <c r="BJ9">
-        <v>10</v>
-      </c>
-      <c r="BK9">
-        <v>5.2</v>
-      </c>
-      <c r="BL9">
-        <v>1000</v>
-      </c>
-      <c r="BM9">
-        <v>2.54</v>
-      </c>
-      <c r="BN9">
-        <v>5.8</v>
-      </c>
-      <c r="BO9">
-        <v>3.75</v>
-      </c>
-      <c r="BP9">
-        <v>21</v>
-      </c>
-      <c r="BQ9">
-        <v>7</v>
-      </c>
-      <c r="BR9">
-        <v>1000</v>
-      </c>
-      <c r="BS9">
-        <v>2.42</v>
-      </c>
-      <c r="BT9">
-        <v>6.2</v>
-      </c>
-      <c r="BU9">
-        <v>3.95</v>
-      </c>
-      <c r="BV9">
-        <v>25</v>
-      </c>
-      <c r="BW9">
-        <v>7.6</v>
-      </c>
-      <c r="BX9">
-        <v>1000</v>
-      </c>
-      <c r="BY9">
-        <v>2.42</v>
-      </c>
-      <c r="BZ9">
-        <v>32</v>
-      </c>
       <c r="CA9">
-        <v>2.4</v>
+        <v>6.8</v>
       </c>
       <c r="CB9" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
     </row>
     <row r="10" spans="1:80">
       <c r="A10" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B10" t="s">
         <v>87</v>
@@ -2921,31 +2939,31 @@
         <v>96</v>
       </c>
       <c r="D10" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E10" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="F10">
-        <v>2.22</v>
+        <v>2.58</v>
       </c>
       <c r="G10">
-        <v>2.46</v>
+        <v>2.92</v>
       </c>
       <c r="H10">
+        <v>2.7</v>
+      </c>
+      <c r="I10">
         <v>3.05</v>
       </c>
-      <c r="I10">
-        <v>3.65</v>
-      </c>
       <c r="J10">
-        <v>3.45</v>
+        <v>3.2</v>
       </c>
       <c r="K10">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="L10">
-        <v>1.41</v>
+        <v>1.35</v>
       </c>
       <c r="M10">
         <v>1.07</v>
@@ -2954,61 +2972,61 @@
         <v>3.5</v>
       </c>
       <c r="O10">
+        <v>1.34</v>
+      </c>
+      <c r="P10">
+        <v>1.84</v>
+      </c>
+      <c r="Q10">
+        <v>1.98</v>
+      </c>
+      <c r="R10">
         <v>1.32</v>
       </c>
-      <c r="P10">
-        <v>1.9</v>
-      </c>
-      <c r="Q10">
-        <v>1.92</v>
-      </c>
-      <c r="R10">
-        <v>1.35</v>
-      </c>
       <c r="S10">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="T10">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="U10">
-        <v>2.14</v>
+        <v>2.08</v>
       </c>
       <c r="V10">
-        <v>1.37</v>
+        <v>1.48</v>
       </c>
       <c r="W10">
-        <v>1.68</v>
+        <v>1.5</v>
       </c>
       <c r="X10">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="Y10">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="Z10">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="AA10">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AB10">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AC10">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AD10">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AE10">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AF10">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AG10">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AH10">
         <v>21</v>
@@ -3017,139 +3035,139 @@
         <v>60</v>
       </c>
       <c r="AJ10">
+        <v>50</v>
+      </c>
+      <c r="AK10">
         <v>38</v>
       </c>
-      <c r="AK10">
-        <v>32</v>
-      </c>
       <c r="AL10">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="AM10">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AN10">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="AO10">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AP10">
-        <v>3.6</v>
+        <v>11.5</v>
       </c>
       <c r="AQ10">
-        <v>3.5</v>
+        <v>8.4</v>
       </c>
       <c r="AR10">
-        <v>3.9</v>
+        <v>14</v>
       </c>
       <c r="AS10">
         <v>4.2</v>
       </c>
       <c r="AT10">
-        <v>3.3</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU10">
-        <v>3.05</v>
+        <v>5.9</v>
       </c>
       <c r="AV10">
-        <v>3.55</v>
+        <v>11</v>
       </c>
       <c r="AW10">
-        <v>4.1</v>
+        <v>20</v>
       </c>
       <c r="AX10">
-        <v>3.65</v>
+        <v>13</v>
       </c>
       <c r="AY10">
-        <v>3.4</v>
+        <v>10.5</v>
       </c>
       <c r="AZ10">
-        <v>3.7</v>
+        <v>14.5</v>
       </c>
       <c r="BA10">
-        <v>4.2</v>
+        <v>27</v>
       </c>
       <c r="BB10">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="BC10">
-        <v>3.95</v>
+        <v>21</v>
       </c>
       <c r="BD10">
-        <v>4.1</v>
+        <v>30</v>
       </c>
       <c r="BE10">
         <v>4.3</v>
       </c>
       <c r="BF10">
-        <v>3.8</v>
+        <v>4.9</v>
       </c>
       <c r="BG10">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BH10">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="BI10">
-        <v>2.72</v>
+        <v>2.96</v>
       </c>
       <c r="BJ10">
         <v>9.800000000000001</v>
       </c>
       <c r="BK10">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="BL10">
         <v>1000</v>
       </c>
       <c r="BM10">
-        <v>2.62</v>
+        <v>9.6</v>
       </c>
       <c r="BN10">
-        <v>5.4</v>
+        <v>5.9</v>
       </c>
       <c r="BO10">
-        <v>3.65</v>
+        <v>4.3</v>
       </c>
       <c r="BP10">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="BQ10">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BR10">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BS10">
-        <v>2.46</v>
+        <v>8</v>
       </c>
       <c r="BT10">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="BU10">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="BV10">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="BW10">
-        <v>2.44</v>
+        <v>7.2</v>
       </c>
       <c r="BX10">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="BY10">
-        <v>2.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA10">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="CB10" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
     </row>
     <row r="11" spans="1:80">
@@ -3163,240 +3181,240 @@
         <v>97</v>
       </c>
       <c r="D11" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E11" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="F11">
-        <v>1.77</v>
+        <v>2.24</v>
       </c>
       <c r="G11">
-        <v>1.89</v>
+        <v>2.46</v>
       </c>
       <c r="H11">
-        <v>4.6</v>
+        <v>3.2</v>
       </c>
       <c r="I11">
-        <v>5</v>
+        <v>3.6</v>
       </c>
       <c r="J11">
-        <v>3.65</v>
+        <v>3.45</v>
       </c>
       <c r="K11">
-        <v>4.3</v>
+        <v>3.7</v>
       </c>
       <c r="L11">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="M11">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="N11">
-        <v>2.84</v>
+        <v>3.6</v>
       </c>
       <c r="O11">
-        <v>1.45</v>
+        <v>1.32</v>
       </c>
       <c r="P11">
+        <v>1.87</v>
+      </c>
+      <c r="Q11">
+        <v>1.85</v>
+      </c>
+      <c r="R11">
+        <v>1.34</v>
+      </c>
+      <c r="S11">
+        <v>3.25</v>
+      </c>
+      <c r="T11">
+        <v>1.75</v>
+      </c>
+      <c r="U11">
+        <v>2.12</v>
+      </c>
+      <c r="V11">
+        <v>1.38</v>
+      </c>
+      <c r="W11">
         <v>1.68</v>
       </c>
-      <c r="Q11">
-        <v>2.28</v>
-      </c>
-      <c r="R11">
-        <v>1.25</v>
-      </c>
-      <c r="S11">
-        <v>3.85</v>
-      </c>
-      <c r="T11">
-        <v>2.16</v>
-      </c>
-      <c r="U11">
-        <v>1.74</v>
-      </c>
-      <c r="V11">
-        <v>1.25</v>
-      </c>
-      <c r="W11">
-        <v>2.12</v>
-      </c>
       <c r="X11">
+        <v>17</v>
+      </c>
+      <c r="Y11">
+        <v>16</v>
+      </c>
+      <c r="Z11">
+        <v>29</v>
+      </c>
+      <c r="AA11">
+        <v>75</v>
+      </c>
+      <c r="AB11">
+        <v>12.5</v>
+      </c>
+      <c r="AC11">
+        <v>9.6</v>
+      </c>
+      <c r="AD11">
+        <v>17.5</v>
+      </c>
+      <c r="AE11">
+        <v>48</v>
+      </c>
+      <c r="AF11">
+        <v>18.5</v>
+      </c>
+      <c r="AG11">
+        <v>14</v>
+      </c>
+      <c r="AH11">
+        <v>21</v>
+      </c>
+      <c r="AI11">
+        <v>60</v>
+      </c>
+      <c r="AJ11">
+        <v>34</v>
+      </c>
+      <c r="AK11">
+        <v>32</v>
+      </c>
+      <c r="AL11">
+        <v>48</v>
+      </c>
+      <c r="AM11">
+        <v>120</v>
+      </c>
+      <c r="AN11">
+        <v>24</v>
+      </c>
+      <c r="AO11">
+        <v>48</v>
+      </c>
+      <c r="AP11">
+        <v>12</v>
+      </c>
+      <c r="AQ11">
+        <v>11</v>
+      </c>
+      <c r="AR11">
+        <v>20</v>
+      </c>
+      <c r="AS11">
+        <v>4.1</v>
+      </c>
+      <c r="AT11">
+        <v>7.6</v>
+      </c>
+      <c r="AU11">
+        <v>6</v>
+      </c>
+      <c r="AV11">
+        <v>12</v>
+      </c>
+      <c r="AW11">
+        <v>4</v>
+      </c>
+      <c r="AX11">
+        <v>13</v>
+      </c>
+      <c r="AY11">
+        <v>9.6</v>
+      </c>
+      <c r="AZ11">
         <v>14.5</v>
       </c>
-      <c r="Y11">
-        <v>13</v>
-      </c>
-      <c r="Z11">
-        <v>46</v>
-      </c>
-      <c r="AA11">
-        <v>180</v>
-      </c>
-      <c r="AB11">
+      <c r="BA11">
+        <v>4.1</v>
+      </c>
+      <c r="BB11">
+        <v>3.9</v>
+      </c>
+      <c r="BC11">
+        <v>21</v>
+      </c>
+      <c r="BD11">
+        <v>4</v>
+      </c>
+      <c r="BE11">
+        <v>4.2</v>
+      </c>
+      <c r="BF11">
+        <v>16.5</v>
+      </c>
+      <c r="BG11">
+        <v>4</v>
+      </c>
+      <c r="BH11">
+        <v>3.5</v>
+      </c>
+      <c r="BI11">
+        <v>2.7</v>
+      </c>
+      <c r="BJ11">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BK11">
+        <v>5.2</v>
+      </c>
+      <c r="BL11">
+        <v>1000</v>
+      </c>
+      <c r="BM11">
+        <v>2.62</v>
+      </c>
+      <c r="BN11">
+        <v>5.4</v>
+      </c>
+      <c r="BO11">
+        <v>3.6</v>
+      </c>
+      <c r="BP11">
+        <v>18</v>
+      </c>
+      <c r="BQ11">
         <v>6.8</v>
       </c>
-      <c r="AC11">
-        <v>9.4</v>
-      </c>
-      <c r="AD11">
-        <v>20</v>
-      </c>
-      <c r="AE11">
-        <v>110</v>
-      </c>
-      <c r="AF11">
-        <v>10</v>
-      </c>
-      <c r="AG11">
-        <v>11</v>
-      </c>
-      <c r="AH11">
-        <v>29</v>
-      </c>
-      <c r="AI11">
-        <v>120</v>
-      </c>
-      <c r="AJ11">
-        <v>21</v>
-      </c>
-      <c r="AK11">
-        <v>24</v>
-      </c>
-      <c r="AL11">
-        <v>65</v>
-      </c>
-      <c r="AM11">
-        <v>260</v>
-      </c>
-      <c r="AN11">
-        <v>18</v>
-      </c>
-      <c r="AO11">
-        <v>170</v>
-      </c>
-      <c r="AP11">
-        <v>5.5</v>
-      </c>
-      <c r="AQ11">
-        <v>5.3</v>
-      </c>
-      <c r="AR11">
-        <v>7.4</v>
-      </c>
-      <c r="AS11">
-        <v>8.6</v>
-      </c>
-      <c r="AT11">
-        <v>5.1</v>
-      </c>
-      <c r="AU11">
-        <v>4.6</v>
-      </c>
-      <c r="AV11">
-        <v>6.2</v>
-      </c>
-      <c r="AW11">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AX11">
-        <v>4.7</v>
-      </c>
-      <c r="AY11">
-        <v>4.9</v>
-      </c>
-      <c r="AZ11">
+      <c r="BR11">
+        <v>32</v>
+      </c>
+      <c r="BS11">
+        <v>2.46</v>
+      </c>
+      <c r="BT11">
         <v>6.8</v>
       </c>
-      <c r="BA11">
-        <v>8.4</v>
-      </c>
-      <c r="BB11">
-        <v>6.2</v>
-      </c>
-      <c r="BC11">
-        <v>6.4</v>
-      </c>
-      <c r="BD11">
-        <v>7.8</v>
-      </c>
-      <c r="BE11">
-        <v>8.6</v>
-      </c>
-      <c r="BF11">
-        <v>6</v>
-      </c>
-      <c r="BG11">
-        <v>8.4</v>
-      </c>
-      <c r="BH11">
-        <v>2.94</v>
-      </c>
-      <c r="BI11">
+      <c r="BU11">
+        <v>4.2</v>
+      </c>
+      <c r="BV11">
+        <v>28</v>
+      </c>
+      <c r="BW11">
         <v>2.44</v>
       </c>
-      <c r="BJ11">
-        <v>12</v>
-      </c>
-      <c r="BK11">
-        <v>6.4</v>
-      </c>
-      <c r="BL11">
-        <v>1000</v>
-      </c>
-      <c r="BM11">
-        <v>2.4</v>
-      </c>
-      <c r="BN11">
-        <v>4.3</v>
-      </c>
-      <c r="BO11">
-        <v>3.3</v>
-      </c>
-      <c r="BP11">
-        <v>14</v>
-      </c>
-      <c r="BQ11">
-        <v>7</v>
-      </c>
-      <c r="BR11">
-        <v>36</v>
-      </c>
-      <c r="BS11">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BT11">
-        <v>9</v>
-      </c>
-      <c r="BU11">
-        <v>5.5</v>
-      </c>
-      <c r="BV11">
-        <v>1000</v>
-      </c>
-      <c r="BW11">
-        <v>9.199999999999999</v>
-      </c>
       <c r="BX11">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BY11">
-        <v>2.36</v>
+        <v>2.5</v>
       </c>
       <c r="BZ11">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="CA11">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="CB11" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
     </row>
     <row r="12" spans="1:80">
       <c r="A12" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="B12" t="s">
         <v>87</v>
@@ -3405,240 +3423,240 @@
         <v>98</v>
       </c>
       <c r="D12" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E12" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="F12">
+        <v>1.83</v>
+      </c>
+      <c r="G12">
+        <v>1.9</v>
+      </c>
+      <c r="H12">
+        <v>4.5</v>
+      </c>
+      <c r="I12">
+        <v>4.9</v>
+      </c>
+      <c r="J12">
+        <v>3.7</v>
+      </c>
+      <c r="K12">
+        <v>4.4</v>
+      </c>
+      <c r="L12">
+        <v>1.42</v>
+      </c>
+      <c r="M12">
+        <v>1.09</v>
+      </c>
+      <c r="N12">
+        <v>2.84</v>
+      </c>
+      <c r="O12">
+        <v>1.46</v>
+      </c>
+      <c r="P12">
+        <v>1.66</v>
+      </c>
+      <c r="Q12">
+        <v>2.3</v>
+      </c>
+      <c r="R12">
+        <v>1.23</v>
+      </c>
+      <c r="S12">
+        <v>4.1</v>
+      </c>
+      <c r="T12">
+        <v>2.18</v>
+      </c>
+      <c r="U12">
+        <v>1.73</v>
+      </c>
+      <c r="V12">
+        <v>1.25</v>
+      </c>
+      <c r="W12">
+        <v>2.1</v>
+      </c>
+      <c r="X12">
+        <v>14</v>
+      </c>
+      <c r="Y12">
+        <v>14.5</v>
+      </c>
+      <c r="Z12">
+        <v>42</v>
+      </c>
+      <c r="AA12">
+        <v>170</v>
+      </c>
+      <c r="AB12">
+        <v>6.8</v>
+      </c>
+      <c r="AC12">
+        <v>11.5</v>
+      </c>
+      <c r="AD12">
+        <v>19</v>
+      </c>
+      <c r="AE12">
+        <v>100</v>
+      </c>
+      <c r="AF12">
+        <v>10</v>
+      </c>
+      <c r="AG12">
+        <v>11</v>
+      </c>
+      <c r="AH12">
+        <v>36</v>
+      </c>
+      <c r="AI12">
+        <v>110</v>
+      </c>
+      <c r="AJ12">
+        <v>21</v>
+      </c>
+      <c r="AK12">
+        <v>24</v>
+      </c>
+      <c r="AL12">
+        <v>55</v>
+      </c>
+      <c r="AM12">
+        <v>260</v>
+      </c>
+      <c r="AN12">
+        <v>18</v>
+      </c>
+      <c r="AO12">
+        <v>170</v>
+      </c>
+      <c r="AP12">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AQ12">
+        <v>4.9</v>
+      </c>
+      <c r="AR12">
+        <v>21</v>
+      </c>
+      <c r="AS12">
+        <v>7.2</v>
+      </c>
+      <c r="AT12">
+        <v>5</v>
+      </c>
+      <c r="AU12">
+        <v>7.2</v>
+      </c>
+      <c r="AV12">
+        <v>5.3</v>
+      </c>
+      <c r="AW12">
+        <v>7</v>
+      </c>
+      <c r="AX12">
+        <v>7.2</v>
+      </c>
+      <c r="AY12">
+        <v>7.8</v>
+      </c>
+      <c r="AZ12">
+        <v>20</v>
+      </c>
+      <c r="BA12">
+        <v>7</v>
+      </c>
+      <c r="BB12">
+        <v>14.5</v>
+      </c>
+      <c r="BC12">
+        <v>17</v>
+      </c>
+      <c r="BD12">
+        <v>6.6</v>
+      </c>
+      <c r="BE12">
+        <v>7.2</v>
+      </c>
+      <c r="BF12">
+        <v>13</v>
+      </c>
+      <c r="BG12">
+        <v>7.2</v>
+      </c>
+      <c r="BH12">
+        <v>2.94</v>
+      </c>
+      <c r="BI12">
+        <v>2.44</v>
+      </c>
+      <c r="BJ12">
+        <v>12</v>
+      </c>
+      <c r="BK12">
+        <v>6.4</v>
+      </c>
+      <c r="BL12">
+        <v>1000</v>
+      </c>
+      <c r="BM12">
         <v>2.4</v>
       </c>
-      <c r="G12">
-        <v>2.5</v>
-      </c>
-      <c r="H12">
-        <v>3.5</v>
-      </c>
-      <c r="I12">
-        <v>3.8</v>
-      </c>
-      <c r="J12">
-        <v>3.05</v>
-      </c>
-      <c r="K12">
-        <v>3.15</v>
-      </c>
-      <c r="L12">
-        <v>1.47</v>
-      </c>
-      <c r="M12">
-        <v>1.12</v>
-      </c>
-      <c r="N12">
-        <v>2.62</v>
-      </c>
-      <c r="O12">
-        <v>1.54</v>
-      </c>
-      <c r="P12">
-        <v>1.55</v>
-      </c>
-      <c r="Q12">
-        <v>2.66</v>
-      </c>
-      <c r="R12">
-        <v>1.2</v>
-      </c>
-      <c r="S12">
-        <v>5.4</v>
-      </c>
-      <c r="T12">
-        <v>2.1</v>
-      </c>
-      <c r="U12">
-        <v>1.8</v>
-      </c>
-      <c r="V12">
-        <v>1.36</v>
-      </c>
-      <c r="W12">
-        <v>1.66</v>
-      </c>
-      <c r="X12">
-        <v>10.5</v>
-      </c>
-      <c r="Y12">
-        <v>12</v>
-      </c>
-      <c r="Z12">
-        <v>26</v>
-      </c>
-      <c r="AA12">
-        <v>100</v>
-      </c>
-      <c r="AB12">
-        <v>7.6</v>
-      </c>
-      <c r="AC12">
-        <v>7.4</v>
-      </c>
-      <c r="AD12">
-        <v>17</v>
-      </c>
-      <c r="AE12">
-        <v>75</v>
-      </c>
-      <c r="AF12">
-        <v>15</v>
-      </c>
-      <c r="AG12">
-        <v>13</v>
-      </c>
-      <c r="AH12">
-        <v>25</v>
-      </c>
-      <c r="AI12">
-        <v>100</v>
-      </c>
-      <c r="AJ12">
-        <v>46</v>
-      </c>
-      <c r="AK12">
-        <v>42</v>
-      </c>
-      <c r="AL12">
-        <v>75</v>
-      </c>
-      <c r="AM12">
-        <v>220</v>
-      </c>
-      <c r="AN12">
-        <v>44</v>
-      </c>
-      <c r="AO12">
-        <v>100</v>
-      </c>
-      <c r="AP12">
-        <v>7.8</v>
-      </c>
-      <c r="AQ12">
+      <c r="BN12">
+        <v>4.3</v>
+      </c>
+      <c r="BO12">
+        <v>3.75</v>
+      </c>
+      <c r="BP12">
+        <v>14</v>
+      </c>
+      <c r="BQ12">
+        <v>7</v>
+      </c>
+      <c r="BR12">
+        <v>36</v>
+      </c>
+      <c r="BS12">
+        <v>2.28</v>
+      </c>
+      <c r="BT12">
         <v>9</v>
       </c>
-      <c r="AR12">
-        <v>17.5</v>
-      </c>
-      <c r="AS12">
-        <v>6.4</v>
-      </c>
-      <c r="AT12">
-        <v>6.6</v>
-      </c>
-      <c r="AU12">
-        <v>6.4</v>
-      </c>
-      <c r="AV12">
-        <v>14</v>
-      </c>
-      <c r="AW12">
-        <v>6.2</v>
-      </c>
-      <c r="AX12">
-        <v>10</v>
-      </c>
-      <c r="AY12">
-        <v>10.5</v>
-      </c>
-      <c r="AZ12">
-        <v>5.4</v>
-      </c>
-      <c r="BA12">
-        <v>6.4</v>
-      </c>
-      <c r="BB12">
-        <v>6</v>
-      </c>
-      <c r="BC12">
-        <v>24</v>
-      </c>
-      <c r="BD12">
-        <v>6.2</v>
-      </c>
-      <c r="BE12">
-        <v>6.6</v>
-      </c>
-      <c r="BF12">
-        <v>5.9</v>
-      </c>
-      <c r="BG12">
-        <v>6.4</v>
-      </c>
-      <c r="BH12">
-        <v>3.15</v>
-      </c>
-      <c r="BI12">
-        <v>2.24</v>
-      </c>
-      <c r="BJ12">
-        <v>13.5</v>
-      </c>
-      <c r="BK12">
-        <v>3.65</v>
-      </c>
-      <c r="BL12">
-        <v>1000</v>
-      </c>
-      <c r="BM12">
-        <v>4.9</v>
-      </c>
-      <c r="BN12">
-        <v>6</v>
-      </c>
-      <c r="BO12">
-        <v>3.9</v>
-      </c>
-      <c r="BP12">
-        <v>26</v>
-      </c>
-      <c r="BQ12">
-        <v>4.2</v>
-      </c>
-      <c r="BR12">
-        <v>55</v>
-      </c>
-      <c r="BS12">
-        <v>4.6</v>
-      </c>
-      <c r="BT12">
-        <v>7.8</v>
-      </c>
       <c r="BU12">
-        <v>5</v>
+        <v>6.8</v>
       </c>
       <c r="BV12">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="BW12">
-        <v>4.5</v>
+        <v>2.34</v>
       </c>
       <c r="BX12">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="BY12">
-        <v>4.6</v>
+        <v>2.36</v>
       </c>
       <c r="BZ12">
-        <v>60</v>
+        <v>34</v>
       </c>
       <c r="CA12">
-        <v>4.6</v>
+        <v>2.28</v>
       </c>
       <c r="CB12" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
     </row>
     <row r="13" spans="1:80">
       <c r="A13" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="B13" t="s">
         <v>87</v>
@@ -3647,240 +3665,240 @@
         <v>99</v>
       </c>
       <c r="D13" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E13" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="F13">
-        <v>2.24</v>
+        <v>2.4</v>
       </c>
       <c r="G13">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="H13">
-        <v>3.75</v>
+        <v>3.55</v>
       </c>
       <c r="I13">
-        <v>4.5</v>
+        <v>3.8</v>
       </c>
       <c r="J13">
-        <v>2.82</v>
+        <v>3.05</v>
       </c>
       <c r="K13">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="L13">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="M13">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="N13">
-        <v>2.22</v>
+        <v>2.62</v>
       </c>
       <c r="O13">
-        <v>1.59</v>
+        <v>1.54</v>
       </c>
       <c r="P13">
-        <v>1.42</v>
+        <v>1.55</v>
       </c>
       <c r="Q13">
-        <v>2.78</v>
+        <v>2.66</v>
       </c>
       <c r="R13">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="S13">
-        <v>5.8</v>
+        <v>5.4</v>
       </c>
       <c r="T13">
-        <v>2.26</v>
+        <v>2.1</v>
       </c>
       <c r="U13">
-        <v>1.58</v>
+        <v>1.8</v>
       </c>
       <c r="V13">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="W13">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="X13">
-        <v>8.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="Y13">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="Z13">
         <v>29</v>
       </c>
       <c r="AA13">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="AB13">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="AC13">
-        <v>7.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD13">
         <v>20</v>
       </c>
       <c r="AE13">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="AF13">
+        <v>14.5</v>
+      </c>
+      <c r="AG13">
+        <v>12.5</v>
+      </c>
+      <c r="AH13">
+        <v>24</v>
+      </c>
+      <c r="AI13">
+        <v>100</v>
+      </c>
+      <c r="AJ13">
+        <v>46</v>
+      </c>
+      <c r="AK13">
+        <v>42</v>
+      </c>
+      <c r="AL13">
+        <v>75</v>
+      </c>
+      <c r="AM13">
+        <v>220</v>
+      </c>
+      <c r="AN13">
+        <v>44</v>
+      </c>
+      <c r="AO13">
+        <v>100</v>
+      </c>
+      <c r="AP13">
+        <v>7.8</v>
+      </c>
+      <c r="AQ13">
+        <v>9</v>
+      </c>
+      <c r="AR13">
+        <v>17.5</v>
+      </c>
+      <c r="AS13">
+        <v>5.3</v>
+      </c>
+      <c r="AT13">
+        <v>6.6</v>
+      </c>
+      <c r="AU13">
+        <v>6.6</v>
+      </c>
+      <c r="AV13">
         <v>14</v>
       </c>
-      <c r="AG13">
-        <v>13.5</v>
-      </c>
-      <c r="AH13">
-        <v>32</v>
-      </c>
-      <c r="AI13">
-        <v>130</v>
-      </c>
-      <c r="AJ13">
-        <v>38</v>
-      </c>
-      <c r="AK13">
-        <v>40</v>
-      </c>
-      <c r="AL13">
-        <v>80</v>
-      </c>
-      <c r="AM13">
-        <v>270</v>
-      </c>
-      <c r="AN13">
-        <v>50</v>
-      </c>
-      <c r="AO13">
-        <v>150</v>
-      </c>
-      <c r="AP13">
-        <v>4</v>
-      </c>
-      <c r="AQ13">
-        <v>4.5</v>
-      </c>
-      <c r="AR13">
-        <v>6.2</v>
-      </c>
-      <c r="AS13">
-        <v>7.4</v>
-      </c>
-      <c r="AT13">
+      <c r="AW13">
         <v>5.2</v>
       </c>
-      <c r="AU13">
-        <v>3.85</v>
-      </c>
-      <c r="AV13">
-        <v>5.6</v>
-      </c>
-      <c r="AW13">
-        <v>7.2</v>
-      </c>
       <c r="AX13">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AY13">
         <v>10.5</v>
       </c>
       <c r="AZ13">
-        <v>6.2</v>
+        <v>5</v>
       </c>
       <c r="BA13">
-        <v>7.4</v>
+        <v>5.3</v>
       </c>
       <c r="BB13">
-        <v>6.4</v>
+        <v>5</v>
       </c>
       <c r="BC13">
-        <v>6.6</v>
+        <v>5</v>
       </c>
       <c r="BD13">
-        <v>7</v>
+        <v>5.2</v>
       </c>
       <c r="BE13">
-        <v>7.6</v>
+        <v>5.5</v>
       </c>
       <c r="BF13">
-        <v>6.8</v>
+        <v>5</v>
       </c>
       <c r="BG13">
-        <v>7.4</v>
+        <v>5.3</v>
       </c>
       <c r="BH13">
-        <v>2.76</v>
+        <v>3.15</v>
       </c>
       <c r="BI13">
-        <v>2.14</v>
+        <v>2.24</v>
       </c>
       <c r="BJ13">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BK13">
-        <v>4.4</v>
+        <v>3.6</v>
       </c>
       <c r="BL13">
         <v>1000</v>
       </c>
       <c r="BM13">
-        <v>6.2</v>
+        <v>4.8</v>
       </c>
       <c r="BN13">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="BO13">
-        <v>3.9</v>
+        <v>4.5</v>
       </c>
       <c r="BP13">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BQ13">
-        <v>5.1</v>
+        <v>4.1</v>
       </c>
       <c r="BR13">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="BS13">
-        <v>5.8</v>
+        <v>4.5</v>
       </c>
       <c r="BT13">
         <v>8</v>
       </c>
       <c r="BU13">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="BV13">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="BW13">
-        <v>5.7</v>
+        <v>4.4</v>
       </c>
       <c r="BX13">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="BY13">
-        <v>5.9</v>
+        <v>4.6</v>
       </c>
       <c r="BZ13">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="CA13">
-        <v>5.9</v>
+        <v>4.5</v>
       </c>
       <c r="CB13" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
     </row>
     <row r="14" spans="1:80">
       <c r="A14" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="B14" t="s">
         <v>87</v>
@@ -3889,28 +3907,28 @@
         <v>100</v>
       </c>
       <c r="D14" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E14" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="F14">
-        <v>1.52</v>
+        <v>1.04</v>
       </c>
       <c r="G14">
-        <v>990</v>
+        <v>110</v>
       </c>
       <c r="H14">
-        <v>1.32</v>
+        <v>1.04</v>
       </c>
       <c r="I14">
-        <v>990</v>
+        <v>110</v>
       </c>
       <c r="J14">
-        <v>1.12</v>
+        <v>1.02</v>
       </c>
       <c r="K14">
-        <v>4.2</v>
+        <v>950</v>
       </c>
       <c r="L14">
         <v>1.01</v>
@@ -3919,22 +3937,22 @@
         <v>1.01</v>
       </c>
       <c r="N14">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="O14">
-        <v>1.14</v>
+        <v>1.01</v>
       </c>
       <c r="P14">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="Q14">
-        <v>1.14</v>
+        <v>1.41</v>
       </c>
       <c r="R14">
-        <v>1.28</v>
+        <v>1.18</v>
       </c>
       <c r="S14">
-        <v>1.05</v>
+        <v>1.41</v>
       </c>
       <c r="T14">
         <v>1.11</v>
@@ -3943,7 +3961,7 @@
         <v>1.11</v>
       </c>
       <c r="V14">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="W14">
         <v>1.01</v>
@@ -4003,52 +4021,52 @@
         <v>1000</v>
       </c>
       <c r="AP14">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ14">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR14">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS14">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT14">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU14">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV14">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW14">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX14">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY14">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ14">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA14">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB14">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC14">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD14">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE14">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF14">
         <v>1.01</v>
@@ -4060,64 +4078,548 @@
         <v>1000</v>
       </c>
       <c r="BI14">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BJ14">
         <v>1000</v>
       </c>
       <c r="BK14">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BL14">
         <v>1000</v>
       </c>
       <c r="BM14">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BN14">
         <v>1000</v>
       </c>
       <c r="BO14">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BP14">
         <v>1000</v>
       </c>
       <c r="BQ14">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BR14">
         <v>1000</v>
       </c>
       <c r="BS14">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BT14">
         <v>1000</v>
       </c>
       <c r="BU14">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BV14">
         <v>1000</v>
       </c>
       <c r="BW14">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BX14">
         <v>1000</v>
       </c>
       <c r="BY14">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BZ14">
+        <v>1000</v>
+      </c>
+      <c r="CA14">
+        <v>1.01</v>
+      </c>
+      <c r="CB14" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="15" spans="1:80">
+      <c r="A15" t="s">
+        <v>84</v>
+      </c>
+      <c r="B15" t="s">
+        <v>87</v>
+      </c>
+      <c r="C15" t="s">
+        <v>101</v>
+      </c>
+      <c r="D15" t="s">
+        <v>116</v>
+      </c>
+      <c r="E15" t="s">
+        <v>131</v>
+      </c>
+      <c r="F15">
+        <v>1.96</v>
+      </c>
+      <c r="G15">
+        <v>2.14</v>
+      </c>
+      <c r="H15">
+        <v>4.5</v>
+      </c>
+      <c r="I15">
+        <v>5.5</v>
+      </c>
+      <c r="J15">
+        <v>2.94</v>
+      </c>
+      <c r="K15">
+        <v>3.4</v>
+      </c>
+      <c r="L15">
+        <v>1.54</v>
+      </c>
+      <c r="M15">
+        <v>1.14</v>
+      </c>
+      <c r="N15">
+        <v>2.32</v>
+      </c>
+      <c r="O15">
+        <v>1.58</v>
+      </c>
+      <c r="P15">
+        <v>1.45</v>
+      </c>
+      <c r="Q15">
+        <v>2.76</v>
+      </c>
+      <c r="R15">
+        <v>1.16</v>
+      </c>
+      <c r="S15">
+        <v>5.9</v>
+      </c>
+      <c r="T15">
+        <v>2.32</v>
+      </c>
+      <c r="U15">
+        <v>1.57</v>
+      </c>
+      <c r="V15">
+        <v>1.22</v>
+      </c>
+      <c r="W15">
+        <v>1.87</v>
+      </c>
+      <c r="X15">
+        <v>8.4</v>
+      </c>
+      <c r="Y15">
+        <v>12.5</v>
+      </c>
+      <c r="Z15">
+        <v>40</v>
+      </c>
+      <c r="AA15">
+        <v>180</v>
+      </c>
+      <c r="AB15">
+        <v>6.4</v>
+      </c>
+      <c r="AC15">
+        <v>7.8</v>
+      </c>
+      <c r="AD15">
+        <v>26</v>
+      </c>
+      <c r="AE15">
+        <v>120</v>
+      </c>
+      <c r="AF15">
+        <v>11</v>
+      </c>
+      <c r="AG15">
+        <v>12.5</v>
+      </c>
+      <c r="AH15">
+        <v>40</v>
+      </c>
+      <c r="AI15">
+        <v>150</v>
+      </c>
+      <c r="AJ15">
+        <v>28</v>
+      </c>
+      <c r="AK15">
+        <v>34</v>
+      </c>
+      <c r="AL15">
+        <v>80</v>
+      </c>
+      <c r="AM15">
+        <v>290</v>
+      </c>
+      <c r="AN15">
+        <v>36</v>
+      </c>
+      <c r="AO15">
+        <v>220</v>
+      </c>
+      <c r="AP15">
+        <v>6.2</v>
+      </c>
+      <c r="AQ15">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AR15">
+        <v>23</v>
+      </c>
+      <c r="AS15">
+        <v>8.6</v>
+      </c>
+      <c r="AT15">
+        <v>3.75</v>
+      </c>
+      <c r="AU15">
+        <v>5.9</v>
+      </c>
+      <c r="AV15">
+        <v>18.5</v>
+      </c>
+      <c r="AW15">
+        <v>8.4</v>
+      </c>
+      <c r="AX15">
+        <v>4.9</v>
+      </c>
+      <c r="AY15">
+        <v>5.2</v>
+      </c>
+      <c r="AZ15">
+        <v>18</v>
+      </c>
+      <c r="BA15">
+        <v>8.4</v>
+      </c>
+      <c r="BB15">
+        <v>17</v>
+      </c>
+      <c r="BC15">
+        <v>19.5</v>
+      </c>
+      <c r="BD15">
+        <v>8</v>
+      </c>
+      <c r="BE15">
+        <v>8.6</v>
+      </c>
+      <c r="BF15">
+        <v>18.5</v>
+      </c>
+      <c r="BG15">
+        <v>8.6</v>
+      </c>
+      <c r="BH15">
+        <v>2.86</v>
+      </c>
+      <c r="BI15">
+        <v>2.2</v>
+      </c>
+      <c r="BJ15">
+        <v>14.5</v>
+      </c>
+      <c r="BK15">
+        <v>4.3</v>
+      </c>
+      <c r="BL15">
+        <v>1000</v>
+      </c>
+      <c r="BM15">
+        <v>6</v>
+      </c>
+      <c r="BN15">
+        <v>5</v>
+      </c>
+      <c r="BO15">
+        <v>3.6</v>
+      </c>
+      <c r="BP15">
+        <v>20</v>
+      </c>
+      <c r="BQ15">
+        <v>4.7</v>
+      </c>
+      <c r="BR15">
+        <v>1000</v>
+      </c>
+      <c r="BS15">
+        <v>5.6</v>
+      </c>
+      <c r="BT15">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BU15">
+        <v>3.7</v>
+      </c>
+      <c r="BV15">
+        <v>1000</v>
+      </c>
+      <c r="BW15">
+        <v>5.7</v>
+      </c>
+      <c r="BX15">
+        <v>1000</v>
+      </c>
+      <c r="BY15">
+        <v>5.9</v>
+      </c>
+      <c r="BZ15">
+        <v>1000</v>
+      </c>
+      <c r="CA15">
+        <v>5.7</v>
+      </c>
+      <c r="CB15" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="16" spans="1:80">
+      <c r="A16" t="s">
+        <v>80</v>
+      </c>
+      <c r="B16" t="s">
+        <v>87</v>
+      </c>
+      <c r="C16" t="s">
+        <v>102</v>
+      </c>
+      <c r="D16" t="s">
+        <v>117</v>
+      </c>
+      <c r="E16" t="s">
+        <v>132</v>
+      </c>
+      <c r="F16">
+        <v>2.8</v>
+      </c>
+      <c r="G16">
+        <v>3.75</v>
+      </c>
+      <c r="H16">
+        <v>2</v>
+      </c>
+      <c r="I16">
+        <v>2.5</v>
+      </c>
+      <c r="J16">
+        <v>3.8</v>
+      </c>
+      <c r="K16">
+        <v>4.2</v>
+      </c>
+      <c r="L16">
+        <v>1.23</v>
+      </c>
+      <c r="M16">
+        <v>1.01</v>
+      </c>
+      <c r="N16">
+        <v>1.1</v>
+      </c>
+      <c r="O16">
+        <v>1.16</v>
+      </c>
+      <c r="P16">
+        <v>2.58</v>
+      </c>
+      <c r="Q16">
+        <v>1.5</v>
+      </c>
+      <c r="R16">
+        <v>1.53</v>
+      </c>
+      <c r="S16">
+        <v>2.08</v>
+      </c>
+      <c r="T16">
+        <v>1.12</v>
+      </c>
+      <c r="U16">
+        <v>2.56</v>
+      </c>
+      <c r="V16">
+        <v>1.66</v>
+      </c>
+      <c r="W16">
+        <v>1.37</v>
+      </c>
+      <c r="X16">
+        <v>29</v>
+      </c>
+      <c r="Y16">
+        <v>17</v>
+      </c>
+      <c r="Z16">
+        <v>20</v>
+      </c>
+      <c r="AA16">
+        <v>34</v>
+      </c>
+      <c r="AB16">
+        <v>20</v>
+      </c>
+      <c r="AC16">
+        <v>11</v>
+      </c>
+      <c r="AD16">
+        <v>13</v>
+      </c>
+      <c r="AE16">
+        <v>23</v>
+      </c>
+      <c r="AF16">
+        <v>28</v>
+      </c>
+      <c r="AG16">
+        <v>15</v>
+      </c>
+      <c r="AH16">
+        <v>16</v>
+      </c>
+      <c r="AI16">
+        <v>29</v>
+      </c>
+      <c r="AJ16">
+        <v>60</v>
+      </c>
+      <c r="AK16">
+        <v>32</v>
+      </c>
+      <c r="AL16">
+        <v>34</v>
+      </c>
+      <c r="AM16">
+        <v>65</v>
+      </c>
+      <c r="AN16">
+        <v>19</v>
+      </c>
+      <c r="AO16">
+        <v>12</v>
+      </c>
+      <c r="AP16">
+        <v>5.8</v>
+      </c>
+      <c r="AQ16">
+        <v>5.1</v>
+      </c>
+      <c r="AR16">
+        <v>5.3</v>
+      </c>
+      <c r="AS16">
+        <v>6</v>
+      </c>
+      <c r="AT16">
+        <v>5.3</v>
+      </c>
+      <c r="AU16">
+        <v>4.4</v>
+      </c>
+      <c r="AV16">
+        <v>4.7</v>
+      </c>
+      <c r="AW16">
+        <v>5.5</v>
+      </c>
+      <c r="AX16">
+        <v>5.8</v>
+      </c>
+      <c r="AY16">
+        <v>4.9</v>
+      </c>
+      <c r="AZ16">
+        <v>5</v>
+      </c>
+      <c r="BA16">
+        <v>5.8</v>
+      </c>
+      <c r="BB16">
+        <v>6.4</v>
+      </c>
+      <c r="BC16">
+        <v>5.9</v>
+      </c>
+      <c r="BD16">
+        <v>6</v>
+      </c>
+      <c r="BE16">
+        <v>6.6</v>
+      </c>
+      <c r="BF16">
+        <v>5.3</v>
+      </c>
+      <c r="BG16">
+        <v>4.5</v>
+      </c>
+      <c r="BH16">
+        <v>5.4</v>
+      </c>
+      <c r="BI16">
+        <v>2.8</v>
+      </c>
+      <c r="BJ16">
+        <v>10.5</v>
+      </c>
+      <c r="BK16">
+        <v>3.75</v>
+      </c>
+      <c r="BL16">
+        <v>85</v>
+      </c>
+      <c r="BM16">
+        <v>5.4</v>
+      </c>
+      <c r="BN16">
+        <v>7.2</v>
+      </c>
+      <c r="BO16">
+        <v>3.2</v>
+      </c>
+      <c r="BP16">
+        <v>22</v>
+      </c>
+      <c r="BQ16">
+        <v>4.6</v>
+      </c>
+      <c r="BR16">
+        <v>28</v>
+      </c>
+      <c r="BS16">
+        <v>4.8</v>
+      </c>
+      <c r="BT16">
+        <v>6.2</v>
+      </c>
+      <c r="BU16">
+        <v>3</v>
+      </c>
+      <c r="BV16">
+        <v>17.5</v>
+      </c>
+      <c r="BW16">
+        <v>4.3</v>
+      </c>
+      <c r="BX16">
+        <v>24</v>
+      </c>
+      <c r="BY16">
+        <v>4.7</v>
+      </c>
+      <c r="BZ16">
         <v>0</v>
       </c>
-      <c r="CA14">
+      <c r="CA16">
         <v>0</v>
       </c>
-      <c r="CB14" t="s">
-        <v>127</v>
+      <c r="CB16" t="s">
+        <v>133</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-06.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-06.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="138">
   <si>
     <t>League</t>
   </si>
@@ -277,6 +277,9 @@
     <t>Venezuelan Primera Division</t>
   </si>
   <si>
+    <t>Ecuadorian Serie B</t>
+  </si>
+  <si>
     <t>2026-08-06</t>
   </si>
   <si>
@@ -307,6 +310,9 @@
     <t>20:00:00</t>
   </si>
   <si>
+    <t>20:30:00</t>
+  </si>
+  <si>
     <t>21:00:00</t>
   </si>
   <si>
@@ -352,6 +358,9 @@
     <t>Estudiantes de Merida</t>
   </si>
   <si>
+    <t>Independiente Juniors</t>
+  </si>
+  <si>
     <t>Atletico FC Cali</t>
   </si>
   <si>
@@ -397,6 +406,9 @@
     <t>Zamora FC</t>
   </si>
   <si>
+    <t>22 de Julio FC</t>
+  </si>
+  <si>
     <t>Real Santander</t>
   </si>
   <si>
@@ -415,7 +427,7 @@
     <t>Always Ready</t>
   </si>
   <si>
-    <t>2026-08-05 12:33:42</t>
+    <t>2026-08-05 14:41:37</t>
   </si>
 </sst>
 </file>
@@ -747,7 +759,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB16"/>
+  <dimension ref="A1:CB17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -997,16 +1009,16 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D2" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="E2" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="F2">
         <v>1.13</v>
@@ -1015,19 +1027,19 @@
         <v>1.15</v>
       </c>
       <c r="H2">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I2">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="J2">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="K2">
         <v>14.5</v>
       </c>
       <c r="L2">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="M2">
         <v>1.01</v>
@@ -1036,22 +1048,22 @@
         <v>14</v>
       </c>
       <c r="O2">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="P2">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="Q2">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="R2">
-        <v>2.7</v>
+        <v>2.76</v>
       </c>
       <c r="S2">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="T2">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="U2">
         <v>1.96</v>
@@ -1063,7 +1075,7 @@
         <v>7.6</v>
       </c>
       <c r="X2">
-        <v>110</v>
+        <v>950</v>
       </c>
       <c r="Y2">
         <v>950</v>
@@ -1075,7 +1087,7 @@
         <v>1000</v>
       </c>
       <c r="AB2">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AC2">
         <v>36</v>
@@ -1084,10 +1096,10 @@
         <v>95</v>
       </c>
       <c r="AE2">
-        <v>390</v>
+        <v>410</v>
       </c>
       <c r="AF2">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AG2">
         <v>21</v>
@@ -1096,133 +1108,133 @@
         <v>46</v>
       </c>
       <c r="AI2">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="AJ2">
         <v>12.5</v>
       </c>
       <c r="AK2">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="AL2">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AM2">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AN2">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AO2">
-        <v>290</v>
+        <v>320</v>
       </c>
       <c r="AP2">
+        <v>7</v>
+      </c>
+      <c r="AQ2">
+        <v>7</v>
+      </c>
+      <c r="AR2">
         <v>7.2</v>
       </c>
-      <c r="AQ2">
+      <c r="AS2">
         <v>7.4</v>
       </c>
-      <c r="AR2">
-        <v>7.6</v>
-      </c>
-      <c r="AS2">
-        <v>7.8</v>
-      </c>
       <c r="AT2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AU2">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AV2">
+        <v>6.8</v>
+      </c>
+      <c r="AW2">
         <v>7.2</v>
       </c>
-      <c r="AW2">
-        <v>7.6</v>
-      </c>
       <c r="AX2">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AY2">
         <v>14.5</v>
       </c>
       <c r="AZ2">
-        <v>32</v>
+        <v>6.4</v>
       </c>
       <c r="BA2">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BB2">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BC2">
         <v>13</v>
       </c>
       <c r="BD2">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="BE2">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="BF2">
-        <v>1.82</v>
+        <v>1.77</v>
       </c>
       <c r="BG2">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="BH2">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="BI2">
-        <v>3.95</v>
+        <v>1.04</v>
       </c>
       <c r="BJ2">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="BK2">
-        <v>4.9</v>
+        <v>1.04</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>6.8</v>
+        <v>1.04</v>
       </c>
       <c r="BN2">
-        <v>5</v>
+        <v>1000</v>
       </c>
       <c r="BO2">
-        <v>3.75</v>
+        <v>1.04</v>
       </c>
       <c r="BP2">
-        <v>6.4</v>
+        <v>1000</v>
       </c>
       <c r="BQ2">
-        <v>4.6</v>
+        <v>1.04</v>
       </c>
       <c r="BR2">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="BS2">
-        <v>5.2</v>
+        <v>1.04</v>
       </c>
       <c r="BT2">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="BU2">
-        <v>5.7</v>
+        <v>1.04</v>
       </c>
       <c r="BV2">
         <v>1000</v>
       </c>
       <c r="BW2">
-        <v>6.8</v>
+        <v>1.04</v>
       </c>
       <c r="BX2">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="BY2">
-        <v>6.6</v>
+        <v>1.04</v>
       </c>
       <c r="BZ2">
         <v>0</v>
@@ -1231,7 +1243,7 @@
         <v>0</v>
       </c>
       <c r="CB2" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1239,16 +1251,16 @@
         <v>81</v>
       </c>
       <c r="B3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D3" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E3" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="F3">
         <v>2.64</v>
@@ -1260,43 +1272,43 @@
         <v>3.7</v>
       </c>
       <c r="I3">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="J3">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="K3">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="L3">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="M3">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="N3">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="O3">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="P3">
         <v>1.34</v>
       </c>
       <c r="Q3">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="R3">
         <v>1.11</v>
       </c>
       <c r="S3">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="T3">
         <v>2.66</v>
       </c>
       <c r="U3">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="V3">
         <v>1.35</v>
@@ -1305,13 +1317,13 @@
         <v>1.59</v>
       </c>
       <c r="X3">
-        <v>6.2</v>
+        <v>5.8</v>
       </c>
       <c r="Y3">
-        <v>9.199999999999999</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Z3">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="AA3">
         <v>100</v>
@@ -1323,7 +1335,7 @@
         <v>7</v>
       </c>
       <c r="AD3">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AE3">
         <v>90</v>
@@ -1338,7 +1350,7 @@
         <v>38</v>
       </c>
       <c r="AI3">
-        <v>180</v>
+        <v>160</v>
       </c>
       <c r="AJ3">
         <v>46</v>
@@ -1347,19 +1359,19 @@
         <v>55</v>
       </c>
       <c r="AL3">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="AM3">
-        <v>490</v>
+        <v>440</v>
       </c>
       <c r="AN3">
         <v>80</v>
       </c>
       <c r="AO3">
-        <v>180</v>
+        <v>160</v>
       </c>
       <c r="AP3">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="AQ3">
         <v>7.6</v>
@@ -1371,10 +1383,10 @@
         <v>60</v>
       </c>
       <c r="AT3">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="AU3">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AV3">
         <v>18</v>
@@ -1410,7 +1422,7 @@
         <v>32</v>
       </c>
       <c r="BG3">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="BH3">
         <v>1000</v>
@@ -1473,7 +1485,7 @@
         <v>1.04</v>
       </c>
       <c r="CB3" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1481,127 +1493,127 @@
         <v>82</v>
       </c>
       <c r="B4" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C4" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D4" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E4" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="F4">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="G4">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="H4">
-        <v>2.78</v>
+        <v>2.72</v>
       </c>
       <c r="I4">
         <v>2.94</v>
       </c>
       <c r="J4">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="K4">
         <v>3.15</v>
       </c>
       <c r="L4">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="M4">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="N4">
-        <v>2.64</v>
+        <v>2.82</v>
       </c>
       <c r="O4">
-        <v>1.56</v>
+        <v>1.51</v>
       </c>
       <c r="P4">
-        <v>1.53</v>
+        <v>1.59</v>
       </c>
       <c r="Q4">
-        <v>2.72</v>
+        <v>2.58</v>
       </c>
       <c r="R4">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="S4">
-        <v>5.5</v>
+        <v>5.1</v>
       </c>
       <c r="T4">
-        <v>2.08</v>
+        <v>2.02</v>
       </c>
       <c r="U4">
-        <v>1.8</v>
+        <v>1.86</v>
       </c>
       <c r="V4">
         <v>1.52</v>
       </c>
       <c r="W4">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="X4">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Y4">
         <v>8.6</v>
       </c>
       <c r="Z4">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AA4">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="AB4">
-        <v>9.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="AC4">
         <v>7</v>
       </c>
       <c r="AD4">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AE4">
-        <v>44</v>
+        <v>100</v>
       </c>
       <c r="AF4">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="AG4">
         <v>14.5</v>
       </c>
       <c r="AH4">
-        <v>950</v>
+        <v>23</v>
       </c>
       <c r="AI4">
+        <v>80</v>
+      </c>
+      <c r="AJ4">
+        <v>95</v>
+      </c>
+      <c r="AK4">
+        <v>65</v>
+      </c>
+      <c r="AL4">
+        <v>85</v>
+      </c>
+      <c r="AM4">
+        <v>190</v>
+      </c>
+      <c r="AN4">
+        <v>80</v>
+      </c>
+      <c r="AO4">
         <v>70</v>
       </c>
-      <c r="AJ4">
-        <v>60</v>
-      </c>
-      <c r="AK4">
-        <v>48</v>
-      </c>
-      <c r="AL4">
-        <v>75</v>
-      </c>
-      <c r="AM4">
-        <v>220</v>
-      </c>
-      <c r="AN4">
-        <v>75</v>
-      </c>
-      <c r="AO4">
-        <v>65</v>
-      </c>
       <c r="AP4">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ4">
         <v>7.6</v>
@@ -1610,70 +1622,70 @@
         <v>14.5</v>
       </c>
       <c r="AS4">
-        <v>9.6</v>
+        <v>28</v>
       </c>
       <c r="AT4">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU4">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AV4">
         <v>11.5</v>
       </c>
       <c r="AW4">
-        <v>9.199999999999999</v>
+        <v>27</v>
       </c>
       <c r="AX4">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AY4">
         <v>12</v>
       </c>
       <c r="AZ4">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BA4">
+        <v>42</v>
+      </c>
+      <c r="BB4">
+        <v>9.6</v>
+      </c>
+      <c r="BC4">
+        <v>29</v>
+      </c>
+      <c r="BD4">
+        <v>42</v>
+      </c>
+      <c r="BE4">
         <v>10</v>
       </c>
-      <c r="BB4">
+      <c r="BF4">
         <v>9.800000000000001</v>
       </c>
-      <c r="BC4">
-        <v>38</v>
-      </c>
-      <c r="BD4">
-        <v>10</v>
-      </c>
-      <c r="BE4">
+      <c r="BG4">
+        <v>9.4</v>
+      </c>
+      <c r="BH4">
+        <v>2.78</v>
+      </c>
+      <c r="BI4">
+        <v>2.4</v>
+      </c>
+      <c r="BJ4">
         <v>11</v>
       </c>
-      <c r="BF4">
-        <v>10</v>
-      </c>
-      <c r="BG4">
-        <v>10</v>
-      </c>
-      <c r="BH4">
-        <v>2.68</v>
-      </c>
-      <c r="BI4">
-        <v>2.28</v>
-      </c>
-      <c r="BJ4">
-        <v>11.5</v>
-      </c>
       <c r="BK4">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>2.26</v>
+        <v>2.38</v>
       </c>
       <c r="BN4">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BO4">
         <v>4.5</v>
@@ -1682,40 +1694,40 @@
         <v>1000</v>
       </c>
       <c r="BQ4">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BR4">
         <v>1000</v>
       </c>
       <c r="BS4">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="BT4">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BU4">
         <v>4.3</v>
       </c>
       <c r="BV4">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BW4">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="BX4">
         <v>1000</v>
       </c>
       <c r="BY4">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BZ4">
         <v>1000</v>
       </c>
       <c r="CA4">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="CB4" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1723,28 +1735,28 @@
         <v>82</v>
       </c>
       <c r="B5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C5" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D5" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E5" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="F5">
-        <v>1.72</v>
+        <v>1.76</v>
       </c>
       <c r="G5">
-        <v>1.77</v>
+        <v>1.81</v>
       </c>
       <c r="H5">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="I5">
-        <v>5.2</v>
+        <v>4.8</v>
       </c>
       <c r="J5">
         <v>4.3</v>
@@ -1756,10 +1768,10 @@
         <v>1.3</v>
       </c>
       <c r="M5">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N5">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="O5">
         <v>1.2</v>
@@ -1777,49 +1789,49 @@
         <v>2.52</v>
       </c>
       <c r="T5">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="U5">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="V5">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="W5">
-        <v>2.28</v>
+        <v>2.22</v>
       </c>
       <c r="X5">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="Y5">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Z5">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="AA5">
-        <v>120</v>
+        <v>190</v>
       </c>
       <c r="AB5">
         <v>13</v>
       </c>
       <c r="AC5">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AD5">
-        <v>950</v>
+        <v>23</v>
       </c>
       <c r="AE5">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AF5">
         <v>13.5</v>
       </c>
       <c r="AG5">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AH5">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AI5">
         <v>60</v>
@@ -1831,16 +1843,16 @@
         <v>17</v>
       </c>
       <c r="AL5">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AM5">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AN5">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AO5">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AP5">
         <v>20</v>
@@ -1849,22 +1861,22 @@
         <v>20</v>
       </c>
       <c r="AR5">
-        <v>6.2</v>
+        <v>30</v>
       </c>
       <c r="AS5">
-        <v>7</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT5">
         <v>10</v>
       </c>
       <c r="AU5">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AV5">
         <v>16.5</v>
       </c>
       <c r="AW5">
-        <v>6.6</v>
+        <v>34</v>
       </c>
       <c r="AX5">
         <v>11</v>
@@ -1876,7 +1888,7 @@
         <v>14.5</v>
       </c>
       <c r="BA5">
-        <v>6.6</v>
+        <v>30</v>
       </c>
       <c r="BB5">
         <v>16</v>
@@ -1885,79 +1897,79 @@
         <v>13.5</v>
       </c>
       <c r="BD5">
-        <v>6.2</v>
+        <v>21</v>
       </c>
       <c r="BE5">
-        <v>6.8</v>
+        <v>55</v>
       </c>
       <c r="BF5">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BG5">
-        <v>6.2</v>
+        <v>28</v>
       </c>
       <c r="BH5">
         <v>4.5</v>
       </c>
       <c r="BI5">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="BJ5">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BK5">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="BL5">
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BN5">
         <v>4.9</v>
       </c>
       <c r="BO5">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="BP5">
         <v>11.5</v>
       </c>
       <c r="BQ5">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="BR5">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BS5">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BT5">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BU5">
+        <v>5</v>
+      </c>
+      <c r="BV5">
+        <v>1000</v>
+      </c>
+      <c r="BW5">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BX5">
+        <v>1000</v>
+      </c>
+      <c r="BY5">
         <v>9</v>
       </c>
-      <c r="BU5">
-        <v>4.8</v>
-      </c>
-      <c r="BV5">
-        <v>1000</v>
-      </c>
-      <c r="BW5">
-        <v>8</v>
-      </c>
-      <c r="BX5">
-        <v>1000</v>
-      </c>
-      <c r="BY5">
-        <v>8.199999999999999</v>
-      </c>
       <c r="BZ5">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="CA5">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="CB5" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -1965,19 +1977,19 @@
         <v>83</v>
       </c>
       <c r="B6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C6" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D6" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E6" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="F6">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="G6">
         <v>2.26</v>
@@ -1989,7 +2001,7 @@
         <v>3.95</v>
       </c>
       <c r="J6">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K6">
         <v>3.5</v>
@@ -2004,7 +2016,7 @@
         <v>3.4</v>
       </c>
       <c r="O6">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="P6">
         <v>1.78</v>
@@ -2013,7 +2025,7 @@
         <v>2.2</v>
       </c>
       <c r="R6">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="S6">
         <v>4.1</v>
@@ -2031,13 +2043,13 @@
         <v>1.79</v>
       </c>
       <c r="X6">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Y6">
         <v>13.5</v>
       </c>
       <c r="Z6">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AA6">
         <v>85</v>
@@ -2046,10 +2058,10 @@
         <v>9</v>
       </c>
       <c r="AC6">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AD6">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AE6">
         <v>55</v>
@@ -2064,7 +2076,7 @@
         <v>20</v>
       </c>
       <c r="AI6">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AJ6">
         <v>32</v>
@@ -2106,7 +2118,7 @@
         <v>14</v>
       </c>
       <c r="AW6">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="AX6">
         <v>11</v>
@@ -2124,13 +2136,13 @@
         <v>24</v>
       </c>
       <c r="BC6">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BD6">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BE6">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF6">
         <v>18</v>
@@ -2148,13 +2160,13 @@
         <v>10.5</v>
       </c>
       <c r="BK6">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BL6">
         <v>1000</v>
       </c>
       <c r="BM6">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BN6">
         <v>5.1</v>
@@ -2166,40 +2178,40 @@
         <v>17.5</v>
       </c>
       <c r="BQ6">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BR6">
         <v>36</v>
       </c>
       <c r="BS6">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BT6">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BU6">
         <v>5.3</v>
       </c>
       <c r="BV6">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BW6">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX6">
         <v>48</v>
       </c>
       <c r="BY6">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ6">
         <v>34</v>
       </c>
       <c r="CA6">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CB6" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
     </row>
     <row r="7" spans="1:80">
@@ -2207,19 +2219,19 @@
         <v>84</v>
       </c>
       <c r="B7" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C7" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D7" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E7" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="F7">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="G7">
         <v>2.04</v>
@@ -2231,40 +2243,40 @@
         <v>6.4</v>
       </c>
       <c r="J7">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="K7">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="L7">
         <v>1.01</v>
       </c>
       <c r="M7">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="N7">
-        <v>2.52</v>
+        <v>2.46</v>
       </c>
       <c r="O7">
         <v>1.56</v>
       </c>
       <c r="P7">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="Q7">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="R7">
         <v>1.15</v>
       </c>
       <c r="S7">
-        <v>5.7</v>
+        <v>5.2</v>
       </c>
       <c r="T7">
-        <v>2.32</v>
+        <v>2.14</v>
       </c>
       <c r="U7">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="V7">
         <v>1.19</v>
@@ -2273,7 +2285,7 @@
         <v>1.96</v>
       </c>
       <c r="X7">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="Y7">
         <v>15.5</v>
@@ -2306,7 +2318,7 @@
         <v>34</v>
       </c>
       <c r="AI7">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="AJ7">
         <v>27</v>
@@ -2318,22 +2330,22 @@
         <v>80</v>
       </c>
       <c r="AM7">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="AN7">
         <v>29</v>
       </c>
       <c r="AO7">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="AP7">
         <v>6.4</v>
       </c>
       <c r="AQ7">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AR7">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="AS7">
         <v>5.1</v>
@@ -2342,49 +2354,49 @@
         <v>4.8</v>
       </c>
       <c r="AU7">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="AV7">
         <v>18.5</v>
       </c>
       <c r="AW7">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="AX7">
         <v>7.8</v>
       </c>
       <c r="AY7">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AZ7">
-        <v>4.7</v>
+        <v>21</v>
       </c>
       <c r="BA7">
         <v>5.1</v>
       </c>
       <c r="BB7">
-        <v>17.5</v>
+        <v>19.5</v>
       </c>
       <c r="BC7">
-        <v>21</v>
+        <v>4.5</v>
       </c>
       <c r="BD7">
         <v>4.9</v>
       </c>
       <c r="BE7">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BF7">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BG7">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BH7">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="BI7">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="BJ7">
         <v>14.5</v>
@@ -2402,19 +2414,19 @@
         <v>4.8</v>
       </c>
       <c r="BO7">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="BP7">
         <v>18</v>
       </c>
       <c r="BQ7">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BR7">
         <v>50</v>
       </c>
       <c r="BS7">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BT7">
         <v>10</v>
@@ -2426,7 +2438,7 @@
         <v>75</v>
       </c>
       <c r="BW7">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BX7">
         <v>100</v>
@@ -2441,7 +2453,7 @@
         <v>0</v>
       </c>
       <c r="CB7" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
     </row>
     <row r="8" spans="1:80">
@@ -2449,19 +2461,19 @@
         <v>85</v>
       </c>
       <c r="B8" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C8" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D8" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E8" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="F8">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="G8">
         <v>1.7</v>
@@ -2470,10 +2482,10 @@
         <v>4.6</v>
       </c>
       <c r="I8">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="J8">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="K8">
         <v>5.8</v>
@@ -2482,43 +2494,43 @@
         <v>1.01</v>
       </c>
       <c r="M8">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N8">
-        <v>8.6</v>
+        <v>7.6</v>
       </c>
       <c r="O8">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="P8">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="Q8">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="R8">
         <v>2.02</v>
       </c>
       <c r="S8">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="T8">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="U8">
-        <v>2.84</v>
+        <v>1.11</v>
       </c>
       <c r="V8">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="W8">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="X8">
-        <v>55</v>
+        <v>950</v>
       </c>
       <c r="Y8">
-        <v>44</v>
+        <v>950</v>
       </c>
       <c r="Z8">
         <v>65</v>
@@ -2533,13 +2545,13 @@
         <v>15.5</v>
       </c>
       <c r="AD8">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AE8">
         <v>55</v>
       </c>
       <c r="AF8">
-        <v>17.5</v>
+        <v>19.5</v>
       </c>
       <c r="AG8">
         <v>12.5</v>
@@ -2548,16 +2560,16 @@
         <v>17.5</v>
       </c>
       <c r="AI8">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AJ8">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AK8">
         <v>16</v>
       </c>
       <c r="AL8">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AM8">
         <v>55</v>
@@ -2566,91 +2578,91 @@
         <v>4.8</v>
       </c>
       <c r="AO8">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="AP8">
-        <v>7.2</v>
+        <v>6.6</v>
       </c>
       <c r="AQ8">
+        <v>6.2</v>
+      </c>
+      <c r="AR8">
         <v>6.8</v>
       </c>
-      <c r="AR8">
-        <v>7.2</v>
-      </c>
       <c r="AS8">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="AT8">
-        <v>16.5</v>
+        <v>5.5</v>
       </c>
       <c r="AU8">
-        <v>11</v>
+        <v>5.1</v>
       </c>
       <c r="AV8">
-        <v>18.5</v>
+        <v>5.7</v>
       </c>
       <c r="AW8">
-        <v>7.2</v>
+        <v>6.6</v>
       </c>
       <c r="AX8">
+        <v>5.4</v>
+      </c>
+      <c r="AY8">
+        <v>4.7</v>
+      </c>
+      <c r="AZ8">
+        <v>5.3</v>
+      </c>
+      <c r="BA8">
+        <v>6.4</v>
+      </c>
+      <c r="BB8">
         <v>5.6</v>
       </c>
-      <c r="AY8">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ8">
-        <v>12.5</v>
-      </c>
-      <c r="BA8">
-        <v>7</v>
-      </c>
-      <c r="BB8">
-        <v>16</v>
-      </c>
       <c r="BC8">
-        <v>11.5</v>
+        <v>5.1</v>
       </c>
       <c r="BD8">
+        <v>5.7</v>
+      </c>
+      <c r="BE8">
+        <v>6.6</v>
+      </c>
+      <c r="BF8">
+        <v>2.94</v>
+      </c>
+      <c r="BG8">
         <v>6</v>
-      </c>
-      <c r="BE8">
-        <v>7.2</v>
-      </c>
-      <c r="BF8">
-        <v>3.7</v>
-      </c>
-      <c r="BG8">
-        <v>6.2</v>
       </c>
       <c r="BH8">
         <v>6.8</v>
       </c>
       <c r="BI8">
-        <v>3.05</v>
+        <v>4.6</v>
       </c>
       <c r="BJ8">
         <v>10</v>
       </c>
       <c r="BK8">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="BL8">
         <v>1000</v>
       </c>
       <c r="BM8">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BN8">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BO8">
-        <v>2.88</v>
+        <v>2.82</v>
       </c>
       <c r="BP8">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BQ8">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="BR8">
         <v>18.5</v>
@@ -2662,28 +2674,28 @@
         <v>11</v>
       </c>
       <c r="BU8">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="BV8">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BW8">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BX8">
         <v>34</v>
       </c>
       <c r="BY8">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BZ8">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="CA8">
         <v>3.55</v>
       </c>
       <c r="CB8" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
     </row>
     <row r="9" spans="1:80">
@@ -2691,181 +2703,181 @@
         <v>86</v>
       </c>
       <c r="B9" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D9" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E9" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="F9">
-        <v>2.12</v>
+        <v>1.04</v>
       </c>
       <c r="G9">
-        <v>2.44</v>
+        <v>990</v>
       </c>
       <c r="H9">
-        <v>3.15</v>
+        <v>1.04</v>
       </c>
       <c r="I9">
-        <v>4.8</v>
+        <v>990</v>
       </c>
       <c r="J9">
         <v>3.05</v>
       </c>
       <c r="K9">
-        <v>3.65</v>
+        <v>950</v>
       </c>
       <c r="L9">
-        <v>1.4</v>
+        <v>1.01</v>
       </c>
       <c r="M9">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="N9">
-        <v>2.5</v>
+        <v>1.63</v>
       </c>
       <c r="O9">
         <v>1.38</v>
       </c>
       <c r="P9">
-        <v>1.57</v>
+        <v>1.25</v>
       </c>
       <c r="Q9">
-        <v>2.02</v>
+        <v>1.38</v>
       </c>
       <c r="R9">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="S9">
+        <v>1.38</v>
+      </c>
+      <c r="T9">
+        <v>1.11</v>
+      </c>
+      <c r="U9">
+        <v>1.11</v>
+      </c>
+      <c r="V9">
+        <v>1.01</v>
+      </c>
+      <c r="W9">
+        <v>1.01</v>
+      </c>
+      <c r="X9">
+        <v>1000</v>
+      </c>
+      <c r="Y9">
+        <v>1000</v>
+      </c>
+      <c r="Z9">
+        <v>1000</v>
+      </c>
+      <c r="AA9">
+        <v>1000</v>
+      </c>
+      <c r="AB9">
+        <v>1000</v>
+      </c>
+      <c r="AC9">
+        <v>1000</v>
+      </c>
+      <c r="AD9">
+        <v>1000</v>
+      </c>
+      <c r="AE9">
+        <v>1000</v>
+      </c>
+      <c r="AF9">
+        <v>1000</v>
+      </c>
+      <c r="AG9">
+        <v>1000</v>
+      </c>
+      <c r="AH9">
+        <v>1000</v>
+      </c>
+      <c r="AI9">
+        <v>1000</v>
+      </c>
+      <c r="AJ9">
+        <v>1000</v>
+      </c>
+      <c r="AK9">
+        <v>1000</v>
+      </c>
+      <c r="AL9">
+        <v>1000</v>
+      </c>
+      <c r="AM9">
+        <v>1000</v>
+      </c>
+      <c r="AN9">
+        <v>1000</v>
+      </c>
+      <c r="AO9">
+        <v>1000</v>
+      </c>
+      <c r="AP9">
+        <v>1.01</v>
+      </c>
+      <c r="AQ9">
+        <v>1.01</v>
+      </c>
+      <c r="AR9">
+        <v>1.01</v>
+      </c>
+      <c r="AS9">
+        <v>1.01</v>
+      </c>
+      <c r="AT9">
+        <v>1.01</v>
+      </c>
+      <c r="AU9">
+        <v>1.01</v>
+      </c>
+      <c r="AV9">
+        <v>1.01</v>
+      </c>
+      <c r="AW9">
+        <v>1.01</v>
+      </c>
+      <c r="AX9">
+        <v>1.01</v>
+      </c>
+      <c r="AY9">
+        <v>1.01</v>
+      </c>
+      <c r="AZ9">
+        <v>1.01</v>
+      </c>
+      <c r="BA9">
+        <v>1.01</v>
+      </c>
+      <c r="BB9">
+        <v>1.01</v>
+      </c>
+      <c r="BC9">
+        <v>1.01</v>
+      </c>
+      <c r="BD9">
+        <v>1.01</v>
+      </c>
+      <c r="BE9">
+        <v>1.01</v>
+      </c>
+      <c r="BF9">
+        <v>1.01</v>
+      </c>
+      <c r="BG9">
+        <v>1.01</v>
+      </c>
+      <c r="BH9">
         <v>3.45</v>
-      </c>
-      <c r="T9">
-        <v>1.77</v>
-      </c>
-      <c r="U9">
-        <v>1.76</v>
-      </c>
-      <c r="V9">
-        <v>1.26</v>
-      </c>
-      <c r="W9">
-        <v>1.69</v>
-      </c>
-      <c r="X9">
-        <v>13.5</v>
-      </c>
-      <c r="Y9">
-        <v>14.5</v>
-      </c>
-      <c r="Z9">
-        <v>34</v>
-      </c>
-      <c r="AA9">
-        <v>100</v>
-      </c>
-      <c r="AB9">
-        <v>10</v>
-      </c>
-      <c r="AC9">
-        <v>9</v>
-      </c>
-      <c r="AD9">
-        <v>19.5</v>
-      </c>
-      <c r="AE9">
-        <v>70</v>
-      </c>
-      <c r="AF9">
-        <v>16.5</v>
-      </c>
-      <c r="AG9">
-        <v>14</v>
-      </c>
-      <c r="AH9">
-        <v>25</v>
-      </c>
-      <c r="AI9">
-        <v>85</v>
-      </c>
-      <c r="AJ9">
-        <v>38</v>
-      </c>
-      <c r="AK9">
-        <v>34</v>
-      </c>
-      <c r="AL9">
-        <v>60</v>
-      </c>
-      <c r="AM9">
-        <v>170</v>
-      </c>
-      <c r="AN9">
-        <v>30</v>
-      </c>
-      <c r="AO9">
-        <v>85</v>
-      </c>
-      <c r="AP9">
-        <v>1.03</v>
-      </c>
-      <c r="AQ9">
-        <v>1.03</v>
-      </c>
-      <c r="AR9">
-        <v>1.03</v>
-      </c>
-      <c r="AS9">
-        <v>1.03</v>
-      </c>
-      <c r="AT9">
-        <v>1.03</v>
-      </c>
-      <c r="AU9">
-        <v>1.03</v>
-      </c>
-      <c r="AV9">
-        <v>1.03</v>
-      </c>
-      <c r="AW9">
-        <v>1.03</v>
-      </c>
-      <c r="AX9">
-        <v>1.03</v>
-      </c>
-      <c r="AY9">
-        <v>1.03</v>
-      </c>
-      <c r="AZ9">
-        <v>1.03</v>
-      </c>
-      <c r="BA9">
-        <v>1.03</v>
-      </c>
-      <c r="BB9">
-        <v>1.03</v>
-      </c>
-      <c r="BC9">
-        <v>1.03</v>
-      </c>
-      <c r="BD9">
-        <v>1.03</v>
-      </c>
-      <c r="BE9">
-        <v>1.03</v>
-      </c>
-      <c r="BF9">
-        <v>17.5</v>
-      </c>
-      <c r="BG9">
-        <v>1.01</v>
-      </c>
-      <c r="BH9">
-        <v>3.15</v>
       </c>
       <c r="BI9">
         <v>2.44</v>
@@ -2874,58 +2886,58 @@
         <v>12.5</v>
       </c>
       <c r="BK9">
-        <v>4.9</v>
+        <v>3.55</v>
       </c>
       <c r="BL9">
         <v>1000</v>
       </c>
       <c r="BM9">
-        <v>7.8</v>
+        <v>4.8</v>
       </c>
       <c r="BN9">
-        <v>5.2</v>
+        <v>5.8</v>
       </c>
       <c r="BO9">
-        <v>3.4</v>
+        <v>2.68</v>
       </c>
       <c r="BP9">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="BQ9">
-        <v>5.7</v>
+        <v>4</v>
       </c>
       <c r="BR9">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="BS9">
-        <v>6.8</v>
+        <v>4.5</v>
       </c>
       <c r="BT9">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BU9">
-        <v>3.9</v>
+        <v>3.1</v>
       </c>
       <c r="BV9">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="BW9">
-        <v>6.6</v>
+        <v>4.4</v>
       </c>
       <c r="BX9">
         <v>60</v>
       </c>
       <c r="BY9">
-        <v>7.2</v>
+        <v>4.6</v>
       </c>
       <c r="BZ9">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="CA9">
-        <v>6.8</v>
+        <v>4.5</v>
       </c>
       <c r="CB9" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
     </row>
     <row r="10" spans="1:80">
@@ -2933,31 +2945,31 @@
         <v>86</v>
       </c>
       <c r="B10" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C10" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D10" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E10" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="F10">
         <v>2.58</v>
       </c>
       <c r="G10">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="H10">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="I10">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="J10">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="K10">
         <v>3.8</v>
@@ -2978,7 +2990,7 @@
         <v>1.84</v>
       </c>
       <c r="Q10">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="R10">
         <v>1.32</v>
@@ -2990,13 +3002,13 @@
         <v>1.75</v>
       </c>
       <c r="U10">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="V10">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="W10">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="X10">
         <v>16.5</v>
@@ -3005,10 +3017,10 @@
         <v>14</v>
       </c>
       <c r="Z10">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AA10">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AB10">
         <v>13.5</v>
@@ -3020,25 +3032,25 @@
         <v>16</v>
       </c>
       <c r="AE10">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="AF10">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="AG10">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AH10">
         <v>21</v>
       </c>
       <c r="AI10">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AJ10">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AK10">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AL10">
         <v>55</v>
@@ -3050,67 +3062,67 @@
         <v>36</v>
       </c>
       <c r="AO10">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AP10">
-        <v>11.5</v>
+        <v>3.35</v>
       </c>
       <c r="AQ10">
-        <v>8.4</v>
+        <v>3.25</v>
       </c>
       <c r="AR10">
-        <v>14</v>
+        <v>3.55</v>
       </c>
       <c r="AS10">
-        <v>4.2</v>
+        <v>3.95</v>
       </c>
       <c r="AT10">
-        <v>9.199999999999999</v>
+        <v>3.2</v>
       </c>
       <c r="AU10">
-        <v>5.9</v>
+        <v>2.92</v>
       </c>
       <c r="AV10">
-        <v>11</v>
+        <v>3.35</v>
       </c>
       <c r="AW10">
-        <v>20</v>
+        <v>3.8</v>
       </c>
       <c r="AX10">
-        <v>13</v>
+        <v>3.55</v>
       </c>
       <c r="AY10">
-        <v>10.5</v>
+        <v>3.3</v>
       </c>
       <c r="AZ10">
-        <v>14.5</v>
+        <v>3.5</v>
       </c>
       <c r="BA10">
-        <v>27</v>
+        <v>3.95</v>
       </c>
       <c r="BB10">
-        <v>24</v>
+        <v>3.95</v>
       </c>
       <c r="BC10">
-        <v>21</v>
+        <v>3.85</v>
       </c>
       <c r="BD10">
-        <v>30</v>
+        <v>3.95</v>
       </c>
       <c r="BE10">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="BF10">
-        <v>4.9</v>
+        <v>3.8</v>
       </c>
       <c r="BG10">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="BH10">
         <v>3.45</v>
       </c>
       <c r="BI10">
-        <v>2.96</v>
+        <v>2.66</v>
       </c>
       <c r="BJ10">
         <v>9.800000000000001</v>
@@ -3167,249 +3179,249 @@
         <v>7.6</v>
       </c>
       <c r="CB10" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
     </row>
     <row r="11" spans="1:80">
       <c r="A11" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="B11" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C11" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D11" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E11" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="F11">
-        <v>2.24</v>
+        <v>1.04</v>
       </c>
       <c r="G11">
-        <v>2.46</v>
+        <v>1000</v>
       </c>
       <c r="H11">
-        <v>3.2</v>
+        <v>1.04</v>
       </c>
       <c r="I11">
-        <v>3.6</v>
+        <v>1000</v>
       </c>
       <c r="J11">
-        <v>3.45</v>
+        <v>1.01</v>
       </c>
       <c r="K11">
-        <v>3.7</v>
+        <v>1000</v>
       </c>
       <c r="L11">
-        <v>1.41</v>
+        <v>1.01</v>
       </c>
       <c r="M11">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="N11">
-        <v>3.6</v>
+        <v>1.26</v>
       </c>
       <c r="O11">
-        <v>1.32</v>
+        <v>1.23</v>
       </c>
       <c r="P11">
-        <v>1.87</v>
+        <v>1.25</v>
       </c>
       <c r="Q11">
-        <v>1.85</v>
+        <v>1.23</v>
       </c>
       <c r="R11">
-        <v>1.34</v>
+        <v>1.18</v>
       </c>
       <c r="S11">
-        <v>3.25</v>
+        <v>1.23</v>
       </c>
       <c r="T11">
-        <v>1.75</v>
+        <v>1.01</v>
       </c>
       <c r="U11">
-        <v>2.12</v>
+        <v>1.01</v>
       </c>
       <c r="V11">
-        <v>1.38</v>
+        <v>1.01</v>
       </c>
       <c r="W11">
-        <v>1.68</v>
+        <v>1.01</v>
       </c>
       <c r="X11">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="Y11">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="Z11">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AA11">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AB11">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AC11">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="AD11">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AE11">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AF11">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AG11">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AH11">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AI11">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AJ11">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AK11">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AL11">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AM11">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AN11">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AO11">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AP11">
-        <v>12</v>
+        <v>1.03</v>
       </c>
       <c r="AQ11">
-        <v>11</v>
+        <v>1.03</v>
       </c>
       <c r="AR11">
-        <v>20</v>
+        <v>1.03</v>
       </c>
       <c r="AS11">
-        <v>4.1</v>
+        <v>1.03</v>
       </c>
       <c r="AT11">
-        <v>7.6</v>
+        <v>1.03</v>
       </c>
       <c r="AU11">
-        <v>6</v>
+        <v>1.03</v>
       </c>
       <c r="AV11">
-        <v>12</v>
+        <v>1.03</v>
       </c>
       <c r="AW11">
-        <v>4</v>
+        <v>1.03</v>
       </c>
       <c r="AX11">
-        <v>13</v>
+        <v>1.03</v>
       </c>
       <c r="AY11">
-        <v>9.6</v>
+        <v>1.03</v>
       </c>
       <c r="AZ11">
-        <v>14.5</v>
+        <v>1.03</v>
       </c>
       <c r="BA11">
-        <v>4.1</v>
+        <v>1.03</v>
       </c>
       <c r="BB11">
-        <v>3.9</v>
+        <v>1.03</v>
       </c>
       <c r="BC11">
-        <v>21</v>
+        <v>1.03</v>
       </c>
       <c r="BD11">
-        <v>4</v>
+        <v>1.03</v>
       </c>
       <c r="BE11">
-        <v>4.2</v>
+        <v>1.03</v>
       </c>
       <c r="BF11">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="BG11">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="BH11">
-        <v>3.5</v>
+        <v>1000</v>
       </c>
       <c r="BI11">
-        <v>2.7</v>
+        <v>1.01</v>
       </c>
       <c r="BJ11">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="BK11">
-        <v>5.2</v>
+        <v>1.01</v>
       </c>
       <c r="BL11">
         <v>1000</v>
       </c>
       <c r="BM11">
-        <v>2.62</v>
+        <v>1.01</v>
       </c>
       <c r="BN11">
-        <v>5.4</v>
+        <v>1000</v>
       </c>
       <c r="BO11">
-        <v>3.6</v>
+        <v>1.01</v>
       </c>
       <c r="BP11">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="BQ11">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="BR11">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BS11">
-        <v>2.46</v>
+        <v>1.01</v>
       </c>
       <c r="BT11">
-        <v>6.8</v>
+        <v>1000</v>
       </c>
       <c r="BU11">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="BV11">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="BW11">
-        <v>2.44</v>
+        <v>1.01</v>
       </c>
       <c r="BX11">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="BY11">
-        <v>2.5</v>
+        <v>1.01</v>
       </c>
       <c r="BZ11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB11" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
     </row>
     <row r="12" spans="1:80">
@@ -3417,1209 +3429,1451 @@
         <v>84</v>
       </c>
       <c r="B12" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C12" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D12" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E12" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="F12">
-        <v>1.83</v>
+        <v>2.24</v>
       </c>
       <c r="G12">
-        <v>1.9</v>
+        <v>2.46</v>
       </c>
       <c r="H12">
-        <v>4.5</v>
+        <v>3.2</v>
       </c>
       <c r="I12">
-        <v>4.9</v>
+        <v>3.6</v>
       </c>
       <c r="J12">
+        <v>3.45</v>
+      </c>
+      <c r="K12">
         <v>3.7</v>
       </c>
-      <c r="K12">
-        <v>4.4</v>
-      </c>
       <c r="L12">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="M12">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="N12">
-        <v>2.84</v>
+        <v>3.6</v>
       </c>
       <c r="O12">
-        <v>1.46</v>
+        <v>1.32</v>
       </c>
       <c r="P12">
-        <v>1.66</v>
+        <v>1.87</v>
       </c>
       <c r="Q12">
-        <v>2.3</v>
+        <v>1.85</v>
       </c>
       <c r="R12">
-        <v>1.23</v>
+        <v>1.34</v>
       </c>
       <c r="S12">
+        <v>3.25</v>
+      </c>
+      <c r="T12">
+        <v>1.73</v>
+      </c>
+      <c r="U12">
+        <v>2.08</v>
+      </c>
+      <c r="V12">
+        <v>1.38</v>
+      </c>
+      <c r="W12">
+        <v>1.68</v>
+      </c>
+      <c r="X12">
+        <v>17</v>
+      </c>
+      <c r="Y12">
+        <v>16</v>
+      </c>
+      <c r="Z12">
+        <v>29</v>
+      </c>
+      <c r="AA12">
+        <v>75</v>
+      </c>
+      <c r="AB12">
+        <v>12.5</v>
+      </c>
+      <c r="AC12">
+        <v>9.6</v>
+      </c>
+      <c r="AD12">
+        <v>17.5</v>
+      </c>
+      <c r="AE12">
+        <v>48</v>
+      </c>
+      <c r="AF12">
+        <v>18.5</v>
+      </c>
+      <c r="AG12">
+        <v>14</v>
+      </c>
+      <c r="AH12">
+        <v>21</v>
+      </c>
+      <c r="AI12">
+        <v>60</v>
+      </c>
+      <c r="AJ12">
+        <v>34</v>
+      </c>
+      <c r="AK12">
+        <v>32</v>
+      </c>
+      <c r="AL12">
+        <v>48</v>
+      </c>
+      <c r="AM12">
+        <v>120</v>
+      </c>
+      <c r="AN12">
+        <v>24</v>
+      </c>
+      <c r="AO12">
+        <v>48</v>
+      </c>
+      <c r="AP12">
+        <v>3.5</v>
+      </c>
+      <c r="AQ12">
+        <v>3.45</v>
+      </c>
+      <c r="AR12">
+        <v>3.8</v>
+      </c>
+      <c r="AS12">
         <v>4.1</v>
       </c>
-      <c r="T12">
-        <v>2.18</v>
-      </c>
-      <c r="U12">
-        <v>1.73</v>
-      </c>
-      <c r="V12">
-        <v>1.25</v>
-      </c>
-      <c r="W12">
-        <v>2.1</v>
-      </c>
-      <c r="X12">
-        <v>14</v>
-      </c>
-      <c r="Y12">
-        <v>14.5</v>
-      </c>
-      <c r="Z12">
-        <v>42</v>
-      </c>
-      <c r="AA12">
-        <v>170</v>
-      </c>
-      <c r="AB12">
+      <c r="AT12">
+        <v>3.25</v>
+      </c>
+      <c r="AU12">
+        <v>3</v>
+      </c>
+      <c r="AV12">
+        <v>3.5</v>
+      </c>
+      <c r="AW12">
+        <v>4</v>
+      </c>
+      <c r="AX12">
+        <v>3.55</v>
+      </c>
+      <c r="AY12">
+        <v>3.35</v>
+      </c>
+      <c r="AZ12">
+        <v>3.6</v>
+      </c>
+      <c r="BA12">
+        <v>4.1</v>
+      </c>
+      <c r="BB12">
+        <v>3.9</v>
+      </c>
+      <c r="BC12">
+        <v>3.85</v>
+      </c>
+      <c r="BD12">
+        <v>4</v>
+      </c>
+      <c r="BE12">
+        <v>4.2</v>
+      </c>
+      <c r="BF12">
+        <v>3.7</v>
+      </c>
+      <c r="BG12">
+        <v>4</v>
+      </c>
+      <c r="BH12">
+        <v>3.5</v>
+      </c>
+      <c r="BI12">
+        <v>2.72</v>
+      </c>
+      <c r="BJ12">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BK12">
+        <v>5.2</v>
+      </c>
+      <c r="BL12">
+        <v>1000</v>
+      </c>
+      <c r="BM12">
+        <v>2.62</v>
+      </c>
+      <c r="BN12">
+        <v>5.4</v>
+      </c>
+      <c r="BO12">
+        <v>3.65</v>
+      </c>
+      <c r="BP12">
+        <v>18</v>
+      </c>
+      <c r="BQ12">
         <v>6.8</v>
       </c>
-      <c r="AC12">
-        <v>11.5</v>
-      </c>
-      <c r="AD12">
-        <v>19</v>
-      </c>
-      <c r="AE12">
-        <v>100</v>
-      </c>
-      <c r="AF12">
-        <v>10</v>
-      </c>
-      <c r="AG12">
-        <v>11</v>
-      </c>
-      <c r="AH12">
-        <v>36</v>
-      </c>
-      <c r="AI12">
-        <v>110</v>
-      </c>
-      <c r="AJ12">
-        <v>21</v>
-      </c>
-      <c r="AK12">
-        <v>24</v>
-      </c>
-      <c r="AL12">
-        <v>55</v>
-      </c>
-      <c r="AM12">
-        <v>260</v>
-      </c>
-      <c r="AN12">
-        <v>18</v>
-      </c>
-      <c r="AO12">
-        <v>170</v>
-      </c>
-      <c r="AP12">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AQ12">
-        <v>4.9</v>
-      </c>
-      <c r="AR12">
-        <v>21</v>
-      </c>
-      <c r="AS12">
-        <v>7.2</v>
-      </c>
-      <c r="AT12">
-        <v>5</v>
-      </c>
-      <c r="AU12">
-        <v>7.2</v>
-      </c>
-      <c r="AV12">
-        <v>5.3</v>
-      </c>
-      <c r="AW12">
-        <v>7</v>
-      </c>
-      <c r="AX12">
-        <v>7.2</v>
-      </c>
-      <c r="AY12">
-        <v>7.8</v>
-      </c>
-      <c r="AZ12">
-        <v>20</v>
-      </c>
-      <c r="BA12">
-        <v>7</v>
-      </c>
-      <c r="BB12">
-        <v>14.5</v>
-      </c>
-      <c r="BC12">
-        <v>17</v>
-      </c>
-      <c r="BD12">
-        <v>6.6</v>
-      </c>
-      <c r="BE12">
-        <v>7.2</v>
-      </c>
-      <c r="BF12">
-        <v>13</v>
-      </c>
-      <c r="BG12">
-        <v>7.2</v>
-      </c>
-      <c r="BH12">
-        <v>2.94</v>
-      </c>
-      <c r="BI12">
+      <c r="BR12">
+        <v>32</v>
+      </c>
+      <c r="BS12">
+        <v>2.46</v>
+      </c>
+      <c r="BT12">
+        <v>6.8</v>
+      </c>
+      <c r="BU12">
+        <v>4.2</v>
+      </c>
+      <c r="BV12">
+        <v>28</v>
+      </c>
+      <c r="BW12">
         <v>2.44</v>
       </c>
-      <c r="BJ12">
-        <v>12</v>
-      </c>
-      <c r="BK12">
-        <v>6.4</v>
-      </c>
-      <c r="BL12">
-        <v>1000</v>
-      </c>
-      <c r="BM12">
-        <v>2.4</v>
-      </c>
-      <c r="BN12">
-        <v>4.3</v>
-      </c>
-      <c r="BO12">
-        <v>3.75</v>
-      </c>
-      <c r="BP12">
-        <v>14</v>
-      </c>
-      <c r="BQ12">
-        <v>7</v>
-      </c>
-      <c r="BR12">
-        <v>36</v>
-      </c>
-      <c r="BS12">
-        <v>2.28</v>
-      </c>
-      <c r="BT12">
-        <v>9</v>
-      </c>
-      <c r="BU12">
-        <v>6.8</v>
-      </c>
-      <c r="BV12">
-        <v>1000</v>
-      </c>
-      <c r="BW12">
-        <v>2.34</v>
-      </c>
       <c r="BX12">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BY12">
-        <v>2.36</v>
+        <v>2.5</v>
       </c>
       <c r="BZ12">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="CA12">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="CB12" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
     </row>
     <row r="13" spans="1:80">
       <c r="A13" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="B13" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C13" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D13" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E13" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="F13">
-        <v>2.4</v>
+        <v>1.82</v>
       </c>
       <c r="G13">
+        <v>1.9</v>
+      </c>
+      <c r="H13">
+        <v>4.5</v>
+      </c>
+      <c r="I13">
+        <v>5</v>
+      </c>
+      <c r="J13">
+        <v>3.65</v>
+      </c>
+      <c r="K13">
+        <v>4.4</v>
+      </c>
+      <c r="L13">
+        <v>1.5</v>
+      </c>
+      <c r="M13">
+        <v>1.08</v>
+      </c>
+      <c r="N13">
+        <v>2.98</v>
+      </c>
+      <c r="O13">
+        <v>1.39</v>
+      </c>
+      <c r="P13">
+        <v>1.69</v>
+      </c>
+      <c r="Q13">
+        <v>2.12</v>
+      </c>
+      <c r="R13">
+        <v>1.26</v>
+      </c>
+      <c r="S13">
+        <v>3.45</v>
+      </c>
+      <c r="T13">
+        <v>1.11</v>
+      </c>
+      <c r="U13">
+        <v>1.11</v>
+      </c>
+      <c r="V13">
+        <v>1.25</v>
+      </c>
+      <c r="W13">
+        <v>2.12</v>
+      </c>
+      <c r="X13">
+        <v>14</v>
+      </c>
+      <c r="Y13">
+        <v>14.5</v>
+      </c>
+      <c r="Z13">
+        <v>42</v>
+      </c>
+      <c r="AA13">
+        <v>170</v>
+      </c>
+      <c r="AB13">
+        <v>6.8</v>
+      </c>
+      <c r="AC13">
+        <v>11.5</v>
+      </c>
+      <c r="AD13">
+        <v>22</v>
+      </c>
+      <c r="AE13">
+        <v>100</v>
+      </c>
+      <c r="AF13">
+        <v>10</v>
+      </c>
+      <c r="AG13">
+        <v>11</v>
+      </c>
+      <c r="AH13">
+        <v>30</v>
+      </c>
+      <c r="AI13">
+        <v>110</v>
+      </c>
+      <c r="AJ13">
+        <v>21</v>
+      </c>
+      <c r="AK13">
+        <v>24</v>
+      </c>
+      <c r="AL13">
+        <v>55</v>
+      </c>
+      <c r="AM13">
+        <v>260</v>
+      </c>
+      <c r="AN13">
+        <v>18</v>
+      </c>
+      <c r="AO13">
+        <v>170</v>
+      </c>
+      <c r="AP13">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AQ13">
+        <v>10.5</v>
+      </c>
+      <c r="AR13">
+        <v>6.2</v>
+      </c>
+      <c r="AS13">
+        <v>7</v>
+      </c>
+      <c r="AT13">
+        <v>5</v>
+      </c>
+      <c r="AU13">
+        <v>7</v>
+      </c>
+      <c r="AV13">
+        <v>16.5</v>
+      </c>
+      <c r="AW13">
+        <v>6.8</v>
+      </c>
+      <c r="AX13">
+        <v>7.2</v>
+      </c>
+      <c r="AY13">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ13">
+        <v>21</v>
+      </c>
+      <c r="BA13">
+        <v>6.8</v>
+      </c>
+      <c r="BB13">
+        <v>14.5</v>
+      </c>
+      <c r="BC13">
+        <v>17</v>
+      </c>
+      <c r="BD13">
+        <v>6.4</v>
+      </c>
+      <c r="BE13">
+        <v>7.2</v>
+      </c>
+      <c r="BF13">
+        <v>13</v>
+      </c>
+      <c r="BG13">
+        <v>7</v>
+      </c>
+      <c r="BH13">
+        <v>2.98</v>
+      </c>
+      <c r="BI13">
         <v>2.5</v>
       </c>
-      <c r="H13">
-        <v>3.55</v>
-      </c>
-      <c r="I13">
-        <v>3.8</v>
-      </c>
-      <c r="J13">
-        <v>3.05</v>
-      </c>
-      <c r="K13">
-        <v>3.15</v>
-      </c>
-      <c r="L13">
-        <v>1.47</v>
-      </c>
-      <c r="M13">
-        <v>1.13</v>
-      </c>
-      <c r="N13">
-        <v>2.62</v>
-      </c>
-      <c r="O13">
-        <v>1.54</v>
-      </c>
-      <c r="P13">
-        <v>1.55</v>
-      </c>
-      <c r="Q13">
-        <v>2.66</v>
-      </c>
-      <c r="R13">
-        <v>1.2</v>
-      </c>
-      <c r="S13">
-        <v>5.4</v>
-      </c>
-      <c r="T13">
-        <v>2.1</v>
-      </c>
-      <c r="U13">
-        <v>1.8</v>
-      </c>
-      <c r="V13">
-        <v>1.36</v>
-      </c>
-      <c r="W13">
-        <v>1.66</v>
-      </c>
-      <c r="X13">
-        <v>11</v>
-      </c>
-      <c r="Y13">
+      <c r="BJ13">
+        <v>11.5</v>
+      </c>
+      <c r="BK13">
+        <v>6.6</v>
+      </c>
+      <c r="BL13">
+        <v>1000</v>
+      </c>
+      <c r="BM13">
+        <v>14.5</v>
+      </c>
+      <c r="BN13">
+        <v>4.3</v>
+      </c>
+      <c r="BO13">
+        <v>3.35</v>
+      </c>
+      <c r="BP13">
+        <v>14</v>
+      </c>
+      <c r="BQ13">
+        <v>7.4</v>
+      </c>
+      <c r="BR13">
+        <v>1000</v>
+      </c>
+      <c r="BS13">
+        <v>10.5</v>
+      </c>
+      <c r="BT13">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BU13">
+        <v>6.4</v>
+      </c>
+      <c r="BV13">
+        <v>1000</v>
+      </c>
+      <c r="BW13">
         <v>12</v>
       </c>
-      <c r="Z13">
-        <v>29</v>
-      </c>
-      <c r="AA13">
-        <v>100</v>
-      </c>
-      <c r="AB13">
-        <v>7.6</v>
-      </c>
-      <c r="AC13">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AD13">
-        <v>20</v>
-      </c>
-      <c r="AE13">
-        <v>75</v>
-      </c>
-      <c r="AF13">
-        <v>14.5</v>
-      </c>
-      <c r="AG13">
+      <c r="BX13">
+        <v>1000</v>
+      </c>
+      <c r="BY13">
         <v>12.5</v>
       </c>
-      <c r="AH13">
-        <v>24</v>
-      </c>
-      <c r="AI13">
-        <v>100</v>
-      </c>
-      <c r="AJ13">
-        <v>46</v>
-      </c>
-      <c r="AK13">
-        <v>42</v>
-      </c>
-      <c r="AL13">
-        <v>75</v>
-      </c>
-      <c r="AM13">
-        <v>220</v>
-      </c>
-      <c r="AN13">
-        <v>44</v>
-      </c>
-      <c r="AO13">
-        <v>100</v>
-      </c>
-      <c r="AP13">
-        <v>7.8</v>
-      </c>
-      <c r="AQ13">
-        <v>9</v>
-      </c>
-      <c r="AR13">
-        <v>17.5</v>
-      </c>
-      <c r="AS13">
-        <v>5.3</v>
-      </c>
-      <c r="AT13">
-        <v>6.6</v>
-      </c>
-      <c r="AU13">
-        <v>6.6</v>
-      </c>
-      <c r="AV13">
-        <v>14</v>
-      </c>
-      <c r="AW13">
-        <v>5.2</v>
-      </c>
-      <c r="AX13">
-        <v>12</v>
-      </c>
-      <c r="AY13">
+      <c r="BZ13">
+        <v>1000</v>
+      </c>
+      <c r="CA13">
         <v>10.5</v>
       </c>
-      <c r="AZ13">
-        <v>5</v>
-      </c>
-      <c r="BA13">
-        <v>5.3</v>
-      </c>
-      <c r="BB13">
-        <v>5</v>
-      </c>
-      <c r="BC13">
-        <v>5</v>
-      </c>
-      <c r="BD13">
-        <v>5.2</v>
-      </c>
-      <c r="BE13">
-        <v>5.5</v>
-      </c>
-      <c r="BF13">
-        <v>5</v>
-      </c>
-      <c r="BG13">
-        <v>5.3</v>
-      </c>
-      <c r="BH13">
-        <v>3.15</v>
-      </c>
-      <c r="BI13">
-        <v>2.24</v>
-      </c>
-      <c r="BJ13">
-        <v>13.5</v>
-      </c>
-      <c r="BK13">
-        <v>3.6</v>
-      </c>
-      <c r="BL13">
-        <v>1000</v>
-      </c>
-      <c r="BM13">
-        <v>4.8</v>
-      </c>
-      <c r="BN13">
-        <v>6</v>
-      </c>
-      <c r="BO13">
-        <v>4.5</v>
-      </c>
-      <c r="BP13">
-        <v>26</v>
-      </c>
-      <c r="BQ13">
-        <v>4.1</v>
-      </c>
-      <c r="BR13">
-        <v>55</v>
-      </c>
-      <c r="BS13">
-        <v>4.5</v>
-      </c>
-      <c r="BT13">
-        <v>8</v>
-      </c>
-      <c r="BU13">
-        <v>5</v>
-      </c>
-      <c r="BV13">
-        <v>44</v>
-      </c>
-      <c r="BW13">
-        <v>4.4</v>
-      </c>
-      <c r="BX13">
-        <v>70</v>
-      </c>
-      <c r="BY13">
-        <v>4.6</v>
-      </c>
-      <c r="BZ13">
-        <v>60</v>
-      </c>
-      <c r="CA13">
-        <v>4.5</v>
-      </c>
       <c r="CB13" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
     </row>
     <row r="14" spans="1:80">
       <c r="A14" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="B14" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C14" t="s">
+        <v>101</v>
+      </c>
+      <c r="D14" t="s">
+        <v>117</v>
+      </c>
+      <c r="E14" t="s">
+        <v>133</v>
+      </c>
+      <c r="F14">
+        <v>2.4</v>
+      </c>
+      <c r="G14">
+        <v>2.52</v>
+      </c>
+      <c r="H14">
+        <v>3.55</v>
+      </c>
+      <c r="I14">
+        <v>3.8</v>
+      </c>
+      <c r="J14">
+        <v>3.05</v>
+      </c>
+      <c r="K14">
+        <v>3.15</v>
+      </c>
+      <c r="L14">
+        <v>1.47</v>
+      </c>
+      <c r="M14">
+        <v>1.12</v>
+      </c>
+      <c r="N14">
+        <v>2.62</v>
+      </c>
+      <c r="O14">
+        <v>1.54</v>
+      </c>
+      <c r="P14">
+        <v>1.55</v>
+      </c>
+      <c r="Q14">
+        <v>2.66</v>
+      </c>
+      <c r="R14">
+        <v>1.2</v>
+      </c>
+      <c r="S14">
+        <v>5.4</v>
+      </c>
+      <c r="T14">
+        <v>2.1</v>
+      </c>
+      <c r="U14">
+        <v>1.8</v>
+      </c>
+      <c r="V14">
+        <v>1.36</v>
+      </c>
+      <c r="W14">
+        <v>1.65</v>
+      </c>
+      <c r="X14">
+        <v>9</v>
+      </c>
+      <c r="Y14">
+        <v>12</v>
+      </c>
+      <c r="Z14">
+        <v>29</v>
+      </c>
+      <c r="AA14">
         <v>100</v>
       </c>
-      <c r="D14" t="s">
-        <v>115</v>
-      </c>
-      <c r="E14" t="s">
-        <v>130</v>
-      </c>
-      <c r="F14">
-        <v>1.04</v>
-      </c>
-      <c r="G14">
-        <v>110</v>
-      </c>
-      <c r="H14">
-        <v>1.04</v>
-      </c>
-      <c r="I14">
-        <v>110</v>
-      </c>
-      <c r="J14">
-        <v>1.02</v>
-      </c>
-      <c r="K14">
-        <v>950</v>
-      </c>
-      <c r="L14">
-        <v>1.01</v>
-      </c>
-      <c r="M14">
-        <v>1.01</v>
-      </c>
-      <c r="N14">
-        <v>1.26</v>
-      </c>
-      <c r="O14">
-        <v>1.01</v>
-      </c>
-      <c r="P14">
-        <v>1.25</v>
-      </c>
-      <c r="Q14">
-        <v>1.41</v>
-      </c>
-      <c r="R14">
-        <v>1.18</v>
-      </c>
-      <c r="S14">
-        <v>1.41</v>
-      </c>
-      <c r="T14">
-        <v>1.11</v>
-      </c>
-      <c r="U14">
-        <v>1.11</v>
-      </c>
-      <c r="V14">
-        <v>1.01</v>
-      </c>
-      <c r="W14">
-        <v>1.01</v>
-      </c>
-      <c r="X14">
-        <v>1000</v>
-      </c>
-      <c r="Y14">
-        <v>1000</v>
-      </c>
-      <c r="Z14">
-        <v>1000</v>
-      </c>
-      <c r="AA14">
-        <v>1000</v>
-      </c>
       <c r="AB14">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="AC14">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="AD14">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AE14">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AF14">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AG14">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH14">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AI14">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AJ14">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AK14">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AL14">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AM14">
-        <v>1000</v>
+        <v>220</v>
       </c>
       <c r="AN14">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AO14">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AP14">
-        <v>1.03</v>
+        <v>7.8</v>
       </c>
       <c r="AQ14">
-        <v>1.03</v>
+        <v>9</v>
       </c>
       <c r="AR14">
-        <v>1.03</v>
+        <v>17.5</v>
       </c>
       <c r="AS14">
-        <v>1.03</v>
+        <v>6.8</v>
       </c>
       <c r="AT14">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="AU14">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="AV14">
-        <v>1.03</v>
+        <v>14</v>
       </c>
       <c r="AW14">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="AX14">
-        <v>1.03</v>
+        <v>12</v>
       </c>
       <c r="AY14">
-        <v>1.03</v>
+        <v>10.5</v>
       </c>
       <c r="AZ14">
-        <v>1.03</v>
+        <v>5.6</v>
       </c>
       <c r="BA14">
-        <v>1.03</v>
+        <v>6.8</v>
       </c>
       <c r="BB14">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="BC14">
-        <v>1.03</v>
+        <v>24</v>
       </c>
       <c r="BD14">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="BE14">
-        <v>1.03</v>
+        <v>7.2</v>
       </c>
       <c r="BF14">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BG14">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BH14">
-        <v>1000</v>
+        <v>3.15</v>
       </c>
       <c r="BI14">
-        <v>1.01</v>
+        <v>2.24</v>
       </c>
       <c r="BJ14">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="BK14">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BL14">
         <v>1000</v>
       </c>
       <c r="BM14">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BN14">
-        <v>1000</v>
+        <v>6</v>
       </c>
       <c r="BO14">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="BP14">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="BQ14">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BR14">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BS14">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BT14">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="BU14">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BV14">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="BW14">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BX14">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="BY14">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BZ14">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="CA14">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="CB14" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
     </row>
     <row r="15" spans="1:80">
       <c r="A15" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B15" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C15" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D15" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E15" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="F15">
+        <v>1.71</v>
+      </c>
+      <c r="G15">
+        <v>2.2</v>
+      </c>
+      <c r="H15">
+        <v>3.95</v>
+      </c>
+      <c r="I15">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="J15">
+        <v>2.96</v>
+      </c>
+      <c r="K15">
+        <v>3.95</v>
+      </c>
+      <c r="L15">
+        <v>1.36</v>
+      </c>
+      <c r="M15">
+        <v>1.01</v>
+      </c>
+      <c r="N15">
+        <v>2.38</v>
+      </c>
+      <c r="O15">
+        <v>1.4</v>
+      </c>
+      <c r="P15">
+        <v>1.55</v>
+      </c>
+      <c r="Q15">
         <v>1.96</v>
       </c>
-      <c r="G15">
-        <v>2.14</v>
-      </c>
-      <c r="H15">
-        <v>4.5</v>
-      </c>
-      <c r="I15">
-        <v>5.5</v>
-      </c>
-      <c r="J15">
-        <v>2.94</v>
-      </c>
-      <c r="K15">
-        <v>3.4</v>
-      </c>
-      <c r="L15">
-        <v>1.54</v>
-      </c>
-      <c r="M15">
-        <v>1.14</v>
-      </c>
-      <c r="N15">
-        <v>2.32</v>
-      </c>
-      <c r="O15">
-        <v>1.58</v>
-      </c>
-      <c r="P15">
-        <v>1.45</v>
-      </c>
-      <c r="Q15">
-        <v>2.76</v>
-      </c>
       <c r="R15">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="S15">
-        <v>5.9</v>
+        <v>2.78</v>
       </c>
       <c r="T15">
-        <v>2.32</v>
+        <v>1.11</v>
       </c>
       <c r="U15">
-        <v>1.57</v>
+        <v>1.11</v>
       </c>
       <c r="V15">
-        <v>1.22</v>
+        <v>1.13</v>
       </c>
       <c r="W15">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="X15">
-        <v>8.4</v>
+        <v>1000</v>
       </c>
       <c r="Y15">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="Z15">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AA15">
-        <v>180</v>
+        <v>1000</v>
       </c>
       <c r="AB15">
-        <v>6.4</v>
+        <v>1000</v>
       </c>
       <c r="AC15">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="AD15">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AE15">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AF15">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AG15">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AH15">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AI15">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AJ15">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AK15">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AL15">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AM15">
-        <v>290</v>
+        <v>1000</v>
       </c>
       <c r="AN15">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AO15">
-        <v>220</v>
+        <v>1000</v>
       </c>
       <c r="AP15">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="AQ15">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AR15">
-        <v>23</v>
+        <v>1.01</v>
       </c>
       <c r="AS15">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="AT15">
-        <v>3.75</v>
+        <v>1.01</v>
       </c>
       <c r="AU15">
-        <v>5.9</v>
+        <v>1.01</v>
       </c>
       <c r="AV15">
-        <v>18.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW15">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="AX15">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="AY15">
-        <v>5.2</v>
+        <v>1.01</v>
       </c>
       <c r="AZ15">
-        <v>18</v>
+        <v>1.01</v>
       </c>
       <c r="BA15">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="BB15">
-        <v>17</v>
+        <v>1.01</v>
       </c>
       <c r="BC15">
-        <v>19.5</v>
+        <v>1.01</v>
       </c>
       <c r="BD15">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="BE15">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="BF15">
-        <v>18.5</v>
+        <v>1.01</v>
       </c>
       <c r="BG15">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="BH15">
-        <v>2.86</v>
+        <v>1000</v>
       </c>
       <c r="BI15">
-        <v>2.2</v>
+        <v>1.04</v>
       </c>
       <c r="BJ15">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="BK15">
-        <v>4.3</v>
+        <v>1.04</v>
       </c>
       <c r="BL15">
         <v>1000</v>
       </c>
       <c r="BM15">
-        <v>6</v>
+        <v>1.04</v>
       </c>
       <c r="BN15">
-        <v>5</v>
+        <v>1000</v>
       </c>
       <c r="BO15">
-        <v>3.6</v>
+        <v>1.04</v>
       </c>
       <c r="BP15">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="BQ15">
-        <v>4.7</v>
+        <v>1.04</v>
       </c>
       <c r="BR15">
         <v>1000</v>
       </c>
       <c r="BS15">
-        <v>5.6</v>
+        <v>1.04</v>
       </c>
       <c r="BT15">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="BU15">
-        <v>3.7</v>
+        <v>1.04</v>
       </c>
       <c r="BV15">
         <v>1000</v>
       </c>
       <c r="BW15">
-        <v>5.7</v>
+        <v>1.04</v>
       </c>
       <c r="BX15">
         <v>1000</v>
       </c>
       <c r="BY15">
-        <v>5.9</v>
+        <v>1.04</v>
       </c>
       <c r="BZ15">
         <v>1000</v>
       </c>
       <c r="CA15">
-        <v>5.7</v>
+        <v>1.04</v>
       </c>
       <c r="CB15" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
     </row>
     <row r="16" spans="1:80">
       <c r="A16" t="s">
+        <v>84</v>
+      </c>
+      <c r="B16" t="s">
+        <v>88</v>
+      </c>
+      <c r="C16" t="s">
+        <v>103</v>
+      </c>
+      <c r="D16" t="s">
+        <v>119</v>
+      </c>
+      <c r="E16" t="s">
+        <v>135</v>
+      </c>
+      <c r="F16">
+        <v>1.97</v>
+      </c>
+      <c r="G16">
+        <v>2.2</v>
+      </c>
+      <c r="H16">
+        <v>4.3</v>
+      </c>
+      <c r="I16">
+        <v>5.5</v>
+      </c>
+      <c r="J16">
+        <v>2.96</v>
+      </c>
+      <c r="K16">
+        <v>3.65</v>
+      </c>
+      <c r="L16">
+        <v>1.54</v>
+      </c>
+      <c r="M16">
+        <v>1.14</v>
+      </c>
+      <c r="N16">
+        <v>2.36</v>
+      </c>
+      <c r="O16">
+        <v>1.58</v>
+      </c>
+      <c r="P16">
+        <v>1.45</v>
+      </c>
+      <c r="Q16">
+        <v>2.78</v>
+      </c>
+      <c r="R16">
+        <v>1.16</v>
+      </c>
+      <c r="S16">
+        <v>5.9</v>
+      </c>
+      <c r="T16">
+        <v>2.32</v>
+      </c>
+      <c r="U16">
+        <v>1.57</v>
+      </c>
+      <c r="V16">
+        <v>1.22</v>
+      </c>
+      <c r="W16">
+        <v>1.84</v>
+      </c>
+      <c r="X16">
+        <v>8.4</v>
+      </c>
+      <c r="Y16">
+        <v>12.5</v>
+      </c>
+      <c r="Z16">
+        <v>40</v>
+      </c>
+      <c r="AA16">
+        <v>180</v>
+      </c>
+      <c r="AB16">
+        <v>6.4</v>
+      </c>
+      <c r="AC16">
+        <v>7.8</v>
+      </c>
+      <c r="AD16">
+        <v>26</v>
+      </c>
+      <c r="AE16">
+        <v>120</v>
+      </c>
+      <c r="AF16">
+        <v>13</v>
+      </c>
+      <c r="AG16">
+        <v>12.5</v>
+      </c>
+      <c r="AH16">
+        <v>34</v>
+      </c>
+      <c r="AI16">
+        <v>150</v>
+      </c>
+      <c r="AJ16">
+        <v>28</v>
+      </c>
+      <c r="AK16">
+        <v>34</v>
+      </c>
+      <c r="AL16">
         <v>80</v>
       </c>
-      <c r="B16" t="s">
-        <v>87</v>
-      </c>
-      <c r="C16" t="s">
-        <v>102</v>
-      </c>
-      <c r="D16" t="s">
-        <v>117</v>
-      </c>
-      <c r="E16" t="s">
-        <v>132</v>
-      </c>
-      <c r="F16">
+      <c r="AM16">
+        <v>290</v>
+      </c>
+      <c r="AN16">
+        <v>32</v>
+      </c>
+      <c r="AO16">
+        <v>210</v>
+      </c>
+      <c r="AP16">
+        <v>6</v>
+      </c>
+      <c r="AQ16">
+        <v>4.8</v>
+      </c>
+      <c r="AR16">
+        <v>23</v>
+      </c>
+      <c r="AS16">
+        <v>7.4</v>
+      </c>
+      <c r="AT16">
+        <v>3.5</v>
+      </c>
+      <c r="AU16">
+        <v>5.9</v>
+      </c>
+      <c r="AV16">
+        <v>16.5</v>
+      </c>
+      <c r="AW16">
+        <v>7.2</v>
+      </c>
+      <c r="AX16">
+        <v>4.8</v>
+      </c>
+      <c r="AY16">
+        <v>4.8</v>
+      </c>
+      <c r="AZ16">
+        <v>18</v>
+      </c>
+      <c r="BA16">
+        <v>7.4</v>
+      </c>
+      <c r="BB16">
+        <v>18</v>
+      </c>
+      <c r="BC16">
+        <v>21</v>
+      </c>
+      <c r="BD16">
+        <v>7</v>
+      </c>
+      <c r="BE16">
+        <v>7.6</v>
+      </c>
+      <c r="BF16">
+        <v>19.5</v>
+      </c>
+      <c r="BG16">
+        <v>7.4</v>
+      </c>
+      <c r="BH16">
+        <v>2.84</v>
+      </c>
+      <c r="BI16">
+        <v>2.18</v>
+      </c>
+      <c r="BJ16">
+        <v>14.5</v>
+      </c>
+      <c r="BK16">
+        <v>4.3</v>
+      </c>
+      <c r="BL16">
+        <v>1000</v>
+      </c>
+      <c r="BM16">
+        <v>6</v>
+      </c>
+      <c r="BN16">
+        <v>5</v>
+      </c>
+      <c r="BO16">
+        <v>3.6</v>
+      </c>
+      <c r="BP16">
+        <v>21</v>
+      </c>
+      <c r="BQ16">
+        <v>4.8</v>
+      </c>
+      <c r="BR16">
+        <v>1000</v>
+      </c>
+      <c r="BS16">
+        <v>5.6</v>
+      </c>
+      <c r="BT16">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BU16">
+        <v>3.7</v>
+      </c>
+      <c r="BV16">
+        <v>1000</v>
+      </c>
+      <c r="BW16">
+        <v>5.7</v>
+      </c>
+      <c r="BX16">
+        <v>1000</v>
+      </c>
+      <c r="BY16">
+        <v>5.9</v>
+      </c>
+      <c r="BZ16">
+        <v>1000</v>
+      </c>
+      <c r="CA16">
+        <v>5.7</v>
+      </c>
+      <c r="CB16" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="17" spans="1:80">
+      <c r="A17" t="s">
+        <v>80</v>
+      </c>
+      <c r="B17" t="s">
+        <v>88</v>
+      </c>
+      <c r="C17" t="s">
+        <v>104</v>
+      </c>
+      <c r="D17" t="s">
+        <v>120</v>
+      </c>
+      <c r="E17" t="s">
+        <v>136</v>
+      </c>
+      <c r="F17">
         <v>2.8</v>
       </c>
-      <c r="G16">
-        <v>3.75</v>
-      </c>
-      <c r="H16">
-        <v>2</v>
-      </c>
-      <c r="I16">
+      <c r="G17">
+        <v>3.35</v>
+      </c>
+      <c r="H17">
+        <v>2.14</v>
+      </c>
+      <c r="I17">
         <v>2.5</v>
       </c>
-      <c r="J16">
+      <c r="J17">
         <v>3.8</v>
       </c>
-      <c r="K16">
+      <c r="K17">
         <v>4.2</v>
       </c>
-      <c r="L16">
+      <c r="L17">
         <v>1.23</v>
       </c>
-      <c r="M16">
-        <v>1.01</v>
-      </c>
-      <c r="N16">
-        <v>1.1</v>
-      </c>
-      <c r="O16">
-        <v>1.16</v>
-      </c>
-      <c r="P16">
-        <v>2.58</v>
-      </c>
-      <c r="Q16">
-        <v>1.5</v>
-      </c>
-      <c r="R16">
+      <c r="M17">
+        <v>1.01</v>
+      </c>
+      <c r="N17">
+        <v>3.45</v>
+      </c>
+      <c r="O17">
+        <v>1.17</v>
+      </c>
+      <c r="P17">
+        <v>2.48</v>
+      </c>
+      <c r="Q17">
+        <v>1.51</v>
+      </c>
+      <c r="R17">
         <v>1.53</v>
       </c>
-      <c r="S16">
-        <v>2.08</v>
-      </c>
-      <c r="T16">
-        <v>1.12</v>
-      </c>
-      <c r="U16">
-        <v>2.56</v>
-      </c>
-      <c r="V16">
+      <c r="S17">
+        <v>2.1</v>
+      </c>
+      <c r="T17">
+        <v>1.43</v>
+      </c>
+      <c r="U17">
+        <v>2.36</v>
+      </c>
+      <c r="V17">
         <v>1.66</v>
       </c>
-      <c r="W16">
-        <v>1.37</v>
-      </c>
-      <c r="X16">
+      <c r="W17">
+        <v>1.42</v>
+      </c>
+      <c r="X17">
+        <v>28</v>
+      </c>
+      <c r="Y17">
+        <v>17</v>
+      </c>
+      <c r="Z17">
+        <v>20</v>
+      </c>
+      <c r="AA17">
+        <v>34</v>
+      </c>
+      <c r="AB17">
+        <v>20</v>
+      </c>
+      <c r="AC17">
+        <v>11</v>
+      </c>
+      <c r="AD17">
+        <v>13</v>
+      </c>
+      <c r="AE17">
+        <v>23</v>
+      </c>
+      <c r="AF17">
+        <v>27</v>
+      </c>
+      <c r="AG17">
+        <v>15.5</v>
+      </c>
+      <c r="AH17">
+        <v>16</v>
+      </c>
+      <c r="AI17">
         <v>29</v>
       </c>
-      <c r="Y16">
-        <v>17</v>
-      </c>
-      <c r="Z16">
-        <v>20</v>
-      </c>
-      <c r="AA16">
-        <v>34</v>
-      </c>
-      <c r="AB16">
-        <v>20</v>
-      </c>
-      <c r="AC16">
-        <v>11</v>
-      </c>
-      <c r="AD16">
-        <v>13</v>
-      </c>
-      <c r="AE16">
-        <v>23</v>
-      </c>
-      <c r="AF16">
+      <c r="AJ17">
+        <v>60</v>
+      </c>
+      <c r="AK17">
+        <v>32</v>
+      </c>
+      <c r="AL17">
+        <v>36</v>
+      </c>
+      <c r="AM17">
+        <v>65</v>
+      </c>
+      <c r="AN17">
+        <v>19</v>
+      </c>
+      <c r="AO17">
+        <v>12</v>
+      </c>
+      <c r="AP17">
+        <v>5.7</v>
+      </c>
+      <c r="AQ17">
+        <v>5.1</v>
+      </c>
+      <c r="AR17">
+        <v>5.3</v>
+      </c>
+      <c r="AS17">
+        <v>6</v>
+      </c>
+      <c r="AT17">
+        <v>5.3</v>
+      </c>
+      <c r="AU17">
+        <v>4.3</v>
+      </c>
+      <c r="AV17">
+        <v>4.6</v>
+      </c>
+      <c r="AW17">
+        <v>5.5</v>
+      </c>
+      <c r="AX17">
+        <v>5.7</v>
+      </c>
+      <c r="AY17">
+        <v>4.9</v>
+      </c>
+      <c r="AZ17">
+        <v>5</v>
+      </c>
+      <c r="BA17">
+        <v>5.8</v>
+      </c>
+      <c r="BB17">
+        <v>6.4</v>
+      </c>
+      <c r="BC17">
+        <v>5.9</v>
+      </c>
+      <c r="BD17">
+        <v>6</v>
+      </c>
+      <c r="BE17">
+        <v>6.4</v>
+      </c>
+      <c r="BF17">
+        <v>5.2</v>
+      </c>
+      <c r="BG17">
+        <v>4.5</v>
+      </c>
+      <c r="BH17">
+        <v>5.4</v>
+      </c>
+      <c r="BI17">
+        <v>2.6</v>
+      </c>
+      <c r="BJ17">
+        <v>10.5</v>
+      </c>
+      <c r="BK17">
+        <v>3.4</v>
+      </c>
+      <c r="BL17">
+        <v>85</v>
+      </c>
+      <c r="BM17">
+        <v>4.7</v>
+      </c>
+      <c r="BN17">
+        <v>7.2</v>
+      </c>
+      <c r="BO17">
+        <v>2.96</v>
+      </c>
+      <c r="BP17">
+        <v>25</v>
+      </c>
+      <c r="BQ17">
+        <v>4.2</v>
+      </c>
+      <c r="BR17">
         <v>28</v>
       </c>
-      <c r="AG16">
-        <v>15</v>
-      </c>
-      <c r="AH16">
-        <v>16</v>
-      </c>
-      <c r="AI16">
-        <v>29</v>
-      </c>
-      <c r="AJ16">
-        <v>60</v>
-      </c>
-      <c r="AK16">
-        <v>32</v>
-      </c>
-      <c r="AL16">
-        <v>34</v>
-      </c>
-      <c r="AM16">
-        <v>65</v>
-      </c>
-      <c r="AN16">
-        <v>19</v>
-      </c>
-      <c r="AO16">
-        <v>12</v>
-      </c>
-      <c r="AP16">
-        <v>5.8</v>
-      </c>
-      <c r="AQ16">
-        <v>5.1</v>
-      </c>
-      <c r="AR16">
-        <v>5.3</v>
-      </c>
-      <c r="AS16">
-        <v>6</v>
-      </c>
-      <c r="AT16">
-        <v>5.3</v>
-      </c>
-      <c r="AU16">
-        <v>4.4</v>
-      </c>
-      <c r="AV16">
-        <v>4.7</v>
-      </c>
-      <c r="AW16">
-        <v>5.5</v>
-      </c>
-      <c r="AX16">
-        <v>5.8</v>
-      </c>
-      <c r="AY16">
-        <v>4.9</v>
-      </c>
-      <c r="AZ16">
-        <v>5</v>
-      </c>
-      <c r="BA16">
-        <v>5.8</v>
-      </c>
-      <c r="BB16">
-        <v>6.4</v>
-      </c>
-      <c r="BC16">
-        <v>5.9</v>
-      </c>
-      <c r="BD16">
-        <v>6</v>
-      </c>
-      <c r="BE16">
-        <v>6.6</v>
-      </c>
-      <c r="BF16">
-        <v>5.3</v>
-      </c>
-      <c r="BG16">
-        <v>4.5</v>
-      </c>
-      <c r="BH16">
-        <v>5.4</v>
-      </c>
-      <c r="BI16">
-        <v>2.8</v>
-      </c>
-      <c r="BJ16">
-        <v>10.5</v>
-      </c>
-      <c r="BK16">
-        <v>3.75</v>
-      </c>
-      <c r="BL16">
-        <v>85</v>
-      </c>
-      <c r="BM16">
-        <v>5.4</v>
-      </c>
-      <c r="BN16">
-        <v>7.2</v>
-      </c>
-      <c r="BO16">
-        <v>3.2</v>
-      </c>
-      <c r="BP16">
-        <v>22</v>
-      </c>
-      <c r="BQ16">
-        <v>4.6</v>
-      </c>
-      <c r="BR16">
-        <v>28</v>
-      </c>
-      <c r="BS16">
-        <v>4.8</v>
-      </c>
-      <c r="BT16">
-        <v>6.2</v>
-      </c>
-      <c r="BU16">
-        <v>3</v>
-      </c>
-      <c r="BV16">
-        <v>17.5</v>
-      </c>
-      <c r="BW16">
-        <v>4.3</v>
-      </c>
-      <c r="BX16">
-        <v>24</v>
-      </c>
-      <c r="BY16">
-        <v>4.7</v>
-      </c>
-      <c r="BZ16">
+      <c r="BS17">
+        <v>4.2</v>
+      </c>
+      <c r="BT17">
+        <v>6.8</v>
+      </c>
+      <c r="BU17">
+        <v>2.88</v>
+      </c>
+      <c r="BV17">
+        <v>18</v>
+      </c>
+      <c r="BW17">
+        <v>3.9</v>
+      </c>
+      <c r="BX17">
+        <v>27</v>
+      </c>
+      <c r="BY17">
+        <v>4.2</v>
+      </c>
+      <c r="BZ17">
         <v>0</v>
       </c>
-      <c r="CA16">
+      <c r="CA17">
         <v>0</v>
       </c>
-      <c r="CB16" t="s">
-        <v>133</v>
+      <c r="CB17" t="s">
+        <v>137</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-06.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-06.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="145">
   <si>
     <t>League</t>
   </si>
@@ -277,6 +277,9 @@
     <t>Venezuelan Primera Division</t>
   </si>
   <si>
+    <t>Peruvian Primera Division</t>
+  </si>
+  <si>
     <t>Ecuadorian Serie B</t>
   </si>
   <si>
@@ -346,6 +349,9 @@
     <t>Once Caldas</t>
   </si>
   <si>
+    <t>Universitario de Vinto</t>
+  </si>
+  <si>
     <t>Real Soacha Cundinamarca FC</t>
   </si>
   <si>
@@ -358,9 +364,15 @@
     <t>Estudiantes de Merida</t>
   </si>
   <si>
+    <t>Alianza Atletico</t>
+  </si>
+  <si>
     <t>Independiente Juniors</t>
   </si>
   <si>
+    <t>Atletico Rojiblanco</t>
+  </si>
+  <si>
     <t>Atletico FC Cali</t>
   </si>
   <si>
@@ -394,6 +406,9 @@
     <t>America de Cali S.A</t>
   </si>
   <si>
+    <t>Real Potosi</t>
+  </si>
+  <si>
     <t>Boca Juniors de Cali</t>
   </si>
   <si>
@@ -406,9 +421,15 @@
     <t>Zamora FC</t>
   </si>
   <si>
+    <t>Cienciano</t>
+  </si>
+  <si>
     <t>22 de Julio FC</t>
   </si>
   <si>
+    <t>Deportivo Santo Domingo</t>
+  </si>
+  <si>
     <t>Real Santander</t>
   </si>
   <si>
@@ -427,7 +448,7 @@
     <t>Always Ready</t>
   </si>
   <si>
-    <t>2026-08-05 14:41:37</t>
+    <t>2026-08-05 16:52:06</t>
   </si>
 </sst>
 </file>
@@ -759,7 +780,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB17"/>
+  <dimension ref="A1:CB20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -1009,37 +1030,37 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E2" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="F2">
+        <v>1.15</v>
+      </c>
+      <c r="G2">
+        <v>1.16</v>
+      </c>
+      <c r="H2">
+        <v>19.5</v>
+      </c>
+      <c r="I2">
+        <v>25</v>
+      </c>
+      <c r="J2">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="K2">
+        <v>12.5</v>
+      </c>
+      <c r="L2">
         <v>1.13</v>
-      </c>
-      <c r="G2">
-        <v>1.15</v>
-      </c>
-      <c r="H2">
-        <v>23</v>
-      </c>
-      <c r="I2">
-        <v>32</v>
-      </c>
-      <c r="J2">
-        <v>11</v>
-      </c>
-      <c r="K2">
-        <v>14.5</v>
-      </c>
-      <c r="L2">
-        <v>1.14</v>
       </c>
       <c r="M2">
         <v>1.01</v>
@@ -1051,190 +1072,190 @@
         <v>1.06</v>
       </c>
       <c r="P2">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="Q2">
         <v>1.22</v>
       </c>
       <c r="R2">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="S2">
-        <v>1.54</v>
+        <v>1.51</v>
       </c>
       <c r="T2">
-        <v>1.87</v>
+        <v>1.77</v>
       </c>
       <c r="U2">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="V2">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="W2">
-        <v>7.6</v>
+        <v>6.8</v>
       </c>
       <c r="X2">
-        <v>950</v>
+        <v>95</v>
       </c>
       <c r="Y2">
         <v>950</v>
       </c>
       <c r="Z2">
-        <v>350</v>
+        <v>330</v>
       </c>
       <c r="AA2">
         <v>1000</v>
       </c>
       <c r="AB2">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AC2">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AD2">
-        <v>95</v>
+        <v>950</v>
       </c>
       <c r="AE2">
-        <v>410</v>
+        <v>330</v>
       </c>
       <c r="AF2">
         <v>14.5</v>
       </c>
       <c r="AG2">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AH2">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AI2">
-        <v>210</v>
+        <v>170</v>
       </c>
       <c r="AJ2">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AK2">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AL2">
         <v>40</v>
       </c>
       <c r="AM2">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AN2">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="AO2">
-        <v>320</v>
+        <v>230</v>
       </c>
       <c r="AP2">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="AQ2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AR2">
-        <v>7.2</v>
+        <v>8.4</v>
       </c>
       <c r="AS2">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="AT2">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AU2">
-        <v>6.4</v>
+        <v>23</v>
       </c>
       <c r="AV2">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="AW2">
-        <v>7.2</v>
+        <v>8.4</v>
       </c>
       <c r="AX2">
         <v>11</v>
       </c>
       <c r="AY2">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AZ2">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="BA2">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB2">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BC2">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BD2">
-        <v>6.4</v>
+        <v>7.6</v>
       </c>
       <c r="BE2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BF2">
-        <v>1.77</v>
+        <v>1.95</v>
       </c>
       <c r="BG2">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH2">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="BI2">
-        <v>1.04</v>
+        <v>6</v>
       </c>
       <c r="BJ2">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="BK2">
-        <v>1.04</v>
+        <v>5.6</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>1.04</v>
+        <v>8.6</v>
       </c>
       <c r="BN2">
-        <v>1000</v>
+        <v>4.9</v>
       </c>
       <c r="BO2">
-        <v>1.04</v>
+        <v>3.75</v>
       </c>
       <c r="BP2">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="BQ2">
-        <v>1.04</v>
+        <v>4.7</v>
       </c>
       <c r="BR2">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="BS2">
-        <v>1.04</v>
+        <v>6</v>
       </c>
       <c r="BT2">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="BU2">
-        <v>1.04</v>
+        <v>6.8</v>
       </c>
       <c r="BV2">
         <v>1000</v>
       </c>
       <c r="BW2">
-        <v>1.04</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX2">
         <v>1000</v>
       </c>
       <c r="BY2">
-        <v>1.04</v>
+        <v>8.4</v>
       </c>
       <c r="BZ2">
         <v>0</v>
@@ -1243,7 +1264,7 @@
         <v>0</v>
       </c>
       <c r="CB2" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1251,16 +1272,16 @@
         <v>81</v>
       </c>
       <c r="B3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E3" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="F3">
         <v>2.64</v>
@@ -1269,7 +1290,7 @@
         <v>2.68</v>
       </c>
       <c r="H3">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="I3">
         <v>3.85</v>
@@ -1278,34 +1299,34 @@
         <v>2.76</v>
       </c>
       <c r="K3">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="L3">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="M3">
         <v>1.21</v>
       </c>
       <c r="N3">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="O3">
         <v>1.88</v>
       </c>
       <c r="P3">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="Q3">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="R3">
         <v>1.11</v>
       </c>
       <c r="S3">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="T3">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="U3">
         <v>1.55</v>
@@ -1314,7 +1335,7 @@
         <v>1.35</v>
       </c>
       <c r="W3">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="X3">
         <v>5.8</v>
@@ -1335,7 +1356,7 @@
         <v>7</v>
       </c>
       <c r="AD3">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AE3">
         <v>90</v>
@@ -1383,7 +1404,7 @@
         <v>60</v>
       </c>
       <c r="AT3">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="AU3">
         <v>6.6</v>
@@ -1410,7 +1431,7 @@
         <v>38</v>
       </c>
       <c r="BC3">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BD3">
         <v>70</v>
@@ -1422,7 +1443,7 @@
         <v>32</v>
       </c>
       <c r="BG3">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="BH3">
         <v>1000</v>
@@ -1485,7 +1506,7 @@
         <v>1.04</v>
       </c>
       <c r="CB3" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1493,94 +1514,94 @@
         <v>82</v>
       </c>
       <c r="B4" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C4" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D4" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E4" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="F4">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="G4">
         <v>3.2</v>
       </c>
       <c r="H4">
-        <v>2.72</v>
+        <v>2.8</v>
       </c>
       <c r="I4">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="J4">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="K4">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="L4">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="M4">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="N4">
-        <v>2.82</v>
+        <v>2.68</v>
       </c>
       <c r="O4">
+        <v>1.55</v>
+      </c>
+      <c r="P4">
+        <v>1.56</v>
+      </c>
+      <c r="Q4">
+        <v>2.7</v>
+      </c>
+      <c r="R4">
+        <v>1.2</v>
+      </c>
+      <c r="S4">
+        <v>5.4</v>
+      </c>
+      <c r="T4">
+        <v>2.1</v>
+      </c>
+      <c r="U4">
+        <v>1.81</v>
+      </c>
+      <c r="V4">
         <v>1.51</v>
-      </c>
-      <c r="P4">
-        <v>1.59</v>
-      </c>
-      <c r="Q4">
-        <v>2.58</v>
-      </c>
-      <c r="R4">
-        <v>1.22</v>
-      </c>
-      <c r="S4">
-        <v>5.1</v>
-      </c>
-      <c r="T4">
-        <v>2.02</v>
-      </c>
-      <c r="U4">
-        <v>1.86</v>
-      </c>
-      <c r="V4">
-        <v>1.52</v>
       </c>
       <c r="W4">
         <v>1.45</v>
       </c>
       <c r="X4">
-        <v>9.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="Y4">
         <v>8.6</v>
       </c>
       <c r="Z4">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="AA4">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="AB4">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AC4">
         <v>7</v>
       </c>
       <c r="AD4">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="AE4">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="AF4">
         <v>32</v>
@@ -1589,52 +1610,52 @@
         <v>14.5</v>
       </c>
       <c r="AH4">
-        <v>23</v>
+        <v>950</v>
       </c>
       <c r="AI4">
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="AJ4">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AK4">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="AL4">
-        <v>85</v>
+        <v>110</v>
       </c>
       <c r="AM4">
         <v>190</v>
       </c>
       <c r="AN4">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AO4">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AP4">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AQ4">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AR4">
         <v>14.5</v>
       </c>
       <c r="AS4">
-        <v>28</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT4">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AU4">
         <v>6.2</v>
       </c>
       <c r="AV4">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AW4">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="AX4">
         <v>16.5</v>
@@ -1643,34 +1664,34 @@
         <v>12</v>
       </c>
       <c r="AZ4">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BA4">
-        <v>42</v>
+        <v>8.6</v>
       </c>
       <c r="BB4">
-        <v>9.6</v>
+        <v>8</v>
       </c>
       <c r="BC4">
-        <v>29</v>
+        <v>7.8</v>
       </c>
       <c r="BD4">
-        <v>42</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE4">
-        <v>10</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF4">
-        <v>9.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="BG4">
-        <v>9.4</v>
+        <v>13</v>
       </c>
       <c r="BH4">
-        <v>2.78</v>
+        <v>2.7</v>
       </c>
       <c r="BI4">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="BJ4">
         <v>11</v>
@@ -1682,7 +1703,7 @@
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="BN4">
         <v>5.9</v>
@@ -1691,16 +1712,16 @@
         <v>4.5</v>
       </c>
       <c r="BP4">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="BQ4">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BR4">
         <v>1000</v>
       </c>
       <c r="BS4">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BT4">
         <v>5.6</v>
@@ -1709,25 +1730,25 @@
         <v>4.3</v>
       </c>
       <c r="BV4">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BW4">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BX4">
         <v>1000</v>
       </c>
       <c r="BY4">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BZ4">
         <v>1000</v>
       </c>
       <c r="CA4">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="CB4" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1735,25 +1756,25 @@
         <v>82</v>
       </c>
       <c r="B5" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C5" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D5" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E5" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="F5">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="G5">
         <v>1.81</v>
       </c>
       <c r="H5">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="I5">
         <v>4.8</v>
@@ -1768,7 +1789,7 @@
         <v>1.3</v>
       </c>
       <c r="M5">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N5">
         <v>5.5</v>
@@ -1777,37 +1798,37 @@
         <v>1.2</v>
       </c>
       <c r="P5">
-        <v>2.52</v>
+        <v>2.58</v>
       </c>
       <c r="Q5">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="R5">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="S5">
-        <v>2.52</v>
+        <v>2.48</v>
       </c>
       <c r="T5">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="U5">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="V5">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="W5">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="X5">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="Y5">
         <v>24</v>
       </c>
       <c r="Z5">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AA5">
         <v>190</v>
@@ -1819,7 +1840,7 @@
         <v>11</v>
       </c>
       <c r="AD5">
-        <v>23</v>
+        <v>19.5</v>
       </c>
       <c r="AE5">
         <v>65</v>
@@ -1846,16 +1867,16 @@
         <v>36</v>
       </c>
       <c r="AM5">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AN5">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AO5">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AP5">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AQ5">
         <v>20</v>
@@ -1864,7 +1885,7 @@
         <v>30</v>
       </c>
       <c r="AS5">
-        <v>9.199999999999999</v>
+        <v>60</v>
       </c>
       <c r="AT5">
         <v>10</v>
@@ -1876,13 +1897,13 @@
         <v>16.5</v>
       </c>
       <c r="AW5">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AX5">
         <v>11</v>
       </c>
       <c r="AY5">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ5">
         <v>14.5</v>
@@ -1897,7 +1918,7 @@
         <v>13.5</v>
       </c>
       <c r="BD5">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BE5">
         <v>55</v>
@@ -1924,13 +1945,13 @@
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BN5">
         <v>4.9</v>
       </c>
       <c r="BO5">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="BP5">
         <v>11.5</v>
@@ -1942,7 +1963,7 @@
         <v>21</v>
       </c>
       <c r="BS5">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BT5">
         <v>8.800000000000001</v>
@@ -1951,7 +1972,7 @@
         <v>5</v>
       </c>
       <c r="BV5">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BW5">
         <v>8.800000000000001</v>
@@ -1969,7 +1990,7 @@
         <v>6.4</v>
       </c>
       <c r="CB5" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -1977,28 +1998,28 @@
         <v>83</v>
       </c>
       <c r="B6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D6" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E6" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="F6">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="G6">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="H6">
         <v>3.75</v>
       </c>
       <c r="I6">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="J6">
         <v>3.4</v>
@@ -2016,10 +2037,10 @@
         <v>3.4</v>
       </c>
       <c r="O6">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="P6">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="Q6">
         <v>2.2</v>
@@ -2037,28 +2058,28 @@
         <v>2</v>
       </c>
       <c r="V6">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="W6">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="X6">
         <v>12</v>
       </c>
       <c r="Y6">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Z6">
         <v>27</v>
       </c>
       <c r="AA6">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AB6">
         <v>9</v>
       </c>
       <c r="AC6">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AD6">
         <v>16</v>
@@ -2067,7 +2088,7 @@
         <v>55</v>
       </c>
       <c r="AF6">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AG6">
         <v>11.5</v>
@@ -2088,13 +2109,13 @@
         <v>46</v>
       </c>
       <c r="AM6">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="AN6">
         <v>23</v>
       </c>
       <c r="AO6">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AP6">
         <v>10</v>
@@ -2130,7 +2151,7 @@
         <v>17</v>
       </c>
       <c r="BA6">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="BB6">
         <v>24</v>
@@ -2139,10 +2160,10 @@
         <v>22</v>
       </c>
       <c r="BD6">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BE6">
-        <v>9.800000000000001</v>
+        <v>90</v>
       </c>
       <c r="BF6">
         <v>18</v>
@@ -2160,7 +2181,7 @@
         <v>10.5</v>
       </c>
       <c r="BK6">
-        <v>5.3</v>
+        <v>7.4</v>
       </c>
       <c r="BL6">
         <v>1000</v>
@@ -2172,7 +2193,7 @@
         <v>5.1</v>
       </c>
       <c r="BO6">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="BP6">
         <v>17.5</v>
@@ -2211,240 +2232,240 @@
         <v>8.199999999999999</v>
       </c>
       <c r="CB6" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
     </row>
     <row r="7" spans="1:80">
       <c r="A7" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="B7" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C7" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D7" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E7" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="F7">
-        <v>1.83</v>
+        <v>2.06</v>
       </c>
       <c r="G7">
-        <v>2.04</v>
+        <v>2.26</v>
       </c>
       <c r="H7">
-        <v>5.1</v>
+        <v>3.3</v>
       </c>
       <c r="I7">
-        <v>6.4</v>
+        <v>3.8</v>
       </c>
       <c r="J7">
-        <v>3.1</v>
+        <v>1.03</v>
       </c>
       <c r="K7">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="L7">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="M7">
-        <v>1.12</v>
+        <v>1.01</v>
       </c>
       <c r="N7">
-        <v>2.46</v>
+        <v>2.98</v>
       </c>
       <c r="O7">
+        <v>1.22</v>
+      </c>
+      <c r="P7">
+        <v>2.28</v>
+      </c>
+      <c r="Q7">
+        <v>1.69</v>
+      </c>
+      <c r="R7">
+        <v>1.48</v>
+      </c>
+      <c r="S7">
+        <v>2.52</v>
+      </c>
+      <c r="T7">
         <v>1.56</v>
       </c>
-      <c r="P7">
-        <v>1.48</v>
-      </c>
-      <c r="Q7">
-        <v>2.66</v>
-      </c>
-      <c r="R7">
-        <v>1.15</v>
-      </c>
-      <c r="S7">
-        <v>5.2</v>
-      </c>
-      <c r="T7">
-        <v>2.14</v>
-      </c>
       <c r="U7">
-        <v>1.57</v>
+        <v>2.36</v>
       </c>
       <c r="V7">
-        <v>1.19</v>
+        <v>1.36</v>
       </c>
       <c r="W7">
-        <v>1.96</v>
+        <v>1.79</v>
       </c>
       <c r="X7">
-        <v>9.6</v>
+        <v>21</v>
       </c>
       <c r="Y7">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="Z7">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AA7">
-        <v>220</v>
+        <v>1000</v>
       </c>
       <c r="AB7">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="AC7">
-        <v>9</v>
+        <v>17.5</v>
       </c>
       <c r="AD7">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AE7">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AF7">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AG7">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="AH7">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AI7">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AJ7">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AK7">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AL7">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AM7">
-        <v>300</v>
+        <v>1000</v>
       </c>
       <c r="AN7">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AO7">
-        <v>250</v>
+        <v>1000</v>
       </c>
       <c r="AP7">
         <v>6.4</v>
       </c>
       <c r="AQ7">
-        <v>11</v>
+        <v>1.22</v>
       </c>
       <c r="AR7">
-        <v>4.7</v>
+        <v>1.22</v>
       </c>
       <c r="AS7">
-        <v>5.1</v>
+        <v>1.22</v>
       </c>
       <c r="AT7">
-        <v>4.8</v>
+        <v>6.4</v>
       </c>
       <c r="AU7">
-        <v>6.6</v>
+        <v>1.14</v>
       </c>
       <c r="AV7">
-        <v>18.5</v>
+        <v>1.22</v>
       </c>
       <c r="AW7">
-        <v>5</v>
+        <v>1.22</v>
       </c>
       <c r="AX7">
-        <v>7.8</v>
+        <v>1.22</v>
       </c>
       <c r="AY7">
-        <v>9.6</v>
+        <v>5.4</v>
       </c>
       <c r="AZ7">
-        <v>21</v>
+        <v>1.22</v>
       </c>
       <c r="BA7">
-        <v>5.1</v>
+        <v>1.22</v>
       </c>
       <c r="BB7">
-        <v>19.5</v>
+        <v>1.22</v>
       </c>
       <c r="BC7">
-        <v>4.5</v>
+        <v>1.22</v>
       </c>
       <c r="BD7">
-        <v>4.9</v>
+        <v>1.22</v>
       </c>
       <c r="BE7">
-        <v>5.1</v>
+        <v>1.22</v>
       </c>
       <c r="BF7">
-        <v>18.5</v>
+        <v>1.22</v>
       </c>
       <c r="BG7">
-        <v>5.1</v>
+        <v>1.22</v>
       </c>
       <c r="BH7">
-        <v>2.94</v>
+        <v>1000</v>
       </c>
       <c r="BI7">
-        <v>2.26</v>
+        <v>1.01</v>
       </c>
       <c r="BJ7">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="BK7">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="BL7">
         <v>1000</v>
       </c>
       <c r="BM7">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="BN7">
-        <v>4.8</v>
+        <v>1000</v>
       </c>
       <c r="BO7">
-        <v>2.68</v>
+        <v>1.01</v>
       </c>
       <c r="BP7">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="BQ7">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="BR7">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="BS7">
-        <v>5.4</v>
+        <v>1.01</v>
       </c>
       <c r="BT7">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="BU7">
-        <v>3.8</v>
+        <v>1.01</v>
       </c>
       <c r="BV7">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="BW7">
-        <v>5.6</v>
+        <v>1.01</v>
       </c>
       <c r="BX7">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="BY7">
-        <v>5.8</v>
+        <v>1.01</v>
       </c>
       <c r="BZ7">
         <v>0</v>
@@ -2453,491 +2474,491 @@
         <v>0</v>
       </c>
       <c r="CB7" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
     </row>
     <row r="8" spans="1:80">
       <c r="A8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B8" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C8" t="s">
         <v>95</v>
       </c>
       <c r="D8" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E8" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="F8">
-        <v>1.56</v>
+        <v>1.86</v>
       </c>
       <c r="G8">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="H8">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="I8">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="J8">
-        <v>4.8</v>
+        <v>3.1</v>
       </c>
       <c r="K8">
-        <v>5.8</v>
+        <v>3.5</v>
       </c>
       <c r="L8">
-        <v>1.01</v>
+        <v>1.52</v>
       </c>
       <c r="M8">
-        <v>1.02</v>
+        <v>1.13</v>
       </c>
       <c r="N8">
-        <v>7.6</v>
+        <v>2.46</v>
       </c>
       <c r="O8">
-        <v>1.11</v>
+        <v>1.57</v>
       </c>
       <c r="P8">
-        <v>3.35</v>
+        <v>1.49</v>
       </c>
       <c r="Q8">
-        <v>1.33</v>
+        <v>2.7</v>
       </c>
       <c r="R8">
-        <v>2.02</v>
+        <v>1.17</v>
       </c>
       <c r="S8">
-        <v>1.8</v>
+        <v>5.6</v>
       </c>
       <c r="T8">
-        <v>1.45</v>
+        <v>2.32</v>
       </c>
       <c r="U8">
-        <v>1.11</v>
+        <v>1.65</v>
       </c>
       <c r="V8">
         <v>1.2</v>
       </c>
       <c r="W8">
-        <v>2.38</v>
+        <v>2</v>
       </c>
       <c r="X8">
-        <v>950</v>
+        <v>9.6</v>
       </c>
       <c r="Y8">
-        <v>950</v>
+        <v>15.5</v>
       </c>
       <c r="Z8">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="AA8">
-        <v>120</v>
+        <v>220</v>
       </c>
       <c r="AB8">
-        <v>21</v>
+        <v>6.4</v>
       </c>
       <c r="AC8">
-        <v>15.5</v>
+        <v>9</v>
       </c>
       <c r="AD8">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="AE8">
-        <v>55</v>
+        <v>140</v>
       </c>
       <c r="AF8">
+        <v>11.5</v>
+      </c>
+      <c r="AG8">
+        <v>13</v>
+      </c>
+      <c r="AH8">
+        <v>34</v>
+      </c>
+      <c r="AI8">
+        <v>160</v>
+      </c>
+      <c r="AJ8">
+        <v>27</v>
+      </c>
+      <c r="AK8">
+        <v>34</v>
+      </c>
+      <c r="AL8">
+        <v>80</v>
+      </c>
+      <c r="AM8">
+        <v>300</v>
+      </c>
+      <c r="AN8">
+        <v>29</v>
+      </c>
+      <c r="AO8">
+        <v>250</v>
+      </c>
+      <c r="AP8">
+        <v>6.4</v>
+      </c>
+      <c r="AQ8">
+        <v>11</v>
+      </c>
+      <c r="AR8">
+        <v>5</v>
+      </c>
+      <c r="AS8">
+        <v>5.5</v>
+      </c>
+      <c r="AT8">
+        <v>4.8</v>
+      </c>
+      <c r="AU8">
+        <v>6.6</v>
+      </c>
+      <c r="AV8">
+        <v>20</v>
+      </c>
+      <c r="AW8">
+        <v>5.4</v>
+      </c>
+      <c r="AX8">
+        <v>8.4</v>
+      </c>
+      <c r="AY8">
+        <v>9.6</v>
+      </c>
+      <c r="AZ8">
+        <v>4.8</v>
+      </c>
+      <c r="BA8">
+        <v>5.4</v>
+      </c>
+      <c r="BB8">
         <v>19.5</v>
       </c>
-      <c r="AG8">
-        <v>12.5</v>
-      </c>
-      <c r="AH8">
-        <v>17.5</v>
-      </c>
-      <c r="AI8">
-        <v>42</v>
-      </c>
-      <c r="AJ8">
-        <v>22</v>
-      </c>
-      <c r="AK8">
-        <v>16</v>
-      </c>
-      <c r="AL8">
-        <v>23</v>
-      </c>
-      <c r="AM8">
-        <v>55</v>
-      </c>
-      <c r="AN8">
+      <c r="BC8">
         <v>4.8</v>
       </c>
-      <c r="AO8">
-        <v>32</v>
-      </c>
-      <c r="AP8">
-        <v>6.6</v>
-      </c>
-      <c r="AQ8">
-        <v>6.2</v>
-      </c>
-      <c r="AR8">
-        <v>6.8</v>
-      </c>
-      <c r="AS8">
-        <v>7</v>
-      </c>
-      <c r="AT8">
+      <c r="BD8">
+        <v>5.2</v>
+      </c>
+      <c r="BE8">
         <v>5.5</v>
       </c>
-      <c r="AU8">
-        <v>5.1</v>
-      </c>
-      <c r="AV8">
-        <v>5.7</v>
-      </c>
-      <c r="AW8">
-        <v>6.6</v>
-      </c>
-      <c r="AX8">
+      <c r="BF8">
+        <v>20</v>
+      </c>
+      <c r="BG8">
+        <v>5.5</v>
+      </c>
+      <c r="BH8">
+        <v>2.94</v>
+      </c>
+      <c r="BI8">
+        <v>2.26</v>
+      </c>
+      <c r="BJ8">
+        <v>14.5</v>
+      </c>
+      <c r="BK8">
+        <v>4.3</v>
+      </c>
+      <c r="BL8">
+        <v>1000</v>
+      </c>
+      <c r="BM8">
+        <v>6</v>
+      </c>
+      <c r="BN8">
+        <v>4.8</v>
+      </c>
+      <c r="BO8">
+        <v>2.68</v>
+      </c>
+      <c r="BP8">
+        <v>18</v>
+      </c>
+      <c r="BQ8">
+        <v>4.5</v>
+      </c>
+      <c r="BR8">
+        <v>50</v>
+      </c>
+      <c r="BS8">
         <v>5.4</v>
       </c>
-      <c r="AY8">
-        <v>4.7</v>
-      </c>
-      <c r="AZ8">
-        <v>5.3</v>
-      </c>
-      <c r="BA8">
-        <v>6.4</v>
-      </c>
-      <c r="BB8">
+      <c r="BT8">
+        <v>10</v>
+      </c>
+      <c r="BU8">
+        <v>3.8</v>
+      </c>
+      <c r="BV8">
+        <v>75</v>
+      </c>
+      <c r="BW8">
         <v>5.6</v>
       </c>
-      <c r="BC8">
-        <v>5.1</v>
-      </c>
-      <c r="BD8">
-        <v>5.7</v>
-      </c>
-      <c r="BE8">
-        <v>6.6</v>
-      </c>
-      <c r="BF8">
-        <v>2.94</v>
-      </c>
-      <c r="BG8">
-        <v>6</v>
-      </c>
-      <c r="BH8">
-        <v>6.8</v>
-      </c>
-      <c r="BI8">
-        <v>4.6</v>
-      </c>
-      <c r="BJ8">
-        <v>10</v>
-      </c>
-      <c r="BK8">
-        <v>3.5</v>
-      </c>
-      <c r="BL8">
-        <v>1000</v>
-      </c>
-      <c r="BM8">
-        <v>5</v>
-      </c>
-      <c r="BN8">
-        <v>5.9</v>
-      </c>
-      <c r="BO8">
-        <v>2.82</v>
-      </c>
-      <c r="BP8">
-        <v>11.5</v>
-      </c>
-      <c r="BQ8">
-        <v>3.65</v>
-      </c>
-      <c r="BR8">
-        <v>18.5</v>
-      </c>
-      <c r="BS8">
-        <v>4.2</v>
-      </c>
-      <c r="BT8">
-        <v>11</v>
-      </c>
-      <c r="BU8">
-        <v>3.6</v>
-      </c>
-      <c r="BV8">
-        <v>36</v>
-      </c>
-      <c r="BW8">
-        <v>4.7</v>
-      </c>
       <c r="BX8">
-        <v>34</v>
+        <v>100</v>
       </c>
       <c r="BY8">
-        <v>4.6</v>
+        <v>5.8</v>
       </c>
       <c r="BZ8">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="CA8">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="CB8" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
     </row>
     <row r="9" spans="1:80">
       <c r="A9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B9" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C9" t="s">
         <v>96</v>
       </c>
       <c r="D9" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E9" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="F9">
-        <v>1.04</v>
+        <v>1.57</v>
       </c>
       <c r="G9">
-        <v>990</v>
+        <v>1.69</v>
       </c>
       <c r="H9">
-        <v>1.04</v>
+        <v>4.6</v>
       </c>
       <c r="I9">
-        <v>990</v>
+        <v>5.6</v>
       </c>
       <c r="J9">
-        <v>3.05</v>
+        <v>4.9</v>
       </c>
       <c r="K9">
+        <v>6.2</v>
+      </c>
+      <c r="L9">
+        <v>1.01</v>
+      </c>
+      <c r="M9">
+        <v>1.02</v>
+      </c>
+      <c r="N9">
+        <v>7.6</v>
+      </c>
+      <c r="O9">
+        <v>1.11</v>
+      </c>
+      <c r="P9">
+        <v>3.35</v>
+      </c>
+      <c r="Q9">
+        <v>1.33</v>
+      </c>
+      <c r="R9">
+        <v>2.02</v>
+      </c>
+      <c r="S9">
+        <v>1.82</v>
+      </c>
+      <c r="T9">
+        <v>1.46</v>
+      </c>
+      <c r="U9">
+        <v>2.74</v>
+      </c>
+      <c r="V9">
+        <v>1.21</v>
+      </c>
+      <c r="W9">
+        <v>2.44</v>
+      </c>
+      <c r="X9">
         <v>950</v>
       </c>
-      <c r="L9">
-        <v>1.01</v>
-      </c>
-      <c r="M9">
-        <v>1.08</v>
-      </c>
-      <c r="N9">
-        <v>1.63</v>
-      </c>
-      <c r="O9">
-        <v>1.38</v>
-      </c>
-      <c r="P9">
-        <v>1.25</v>
-      </c>
-      <c r="Q9">
-        <v>1.38</v>
-      </c>
-      <c r="R9">
-        <v>1.19</v>
-      </c>
-      <c r="S9">
-        <v>1.38</v>
-      </c>
-      <c r="T9">
-        <v>1.11</v>
-      </c>
-      <c r="U9">
-        <v>1.11</v>
-      </c>
-      <c r="V9">
-        <v>1.01</v>
-      </c>
-      <c r="W9">
-        <v>1.01</v>
-      </c>
-      <c r="X9">
-        <v>1000</v>
-      </c>
       <c r="Y9">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Z9">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AA9">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AB9">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AC9">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AD9">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AE9">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AF9">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AG9">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH9">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AI9">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AJ9">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AK9">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AL9">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AM9">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AN9">
-        <v>1000</v>
+        <v>4.8</v>
       </c>
       <c r="AO9">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AP9">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AQ9">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AR9">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AS9">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AT9">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="AU9">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="AV9">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AW9">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AX9">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="AY9">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AZ9">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BA9">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BB9">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BC9">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BD9">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="BE9">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BF9">
-        <v>1.01</v>
+        <v>3</v>
       </c>
       <c r="BG9">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BH9">
-        <v>3.45</v>
+        <v>6.8</v>
       </c>
       <c r="BI9">
-        <v>2.44</v>
+        <v>4.7</v>
       </c>
       <c r="BJ9">
-        <v>12.5</v>
+        <v>10</v>
       </c>
       <c r="BK9">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="BL9">
         <v>1000</v>
       </c>
       <c r="BM9">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BN9">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BO9">
-        <v>2.68</v>
+        <v>4.2</v>
       </c>
       <c r="BP9">
-        <v>22</v>
+        <v>11.5</v>
       </c>
       <c r="BQ9">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="BR9">
-        <v>44</v>
+        <v>18.5</v>
       </c>
       <c r="BS9">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="BT9">
-        <v>8.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="BU9">
-        <v>3.1</v>
+        <v>3.65</v>
       </c>
       <c r="BV9">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="BW9">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="BX9">
-        <v>60</v>
+        <v>34</v>
       </c>
       <c r="BY9">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BZ9">
-        <v>44</v>
+        <v>10</v>
       </c>
       <c r="CA9">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="CB9" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
     </row>
     <row r="10" spans="1:80">
@@ -2945,34 +2966,34 @@
         <v>86</v>
       </c>
       <c r="B10" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C10" t="s">
         <v>97</v>
       </c>
       <c r="D10" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E10" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="F10">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="G10">
-        <v>2.9</v>
+        <v>2.78</v>
       </c>
       <c r="H10">
-        <v>2.74</v>
+        <v>2.84</v>
       </c>
       <c r="I10">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="J10">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="K10">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="L10">
         <v>1.35</v>
@@ -2984,19 +3005,19 @@
         <v>3.5</v>
       </c>
       <c r="O10">
+        <v>1.31</v>
+      </c>
+      <c r="P10">
+        <v>1.86</v>
+      </c>
+      <c r="Q10">
+        <v>2</v>
+      </c>
+      <c r="R10">
         <v>1.34</v>
       </c>
-      <c r="P10">
-        <v>1.84</v>
-      </c>
-      <c r="Q10">
-        <v>1.96</v>
-      </c>
-      <c r="R10">
-        <v>1.32</v>
-      </c>
       <c r="S10">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="T10">
         <v>1.75</v>
@@ -3005,25 +3026,25 @@
         <v>2.1</v>
       </c>
       <c r="V10">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="W10">
-        <v>1.52</v>
+        <v>1.56</v>
       </c>
       <c r="X10">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="Y10">
         <v>14</v>
       </c>
       <c r="Z10">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AA10">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AB10">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AC10">
         <v>9.4</v>
@@ -3032,13 +3053,13 @@
         <v>16</v>
       </c>
       <c r="AE10">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="AF10">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AG10">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AH10">
         <v>21</v>
@@ -3047,614 +3068,614 @@
         <v>55</v>
       </c>
       <c r="AJ10">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="AK10">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AL10">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AM10">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AN10">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="AO10">
         <v>36</v>
       </c>
       <c r="AP10">
-        <v>3.35</v>
+        <v>10</v>
       </c>
       <c r="AQ10">
-        <v>3.25</v>
+        <v>10</v>
       </c>
       <c r="AR10">
-        <v>3.55</v>
+        <v>15</v>
       </c>
       <c r="AS10">
-        <v>3.95</v>
+        <v>4.3</v>
       </c>
       <c r="AT10">
-        <v>3.2</v>
+        <v>9</v>
       </c>
       <c r="AU10">
-        <v>2.92</v>
+        <v>5.9</v>
       </c>
       <c r="AV10">
-        <v>3.35</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW10">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="AX10">
-        <v>3.55</v>
+        <v>12.5</v>
       </c>
       <c r="AY10">
-        <v>3.3</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ10">
-        <v>3.5</v>
+        <v>12.5</v>
       </c>
       <c r="BA10">
-        <v>3.95</v>
+        <v>4.3</v>
       </c>
       <c r="BB10">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="BC10">
-        <v>3.85</v>
+        <v>21</v>
       </c>
       <c r="BD10">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="BE10">
+        <v>4.5</v>
+      </c>
+      <c r="BF10">
+        <v>17.5</v>
+      </c>
+      <c r="BG10">
         <v>4.1</v>
-      </c>
-      <c r="BF10">
-        <v>3.8</v>
-      </c>
-      <c r="BG10">
-        <v>3.8</v>
       </c>
       <c r="BH10">
         <v>3.45</v>
       </c>
       <c r="BI10">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="BJ10">
-        <v>9.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="BK10">
+        <v>7.2</v>
+      </c>
+      <c r="BL10">
+        <v>150</v>
+      </c>
+      <c r="BM10">
+        <v>6.2</v>
+      </c>
+      <c r="BN10">
+        <v>6.6</v>
+      </c>
+      <c r="BO10">
+        <v>4.8</v>
+      </c>
+      <c r="BP10">
+        <v>21</v>
+      </c>
+      <c r="BQ10">
         <v>5</v>
       </c>
-      <c r="BL10">
-        <v>1000</v>
-      </c>
-      <c r="BM10">
-        <v>9.6</v>
-      </c>
-      <c r="BN10">
-        <v>5.9</v>
-      </c>
-      <c r="BO10">
-        <v>4.3</v>
-      </c>
-      <c r="BP10">
-        <v>22</v>
-      </c>
-      <c r="BQ10">
-        <v>7</v>
-      </c>
       <c r="BR10">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BS10">
-        <v>8</v>
+        <v>5.7</v>
       </c>
       <c r="BT10">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BU10">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BV10">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="BW10">
-        <v>7.2</v>
+        <v>5.4</v>
       </c>
       <c r="BX10">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="BY10">
-        <v>8.199999999999999</v>
+        <v>5.7</v>
       </c>
       <c r="BZ10">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="CA10">
-        <v>7.6</v>
+        <v>5.6</v>
       </c>
       <c r="CB10" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
     </row>
     <row r="11" spans="1:80">
       <c r="A11" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B11" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C11" t="s">
         <v>98</v>
       </c>
       <c r="D11" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E11" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="F11">
-        <v>1.04</v>
+        <v>2.66</v>
       </c>
       <c r="G11">
-        <v>1000</v>
+        <v>2.9</v>
       </c>
       <c r="H11">
-        <v>1.04</v>
+        <v>2.74</v>
       </c>
       <c r="I11">
-        <v>1000</v>
+        <v>3.1</v>
       </c>
       <c r="J11">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="K11">
-        <v>1000</v>
+        <v>3.7</v>
       </c>
       <c r="L11">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="M11">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="N11">
-        <v>1.26</v>
+        <v>3.5</v>
       </c>
       <c r="O11">
-        <v>1.23</v>
+        <v>1.34</v>
       </c>
       <c r="P11">
-        <v>1.25</v>
+        <v>1.86</v>
       </c>
       <c r="Q11">
-        <v>1.23</v>
+        <v>1.98</v>
       </c>
       <c r="R11">
-        <v>1.18</v>
+        <v>1.32</v>
       </c>
       <c r="S11">
-        <v>1.23</v>
+        <v>3.4</v>
       </c>
       <c r="T11">
-        <v>1.01</v>
+        <v>1.75</v>
       </c>
       <c r="U11">
-        <v>1.01</v>
+        <v>2.1</v>
       </c>
       <c r="V11">
-        <v>1.01</v>
+        <v>1.48</v>
       </c>
       <c r="W11">
-        <v>1.01</v>
+        <v>1.52</v>
       </c>
       <c r="X11">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="Y11">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="Z11">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AA11">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AB11">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AC11">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="AD11">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AE11">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AF11">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AG11">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AH11">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AI11">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AJ11">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AK11">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AL11">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AM11">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AN11">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AO11">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AP11">
-        <v>1.03</v>
+        <v>10</v>
       </c>
       <c r="AQ11">
-        <v>1.03</v>
+        <v>8.4</v>
       </c>
       <c r="AR11">
-        <v>1.03</v>
+        <v>14</v>
       </c>
       <c r="AS11">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AT11">
-        <v>1.03</v>
+        <v>8</v>
       </c>
       <c r="AU11">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="AV11">
-        <v>1.03</v>
+        <v>9.6</v>
       </c>
       <c r="AW11">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="AX11">
-        <v>1.03</v>
+        <v>13</v>
       </c>
       <c r="AY11">
-        <v>1.03</v>
+        <v>9</v>
       </c>
       <c r="AZ11">
-        <v>1.03</v>
+        <v>12.5</v>
       </c>
       <c r="BA11">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="BB11">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="BC11">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="BD11">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="BE11">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="BF11">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="BG11">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BH11">
-        <v>1000</v>
+        <v>3.45</v>
       </c>
       <c r="BI11">
-        <v>1.01</v>
+        <v>2.96</v>
       </c>
       <c r="BJ11">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK11">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BL11">
         <v>1000</v>
       </c>
       <c r="BM11">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="BN11">
-        <v>1000</v>
+        <v>5.9</v>
       </c>
       <c r="BO11">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BP11">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="BQ11">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BR11">
         <v>1000</v>
       </c>
       <c r="BS11">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BT11">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="BU11">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BV11">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="BW11">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BX11">
         <v>1000</v>
       </c>
       <c r="BY11">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ11">
         <v>1000</v>
       </c>
       <c r="CA11">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="CB11" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
     </row>
     <row r="12" spans="1:80">
       <c r="A12" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="B12" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C12" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D12" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E12" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="F12">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="G12">
-        <v>2.46</v>
+        <v>2.42</v>
       </c>
       <c r="H12">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="I12">
-        <v>3.6</v>
+        <v>4.3</v>
       </c>
       <c r="J12">
-        <v>3.45</v>
+        <v>2.84</v>
       </c>
       <c r="K12">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="L12">
-        <v>1.41</v>
+        <v>1.01</v>
       </c>
       <c r="M12">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="N12">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="O12">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="P12">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="Q12">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="R12">
         <v>1.34</v>
       </c>
       <c r="S12">
-        <v>3.25</v>
+        <v>2.78</v>
       </c>
       <c r="T12">
-        <v>1.73</v>
+        <v>1.59</v>
       </c>
       <c r="U12">
-        <v>2.08</v>
+        <v>1.96</v>
       </c>
       <c r="V12">
-        <v>1.38</v>
+        <v>1.31</v>
       </c>
       <c r="W12">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="X12">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="Y12">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="Z12">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AA12">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AB12">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AC12">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="AD12">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AE12">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AF12">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AG12">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AH12">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AI12">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AJ12">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AK12">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AL12">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AM12">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AN12">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AO12">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AP12">
-        <v>3.5</v>
+        <v>1.01</v>
       </c>
       <c r="AQ12">
-        <v>3.45</v>
+        <v>1.01</v>
       </c>
       <c r="AR12">
-        <v>3.8</v>
+        <v>1.01</v>
       </c>
       <c r="AS12">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="AT12">
-        <v>3.25</v>
+        <v>1.01</v>
       </c>
       <c r="AU12">
-        <v>3</v>
+        <v>1.01</v>
       </c>
       <c r="AV12">
-        <v>3.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW12">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="AX12">
-        <v>3.55</v>
+        <v>1.01</v>
       </c>
       <c r="AY12">
-        <v>3.35</v>
+        <v>1.01</v>
       </c>
       <c r="AZ12">
-        <v>3.6</v>
+        <v>1.01</v>
       </c>
       <c r="BA12">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="BB12">
-        <v>3.9</v>
+        <v>1.01</v>
       </c>
       <c r="BC12">
-        <v>3.85</v>
+        <v>1.01</v>
       </c>
       <c r="BD12">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="BE12">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="BF12">
-        <v>3.7</v>
+        <v>1.01</v>
       </c>
       <c r="BG12">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="BH12">
-        <v>3.5</v>
+        <v>1000</v>
       </c>
       <c r="BI12">
-        <v>2.72</v>
+        <v>1.01</v>
       </c>
       <c r="BJ12">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="BK12">
-        <v>5.2</v>
+        <v>1.01</v>
       </c>
       <c r="BL12">
         <v>1000</v>
       </c>
       <c r="BM12">
-        <v>2.62</v>
+        <v>1.01</v>
       </c>
       <c r="BN12">
-        <v>5.4</v>
+        <v>1000</v>
       </c>
       <c r="BO12">
-        <v>3.65</v>
+        <v>1.01</v>
       </c>
       <c r="BP12">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="BQ12">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="BR12">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BS12">
-        <v>2.46</v>
+        <v>1.01</v>
       </c>
       <c r="BT12">
-        <v>6.8</v>
+        <v>1000</v>
       </c>
       <c r="BU12">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="BV12">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="BW12">
-        <v>2.44</v>
+        <v>1.01</v>
       </c>
       <c r="BX12">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="BY12">
-        <v>2.5</v>
+        <v>1.01</v>
       </c>
       <c r="BZ12">
         <v>0</v>
@@ -3663,733 +3684,733 @@
         <v>0</v>
       </c>
       <c r="CB12" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
     </row>
     <row r="13" spans="1:80">
       <c r="A13" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="B13" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C13" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D13" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E13" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="F13">
-        <v>1.82</v>
+        <v>1.04</v>
       </c>
       <c r="G13">
-        <v>1.9</v>
+        <v>970</v>
       </c>
       <c r="H13">
-        <v>4.5</v>
+        <v>1.04</v>
       </c>
       <c r="I13">
-        <v>5</v>
+        <v>190</v>
       </c>
       <c r="J13">
-        <v>3.65</v>
+        <v>1.01</v>
       </c>
       <c r="K13">
-        <v>4.4</v>
+        <v>110</v>
       </c>
       <c r="L13">
-        <v>1.5</v>
+        <v>1.01</v>
       </c>
       <c r="M13">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="N13">
-        <v>2.98</v>
+        <v>1.28</v>
       </c>
       <c r="O13">
-        <v>1.39</v>
+        <v>1.23</v>
       </c>
       <c r="P13">
-        <v>1.69</v>
+        <v>1.28</v>
       </c>
       <c r="Q13">
-        <v>2.12</v>
+        <v>1.23</v>
       </c>
       <c r="R13">
-        <v>1.26</v>
+        <v>1.18</v>
       </c>
       <c r="S13">
-        <v>3.45</v>
+        <v>1.23</v>
       </c>
       <c r="T13">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="U13">
-        <v>1.11</v>
+        <v>1.56</v>
       </c>
       <c r="V13">
-        <v>1.25</v>
+        <v>1.01</v>
       </c>
       <c r="W13">
-        <v>2.12</v>
+        <v>1.02</v>
       </c>
       <c r="X13">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="Y13">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="Z13">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AA13">
-        <v>170</v>
+        <v>1000</v>
       </c>
       <c r="AB13">
-        <v>6.8</v>
+        <v>1000</v>
       </c>
       <c r="AC13">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AD13">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AE13">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AF13">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="AG13">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AH13">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AI13">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AJ13">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AK13">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AL13">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AM13">
-        <v>260</v>
+        <v>1000</v>
       </c>
       <c r="AN13">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AO13">
-        <v>170</v>
+        <v>1000</v>
       </c>
       <c r="AP13">
-        <v>8.800000000000001</v>
+        <v>1.03</v>
       </c>
       <c r="AQ13">
-        <v>10.5</v>
+        <v>1.03</v>
       </c>
       <c r="AR13">
-        <v>6.2</v>
+        <v>1.03</v>
       </c>
       <c r="AS13">
-        <v>7</v>
+        <v>1.03</v>
       </c>
       <c r="AT13">
-        <v>5</v>
+        <v>1.03</v>
       </c>
       <c r="AU13">
-        <v>7</v>
+        <v>1.03</v>
       </c>
       <c r="AV13">
-        <v>16.5</v>
+        <v>1.03</v>
       </c>
       <c r="AW13">
-        <v>6.8</v>
+        <v>1.03</v>
       </c>
       <c r="AX13">
-        <v>7.2</v>
+        <v>1.03</v>
       </c>
       <c r="AY13">
-        <v>9.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="AZ13">
-        <v>21</v>
+        <v>1.03</v>
       </c>
       <c r="BA13">
-        <v>6.8</v>
+        <v>1.03</v>
       </c>
       <c r="BB13">
-        <v>14.5</v>
+        <v>1.03</v>
       </c>
       <c r="BC13">
-        <v>17</v>
+        <v>1.03</v>
       </c>
       <c r="BD13">
-        <v>6.4</v>
+        <v>1.03</v>
       </c>
       <c r="BE13">
-        <v>7.2</v>
+        <v>1.03</v>
       </c>
       <c r="BF13">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="BG13">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="BH13">
-        <v>2.98</v>
+        <v>1000</v>
       </c>
       <c r="BI13">
-        <v>2.5</v>
+        <v>1.01</v>
       </c>
       <c r="BJ13">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="BK13">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="BL13">
         <v>1000</v>
       </c>
       <c r="BM13">
-        <v>14.5</v>
+        <v>1.01</v>
       </c>
       <c r="BN13">
-        <v>4.3</v>
+        <v>1000</v>
       </c>
       <c r="BO13">
-        <v>3.35</v>
+        <v>1.01</v>
       </c>
       <c r="BP13">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="BQ13">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="BR13">
         <v>1000</v>
       </c>
       <c r="BS13">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="BT13">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="BU13">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="BV13">
         <v>1000</v>
       </c>
       <c r="BW13">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="BX13">
         <v>1000</v>
       </c>
       <c r="BY13">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="BZ13">
         <v>1000</v>
       </c>
       <c r="CA13">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="CB13" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
     </row>
     <row r="14" spans="1:80">
       <c r="A14" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="B14" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C14" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D14" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E14" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="F14">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="G14">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="H14">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="I14">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="J14">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="K14">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="L14">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="M14">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="N14">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="O14">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="P14">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="Q14">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="R14">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="S14">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="T14">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="U14">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="V14">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W14">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="X14">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="Y14">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="Z14">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="AA14">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AB14">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="AC14">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="AD14">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AE14">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="AF14">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="AG14">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="AH14">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="AI14">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AJ14">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="AK14">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="AL14">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="AM14">
-        <v>220</v>
+        <v>0</v>
       </c>
       <c r="AN14">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="AO14">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AP14">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="AQ14">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AR14">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="AS14">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="AT14">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="AU14">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="AV14">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="AW14">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="AX14">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AY14">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AZ14">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="BA14">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="BB14">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="BC14">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="BD14">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="BE14">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="BF14">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="BG14">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="BH14">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="BI14">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="BJ14">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="BK14">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BL14">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM14">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="BN14">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="BO14">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="BP14">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="BQ14">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="BR14">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="BS14">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="BT14">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="BU14">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="BV14">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="BW14">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="BX14">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="BY14">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="BZ14">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="CA14">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="CB14" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
     </row>
     <row r="15" spans="1:80">
       <c r="A15" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B15" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C15" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D15" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E15" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="F15">
-        <v>1.71</v>
+        <v>2.24</v>
       </c>
       <c r="G15">
-        <v>2.2</v>
+        <v>2.46</v>
       </c>
       <c r="H15">
-        <v>3.95</v>
+        <v>3.2</v>
       </c>
       <c r="I15">
-        <v>8.199999999999999</v>
+        <v>3.6</v>
       </c>
       <c r="J15">
-        <v>2.96</v>
+        <v>3.45</v>
       </c>
       <c r="K15">
-        <v>3.95</v>
+        <v>3.7</v>
       </c>
       <c r="L15">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="M15">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="N15">
-        <v>2.38</v>
+        <v>3.6</v>
       </c>
       <c r="O15">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="P15">
-        <v>1.55</v>
+        <v>1.87</v>
       </c>
       <c r="Q15">
-        <v>1.96</v>
+        <v>1.85</v>
       </c>
       <c r="R15">
-        <v>1.18</v>
+        <v>1.34</v>
       </c>
       <c r="S15">
-        <v>2.78</v>
+        <v>3.25</v>
       </c>
       <c r="T15">
-        <v>1.11</v>
+        <v>1.75</v>
       </c>
       <c r="U15">
-        <v>1.11</v>
+        <v>2.12</v>
       </c>
       <c r="V15">
-        <v>1.13</v>
+        <v>1.38</v>
       </c>
       <c r="W15">
-        <v>1.83</v>
+        <v>1.68</v>
       </c>
       <c r="X15">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="Y15">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="Z15">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AA15">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AB15">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AC15">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="AD15">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AE15">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AF15">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AG15">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AH15">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AI15">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AJ15">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AK15">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AL15">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AM15">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AN15">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AO15">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AP15">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="AQ15">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="AR15">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="AS15">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AT15">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="AU15">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AV15">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="AW15">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AX15">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="AY15">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="AZ15">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="BA15">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BB15">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="BC15">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="BD15">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BE15">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BF15">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="BG15">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BH15">
-        <v>1000</v>
+        <v>3.5</v>
       </c>
       <c r="BI15">
-        <v>1.04</v>
+        <v>2.7</v>
       </c>
       <c r="BJ15">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK15">
-        <v>1.04</v>
+        <v>5.2</v>
       </c>
       <c r="BL15">
         <v>1000</v>
       </c>
       <c r="BM15">
-        <v>1.04</v>
+        <v>2.62</v>
       </c>
       <c r="BN15">
-        <v>1000</v>
+        <v>5.4</v>
       </c>
       <c r="BO15">
-        <v>1.04</v>
+        <v>3.6</v>
       </c>
       <c r="BP15">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="BQ15">
-        <v>1.04</v>
+        <v>6.8</v>
       </c>
       <c r="BR15">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BS15">
-        <v>1.04</v>
+        <v>2.46</v>
       </c>
       <c r="BT15">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="BU15">
-        <v>1.04</v>
+        <v>4.2</v>
       </c>
       <c r="BV15">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="BW15">
-        <v>1.04</v>
+        <v>2.44</v>
       </c>
       <c r="BX15">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BY15">
-        <v>1.04</v>
+        <v>2.5</v>
       </c>
       <c r="BZ15">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA15">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="CB15" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
     </row>
     <row r="16" spans="1:80">
@@ -4397,483 +4418,1209 @@
         <v>84</v>
       </c>
       <c r="B16" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C16" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D16" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E16" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="F16">
-        <v>1.97</v>
+        <v>1.84</v>
       </c>
       <c r="G16">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="H16">
+        <v>4.5</v>
+      </c>
+      <c r="I16">
+        <v>5</v>
+      </c>
+      <c r="J16">
+        <v>3.7</v>
+      </c>
+      <c r="K16">
         <v>4.3</v>
       </c>
-      <c r="I16">
-        <v>5.5</v>
-      </c>
-      <c r="J16">
-        <v>2.96</v>
-      </c>
-      <c r="K16">
-        <v>3.65</v>
-      </c>
       <c r="L16">
-        <v>1.54</v>
+        <v>1.42</v>
       </c>
       <c r="M16">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="N16">
-        <v>2.36</v>
+        <v>2.84</v>
       </c>
       <c r="O16">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="P16">
-        <v>1.45</v>
+        <v>1.66</v>
       </c>
       <c r="Q16">
-        <v>2.78</v>
+        <v>2.3</v>
       </c>
       <c r="R16">
-        <v>1.16</v>
+        <v>1.23</v>
       </c>
       <c r="S16">
-        <v>5.9</v>
+        <v>4.7</v>
       </c>
       <c r="T16">
-        <v>2.32</v>
+        <v>2.18</v>
       </c>
       <c r="U16">
-        <v>1.57</v>
+        <v>1.73</v>
       </c>
       <c r="V16">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="W16">
-        <v>1.84</v>
+        <v>2.12</v>
       </c>
       <c r="X16">
-        <v>8.4</v>
+        <v>14.5</v>
       </c>
       <c r="Y16">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="Z16">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AA16">
         <v>180</v>
       </c>
       <c r="AB16">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AC16">
-        <v>7.8</v>
+        <v>9.6</v>
       </c>
       <c r="AD16">
-        <v>26</v>
+        <v>19.5</v>
       </c>
       <c r="AE16">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="AF16">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AG16">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AH16">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AI16">
-        <v>150</v>
+        <v>110</v>
       </c>
       <c r="AJ16">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="AK16">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="AL16">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="AM16">
-        <v>290</v>
+        <v>270</v>
       </c>
       <c r="AN16">
-        <v>32</v>
+        <v>18.5</v>
       </c>
       <c r="AO16">
-        <v>210</v>
+        <v>170</v>
       </c>
       <c r="AP16">
-        <v>6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ16">
-        <v>4.8</v>
+        <v>10.5</v>
       </c>
       <c r="AR16">
-        <v>23</v>
+        <v>7.4</v>
       </c>
       <c r="AS16">
-        <v>7.4</v>
+        <v>9</v>
       </c>
       <c r="AT16">
-        <v>3.5</v>
+        <v>5</v>
       </c>
       <c r="AU16">
-        <v>5.9</v>
+        <v>7</v>
       </c>
       <c r="AV16">
         <v>16.5</v>
       </c>
       <c r="AW16">
+        <v>8.6</v>
+      </c>
+      <c r="AX16">
         <v>7.2</v>
       </c>
-      <c r="AX16">
-        <v>4.8</v>
-      </c>
       <c r="AY16">
-        <v>4.8</v>
+        <v>7.8</v>
       </c>
       <c r="AZ16">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="BA16">
-        <v>7.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB16">
-        <v>18</v>
+        <v>14.5</v>
       </c>
       <c r="BC16">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="BD16">
+        <v>8</v>
+      </c>
+      <c r="BE16">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BF16">
+        <v>13</v>
+      </c>
+      <c r="BG16">
+        <v>9</v>
+      </c>
+      <c r="BH16">
+        <v>2.94</v>
+      </c>
+      <c r="BI16">
+        <v>2.66</v>
+      </c>
+      <c r="BJ16">
+        <v>12</v>
+      </c>
+      <c r="BK16">
+        <v>6.4</v>
+      </c>
+      <c r="BL16">
+        <v>1000</v>
+      </c>
+      <c r="BM16">
+        <v>13</v>
+      </c>
+      <c r="BN16">
+        <v>4.3</v>
+      </c>
+      <c r="BO16">
+        <v>3.3</v>
+      </c>
+      <c r="BP16">
+        <v>14</v>
+      </c>
+      <c r="BQ16">
         <v>7</v>
       </c>
-      <c r="BE16">
-        <v>7.6</v>
-      </c>
-      <c r="BF16">
-        <v>19.5</v>
-      </c>
-      <c r="BG16">
-        <v>7.4</v>
-      </c>
-      <c r="BH16">
-        <v>2.84</v>
-      </c>
-      <c r="BI16">
-        <v>2.18</v>
-      </c>
-      <c r="BJ16">
-        <v>14.5</v>
-      </c>
-      <c r="BK16">
-        <v>4.3</v>
-      </c>
-      <c r="BL16">
-        <v>1000</v>
-      </c>
-      <c r="BM16">
-        <v>6</v>
-      </c>
-      <c r="BN16">
-        <v>5</v>
-      </c>
-      <c r="BO16">
-        <v>3.6</v>
-      </c>
-      <c r="BP16">
-        <v>21</v>
-      </c>
-      <c r="BQ16">
-        <v>4.8</v>
-      </c>
       <c r="BR16">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BS16">
-        <v>5.6</v>
+        <v>10</v>
       </c>
       <c r="BT16">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BU16">
-        <v>3.7</v>
+        <v>5.5</v>
       </c>
       <c r="BV16">
         <v>1000</v>
       </c>
       <c r="BW16">
-        <v>5.7</v>
+        <v>11.5</v>
       </c>
       <c r="BX16">
         <v>1000</v>
       </c>
       <c r="BY16">
-        <v>5.9</v>
+        <v>12</v>
       </c>
       <c r="BZ16">
         <v>1000</v>
       </c>
       <c r="CA16">
-        <v>5.7</v>
+        <v>10</v>
       </c>
       <c r="CB16" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
     </row>
     <row r="17" spans="1:80">
       <c r="A17" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B17" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C17" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D17" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E17" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="F17">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="G17">
-        <v>3.35</v>
+        <v>2.48</v>
       </c>
       <c r="H17">
-        <v>2.14</v>
+        <v>3.55</v>
       </c>
       <c r="I17">
-        <v>2.5</v>
+        <v>3.8</v>
       </c>
       <c r="J17">
-        <v>3.8</v>
+        <v>3.05</v>
       </c>
       <c r="K17">
-        <v>4.2</v>
+        <v>3.15</v>
       </c>
       <c r="L17">
-        <v>1.23</v>
+        <v>1.47</v>
       </c>
       <c r="M17">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="N17">
-        <v>3.45</v>
+        <v>2.66</v>
       </c>
       <c r="O17">
-        <v>1.17</v>
+        <v>1.54</v>
       </c>
       <c r="P17">
-        <v>2.48</v>
+        <v>1.56</v>
       </c>
       <c r="Q17">
-        <v>1.51</v>
+        <v>2.66</v>
       </c>
       <c r="R17">
-        <v>1.53</v>
+        <v>1.2</v>
       </c>
       <c r="S17">
+        <v>5.4</v>
+      </c>
+      <c r="T17">
         <v>2.1</v>
       </c>
-      <c r="T17">
-        <v>1.43</v>
-      </c>
       <c r="U17">
-        <v>2.36</v>
+        <v>1.8</v>
       </c>
       <c r="V17">
-        <v>1.66</v>
+        <v>1.36</v>
       </c>
       <c r="W17">
-        <v>1.42</v>
+        <v>1.67</v>
       </c>
       <c r="X17">
+        <v>10.5</v>
+      </c>
+      <c r="Y17">
+        <v>12</v>
+      </c>
+      <c r="Z17">
+        <v>29</v>
+      </c>
+      <c r="AA17">
+        <v>100</v>
+      </c>
+      <c r="AB17">
+        <v>7.6</v>
+      </c>
+      <c r="AC17">
+        <v>7.4</v>
+      </c>
+      <c r="AD17">
+        <v>20</v>
+      </c>
+      <c r="AE17">
+        <v>75</v>
+      </c>
+      <c r="AF17">
+        <v>14.5</v>
+      </c>
+      <c r="AG17">
+        <v>12.5</v>
+      </c>
+      <c r="AH17">
         <v>28</v>
       </c>
-      <c r="Y17">
-        <v>17</v>
-      </c>
-      <c r="Z17">
-        <v>20</v>
-      </c>
-      <c r="AA17">
-        <v>34</v>
-      </c>
-      <c r="AB17">
-        <v>20</v>
-      </c>
-      <c r="AC17">
-        <v>11</v>
-      </c>
-      <c r="AD17">
-        <v>13</v>
-      </c>
-      <c r="AE17">
-        <v>23</v>
-      </c>
-      <c r="AF17">
-        <v>27</v>
-      </c>
-      <c r="AG17">
-        <v>15.5</v>
-      </c>
-      <c r="AH17">
-        <v>16</v>
-      </c>
       <c r="AI17">
-        <v>29</v>
+        <v>100</v>
       </c>
       <c r="AJ17">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="AK17">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="AL17">
-        <v>36</v>
+        <v>75</v>
       </c>
       <c r="AM17">
-        <v>65</v>
+        <v>220</v>
       </c>
       <c r="AN17">
-        <v>19</v>
+        <v>44</v>
       </c>
       <c r="AO17">
-        <v>12</v>
+        <v>100</v>
       </c>
       <c r="AP17">
-        <v>5.7</v>
+        <v>7.8</v>
       </c>
       <c r="AQ17">
-        <v>5.1</v>
+        <v>9</v>
       </c>
       <c r="AR17">
-        <v>5.3</v>
+        <v>17.5</v>
       </c>
       <c r="AS17">
         <v>6</v>
       </c>
       <c r="AT17">
+        <v>6.6</v>
+      </c>
+      <c r="AU17">
+        <v>6.6</v>
+      </c>
+      <c r="AV17">
+        <v>14</v>
+      </c>
+      <c r="AW17">
+        <v>5.9</v>
+      </c>
+      <c r="AX17">
+        <v>12</v>
+      </c>
+      <c r="AY17">
+        <v>10.5</v>
+      </c>
+      <c r="AZ17">
+        <v>16.5</v>
+      </c>
+      <c r="BA17">
+        <v>6</v>
+      </c>
+      <c r="BB17">
+        <v>5.6</v>
+      </c>
+      <c r="BC17">
+        <v>24</v>
+      </c>
+      <c r="BD17">
+        <v>5.9</v>
+      </c>
+      <c r="BE17">
+        <v>6.2</v>
+      </c>
+      <c r="BF17">
+        <v>5.5</v>
+      </c>
+      <c r="BG17">
+        <v>6</v>
+      </c>
+      <c r="BH17">
+        <v>3.15</v>
+      </c>
+      <c r="BI17">
+        <v>2.24</v>
+      </c>
+      <c r="BJ17">
+        <v>13.5</v>
+      </c>
+      <c r="BK17">
+        <v>3.6</v>
+      </c>
+      <c r="BL17">
+        <v>1000</v>
+      </c>
+      <c r="BM17">
+        <v>4.8</v>
+      </c>
+      <c r="BN17">
+        <v>6</v>
+      </c>
+      <c r="BO17">
+        <v>3.9</v>
+      </c>
+      <c r="BP17">
+        <v>26</v>
+      </c>
+      <c r="BQ17">
+        <v>4.1</v>
+      </c>
+      <c r="BR17">
+        <v>55</v>
+      </c>
+      <c r="BS17">
+        <v>4.5</v>
+      </c>
+      <c r="BT17">
+        <v>8</v>
+      </c>
+      <c r="BU17">
+        <v>5</v>
+      </c>
+      <c r="BV17">
+        <v>44</v>
+      </c>
+      <c r="BW17">
+        <v>4.4</v>
+      </c>
+      <c r="BX17">
+        <v>70</v>
+      </c>
+      <c r="BY17">
+        <v>4.6</v>
+      </c>
+      <c r="BZ17">
+        <v>60</v>
+      </c>
+      <c r="CA17">
+        <v>4.5</v>
+      </c>
+      <c r="CB17" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="18" spans="1:80">
+      <c r="A18" t="s">
+        <v>86</v>
+      </c>
+      <c r="B18" t="s">
+        <v>89</v>
+      </c>
+      <c r="C18" t="s">
+        <v>103</v>
+      </c>
+      <c r="D18" t="s">
+        <v>122</v>
+      </c>
+      <c r="E18" t="s">
+        <v>141</v>
+      </c>
+      <c r="F18">
+        <v>1.74</v>
+      </c>
+      <c r="G18">
+        <v>2.2</v>
+      </c>
+      <c r="H18">
+        <v>4</v>
+      </c>
+      <c r="I18">
+        <v>7.2</v>
+      </c>
+      <c r="J18">
+        <v>3.15</v>
+      </c>
+      <c r="K18">
+        <v>6.2</v>
+      </c>
+      <c r="L18">
+        <v>1.39</v>
+      </c>
+      <c r="M18">
+        <v>1.09</v>
+      </c>
+      <c r="N18">
+        <v>2.4</v>
+      </c>
+      <c r="O18">
+        <v>1.41</v>
+      </c>
+      <c r="P18">
+        <v>1.53</v>
+      </c>
+      <c r="Q18">
+        <v>2.18</v>
+      </c>
+      <c r="R18">
+        <v>1.18</v>
+      </c>
+      <c r="S18">
+        <v>2.96</v>
+      </c>
+      <c r="T18">
+        <v>1.11</v>
+      </c>
+      <c r="U18">
+        <v>1.11</v>
+      </c>
+      <c r="V18">
+        <v>1.16</v>
+      </c>
+      <c r="W18">
+        <v>1.83</v>
+      </c>
+      <c r="X18">
+        <v>1000</v>
+      </c>
+      <c r="Y18">
+        <v>1000</v>
+      </c>
+      <c r="Z18">
+        <v>1000</v>
+      </c>
+      <c r="AA18">
+        <v>1000</v>
+      </c>
+      <c r="AB18">
+        <v>1000</v>
+      </c>
+      <c r="AC18">
+        <v>1000</v>
+      </c>
+      <c r="AD18">
+        <v>1000</v>
+      </c>
+      <c r="AE18">
+        <v>1000</v>
+      </c>
+      <c r="AF18">
+        <v>1000</v>
+      </c>
+      <c r="AG18">
+        <v>1000</v>
+      </c>
+      <c r="AH18">
+        <v>1000</v>
+      </c>
+      <c r="AI18">
+        <v>1000</v>
+      </c>
+      <c r="AJ18">
+        <v>1000</v>
+      </c>
+      <c r="AK18">
+        <v>1000</v>
+      </c>
+      <c r="AL18">
+        <v>1000</v>
+      </c>
+      <c r="AM18">
+        <v>1000</v>
+      </c>
+      <c r="AN18">
+        <v>1000</v>
+      </c>
+      <c r="AO18">
+        <v>1000</v>
+      </c>
+      <c r="AP18">
+        <v>1.01</v>
+      </c>
+      <c r="AQ18">
+        <v>1.01</v>
+      </c>
+      <c r="AR18">
+        <v>1.01</v>
+      </c>
+      <c r="AS18">
+        <v>1.01</v>
+      </c>
+      <c r="AT18">
+        <v>1.01</v>
+      </c>
+      <c r="AU18">
+        <v>1.01</v>
+      </c>
+      <c r="AV18">
+        <v>1.01</v>
+      </c>
+      <c r="AW18">
+        <v>1.01</v>
+      </c>
+      <c r="AX18">
+        <v>1.01</v>
+      </c>
+      <c r="AY18">
+        <v>1.01</v>
+      </c>
+      <c r="AZ18">
+        <v>1.01</v>
+      </c>
+      <c r="BA18">
+        <v>1.01</v>
+      </c>
+      <c r="BB18">
+        <v>1.01</v>
+      </c>
+      <c r="BC18">
+        <v>1.01</v>
+      </c>
+      <c r="BD18">
+        <v>1.01</v>
+      </c>
+      <c r="BE18">
+        <v>1.01</v>
+      </c>
+      <c r="BF18">
+        <v>1.01</v>
+      </c>
+      <c r="BG18">
+        <v>1.01</v>
+      </c>
+      <c r="BH18">
+        <v>1000</v>
+      </c>
+      <c r="BI18">
+        <v>1.04</v>
+      </c>
+      <c r="BJ18">
+        <v>1000</v>
+      </c>
+      <c r="BK18">
+        <v>1.04</v>
+      </c>
+      <c r="BL18">
+        <v>1000</v>
+      </c>
+      <c r="BM18">
+        <v>1.04</v>
+      </c>
+      <c r="BN18">
+        <v>1000</v>
+      </c>
+      <c r="BO18">
+        <v>1.04</v>
+      </c>
+      <c r="BP18">
+        <v>1000</v>
+      </c>
+      <c r="BQ18">
+        <v>1.04</v>
+      </c>
+      <c r="BR18">
+        <v>1000</v>
+      </c>
+      <c r="BS18">
+        <v>1.04</v>
+      </c>
+      <c r="BT18">
+        <v>1000</v>
+      </c>
+      <c r="BU18">
+        <v>1.04</v>
+      </c>
+      <c r="BV18">
+        <v>1000</v>
+      </c>
+      <c r="BW18">
+        <v>1.04</v>
+      </c>
+      <c r="BX18">
+        <v>1000</v>
+      </c>
+      <c r="BY18">
+        <v>1.04</v>
+      </c>
+      <c r="BZ18">
+        <v>1000</v>
+      </c>
+      <c r="CA18">
+        <v>1.04</v>
+      </c>
+      <c r="CB18" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="19" spans="1:80">
+      <c r="A19" t="s">
+        <v>84</v>
+      </c>
+      <c r="B19" t="s">
+        <v>89</v>
+      </c>
+      <c r="C19" t="s">
+        <v>104</v>
+      </c>
+      <c r="D19" t="s">
+        <v>123</v>
+      </c>
+      <c r="E19" t="s">
+        <v>142</v>
+      </c>
+      <c r="F19">
+        <v>1.97</v>
+      </c>
+      <c r="G19">
+        <v>2.2</v>
+      </c>
+      <c r="H19">
+        <v>4.3</v>
+      </c>
+      <c r="I19">
+        <v>5.5</v>
+      </c>
+      <c r="J19">
+        <v>2.92</v>
+      </c>
+      <c r="K19">
+        <v>3.65</v>
+      </c>
+      <c r="L19">
+        <v>1.54</v>
+      </c>
+      <c r="M19">
+        <v>1.14</v>
+      </c>
+      <c r="N19">
+        <v>2.36</v>
+      </c>
+      <c r="O19">
+        <v>1.58</v>
+      </c>
+      <c r="P19">
+        <v>1.45</v>
+      </c>
+      <c r="Q19">
+        <v>2.78</v>
+      </c>
+      <c r="R19">
+        <v>1.16</v>
+      </c>
+      <c r="S19">
+        <v>5.9</v>
+      </c>
+      <c r="T19">
+        <v>2.32</v>
+      </c>
+      <c r="U19">
+        <v>1.57</v>
+      </c>
+      <c r="V19">
+        <v>1.22</v>
+      </c>
+      <c r="W19">
+        <v>1.83</v>
+      </c>
+      <c r="X19">
+        <v>8.4</v>
+      </c>
+      <c r="Y19">
+        <v>12.5</v>
+      </c>
+      <c r="Z19">
+        <v>38</v>
+      </c>
+      <c r="AA19">
+        <v>180</v>
+      </c>
+      <c r="AB19">
+        <v>6.4</v>
+      </c>
+      <c r="AC19">
+        <v>7.8</v>
+      </c>
+      <c r="AD19">
+        <v>26</v>
+      </c>
+      <c r="AE19">
+        <v>120</v>
+      </c>
+      <c r="AF19">
+        <v>13</v>
+      </c>
+      <c r="AG19">
+        <v>12.5</v>
+      </c>
+      <c r="AH19">
+        <v>34</v>
+      </c>
+      <c r="AI19">
+        <v>150</v>
+      </c>
+      <c r="AJ19">
+        <v>28</v>
+      </c>
+      <c r="AK19">
+        <v>34</v>
+      </c>
+      <c r="AL19">
+        <v>80</v>
+      </c>
+      <c r="AM19">
+        <v>290</v>
+      </c>
+      <c r="AN19">
+        <v>32</v>
+      </c>
+      <c r="AO19">
+        <v>210</v>
+      </c>
+      <c r="AP19">
+        <v>6</v>
+      </c>
+      <c r="AQ19">
+        <v>4.8</v>
+      </c>
+      <c r="AR19">
+        <v>23</v>
+      </c>
+      <c r="AS19">
+        <v>7.4</v>
+      </c>
+      <c r="AT19">
+        <v>3.5</v>
+      </c>
+      <c r="AU19">
+        <v>5.9</v>
+      </c>
+      <c r="AV19">
+        <v>16.5</v>
+      </c>
+      <c r="AW19">
+        <v>7.2</v>
+      </c>
+      <c r="AX19">
+        <v>4.8</v>
+      </c>
+      <c r="AY19">
+        <v>4.8</v>
+      </c>
+      <c r="AZ19">
+        <v>18</v>
+      </c>
+      <c r="BA19">
+        <v>7.4</v>
+      </c>
+      <c r="BB19">
+        <v>18</v>
+      </c>
+      <c r="BC19">
+        <v>6.2</v>
+      </c>
+      <c r="BD19">
+        <v>7</v>
+      </c>
+      <c r="BE19">
+        <v>7.6</v>
+      </c>
+      <c r="BF19">
+        <v>19.5</v>
+      </c>
+      <c r="BG19">
+        <v>7.4</v>
+      </c>
+      <c r="BH19">
+        <v>2.84</v>
+      </c>
+      <c r="BI19">
+        <v>2.18</v>
+      </c>
+      <c r="BJ19">
+        <v>14.5</v>
+      </c>
+      <c r="BK19">
+        <v>4.3</v>
+      </c>
+      <c r="BL19">
+        <v>1000</v>
+      </c>
+      <c r="BM19">
+        <v>6</v>
+      </c>
+      <c r="BN19">
+        <v>5</v>
+      </c>
+      <c r="BO19">
+        <v>3.6</v>
+      </c>
+      <c r="BP19">
+        <v>21</v>
+      </c>
+      <c r="BQ19">
+        <v>4.8</v>
+      </c>
+      <c r="BR19">
+        <v>1000</v>
+      </c>
+      <c r="BS19">
+        <v>5.6</v>
+      </c>
+      <c r="BT19">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BU19">
+        <v>3.7</v>
+      </c>
+      <c r="BV19">
+        <v>1000</v>
+      </c>
+      <c r="BW19">
+        <v>5.7</v>
+      </c>
+      <c r="BX19">
+        <v>1000</v>
+      </c>
+      <c r="BY19">
+        <v>5.9</v>
+      </c>
+      <c r="BZ19">
+        <v>1000</v>
+      </c>
+      <c r="CA19">
+        <v>5.7</v>
+      </c>
+      <c r="CB19" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="20" spans="1:80">
+      <c r="A20" t="s">
+        <v>80</v>
+      </c>
+      <c r="B20" t="s">
+        <v>89</v>
+      </c>
+      <c r="C20" t="s">
+        <v>105</v>
+      </c>
+      <c r="D20" t="s">
+        <v>124</v>
+      </c>
+      <c r="E20" t="s">
+        <v>143</v>
+      </c>
+      <c r="F20">
+        <v>2.7</v>
+      </c>
+      <c r="G20">
+        <v>3.3</v>
+      </c>
+      <c r="H20">
+        <v>2.2</v>
+      </c>
+      <c r="I20">
+        <v>2.58</v>
+      </c>
+      <c r="J20">
+        <v>3.25</v>
+      </c>
+      <c r="K20">
+        <v>4.1</v>
+      </c>
+      <c r="L20">
+        <v>1.23</v>
+      </c>
+      <c r="M20">
+        <v>1.01</v>
+      </c>
+      <c r="N20">
+        <v>5.2</v>
+      </c>
+      <c r="O20">
+        <v>1.15</v>
+      </c>
+      <c r="P20">
+        <v>2.48</v>
+      </c>
+      <c r="Q20">
+        <v>1.45</v>
+      </c>
+      <c r="R20">
+        <v>1.6</v>
+      </c>
+      <c r="S20">
+        <v>2.1</v>
+      </c>
+      <c r="T20">
+        <v>1.43</v>
+      </c>
+      <c r="U20">
+        <v>2.36</v>
+      </c>
+      <c r="V20">
+        <v>1.63</v>
+      </c>
+      <c r="W20">
+        <v>1.44</v>
+      </c>
+      <c r="X20">
+        <v>29</v>
+      </c>
+      <c r="Y20">
+        <v>17.5</v>
+      </c>
+      <c r="Z20">
+        <v>21</v>
+      </c>
+      <c r="AA20">
+        <v>34</v>
+      </c>
+      <c r="AB20">
+        <v>19.5</v>
+      </c>
+      <c r="AC20">
+        <v>11</v>
+      </c>
+      <c r="AD20">
+        <v>13.5</v>
+      </c>
+      <c r="AE20">
+        <v>24</v>
+      </c>
+      <c r="AF20">
+        <v>26</v>
+      </c>
+      <c r="AG20">
+        <v>15</v>
+      </c>
+      <c r="AH20">
+        <v>16</v>
+      </c>
+      <c r="AI20">
+        <v>30</v>
+      </c>
+      <c r="AJ20">
+        <v>55</v>
+      </c>
+      <c r="AK20">
+        <v>30</v>
+      </c>
+      <c r="AL20">
+        <v>34</v>
+      </c>
+      <c r="AM20">
+        <v>65</v>
+      </c>
+      <c r="AN20">
+        <v>18</v>
+      </c>
+      <c r="AO20">
+        <v>12.5</v>
+      </c>
+      <c r="AP20">
+        <v>5.7</v>
+      </c>
+      <c r="AQ20">
+        <v>5.1</v>
+      </c>
+      <c r="AR20">
         <v>5.3</v>
       </c>
-      <c r="AU17">
+      <c r="AS20">
+        <v>5.9</v>
+      </c>
+      <c r="AT20">
+        <v>5.2</v>
+      </c>
+      <c r="AU20">
         <v>4.3</v>
       </c>
-      <c r="AV17">
-        <v>4.6</v>
-      </c>
-      <c r="AW17">
+      <c r="AV20">
+        <v>4.7</v>
+      </c>
+      <c r="AW20">
         <v>5.5</v>
       </c>
-      <c r="AX17">
-        <v>5.7</v>
-      </c>
-      <c r="AY17">
+      <c r="AX20">
+        <v>5.6</v>
+      </c>
+      <c r="AY20">
+        <v>4.8</v>
+      </c>
+      <c r="AZ20">
         <v>4.9</v>
       </c>
-      <c r="AZ17">
-        <v>5</v>
-      </c>
-      <c r="BA17">
+      <c r="BA20">
         <v>5.8</v>
       </c>
-      <c r="BB17">
+      <c r="BB20">
+        <v>6.2</v>
+      </c>
+      <c r="BC20">
+        <v>5.8</v>
+      </c>
+      <c r="BD20">
+        <v>5.9</v>
+      </c>
+      <c r="BE20">
         <v>6.4</v>
       </c>
-      <c r="BC17">
-        <v>5.9</v>
-      </c>
-      <c r="BD17">
-        <v>6</v>
-      </c>
-      <c r="BE17">
-        <v>6.4</v>
-      </c>
-      <c r="BF17">
-        <v>5.2</v>
-      </c>
-      <c r="BG17">
+      <c r="BF20">
+        <v>5.1</v>
+      </c>
+      <c r="BG20">
         <v>4.5</v>
       </c>
-      <c r="BH17">
+      <c r="BH20">
         <v>5.4</v>
       </c>
-      <c r="BI17">
+      <c r="BI20">
         <v>2.6</v>
       </c>
-      <c r="BJ17">
-        <v>10.5</v>
-      </c>
-      <c r="BK17">
-        <v>3.4</v>
-      </c>
-      <c r="BL17">
+      <c r="BJ20">
+        <v>10</v>
+      </c>
+      <c r="BK20">
+        <v>3.35</v>
+      </c>
+      <c r="BL20">
         <v>85</v>
       </c>
-      <c r="BM17">
+      <c r="BM20">
         <v>4.7</v>
       </c>
-      <c r="BN17">
-        <v>7.2</v>
-      </c>
-      <c r="BO17">
-        <v>2.96</v>
-      </c>
-      <c r="BP17">
-        <v>25</v>
-      </c>
-      <c r="BQ17">
+      <c r="BN20">
+        <v>7</v>
+      </c>
+      <c r="BO20">
+        <v>2.92</v>
+      </c>
+      <c r="BP20">
+        <v>24</v>
+      </c>
+      <c r="BQ20">
+        <v>4.1</v>
+      </c>
+      <c r="BR20">
+        <v>32</v>
+      </c>
+      <c r="BS20">
+        <v>4.3</v>
+      </c>
+      <c r="BT20">
+        <v>7</v>
+      </c>
+      <c r="BU20">
+        <v>4.4</v>
+      </c>
+      <c r="BV20">
+        <v>19</v>
+      </c>
+      <c r="BW20">
+        <v>3.95</v>
+      </c>
+      <c r="BX20">
+        <v>27</v>
+      </c>
+      <c r="BY20">
         <v>4.2</v>
       </c>
-      <c r="BR17">
-        <v>28</v>
-      </c>
-      <c r="BS17">
-        <v>4.2</v>
-      </c>
-      <c r="BT17">
-        <v>6.8</v>
-      </c>
-      <c r="BU17">
-        <v>2.88</v>
-      </c>
-      <c r="BV17">
-        <v>18</v>
-      </c>
-      <c r="BW17">
-        <v>3.9</v>
-      </c>
-      <c r="BX17">
-        <v>27</v>
-      </c>
-      <c r="BY17">
-        <v>4.2</v>
-      </c>
-      <c r="BZ17">
-        <v>0</v>
-      </c>
-      <c r="CA17">
-        <v>0</v>
-      </c>
-      <c r="CB17" t="s">
-        <v>137</v>
+      <c r="BZ20">
+        <v>0</v>
+      </c>
+      <c r="CA20">
+        <v>0</v>
+      </c>
+      <c r="CB20" t="s">
+        <v>144</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-06.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-06.xlsx
@@ -448,7 +448,7 @@
     <t>Always Ready</t>
   </si>
   <si>
-    <t>2026-08-05 16:52:06</t>
+    <t>2026-08-05 19:02:54</t>
   </si>
 </sst>
 </file>
@@ -1042,61 +1042,61 @@
         <v>125</v>
       </c>
       <c r="F2">
+        <v>1.17</v>
+      </c>
+      <c r="G2">
+        <v>1.2</v>
+      </c>
+      <c r="H2">
+        <v>16</v>
+      </c>
+      <c r="I2">
+        <v>18.5</v>
+      </c>
+      <c r="J2">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="K2">
+        <v>11.5</v>
+      </c>
+      <c r="L2">
         <v>1.15</v>
       </c>
-      <c r="G2">
-        <v>1.16</v>
-      </c>
-      <c r="H2">
-        <v>19.5</v>
-      </c>
-      <c r="I2">
-        <v>25</v>
-      </c>
-      <c r="J2">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="K2">
-        <v>12.5</v>
-      </c>
-      <c r="L2">
-        <v>1.13</v>
-      </c>
       <c r="M2">
         <v>1.01</v>
       </c>
       <c r="N2">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="O2">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="P2">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="Q2">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="R2">
-        <v>2.8</v>
+        <v>2.66</v>
       </c>
       <c r="S2">
-        <v>1.51</v>
+        <v>1.58</v>
       </c>
       <c r="T2">
         <v>1.77</v>
       </c>
       <c r="U2">
-        <v>2</v>
+        <v>2.16</v>
       </c>
       <c r="V2">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="W2">
-        <v>6.8</v>
+        <v>6</v>
       </c>
       <c r="X2">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="Y2">
         <v>950</v>
@@ -1108,154 +1108,154 @@
         <v>1000</v>
       </c>
       <c r="AB2">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AC2">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AD2">
-        <v>950</v>
+        <v>70</v>
       </c>
       <c r="AE2">
-        <v>330</v>
+        <v>270</v>
       </c>
       <c r="AF2">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AG2">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AH2">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="AI2">
+        <v>140</v>
+      </c>
+      <c r="AJ2">
+        <v>12.5</v>
+      </c>
+      <c r="AK2">
+        <v>15.5</v>
+      </c>
+      <c r="AL2">
+        <v>34</v>
+      </c>
+      <c r="AM2">
+        <v>120</v>
+      </c>
+      <c r="AN2">
+        <v>2.34</v>
+      </c>
+      <c r="AO2">
         <v>170</v>
       </c>
-      <c r="AJ2">
-        <v>13</v>
-      </c>
-      <c r="AK2">
-        <v>17.5</v>
-      </c>
-      <c r="AL2">
-        <v>40</v>
-      </c>
-      <c r="AM2">
-        <v>140</v>
-      </c>
-      <c r="AN2">
-        <v>2.18</v>
-      </c>
-      <c r="AO2">
-        <v>230</v>
-      </c>
       <c r="AP2">
-        <v>7.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ2">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="AR2">
-        <v>8.4</v>
+        <v>10</v>
       </c>
       <c r="AS2">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="AT2">
         <v>20</v>
       </c>
       <c r="AU2">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AV2">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AW2">
+        <v>10</v>
+      </c>
+      <c r="AX2">
+        <v>11.5</v>
+      </c>
+      <c r="AY2">
+        <v>12</v>
+      </c>
+      <c r="AZ2">
+        <v>8</v>
+      </c>
+      <c r="BA2">
+        <v>9.6</v>
+      </c>
+      <c r="BB2">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BC2">
+        <v>11</v>
+      </c>
+      <c r="BD2">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BE2">
+        <v>9.4</v>
+      </c>
+      <c r="BF2">
+        <v>2.02</v>
+      </c>
+      <c r="BG2">
+        <v>9.6</v>
+      </c>
+      <c r="BH2">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BI2">
+        <v>6.4</v>
+      </c>
+      <c r="BJ2">
+        <v>13</v>
+      </c>
+      <c r="BK2">
+        <v>5.2</v>
+      </c>
+      <c r="BL2">
+        <v>1000</v>
+      </c>
+      <c r="BM2">
         <v>7.8</v>
       </c>
-      <c r="AW2">
-        <v>8.4</v>
-      </c>
-      <c r="AX2">
-        <v>11</v>
-      </c>
-      <c r="AY2">
-        <v>13.5</v>
-      </c>
-      <c r="AZ2">
-        <v>7</v>
-      </c>
-      <c r="BA2">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BB2">
-        <v>9.4</v>
-      </c>
-      <c r="BC2">
-        <v>12.5</v>
-      </c>
-      <c r="BD2">
+      <c r="BN2">
+        <v>5</v>
+      </c>
+      <c r="BO2">
+        <v>4</v>
+      </c>
+      <c r="BP2">
+        <v>6.6</v>
+      </c>
+      <c r="BQ2">
+        <v>5.2</v>
+      </c>
+      <c r="BR2">
+        <v>17</v>
+      </c>
+      <c r="BS2">
+        <v>5.7</v>
+      </c>
+      <c r="BT2">
+        <v>22</v>
+      </c>
+      <c r="BU2">
+        <v>6.2</v>
+      </c>
+      <c r="BV2">
+        <v>1000</v>
+      </c>
+      <c r="BW2">
+        <v>8</v>
+      </c>
+      <c r="BX2">
+        <v>70</v>
+      </c>
+      <c r="BY2">
         <v>7.6</v>
-      </c>
-      <c r="BE2">
-        <v>8</v>
-      </c>
-      <c r="BF2">
-        <v>1.95</v>
-      </c>
-      <c r="BG2">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BH2">
-        <v>8</v>
-      </c>
-      <c r="BI2">
-        <v>6</v>
-      </c>
-      <c r="BJ2">
-        <v>14</v>
-      </c>
-      <c r="BK2">
-        <v>5.6</v>
-      </c>
-      <c r="BL2">
-        <v>1000</v>
-      </c>
-      <c r="BM2">
-        <v>8.6</v>
-      </c>
-      <c r="BN2">
-        <v>4.9</v>
-      </c>
-      <c r="BO2">
-        <v>3.75</v>
-      </c>
-      <c r="BP2">
-        <v>6.2</v>
-      </c>
-      <c r="BQ2">
-        <v>4.7</v>
-      </c>
-      <c r="BR2">
-        <v>17.5</v>
-      </c>
-      <c r="BS2">
-        <v>6</v>
-      </c>
-      <c r="BT2">
-        <v>24</v>
-      </c>
-      <c r="BU2">
-        <v>6.8</v>
-      </c>
-      <c r="BV2">
-        <v>1000</v>
-      </c>
-      <c r="BW2">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BX2">
-        <v>1000</v>
-      </c>
-      <c r="BY2">
-        <v>8.4</v>
       </c>
       <c r="BZ2">
         <v>0</v>
@@ -1284,10 +1284,10 @@
         <v>126</v>
       </c>
       <c r="F3">
+        <v>2.6</v>
+      </c>
+      <c r="G3">
         <v>2.64</v>
-      </c>
-      <c r="G3">
-        <v>2.68</v>
       </c>
       <c r="H3">
         <v>3.75</v>
@@ -1299,7 +1299,7 @@
         <v>2.76</v>
       </c>
       <c r="K3">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="L3">
         <v>1.83</v>
@@ -1308,10 +1308,10 @@
         <v>1.21</v>
       </c>
       <c r="N3">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="O3">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="P3">
         <v>1.33</v>
@@ -1320,7 +1320,7 @@
         <v>3.85</v>
       </c>
       <c r="R3">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="S3">
         <v>9.4</v>
@@ -1329,7 +1329,7 @@
         <v>2.7</v>
       </c>
       <c r="U3">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="V3">
         <v>1.35</v>
@@ -1341,13 +1341,13 @@
         <v>5.8</v>
       </c>
       <c r="Y3">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="Z3">
         <v>24</v>
       </c>
       <c r="AA3">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AB3">
         <v>6.2</v>
@@ -1356,13 +1356,13 @@
         <v>7</v>
       </c>
       <c r="AD3">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AE3">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AF3">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AG3">
         <v>15.5</v>
@@ -1371,7 +1371,7 @@
         <v>38</v>
       </c>
       <c r="AI3">
-        <v>160</v>
+        <v>200</v>
       </c>
       <c r="AJ3">
         <v>46</v>
@@ -1380,7 +1380,7 @@
         <v>55</v>
       </c>
       <c r="AL3">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AM3">
         <v>440</v>
@@ -1389,13 +1389,13 @@
         <v>80</v>
       </c>
       <c r="AO3">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="AP3">
         <v>5.4</v>
       </c>
       <c r="AQ3">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AR3">
         <v>20</v>
@@ -1404,16 +1404,16 @@
         <v>60</v>
       </c>
       <c r="AT3">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="AU3">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AV3">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AW3">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AX3">
         <v>12.5</v>
@@ -1425,10 +1425,10 @@
         <v>32</v>
       </c>
       <c r="BA3">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="BB3">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="BC3">
         <v>38</v>
@@ -1437,73 +1437,73 @@
         <v>70</v>
       </c>
       <c r="BE3">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="BF3">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="BG3">
         <v>90</v>
       </c>
       <c r="BH3">
-        <v>1000</v>
+        <v>4.9</v>
       </c>
       <c r="BI3">
-        <v>1.04</v>
+        <v>2.02</v>
       </c>
       <c r="BJ3">
         <v>1000</v>
       </c>
       <c r="BK3">
-        <v>1.04</v>
+        <v>3.25</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>1.04</v>
+        <v>38</v>
       </c>
       <c r="BN3">
         <v>1000</v>
       </c>
       <c r="BO3">
-        <v>1.04</v>
+        <v>4.7</v>
       </c>
       <c r="BP3">
         <v>1000</v>
       </c>
       <c r="BQ3">
-        <v>1.04</v>
+        <v>3.2</v>
       </c>
       <c r="BR3">
         <v>1000</v>
       </c>
       <c r="BS3">
-        <v>1.04</v>
+        <v>3.2</v>
       </c>
       <c r="BT3">
         <v>1000</v>
       </c>
       <c r="BU3">
-        <v>1.04</v>
+        <v>5.6</v>
       </c>
       <c r="BV3">
         <v>1000</v>
       </c>
       <c r="BW3">
-        <v>1.04</v>
+        <v>3.2</v>
       </c>
       <c r="BX3">
         <v>1000</v>
       </c>
       <c r="BY3">
-        <v>1.04</v>
+        <v>1.38</v>
       </c>
       <c r="BZ3">
         <v>1000</v>
       </c>
       <c r="CA3">
-        <v>1.04</v>
+        <v>1.38</v>
       </c>
       <c r="CB3" t="s">
         <v>144</v>
@@ -1526,67 +1526,67 @@
         <v>127</v>
       </c>
       <c r="F4">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="G4">
         <v>3.2</v>
       </c>
       <c r="H4">
-        <v>2.8</v>
+        <v>2.74</v>
       </c>
       <c r="I4">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="J4">
-        <v>2.92</v>
+        <v>2.98</v>
       </c>
       <c r="K4">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="L4">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="M4">
         <v>1.13</v>
       </c>
       <c r="N4">
-        <v>2.68</v>
+        <v>2.74</v>
       </c>
       <c r="O4">
         <v>1.55</v>
       </c>
       <c r="P4">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="Q4">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="R4">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="S4">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="T4">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="U4">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="V4">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="W4">
         <v>1.45</v>
       </c>
       <c r="X4">
-        <v>11</v>
+        <v>9.4</v>
       </c>
       <c r="Y4">
         <v>8.6</v>
       </c>
       <c r="Z4">
-        <v>28</v>
+        <v>17.5</v>
       </c>
       <c r="AA4">
         <v>75</v>
@@ -1601,25 +1601,25 @@
         <v>14.5</v>
       </c>
       <c r="AE4">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AF4">
-        <v>32</v>
+        <v>19.5</v>
       </c>
       <c r="AG4">
         <v>14.5</v>
       </c>
       <c r="AH4">
-        <v>950</v>
+        <v>22</v>
       </c>
       <c r="AI4">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AJ4">
         <v>90</v>
       </c>
       <c r="AK4">
-        <v>48</v>
+        <v>70</v>
       </c>
       <c r="AL4">
         <v>110</v>
@@ -1631,10 +1631,10 @@
         <v>75</v>
       </c>
       <c r="AO4">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AP4">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AQ4">
         <v>7.4</v>
@@ -1643,7 +1643,7 @@
         <v>14.5</v>
       </c>
       <c r="AS4">
-        <v>8.199999999999999</v>
+        <v>40</v>
       </c>
       <c r="AT4">
         <v>8</v>
@@ -1652,10 +1652,10 @@
         <v>6.2</v>
       </c>
       <c r="AV4">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AW4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AX4">
         <v>16.5</v>
@@ -1667,31 +1667,31 @@
         <v>19</v>
       </c>
       <c r="BA4">
-        <v>8.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BB4">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BC4">
-        <v>7.8</v>
+        <v>9.4</v>
       </c>
       <c r="BD4">
-        <v>8.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BE4">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BF4">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="BG4">
         <v>13</v>
       </c>
       <c r="BH4">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="BI4">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="BJ4">
         <v>11</v>
@@ -1703,7 +1703,7 @@
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="BN4">
         <v>5.9</v>
@@ -1712,10 +1712,10 @@
         <v>4.5</v>
       </c>
       <c r="BP4">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BQ4">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BR4">
         <v>1000</v>
@@ -1733,19 +1733,19 @@
         <v>26</v>
       </c>
       <c r="BW4">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BX4">
         <v>1000</v>
       </c>
       <c r="BY4">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BZ4">
         <v>1000</v>
       </c>
       <c r="CA4">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="CB4" t="s">
         <v>144</v>
@@ -1768,13 +1768,13 @@
         <v>128</v>
       </c>
       <c r="F5">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="G5">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="H5">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="I5">
         <v>4.8</v>
@@ -1804,7 +1804,7 @@
         <v>1.59</v>
       </c>
       <c r="R5">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="S5">
         <v>2.48</v>
@@ -1819,7 +1819,7 @@
         <v>1.27</v>
       </c>
       <c r="W5">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="X5">
         <v>27</v>
@@ -1876,19 +1876,19 @@
         <v>42</v>
       </c>
       <c r="AP5">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AQ5">
         <v>20</v>
       </c>
       <c r="AR5">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AS5">
         <v>60</v>
       </c>
       <c r="AT5">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AU5">
         <v>9</v>
@@ -1897,13 +1897,13 @@
         <v>16.5</v>
       </c>
       <c r="AW5">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AX5">
         <v>11</v>
       </c>
       <c r="AY5">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AZ5">
         <v>14.5</v>
@@ -1912,7 +1912,7 @@
         <v>30</v>
       </c>
       <c r="BB5">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BC5">
         <v>13.5</v>
@@ -1921,7 +1921,7 @@
         <v>22</v>
       </c>
       <c r="BE5">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="BF5">
         <v>7</v>
@@ -2010,25 +2010,25 @@
         <v>129</v>
       </c>
       <c r="F6">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="G6">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="H6">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="I6">
         <v>3.85</v>
       </c>
       <c r="J6">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="K6">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="L6">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="M6">
         <v>1.09</v>
@@ -2037,13 +2037,13 @@
         <v>3.4</v>
       </c>
       <c r="O6">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="P6">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="Q6">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="R6">
         <v>1.29</v>
@@ -2052,7 +2052,7 @@
         <v>4.1</v>
       </c>
       <c r="T6">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="U6">
         <v>2</v>
@@ -2061,7 +2061,7 @@
         <v>1.35</v>
       </c>
       <c r="W6">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="X6">
         <v>12</v>
@@ -2070,22 +2070,22 @@
         <v>13</v>
       </c>
       <c r="Z6">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AA6">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="AB6">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC6">
         <v>7.8</v>
       </c>
       <c r="AD6">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AE6">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AF6">
         <v>14</v>
@@ -2094,7 +2094,7 @@
         <v>11.5</v>
       </c>
       <c r="AH6">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AI6">
         <v>65</v>
@@ -2106,7 +2106,7 @@
         <v>27</v>
       </c>
       <c r="AL6">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AM6">
         <v>120</v>
@@ -2121,19 +2121,19 @@
         <v>10</v>
       </c>
       <c r="AQ6">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AR6">
         <v>22</v>
       </c>
       <c r="AS6">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AT6">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU6">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AV6">
         <v>14</v>
@@ -2142,37 +2142,37 @@
         <v>42</v>
       </c>
       <c r="AX6">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AY6">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AZ6">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BA6">
         <v>50</v>
       </c>
       <c r="BB6">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="BC6">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BD6">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BE6">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="BF6">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="BG6">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="BH6">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="BI6">
         <v>2.54</v>
@@ -2184,10 +2184,10 @@
         <v>7.4</v>
       </c>
       <c r="BL6">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="BM6">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BN6">
         <v>5.1</v>
@@ -2196,40 +2196,40 @@
         <v>4.3</v>
       </c>
       <c r="BP6">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BQ6">
-        <v>6.6</v>
+        <v>11</v>
       </c>
       <c r="BR6">
         <v>36</v>
       </c>
       <c r="BS6">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT6">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BU6">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="BV6">
         <v>34</v>
       </c>
       <c r="BW6">
-        <v>8.199999999999999</v>
+        <v>19</v>
       </c>
       <c r="BX6">
         <v>48</v>
       </c>
       <c r="BY6">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BZ6">
         <v>34</v>
       </c>
       <c r="CA6">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB6" t="s">
         <v>144</v>
@@ -2252,166 +2252,166 @@
         <v>130</v>
       </c>
       <c r="F7">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="G7">
-        <v>2.26</v>
+        <v>2.16</v>
       </c>
       <c r="H7">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="I7">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="J7">
-        <v>1.03</v>
+        <v>3.9</v>
       </c>
       <c r="K7">
         <v>4.2</v>
       </c>
       <c r="L7">
-        <v>1.3</v>
+        <v>1.01</v>
       </c>
       <c r="M7">
         <v>1.01</v>
       </c>
       <c r="N7">
-        <v>2.98</v>
+        <v>4.8</v>
       </c>
       <c r="O7">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="P7">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="Q7">
         <v>1.69</v>
       </c>
       <c r="R7">
-        <v>1.48</v>
+        <v>1.52</v>
       </c>
       <c r="S7">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="T7">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="U7">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="V7">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W7">
-        <v>1.79</v>
+        <v>1.86</v>
       </c>
       <c r="X7">
+        <v>24</v>
+      </c>
+      <c r="Y7">
+        <v>22</v>
+      </c>
+      <c r="Z7">
+        <v>34</v>
+      </c>
+      <c r="AA7">
+        <v>70</v>
+      </c>
+      <c r="AB7">
+        <v>13</v>
+      </c>
+      <c r="AC7">
+        <v>10.5</v>
+      </c>
+      <c r="AD7">
+        <v>16.5</v>
+      </c>
+      <c r="AE7">
+        <v>42</v>
+      </c>
+      <c r="AF7">
+        <v>16</v>
+      </c>
+      <c r="AG7">
+        <v>11.5</v>
+      </c>
+      <c r="AH7">
+        <v>17</v>
+      </c>
+      <c r="AI7">
+        <v>42</v>
+      </c>
+      <c r="AJ7">
+        <v>27</v>
+      </c>
+      <c r="AK7">
+        <v>23</v>
+      </c>
+      <c r="AL7">
+        <v>29</v>
+      </c>
+      <c r="AM7">
+        <v>75</v>
+      </c>
+      <c r="AN7">
+        <v>12</v>
+      </c>
+      <c r="AO7">
+        <v>32</v>
+      </c>
+      <c r="AP7">
+        <v>19</v>
+      </c>
+      <c r="AQ7">
+        <v>14</v>
+      </c>
+      <c r="AR7">
         <v>21</v>
       </c>
-      <c r="Y7">
-        <v>1000</v>
-      </c>
-      <c r="Z7">
-        <v>1000</v>
-      </c>
-      <c r="AA7">
-        <v>1000</v>
-      </c>
-      <c r="AB7">
-        <v>26</v>
-      </c>
-      <c r="AC7">
-        <v>17.5</v>
-      </c>
-      <c r="AD7">
-        <v>1000</v>
-      </c>
-      <c r="AE7">
-        <v>1000</v>
-      </c>
-      <c r="AF7">
-        <v>1000</v>
-      </c>
-      <c r="AG7">
-        <v>26</v>
-      </c>
-      <c r="AH7">
-        <v>1000</v>
-      </c>
-      <c r="AI7">
-        <v>1000</v>
-      </c>
-      <c r="AJ7">
-        <v>1000</v>
-      </c>
-      <c r="AK7">
-        <v>1000</v>
-      </c>
-      <c r="AL7">
-        <v>1000</v>
-      </c>
-      <c r="AM7">
-        <v>1000</v>
-      </c>
-      <c r="AN7">
-        <v>1000</v>
-      </c>
-      <c r="AO7">
-        <v>1000</v>
-      </c>
-      <c r="AP7">
-        <v>6.4</v>
-      </c>
-      <c r="AQ7">
-        <v>1.22</v>
-      </c>
-      <c r="AR7">
-        <v>1.22</v>
-      </c>
       <c r="AS7">
-        <v>1.22</v>
+        <v>6.6</v>
       </c>
       <c r="AT7">
-        <v>6.4</v>
+        <v>10.5</v>
       </c>
       <c r="AU7">
-        <v>1.14</v>
+        <v>8.4</v>
       </c>
       <c r="AV7">
-        <v>1.22</v>
+        <v>13</v>
       </c>
       <c r="AW7">
-        <v>1.22</v>
+        <v>6.2</v>
       </c>
       <c r="AX7">
-        <v>1.22</v>
+        <v>13</v>
       </c>
       <c r="AY7">
-        <v>5.4</v>
+        <v>9</v>
       </c>
       <c r="AZ7">
-        <v>1.22</v>
+        <v>13.5</v>
       </c>
       <c r="BA7">
-        <v>1.22</v>
+        <v>6.2</v>
       </c>
       <c r="BB7">
-        <v>1.22</v>
+        <v>19.5</v>
       </c>
       <c r="BC7">
-        <v>1.22</v>
+        <v>16.5</v>
       </c>
       <c r="BD7">
-        <v>1.22</v>
+        <v>5.8</v>
       </c>
       <c r="BE7">
-        <v>1.22</v>
+        <v>6.6</v>
       </c>
       <c r="BF7">
-        <v>1.22</v>
+        <v>9.4</v>
       </c>
       <c r="BG7">
-        <v>1.22</v>
+        <v>5.9</v>
       </c>
       <c r="BH7">
         <v>1000</v>
@@ -2500,10 +2500,10 @@
         <v>2</v>
       </c>
       <c r="H8">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="I8">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="J8">
         <v>3.1</v>
@@ -2614,7 +2614,7 @@
         <v>5.5</v>
       </c>
       <c r="AT8">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="AU8">
         <v>6.6</v>
@@ -2736,13 +2736,13 @@
         <v>132</v>
       </c>
       <c r="F9">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="G9">
         <v>1.69</v>
       </c>
       <c r="H9">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="I9">
         <v>5.6</v>
@@ -2751,7 +2751,7 @@
         <v>4.9</v>
       </c>
       <c r="K9">
-        <v>6.2</v>
+        <v>5.7</v>
       </c>
       <c r="L9">
         <v>1.01</v>
@@ -2781,7 +2781,7 @@
         <v>1.46</v>
       </c>
       <c r="U9">
-        <v>2.74</v>
+        <v>2.82</v>
       </c>
       <c r="V9">
         <v>1.21</v>
@@ -2790,7 +2790,7 @@
         <v>2.44</v>
       </c>
       <c r="X9">
-        <v>950</v>
+        <v>240</v>
       </c>
       <c r="Y9">
         <v>950</v>
@@ -2811,7 +2811,7 @@
         <v>24</v>
       </c>
       <c r="AE9">
-        <v>55</v>
+        <v>200</v>
       </c>
       <c r="AF9">
         <v>19.5</v>
@@ -2841,58 +2841,58 @@
         <v>4.8</v>
       </c>
       <c r="AO9">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AP9">
-        <v>6.8</v>
+        <v>32</v>
       </c>
       <c r="AQ9">
-        <v>6.4</v>
+        <v>18</v>
       </c>
       <c r="AR9">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AS9">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AT9">
-        <v>5.8</v>
+        <v>15</v>
       </c>
       <c r="AU9">
-        <v>5.2</v>
+        <v>11</v>
       </c>
       <c r="AV9">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="AW9">
         <v>7</v>
       </c>
       <c r="AX9">
-        <v>5.6</v>
+        <v>14.5</v>
       </c>
       <c r="AY9">
-        <v>4.8</v>
+        <v>10</v>
       </c>
       <c r="AZ9">
-        <v>5.5</v>
+        <v>12.5</v>
       </c>
       <c r="BA9">
-        <v>6.6</v>
+        <v>9</v>
       </c>
       <c r="BB9">
-        <v>5.7</v>
+        <v>16.5</v>
       </c>
       <c r="BC9">
-        <v>5.3</v>
+        <v>12.5</v>
       </c>
       <c r="BD9">
         <v>18</v>
       </c>
       <c r="BE9">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="BF9">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BG9">
         <v>6.2</v>
@@ -2981,10 +2981,10 @@
         <v>2.56</v>
       </c>
       <c r="G10">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="H10">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="I10">
         <v>3.2</v>
@@ -2993,43 +2993,43 @@
         <v>3.25</v>
       </c>
       <c r="K10">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="L10">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="M10">
         <v>1.07</v>
       </c>
       <c r="N10">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="O10">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="P10">
-        <v>1.86</v>
+        <v>1.81</v>
       </c>
       <c r="Q10">
         <v>2</v>
       </c>
       <c r="R10">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="S10">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="T10">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="U10">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="V10">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="W10">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="X10">
         <v>15.5</v>
@@ -3047,7 +3047,7 @@
         <v>12.5</v>
       </c>
       <c r="AC10">
-        <v>9.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD10">
         <v>16</v>
@@ -3095,55 +3095,55 @@
         <v>15</v>
       </c>
       <c r="AS10">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="AT10">
         <v>9</v>
       </c>
       <c r="AU10">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="AV10">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="AW10">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="AX10">
         <v>12.5</v>
       </c>
       <c r="AY10">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AZ10">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="BA10">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="BB10">
-        <v>4.2</v>
+        <v>13</v>
       </c>
       <c r="BC10">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="BD10">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="BE10">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="BF10">
         <v>17.5</v>
       </c>
       <c r="BG10">
-        <v>4.1</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH10">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="BI10">
-        <v>2.68</v>
+        <v>2.64</v>
       </c>
       <c r="BJ10">
         <v>11.5</v>
@@ -3155,49 +3155,49 @@
         <v>150</v>
       </c>
       <c r="BM10">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="BN10">
         <v>6.6</v>
       </c>
       <c r="BO10">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BP10">
         <v>21</v>
       </c>
       <c r="BQ10">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="BR10">
+        <v>36</v>
+      </c>
+      <c r="BS10">
+        <v>5.3</v>
+      </c>
+      <c r="BT10">
+        <v>7.2</v>
+      </c>
+      <c r="BU10">
+        <v>5.2</v>
+      </c>
+      <c r="BV10">
+        <v>30</v>
+      </c>
+      <c r="BW10">
+        <v>5.1</v>
+      </c>
+      <c r="BX10">
         <v>40</v>
       </c>
-      <c r="BS10">
-        <v>5.7</v>
-      </c>
-      <c r="BT10">
-        <v>6.4</v>
-      </c>
-      <c r="BU10">
-        <v>4.6</v>
-      </c>
-      <c r="BV10">
-        <v>29</v>
-      </c>
-      <c r="BW10">
-        <v>5.4</v>
-      </c>
-      <c r="BX10">
-        <v>42</v>
-      </c>
       <c r="BY10">
-        <v>5.7</v>
+        <v>5.3</v>
       </c>
       <c r="BZ10">
         <v>36</v>
       </c>
       <c r="CA10">
-        <v>5.6</v>
+        <v>5.3</v>
       </c>
       <c r="CB10" t="s">
         <v>144</v>
@@ -3220,25 +3220,25 @@
         <v>134</v>
       </c>
       <c r="F11">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="G11">
-        <v>2.9</v>
+        <v>2.86</v>
       </c>
       <c r="H11">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="I11">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="J11">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="K11">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="L11">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="M11">
         <v>1.07</v>
@@ -3247,31 +3247,31 @@
         <v>3.5</v>
       </c>
       <c r="O11">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="P11">
         <v>1.86</v>
       </c>
       <c r="Q11">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="R11">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="S11">
         <v>3.4</v>
       </c>
       <c r="T11">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="U11">
         <v>2.1</v>
       </c>
       <c r="V11">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="W11">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="X11">
         <v>16.5</v>
@@ -3280,52 +3280,52 @@
         <v>14</v>
       </c>
       <c r="Z11">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AA11">
         <v>55</v>
       </c>
       <c r="AB11">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AC11">
-        <v>9.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD11">
         <v>16</v>
       </c>
       <c r="AE11">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="AF11">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AG11">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AH11">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AI11">
-        <v>55</v>
+        <v>150</v>
       </c>
       <c r="AJ11">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="AK11">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AL11">
         <v>55</v>
       </c>
       <c r="AM11">
-        <v>120</v>
+        <v>380</v>
       </c>
       <c r="AN11">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AO11">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="AP11">
         <v>10</v>
@@ -3334,13 +3334,13 @@
         <v>8.4</v>
       </c>
       <c r="AR11">
-        <v>14</v>
+        <v>16.5</v>
       </c>
       <c r="AS11">
-        <v>4.2</v>
+        <v>14.5</v>
       </c>
       <c r="AT11">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU11">
         <v>6.6</v>
@@ -3349,31 +3349,31 @@
         <v>9.6</v>
       </c>
       <c r="AW11">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="AX11">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AY11">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="AZ11">
         <v>12.5</v>
       </c>
       <c r="BA11">
-        <v>4.2</v>
+        <v>5.2</v>
       </c>
       <c r="BB11">
-        <v>4.1</v>
+        <v>16</v>
       </c>
       <c r="BC11">
-        <v>4</v>
+        <v>14.5</v>
       </c>
       <c r="BD11">
-        <v>4.2</v>
+        <v>5.3</v>
       </c>
       <c r="BE11">
-        <v>4.3</v>
+        <v>5.5</v>
       </c>
       <c r="BF11">
         <v>19</v>
@@ -3385,7 +3385,7 @@
         <v>3.45</v>
       </c>
       <c r="BI11">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="BJ11">
         <v>9.800000000000001</v>
@@ -3436,7 +3436,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BZ11">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="CA11">
         <v>7.6</v>
@@ -3462,166 +3462,166 @@
         <v>135</v>
       </c>
       <c r="F12">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="G12">
         <v>2.42</v>
       </c>
       <c r="H12">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="I12">
-        <v>4.3</v>
+        <v>3.65</v>
       </c>
       <c r="J12">
-        <v>2.84</v>
+        <v>3.35</v>
       </c>
       <c r="K12">
-        <v>3.75</v>
+        <v>3.55</v>
       </c>
       <c r="L12">
         <v>1.01</v>
       </c>
       <c r="M12">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="N12">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="O12">
         <v>1.28</v>
       </c>
       <c r="P12">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="Q12">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="R12">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="S12">
-        <v>2.78</v>
+        <v>3.35</v>
       </c>
       <c r="T12">
-        <v>1.59</v>
+        <v>1.74</v>
       </c>
       <c r="U12">
-        <v>1.96</v>
+        <v>2.18</v>
       </c>
       <c r="V12">
-        <v>1.31</v>
+        <v>1.38</v>
       </c>
       <c r="W12">
         <v>1.7</v>
       </c>
       <c r="X12">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="Y12">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="Z12">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AA12">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AB12">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AC12">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="AD12">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AE12">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AF12">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AG12">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AH12">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AI12">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AJ12">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AK12">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AL12">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AM12">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AN12">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AO12">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AP12">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AQ12">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AR12">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="AS12">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="AT12">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="AU12">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AV12">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AW12">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="AX12">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="AY12">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ12">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="BA12">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BB12">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="BC12">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BD12">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BE12">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BF12">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="BG12">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BH12">
         <v>1000</v>
@@ -3704,13 +3704,13 @@
         <v>136</v>
       </c>
       <c r="F13">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="G13">
         <v>970</v>
       </c>
       <c r="H13">
-        <v>1.04</v>
+        <v>2</v>
       </c>
       <c r="I13">
         <v>190</v>
@@ -3728,13 +3728,13 @@
         <v>1.01</v>
       </c>
       <c r="N13">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="O13">
         <v>1.23</v>
       </c>
       <c r="P13">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Q13">
         <v>1.23</v>
@@ -3749,13 +3749,13 @@
         <v>1.01</v>
       </c>
       <c r="U13">
-        <v>1.56</v>
+        <v>1.01</v>
       </c>
       <c r="V13">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W13">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X13">
         <v>1000</v>
@@ -3812,52 +3812,52 @@
         <v>1000</v>
       </c>
       <c r="AP13">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ13">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR13">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS13">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT13">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU13">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV13">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW13">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX13">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY13">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ13">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA13">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB13">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC13">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD13">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE13">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF13">
         <v>1.01</v>
@@ -3946,226 +3946,226 @@
         <v>137</v>
       </c>
       <c r="F14">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="G14">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H14">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="I14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="J14">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="K14">
-        <v>0</v>
+        <v>950</v>
       </c>
       <c r="L14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M14">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="N14">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O14">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="P14">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Q14">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="R14">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S14">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="T14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB14">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="AC14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF14">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="AG14">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="AH14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ14">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="AK14">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="AL14">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="AM14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN14">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="AO14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB14" t="s">
         <v>144</v>
@@ -4188,7 +4188,7 @@
         <v>138</v>
       </c>
       <c r="F15">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="G15">
         <v>2.46</v>
@@ -4200,13 +4200,13 @@
         <v>3.6</v>
       </c>
       <c r="J15">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="K15">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="L15">
-        <v>1.41</v>
+        <v>1.18</v>
       </c>
       <c r="M15">
         <v>1.07</v>
@@ -4215,34 +4215,34 @@
         <v>3.6</v>
       </c>
       <c r="O15">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="P15">
         <v>1.87</v>
       </c>
       <c r="Q15">
-        <v>1.85</v>
+        <v>1.94</v>
       </c>
       <c r="R15">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="S15">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="T15">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="U15">
         <v>2.12</v>
       </c>
       <c r="V15">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="W15">
         <v>1.68</v>
       </c>
       <c r="X15">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="Y15">
         <v>16</v>
@@ -4272,7 +4272,7 @@
         <v>14</v>
       </c>
       <c r="AH15">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="AI15">
         <v>60</v>
@@ -4296,16 +4296,16 @@
         <v>48</v>
       </c>
       <c r="AP15">
-        <v>3.5</v>
+        <v>12</v>
       </c>
       <c r="AQ15">
-        <v>3.45</v>
+        <v>11</v>
       </c>
       <c r="AR15">
-        <v>3.8</v>
+        <v>20</v>
       </c>
       <c r="AS15">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="AT15">
         <v>7.6</v>
@@ -4314,40 +4314,40 @@
         <v>6</v>
       </c>
       <c r="AV15">
-        <v>3.5</v>
+        <v>12</v>
       </c>
       <c r="AW15">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="AX15">
-        <v>3.55</v>
+        <v>13</v>
       </c>
       <c r="AY15">
-        <v>3.35</v>
+        <v>9.6</v>
       </c>
       <c r="AZ15">
-        <v>3.6</v>
+        <v>14.5</v>
       </c>
       <c r="BA15">
+        <v>4.3</v>
+      </c>
+      <c r="BB15">
         <v>4.1</v>
       </c>
-      <c r="BB15">
-        <v>3.9</v>
-      </c>
       <c r="BC15">
-        <v>3.85</v>
+        <v>21</v>
       </c>
       <c r="BD15">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="BE15">
+        <v>4.5</v>
+      </c>
+      <c r="BF15">
+        <v>16.5</v>
+      </c>
+      <c r="BG15">
         <v>4.2</v>
-      </c>
-      <c r="BF15">
-        <v>3.7</v>
-      </c>
-      <c r="BG15">
-        <v>4</v>
       </c>
       <c r="BH15">
         <v>3.5</v>
@@ -4430,226 +4430,226 @@
         <v>139</v>
       </c>
       <c r="F16">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
       <c r="G16">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="H16">
-        <v>4.5</v>
+        <v>5.4</v>
       </c>
       <c r="I16">
-        <v>5</v>
+        <v>6.2</v>
       </c>
       <c r="J16">
-        <v>3.7</v>
+        <v>3.25</v>
       </c>
       <c r="K16">
-        <v>4.3</v>
+        <v>3.75</v>
       </c>
       <c r="L16">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="M16">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="N16">
         <v>2.84</v>
       </c>
       <c r="O16">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="P16">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="Q16">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="R16">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="S16">
         <v>4.7</v>
       </c>
       <c r="T16">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="U16">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="V16">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="W16">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="X16">
-        <v>14.5</v>
+        <v>10</v>
       </c>
       <c r="Y16">
-        <v>13</v>
+        <v>15.5</v>
       </c>
       <c r="Z16">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="AA16">
-        <v>180</v>
+        <v>700</v>
       </c>
       <c r="AB16">
         <v>6.8</v>
       </c>
       <c r="AC16">
-        <v>9.6</v>
+        <v>8</v>
       </c>
       <c r="AD16">
-        <v>19.5</v>
+        <v>24</v>
       </c>
       <c r="AE16">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="AF16">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AG16">
         <v>11</v>
       </c>
       <c r="AH16">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="AI16">
-        <v>110</v>
+        <v>540</v>
       </c>
       <c r="AJ16">
         <v>21</v>
       </c>
       <c r="AK16">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AL16">
         <v>55</v>
       </c>
       <c r="AM16">
-        <v>270</v>
+        <v>500</v>
       </c>
       <c r="AN16">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AO16">
-        <v>170</v>
+        <v>210</v>
       </c>
       <c r="AP16">
-        <v>8.800000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="AQ16">
-        <v>10.5</v>
+        <v>13</v>
       </c>
       <c r="AR16">
-        <v>7.4</v>
+        <v>15</v>
       </c>
       <c r="AS16">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AT16">
-        <v>5</v>
+        <v>5.9</v>
       </c>
       <c r="AU16">
         <v>7</v>
       </c>
       <c r="AV16">
-        <v>16.5</v>
+        <v>20</v>
       </c>
       <c r="AW16">
-        <v>8.6</v>
+        <v>10.5</v>
       </c>
       <c r="AX16">
-        <v>7.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY16">
-        <v>7.8</v>
+        <v>9.4</v>
       </c>
       <c r="AZ16">
         <v>21</v>
       </c>
       <c r="BA16">
-        <v>8.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BB16">
-        <v>14.5</v>
+        <v>18</v>
       </c>
       <c r="BC16">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="BD16">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="BE16">
-        <v>9.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="BF16">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="BG16">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="BH16">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="BI16">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="BJ16">
         <v>12</v>
       </c>
       <c r="BK16">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BL16">
         <v>1000</v>
       </c>
       <c r="BM16">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="BN16">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BO16">
-        <v>3.3</v>
+        <v>3.75</v>
       </c>
       <c r="BP16">
         <v>14</v>
       </c>
       <c r="BQ16">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BR16">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="BS16">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BT16">
         <v>9</v>
       </c>
       <c r="BU16">
-        <v>5.5</v>
+        <v>6.6</v>
       </c>
       <c r="BV16">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BW16">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BX16">
         <v>1000</v>
       </c>
       <c r="BY16">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BZ16">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="CA16">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="CB16" t="s">
         <v>144</v>
@@ -4672,16 +4672,16 @@
         <v>140</v>
       </c>
       <c r="F17">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="G17">
         <v>2.48</v>
       </c>
       <c r="H17">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="I17">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="J17">
         <v>3.05</v>
@@ -4690,16 +4690,16 @@
         <v>3.15</v>
       </c>
       <c r="L17">
-        <v>1.47</v>
+        <v>1.57</v>
       </c>
       <c r="M17">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="N17">
         <v>2.66</v>
       </c>
       <c r="O17">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="P17">
         <v>1.56</v>
@@ -4714,124 +4714,124 @@
         <v>5.4</v>
       </c>
       <c r="T17">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="U17">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="V17">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W17">
         <v>1.67</v>
       </c>
       <c r="X17">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="Y17">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="Z17">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="AA17">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AB17">
         <v>7.6</v>
       </c>
       <c r="AC17">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AD17">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AE17">
         <v>75</v>
       </c>
       <c r="AF17">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AG17">
         <v>12.5</v>
       </c>
       <c r="AH17">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="AI17">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="AJ17">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AK17">
+        <v>40</v>
+      </c>
+      <c r="AL17">
+        <v>1000</v>
+      </c>
+      <c r="AM17">
+        <v>1000</v>
+      </c>
+      <c r="AN17">
         <v>42</v>
       </c>
-      <c r="AL17">
-        <v>75</v>
-      </c>
-      <c r="AM17">
-        <v>220</v>
-      </c>
-      <c r="AN17">
-        <v>44</v>
-      </c>
       <c r="AO17">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="AP17">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AQ17">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR17">
-        <v>17.5</v>
+        <v>15.5</v>
       </c>
       <c r="AS17">
-        <v>6</v>
+        <v>32</v>
       </c>
       <c r="AT17">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AU17">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AV17">
         <v>14</v>
       </c>
       <c r="AW17">
-        <v>5.9</v>
+        <v>29</v>
       </c>
       <c r="AX17">
         <v>12</v>
       </c>
       <c r="AY17">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AZ17">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BA17">
-        <v>6</v>
+        <v>36</v>
       </c>
       <c r="BB17">
-        <v>5.6</v>
+        <v>21</v>
       </c>
       <c r="BC17">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="BD17">
-        <v>5.9</v>
+        <v>32</v>
       </c>
       <c r="BE17">
-        <v>6.2</v>
+        <v>48</v>
       </c>
       <c r="BF17">
-        <v>5.5</v>
+        <v>22</v>
       </c>
       <c r="BG17">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="BH17">
         <v>3.15</v>
@@ -4843,13 +4843,13 @@
         <v>13.5</v>
       </c>
       <c r="BK17">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="BL17">
         <v>1000</v>
       </c>
       <c r="BM17">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="BN17">
         <v>6</v>
@@ -4861,16 +4861,16 @@
         <v>26</v>
       </c>
       <c r="BQ17">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="BR17">
         <v>55</v>
       </c>
       <c r="BS17">
-        <v>4.5</v>
+        <v>5.1</v>
       </c>
       <c r="BT17">
-        <v>8</v>
+        <v>6.6</v>
       </c>
       <c r="BU17">
         <v>5</v>
@@ -4879,19 +4879,19 @@
         <v>44</v>
       </c>
       <c r="BW17">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="BX17">
         <v>70</v>
       </c>
       <c r="BY17">
-        <v>4.6</v>
+        <v>5.2</v>
       </c>
       <c r="BZ17">
         <v>60</v>
       </c>
       <c r="CA17">
-        <v>4.5</v>
+        <v>5.1</v>
       </c>
       <c r="CB17" t="s">
         <v>144</v>
@@ -4917,43 +4917,43 @@
         <v>1.74</v>
       </c>
       <c r="G18">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="H18">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="I18">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="J18">
-        <v>3.15</v>
+        <v>2.8</v>
       </c>
       <c r="K18">
-        <v>6.2</v>
+        <v>4.4</v>
       </c>
       <c r="L18">
+        <v>1.34</v>
+      </c>
+      <c r="M18">
+        <v>1.04</v>
+      </c>
+      <c r="N18">
+        <v>3.05</v>
+      </c>
+      <c r="O18">
         <v>1.39</v>
       </c>
-      <c r="M18">
-        <v>1.09</v>
-      </c>
-      <c r="N18">
-        <v>2.4</v>
-      </c>
-      <c r="O18">
-        <v>1.41</v>
-      </c>
       <c r="P18">
-        <v>1.53</v>
+        <v>1.64</v>
       </c>
       <c r="Q18">
-        <v>2.18</v>
+        <v>1.92</v>
       </c>
       <c r="R18">
         <v>1.18</v>
       </c>
       <c r="S18">
-        <v>2.96</v>
+        <v>2.56</v>
       </c>
       <c r="T18">
         <v>1.11</v>
@@ -4962,118 +4962,118 @@
         <v>1.11</v>
       </c>
       <c r="V18">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="W18">
+        <v>1.86</v>
+      </c>
+      <c r="X18">
+        <v>970</v>
+      </c>
+      <c r="Y18">
+        <v>950</v>
+      </c>
+      <c r="Z18">
+        <v>500</v>
+      </c>
+      <c r="AA18">
+        <v>900</v>
+      </c>
+      <c r="AB18">
+        <v>970</v>
+      </c>
+      <c r="AC18">
+        <v>950</v>
+      </c>
+      <c r="AD18">
+        <v>950</v>
+      </c>
+      <c r="AE18">
+        <v>500</v>
+      </c>
+      <c r="AF18">
+        <v>500</v>
+      </c>
+      <c r="AG18">
+        <v>500</v>
+      </c>
+      <c r="AH18">
+        <v>950</v>
+      </c>
+      <c r="AI18">
+        <v>500</v>
+      </c>
+      <c r="AJ18">
+        <v>900</v>
+      </c>
+      <c r="AK18">
+        <v>500</v>
+      </c>
+      <c r="AL18">
+        <v>500</v>
+      </c>
+      <c r="AM18">
+        <v>580</v>
+      </c>
+      <c r="AN18">
+        <v>500</v>
+      </c>
+      <c r="AO18">
+        <v>1000</v>
+      </c>
+      <c r="AP18">
+        <v>2.5</v>
+      </c>
+      <c r="AQ18">
+        <v>1.7</v>
+      </c>
+      <c r="AR18">
+        <v>1.8</v>
+      </c>
+      <c r="AS18">
+        <v>1.82</v>
+      </c>
+      <c r="AT18">
+        <v>4.2</v>
+      </c>
+      <c r="AU18">
+        <v>4.4</v>
+      </c>
+      <c r="AV18">
+        <v>1.76</v>
+      </c>
+      <c r="AW18">
+        <v>1.82</v>
+      </c>
+      <c r="AX18">
+        <v>2.5</v>
+      </c>
+      <c r="AY18">
+        <v>1.67</v>
+      </c>
+      <c r="AZ18">
+        <v>1.77</v>
+      </c>
+      <c r="BA18">
+        <v>1.82</v>
+      </c>
+      <c r="BB18">
+        <v>1.79</v>
+      </c>
+      <c r="BC18">
+        <v>1.78</v>
+      </c>
+      <c r="BD18">
+        <v>1.81</v>
+      </c>
+      <c r="BE18">
+        <v>1.82</v>
+      </c>
+      <c r="BF18">
+        <v>4.4</v>
+      </c>
+      <c r="BG18">
         <v>1.83</v>
-      </c>
-      <c r="X18">
-        <v>1000</v>
-      </c>
-      <c r="Y18">
-        <v>1000</v>
-      </c>
-      <c r="Z18">
-        <v>1000</v>
-      </c>
-      <c r="AA18">
-        <v>1000</v>
-      </c>
-      <c r="AB18">
-        <v>1000</v>
-      </c>
-      <c r="AC18">
-        <v>1000</v>
-      </c>
-      <c r="AD18">
-        <v>1000</v>
-      </c>
-      <c r="AE18">
-        <v>1000</v>
-      </c>
-      <c r="AF18">
-        <v>1000</v>
-      </c>
-      <c r="AG18">
-        <v>1000</v>
-      </c>
-      <c r="AH18">
-        <v>1000</v>
-      </c>
-      <c r="AI18">
-        <v>1000</v>
-      </c>
-      <c r="AJ18">
-        <v>1000</v>
-      </c>
-      <c r="AK18">
-        <v>1000</v>
-      </c>
-      <c r="AL18">
-        <v>1000</v>
-      </c>
-      <c r="AM18">
-        <v>1000</v>
-      </c>
-      <c r="AN18">
-        <v>1000</v>
-      </c>
-      <c r="AO18">
-        <v>1000</v>
-      </c>
-      <c r="AP18">
-        <v>1.01</v>
-      </c>
-      <c r="AQ18">
-        <v>1.01</v>
-      </c>
-      <c r="AR18">
-        <v>1.01</v>
-      </c>
-      <c r="AS18">
-        <v>1.01</v>
-      </c>
-      <c r="AT18">
-        <v>1.01</v>
-      </c>
-      <c r="AU18">
-        <v>1.01</v>
-      </c>
-      <c r="AV18">
-        <v>1.01</v>
-      </c>
-      <c r="AW18">
-        <v>1.01</v>
-      </c>
-      <c r="AX18">
-        <v>1.01</v>
-      </c>
-      <c r="AY18">
-        <v>1.01</v>
-      </c>
-      <c r="AZ18">
-        <v>1.01</v>
-      </c>
-      <c r="BA18">
-        <v>1.01</v>
-      </c>
-      <c r="BB18">
-        <v>1.01</v>
-      </c>
-      <c r="BC18">
-        <v>1.01</v>
-      </c>
-      <c r="BD18">
-        <v>1.01</v>
-      </c>
-      <c r="BE18">
-        <v>1.01</v>
-      </c>
-      <c r="BF18">
-        <v>1.01</v>
-      </c>
-      <c r="BG18">
-        <v>1.01</v>
       </c>
       <c r="BH18">
         <v>1000</v>
@@ -5159,10 +5159,10 @@
         <v>1.97</v>
       </c>
       <c r="G19">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="H19">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="I19">
         <v>5.5</v>
@@ -5180,7 +5180,7 @@
         <v>1.14</v>
       </c>
       <c r="N19">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="O19">
         <v>1.58</v>
@@ -5201,13 +5201,13 @@
         <v>2.32</v>
       </c>
       <c r="U19">
-        <v>1.57</v>
+        <v>1.63</v>
       </c>
       <c r="V19">
         <v>1.22</v>
       </c>
       <c r="W19">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="X19">
         <v>8.4</v>
@@ -5276,7 +5276,7 @@
         <v>7.4</v>
       </c>
       <c r="AT19">
-        <v>3.5</v>
+        <v>5.2</v>
       </c>
       <c r="AU19">
         <v>5.9</v>
@@ -5291,7 +5291,7 @@
         <v>4.8</v>
       </c>
       <c r="AY19">
-        <v>4.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ19">
         <v>18</v>
@@ -5303,7 +5303,7 @@
         <v>18</v>
       </c>
       <c r="BC19">
-        <v>6.2</v>
+        <v>21</v>
       </c>
       <c r="BD19">
         <v>7</v>
@@ -5401,28 +5401,28 @@
         <v>2.7</v>
       </c>
       <c r="G20">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="H20">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="I20">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="J20">
-        <v>3.25</v>
+        <v>3.8</v>
       </c>
       <c r="K20">
         <v>4.1</v>
       </c>
       <c r="L20">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="M20">
         <v>1.01</v>
       </c>
       <c r="N20">
-        <v>5.2</v>
+        <v>4.7</v>
       </c>
       <c r="O20">
         <v>1.15</v>
@@ -5563,55 +5563,55 @@
         <v>5.4</v>
       </c>
       <c r="BI20">
-        <v>2.6</v>
+        <v>2.52</v>
       </c>
       <c r="BJ20">
         <v>10</v>
       </c>
       <c r="BK20">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="BL20">
         <v>85</v>
       </c>
       <c r="BM20">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="BN20">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BO20">
-        <v>2.92</v>
+        <v>2.98</v>
       </c>
       <c r="BP20">
         <v>24</v>
       </c>
       <c r="BQ20">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="BR20">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="BS20">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="BT20">
         <v>7</v>
       </c>
       <c r="BU20">
-        <v>4.4</v>
+        <v>2.82</v>
       </c>
       <c r="BV20">
         <v>19</v>
       </c>
       <c r="BW20">
-        <v>3.95</v>
+        <v>3.8</v>
       </c>
       <c r="BX20">
         <v>27</v>
       </c>
       <c r="BY20">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="BZ20">
         <v>0</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-06.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-06.xlsx
@@ -448,7 +448,7 @@
     <t>Always Ready</t>
   </si>
   <si>
-    <t>2026-08-05 19:02:54</t>
+    <t>2026-08-05 21:13:17</t>
   </si>
 </sst>
 </file>
@@ -1042,124 +1042,124 @@
         <v>125</v>
       </c>
       <c r="F2">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="G2">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="H2">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="I2">
-        <v>18.5</v>
+        <v>23</v>
       </c>
       <c r="J2">
-        <v>8.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="K2">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="L2">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="M2">
         <v>1.01</v>
       </c>
       <c r="N2">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="O2">
         <v>1.07</v>
       </c>
       <c r="P2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q2">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="R2">
-        <v>2.66</v>
+        <v>2.4</v>
       </c>
       <c r="S2">
-        <v>1.58</v>
+        <v>1.67</v>
       </c>
       <c r="T2">
-        <v>1.77</v>
+        <v>1.9</v>
       </c>
       <c r="U2">
-        <v>2.16</v>
+        <v>1.96</v>
       </c>
       <c r="V2">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="W2">
-        <v>6</v>
+        <v>7.2</v>
       </c>
       <c r="X2">
-        <v>80</v>
+        <v>110</v>
       </c>
       <c r="Y2">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="Z2">
-        <v>330</v>
+        <v>1000</v>
       </c>
       <c r="AA2">
         <v>1000</v>
       </c>
       <c r="AB2">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AC2">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="AD2">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AE2">
-        <v>270</v>
+        <v>1000</v>
       </c>
       <c r="AF2">
+        <v>13</v>
+      </c>
+      <c r="AG2">
+        <v>17.5</v>
+      </c>
+      <c r="AH2">
+        <v>1000</v>
+      </c>
+      <c r="AI2">
+        <v>220</v>
+      </c>
+      <c r="AJ2">
+        <v>11</v>
+      </c>
+      <c r="AK2">
         <v>15</v>
       </c>
-      <c r="AG2">
-        <v>17</v>
-      </c>
-      <c r="AH2">
-        <v>34</v>
-      </c>
-      <c r="AI2">
-        <v>140</v>
-      </c>
-      <c r="AJ2">
-        <v>12.5</v>
-      </c>
-      <c r="AK2">
-        <v>15.5</v>
-      </c>
       <c r="AL2">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="AM2">
-        <v>120</v>
+        <v>160</v>
       </c>
       <c r="AN2">
-        <v>2.34</v>
+        <v>2.5</v>
       </c>
       <c r="AO2">
-        <v>170</v>
+        <v>310</v>
       </c>
       <c r="AP2">
-        <v>9.199999999999999</v>
+        <v>5.8</v>
       </c>
       <c r="AQ2">
-        <v>25</v>
+        <v>6.6</v>
       </c>
       <c r="AR2">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AS2">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="AT2">
         <v>20</v>
@@ -1168,94 +1168,94 @@
         <v>21</v>
       </c>
       <c r="AV2">
-        <v>9.199999999999999</v>
+        <v>55</v>
       </c>
       <c r="AW2">
-        <v>10</v>
+        <v>3.75</v>
       </c>
       <c r="AX2">
-        <v>11.5</v>
+        <v>9.6</v>
       </c>
       <c r="AY2">
+        <v>12.5</v>
+      </c>
+      <c r="AZ2">
+        <v>25</v>
+      </c>
+      <c r="BA2">
+        <v>3.7</v>
+      </c>
+      <c r="BB2">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BC2">
         <v>12</v>
       </c>
-      <c r="AZ2">
-        <v>8</v>
-      </c>
-      <c r="BA2">
-        <v>9.6</v>
-      </c>
-      <c r="BB2">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BC2">
+      <c r="BD2">
+        <v>21</v>
+      </c>
+      <c r="BE2">
+        <v>70</v>
+      </c>
+      <c r="BF2">
+        <v>1.79</v>
+      </c>
+      <c r="BG2">
+        <v>3.7</v>
+      </c>
+      <c r="BH2">
+        <v>6.8</v>
+      </c>
+      <c r="BI2">
+        <v>5.6</v>
+      </c>
+      <c r="BJ2">
+        <v>15</v>
+      </c>
+      <c r="BK2">
         <v>11</v>
       </c>
-      <c r="BD2">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BE2">
-        <v>9.4</v>
-      </c>
-      <c r="BF2">
-        <v>2.02</v>
-      </c>
-      <c r="BG2">
-        <v>9.6</v>
-      </c>
-      <c r="BH2">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BI2">
-        <v>6.4</v>
-      </c>
-      <c r="BJ2">
-        <v>13</v>
-      </c>
-      <c r="BK2">
-        <v>5.2</v>
-      </c>
       <c r="BL2">
-        <v>1000</v>
+        <v>940</v>
       </c>
       <c r="BM2">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BN2">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="BO2">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="BP2">
+        <v>6</v>
+      </c>
+      <c r="BQ2">
+        <v>4.8</v>
+      </c>
+      <c r="BR2">
+        <v>24</v>
+      </c>
+      <c r="BS2">
+        <v>6</v>
+      </c>
+      <c r="BT2">
+        <v>30</v>
+      </c>
+      <c r="BU2">
+        <v>6.8</v>
+      </c>
+      <c r="BV2">
+        <v>170</v>
+      </c>
+      <c r="BW2">
         <v>6.6</v>
       </c>
-      <c r="BQ2">
-        <v>5.2</v>
-      </c>
-      <c r="BR2">
-        <v>17</v>
-      </c>
-      <c r="BS2">
-        <v>5.7</v>
-      </c>
-      <c r="BT2">
-        <v>22</v>
-      </c>
-      <c r="BU2">
-        <v>6.2</v>
-      </c>
-      <c r="BV2">
-        <v>1000</v>
-      </c>
-      <c r="BW2">
-        <v>8</v>
-      </c>
       <c r="BX2">
-        <v>70</v>
+        <v>110</v>
       </c>
       <c r="BY2">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BZ2">
         <v>0</v>
@@ -1284,67 +1284,67 @@
         <v>126</v>
       </c>
       <c r="F3">
-        <v>2.6</v>
+        <v>2.48</v>
       </c>
       <c r="G3">
-        <v>2.64</v>
+        <v>2.54</v>
       </c>
       <c r="H3">
-        <v>3.75</v>
+        <v>4.1</v>
       </c>
       <c r="I3">
-        <v>3.85</v>
+        <v>4.2</v>
       </c>
       <c r="J3">
         <v>2.76</v>
       </c>
       <c r="K3">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="L3">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="M3">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="N3">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="O3">
-        <v>1.86</v>
+        <v>1.82</v>
       </c>
       <c r="P3">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="Q3">
-        <v>3.85</v>
+        <v>3.6</v>
       </c>
       <c r="R3">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="S3">
-        <v>9.4</v>
+        <v>8.6</v>
       </c>
       <c r="T3">
-        <v>2.7</v>
+        <v>2.56</v>
       </c>
       <c r="U3">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="V3">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="W3">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="X3">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="Y3">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z3">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AA3">
         <v>110</v>
@@ -1356,133 +1356,133 @@
         <v>7</v>
       </c>
       <c r="AD3">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AE3">
-        <v>95</v>
+        <v>160</v>
       </c>
       <c r="AF3">
+        <v>12.5</v>
+      </c>
+      <c r="AG3">
         <v>14</v>
       </c>
-      <c r="AG3">
-        <v>15.5</v>
-      </c>
       <c r="AH3">
+        <v>36</v>
+      </c>
+      <c r="AI3">
+        <v>150</v>
+      </c>
+      <c r="AJ3">
         <v>38</v>
-      </c>
-      <c r="AI3">
-        <v>200</v>
-      </c>
-      <c r="AJ3">
-        <v>46</v>
       </c>
       <c r="AK3">
         <v>55</v>
       </c>
       <c r="AL3">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AM3">
-        <v>440</v>
+        <v>360</v>
       </c>
       <c r="AN3">
+        <v>55</v>
+      </c>
+      <c r="AO3">
+        <v>1000</v>
+      </c>
+      <c r="AP3">
+        <v>5.8</v>
+      </c>
+      <c r="AQ3">
+        <v>8.4</v>
+      </c>
+      <c r="AR3">
+        <v>23</v>
+      </c>
+      <c r="AS3">
         <v>80</v>
-      </c>
-      <c r="AO3">
-        <v>170</v>
-      </c>
-      <c r="AP3">
-        <v>5.4</v>
-      </c>
-      <c r="AQ3">
-        <v>7.8</v>
-      </c>
-      <c r="AR3">
-        <v>20</v>
-      </c>
-      <c r="AS3">
-        <v>60</v>
       </c>
       <c r="AT3">
         <v>5.8</v>
       </c>
       <c r="AU3">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AV3">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AW3">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="AX3">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AY3">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AZ3">
+        <v>28</v>
+      </c>
+      <c r="BA3">
+        <v>95</v>
+      </c>
+      <c r="BB3">
         <v>32</v>
       </c>
-      <c r="BA3">
-        <v>100</v>
-      </c>
-      <c r="BB3">
+      <c r="BC3">
         <v>34</v>
       </c>
-      <c r="BC3">
-        <v>38</v>
-      </c>
       <c r="BD3">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="BE3">
-        <v>75</v>
+        <v>230</v>
       </c>
       <c r="BF3">
         <v>36</v>
       </c>
       <c r="BG3">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="BH3">
-        <v>4.9</v>
+        <v>3</v>
       </c>
       <c r="BI3">
-        <v>2.02</v>
+        <v>2.14</v>
       </c>
       <c r="BJ3">
         <v>1000</v>
       </c>
       <c r="BK3">
+        <v>3.3</v>
+      </c>
+      <c r="BL3">
+        <v>1000</v>
+      </c>
+      <c r="BM3">
+        <v>300</v>
+      </c>
+      <c r="BN3">
+        <v>7.2</v>
+      </c>
+      <c r="BO3">
         <v>3.25</v>
       </c>
-      <c r="BL3">
-        <v>1000</v>
-      </c>
-      <c r="BM3">
-        <v>38</v>
-      </c>
-      <c r="BN3">
-        <v>1000</v>
-      </c>
-      <c r="BO3">
-        <v>4.7</v>
-      </c>
       <c r="BP3">
         <v>1000</v>
       </c>
       <c r="BQ3">
-        <v>3.2</v>
+        <v>9.6</v>
       </c>
       <c r="BR3">
         <v>1000</v>
       </c>
       <c r="BS3">
-        <v>3.2</v>
+        <v>2.54</v>
       </c>
       <c r="BT3">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BU3">
         <v>5.6</v>
@@ -1491,19 +1491,19 @@
         <v>1000</v>
       </c>
       <c r="BW3">
-        <v>3.2</v>
+        <v>2.54</v>
       </c>
       <c r="BX3">
         <v>1000</v>
       </c>
       <c r="BY3">
-        <v>1.38</v>
+        <v>2.54</v>
       </c>
       <c r="BZ3">
         <v>1000</v>
       </c>
       <c r="CA3">
-        <v>1.38</v>
+        <v>2.54</v>
       </c>
       <c r="CB3" t="s">
         <v>144</v>
@@ -1526,40 +1526,40 @@
         <v>127</v>
       </c>
       <c r="F4">
-        <v>2.96</v>
+        <v>3.25</v>
       </c>
       <c r="G4">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="H4">
-        <v>2.74</v>
+        <v>2.62</v>
       </c>
       <c r="I4">
-        <v>2.92</v>
+        <v>2.66</v>
       </c>
       <c r="J4">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="K4">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="L4">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="M4">
         <v>1.13</v>
       </c>
       <c r="N4">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="O4">
         <v>1.55</v>
       </c>
       <c r="P4">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="Q4">
-        <v>2.62</v>
+        <v>2.72</v>
       </c>
       <c r="R4">
         <v>1.21</v>
@@ -1568,184 +1568,184 @@
         <v>5.5</v>
       </c>
       <c r="T4">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="U4">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
       <c r="V4">
-        <v>1.52</v>
+        <v>1.6</v>
       </c>
       <c r="W4">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="X4">
-        <v>9.4</v>
+        <v>8.4</v>
       </c>
       <c r="Y4">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Z4">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="AA4">
-        <v>75</v>
+        <v>46</v>
       </c>
       <c r="AB4">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC4">
         <v>7</v>
       </c>
       <c r="AD4">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AE4">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="AF4">
-        <v>19.5</v>
+        <v>22</v>
       </c>
       <c r="AG4">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AH4">
+        <v>23</v>
+      </c>
+      <c r="AI4">
+        <v>80</v>
+      </c>
+      <c r="AJ4">
+        <v>70</v>
+      </c>
+      <c r="AK4">
+        <v>55</v>
+      </c>
+      <c r="AL4">
+        <v>120</v>
+      </c>
+      <c r="AM4">
+        <v>210</v>
+      </c>
+      <c r="AN4">
+        <v>70</v>
+      </c>
+      <c r="AO4">
+        <v>44</v>
+      </c>
+      <c r="AP4">
+        <v>7.6</v>
+      </c>
+      <c r="AQ4">
+        <v>7.2</v>
+      </c>
+      <c r="AR4">
+        <v>13.5</v>
+      </c>
+      <c r="AS4">
         <v>22</v>
       </c>
-      <c r="AI4">
-        <v>110</v>
-      </c>
-      <c r="AJ4">
-        <v>90</v>
-      </c>
-      <c r="AK4">
-        <v>70</v>
-      </c>
-      <c r="AL4">
-        <v>110</v>
-      </c>
-      <c r="AM4">
-        <v>190</v>
-      </c>
-      <c r="AN4">
-        <v>75</v>
-      </c>
-      <c r="AO4">
-        <v>60</v>
-      </c>
-      <c r="AP4">
-        <v>8</v>
-      </c>
-      <c r="AQ4">
-        <v>7.4</v>
-      </c>
-      <c r="AR4">
-        <v>14.5</v>
-      </c>
-      <c r="AS4">
-        <v>40</v>
-      </c>
       <c r="AT4">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AU4">
         <v>6.2</v>
       </c>
       <c r="AV4">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AW4">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="AX4">
-        <v>16.5</v>
+        <v>18.5</v>
       </c>
       <c r="AY4">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AZ4">
         <v>19</v>
       </c>
       <c r="BA4">
-        <v>9.800000000000001</v>
+        <v>12</v>
       </c>
       <c r="BB4">
-        <v>9.199999999999999</v>
+        <v>34</v>
       </c>
       <c r="BC4">
-        <v>9.4</v>
+        <v>28</v>
       </c>
       <c r="BD4">
-        <v>9.4</v>
+        <v>36</v>
       </c>
       <c r="BE4">
-        <v>10</v>
+        <v>13.5</v>
       </c>
       <c r="BF4">
-        <v>9.6</v>
+        <v>38</v>
       </c>
       <c r="BG4">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="BH4">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="BI4">
-        <v>2.38</v>
+        <v>2.32</v>
       </c>
       <c r="BJ4">
         <v>11</v>
       </c>
       <c r="BK4">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>2.36</v>
+        <v>15</v>
       </c>
       <c r="BN4">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="BO4">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BP4">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="BQ4">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BR4">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BS4">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="BT4">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BU4">
         <v>4.3</v>
       </c>
       <c r="BV4">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BW4">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BX4">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="BY4">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BZ4">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="CA4">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="CB4" t="s">
         <v>144</v>
@@ -1768,22 +1768,22 @@
         <v>128</v>
       </c>
       <c r="F5">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="G5">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="H5">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="I5">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="J5">
         <v>4.3</v>
       </c>
       <c r="K5">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="L5">
         <v>1.3</v>
@@ -1792,7 +1792,7 @@
         <v>1.04</v>
       </c>
       <c r="N5">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="O5">
         <v>1.2</v>
@@ -1801,19 +1801,19 @@
         <v>2.58</v>
       </c>
       <c r="Q5">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="R5">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="S5">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="T5">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="U5">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="V5">
         <v>1.27</v>
@@ -1831,7 +1831,7 @@
         <v>48</v>
       </c>
       <c r="AA5">
-        <v>190</v>
+        <v>95</v>
       </c>
       <c r="AB5">
         <v>13</v>
@@ -1843,7 +1843,7 @@
         <v>19.5</v>
       </c>
       <c r="AE5">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="AF5">
         <v>13.5</v>
@@ -1855,7 +1855,7 @@
         <v>17.5</v>
       </c>
       <c r="AI5">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AJ5">
         <v>19.5</v>
@@ -1867,16 +1867,16 @@
         <v>36</v>
       </c>
       <c r="AM5">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="AN5">
         <v>8</v>
       </c>
       <c r="AO5">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="AP5">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AQ5">
         <v>20</v>
@@ -1885,7 +1885,7 @@
         <v>32</v>
       </c>
       <c r="AS5">
-        <v>60</v>
+        <v>9.6</v>
       </c>
       <c r="AT5">
         <v>11</v>
@@ -1909,31 +1909,31 @@
         <v>14.5</v>
       </c>
       <c r="BA5">
-        <v>30</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB5">
         <v>17</v>
       </c>
       <c r="BC5">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="BD5">
         <v>22</v>
       </c>
       <c r="BE5">
-        <v>50</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF5">
         <v>7</v>
       </c>
       <c r="BG5">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="BH5">
         <v>4.5</v>
       </c>
       <c r="BI5">
-        <v>3.6</v>
+        <v>3.85</v>
       </c>
       <c r="BJ5">
         <v>9.4</v>
@@ -1951,7 +1951,7 @@
         <v>4.9</v>
       </c>
       <c r="BO5">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="BP5">
         <v>11.5</v>
@@ -2010,16 +2010,16 @@
         <v>129</v>
       </c>
       <c r="F6">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="G6">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="H6">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="I6">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="J6">
         <v>3.35</v>
@@ -2028,19 +2028,19 @@
         <v>3.45</v>
       </c>
       <c r="L6">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="M6">
         <v>1.09</v>
       </c>
       <c r="N6">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="O6">
         <v>1.4</v>
       </c>
       <c r="P6">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="Q6">
         <v>2.22</v>
@@ -2049,19 +2049,19 @@
         <v>1.29</v>
       </c>
       <c r="S6">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="T6">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="U6">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="V6">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="W6">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="X6">
         <v>12</v>
@@ -2115,10 +2115,10 @@
         <v>23</v>
       </c>
       <c r="AO6">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AP6">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AQ6">
         <v>11.5</v>
@@ -2127,7 +2127,7 @@
         <v>22</v>
       </c>
       <c r="AS6">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AT6">
         <v>8.199999999999999</v>
@@ -2136,13 +2136,13 @@
         <v>7</v>
       </c>
       <c r="AV6">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AW6">
         <v>42</v>
       </c>
       <c r="AX6">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AY6">
         <v>10</v>
@@ -2163,25 +2163,25 @@
         <v>38</v>
       </c>
       <c r="BE6">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="BF6">
         <v>19.5</v>
       </c>
       <c r="BG6">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="BH6">
         <v>3.2</v>
       </c>
       <c r="BI6">
-        <v>2.54</v>
+        <v>2.86</v>
       </c>
       <c r="BJ6">
         <v>10.5</v>
       </c>
       <c r="BK6">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="BL6">
         <v>150</v>
@@ -2205,31 +2205,31 @@
         <v>36</v>
       </c>
       <c r="BS6">
-        <v>8.800000000000001</v>
+        <v>21</v>
       </c>
       <c r="BT6">
         <v>7</v>
       </c>
       <c r="BU6">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BV6">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BW6">
         <v>19</v>
       </c>
       <c r="BX6">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="BY6">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BZ6">
         <v>34</v>
       </c>
       <c r="CA6">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="CB6" t="s">
         <v>144</v>
@@ -2252,19 +2252,19 @@
         <v>130</v>
       </c>
       <c r="F7">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="G7">
         <v>2.16</v>
       </c>
       <c r="H7">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="I7">
         <v>3.65</v>
       </c>
       <c r="J7">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="K7">
         <v>4.2</v>
@@ -2294,10 +2294,10 @@
         <v>2.56</v>
       </c>
       <c r="T7">
-        <v>1.59</v>
+        <v>1.65</v>
       </c>
       <c r="U7">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="V7">
         <v>1.37</v>
@@ -2357,19 +2357,19 @@
         <v>12</v>
       </c>
       <c r="AO7">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AP7">
         <v>19</v>
       </c>
       <c r="AQ7">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="AR7">
-        <v>21</v>
+        <v>11.5</v>
       </c>
       <c r="AS7">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AT7">
         <v>10.5</v>
@@ -2381,7 +2381,7 @@
         <v>13</v>
       </c>
       <c r="AW7">
-        <v>6.2</v>
+        <v>14.5</v>
       </c>
       <c r="AX7">
         <v>13</v>
@@ -2393,19 +2393,19 @@
         <v>13.5</v>
       </c>
       <c r="BA7">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BB7">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="BC7">
         <v>16.5</v>
       </c>
       <c r="BD7">
-        <v>5.8</v>
+        <v>16</v>
       </c>
       <c r="BE7">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BF7">
         <v>9.4</v>
@@ -2503,7 +2503,7 @@
         <v>5.3</v>
       </c>
       <c r="I8">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="J8">
         <v>3.1</v>
@@ -2533,10 +2533,10 @@
         <v>1.17</v>
       </c>
       <c r="S8">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="T8">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="U8">
         <v>1.65</v>
@@ -2557,7 +2557,7 @@
         <v>50</v>
       </c>
       <c r="AA8">
-        <v>220</v>
+        <v>900</v>
       </c>
       <c r="AB8">
         <v>6.4</v>
@@ -2581,7 +2581,7 @@
         <v>34</v>
       </c>
       <c r="AI8">
-        <v>160</v>
+        <v>700</v>
       </c>
       <c r="AJ8">
         <v>27</v>
@@ -2593,13 +2593,13 @@
         <v>80</v>
       </c>
       <c r="AM8">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="AN8">
         <v>29</v>
       </c>
       <c r="AO8">
-        <v>250</v>
+        <v>700</v>
       </c>
       <c r="AP8">
         <v>6.4</v>
@@ -2617,7 +2617,7 @@
         <v>5.2</v>
       </c>
       <c r="AU8">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AV8">
         <v>20</v>
@@ -2766,7 +2766,7 @@
         <v>1.11</v>
       </c>
       <c r="P9">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="Q9">
         <v>1.33</v>
@@ -2790,16 +2790,16 @@
         <v>2.44</v>
       </c>
       <c r="X9">
-        <v>240</v>
+        <v>120</v>
       </c>
       <c r="Y9">
-        <v>950</v>
+        <v>80</v>
       </c>
       <c r="Z9">
         <v>65</v>
       </c>
       <c r="AA9">
-        <v>120</v>
+        <v>700</v>
       </c>
       <c r="AB9">
         <v>21</v>
@@ -2811,10 +2811,10 @@
         <v>24</v>
       </c>
       <c r="AE9">
-        <v>200</v>
+        <v>120</v>
       </c>
       <c r="AF9">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="AG9">
         <v>12.5</v>
@@ -2823,7 +2823,7 @@
         <v>17.5</v>
       </c>
       <c r="AI9">
-        <v>42</v>
+        <v>150</v>
       </c>
       <c r="AJ9">
         <v>20</v>
@@ -2853,7 +2853,7 @@
         <v>9</v>
       </c>
       <c r="AS9">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AT9">
         <v>15</v>
@@ -2865,7 +2865,7 @@
         <v>17</v>
       </c>
       <c r="AW9">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AX9">
         <v>14.5</v>
@@ -2895,7 +2895,7 @@
         <v>4</v>
       </c>
       <c r="BG9">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BH9">
         <v>6.8</v>
@@ -2996,7 +2996,7 @@
         <v>3.7</v>
       </c>
       <c r="L10">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="M10">
         <v>1.07</v>
@@ -3014,7 +3014,7 @@
         <v>2</v>
       </c>
       <c r="R10">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="S10">
         <v>3.55</v>
@@ -3029,7 +3029,7 @@
         <v>1.46</v>
       </c>
       <c r="W10">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="X10">
         <v>15.5</v>
@@ -3086,19 +3086,19 @@
         <v>36</v>
       </c>
       <c r="AP10">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ10">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR10">
-        <v>15</v>
+        <v>17.5</v>
       </c>
       <c r="AS10">
         <v>4.6</v>
       </c>
       <c r="AT10">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU10">
         <v>6.6</v>
@@ -3110,7 +3110,7 @@
         <v>4.5</v>
       </c>
       <c r="AX10">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="AY10">
         <v>10</v>
@@ -3125,7 +3125,7 @@
         <v>13</v>
       </c>
       <c r="BC10">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="BD10">
         <v>4.6</v>
@@ -3134,13 +3134,13 @@
         <v>4.8</v>
       </c>
       <c r="BF10">
-        <v>17.5</v>
+        <v>21</v>
       </c>
       <c r="BG10">
         <v>9.800000000000001</v>
       </c>
       <c r="BH10">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="BI10">
         <v>2.64</v>
@@ -3149,55 +3149,55 @@
         <v>11.5</v>
       </c>
       <c r="BK10">
-        <v>7.2</v>
+        <v>3.4</v>
       </c>
       <c r="BL10">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="BM10">
-        <v>5.9</v>
+        <v>4.7</v>
       </c>
       <c r="BN10">
         <v>6.6</v>
       </c>
       <c r="BO10">
-        <v>4.7</v>
+        <v>4.2</v>
       </c>
       <c r="BP10">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="BQ10">
-        <v>4.8</v>
+        <v>4</v>
       </c>
       <c r="BR10">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="BS10">
-        <v>5.3</v>
+        <v>4.4</v>
       </c>
       <c r="BT10">
         <v>7.2</v>
       </c>
       <c r="BU10">
-        <v>5.2</v>
+        <v>4.6</v>
       </c>
       <c r="BV10">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BW10">
-        <v>5.1</v>
+        <v>4.2</v>
       </c>
       <c r="BX10">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="BY10">
-        <v>5.3</v>
+        <v>4.4</v>
       </c>
       <c r="BZ10">
         <v>36</v>
       </c>
       <c r="CA10">
-        <v>5.3</v>
+        <v>4.3</v>
       </c>
       <c r="CB10" t="s">
         <v>144</v>
@@ -3223,7 +3223,7 @@
         <v>2.64</v>
       </c>
       <c r="G11">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="H11">
         <v>2.76</v>
@@ -3238,7 +3238,7 @@
         <v>3.65</v>
       </c>
       <c r="L11">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="M11">
         <v>1.07</v>
@@ -3253,7 +3253,7 @@
         <v>1.86</v>
       </c>
       <c r="Q11">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="R11">
         <v>1.33</v>
@@ -3280,7 +3280,7 @@
         <v>14</v>
       </c>
       <c r="Z11">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AA11">
         <v>55</v>
@@ -3313,13 +3313,13 @@
         <v>44</v>
       </c>
       <c r="AK11">
-        <v>36</v>
+        <v>80</v>
       </c>
       <c r="AL11">
         <v>55</v>
       </c>
       <c r="AM11">
-        <v>380</v>
+        <v>580</v>
       </c>
       <c r="AN11">
         <v>29</v>
@@ -3328,58 +3328,58 @@
         <v>55</v>
       </c>
       <c r="AP11">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AQ11">
-        <v>8.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR11">
         <v>16.5</v>
       </c>
       <c r="AS11">
-        <v>14.5</v>
+        <v>21</v>
       </c>
       <c r="AT11">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AU11">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AV11">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="AW11">
         <v>16</v>
       </c>
       <c r="AX11">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AY11">
         <v>10.5</v>
       </c>
       <c r="AZ11">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="BA11">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BB11">
-        <v>16</v>
+        <v>5.3</v>
       </c>
       <c r="BC11">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BD11">
-        <v>5.3</v>
+        <v>22</v>
       </c>
       <c r="BE11">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BF11">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="BG11">
-        <v>21</v>
+        <v>6.2</v>
       </c>
       <c r="BH11">
         <v>3.45</v>
@@ -3462,10 +3462,10 @@
         <v>135</v>
       </c>
       <c r="F12">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="G12">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="H12">
         <v>3.45</v>
@@ -3477,7 +3477,7 @@
         <v>3.35</v>
       </c>
       <c r="K12">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="L12">
         <v>1.01</v>
@@ -3492,13 +3492,13 @@
         <v>1.28</v>
       </c>
       <c r="P12">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="Q12">
         <v>1.92</v>
       </c>
       <c r="R12">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="S12">
         <v>3.35</v>
@@ -3510,10 +3510,10 @@
         <v>2.18</v>
       </c>
       <c r="V12">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="W12">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="X12">
         <v>15</v>
@@ -3707,19 +3707,19 @@
         <v>1.05</v>
       </c>
       <c r="G13">
-        <v>970</v>
+        <v>1.67</v>
       </c>
       <c r="H13">
-        <v>2</v>
+        <v>5.4</v>
       </c>
       <c r="I13">
-        <v>190</v>
+        <v>990</v>
       </c>
       <c r="J13">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="K13">
-        <v>110</v>
+        <v>500</v>
       </c>
       <c r="L13">
         <v>1.01</v>
@@ -3728,13 +3728,13 @@
         <v>1.01</v>
       </c>
       <c r="N13">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="O13">
         <v>1.23</v>
       </c>
       <c r="P13">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="Q13">
         <v>1.23</v>
@@ -3743,19 +3743,19 @@
         <v>1.18</v>
       </c>
       <c r="S13">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="T13">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U13">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V13">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W13">
-        <v>1.03</v>
+        <v>2.5</v>
       </c>
       <c r="X13">
         <v>1000</v>
@@ -3806,7 +3806,7 @@
         <v>1000</v>
       </c>
       <c r="AN13">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AO13">
         <v>1000</v>
@@ -3863,7 +3863,7 @@
         <v>1.01</v>
       </c>
       <c r="BG13">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BH13">
         <v>1000</v>
@@ -3949,16 +3949,16 @@
         <v>1.3</v>
       </c>
       <c r="G14">
-        <v>200</v>
+        <v>14</v>
       </c>
       <c r="H14">
         <v>2.4</v>
       </c>
       <c r="I14">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="J14">
-        <v>1.02</v>
+        <v>2.32</v>
       </c>
       <c r="K14">
         <v>950</v>
@@ -3970,7 +3970,7 @@
         <v>1.12</v>
       </c>
       <c r="N14">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="O14">
         <v>1.47</v>
@@ -3988,16 +3988,16 @@
         <v>3.5</v>
       </c>
       <c r="T14">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U14">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V14">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W14">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="X14">
         <v>1000</v>
@@ -4105,7 +4105,7 @@
         <v>1.01</v>
       </c>
       <c r="BG14">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BH14">
         <v>1000</v>
@@ -4194,7 +4194,7 @@
         <v>2.46</v>
       </c>
       <c r="H15">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="I15">
         <v>3.6</v>
@@ -4203,7 +4203,7 @@
         <v>3.4</v>
       </c>
       <c r="K15">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="L15">
         <v>1.18</v>
@@ -4221,7 +4221,7 @@
         <v>1.87</v>
       </c>
       <c r="Q15">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="R15">
         <v>1.33</v>
@@ -4230,43 +4230,43 @@
         <v>3.45</v>
       </c>
       <c r="T15">
-        <v>1.76</v>
+        <v>1.87</v>
       </c>
       <c r="U15">
         <v>2.12</v>
       </c>
       <c r="V15">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="W15">
         <v>1.68</v>
       </c>
       <c r="X15">
+        <v>14.5</v>
+      </c>
+      <c r="Y15">
+        <v>15.5</v>
+      </c>
+      <c r="Z15">
+        <v>25</v>
+      </c>
+      <c r="AA15">
+        <v>65</v>
+      </c>
+      <c r="AB15">
+        <v>10.5</v>
+      </c>
+      <c r="AC15">
+        <v>8.4</v>
+      </c>
+      <c r="AD15">
         <v>15</v>
       </c>
-      <c r="Y15">
+      <c r="AE15">
+        <v>42</v>
+      </c>
+      <c r="AF15">
         <v>16</v>
-      </c>
-      <c r="Z15">
-        <v>29</v>
-      </c>
-      <c r="AA15">
-        <v>75</v>
-      </c>
-      <c r="AB15">
-        <v>12.5</v>
-      </c>
-      <c r="AC15">
-        <v>9.6</v>
-      </c>
-      <c r="AD15">
-        <v>17.5</v>
-      </c>
-      <c r="AE15">
-        <v>48</v>
-      </c>
-      <c r="AF15">
-        <v>18.5</v>
       </c>
       <c r="AG15">
         <v>14</v>
@@ -4275,16 +4275,16 @@
         <v>18.5</v>
       </c>
       <c r="AI15">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AJ15">
         <v>34</v>
       </c>
       <c r="AK15">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="AL15">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="AM15">
         <v>120</v>
@@ -4305,19 +4305,19 @@
         <v>20</v>
       </c>
       <c r="AS15">
-        <v>4.4</v>
+        <v>6.4</v>
       </c>
       <c r="AT15">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="AU15">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="AV15">
         <v>12</v>
       </c>
       <c r="AW15">
-        <v>4.2</v>
+        <v>6</v>
       </c>
       <c r="AX15">
         <v>13</v>
@@ -4329,25 +4329,25 @@
         <v>14.5</v>
       </c>
       <c r="BA15">
-        <v>4.3</v>
+        <v>6.2</v>
       </c>
       <c r="BB15">
-        <v>4.1</v>
+        <v>5.9</v>
       </c>
       <c r="BC15">
         <v>21</v>
       </c>
       <c r="BD15">
-        <v>4.2</v>
+        <v>32</v>
       </c>
       <c r="BE15">
-        <v>4.5</v>
+        <v>6.6</v>
       </c>
       <c r="BF15">
         <v>16.5</v>
       </c>
       <c r="BG15">
-        <v>4.2</v>
+        <v>6.2</v>
       </c>
       <c r="BH15">
         <v>3.5</v>
@@ -4356,7 +4356,7 @@
         <v>2.7</v>
       </c>
       <c r="BJ15">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BK15">
         <v>5.2</v>
@@ -4365,7 +4365,7 @@
         <v>1000</v>
       </c>
       <c r="BM15">
-        <v>2.62</v>
+        <v>10</v>
       </c>
       <c r="BN15">
         <v>5.4</v>
@@ -4383,25 +4383,25 @@
         <v>32</v>
       </c>
       <c r="BS15">
-        <v>2.46</v>
+        <v>8</v>
       </c>
       <c r="BT15">
         <v>6.8</v>
       </c>
       <c r="BU15">
-        <v>4.2</v>
+        <v>4.9</v>
       </c>
       <c r="BV15">
         <v>28</v>
       </c>
       <c r="BW15">
-        <v>2.44</v>
+        <v>7.8</v>
       </c>
       <c r="BX15">
         <v>40</v>
       </c>
       <c r="BY15">
-        <v>2.5</v>
+        <v>8.6</v>
       </c>
       <c r="BZ15">
         <v>0</v>
@@ -4430,22 +4430,22 @@
         <v>139</v>
       </c>
       <c r="F16">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="G16">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="H16">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="I16">
-        <v>6.2</v>
+        <v>5.8</v>
       </c>
       <c r="J16">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K16">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="L16">
         <v>1.43</v>
@@ -4454,13 +4454,13 @@
         <v>1.11</v>
       </c>
       <c r="N16">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="O16">
         <v>1.47</v>
       </c>
       <c r="P16">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="Q16">
         <v>2.4</v>
@@ -4475,10 +4475,10 @@
         <v>2.14</v>
       </c>
       <c r="U16">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="V16">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="W16">
         <v>2.08</v>
@@ -4487,13 +4487,13 @@
         <v>10</v>
       </c>
       <c r="Y16">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="Z16">
         <v>60</v>
       </c>
       <c r="AA16">
-        <v>700</v>
+        <v>900</v>
       </c>
       <c r="AB16">
         <v>6.8</v>
@@ -4502,10 +4502,10 @@
         <v>8</v>
       </c>
       <c r="AD16">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AE16">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AF16">
         <v>10.5</v>
@@ -4517,37 +4517,37 @@
         <v>25</v>
       </c>
       <c r="AI16">
-        <v>540</v>
+        <v>700</v>
       </c>
       <c r="AJ16">
         <v>21</v>
       </c>
       <c r="AK16">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AL16">
-        <v>55</v>
+        <v>120</v>
       </c>
       <c r="AM16">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN16">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AO16">
-        <v>210</v>
+        <v>700</v>
       </c>
       <c r="AP16">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="AQ16">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AR16">
         <v>15</v>
       </c>
       <c r="AS16">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AT16">
         <v>5.9</v>
@@ -4556,10 +4556,10 @@
         <v>7</v>
       </c>
       <c r="AV16">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AW16">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AX16">
         <v>8.800000000000001</v>
@@ -4571,7 +4571,7 @@
         <v>21</v>
       </c>
       <c r="BA16">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="BB16">
         <v>18</v>
@@ -4583,13 +4583,13 @@
         <v>30</v>
       </c>
       <c r="BE16">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="BF16">
         <v>16</v>
       </c>
       <c r="BG16">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="BH16">
         <v>2.92</v>
@@ -4601,7 +4601,7 @@
         <v>12</v>
       </c>
       <c r="BK16">
-        <v>6.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BL16">
         <v>1000</v>
@@ -4631,7 +4631,7 @@
         <v>9</v>
       </c>
       <c r="BU16">
-        <v>6.6</v>
+        <v>5.7</v>
       </c>
       <c r="BV16">
         <v>60</v>
@@ -4675,13 +4675,13 @@
         <v>2.42</v>
       </c>
       <c r="G17">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="H17">
         <v>3.6</v>
       </c>
       <c r="I17">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="J17">
         <v>3.05</v>
@@ -4702,7 +4702,7 @@
         <v>1.55</v>
       </c>
       <c r="P17">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="Q17">
         <v>2.66</v>
@@ -4711,7 +4711,7 @@
         <v>1.2</v>
       </c>
       <c r="S17">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="T17">
         <v>2.14</v>
@@ -4720,10 +4720,10 @@
         <v>1.79</v>
       </c>
       <c r="V17">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="W17">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="X17">
         <v>9.4</v>
@@ -4735,7 +4735,7 @@
         <v>24</v>
       </c>
       <c r="AA17">
-        <v>1000</v>
+        <v>490</v>
       </c>
       <c r="AB17">
         <v>7.6</v>
@@ -4759,7 +4759,7 @@
         <v>24</v>
       </c>
       <c r="AI17">
-        <v>500</v>
+        <v>220</v>
       </c>
       <c r="AJ17">
         <v>44</v>
@@ -4768,7 +4768,7 @@
         <v>40</v>
       </c>
       <c r="AL17">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AM17">
         <v>1000</v>
@@ -4777,13 +4777,13 @@
         <v>42</v>
       </c>
       <c r="AO17">
-        <v>500</v>
+        <v>220</v>
       </c>
       <c r="AP17">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AQ17">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR17">
         <v>15.5</v>
@@ -4807,7 +4807,7 @@
         <v>12</v>
       </c>
       <c r="AY17">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AZ17">
         <v>17</v>
@@ -4816,7 +4816,7 @@
         <v>36</v>
       </c>
       <c r="BB17">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="BC17">
         <v>21</v>
@@ -4825,10 +4825,10 @@
         <v>32</v>
       </c>
       <c r="BE17">
-        <v>48</v>
+        <v>70</v>
       </c>
       <c r="BF17">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="BG17">
         <v>34</v>
@@ -4843,13 +4843,13 @@
         <v>13.5</v>
       </c>
       <c r="BK17">
-        <v>4</v>
+        <v>3.65</v>
       </c>
       <c r="BL17">
         <v>1000</v>
       </c>
       <c r="BM17">
-        <v>5.5</v>
+        <v>4.9</v>
       </c>
       <c r="BN17">
         <v>6</v>
@@ -4861,16 +4861,16 @@
         <v>26</v>
       </c>
       <c r="BQ17">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="BR17">
         <v>55</v>
       </c>
       <c r="BS17">
-        <v>5.1</v>
+        <v>4.5</v>
       </c>
       <c r="BT17">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="BU17">
         <v>5</v>
@@ -4879,19 +4879,19 @@
         <v>44</v>
       </c>
       <c r="BW17">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="BX17">
         <v>70</v>
       </c>
       <c r="BY17">
-        <v>5.2</v>
+        <v>4.6</v>
       </c>
       <c r="BZ17">
         <v>60</v>
       </c>
       <c r="CA17">
-        <v>5.1</v>
+        <v>4.6</v>
       </c>
       <c r="CB17" t="s">
         <v>144</v>
@@ -4914,10 +4914,10 @@
         <v>141</v>
       </c>
       <c r="F18">
-        <v>1.74</v>
+        <v>1.8</v>
       </c>
       <c r="G18">
-        <v>2.16</v>
+        <v>2.06</v>
       </c>
       <c r="H18">
         <v>4.2</v>
@@ -4926,19 +4926,19 @@
         <v>6.8</v>
       </c>
       <c r="J18">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="K18">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="L18">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="M18">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N18">
-        <v>3.05</v>
+        <v>2.86</v>
       </c>
       <c r="O18">
         <v>1.39</v>
@@ -4947,7 +4947,7 @@
         <v>1.64</v>
       </c>
       <c r="Q18">
-        <v>1.92</v>
+        <v>2.02</v>
       </c>
       <c r="R18">
         <v>1.18</v>
@@ -4959,22 +4959,22 @@
         <v>1.11</v>
       </c>
       <c r="U18">
-        <v>1.11</v>
+        <v>1.81</v>
       </c>
       <c r="V18">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="W18">
-        <v>1.86</v>
+        <v>1.94</v>
       </c>
       <c r="X18">
-        <v>970</v>
+        <v>15</v>
       </c>
       <c r="Y18">
         <v>950</v>
       </c>
       <c r="Z18">
-        <v>500</v>
+        <v>120</v>
       </c>
       <c r="AA18">
         <v>900</v>
@@ -4983,7 +4983,7 @@
         <v>970</v>
       </c>
       <c r="AC18">
-        <v>950</v>
+        <v>42</v>
       </c>
       <c r="AD18">
         <v>950</v>
@@ -4992,13 +4992,13 @@
         <v>500</v>
       </c>
       <c r="AF18">
-        <v>500</v>
+        <v>24</v>
       </c>
       <c r="AG18">
-        <v>500</v>
+        <v>18.5</v>
       </c>
       <c r="AH18">
-        <v>950</v>
+        <v>60</v>
       </c>
       <c r="AI18">
         <v>500</v>
@@ -5022,58 +5022,58 @@
         <v>1000</v>
       </c>
       <c r="AP18">
+        <v>5.7</v>
+      </c>
+      <c r="AQ18">
+        <v>7.8</v>
+      </c>
+      <c r="AR18">
+        <v>15.5</v>
+      </c>
+      <c r="AS18">
         <v>2.5</v>
       </c>
-      <c r="AQ18">
-        <v>1.7</v>
-      </c>
-      <c r="AR18">
-        <v>1.8</v>
-      </c>
-      <c r="AS18">
-        <v>1.82</v>
-      </c>
       <c r="AT18">
-        <v>4.2</v>
+        <v>5.1</v>
       </c>
       <c r="AU18">
-        <v>4.4</v>
+        <v>5.1</v>
       </c>
       <c r="AV18">
-        <v>1.76</v>
+        <v>1.85</v>
       </c>
       <c r="AW18">
-        <v>1.82</v>
+        <v>28</v>
       </c>
       <c r="AX18">
-        <v>2.5</v>
+        <v>5.6</v>
       </c>
       <c r="AY18">
-        <v>1.67</v>
+        <v>6.2</v>
       </c>
       <c r="AZ18">
-        <v>1.77</v>
+        <v>12.5</v>
       </c>
       <c r="BA18">
-        <v>1.82</v>
+        <v>28</v>
       </c>
       <c r="BB18">
-        <v>1.79</v>
+        <v>10.5</v>
       </c>
       <c r="BC18">
-        <v>1.78</v>
+        <v>11.5</v>
       </c>
       <c r="BD18">
-        <v>1.81</v>
+        <v>24</v>
       </c>
       <c r="BE18">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="BF18">
         <v>4.4</v>
       </c>
       <c r="BG18">
-        <v>1.83</v>
+        <v>1.93</v>
       </c>
       <c r="BH18">
         <v>1000</v>
@@ -5162,13 +5162,13 @@
         <v>2.18</v>
       </c>
       <c r="H19">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="I19">
         <v>5.5</v>
       </c>
       <c r="J19">
-        <v>2.92</v>
+        <v>3.05</v>
       </c>
       <c r="K19">
         <v>3.65</v>
@@ -5180,25 +5180,25 @@
         <v>1.14</v>
       </c>
       <c r="N19">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="O19">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="P19">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="Q19">
         <v>2.78</v>
       </c>
       <c r="R19">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="S19">
         <v>5.9</v>
       </c>
       <c r="T19">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="U19">
         <v>1.63</v>
@@ -5228,10 +5228,10 @@
         <v>7.8</v>
       </c>
       <c r="AD19">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AE19">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AF19">
         <v>13</v>
@@ -5240,16 +5240,16 @@
         <v>12.5</v>
       </c>
       <c r="AH19">
+        <v>950</v>
+      </c>
+      <c r="AI19">
+        <v>140</v>
+      </c>
+      <c r="AJ19">
         <v>34</v>
       </c>
-      <c r="AI19">
-        <v>150</v>
-      </c>
-      <c r="AJ19">
-        <v>28</v>
-      </c>
       <c r="AK19">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="AL19">
         <v>80</v>
@@ -5258,22 +5258,22 @@
         <v>290</v>
       </c>
       <c r="AN19">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AO19">
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="AP19">
         <v>6</v>
       </c>
       <c r="AQ19">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AR19">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AS19">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AT19">
         <v>5.2</v>
@@ -5285,37 +5285,37 @@
         <v>16.5</v>
       </c>
       <c r="AW19">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AX19">
-        <v>4.8</v>
+        <v>9.4</v>
       </c>
       <c r="AY19">
-        <v>9.800000000000001</v>
+        <v>4.9</v>
       </c>
       <c r="AZ19">
         <v>18</v>
       </c>
       <c r="BA19">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BB19">
         <v>18</v>
       </c>
       <c r="BC19">
-        <v>21</v>
+        <v>6.4</v>
       </c>
       <c r="BD19">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BE19">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BF19">
         <v>19.5</v>
       </c>
       <c r="BG19">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BH19">
         <v>2.84</v>
@@ -5398,181 +5398,181 @@
         <v>143</v>
       </c>
       <c r="F20">
-        <v>2.7</v>
+        <v>3.05</v>
       </c>
       <c r="G20">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="H20">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="I20">
-        <v>2.6</v>
+        <v>2.44</v>
       </c>
       <c r="J20">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="K20">
         <v>4.1</v>
       </c>
       <c r="L20">
-        <v>1.25</v>
+        <v>1.01</v>
       </c>
       <c r="M20">
         <v>1.01</v>
       </c>
       <c r="N20">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="O20">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="P20">
-        <v>2.48</v>
+        <v>2.32</v>
       </c>
       <c r="Q20">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="R20">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="S20">
-        <v>2.1</v>
+        <v>2.44</v>
       </c>
       <c r="T20">
-        <v>1.43</v>
+        <v>1.54</v>
       </c>
       <c r="U20">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="V20">
-        <v>1.63</v>
+        <v>1.69</v>
       </c>
       <c r="W20">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="X20">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="Y20">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="Z20">
         <v>21</v>
       </c>
       <c r="AA20">
+        <v>32</v>
+      </c>
+      <c r="AB20">
+        <v>18.5</v>
+      </c>
+      <c r="AC20">
+        <v>11.5</v>
+      </c>
+      <c r="AD20">
+        <v>12.5</v>
+      </c>
+      <c r="AE20">
+        <v>26</v>
+      </c>
+      <c r="AF20">
+        <v>27</v>
+      </c>
+      <c r="AG20">
+        <v>15.5</v>
+      </c>
+      <c r="AH20">
+        <v>16.5</v>
+      </c>
+      <c r="AI20">
+        <v>32</v>
+      </c>
+      <c r="AJ20">
+        <v>65</v>
+      </c>
+      <c r="AK20">
         <v>34</v>
       </c>
-      <c r="AB20">
-        <v>19.5</v>
-      </c>
-      <c r="AC20">
-        <v>11</v>
-      </c>
-      <c r="AD20">
-        <v>13.5</v>
-      </c>
-      <c r="AE20">
+      <c r="AL20">
+        <v>44</v>
+      </c>
+      <c r="AM20">
+        <v>75</v>
+      </c>
+      <c r="AN20">
+        <v>23</v>
+      </c>
+      <c r="AO20">
+        <v>13</v>
+      </c>
+      <c r="AP20">
+        <v>18.5</v>
+      </c>
+      <c r="AQ20">
+        <v>11.5</v>
+      </c>
+      <c r="AR20">
+        <v>14</v>
+      </c>
+      <c r="AS20">
         <v>24</v>
       </c>
-      <c r="AF20">
-        <v>26</v>
-      </c>
-      <c r="AG20">
-        <v>15</v>
-      </c>
-      <c r="AH20">
-        <v>16</v>
-      </c>
-      <c r="AI20">
-        <v>30</v>
-      </c>
-      <c r="AJ20">
-        <v>55</v>
-      </c>
-      <c r="AK20">
-        <v>30</v>
-      </c>
-      <c r="AL20">
-        <v>34</v>
-      </c>
-      <c r="AM20">
-        <v>65</v>
-      </c>
-      <c r="AN20">
-        <v>18</v>
-      </c>
-      <c r="AO20">
+      <c r="AT20">
+        <v>14</v>
+      </c>
+      <c r="AU20">
+        <v>8</v>
+      </c>
+      <c r="AV20">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AW20">
+        <v>17.5</v>
+      </c>
+      <c r="AX20">
+        <v>20</v>
+      </c>
+      <c r="AY20">
+        <v>11.5</v>
+      </c>
+      <c r="AZ20">
         <v>12.5</v>
       </c>
-      <c r="AP20">
-        <v>5.7</v>
-      </c>
-      <c r="AQ20">
-        <v>5.1</v>
-      </c>
-      <c r="AR20">
-        <v>5.3</v>
-      </c>
-      <c r="AS20">
-        <v>5.9</v>
-      </c>
-      <c r="AT20">
+      <c r="BA20">
+        <v>18.5</v>
+      </c>
+      <c r="BB20">
+        <v>5.5</v>
+      </c>
+      <c r="BC20">
+        <v>21</v>
+      </c>
+      <c r="BD20">
         <v>5.2</v>
       </c>
-      <c r="AU20">
-        <v>4.3</v>
-      </c>
-      <c r="AV20">
-        <v>4.7</v>
-      </c>
-      <c r="AW20">
+      <c r="BE20">
         <v>5.5</v>
       </c>
-      <c r="AX20">
-        <v>5.6</v>
-      </c>
-      <c r="AY20">
-        <v>4.8</v>
-      </c>
-      <c r="AZ20">
-        <v>4.9</v>
-      </c>
-      <c r="BA20">
-        <v>5.8</v>
-      </c>
-      <c r="BB20">
-        <v>6.2</v>
-      </c>
-      <c r="BC20">
-        <v>5.8</v>
-      </c>
-      <c r="BD20">
-        <v>5.9</v>
-      </c>
-      <c r="BE20">
-        <v>6.4</v>
-      </c>
       <c r="BF20">
-        <v>5.1</v>
+        <v>17.5</v>
       </c>
       <c r="BG20">
-        <v>4.5</v>
+        <v>10</v>
       </c>
       <c r="BH20">
-        <v>5.4</v>
+        <v>5</v>
       </c>
       <c r="BI20">
-        <v>2.52</v>
+        <v>3.3</v>
       </c>
       <c r="BJ20">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BK20">
         <v>3.2</v>
       </c>
       <c r="BL20">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="BM20">
         <v>4.4</v>
@@ -5581,34 +5581,34 @@
         <v>8</v>
       </c>
       <c r="BO20">
-        <v>2.98</v>
+        <v>5.1</v>
       </c>
       <c r="BP20">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="BQ20">
         <v>3.95</v>
       </c>
       <c r="BR20">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="BS20">
         <v>4</v>
       </c>
       <c r="BT20">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="BU20">
-        <v>2.82</v>
+        <v>4.2</v>
       </c>
       <c r="BV20">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BW20">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="BX20">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="BY20">
         <v>4</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-06.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-06.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="144">
   <si>
     <t>League</t>
   </si>
@@ -256,18 +256,18 @@
     <t>SnapshotTS</t>
   </si>
   <si>
+    <t>Argentinian Primera Division</t>
+  </si>
+  <si>
+    <t>US United Soccer League</t>
+  </si>
+  <si>
+    <t>Colombian Primera A</t>
+  </si>
+  <si>
     <t>Bolivian Liga de Futbol Profesional</t>
   </si>
   <si>
-    <t>Argentinian Primera Division</t>
-  </si>
-  <si>
-    <t>US United Soccer League</t>
-  </si>
-  <si>
-    <t>Colombian Primera A</t>
-  </si>
-  <si>
     <t>Colombian Primera B</t>
   </si>
   <si>
@@ -286,9 +286,6 @@
     <t>2026-08-06</t>
   </si>
   <si>
-    <t>00:00:00</t>
-  </si>
-  <si>
     <t>00:15:00</t>
   </si>
   <si>
@@ -334,9 +331,6 @@
     <t>23:30:00</t>
   </si>
   <si>
-    <t>Bolivar</t>
-  </si>
-  <si>
     <t>Tigre</t>
   </si>
   <si>
@@ -379,6 +373,9 @@
     <t>Bogota</t>
   </si>
   <si>
+    <t>El Nacional</t>
+  </si>
+  <si>
     <t>Union Santa Fe</t>
   </si>
   <si>
@@ -391,9 +388,6 @@
     <t>Blooming Santa Cruz</t>
   </si>
   <si>
-    <t>Oriente Petrolero</t>
-  </si>
-  <si>
     <t>Belgrano</t>
   </si>
   <si>
@@ -436,6 +430,9 @@
     <t>Leones FC</t>
   </si>
   <si>
+    <t>Club Nueve de Octubre</t>
+  </si>
+  <si>
     <t>Lanus</t>
   </si>
   <si>
@@ -448,7 +445,7 @@
     <t>Always Ready</t>
   </si>
   <si>
-    <t>2026-08-05 21:13:17</t>
+    <t>2026-08-05 23:23:14</t>
   </si>
 </sst>
 </file>
@@ -1036,67 +1033,67 @@
         <v>90</v>
       </c>
       <c r="D2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F2">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="G2">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="H2">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="I2">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="J2">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="K2">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="L2">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="M2">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="N2">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="O2">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="P2">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="Q2">
-        <v>1.3</v>
+        <v>1.11</v>
       </c>
       <c r="R2">
-        <v>2.4</v>
+        <v>1.01</v>
       </c>
       <c r="S2">
-        <v>1.67</v>
+        <v>1.11</v>
       </c>
       <c r="T2">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="U2">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="V2">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="W2">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="X2">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="Y2">
         <v>1000</v>
@@ -1108,10 +1105,10 @@
         <v>1000</v>
       </c>
       <c r="AB2">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AC2">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AD2">
         <v>1000</v>
@@ -1120,142 +1117,142 @@
         <v>1000</v>
       </c>
       <c r="AF2">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AG2">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AH2">
         <v>1000</v>
       </c>
       <c r="AI2">
-        <v>220</v>
+        <v>1000</v>
       </c>
       <c r="AJ2">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AK2">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AL2">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AM2">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AN2">
-        <v>2.5</v>
+        <v>1000</v>
       </c>
       <c r="AO2">
-        <v>310</v>
+        <v>1000</v>
       </c>
       <c r="AP2">
-        <v>5.8</v>
+        <v>1.01</v>
       </c>
       <c r="AQ2">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="AR2">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AS2">
-        <v>22</v>
+        <v>1.01</v>
       </c>
       <c r="AT2">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="AU2">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="AV2">
-        <v>55</v>
+        <v>1.01</v>
       </c>
       <c r="AW2">
-        <v>3.75</v>
+        <v>1.01</v>
       </c>
       <c r="AX2">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="AY2">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="AZ2">
-        <v>25</v>
+        <v>1.01</v>
       </c>
       <c r="BA2">
-        <v>3.7</v>
+        <v>1.01</v>
       </c>
       <c r="BB2">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BC2">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="BD2">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BE2">
-        <v>70</v>
+        <v>1.01</v>
       </c>
       <c r="BF2">
-        <v>1.79</v>
+        <v>1.01</v>
       </c>
       <c r="BG2">
-        <v>3.7</v>
+        <v>1.01</v>
       </c>
       <c r="BH2">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="BI2">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="BJ2">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="BK2">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="BL2">
-        <v>940</v>
+        <v>0</v>
       </c>
       <c r="BM2">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="BN2">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="BO2">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="BP2">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="BQ2">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="BR2">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="BS2">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="BT2">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="BU2">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="BV2">
-        <v>170</v>
+        <v>0</v>
       </c>
       <c r="BW2">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="BX2">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="BY2">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="BZ2">
         <v>0</v>
@@ -1264,7 +1261,7 @@
         <v>0</v>
       </c>
       <c r="CB2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1278,240 +1275,240 @@
         <v>91</v>
       </c>
       <c r="D3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F3">
-        <v>2.48</v>
+        <v>1.16</v>
       </c>
       <c r="G3">
-        <v>2.54</v>
+        <v>1.23</v>
       </c>
       <c r="H3">
-        <v>4.1</v>
+        <v>60</v>
       </c>
       <c r="I3">
-        <v>4.2</v>
+        <v>120</v>
       </c>
       <c r="J3">
-        <v>2.76</v>
+        <v>5.8</v>
       </c>
       <c r="K3">
-        <v>2.78</v>
+        <v>7.8</v>
       </c>
       <c r="L3">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3">
+        <v>1.37</v>
+      </c>
+      <c r="O3">
+        <v>3.15</v>
+      </c>
+      <c r="P3">
+        <v>1.04</v>
+      </c>
+      <c r="Q3">
+        <v>17</v>
+      </c>
+      <c r="R3">
+        <v>1.01</v>
+      </c>
+      <c r="S3">
+        <v>130</v>
+      </c>
+      <c r="T3">
+        <v>4.4</v>
+      </c>
+      <c r="U3">
         <v>1.2</v>
       </c>
-      <c r="N3">
-        <v>2.18</v>
-      </c>
-      <c r="O3">
-        <v>1.82</v>
-      </c>
-      <c r="P3">
-        <v>1.37</v>
-      </c>
-      <c r="Q3">
-        <v>3.6</v>
-      </c>
-      <c r="R3">
-        <v>1.12</v>
-      </c>
-      <c r="S3">
-        <v>8.6</v>
-      </c>
-      <c r="T3">
-        <v>2.56</v>
-      </c>
-      <c r="U3">
-        <v>1.58</v>
-      </c>
       <c r="V3">
-        <v>1.31</v>
+        <v>1.01</v>
       </c>
       <c r="W3">
-        <v>1.64</v>
+        <v>5.1</v>
       </c>
       <c r="X3">
+        <v>1000</v>
+      </c>
+      <c r="Y3">
+        <v>1000</v>
+      </c>
+      <c r="Z3">
+        <v>1000</v>
+      </c>
+      <c r="AA3">
+        <v>1000</v>
+      </c>
+      <c r="AB3">
+        <v>1.46</v>
+      </c>
+      <c r="AC3">
+        <v>1000</v>
+      </c>
+      <c r="AD3">
+        <v>970</v>
+      </c>
+      <c r="AE3">
+        <v>1000</v>
+      </c>
+      <c r="AF3">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AG3">
+        <v>65</v>
+      </c>
+      <c r="AH3">
+        <v>1000</v>
+      </c>
+      <c r="AI3">
+        <v>1000</v>
+      </c>
+      <c r="AJ3">
+        <v>200</v>
+      </c>
+      <c r="AK3">
+        <v>1000</v>
+      </c>
+      <c r="AL3">
+        <v>1000</v>
+      </c>
+      <c r="AM3">
+        <v>1000</v>
+      </c>
+      <c r="AN3">
+        <v>1000</v>
+      </c>
+      <c r="AO3">
+        <v>1000</v>
+      </c>
+      <c r="AP3">
         <v>5.9</v>
       </c>
-      <c r="Y3">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="Z3">
-        <v>27</v>
-      </c>
-      <c r="AA3">
-        <v>110</v>
-      </c>
-      <c r="AB3">
-        <v>6.2</v>
-      </c>
-      <c r="AC3">
-        <v>7</v>
-      </c>
-      <c r="AD3">
-        <v>22</v>
-      </c>
-      <c r="AE3">
-        <v>160</v>
-      </c>
-      <c r="AF3">
-        <v>12.5</v>
-      </c>
-      <c r="AG3">
-        <v>14</v>
-      </c>
-      <c r="AH3">
-        <v>36</v>
-      </c>
-      <c r="AI3">
-        <v>150</v>
-      </c>
-      <c r="AJ3">
-        <v>38</v>
-      </c>
-      <c r="AK3">
-        <v>55</v>
-      </c>
-      <c r="AL3">
-        <v>970</v>
-      </c>
-      <c r="AM3">
-        <v>360</v>
-      </c>
-      <c r="AN3">
-        <v>55</v>
-      </c>
-      <c r="AO3">
-        <v>1000</v>
-      </c>
-      <c r="AP3">
-        <v>5.8</v>
-      </c>
       <c r="AQ3">
+        <v>10.5</v>
+      </c>
+      <c r="AR3">
+        <v>10.5</v>
+      </c>
+      <c r="AS3">
+        <v>10.5</v>
+      </c>
+      <c r="AT3">
+        <v>1.36</v>
+      </c>
+      <c r="AU3">
+        <v>6</v>
+      </c>
+      <c r="AV3">
+        <v>11</v>
+      </c>
+      <c r="AW3">
         <v>8.4</v>
       </c>
-      <c r="AR3">
-        <v>23</v>
-      </c>
-      <c r="AS3">
-        <v>80</v>
-      </c>
-      <c r="AT3">
-        <v>5.8</v>
-      </c>
-      <c r="AU3">
+      <c r="AX3">
         <v>6.6</v>
       </c>
-      <c r="AV3">
-        <v>18</v>
-      </c>
-      <c r="AW3">
-        <v>70</v>
-      </c>
-      <c r="AX3">
-        <v>11.5</v>
-      </c>
       <c r="AY3">
-        <v>13</v>
+        <v>9.6</v>
       </c>
       <c r="AZ3">
-        <v>28</v>
+        <v>8.4</v>
       </c>
       <c r="BA3">
-        <v>95</v>
+        <v>8.4</v>
       </c>
       <c r="BB3">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="BC3">
-        <v>34</v>
+        <v>10.5</v>
       </c>
       <c r="BD3">
-        <v>65</v>
+        <v>5.3</v>
       </c>
       <c r="BE3">
-        <v>230</v>
+        <v>5.9</v>
       </c>
       <c r="BF3">
-        <v>36</v>
+        <v>10.5</v>
       </c>
       <c r="BG3">
-        <v>95</v>
+        <v>8.4</v>
       </c>
       <c r="BH3">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BI3">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="BJ3">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BK3">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="BL3">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="BN3">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="BO3">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="BP3">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BQ3">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="BR3">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BS3">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="BT3">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="BU3">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="BV3">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BW3">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="BX3">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BY3">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="BZ3">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA3">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="CB3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="4" spans="1:80">
       <c r="A4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B4" t="s">
         <v>89</v>
@@ -1520,235 +1517,235 @@
         <v>92</v>
       </c>
       <c r="D4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E4" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F4">
-        <v>3.25</v>
+        <v>1.22</v>
       </c>
       <c r="G4">
-        <v>3.4</v>
+        <v>1.27</v>
       </c>
       <c r="H4">
-        <v>2.62</v>
+        <v>15</v>
       </c>
       <c r="I4">
-        <v>2.66</v>
+        <v>30</v>
       </c>
       <c r="J4">
-        <v>3.05</v>
+        <v>5.9</v>
       </c>
       <c r="K4">
-        <v>3.15</v>
+        <v>7.6</v>
       </c>
       <c r="L4">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="M4">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="N4">
-        <v>2.7</v>
+        <v>3.6</v>
       </c>
       <c r="O4">
-        <v>1.55</v>
+        <v>1.25</v>
       </c>
       <c r="P4">
-        <v>1.56</v>
+        <v>1.67</v>
       </c>
       <c r="Q4">
-        <v>2.72</v>
+        <v>2.26</v>
       </c>
       <c r="R4">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="S4">
         <v>5.5</v>
       </c>
       <c r="T4">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="U4">
-        <v>1.81</v>
+        <v>1.6</v>
       </c>
       <c r="V4">
-        <v>1.6</v>
+        <v>1.03</v>
       </c>
       <c r="W4">
-        <v>1.42</v>
+        <v>4.8</v>
       </c>
       <c r="X4">
-        <v>8.4</v>
+        <v>1000</v>
       </c>
       <c r="Y4">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="Z4">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AA4">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AB4">
-        <v>9.800000000000001</v>
+        <v>5.5</v>
       </c>
       <c r="AC4">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="AD4">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AE4">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AF4">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="AG4">
-        <v>15.5</v>
+        <v>990</v>
       </c>
       <c r="AH4">
-        <v>23</v>
+        <v>990</v>
       </c>
       <c r="AI4">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AJ4">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AK4">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AL4">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AM4">
-        <v>210</v>
+        <v>1000</v>
       </c>
       <c r="AN4">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AO4">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AP4">
-        <v>7.6</v>
+        <v>1.8</v>
       </c>
       <c r="AQ4">
-        <v>7.2</v>
+        <v>1.8</v>
       </c>
       <c r="AR4">
-        <v>13.5</v>
+        <v>1.8</v>
       </c>
       <c r="AS4">
-        <v>22</v>
+        <v>1.8</v>
       </c>
       <c r="AT4">
-        <v>8.4</v>
+        <v>1.35</v>
       </c>
       <c r="AU4">
-        <v>6.2</v>
+        <v>5.6</v>
       </c>
       <c r="AV4">
-        <v>11</v>
+        <v>1.8</v>
       </c>
       <c r="AW4">
-        <v>29</v>
+        <v>1.8</v>
       </c>
       <c r="AX4">
-        <v>18.5</v>
+        <v>4</v>
       </c>
       <c r="AY4">
-        <v>13</v>
+        <v>1.8</v>
       </c>
       <c r="AZ4">
-        <v>19</v>
+        <v>1.8</v>
       </c>
       <c r="BA4">
-        <v>12</v>
+        <v>1.8</v>
       </c>
       <c r="BB4">
-        <v>34</v>
+        <v>7.4</v>
       </c>
       <c r="BC4">
-        <v>28</v>
+        <v>1.8</v>
       </c>
       <c r="BD4">
-        <v>36</v>
+        <v>1.8</v>
       </c>
       <c r="BE4">
-        <v>13.5</v>
+        <v>1.8</v>
       </c>
       <c r="BF4">
-        <v>38</v>
+        <v>10.5</v>
       </c>
       <c r="BG4">
-        <v>30</v>
+        <v>1.8</v>
       </c>
       <c r="BH4">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="BI4">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="BJ4">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="BK4">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="BL4">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM4">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="BN4">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="BO4">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="BP4">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="BQ4">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="BR4">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="BS4">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="BT4">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="BU4">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="BV4">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="BW4">
-        <v>9.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="BX4">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="BY4">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="BZ4">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="CA4">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="CB4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1762,235 +1759,235 @@
         <v>93</v>
       </c>
       <c r="D5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E5" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F5">
-        <v>1.77</v>
+        <v>5.7</v>
       </c>
       <c r="G5">
-        <v>1.81</v>
+        <v>5.8</v>
       </c>
       <c r="H5">
+        <v>2.22</v>
+      </c>
+      <c r="I5">
+        <v>2.28</v>
+      </c>
+      <c r="J5">
+        <v>2.6</v>
+      </c>
+      <c r="K5">
+        <v>2.66</v>
+      </c>
+      <c r="L5">
+        <v>0</v>
+      </c>
+      <c r="M5">
+        <v>1.31</v>
+      </c>
+      <c r="N5">
+        <v>1.64</v>
+      </c>
+      <c r="O5">
+        <v>2.52</v>
+      </c>
+      <c r="P5">
+        <v>1.2</v>
+      </c>
+      <c r="Q5">
+        <v>5.5</v>
+      </c>
+      <c r="R5">
+        <v>1.05</v>
+      </c>
+      <c r="S5">
+        <v>17.5</v>
+      </c>
+      <c r="T5">
+        <v>3.9</v>
+      </c>
+      <c r="U5">
+        <v>1.29</v>
+      </c>
+      <c r="V5">
+        <v>1.72</v>
+      </c>
+      <c r="W5">
+        <v>1.22</v>
+      </c>
+      <c r="X5">
+        <v>4</v>
+      </c>
+      <c r="Y5">
         <v>4.4</v>
       </c>
-      <c r="I5">
-        <v>4.7</v>
-      </c>
-      <c r="J5">
-        <v>4.3</v>
-      </c>
-      <c r="K5">
-        <v>4.7</v>
-      </c>
-      <c r="L5">
-        <v>1.3</v>
-      </c>
-      <c r="M5">
-        <v>1.04</v>
-      </c>
-      <c r="N5">
-        <v>5.7</v>
-      </c>
-      <c r="O5">
-        <v>1.2</v>
-      </c>
-      <c r="P5">
-        <v>2.58</v>
-      </c>
-      <c r="Q5">
-        <v>1.6</v>
-      </c>
-      <c r="R5">
-        <v>1.63</v>
-      </c>
-      <c r="S5">
-        <v>2.5</v>
-      </c>
-      <c r="T5">
-        <v>1.61</v>
-      </c>
-      <c r="U5">
-        <v>2.44</v>
-      </c>
-      <c r="V5">
-        <v>1.27</v>
-      </c>
-      <c r="W5">
-        <v>2.22</v>
-      </c>
-      <c r="X5">
-        <v>27</v>
-      </c>
-      <c r="Y5">
-        <v>24</v>
-      </c>
       <c r="Z5">
-        <v>48</v>
+        <v>11.5</v>
       </c>
       <c r="AA5">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AB5">
-        <v>13</v>
+        <v>9.6</v>
       </c>
       <c r="AC5">
-        <v>11</v>
+        <v>9.6</v>
       </c>
       <c r="AD5">
-        <v>19.5</v>
+        <v>990</v>
       </c>
       <c r="AE5">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AF5">
-        <v>13.5</v>
+        <v>55</v>
       </c>
       <c r="AG5">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AH5">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AI5">
+        <v>1000</v>
+      </c>
+      <c r="AJ5">
+        <v>1000</v>
+      </c>
+      <c r="AK5">
+        <v>1000</v>
+      </c>
+      <c r="AL5">
+        <v>1000</v>
+      </c>
+      <c r="AM5">
+        <v>1000</v>
+      </c>
+      <c r="AN5">
+        <v>1000</v>
+      </c>
+      <c r="AO5">
+        <v>1000</v>
+      </c>
+      <c r="AP5">
+        <v>3.5</v>
+      </c>
+      <c r="AQ5">
+        <v>3.95</v>
+      </c>
+      <c r="AR5">
+        <v>9</v>
+      </c>
+      <c r="AS5">
+        <v>26</v>
+      </c>
+      <c r="AT5">
+        <v>8</v>
+      </c>
+      <c r="AU5">
+        <v>8</v>
+      </c>
+      <c r="AV5">
+        <v>12</v>
+      </c>
+      <c r="AW5">
         <v>50</v>
       </c>
-      <c r="AJ5">
-        <v>19.5</v>
-      </c>
-      <c r="AK5">
-        <v>17</v>
-      </c>
-      <c r="AL5">
-        <v>36</v>
-      </c>
-      <c r="AM5">
-        <v>100</v>
-      </c>
-      <c r="AN5">
-        <v>8</v>
-      </c>
-      <c r="AO5">
-        <v>60</v>
-      </c>
-      <c r="AP5">
-        <v>22</v>
-      </c>
-      <c r="AQ5">
-        <v>20</v>
-      </c>
-      <c r="AR5">
+      <c r="AX5">
         <v>32</v>
       </c>
-      <c r="AS5">
-        <v>9.6</v>
-      </c>
-      <c r="AT5">
-        <v>11</v>
-      </c>
-      <c r="AU5">
-        <v>9</v>
-      </c>
-      <c r="AV5">
-        <v>16.5</v>
-      </c>
-      <c r="AW5">
-        <v>34</v>
-      </c>
-      <c r="AX5">
-        <v>11</v>
-      </c>
       <c r="AY5">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="AZ5">
-        <v>14.5</v>
+        <v>5.1</v>
       </c>
       <c r="BA5">
-        <v>8.800000000000001</v>
+        <v>180</v>
       </c>
       <c r="BB5">
-        <v>17</v>
+        <v>160</v>
       </c>
       <c r="BC5">
-        <v>14.5</v>
+        <v>160</v>
       </c>
       <c r="BD5">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BE5">
-        <v>9.199999999999999</v>
+        <v>50</v>
       </c>
       <c r="BF5">
-        <v>7</v>
+        <v>11.5</v>
       </c>
       <c r="BG5">
-        <v>26</v>
+        <v>50</v>
       </c>
       <c r="BH5">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="BI5">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="BJ5">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="BK5">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="BL5">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM5">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="BN5">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="BO5">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="BP5">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="BQ5">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="BR5">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="BS5">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="BT5">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="BU5">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="BV5">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="BW5">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="BX5">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BY5">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="BZ5">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="CA5">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="CB5" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -2004,468 +2001,468 @@
         <v>94</v>
       </c>
       <c r="D6" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E6" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="F6">
-        <v>2.28</v>
+        <v>2.12</v>
       </c>
       <c r="G6">
-        <v>2.34</v>
+        <v>2.16</v>
       </c>
       <c r="H6">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="I6">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="J6">
-        <v>3.35</v>
+        <v>3.9</v>
       </c>
       <c r="K6">
-        <v>3.45</v>
+        <v>4.2</v>
       </c>
       <c r="L6">
-        <v>1.46</v>
+        <v>1.01</v>
       </c>
       <c r="M6">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="N6">
-        <v>3.35</v>
+        <v>4.7</v>
       </c>
       <c r="O6">
-        <v>1.4</v>
+        <v>1.22</v>
       </c>
       <c r="P6">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
       <c r="Q6">
-        <v>2.22</v>
+        <v>1.63</v>
       </c>
       <c r="R6">
-        <v>1.29</v>
+        <v>1.51</v>
       </c>
       <c r="S6">
-        <v>4.2</v>
+        <v>2.62</v>
       </c>
       <c r="T6">
-        <v>1.91</v>
+        <v>1.65</v>
       </c>
       <c r="U6">
-        <v>2.02</v>
+        <v>2.36</v>
       </c>
       <c r="V6">
         <v>1.37</v>
       </c>
       <c r="W6">
-        <v>1.74</v>
+        <v>1.86</v>
       </c>
       <c r="X6">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="Y6">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="Z6">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="AA6">
         <v>75</v>
       </c>
       <c r="AB6">
-        <v>8.800000000000001</v>
+        <v>12.5</v>
       </c>
       <c r="AC6">
-        <v>7.8</v>
+        <v>10.5</v>
       </c>
       <c r="AD6">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="AE6">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="AF6">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AG6">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AH6">
         <v>19</v>
       </c>
       <c r="AI6">
-        <v>65</v>
+        <v>44</v>
       </c>
       <c r="AJ6">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AK6">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="AL6">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="AM6">
-        <v>120</v>
+        <v>80</v>
       </c>
       <c r="AN6">
-        <v>23</v>
+        <v>11.5</v>
       </c>
       <c r="AO6">
-        <v>55</v>
+        <v>34</v>
       </c>
       <c r="AP6">
-        <v>10.5</v>
+        <v>18.5</v>
       </c>
       <c r="AQ6">
+        <v>14</v>
+      </c>
+      <c r="AR6">
         <v>11.5</v>
       </c>
-      <c r="AR6">
-        <v>22</v>
-      </c>
       <c r="AS6">
-        <v>60</v>
+        <v>6.6</v>
       </c>
       <c r="AT6">
-        <v>8.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AU6">
-        <v>7</v>
+        <v>8.4</v>
       </c>
       <c r="AV6">
         <v>13.5</v>
       </c>
       <c r="AW6">
-        <v>42</v>
+        <v>14.5</v>
       </c>
       <c r="AX6">
         <v>12.5</v>
       </c>
       <c r="AY6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ6">
-        <v>17.5</v>
+        <v>13.5</v>
       </c>
       <c r="BA6">
-        <v>50</v>
+        <v>6.2</v>
       </c>
       <c r="BB6">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="BC6">
-        <v>23</v>
+        <v>16.5</v>
       </c>
       <c r="BD6">
-        <v>38</v>
+        <v>16</v>
       </c>
       <c r="BE6">
-        <v>95</v>
+        <v>6.6</v>
       </c>
       <c r="BF6">
-        <v>19.5</v>
+        <v>9.4</v>
       </c>
       <c r="BG6">
-        <v>44</v>
+        <v>6</v>
       </c>
       <c r="BH6">
-        <v>3.2</v>
+        <v>1000</v>
       </c>
       <c r="BI6">
-        <v>2.86</v>
+        <v>1.01</v>
       </c>
       <c r="BJ6">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="BK6">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="BL6">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="BM6">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="BN6">
-        <v>5.1</v>
+        <v>1000</v>
       </c>
       <c r="BO6">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="BP6">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="BQ6">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="BR6">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="BS6">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BT6">
-        <v>7</v>
+        <v>1000</v>
       </c>
       <c r="BU6">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="BV6">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BW6">
-        <v>19</v>
+        <v>1.01</v>
       </c>
       <c r="BX6">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="BY6">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="BZ6">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="CA6">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="CB6" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="7" spans="1:80">
       <c r="A7" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="B7" t="s">
         <v>89</v>
       </c>
       <c r="C7" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D7" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E7" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F7">
-        <v>2.12</v>
+        <v>1.85</v>
       </c>
       <c r="G7">
-        <v>2.16</v>
+        <v>1.98</v>
       </c>
       <c r="H7">
-        <v>3.4</v>
+        <v>5.3</v>
       </c>
       <c r="I7">
-        <v>3.65</v>
+        <v>6.2</v>
       </c>
       <c r="J7">
-        <v>3.95</v>
+        <v>3.15</v>
       </c>
       <c r="K7">
-        <v>4.2</v>
+        <v>3.55</v>
       </c>
       <c r="L7">
-        <v>1.01</v>
+        <v>1.51</v>
       </c>
       <c r="M7">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="N7">
-        <v>4.8</v>
+        <v>2.54</v>
       </c>
       <c r="O7">
-        <v>1.21</v>
+        <v>1.55</v>
       </c>
       <c r="P7">
-        <v>2.32</v>
+        <v>1.51</v>
       </c>
       <c r="Q7">
-        <v>1.69</v>
+        <v>2.62</v>
       </c>
       <c r="R7">
-        <v>1.52</v>
+        <v>1.17</v>
       </c>
       <c r="S7">
-        <v>2.56</v>
+        <v>5.7</v>
       </c>
       <c r="T7">
-        <v>1.65</v>
+        <v>2.26</v>
       </c>
       <c r="U7">
-        <v>2.38</v>
+        <v>1.67</v>
       </c>
       <c r="V7">
-        <v>1.37</v>
+        <v>1.19</v>
       </c>
       <c r="W7">
-        <v>1.86</v>
+        <v>2.02</v>
       </c>
       <c r="X7">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="Y7">
+        <v>15.5</v>
+      </c>
+      <c r="Z7">
+        <v>50</v>
+      </c>
+      <c r="AA7">
+        <v>900</v>
+      </c>
+      <c r="AB7">
+        <v>6.4</v>
+      </c>
+      <c r="AC7">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD7">
+        <v>28</v>
+      </c>
+      <c r="AE7">
+        <v>140</v>
+      </c>
+      <c r="AF7">
+        <v>11.5</v>
+      </c>
+      <c r="AG7">
+        <v>9.4</v>
+      </c>
+      <c r="AH7">
+        <v>34</v>
+      </c>
+      <c r="AI7">
+        <v>700</v>
+      </c>
+      <c r="AJ7">
         <v>24</v>
       </c>
-      <c r="Y7">
-        <v>22</v>
-      </c>
-      <c r="Z7">
-        <v>34</v>
-      </c>
-      <c r="AA7">
-        <v>70</v>
-      </c>
-      <c r="AB7">
-        <v>13</v>
-      </c>
-      <c r="AC7">
-        <v>10.5</v>
-      </c>
-      <c r="AD7">
-        <v>16.5</v>
-      </c>
-      <c r="AE7">
-        <v>42</v>
-      </c>
-      <c r="AF7">
-        <v>16</v>
-      </c>
-      <c r="AG7">
-        <v>11.5</v>
-      </c>
-      <c r="AH7">
-        <v>17</v>
-      </c>
-      <c r="AI7">
-        <v>42</v>
-      </c>
-      <c r="AJ7">
+      <c r="AK7">
+        <v>32</v>
+      </c>
+      <c r="AL7">
+        <v>75</v>
+      </c>
+      <c r="AM7">
+        <v>500</v>
+      </c>
+      <c r="AN7">
         <v>27</v>
       </c>
-      <c r="AK7">
-        <v>23</v>
-      </c>
-      <c r="AL7">
-        <v>29</v>
-      </c>
-      <c r="AM7">
-        <v>75</v>
-      </c>
-      <c r="AN7">
-        <v>12</v>
-      </c>
       <c r="AO7">
-        <v>28</v>
+        <v>700</v>
       </c>
       <c r="AP7">
-        <v>19</v>
+        <v>6.8</v>
       </c>
       <c r="AQ7">
-        <v>15.5</v>
+        <v>11</v>
       </c>
       <c r="AR7">
-        <v>11.5</v>
+        <v>7.2</v>
       </c>
       <c r="AS7">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AT7">
+        <v>5.3</v>
+      </c>
+      <c r="AU7">
         <v>6.8</v>
       </c>
-      <c r="AT7">
-        <v>10.5</v>
-      </c>
-      <c r="AU7">
+      <c r="AV7">
+        <v>20</v>
+      </c>
+      <c r="AW7">
+        <v>8</v>
+      </c>
+      <c r="AX7">
         <v>8.4</v>
-      </c>
-      <c r="AV7">
-        <v>13</v>
-      </c>
-      <c r="AW7">
-        <v>14.5</v>
-      </c>
-      <c r="AX7">
-        <v>13</v>
       </c>
       <c r="AY7">
         <v>9</v>
       </c>
       <c r="AZ7">
-        <v>13.5</v>
+        <v>6.8</v>
       </c>
       <c r="BA7">
-        <v>6.4</v>
+        <v>8</v>
       </c>
       <c r="BB7">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="BC7">
-        <v>16.5</v>
+        <v>6.6</v>
       </c>
       <c r="BD7">
-        <v>16</v>
+        <v>7.6</v>
       </c>
       <c r="BE7">
-        <v>6.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF7">
-        <v>9.4</v>
+        <v>20</v>
       </c>
       <c r="BG7">
-        <v>5.9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH7">
-        <v>1000</v>
+        <v>2.94</v>
       </c>
       <c r="BI7">
-        <v>1.01</v>
+        <v>2.26</v>
       </c>
       <c r="BJ7">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="BK7">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BL7">
         <v>1000</v>
       </c>
       <c r="BM7">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BN7">
-        <v>1000</v>
+        <v>4.8</v>
       </c>
       <c r="BO7">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="BP7">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="BQ7">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BR7">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="BS7">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BT7">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="BU7">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="BV7">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="BW7">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BX7">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="BY7">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BZ7">
         <v>0</v>
@@ -2474,12 +2471,12 @@
         <v>0</v>
       </c>
       <c r="CB7" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="8" spans="1:80">
       <c r="A8" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B8" t="s">
         <v>89</v>
@@ -2488,240 +2485,240 @@
         <v>95</v>
       </c>
       <c r="D8" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E8" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F8">
-        <v>1.86</v>
+        <v>1.58</v>
       </c>
       <c r="G8">
-        <v>2</v>
+        <v>1.69</v>
       </c>
       <c r="H8">
-        <v>5.3</v>
+        <v>4.7</v>
       </c>
       <c r="I8">
-        <v>6.2</v>
+        <v>5.6</v>
       </c>
       <c r="J8">
-        <v>3.1</v>
+        <v>4.9</v>
       </c>
       <c r="K8">
+        <v>5.7</v>
+      </c>
+      <c r="L8">
+        <v>1.01</v>
+      </c>
+      <c r="M8">
+        <v>1.02</v>
+      </c>
+      <c r="N8">
+        <v>7.6</v>
+      </c>
+      <c r="O8">
+        <v>1.11</v>
+      </c>
+      <c r="P8">
+        <v>3.4</v>
+      </c>
+      <c r="Q8">
+        <v>1.33</v>
+      </c>
+      <c r="R8">
+        <v>2.02</v>
+      </c>
+      <c r="S8">
+        <v>1.82</v>
+      </c>
+      <c r="T8">
+        <v>1.46</v>
+      </c>
+      <c r="U8">
+        <v>2.82</v>
+      </c>
+      <c r="V8">
+        <v>1.21</v>
+      </c>
+      <c r="W8">
+        <v>2.44</v>
+      </c>
+      <c r="X8">
+        <v>120</v>
+      </c>
+      <c r="Y8">
+        <v>80</v>
+      </c>
+      <c r="Z8">
+        <v>65</v>
+      </c>
+      <c r="AA8">
+        <v>700</v>
+      </c>
+      <c r="AB8">
+        <v>19</v>
+      </c>
+      <c r="AC8">
+        <v>15.5</v>
+      </c>
+      <c r="AD8">
+        <v>24</v>
+      </c>
+      <c r="AE8">
+        <v>120</v>
+      </c>
+      <c r="AF8">
+        <v>18</v>
+      </c>
+      <c r="AG8">
+        <v>12.5</v>
+      </c>
+      <c r="AH8">
+        <v>17.5</v>
+      </c>
+      <c r="AI8">
+        <v>42</v>
+      </c>
+      <c r="AJ8">
+        <v>20</v>
+      </c>
+      <c r="AK8">
+        <v>16</v>
+      </c>
+      <c r="AL8">
+        <v>23</v>
+      </c>
+      <c r="AM8">
+        <v>55</v>
+      </c>
+      <c r="AN8">
+        <v>4.8</v>
+      </c>
+      <c r="AO8">
+        <v>28</v>
+      </c>
+      <c r="AP8">
+        <v>32</v>
+      </c>
+      <c r="AQ8">
+        <v>18</v>
+      </c>
+      <c r="AR8">
+        <v>9</v>
+      </c>
+      <c r="AS8">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AT8">
+        <v>15</v>
+      </c>
+      <c r="AU8">
+        <v>11</v>
+      </c>
+      <c r="AV8">
+        <v>17</v>
+      </c>
+      <c r="AW8">
+        <v>7.6</v>
+      </c>
+      <c r="AX8">
+        <v>14.5</v>
+      </c>
+      <c r="AY8">
+        <v>10</v>
+      </c>
+      <c r="AZ8">
+        <v>12.5</v>
+      </c>
+      <c r="BA8">
+        <v>9</v>
+      </c>
+      <c r="BB8">
+        <v>16.5</v>
+      </c>
+      <c r="BC8">
+        <v>12.5</v>
+      </c>
+      <c r="BD8">
+        <v>18</v>
+      </c>
+      <c r="BE8">
+        <v>9</v>
+      </c>
+      <c r="BF8">
+        <v>4</v>
+      </c>
+      <c r="BG8">
+        <v>6.6</v>
+      </c>
+      <c r="BH8">
+        <v>6.8</v>
+      </c>
+      <c r="BI8">
+        <v>4.7</v>
+      </c>
+      <c r="BJ8">
+        <v>10</v>
+      </c>
+      <c r="BK8">
         <v>3.5</v>
       </c>
-      <c r="L8">
-        <v>1.52</v>
-      </c>
-      <c r="M8">
-        <v>1.13</v>
-      </c>
-      <c r="N8">
-        <v>2.46</v>
-      </c>
-      <c r="O8">
-        <v>1.57</v>
-      </c>
-      <c r="P8">
-        <v>1.49</v>
-      </c>
-      <c r="Q8">
-        <v>2.7</v>
-      </c>
-      <c r="R8">
-        <v>1.17</v>
-      </c>
-      <c r="S8">
-        <v>5.7</v>
-      </c>
-      <c r="T8">
-        <v>2.3</v>
-      </c>
-      <c r="U8">
-        <v>1.65</v>
-      </c>
-      <c r="V8">
-        <v>1.2</v>
-      </c>
-      <c r="W8">
-        <v>2</v>
-      </c>
-      <c r="X8">
-        <v>9.6</v>
-      </c>
-      <c r="Y8">
-        <v>15.5</v>
-      </c>
-      <c r="Z8">
-        <v>50</v>
-      </c>
-      <c r="AA8">
-        <v>900</v>
-      </c>
-      <c r="AB8">
-        <v>6.4</v>
-      </c>
-      <c r="AC8">
-        <v>9</v>
-      </c>
-      <c r="AD8">
-        <v>28</v>
-      </c>
-      <c r="AE8">
-        <v>140</v>
-      </c>
-      <c r="AF8">
+      <c r="BL8">
+        <v>1000</v>
+      </c>
+      <c r="BM8">
+        <v>5</v>
+      </c>
+      <c r="BN8">
+        <v>6</v>
+      </c>
+      <c r="BO8">
+        <v>4.2</v>
+      </c>
+      <c r="BP8">
         <v>11.5</v>
       </c>
-      <c r="AG8">
-        <v>13</v>
-      </c>
-      <c r="AH8">
+      <c r="BQ8">
+        <v>3.7</v>
+      </c>
+      <c r="BR8">
+        <v>18.5</v>
+      </c>
+      <c r="BS8">
+        <v>4.2</v>
+      </c>
+      <c r="BT8">
+        <v>11</v>
+      </c>
+      <c r="BU8">
+        <v>3.65</v>
+      </c>
+      <c r="BV8">
+        <v>36</v>
+      </c>
+      <c r="BW8">
+        <v>4.7</v>
+      </c>
+      <c r="BX8">
         <v>34</v>
       </c>
-      <c r="AI8">
-        <v>700</v>
-      </c>
-      <c r="AJ8">
-        <v>27</v>
-      </c>
-      <c r="AK8">
-        <v>34</v>
-      </c>
-      <c r="AL8">
-        <v>80</v>
-      </c>
-      <c r="AM8">
-        <v>500</v>
-      </c>
-      <c r="AN8">
-        <v>29</v>
-      </c>
-      <c r="AO8">
-        <v>700</v>
-      </c>
-      <c r="AP8">
-        <v>6.4</v>
-      </c>
-      <c r="AQ8">
-        <v>11</v>
-      </c>
-      <c r="AR8">
-        <v>5</v>
-      </c>
-      <c r="AS8">
-        <v>5.5</v>
-      </c>
-      <c r="AT8">
-        <v>5.2</v>
-      </c>
-      <c r="AU8">
-        <v>6.8</v>
-      </c>
-      <c r="AV8">
-        <v>20</v>
-      </c>
-      <c r="AW8">
-        <v>5.4</v>
-      </c>
-      <c r="AX8">
-        <v>8.4</v>
-      </c>
-      <c r="AY8">
-        <v>9.6</v>
-      </c>
-      <c r="AZ8">
-        <v>4.8</v>
-      </c>
-      <c r="BA8">
-        <v>5.4</v>
-      </c>
-      <c r="BB8">
-        <v>19.5</v>
-      </c>
-      <c r="BC8">
-        <v>4.8</v>
-      </c>
-      <c r="BD8">
-        <v>5.2</v>
-      </c>
-      <c r="BE8">
-        <v>5.5</v>
-      </c>
-      <c r="BF8">
-        <v>20</v>
-      </c>
-      <c r="BG8">
-        <v>5.5</v>
-      </c>
-      <c r="BH8">
-        <v>2.94</v>
-      </c>
-      <c r="BI8">
-        <v>2.26</v>
-      </c>
-      <c r="BJ8">
-        <v>14.5</v>
-      </c>
-      <c r="BK8">
-        <v>4.3</v>
-      </c>
-      <c r="BL8">
-        <v>1000</v>
-      </c>
-      <c r="BM8">
-        <v>6</v>
-      </c>
-      <c r="BN8">
-        <v>4.8</v>
-      </c>
-      <c r="BO8">
-        <v>2.68</v>
-      </c>
-      <c r="BP8">
-        <v>18</v>
-      </c>
-      <c r="BQ8">
-        <v>4.5</v>
-      </c>
-      <c r="BR8">
-        <v>50</v>
-      </c>
-      <c r="BS8">
-        <v>5.4</v>
-      </c>
-      <c r="BT8">
+      <c r="BY8">
+        <v>4.7</v>
+      </c>
+      <c r="BZ8">
         <v>10</v>
       </c>
-      <c r="BU8">
-        <v>3.8</v>
-      </c>
-      <c r="BV8">
-        <v>75</v>
-      </c>
-      <c r="BW8">
-        <v>5.6</v>
-      </c>
-      <c r="BX8">
-        <v>100</v>
-      </c>
-      <c r="BY8">
-        <v>5.8</v>
-      </c>
-      <c r="BZ8">
-        <v>0</v>
-      </c>
       <c r="CA8">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="CB8" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="9" spans="1:80">
       <c r="A9" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B9" t="s">
         <v>89</v>
@@ -2730,235 +2727,235 @@
         <v>96</v>
       </c>
       <c r="D9" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E9" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F9">
-        <v>1.58</v>
+        <v>2.56</v>
       </c>
       <c r="G9">
-        <v>1.69</v>
+        <v>2.8</v>
       </c>
       <c r="H9">
-        <v>4.7</v>
+        <v>2.88</v>
       </c>
       <c r="I9">
-        <v>5.6</v>
+        <v>3.3</v>
       </c>
       <c r="J9">
+        <v>2.88</v>
+      </c>
+      <c r="K9">
+        <v>3.7</v>
+      </c>
+      <c r="L9">
+        <v>1.41</v>
+      </c>
+      <c r="M9">
+        <v>1.07</v>
+      </c>
+      <c r="N9">
+        <v>3.35</v>
+      </c>
+      <c r="O9">
+        <v>1.33</v>
+      </c>
+      <c r="P9">
+        <v>1.81</v>
+      </c>
+      <c r="Q9">
+        <v>2.02</v>
+      </c>
+      <c r="R9">
+        <v>1.31</v>
+      </c>
+      <c r="S9">
+        <v>3.6</v>
+      </c>
+      <c r="T9">
+        <v>1.76</v>
+      </c>
+      <c r="U9">
+        <v>2.06</v>
+      </c>
+      <c r="V9">
+        <v>1.46</v>
+      </c>
+      <c r="W9">
+        <v>1.56</v>
+      </c>
+      <c r="X9">
+        <v>15.5</v>
+      </c>
+      <c r="Y9">
+        <v>14</v>
+      </c>
+      <c r="Z9">
+        <v>25</v>
+      </c>
+      <c r="AA9">
+        <v>60</v>
+      </c>
+      <c r="AB9">
+        <v>12.5</v>
+      </c>
+      <c r="AC9">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD9">
+        <v>16</v>
+      </c>
+      <c r="AE9">
+        <v>42</v>
+      </c>
+      <c r="AF9">
+        <v>18.5</v>
+      </c>
+      <c r="AG9">
+        <v>13</v>
+      </c>
+      <c r="AH9">
+        <v>19</v>
+      </c>
+      <c r="AI9">
+        <v>55</v>
+      </c>
+      <c r="AJ9">
+        <v>46</v>
+      </c>
+      <c r="AK9">
+        <v>36</v>
+      </c>
+      <c r="AL9">
+        <v>50</v>
+      </c>
+      <c r="AM9">
+        <v>110</v>
+      </c>
+      <c r="AN9">
+        <v>30</v>
+      </c>
+      <c r="AO9">
+        <v>36</v>
+      </c>
+      <c r="AP9">
+        <v>11</v>
+      </c>
+      <c r="AQ9">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AR9">
+        <v>17.5</v>
+      </c>
+      <c r="AS9">
+        <v>5.1</v>
+      </c>
+      <c r="AT9">
+        <v>9</v>
+      </c>
+      <c r="AU9">
+        <v>6.6</v>
+      </c>
+      <c r="AV9">
+        <v>11</v>
+      </c>
+      <c r="AW9">
         <v>4.9</v>
       </c>
-      <c r="K9">
-        <v>5.7</v>
-      </c>
-      <c r="L9">
-        <v>1.01</v>
-      </c>
-      <c r="M9">
-        <v>1.02</v>
-      </c>
-      <c r="N9">
-        <v>7.6</v>
-      </c>
-      <c r="O9">
-        <v>1.11</v>
-      </c>
-      <c r="P9">
-        <v>3.4</v>
-      </c>
-      <c r="Q9">
-        <v>1.33</v>
-      </c>
-      <c r="R9">
-        <v>2.02</v>
-      </c>
-      <c r="S9">
-        <v>1.82</v>
-      </c>
-      <c r="T9">
-        <v>1.46</v>
-      </c>
-      <c r="U9">
-        <v>2.82</v>
-      </c>
-      <c r="V9">
-        <v>1.21</v>
-      </c>
-      <c r="W9">
-        <v>2.44</v>
-      </c>
-      <c r="X9">
-        <v>120</v>
-      </c>
-      <c r="Y9">
-        <v>80</v>
-      </c>
-      <c r="Z9">
-        <v>65</v>
-      </c>
-      <c r="AA9">
-        <v>700</v>
-      </c>
-      <c r="AB9">
-        <v>21</v>
-      </c>
-      <c r="AC9">
-        <v>15.5</v>
-      </c>
-      <c r="AD9">
-        <v>24</v>
-      </c>
-      <c r="AE9">
-        <v>120</v>
-      </c>
-      <c r="AF9">
-        <v>18</v>
-      </c>
-      <c r="AG9">
-        <v>12.5</v>
-      </c>
-      <c r="AH9">
-        <v>17.5</v>
-      </c>
-      <c r="AI9">
-        <v>150</v>
-      </c>
-      <c r="AJ9">
-        <v>20</v>
-      </c>
-      <c r="AK9">
-        <v>16</v>
-      </c>
-      <c r="AL9">
-        <v>23</v>
-      </c>
-      <c r="AM9">
-        <v>55</v>
-      </c>
-      <c r="AN9">
-        <v>4.8</v>
-      </c>
-      <c r="AO9">
-        <v>28</v>
-      </c>
-      <c r="AP9">
-        <v>32</v>
-      </c>
-      <c r="AQ9">
-        <v>18</v>
-      </c>
-      <c r="AR9">
-        <v>9</v>
-      </c>
-      <c r="AS9">
-        <v>7.8</v>
-      </c>
-      <c r="AT9">
-        <v>15</v>
-      </c>
-      <c r="AU9">
-        <v>11</v>
-      </c>
-      <c r="AV9">
-        <v>17</v>
-      </c>
-      <c r="AW9">
-        <v>7.2</v>
-      </c>
       <c r="AX9">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AY9">
         <v>10</v>
       </c>
       <c r="AZ9">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="BA9">
-        <v>9</v>
+        <v>5.1</v>
       </c>
       <c r="BB9">
-        <v>16.5</v>
+        <v>13</v>
       </c>
       <c r="BC9">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BD9">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="BE9">
-        <v>9</v>
+        <v>5.3</v>
       </c>
       <c r="BF9">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="BG9">
-        <v>6.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH9">
-        <v>6.8</v>
+        <v>3.8</v>
       </c>
       <c r="BI9">
+        <v>2.64</v>
+      </c>
+      <c r="BJ9">
+        <v>11.5</v>
+      </c>
+      <c r="BK9">
+        <v>3.4</v>
+      </c>
+      <c r="BL9">
+        <v>1000</v>
+      </c>
+      <c r="BM9">
         <v>4.7</v>
       </c>
-      <c r="BJ9">
-        <v>10</v>
-      </c>
-      <c r="BK9">
-        <v>3.5</v>
-      </c>
-      <c r="BL9">
-        <v>1000</v>
-      </c>
-      <c r="BM9">
-        <v>5</v>
-      </c>
       <c r="BN9">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BO9">
         <v>4.2</v>
       </c>
       <c r="BP9">
-        <v>11.5</v>
+        <v>24</v>
       </c>
       <c r="BQ9">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="BR9">
-        <v>18.5</v>
+        <v>42</v>
       </c>
       <c r="BS9">
+        <v>4.4</v>
+      </c>
+      <c r="BT9">
+        <v>7.2</v>
+      </c>
+      <c r="BU9">
+        <v>4.6</v>
+      </c>
+      <c r="BV9">
+        <v>29</v>
+      </c>
+      <c r="BW9">
         <v>4.2</v>
       </c>
-      <c r="BT9">
-        <v>11</v>
-      </c>
-      <c r="BU9">
-        <v>3.65</v>
-      </c>
-      <c r="BV9">
+      <c r="BX9">
+        <v>46</v>
+      </c>
+      <c r="BY9">
+        <v>4.4</v>
+      </c>
+      <c r="BZ9">
         <v>36</v>
       </c>
-      <c r="BW9">
-        <v>4.7</v>
-      </c>
-      <c r="BX9">
-        <v>34</v>
-      </c>
-      <c r="BY9">
-        <v>4.7</v>
-      </c>
-      <c r="BZ9">
-        <v>10</v>
-      </c>
       <c r="CA9">
-        <v>3.5</v>
+        <v>4.3</v>
       </c>
       <c r="CB9" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="10" spans="1:80">
@@ -2972,76 +2969,76 @@
         <v>97</v>
       </c>
       <c r="D10" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E10" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="F10">
-        <v>2.56</v>
+        <v>2.64</v>
       </c>
       <c r="G10">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="H10">
-        <v>2.88</v>
+        <v>2.76</v>
       </c>
       <c r="I10">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="J10">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K10">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="L10">
-        <v>1.41</v>
+        <v>1.34</v>
       </c>
       <c r="M10">
         <v>1.07</v>
       </c>
       <c r="N10">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="O10">
         <v>1.33</v>
       </c>
       <c r="P10">
-        <v>1.81</v>
+        <v>1.86</v>
       </c>
       <c r="Q10">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="R10">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="S10">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="T10">
         <v>1.77</v>
       </c>
       <c r="U10">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="V10">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="W10">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="X10">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="Y10">
         <v>14</v>
       </c>
       <c r="Z10">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="AA10">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AB10">
         <v>12.5</v>
@@ -3053,401 +3050,401 @@
         <v>16</v>
       </c>
       <c r="AE10">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="AF10">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AG10">
         <v>14.5</v>
       </c>
       <c r="AH10">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AI10">
+        <v>150</v>
+      </c>
+      <c r="AJ10">
+        <v>44</v>
+      </c>
+      <c r="AK10">
+        <v>80</v>
+      </c>
+      <c r="AL10">
         <v>55</v>
       </c>
-      <c r="AJ10">
-        <v>46</v>
-      </c>
-      <c r="AK10">
-        <v>36</v>
-      </c>
-      <c r="AL10">
-        <v>50</v>
-      </c>
       <c r="AM10">
-        <v>110</v>
+        <v>580</v>
       </c>
       <c r="AN10">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AO10">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="AP10">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AQ10">
         <v>9.800000000000001</v>
       </c>
       <c r="AR10">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AS10">
-        <v>4.6</v>
+        <v>5.4</v>
       </c>
       <c r="AT10">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AU10">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AV10">
         <v>11</v>
       </c>
       <c r="AW10">
-        <v>4.5</v>
+        <v>16</v>
       </c>
       <c r="AX10">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AY10">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AZ10">
         <v>14.5</v>
       </c>
       <c r="BA10">
-        <v>4.6</v>
+        <v>5.4</v>
       </c>
       <c r="BB10">
-        <v>13</v>
+        <v>16.5</v>
       </c>
       <c r="BC10">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="BD10">
-        <v>4.6</v>
+        <v>22</v>
       </c>
       <c r="BE10">
-        <v>4.8</v>
+        <v>5.7</v>
       </c>
       <c r="BF10">
         <v>21</v>
       </c>
       <c r="BG10">
+        <v>6.2</v>
+      </c>
+      <c r="BH10">
+        <v>3.45</v>
+      </c>
+      <c r="BI10">
+        <v>2.98</v>
+      </c>
+      <c r="BJ10">
         <v>9.800000000000001</v>
       </c>
-      <c r="BH10">
-        <v>3.8</v>
-      </c>
-      <c r="BI10">
-        <v>2.64</v>
-      </c>
-      <c r="BJ10">
-        <v>11.5</v>
-      </c>
       <c r="BK10">
-        <v>3.4</v>
+        <v>5</v>
       </c>
       <c r="BL10">
         <v>1000</v>
       </c>
       <c r="BM10">
-        <v>4.7</v>
+        <v>9.6</v>
       </c>
       <c r="BN10">
-        <v>6.6</v>
+        <v>5.9</v>
       </c>
       <c r="BO10">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BP10">
+        <v>22</v>
+      </c>
+      <c r="BQ10">
+        <v>7</v>
+      </c>
+      <c r="BR10">
+        <v>1000</v>
+      </c>
+      <c r="BS10">
+        <v>8</v>
+      </c>
+      <c r="BT10">
+        <v>6.2</v>
+      </c>
+      <c r="BU10">
+        <v>4.5</v>
+      </c>
+      <c r="BV10">
         <v>24</v>
       </c>
-      <c r="BQ10">
-        <v>4</v>
-      </c>
-      <c r="BR10">
-        <v>42</v>
-      </c>
-      <c r="BS10">
-        <v>4.4</v>
-      </c>
-      <c r="BT10">
+      <c r="BW10">
         <v>7.2</v>
       </c>
-      <c r="BU10">
-        <v>4.6</v>
-      </c>
-      <c r="BV10">
-        <v>29</v>
-      </c>
-      <c r="BW10">
-        <v>4.2</v>
-      </c>
       <c r="BX10">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="BY10">
-        <v>4.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ10">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="CA10">
-        <v>4.3</v>
+        <v>7.6</v>
       </c>
       <c r="CB10" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="11" spans="1:80">
       <c r="A11" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B11" t="s">
         <v>89</v>
       </c>
       <c r="C11" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D11" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E11" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F11">
-        <v>2.64</v>
+        <v>2.28</v>
       </c>
       <c r="G11">
-        <v>2.84</v>
+        <v>2.42</v>
       </c>
       <c r="H11">
-        <v>2.76</v>
+        <v>3.45</v>
       </c>
       <c r="I11">
-        <v>3</v>
+        <v>3.65</v>
       </c>
       <c r="J11">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K11">
         <v>3.65</v>
       </c>
       <c r="L11">
-        <v>1.34</v>
+        <v>1.01</v>
       </c>
       <c r="M11">
         <v>1.07</v>
       </c>
       <c r="N11">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="O11">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="P11">
-        <v>1.86</v>
+        <v>1.91</v>
       </c>
       <c r="Q11">
-        <v>1.98</v>
+        <v>1.92</v>
       </c>
       <c r="R11">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="S11">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="T11">
-        <v>1.77</v>
+        <v>1.74</v>
       </c>
       <c r="U11">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="V11">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="W11">
-        <v>1.54</v>
+        <v>1.71</v>
       </c>
       <c r="X11">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="Y11">
         <v>14</v>
       </c>
       <c r="Z11">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="AA11">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="AB11">
         <v>12.5</v>
       </c>
       <c r="AC11">
-        <v>8.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AD11">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AE11">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AF11">
-        <v>20</v>
+        <v>15.5</v>
       </c>
       <c r="AG11">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AH11">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AI11">
-        <v>150</v>
+        <v>60</v>
       </c>
       <c r="AJ11">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AK11">
-        <v>80</v>
+        <v>32</v>
       </c>
       <c r="AL11">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="AM11">
-        <v>580</v>
+        <v>110</v>
       </c>
       <c r="AN11">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="AO11">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="AP11">
+        <v>12.5</v>
+      </c>
+      <c r="AQ11">
         <v>11.5</v>
       </c>
-      <c r="AQ11">
+      <c r="AR11">
+        <v>21</v>
+      </c>
+      <c r="AS11">
+        <v>5.5</v>
+      </c>
+      <c r="AT11">
+        <v>9</v>
+      </c>
+      <c r="AU11">
+        <v>7</v>
+      </c>
+      <c r="AV11">
+        <v>12.5</v>
+      </c>
+      <c r="AW11">
+        <v>5.3</v>
+      </c>
+      <c r="AX11">
+        <v>13</v>
+      </c>
+      <c r="AY11">
         <v>9.800000000000001</v>
-      </c>
-      <c r="AR11">
-        <v>16.5</v>
-      </c>
-      <c r="AS11">
-        <v>21</v>
-      </c>
-      <c r="AT11">
-        <v>9.4</v>
-      </c>
-      <c r="AU11">
-        <v>6.8</v>
-      </c>
-      <c r="AV11">
-        <v>11</v>
-      </c>
-      <c r="AW11">
-        <v>16</v>
-      </c>
-      <c r="AX11">
-        <v>15</v>
-      </c>
-      <c r="AY11">
-        <v>10.5</v>
       </c>
       <c r="AZ11">
         <v>14.5</v>
       </c>
       <c r="BA11">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BB11">
-        <v>5.3</v>
+        <v>14.5</v>
       </c>
       <c r="BC11">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="BD11">
-        <v>22</v>
+        <v>5.2</v>
       </c>
       <c r="BE11">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BF11">
-        <v>21</v>
+        <v>13.5</v>
       </c>
       <c r="BG11">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BH11">
-        <v>3.45</v>
+        <v>1000</v>
       </c>
       <c r="BI11">
-        <v>2.98</v>
+        <v>1.01</v>
       </c>
       <c r="BJ11">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="BK11">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="BL11">
         <v>1000</v>
       </c>
       <c r="BM11">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="BN11">
-        <v>5.9</v>
+        <v>1000</v>
       </c>
       <c r="BO11">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="BP11">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="BQ11">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="BR11">
         <v>1000</v>
       </c>
       <c r="BS11">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="BT11">
-        <v>6.2</v>
+        <v>1000</v>
       </c>
       <c r="BU11">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="BV11">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="BW11">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="BX11">
         <v>1000</v>
       </c>
       <c r="BY11">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BZ11">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="CA11">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="CB11" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="12" spans="1:80">
       <c r="A12" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B12" t="s">
         <v>89</v>
@@ -3456,172 +3453,172 @@
         <v>98</v>
       </c>
       <c r="D12" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E12" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F12">
-        <v>2.28</v>
+        <v>1.05</v>
       </c>
       <c r="G12">
-        <v>2.44</v>
+        <v>1.64</v>
       </c>
       <c r="H12">
-        <v>3.45</v>
+        <v>5.4</v>
       </c>
       <c r="I12">
-        <v>3.65</v>
+        <v>990</v>
       </c>
       <c r="J12">
-        <v>3.35</v>
+        <v>3.8</v>
       </c>
       <c r="K12">
-        <v>3.65</v>
+        <v>500</v>
       </c>
       <c r="L12">
         <v>1.01</v>
       </c>
       <c r="M12">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="N12">
-        <v>3.7</v>
+        <v>1.32</v>
       </c>
       <c r="O12">
         <v>1.28</v>
       </c>
       <c r="P12">
-        <v>1.91</v>
+        <v>1.25</v>
       </c>
       <c r="Q12">
-        <v>1.92</v>
+        <v>1.28</v>
       </c>
       <c r="R12">
-        <v>1.36</v>
+        <v>1.18</v>
       </c>
       <c r="S12">
-        <v>3.35</v>
+        <v>1.27</v>
       </c>
       <c r="T12">
-        <v>1.74</v>
+        <v>1.11</v>
       </c>
       <c r="U12">
-        <v>2.18</v>
+        <v>1.11</v>
       </c>
       <c r="V12">
-        <v>1.37</v>
+        <v>1.01</v>
       </c>
       <c r="W12">
-        <v>1.69</v>
+        <v>2.52</v>
       </c>
       <c r="X12">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="Y12">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="Z12">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AA12">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AB12">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AC12">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="AD12">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AE12">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AF12">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AG12">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AH12">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AI12">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AJ12">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AK12">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AL12">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AM12">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AN12">
-        <v>23</v>
+        <v>55</v>
       </c>
       <c r="AO12">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AP12">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="AQ12">
-        <v>11.5</v>
+        <v>2.5</v>
       </c>
       <c r="AR12">
-        <v>21</v>
+        <v>2.5</v>
       </c>
       <c r="AS12">
-        <v>5.5</v>
+        <v>2.5</v>
       </c>
       <c r="AT12">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="AU12">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="AV12">
-        <v>12.5</v>
+        <v>2.5</v>
       </c>
       <c r="AW12">
-        <v>5.3</v>
+        <v>2.5</v>
       </c>
       <c r="AX12">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="AY12">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AZ12">
-        <v>14.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA12">
-        <v>5.3</v>
+        <v>2.5</v>
       </c>
       <c r="BB12">
-        <v>14.5</v>
+        <v>1.01</v>
       </c>
       <c r="BC12">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BD12">
-        <v>5.2</v>
+        <v>1.01</v>
       </c>
       <c r="BE12">
-        <v>5.6</v>
+        <v>1.01</v>
       </c>
       <c r="BF12">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="BG12">
-        <v>6.8</v>
+        <v>1.55</v>
       </c>
       <c r="BH12">
         <v>1000</v>
@@ -3678,13 +3675,13 @@
         <v>1.01</v>
       </c>
       <c r="BZ12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB12" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="13" spans="1:80">
@@ -3695,55 +3692,55 @@
         <v>89</v>
       </c>
       <c r="C13" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D13" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E13" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F13">
-        <v>1.05</v>
+        <v>1.3</v>
       </c>
       <c r="G13">
-        <v>1.67</v>
+        <v>110</v>
       </c>
       <c r="H13">
-        <v>5.4</v>
+        <v>2.4</v>
       </c>
       <c r="I13">
         <v>990</v>
       </c>
       <c r="J13">
-        <v>3.8</v>
+        <v>2.32</v>
       </c>
       <c r="K13">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="L13">
         <v>1.01</v>
       </c>
       <c r="M13">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="N13">
-        <v>1.32</v>
+        <v>1.26</v>
       </c>
       <c r="O13">
-        <v>1.23</v>
+        <v>1.53</v>
       </c>
       <c r="P13">
         <v>1.25</v>
       </c>
       <c r="Q13">
-        <v>1.23</v>
+        <v>2.5</v>
       </c>
       <c r="R13">
         <v>1.18</v>
       </c>
       <c r="S13">
-        <v>1.22</v>
+        <v>3.85</v>
       </c>
       <c r="T13">
         <v>1.11</v>
@@ -3752,10 +3749,10 @@
         <v>1.11</v>
       </c>
       <c r="V13">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="W13">
-        <v>2.5</v>
+        <v>1.17</v>
       </c>
       <c r="X13">
         <v>1000</v>
@@ -3770,7 +3767,7 @@
         <v>1000</v>
       </c>
       <c r="AB13">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AC13">
         <v>1000</v>
@@ -3782,10 +3779,10 @@
         <v>1000</v>
       </c>
       <c r="AF13">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AG13">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AH13">
         <v>1000</v>
@@ -3794,19 +3791,19 @@
         <v>1000</v>
       </c>
       <c r="AJ13">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AK13">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AL13">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AM13">
         <v>1000</v>
       </c>
       <c r="AN13">
-        <v>55</v>
+        <v>500</v>
       </c>
       <c r="AO13">
         <v>1000</v>
@@ -3926,12 +3923,12 @@
         <v>1.01</v>
       </c>
       <c r="CB13" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="14" spans="1:80">
       <c r="A14" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B14" t="s">
         <v>89</v>
@@ -3940,235 +3937,235 @@
         <v>99</v>
       </c>
       <c r="D14" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E14" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F14">
-        <v>1.3</v>
+        <v>2.26</v>
       </c>
       <c r="G14">
+        <v>2.46</v>
+      </c>
+      <c r="H14">
+        <v>3.25</v>
+      </c>
+      <c r="I14">
+        <v>3.6</v>
+      </c>
+      <c r="J14">
+        <v>3.4</v>
+      </c>
+      <c r="K14">
+        <v>3.7</v>
+      </c>
+      <c r="L14">
+        <v>1.18</v>
+      </c>
+      <c r="M14">
+        <v>1.07</v>
+      </c>
+      <c r="N14">
+        <v>3.6</v>
+      </c>
+      <c r="O14">
+        <v>1.33</v>
+      </c>
+      <c r="P14">
+        <v>1.87</v>
+      </c>
+      <c r="Q14">
+        <v>1.95</v>
+      </c>
+      <c r="R14">
+        <v>1.34</v>
+      </c>
+      <c r="S14">
+        <v>3.45</v>
+      </c>
+      <c r="T14">
+        <v>1.87</v>
+      </c>
+      <c r="U14">
+        <v>2.12</v>
+      </c>
+      <c r="V14">
+        <v>1.38</v>
+      </c>
+      <c r="W14">
+        <v>1.68</v>
+      </c>
+      <c r="X14">
+        <v>14.5</v>
+      </c>
+      <c r="Y14">
+        <v>15.5</v>
+      </c>
+      <c r="Z14">
+        <v>25</v>
+      </c>
+      <c r="AA14">
+        <v>65</v>
+      </c>
+      <c r="AB14">
+        <v>10.5</v>
+      </c>
+      <c r="AC14">
+        <v>8.4</v>
+      </c>
+      <c r="AD14">
+        <v>15</v>
+      </c>
+      <c r="AE14">
+        <v>42</v>
+      </c>
+      <c r="AF14">
+        <v>16</v>
+      </c>
+      <c r="AG14">
         <v>14</v>
       </c>
-      <c r="H14">
-        <v>2.4</v>
-      </c>
-      <c r="I14">
-        <v>990</v>
-      </c>
-      <c r="J14">
-        <v>2.32</v>
-      </c>
-      <c r="K14">
-        <v>950</v>
-      </c>
-      <c r="L14">
-        <v>1.01</v>
-      </c>
-      <c r="M14">
-        <v>1.12</v>
-      </c>
-      <c r="N14">
-        <v>1.26</v>
-      </c>
-      <c r="O14">
-        <v>1.47</v>
-      </c>
-      <c r="P14">
-        <v>1.25</v>
-      </c>
-      <c r="Q14">
-        <v>2.34</v>
-      </c>
-      <c r="R14">
-        <v>1.18</v>
-      </c>
-      <c r="S14">
+      <c r="AH14">
+        <v>18.5</v>
+      </c>
+      <c r="AI14">
+        <v>55</v>
+      </c>
+      <c r="AJ14">
+        <v>34</v>
+      </c>
+      <c r="AK14">
+        <v>27</v>
+      </c>
+      <c r="AL14">
+        <v>42</v>
+      </c>
+      <c r="AM14">
+        <v>120</v>
+      </c>
+      <c r="AN14">
+        <v>24</v>
+      </c>
+      <c r="AO14">
+        <v>42</v>
+      </c>
+      <c r="AP14">
+        <v>12</v>
+      </c>
+      <c r="AQ14">
+        <v>11</v>
+      </c>
+      <c r="AR14">
+        <v>20</v>
+      </c>
+      <c r="AS14">
+        <v>6.4</v>
+      </c>
+      <c r="AT14">
+        <v>8.6</v>
+      </c>
+      <c r="AU14">
+        <v>6.8</v>
+      </c>
+      <c r="AV14">
+        <v>12</v>
+      </c>
+      <c r="AW14">
+        <v>6.2</v>
+      </c>
+      <c r="AX14">
+        <v>13</v>
+      </c>
+      <c r="AY14">
+        <v>9.6</v>
+      </c>
+      <c r="AZ14">
+        <v>14.5</v>
+      </c>
+      <c r="BA14">
+        <v>6.4</v>
+      </c>
+      <c r="BB14">
+        <v>6</v>
+      </c>
+      <c r="BC14">
+        <v>21</v>
+      </c>
+      <c r="BD14">
+        <v>32</v>
+      </c>
+      <c r="BE14">
+        <v>6.8</v>
+      </c>
+      <c r="BF14">
+        <v>16.5</v>
+      </c>
+      <c r="BG14">
+        <v>6.2</v>
+      </c>
+      <c r="BH14">
         <v>3.5</v>
       </c>
-      <c r="T14">
-        <v>1.11</v>
-      </c>
-      <c r="U14">
-        <v>1.11</v>
-      </c>
-      <c r="V14">
-        <v>1.02</v>
-      </c>
-      <c r="W14">
-        <v>1.17</v>
-      </c>
-      <c r="X14">
-        <v>1000</v>
-      </c>
-      <c r="Y14">
-        <v>1000</v>
-      </c>
-      <c r="Z14">
-        <v>1000</v>
-      </c>
-      <c r="AA14">
-        <v>1000</v>
-      </c>
-      <c r="AB14">
-        <v>500</v>
-      </c>
-      <c r="AC14">
-        <v>1000</v>
-      </c>
-      <c r="AD14">
-        <v>1000</v>
-      </c>
-      <c r="AE14">
-        <v>1000</v>
-      </c>
-      <c r="AF14">
-        <v>500</v>
-      </c>
-      <c r="AG14">
-        <v>500</v>
-      </c>
-      <c r="AH14">
-        <v>1000</v>
-      </c>
-      <c r="AI14">
-        <v>1000</v>
-      </c>
-      <c r="AJ14">
-        <v>500</v>
-      </c>
-      <c r="AK14">
-        <v>500</v>
-      </c>
-      <c r="AL14">
-        <v>500</v>
-      </c>
-      <c r="AM14">
-        <v>1000</v>
-      </c>
-      <c r="AN14">
-        <v>500</v>
-      </c>
-      <c r="AO14">
-        <v>1000</v>
-      </c>
-      <c r="AP14">
-        <v>1.01</v>
-      </c>
-      <c r="AQ14">
-        <v>1.01</v>
-      </c>
-      <c r="AR14">
-        <v>1.01</v>
-      </c>
-      <c r="AS14">
-        <v>1.01</v>
-      </c>
-      <c r="AT14">
-        <v>1.01</v>
-      </c>
-      <c r="AU14">
-        <v>1.01</v>
-      </c>
-      <c r="AV14">
-        <v>1.01</v>
-      </c>
-      <c r="AW14">
-        <v>1.01</v>
-      </c>
-      <c r="AX14">
-        <v>1.01</v>
-      </c>
-      <c r="AY14">
-        <v>1.01</v>
-      </c>
-      <c r="AZ14">
-        <v>1.01</v>
-      </c>
-      <c r="BA14">
-        <v>1.01</v>
-      </c>
-      <c r="BB14">
-        <v>1.01</v>
-      </c>
-      <c r="BC14">
-        <v>1.01</v>
-      </c>
-      <c r="BD14">
-        <v>1.01</v>
-      </c>
-      <c r="BE14">
-        <v>1.01</v>
-      </c>
-      <c r="BF14">
-        <v>1.01</v>
-      </c>
-      <c r="BG14">
-        <v>1.55</v>
-      </c>
-      <c r="BH14">
-        <v>1000</v>
-      </c>
       <c r="BI14">
-        <v>1.01</v>
+        <v>2.7</v>
       </c>
       <c r="BJ14">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="BK14">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BL14">
         <v>1000</v>
       </c>
       <c r="BM14">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BN14">
-        <v>1000</v>
+        <v>5.4</v>
       </c>
       <c r="BO14">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="BP14">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="BQ14">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BR14">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BS14">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BT14">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="BU14">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BV14">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="BW14">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BX14">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BY14">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="BZ14">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA14">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="CB14" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="15" spans="1:80">
@@ -4182,494 +4179,494 @@
         <v>100</v>
       </c>
       <c r="D15" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E15" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F15">
-        <v>2.26</v>
+        <v>1.83</v>
       </c>
       <c r="G15">
-        <v>2.46</v>
+        <v>1.94</v>
       </c>
       <c r="H15">
-        <v>3.25</v>
+        <v>5.2</v>
       </c>
       <c r="I15">
-        <v>3.6</v>
+        <v>5.7</v>
       </c>
       <c r="J15">
         <v>3.4</v>
       </c>
       <c r="K15">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="L15">
-        <v>1.18</v>
+        <v>1.52</v>
       </c>
       <c r="M15">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="N15">
-        <v>3.6</v>
+        <v>2.88</v>
       </c>
       <c r="O15">
-        <v>1.33</v>
+        <v>1.47</v>
       </c>
       <c r="P15">
-        <v>1.87</v>
+        <v>1.62</v>
       </c>
       <c r="Q15">
-        <v>1.95</v>
+        <v>2.4</v>
       </c>
       <c r="R15">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="S15">
-        <v>3.45</v>
+        <v>4.8</v>
       </c>
       <c r="T15">
-        <v>1.87</v>
+        <v>2.12</v>
       </c>
       <c r="U15">
-        <v>2.12</v>
+        <v>1.78</v>
       </c>
       <c r="V15">
-        <v>1.38</v>
+        <v>1.21</v>
       </c>
       <c r="W15">
-        <v>1.68</v>
+        <v>2.06</v>
       </c>
       <c r="X15">
+        <v>10</v>
+      </c>
+      <c r="Y15">
         <v>14.5</v>
       </c>
-      <c r="Y15">
-        <v>15.5</v>
-      </c>
       <c r="Z15">
+        <v>60</v>
+      </c>
+      <c r="AA15">
+        <v>900</v>
+      </c>
+      <c r="AB15">
+        <v>6.8</v>
+      </c>
+      <c r="AC15">
+        <v>8</v>
+      </c>
+      <c r="AD15">
+        <v>23</v>
+      </c>
+      <c r="AE15">
+        <v>120</v>
+      </c>
+      <c r="AF15">
+        <v>10.5</v>
+      </c>
+      <c r="AG15">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AH15">
         <v>25</v>
       </c>
-      <c r="AA15">
-        <v>65</v>
-      </c>
-      <c r="AB15">
-        <v>10.5</v>
-      </c>
-      <c r="AC15">
-        <v>8.4</v>
-      </c>
-      <c r="AD15">
+      <c r="AI15">
+        <v>700</v>
+      </c>
+      <c r="AJ15">
+        <v>22</v>
+      </c>
+      <c r="AK15">
+        <v>25</v>
+      </c>
+      <c r="AL15">
+        <v>55</v>
+      </c>
+      <c r="AM15">
+        <v>580</v>
+      </c>
+      <c r="AN15">
+        <v>20</v>
+      </c>
+      <c r="AO15">
+        <v>700</v>
+      </c>
+      <c r="AP15">
+        <v>8.6</v>
+      </c>
+      <c r="AQ15">
+        <v>12.5</v>
+      </c>
+      <c r="AR15">
         <v>15</v>
       </c>
-      <c r="AE15">
-        <v>42</v>
-      </c>
-      <c r="AF15">
-        <v>16</v>
-      </c>
-      <c r="AG15">
+      <c r="AS15">
+        <v>14.5</v>
+      </c>
+      <c r="AT15">
+        <v>5.9</v>
+      </c>
+      <c r="AU15">
+        <v>7</v>
+      </c>
+      <c r="AV15">
+        <v>19</v>
+      </c>
+      <c r="AW15">
         <v>14</v>
       </c>
-      <c r="AH15">
-        <v>18.5</v>
-      </c>
-      <c r="AI15">
-        <v>55</v>
-      </c>
-      <c r="AJ15">
-        <v>34</v>
-      </c>
-      <c r="AK15">
-        <v>27</v>
-      </c>
-      <c r="AL15">
-        <v>42</v>
-      </c>
-      <c r="AM15">
-        <v>120</v>
-      </c>
-      <c r="AN15">
-        <v>24</v>
-      </c>
-      <c r="AO15">
-        <v>48</v>
-      </c>
-      <c r="AP15">
-        <v>12</v>
-      </c>
-      <c r="AQ15">
-        <v>11</v>
-      </c>
-      <c r="AR15">
-        <v>20</v>
-      </c>
-      <c r="AS15">
-        <v>6.4</v>
-      </c>
-      <c r="AT15">
-        <v>8.6</v>
-      </c>
-      <c r="AU15">
-        <v>6.8</v>
-      </c>
-      <c r="AV15">
-        <v>12</v>
-      </c>
-      <c r="AW15">
-        <v>6</v>
-      </c>
       <c r="AX15">
-        <v>13</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY15">
-        <v>9.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ15">
-        <v>14.5</v>
+        <v>21</v>
       </c>
       <c r="BA15">
-        <v>6.2</v>
+        <v>14</v>
       </c>
       <c r="BB15">
-        <v>5.9</v>
+        <v>18</v>
       </c>
       <c r="BC15">
         <v>21</v>
       </c>
       <c r="BD15">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BE15">
-        <v>6.6</v>
+        <v>15</v>
       </c>
       <c r="BF15">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BG15">
-        <v>6.2</v>
+        <v>15</v>
       </c>
       <c r="BH15">
-        <v>3.5</v>
+        <v>2.9</v>
       </c>
       <c r="BI15">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="BJ15">
+        <v>12</v>
+      </c>
+      <c r="BK15">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BL15">
+        <v>1000</v>
+      </c>
+      <c r="BM15">
+        <v>13.5</v>
+      </c>
+      <c r="BN15">
+        <v>4.3</v>
+      </c>
+      <c r="BO15">
+        <v>3.8</v>
+      </c>
+      <c r="BP15">
+        <v>14.5</v>
+      </c>
+      <c r="BQ15">
+        <v>7.2</v>
+      </c>
+      <c r="BR15">
+        <v>38</v>
+      </c>
+      <c r="BS15">
+        <v>10.5</v>
+      </c>
+      <c r="BT15">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BU15">
+        <v>5.5</v>
+      </c>
+      <c r="BV15">
+        <v>60</v>
+      </c>
+      <c r="BW15">
+        <v>11.5</v>
+      </c>
+      <c r="BX15">
+        <v>1000</v>
+      </c>
+      <c r="BY15">
+        <v>12</v>
+      </c>
+      <c r="BZ15">
+        <v>36</v>
+      </c>
+      <c r="CA15">
         <v>10</v>
       </c>
-      <c r="BK15">
-        <v>5.2</v>
-      </c>
-      <c r="BL15">
-        <v>1000</v>
-      </c>
-      <c r="BM15">
-        <v>10</v>
-      </c>
-      <c r="BN15">
-        <v>5.4</v>
-      </c>
-      <c r="BO15">
-        <v>3.6</v>
-      </c>
-      <c r="BP15">
-        <v>18</v>
-      </c>
-      <c r="BQ15">
-        <v>6.8</v>
-      </c>
-      <c r="BR15">
-        <v>32</v>
-      </c>
-      <c r="BS15">
-        <v>8</v>
-      </c>
-      <c r="BT15">
-        <v>6.8</v>
-      </c>
-      <c r="BU15">
-        <v>4.9</v>
-      </c>
-      <c r="BV15">
-        <v>28</v>
-      </c>
-      <c r="BW15">
-        <v>7.8</v>
-      </c>
-      <c r="BX15">
-        <v>40</v>
-      </c>
-      <c r="BY15">
-        <v>8.6</v>
-      </c>
-      <c r="BZ15">
-        <v>0</v>
-      </c>
-      <c r="CA15">
-        <v>0</v>
-      </c>
       <c r="CB15" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="16" spans="1:80">
       <c r="A16" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="B16" t="s">
         <v>89</v>
       </c>
       <c r="C16" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D16" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E16" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F16">
-        <v>1.82</v>
+        <v>6.8</v>
       </c>
       <c r="G16">
-        <v>1.93</v>
+        <v>100</v>
       </c>
       <c r="H16">
-        <v>5.2</v>
+        <v>1.48</v>
       </c>
       <c r="I16">
-        <v>5.8</v>
+        <v>1.49</v>
       </c>
       <c r="J16">
-        <v>3.3</v>
+        <v>3.75</v>
       </c>
       <c r="K16">
-        <v>3.65</v>
+        <v>5.7</v>
       </c>
       <c r="L16">
-        <v>1.43</v>
+        <v>1.01</v>
       </c>
       <c r="M16">
+        <v>1.01</v>
+      </c>
+      <c r="N16">
+        <v>1.24</v>
+      </c>
+      <c r="O16">
+        <v>1.09</v>
+      </c>
+      <c r="P16">
+        <v>1.24</v>
+      </c>
+      <c r="Q16">
+        <v>1.92</v>
+      </c>
+      <c r="R16">
+        <v>1.18</v>
+      </c>
+      <c r="S16">
+        <v>1.92</v>
+      </c>
+      <c r="T16">
         <v>1.11</v>
       </c>
-      <c r="N16">
-        <v>2.88</v>
-      </c>
-      <c r="O16">
-        <v>1.47</v>
-      </c>
-      <c r="P16">
-        <v>1.63</v>
-      </c>
-      <c r="Q16">
-        <v>2.4</v>
-      </c>
-      <c r="R16">
-        <v>1.24</v>
-      </c>
-      <c r="S16">
-        <v>4.7</v>
-      </c>
-      <c r="T16">
-        <v>2.14</v>
-      </c>
       <c r="U16">
-        <v>1.77</v>
+        <v>1.11</v>
       </c>
       <c r="V16">
-        <v>1.21</v>
+        <v>3</v>
       </c>
       <c r="W16">
-        <v>2.08</v>
+        <v>1.06</v>
       </c>
       <c r="X16">
-        <v>10</v>
+        <v>16.5</v>
       </c>
       <c r="Y16">
-        <v>14.5</v>
+        <v>10.5</v>
       </c>
       <c r="Z16">
-        <v>60</v>
+        <v>13</v>
       </c>
       <c r="AA16">
-        <v>900</v>
+        <v>34</v>
       </c>
       <c r="AB16">
-        <v>6.8</v>
+        <v>40</v>
       </c>
       <c r="AC16">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="AD16">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="AE16">
-        <v>120</v>
+        <v>70</v>
       </c>
       <c r="AF16">
-        <v>10.5</v>
+        <v>470</v>
       </c>
       <c r="AG16">
-        <v>11</v>
+        <v>280</v>
       </c>
       <c r="AH16">
-        <v>25</v>
+        <v>340</v>
       </c>
       <c r="AI16">
         <v>700</v>
       </c>
       <c r="AJ16">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AK16">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AL16">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AM16">
-        <v>580</v>
+        <v>1000</v>
       </c>
       <c r="AN16">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AO16">
-        <v>700</v>
+        <v>70</v>
       </c>
       <c r="AP16">
-        <v>8.6</v>
+        <v>3.7</v>
       </c>
       <c r="AQ16">
-        <v>12.5</v>
+        <v>2.76</v>
       </c>
       <c r="AR16">
-        <v>15</v>
+        <v>4.2</v>
       </c>
       <c r="AS16">
-        <v>12.5</v>
+        <v>8</v>
       </c>
       <c r="AT16">
-        <v>5.9</v>
+        <v>8.4</v>
       </c>
       <c r="AU16">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AV16">
-        <v>19</v>
+        <v>7.8</v>
       </c>
       <c r="AW16">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="AX16">
-        <v>8.800000000000001</v>
+        <v>26</v>
       </c>
       <c r="AY16">
-        <v>9.4</v>
+        <v>14</v>
       </c>
       <c r="AZ16">
-        <v>21</v>
+        <v>15.5</v>
       </c>
       <c r="BA16">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="BB16">
-        <v>18</v>
+        <v>1.01</v>
       </c>
       <c r="BC16">
-        <v>21</v>
+        <v>1.03</v>
       </c>
       <c r="BD16">
-        <v>30</v>
+        <v>1.01</v>
       </c>
       <c r="BE16">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="BF16">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="BG16">
-        <v>12.5</v>
+        <v>5.6</v>
       </c>
       <c r="BH16">
-        <v>2.92</v>
+        <v>1000</v>
       </c>
       <c r="BI16">
-        <v>2.64</v>
+        <v>1.01</v>
       </c>
       <c r="BJ16">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="BK16">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BL16">
         <v>1000</v>
       </c>
       <c r="BM16">
-        <v>14.5</v>
+        <v>1.01</v>
       </c>
       <c r="BN16">
-        <v>4.2</v>
+        <v>1000</v>
       </c>
       <c r="BO16">
-        <v>3.75</v>
+        <v>1.01</v>
       </c>
       <c r="BP16">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="BQ16">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="BR16">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="BS16">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="BT16">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="BU16">
-        <v>5.7</v>
+        <v>1.01</v>
       </c>
       <c r="BV16">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="BW16">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="BX16">
         <v>1000</v>
       </c>
       <c r="BY16">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="BZ16">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="CA16">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="CB16" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="17" spans="1:80">
       <c r="A17" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B17" t="s">
         <v>89</v>
       </c>
       <c r="C17" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D17" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E17" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F17">
         <v>2.42</v>
@@ -4690,31 +4687,31 @@
         <v>3.15</v>
       </c>
       <c r="L17">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="M17">
         <v>1.13</v>
       </c>
       <c r="N17">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="O17">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="P17">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="Q17">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="R17">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="S17">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="T17">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="U17">
         <v>1.79</v>
@@ -4726,16 +4723,16 @@
         <v>1.66</v>
       </c>
       <c r="X17">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="Y17">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Z17">
         <v>24</v>
       </c>
       <c r="AA17">
-        <v>490</v>
+        <v>95</v>
       </c>
       <c r="AB17">
         <v>7.6</v>
@@ -4744,19 +4741,19 @@
         <v>7.2</v>
       </c>
       <c r="AD17">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AE17">
         <v>75</v>
       </c>
       <c r="AF17">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AG17">
         <v>12.5</v>
       </c>
       <c r="AH17">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AI17">
         <v>220</v>
@@ -4783,10 +4780,10 @@
         <v>7.8</v>
       </c>
       <c r="AQ17">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AR17">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AS17">
         <v>32</v>
@@ -4795,10 +4792,10 @@
         <v>6.8</v>
       </c>
       <c r="AU17">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AV17">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AW17">
         <v>29</v>
@@ -4810,7 +4807,7 @@
         <v>11.5</v>
       </c>
       <c r="AZ17">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="BA17">
         <v>36</v>
@@ -4819,7 +4816,7 @@
         <v>32</v>
       </c>
       <c r="BC17">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BD17">
         <v>32</v>
@@ -4843,13 +4840,13 @@
         <v>13.5</v>
       </c>
       <c r="BK17">
-        <v>3.65</v>
+        <v>3.95</v>
       </c>
       <c r="BL17">
         <v>1000</v>
       </c>
       <c r="BM17">
-        <v>4.9</v>
+        <v>5.5</v>
       </c>
       <c r="BN17">
         <v>6</v>
@@ -4861,16 +4858,16 @@
         <v>26</v>
       </c>
       <c r="BQ17">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="BR17">
         <v>55</v>
       </c>
       <c r="BS17">
-        <v>4.5</v>
+        <v>5.1</v>
       </c>
       <c r="BT17">
-        <v>7.8</v>
+        <v>6.6</v>
       </c>
       <c r="BU17">
         <v>5</v>
@@ -4879,22 +4876,22 @@
         <v>44</v>
       </c>
       <c r="BW17">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="BX17">
         <v>70</v>
       </c>
       <c r="BY17">
-        <v>4.6</v>
+        <v>5.2</v>
       </c>
       <c r="BZ17">
         <v>60</v>
       </c>
       <c r="CA17">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="CB17" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="18" spans="1:80">
@@ -4905,13 +4902,13 @@
         <v>89</v>
       </c>
       <c r="C18" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D18" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E18" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F18">
         <v>1.8</v>
@@ -4923,13 +4920,13 @@
         <v>4.2</v>
       </c>
       <c r="I18">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="J18">
         <v>3</v>
       </c>
       <c r="K18">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="L18">
         <v>1.35</v>
@@ -4968,13 +4965,13 @@
         <v>1.94</v>
       </c>
       <c r="X18">
-        <v>15</v>
+        <v>500</v>
       </c>
       <c r="Y18">
         <v>950</v>
       </c>
       <c r="Z18">
-        <v>120</v>
+        <v>500</v>
       </c>
       <c r="AA18">
         <v>900</v>
@@ -4992,13 +4989,13 @@
         <v>500</v>
       </c>
       <c r="AF18">
-        <v>24</v>
+        <v>500</v>
       </c>
       <c r="AG18">
-        <v>18.5</v>
+        <v>500</v>
       </c>
       <c r="AH18">
-        <v>60</v>
+        <v>950</v>
       </c>
       <c r="AI18">
         <v>500</v>
@@ -5022,28 +5019,28 @@
         <v>1000</v>
       </c>
       <c r="AP18">
-        <v>5.7</v>
+        <v>7.8</v>
       </c>
       <c r="AQ18">
-        <v>7.8</v>
+        <v>1.72</v>
       </c>
       <c r="AR18">
-        <v>15.5</v>
+        <v>1.82</v>
       </c>
       <c r="AS18">
-        <v>2.5</v>
+        <v>1.84</v>
       </c>
       <c r="AT18">
-        <v>5.1</v>
+        <v>4.2</v>
       </c>
       <c r="AU18">
-        <v>5.1</v>
+        <v>4.4</v>
       </c>
       <c r="AV18">
-        <v>1.85</v>
+        <v>1.78</v>
       </c>
       <c r="AW18">
-        <v>28</v>
+        <v>1.84</v>
       </c>
       <c r="AX18">
         <v>5.6</v>
@@ -5052,28 +5049,28 @@
         <v>6.2</v>
       </c>
       <c r="AZ18">
-        <v>12.5</v>
+        <v>1.79</v>
       </c>
       <c r="BA18">
-        <v>28</v>
+        <v>1.84</v>
       </c>
       <c r="BB18">
-        <v>10.5</v>
+        <v>1.81</v>
       </c>
       <c r="BC18">
-        <v>11.5</v>
+        <v>1.8</v>
       </c>
       <c r="BD18">
-        <v>24</v>
+        <v>1.83</v>
       </c>
       <c r="BE18">
-        <v>1.92</v>
+        <v>1.84</v>
       </c>
       <c r="BF18">
         <v>4.4</v>
       </c>
       <c r="BG18">
-        <v>1.93</v>
+        <v>1.85</v>
       </c>
       <c r="BH18">
         <v>1000</v>
@@ -5136,7 +5133,7 @@
         <v>1.04</v>
       </c>
       <c r="CB18" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="19" spans="1:80">
@@ -5147,267 +5144,267 @@
         <v>89</v>
       </c>
       <c r="C19" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D19" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E19" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F19">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="G19">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="H19">
-        <v>4.6</v>
+        <v>1.9</v>
       </c>
       <c r="I19">
-        <v>5.5</v>
+        <v>870</v>
       </c>
       <c r="J19">
-        <v>3.05</v>
+        <v>1.1</v>
       </c>
       <c r="K19">
-        <v>3.65</v>
+        <v>950</v>
       </c>
       <c r="L19">
-        <v>1.54</v>
+        <v>1.28</v>
       </c>
       <c r="M19">
-        <v>1.14</v>
+        <v>1.01</v>
       </c>
       <c r="N19">
-        <v>2.36</v>
+        <v>1.33</v>
       </c>
       <c r="O19">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="P19">
-        <v>1.46</v>
+        <v>1.33</v>
       </c>
       <c r="Q19">
-        <v>2.78</v>
+        <v>1.57</v>
       </c>
       <c r="R19">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="S19">
-        <v>5.9</v>
+        <v>1.05</v>
       </c>
       <c r="T19">
-        <v>2.28</v>
+        <v>1.93</v>
       </c>
       <c r="U19">
-        <v>1.63</v>
+        <v>1.32</v>
       </c>
       <c r="V19">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="W19">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="X19">
-        <v>8.4</v>
+        <v>1000</v>
       </c>
       <c r="Y19">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="Z19">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AA19">
-        <v>180</v>
+        <v>1000</v>
       </c>
       <c r="AB19">
-        <v>6.4</v>
+        <v>7.8</v>
       </c>
       <c r="AC19">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="AD19">
-        <v>24</v>
+        <v>950</v>
       </c>
       <c r="AE19">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AF19">
-        <v>13</v>
+        <v>970</v>
       </c>
       <c r="AG19">
-        <v>12.5</v>
+        <v>17</v>
       </c>
       <c r="AH19">
         <v>950</v>
       </c>
       <c r="AI19">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AJ19">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AK19">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AL19">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AM19">
-        <v>290</v>
+        <v>1000</v>
       </c>
       <c r="AN19">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AO19">
-        <v>220</v>
+        <v>1000</v>
       </c>
       <c r="AP19">
-        <v>6</v>
+        <v>1.34</v>
       </c>
       <c r="AQ19">
-        <v>4.9</v>
+        <v>1.34</v>
       </c>
       <c r="AR19">
-        <v>26</v>
+        <v>1.35</v>
       </c>
       <c r="AS19">
-        <v>7.6</v>
+        <v>1.35</v>
       </c>
       <c r="AT19">
-        <v>5.2</v>
+        <v>4.3</v>
       </c>
       <c r="AU19">
-        <v>5.9</v>
+        <v>1.34</v>
       </c>
       <c r="AV19">
-        <v>16.5</v>
+        <v>5.6</v>
       </c>
       <c r="AW19">
-        <v>7.4</v>
+        <v>1.35</v>
       </c>
       <c r="AX19">
-        <v>9.4</v>
+        <v>5.4</v>
       </c>
       <c r="AY19">
-        <v>4.9</v>
+        <v>6.6</v>
       </c>
       <c r="AZ19">
-        <v>18</v>
+        <v>1.31</v>
       </c>
       <c r="BA19">
-        <v>7.6</v>
+        <v>1.35</v>
       </c>
       <c r="BB19">
-        <v>18</v>
+        <v>1.35</v>
       </c>
       <c r="BC19">
-        <v>6.4</v>
+        <v>1.35</v>
       </c>
       <c r="BD19">
-        <v>7.2</v>
+        <v>1.35</v>
       </c>
       <c r="BE19">
-        <v>7.8</v>
+        <v>1.35</v>
       </c>
       <c r="BF19">
-        <v>19.5</v>
+        <v>1.35</v>
       </c>
       <c r="BG19">
-        <v>7.8</v>
+        <v>1.35</v>
       </c>
       <c r="BH19">
-        <v>2.84</v>
+        <v>1000</v>
       </c>
       <c r="BI19">
-        <v>2.18</v>
+        <v>1.04</v>
       </c>
       <c r="BJ19">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="BK19">
-        <v>4.3</v>
+        <v>1.04</v>
       </c>
       <c r="BL19">
         <v>1000</v>
       </c>
       <c r="BM19">
-        <v>6</v>
+        <v>1.04</v>
       </c>
       <c r="BN19">
-        <v>5</v>
+        <v>1000</v>
       </c>
       <c r="BO19">
-        <v>3.6</v>
+        <v>1.04</v>
       </c>
       <c r="BP19">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="BQ19">
-        <v>4.8</v>
+        <v>1.04</v>
       </c>
       <c r="BR19">
         <v>1000</v>
       </c>
       <c r="BS19">
-        <v>5.6</v>
+        <v>1.04</v>
       </c>
       <c r="BT19">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="BU19">
-        <v>3.7</v>
+        <v>1.04</v>
       </c>
       <c r="BV19">
         <v>1000</v>
       </c>
       <c r="BW19">
-        <v>5.7</v>
+        <v>1.04</v>
       </c>
       <c r="BX19">
         <v>1000</v>
       </c>
       <c r="BY19">
-        <v>5.9</v>
+        <v>1.04</v>
       </c>
       <c r="BZ19">
         <v>1000</v>
       </c>
       <c r="CA19">
-        <v>5.7</v>
+        <v>1.04</v>
       </c>
       <c r="CB19" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="20" spans="1:80">
       <c r="A20" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="B20" t="s">
         <v>89</v>
       </c>
       <c r="C20" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D20" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E20" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F20">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="G20">
-        <v>3.45</v>
+        <v>3.75</v>
       </c>
       <c r="H20">
-        <v>2.2</v>
+        <v>2.06</v>
       </c>
       <c r="I20">
-        <v>2.44</v>
+        <v>2.3</v>
       </c>
       <c r="J20">
         <v>3.65</v>
@@ -5428,40 +5425,40 @@
         <v>1.19</v>
       </c>
       <c r="P20">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="Q20">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="R20">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="S20">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="T20">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="U20">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="V20">
-        <v>1.69</v>
+        <v>1.76</v>
       </c>
       <c r="W20">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="X20">
         <v>25</v>
       </c>
       <c r="Y20">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Z20">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AA20">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AB20">
         <v>18.5</v>
@@ -5473,13 +5470,13 @@
         <v>12.5</v>
       </c>
       <c r="AE20">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AF20">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AG20">
-        <v>15.5</v>
+        <v>18</v>
       </c>
       <c r="AH20">
         <v>16.5</v>
@@ -5491,7 +5488,7 @@
         <v>65</v>
       </c>
       <c r="AK20">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AL20">
         <v>44</v>
@@ -5500,7 +5497,7 @@
         <v>75</v>
       </c>
       <c r="AN20">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="AO20">
         <v>13</v>
@@ -5509,58 +5506,58 @@
         <v>18.5</v>
       </c>
       <c r="AQ20">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AR20">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AS20">
-        <v>24</v>
+        <v>4.6</v>
       </c>
       <c r="AT20">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AU20">
         <v>8</v>
       </c>
       <c r="AV20">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AW20">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AX20">
-        <v>20</v>
+        <v>6.2</v>
       </c>
       <c r="AY20">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AZ20">
         <v>12.5</v>
       </c>
       <c r="BA20">
-        <v>18.5</v>
+        <v>10.5</v>
       </c>
       <c r="BB20">
-        <v>5.5</v>
+        <v>5.1</v>
       </c>
       <c r="BC20">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="BD20">
-        <v>5.2</v>
+        <v>22</v>
       </c>
       <c r="BE20">
-        <v>5.5</v>
+        <v>29</v>
       </c>
       <c r="BF20">
         <v>17.5</v>
       </c>
       <c r="BG20">
-        <v>10</v>
+        <v>8.4</v>
       </c>
       <c r="BH20">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BI20">
         <v>3.3</v>
@@ -5569,7 +5566,7 @@
         <v>10.5</v>
       </c>
       <c r="BK20">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="BL20">
         <v>95</v>
@@ -5578,37 +5575,37 @@
         <v>4.4</v>
       </c>
       <c r="BN20">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BO20">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BP20">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="BQ20">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BR20">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BS20">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BT20">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BU20">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BV20">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="BW20">
         <v>3.7</v>
       </c>
       <c r="BX20">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BY20">
         <v>4</v>
@@ -5620,7 +5617,7 @@
         <v>0</v>
       </c>
       <c r="CB20" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-06.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-06.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="130">
   <si>
     <t>League</t>
   </si>
@@ -256,48 +256,30 @@
     <t>SnapshotTS</t>
   </si>
   <si>
+    <t>Bolivian Liga de Futbol Profesional</t>
+  </si>
+  <si>
+    <t>Colombian Primera B</t>
+  </si>
+  <si>
+    <t>Icelandic 1 Deild</t>
+  </si>
+  <si>
+    <t>Venezuelan Primera Division</t>
+  </si>
+  <si>
+    <t>Peruvian Primera Division</t>
+  </si>
+  <si>
+    <t>Ecuadorian Serie B</t>
+  </si>
+  <si>
     <t>Argentinian Primera Division</t>
   </si>
   <si>
-    <t>US United Soccer League</t>
-  </si>
-  <si>
-    <t>Colombian Primera A</t>
-  </si>
-  <si>
-    <t>Bolivian Liga de Futbol Profesional</t>
-  </si>
-  <si>
-    <t>Colombian Primera B</t>
-  </si>
-  <si>
-    <t>Icelandic 1 Deild</t>
-  </si>
-  <si>
-    <t>Venezuelan Primera Division</t>
-  </si>
-  <si>
-    <t>Peruvian Primera Division</t>
-  </si>
-  <si>
-    <t>Ecuadorian Serie B</t>
-  </si>
-  <si>
     <t>2026-08-06</t>
   </si>
   <si>
-    <t>00:15:00</t>
-  </si>
-  <si>
-    <t>00:30:00</t>
-  </si>
-  <si>
-    <t>01:00:00</t>
-  </si>
-  <si>
-    <t>01:30:00</t>
-  </si>
-  <si>
     <t>19:00:00</t>
   </si>
   <si>
@@ -331,18 +313,6 @@
     <t>23:30:00</t>
   </si>
   <si>
-    <t>Tigre</t>
-  </si>
-  <si>
-    <t>Tulsa Roughnecks FC</t>
-  </si>
-  <si>
-    <t>El Paso Locomotive FC</t>
-  </si>
-  <si>
-    <t>Once Caldas</t>
-  </si>
-  <si>
     <t>Universitario de Vinto</t>
   </si>
   <si>
@@ -355,12 +325,12 @@
     <t>Rayo Zuliano</t>
   </si>
   <si>
+    <t>Alianza Atletico</t>
+  </si>
+  <si>
     <t>Estudiantes de Merida</t>
   </si>
   <si>
-    <t>Alianza Atletico</t>
-  </si>
-  <si>
     <t>Independiente Juniors</t>
   </si>
   <si>
@@ -388,18 +358,6 @@
     <t>Blooming Santa Cruz</t>
   </si>
   <si>
-    <t>Belgrano</t>
-  </si>
-  <si>
-    <t>Sacramento Republic</t>
-  </si>
-  <si>
-    <t>Monterey Bay FC</t>
-  </si>
-  <si>
-    <t>America de Cali S.A</t>
-  </si>
-  <si>
     <t>Real Potosi</t>
   </si>
   <si>
@@ -412,12 +370,12 @@
     <t>Academia Anzoategui FC</t>
   </si>
   <si>
+    <t>Cienciano</t>
+  </si>
+  <si>
     <t>Zamora FC</t>
   </si>
   <si>
-    <t>Cienciano</t>
-  </si>
-  <si>
     <t>22 de Julio FC</t>
   </si>
   <si>
@@ -445,7 +403,7 @@
     <t>Always Ready</t>
   </si>
   <si>
-    <t>2026-08-05 23:23:14</t>
+    <t>2026-08-06 01:35:02</t>
   </si>
 </sst>
 </file>
@@ -777,7 +735,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB20"/>
+  <dimension ref="A1:CB16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -1027,65 +985,65 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D2" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="E2" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="I2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="K2">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="L2">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="M2">
+        <v>1.04</v>
+      </c>
+      <c r="N2">
+        <v>4.8</v>
+      </c>
+      <c r="O2">
+        <v>1.22</v>
+      </c>
+      <c r="P2">
+        <v>2.32</v>
+      </c>
+      <c r="Q2">
+        <v>1.67</v>
+      </c>
+      <c r="R2">
+        <v>1.52</v>
+      </c>
+      <c r="S2">
+        <v>2.72</v>
+      </c>
+      <c r="T2">
+        <v>1.65</v>
+      </c>
+      <c r="U2">
         <v>1.11</v>
       </c>
-      <c r="N2">
-        <v>1.01</v>
-      </c>
-      <c r="O2">
-        <v>1.11</v>
-      </c>
-      <c r="P2">
-        <v>1.01</v>
-      </c>
-      <c r="Q2">
-        <v>1.11</v>
-      </c>
-      <c r="R2">
-        <v>1.01</v>
-      </c>
-      <c r="S2">
-        <v>1.11</v>
-      </c>
-      <c r="T2">
-        <v>0</v>
-      </c>
-      <c r="U2">
-        <v>0</v>
-      </c>
       <c r="V2">
         <v>1.01</v>
       </c>
@@ -1093,166 +1051,166 @@
         <v>1.01</v>
       </c>
       <c r="X2">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="Y2">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="Z2">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AA2">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AB2">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AC2">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AD2">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AE2">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AF2">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AG2">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AH2">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AI2">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AJ2">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK2">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AL2">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AM2">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AN2">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AO2">
-        <v>1000</v>
+        <v>220</v>
       </c>
       <c r="AP2">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AQ2">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="AR2">
-        <v>1.01</v>
+        <v>25</v>
       </c>
       <c r="AS2">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="AT2">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AU2">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="AV2">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="AW2">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="AX2">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AY2">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ2">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="BA2">
-        <v>1.01</v>
+        <v>36</v>
       </c>
       <c r="BB2">
-        <v>1.01</v>
+        <v>22</v>
       </c>
       <c r="BC2">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="BD2">
-        <v>1.01</v>
+        <v>24</v>
       </c>
       <c r="BE2">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BF2">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="BG2">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BH2">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI2">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ2">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK2">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL2">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM2">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN2">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO2">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP2">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ2">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR2">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS2">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT2">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU2">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV2">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW2">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX2">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY2">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ2">
         <v>0</v>
@@ -1261,7 +1219,7 @@
         <v>0</v>
       </c>
       <c r="CB2" t="s">
-        <v>143</v>
+        <v>129</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1269,232 +1227,232 @@
         <v>81</v>
       </c>
       <c r="B3" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C3" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="D3" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="E3" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="F3">
-        <v>1.16</v>
+        <v>1.86</v>
       </c>
       <c r="G3">
-        <v>1.23</v>
+        <v>1.96</v>
       </c>
       <c r="H3">
+        <v>4.9</v>
+      </c>
+      <c r="I3">
+        <v>6.2</v>
+      </c>
+      <c r="J3">
+        <v>3.2</v>
+      </c>
+      <c r="K3">
+        <v>3.55</v>
+      </c>
+      <c r="L3">
+        <v>1.59</v>
+      </c>
+      <c r="M3">
+        <v>1.12</v>
+      </c>
+      <c r="N3">
+        <v>2.6</v>
+      </c>
+      <c r="O3">
+        <v>1.55</v>
+      </c>
+      <c r="P3">
+        <v>1.51</v>
+      </c>
+      <c r="Q3">
+        <v>2.74</v>
+      </c>
+      <c r="R3">
+        <v>1.17</v>
+      </c>
+      <c r="S3">
+        <v>5.5</v>
+      </c>
+      <c r="T3">
+        <v>1.11</v>
+      </c>
+      <c r="U3">
+        <v>1.11</v>
+      </c>
+      <c r="V3">
+        <v>1.01</v>
+      </c>
+      <c r="W3">
+        <v>1.01</v>
+      </c>
+      <c r="X3">
+        <v>970</v>
+      </c>
+      <c r="Y3">
+        <v>970</v>
+      </c>
+      <c r="Z3">
+        <v>120</v>
+      </c>
+      <c r="AA3">
+        <v>900</v>
+      </c>
+      <c r="AB3">
+        <v>1000</v>
+      </c>
+      <c r="AC3">
+        <v>42</v>
+      </c>
+      <c r="AD3">
+        <v>1000</v>
+      </c>
+      <c r="AE3">
+        <v>1000</v>
+      </c>
+      <c r="AF3">
+        <v>970</v>
+      </c>
+      <c r="AG3">
+        <v>9.4</v>
+      </c>
+      <c r="AH3">
+        <v>1000</v>
+      </c>
+      <c r="AI3">
+        <v>700</v>
+      </c>
+      <c r="AJ3">
+        <v>900</v>
+      </c>
+      <c r="AK3">
+        <v>75</v>
+      </c>
+      <c r="AL3">
+        <v>170</v>
+      </c>
+      <c r="AM3">
+        <v>500</v>
+      </c>
+      <c r="AN3">
         <v>60</v>
       </c>
-      <c r="I3">
-        <v>120</v>
-      </c>
-      <c r="J3">
-        <v>5.8</v>
-      </c>
-      <c r="K3">
-        <v>7.8</v>
-      </c>
-      <c r="L3">
-        <v>0</v>
-      </c>
-      <c r="M3">
-        <v>0</v>
-      </c>
-      <c r="N3">
-        <v>1.37</v>
-      </c>
-      <c r="O3">
-        <v>3.15</v>
-      </c>
-      <c r="P3">
-        <v>1.04</v>
-      </c>
-      <c r="Q3">
-        <v>17</v>
-      </c>
-      <c r="R3">
-        <v>1.01</v>
-      </c>
-      <c r="S3">
-        <v>130</v>
-      </c>
-      <c r="T3">
-        <v>4.4</v>
-      </c>
-      <c r="U3">
-        <v>1.2</v>
-      </c>
-      <c r="V3">
-        <v>1.01</v>
-      </c>
-      <c r="W3">
-        <v>5.1</v>
-      </c>
-      <c r="X3">
-        <v>1000</v>
-      </c>
-      <c r="Y3">
-        <v>1000</v>
-      </c>
-      <c r="Z3">
-        <v>1000</v>
-      </c>
-      <c r="AA3">
-        <v>1000</v>
-      </c>
-      <c r="AB3">
+      <c r="AO3">
+        <v>700</v>
+      </c>
+      <c r="AP3">
+        <v>1.48</v>
+      </c>
+      <c r="AQ3">
+        <v>1.53</v>
+      </c>
+      <c r="AR3">
+        <v>1.61</v>
+      </c>
+      <c r="AS3">
+        <v>1.63</v>
+      </c>
+      <c r="AT3">
+        <v>1.63</v>
+      </c>
+      <c r="AU3">
         <v>1.46</v>
       </c>
-      <c r="AC3">
-        <v>1000</v>
-      </c>
-      <c r="AD3">
-        <v>970</v>
-      </c>
-      <c r="AE3">
-        <v>1000</v>
-      </c>
-      <c r="AF3">
+      <c r="AV3">
+        <v>1.63</v>
+      </c>
+      <c r="AW3">
+        <v>1.63</v>
+      </c>
+      <c r="AX3">
+        <v>1.5</v>
+      </c>
+      <c r="AY3">
         <v>9.199999999999999</v>
       </c>
-      <c r="AG3">
-        <v>65</v>
-      </c>
-      <c r="AH3">
-        <v>1000</v>
-      </c>
-      <c r="AI3">
-        <v>1000</v>
-      </c>
-      <c r="AJ3">
-        <v>200</v>
-      </c>
-      <c r="AK3">
-        <v>1000</v>
-      </c>
-      <c r="AL3">
-        <v>1000</v>
-      </c>
-      <c r="AM3">
-        <v>1000</v>
-      </c>
-      <c r="AN3">
-        <v>1000</v>
-      </c>
-      <c r="AO3">
-        <v>1000</v>
-      </c>
-      <c r="AP3">
-        <v>5.9</v>
-      </c>
-      <c r="AQ3">
-        <v>10.5</v>
-      </c>
-      <c r="AR3">
-        <v>10.5</v>
-      </c>
-      <c r="AS3">
-        <v>10.5</v>
-      </c>
-      <c r="AT3">
-        <v>1.36</v>
-      </c>
-      <c r="AU3">
-        <v>6</v>
-      </c>
-      <c r="AV3">
-        <v>11</v>
-      </c>
-      <c r="AW3">
-        <v>8.4</v>
-      </c>
-      <c r="AX3">
-        <v>6.6</v>
-      </c>
-      <c r="AY3">
-        <v>9.6</v>
-      </c>
       <c r="AZ3">
-        <v>8.4</v>
+        <v>1.63</v>
       </c>
       <c r="BA3">
-        <v>8.4</v>
+        <v>1.63</v>
       </c>
       <c r="BB3">
-        <v>10</v>
+        <v>1.63</v>
       </c>
       <c r="BC3">
-        <v>10.5</v>
+        <v>1.59</v>
       </c>
       <c r="BD3">
-        <v>5.3</v>
+        <v>1.61</v>
       </c>
       <c r="BE3">
-        <v>5.9</v>
+        <v>1.62</v>
       </c>
       <c r="BF3">
-        <v>10.5</v>
+        <v>1.59</v>
       </c>
       <c r="BG3">
-        <v>8.4</v>
+        <v>1.63</v>
       </c>
       <c r="BH3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI3">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BJ3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK3">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BL3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM3">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BN3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO3">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BP3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ3">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BR3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS3">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BT3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU3">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BV3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW3">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BX3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY3">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BZ3">
         <v>0</v>
@@ -1503,670 +1461,670 @@
         <v>0</v>
       </c>
       <c r="CB3" t="s">
-        <v>143</v>
+        <v>129</v>
       </c>
     </row>
     <row r="4" spans="1:80">
       <c r="A4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B4" t="s">
+        <v>87</v>
+      </c>
+      <c r="C4" t="s">
         <v>89</v>
       </c>
-      <c r="C4" t="s">
-        <v>92</v>
-      </c>
       <c r="D4" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="E4" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
       <c r="F4">
-        <v>1.22</v>
+        <v>1.6</v>
       </c>
       <c r="G4">
-        <v>1.27</v>
+        <v>1.65</v>
       </c>
       <c r="H4">
-        <v>15</v>
+        <v>4.7</v>
       </c>
       <c r="I4">
-        <v>30</v>
+        <v>5.7</v>
       </c>
       <c r="J4">
-        <v>5.9</v>
+        <v>4.8</v>
       </c>
       <c r="K4">
-        <v>7.6</v>
+        <v>5.7</v>
       </c>
       <c r="L4">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="M4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N4">
-        <v>3.6</v>
+        <v>8</v>
       </c>
       <c r="O4">
-        <v>1.25</v>
+        <v>1.1</v>
       </c>
       <c r="P4">
-        <v>1.67</v>
+        <v>3.7</v>
       </c>
       <c r="Q4">
-        <v>2.26</v>
+        <v>1.34</v>
       </c>
       <c r="R4">
-        <v>1.18</v>
+        <v>2.1</v>
       </c>
       <c r="S4">
-        <v>5.5</v>
+        <v>1.84</v>
       </c>
       <c r="T4">
-        <v>2.4</v>
+        <v>1.42</v>
       </c>
       <c r="U4">
-        <v>1.6</v>
+        <v>2.16</v>
       </c>
       <c r="V4">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="W4">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="X4">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Y4">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Z4">
-        <v>1000</v>
+        <v>230</v>
       </c>
       <c r="AA4">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="AB4">
-        <v>5.5</v>
+        <v>970</v>
       </c>
       <c r="AC4">
-        <v>11</v>
+        <v>970</v>
       </c>
       <c r="AD4">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AE4">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AF4">
-        <v>6</v>
+        <v>970</v>
       </c>
       <c r="AG4">
-        <v>990</v>
+        <v>970</v>
       </c>
       <c r="AH4">
-        <v>990</v>
+        <v>970</v>
       </c>
       <c r="AI4">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AJ4">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AK4">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AL4">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AM4">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN4">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AO4">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AP4">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="AQ4">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AR4">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AS4">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="AT4">
-        <v>1.35</v>
+        <v>1.81</v>
       </c>
       <c r="AU4">
-        <v>5.6</v>
+        <v>1.69</v>
       </c>
       <c r="AV4">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AW4">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="AX4">
-        <v>4</v>
+        <v>1.77</v>
       </c>
       <c r="AY4">
-        <v>1.8</v>
+        <v>1.68</v>
       </c>
       <c r="AZ4">
-        <v>1.8</v>
+        <v>1.72</v>
       </c>
       <c r="BA4">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="BB4">
-        <v>7.4</v>
+        <v>1.77</v>
       </c>
       <c r="BC4">
-        <v>1.8</v>
+        <v>1.74</v>
       </c>
       <c r="BD4">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="BE4">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="BF4">
-        <v>10.5</v>
+        <v>1.66</v>
       </c>
       <c r="BG4">
-        <v>1.8</v>
+        <v>4.9</v>
       </c>
       <c r="BH4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI4">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BJ4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK4">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BL4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM4">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BN4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO4">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BP4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ4">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BR4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS4">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BT4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU4">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BV4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW4">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BX4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY4">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BZ4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA4">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="CB4" t="s">
-        <v>143</v>
+        <v>129</v>
       </c>
     </row>
     <row r="5" spans="1:80">
       <c r="A5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B5" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C5" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="D5" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="E5" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="F5">
-        <v>5.7</v>
+        <v>2.56</v>
       </c>
       <c r="G5">
-        <v>5.8</v>
+        <v>2.88</v>
       </c>
       <c r="H5">
-        <v>2.22</v>
+        <v>2.82</v>
       </c>
       <c r="I5">
-        <v>2.28</v>
+        <v>3.25</v>
       </c>
       <c r="J5">
-        <v>2.6</v>
+        <v>3.15</v>
       </c>
       <c r="K5">
-        <v>2.66</v>
+        <v>3.6</v>
       </c>
       <c r="L5">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="M5">
+        <v>1.08</v>
+      </c>
+      <c r="N5">
+        <v>3.5</v>
+      </c>
+      <c r="O5">
+        <v>1.34</v>
+      </c>
+      <c r="P5">
+        <v>1.81</v>
+      </c>
+      <c r="Q5">
+        <v>2.04</v>
+      </c>
+      <c r="R5">
         <v>1.31</v>
       </c>
-      <c r="N5">
-        <v>1.64</v>
-      </c>
-      <c r="O5">
-        <v>2.52</v>
-      </c>
-      <c r="P5">
-        <v>1.2</v>
-      </c>
-      <c r="Q5">
-        <v>5.5</v>
-      </c>
-      <c r="R5">
-        <v>1.05</v>
-      </c>
       <c r="S5">
-        <v>17.5</v>
+        <v>3.6</v>
       </c>
       <c r="T5">
-        <v>3.9</v>
+        <v>1.11</v>
       </c>
       <c r="U5">
-        <v>1.29</v>
+        <v>1.96</v>
       </c>
       <c r="V5">
-        <v>1.72</v>
+        <v>1.01</v>
       </c>
       <c r="W5">
-        <v>1.22</v>
+        <v>1.01</v>
       </c>
       <c r="X5">
-        <v>4</v>
+        <v>970</v>
       </c>
       <c r="Y5">
+        <v>1000</v>
+      </c>
+      <c r="Z5">
+        <v>42</v>
+      </c>
+      <c r="AA5">
+        <v>900</v>
+      </c>
+      <c r="AB5">
+        <v>970</v>
+      </c>
+      <c r="AC5">
+        <v>42</v>
+      </c>
+      <c r="AD5">
+        <v>1000</v>
+      </c>
+      <c r="AE5">
+        <v>230</v>
+      </c>
+      <c r="AF5">
+        <v>1000</v>
+      </c>
+      <c r="AG5">
+        <v>970</v>
+      </c>
+      <c r="AH5">
+        <v>970</v>
+      </c>
+      <c r="AI5">
+        <v>370</v>
+      </c>
+      <c r="AJ5">
+        <v>900</v>
+      </c>
+      <c r="AK5">
+        <v>80</v>
+      </c>
+      <c r="AL5">
+        <v>290</v>
+      </c>
+      <c r="AM5">
+        <v>580</v>
+      </c>
+      <c r="AN5">
+        <v>1000</v>
+      </c>
+      <c r="AO5">
+        <v>150</v>
+      </c>
+      <c r="AP5">
+        <v>1.37</v>
+      </c>
+      <c r="AQ5">
+        <v>1.45</v>
+      </c>
+      <c r="AR5">
+        <v>1.41</v>
+      </c>
+      <c r="AS5">
+        <v>1.44</v>
+      </c>
+      <c r="AT5">
+        <v>4.9</v>
+      </c>
+      <c r="AU5">
         <v>4.4</v>
       </c>
-      <c r="Z5">
-        <v>11.5</v>
-      </c>
-      <c r="AA5">
-        <v>1000</v>
-      </c>
-      <c r="AB5">
-        <v>9.6</v>
-      </c>
-      <c r="AC5">
-        <v>9.6</v>
-      </c>
-      <c r="AD5">
-        <v>990</v>
-      </c>
-      <c r="AE5">
-        <v>1000</v>
-      </c>
-      <c r="AF5">
-        <v>55</v>
-      </c>
-      <c r="AG5">
-        <v>1000</v>
-      </c>
-      <c r="AH5">
-        <v>1000</v>
-      </c>
-      <c r="AI5">
-        <v>1000</v>
-      </c>
-      <c r="AJ5">
-        <v>1000</v>
-      </c>
-      <c r="AK5">
-        <v>1000</v>
-      </c>
-      <c r="AL5">
-        <v>1000</v>
-      </c>
-      <c r="AM5">
-        <v>1000</v>
-      </c>
-      <c r="AN5">
-        <v>1000</v>
-      </c>
-      <c r="AO5">
-        <v>1000</v>
-      </c>
-      <c r="AP5">
-        <v>3.5</v>
-      </c>
-      <c r="AQ5">
-        <v>3.95</v>
-      </c>
-      <c r="AR5">
-        <v>9</v>
-      </c>
-      <c r="AS5">
-        <v>26</v>
-      </c>
-      <c r="AT5">
-        <v>8</v>
-      </c>
-      <c r="AU5">
-        <v>8</v>
-      </c>
       <c r="AV5">
-        <v>12</v>
+        <v>1.45</v>
       </c>
       <c r="AW5">
-        <v>50</v>
+        <v>1.43</v>
       </c>
       <c r="AX5">
-        <v>32</v>
+        <v>1.45</v>
       </c>
       <c r="AY5">
-        <v>30</v>
+        <v>1.37</v>
       </c>
       <c r="AZ5">
-        <v>5.1</v>
+        <v>1.42</v>
       </c>
       <c r="BA5">
-        <v>180</v>
+        <v>1.44</v>
       </c>
       <c r="BB5">
-        <v>160</v>
+        <v>1.44</v>
       </c>
       <c r="BC5">
-        <v>160</v>
+        <v>1.43</v>
       </c>
       <c r="BD5">
-        <v>21</v>
+        <v>1.44</v>
       </c>
       <c r="BE5">
-        <v>50</v>
+        <v>1.45</v>
       </c>
       <c r="BF5">
-        <v>11.5</v>
+        <v>5</v>
       </c>
       <c r="BG5">
-        <v>50</v>
+        <v>1.55</v>
       </c>
       <c r="BH5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI5">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BJ5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK5">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BL5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM5">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BN5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO5">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BP5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ5">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BR5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS5">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BT5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU5">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BV5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW5">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BX5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY5">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BZ5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA5">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="CB5" t="s">
-        <v>143</v>
+        <v>129</v>
       </c>
     </row>
     <row r="6" spans="1:80">
       <c r="A6" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B6" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C6" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="D6" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="E6" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="F6">
-        <v>2.12</v>
+        <v>2.28</v>
       </c>
       <c r="G6">
-        <v>2.16</v>
+        <v>2.46</v>
       </c>
       <c r="H6">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="I6">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="J6">
+        <v>3.15</v>
+      </c>
+      <c r="K6">
+        <v>3.55</v>
+      </c>
+      <c r="L6">
+        <v>1.39</v>
+      </c>
+      <c r="M6">
+        <v>1.07</v>
+      </c>
+      <c r="N6">
         <v>3.9</v>
       </c>
-      <c r="K6">
-        <v>4.2</v>
-      </c>
-      <c r="L6">
-        <v>1.01</v>
-      </c>
-      <c r="M6">
-        <v>1.04</v>
-      </c>
-      <c r="N6">
-        <v>4.7</v>
-      </c>
       <c r="O6">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="P6">
-        <v>2.3</v>
+        <v>1.96</v>
       </c>
       <c r="Q6">
+        <v>1.94</v>
+      </c>
+      <c r="R6">
+        <v>1.38</v>
+      </c>
+      <c r="S6">
+        <v>3.3</v>
+      </c>
+      <c r="T6">
+        <v>1.11</v>
+      </c>
+      <c r="U6">
+        <v>1.11</v>
+      </c>
+      <c r="V6">
+        <v>1.01</v>
+      </c>
+      <c r="W6">
+        <v>1.01</v>
+      </c>
+      <c r="X6">
+        <v>970</v>
+      </c>
+      <c r="Y6">
+        <v>1000</v>
+      </c>
+      <c r="Z6">
+        <v>1000</v>
+      </c>
+      <c r="AA6">
+        <v>900</v>
+      </c>
+      <c r="AB6">
+        <v>970</v>
+      </c>
+      <c r="AC6">
+        <v>970</v>
+      </c>
+      <c r="AD6">
+        <v>970</v>
+      </c>
+      <c r="AE6">
+        <v>120</v>
+      </c>
+      <c r="AF6">
+        <v>970</v>
+      </c>
+      <c r="AG6">
+        <v>970</v>
+      </c>
+      <c r="AH6">
+        <v>970</v>
+      </c>
+      <c r="AI6">
+        <v>250</v>
+      </c>
+      <c r="AJ6">
+        <v>900</v>
+      </c>
+      <c r="AK6">
+        <v>75</v>
+      </c>
+      <c r="AL6">
+        <v>100</v>
+      </c>
+      <c r="AM6">
+        <v>580</v>
+      </c>
+      <c r="AN6">
+        <v>55</v>
+      </c>
+      <c r="AO6">
+        <v>60</v>
+      </c>
+      <c r="AP6">
+        <v>1.56</v>
+      </c>
+      <c r="AQ6">
+        <v>1.66</v>
+      </c>
+      <c r="AR6">
+        <v>1.66</v>
+      </c>
+      <c r="AS6">
+        <v>1.64</v>
+      </c>
+      <c r="AT6">
+        <v>1.54</v>
+      </c>
+      <c r="AU6">
+        <v>4.4</v>
+      </c>
+      <c r="AV6">
+        <v>1.55</v>
+      </c>
+      <c r="AW6">
         <v>1.63</v>
       </c>
-      <c r="R6">
-        <v>1.51</v>
-      </c>
-      <c r="S6">
-        <v>2.62</v>
-      </c>
-      <c r="T6">
+      <c r="AX6">
+        <v>1.57</v>
+      </c>
+      <c r="AY6">
+        <v>1.59</v>
+      </c>
+      <c r="AZ6">
+        <v>1.56</v>
+      </c>
+      <c r="BA6">
+        <v>1.64</v>
+      </c>
+      <c r="BB6">
+        <v>1.63</v>
+      </c>
+      <c r="BC6">
+        <v>1.62</v>
+      </c>
+      <c r="BD6">
+        <v>1.63</v>
+      </c>
+      <c r="BE6">
         <v>1.65</v>
       </c>
-      <c r="U6">
-        <v>2.36</v>
-      </c>
-      <c r="V6">
-        <v>1.37</v>
-      </c>
-      <c r="W6">
-        <v>1.86</v>
-      </c>
-      <c r="X6">
-        <v>24</v>
-      </c>
-      <c r="Y6">
-        <v>22</v>
-      </c>
-      <c r="Z6">
-        <v>34</v>
-      </c>
-      <c r="AA6">
-        <v>75</v>
-      </c>
-      <c r="AB6">
-        <v>12.5</v>
-      </c>
-      <c r="AC6">
-        <v>10.5</v>
-      </c>
-      <c r="AD6">
-        <v>17</v>
-      </c>
-      <c r="AE6">
-        <v>44</v>
-      </c>
-      <c r="AF6">
-        <v>16</v>
-      </c>
-      <c r="AG6">
-        <v>11</v>
-      </c>
-      <c r="AH6">
-        <v>19</v>
-      </c>
-      <c r="AI6">
-        <v>44</v>
-      </c>
-      <c r="AJ6">
-        <v>28</v>
-      </c>
-      <c r="AK6">
-        <v>23</v>
-      </c>
-      <c r="AL6">
-        <v>29</v>
-      </c>
-      <c r="AM6">
-        <v>80</v>
-      </c>
-      <c r="AN6">
-        <v>11.5</v>
-      </c>
-      <c r="AO6">
-        <v>34</v>
-      </c>
-      <c r="AP6">
-        <v>18.5</v>
-      </c>
-      <c r="AQ6">
-        <v>14</v>
-      </c>
-      <c r="AR6">
-        <v>11.5</v>
-      </c>
-      <c r="AS6">
-        <v>6.6</v>
-      </c>
-      <c r="AT6">
-        <v>10</v>
-      </c>
-      <c r="AU6">
-        <v>8.4</v>
-      </c>
-      <c r="AV6">
-        <v>13.5</v>
-      </c>
-      <c r="AW6">
-        <v>14.5</v>
-      </c>
-      <c r="AX6">
-        <v>12.5</v>
-      </c>
-      <c r="AY6">
-        <v>9</v>
-      </c>
-      <c r="AZ6">
-        <v>13.5</v>
-      </c>
-      <c r="BA6">
-        <v>6.2</v>
-      </c>
-      <c r="BB6">
-        <v>21</v>
-      </c>
-      <c r="BC6">
-        <v>16.5</v>
-      </c>
-      <c r="BD6">
-        <v>16</v>
-      </c>
-      <c r="BE6">
-        <v>6.6</v>
-      </c>
       <c r="BF6">
-        <v>9.4</v>
+        <v>4.4</v>
       </c>
       <c r="BG6">
-        <v>6</v>
+        <v>1.61</v>
       </c>
       <c r="BH6">
         <v>1000</v>
@@ -2229,249 +2187,249 @@
         <v>0</v>
       </c>
       <c r="CB6" t="s">
-        <v>143</v>
+        <v>129</v>
       </c>
     </row>
     <row r="7" spans="1:80">
       <c r="A7" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B7" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C7" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="D7" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="E7" t="s">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="F7">
-        <v>1.85</v>
+        <v>2.6</v>
       </c>
       <c r="G7">
-        <v>1.98</v>
+        <v>2.88</v>
       </c>
       <c r="H7">
-        <v>5.3</v>
+        <v>2.74</v>
       </c>
       <c r="I7">
-        <v>6.2</v>
+        <v>3</v>
       </c>
       <c r="J7">
-        <v>3.15</v>
+        <v>3.35</v>
       </c>
       <c r="K7">
+        <v>3.8</v>
+      </c>
+      <c r="L7">
+        <v>1.42</v>
+      </c>
+      <c r="M7">
+        <v>1.07</v>
+      </c>
+      <c r="N7">
         <v>3.55</v>
       </c>
-      <c r="L7">
-        <v>1.51</v>
-      </c>
-      <c r="M7">
-        <v>1.13</v>
-      </c>
-      <c r="N7">
-        <v>2.54</v>
-      </c>
       <c r="O7">
-        <v>1.55</v>
+        <v>1.33</v>
       </c>
       <c r="P7">
-        <v>1.51</v>
+        <v>1.86</v>
       </c>
       <c r="Q7">
-        <v>2.62</v>
+        <v>2</v>
       </c>
       <c r="R7">
-        <v>1.17</v>
+        <v>1.32</v>
       </c>
       <c r="S7">
-        <v>5.7</v>
+        <v>3.55</v>
       </c>
       <c r="T7">
-        <v>2.26</v>
+        <v>1.77</v>
       </c>
       <c r="U7">
-        <v>1.67</v>
+        <v>2.08</v>
       </c>
       <c r="V7">
-        <v>1.19</v>
+        <v>1.01</v>
       </c>
       <c r="W7">
-        <v>2.02</v>
+        <v>1.01</v>
       </c>
       <c r="X7">
-        <v>8.800000000000001</v>
+        <v>970</v>
       </c>
       <c r="Y7">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="Z7">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="AA7">
         <v>900</v>
       </c>
       <c r="AB7">
-        <v>6.4</v>
+        <v>970</v>
       </c>
       <c r="AC7">
-        <v>8.199999999999999</v>
+        <v>42</v>
       </c>
       <c r="AD7">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AE7">
-        <v>140</v>
+        <v>90</v>
       </c>
       <c r="AF7">
-        <v>11.5</v>
+        <v>970</v>
       </c>
       <c r="AG7">
-        <v>9.4</v>
+        <v>970</v>
       </c>
       <c r="AH7">
-        <v>34</v>
+        <v>60</v>
       </c>
       <c r="AI7">
-        <v>700</v>
+        <v>150</v>
       </c>
       <c r="AJ7">
-        <v>24</v>
+        <v>900</v>
       </c>
       <c r="AK7">
-        <v>32</v>
+        <v>80</v>
       </c>
       <c r="AL7">
-        <v>75</v>
+        <v>150</v>
       </c>
       <c r="AM7">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN7">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="AO7">
-        <v>700</v>
+        <v>55</v>
       </c>
       <c r="AP7">
-        <v>6.8</v>
+        <v>1.61</v>
       </c>
       <c r="AQ7">
-        <v>11</v>
+        <v>1.7</v>
       </c>
       <c r="AR7">
-        <v>7.2</v>
+        <v>1.63</v>
       </c>
       <c r="AS7">
-        <v>8.199999999999999</v>
+        <v>1.68</v>
       </c>
       <c r="AT7">
-        <v>5.3</v>
+        <v>1.58</v>
       </c>
       <c r="AU7">
-        <v>6.8</v>
+        <v>4.4</v>
       </c>
       <c r="AV7">
-        <v>20</v>
+        <v>1.7</v>
       </c>
       <c r="AW7">
-        <v>8</v>
+        <v>1.67</v>
       </c>
       <c r="AX7">
-        <v>8.4</v>
+        <v>1.62</v>
       </c>
       <c r="AY7">
-        <v>9</v>
+        <v>1.59</v>
       </c>
       <c r="AZ7">
-        <v>6.8</v>
+        <v>1.6</v>
       </c>
       <c r="BA7">
-        <v>8</v>
+        <v>1.68</v>
       </c>
       <c r="BB7">
-        <v>19.5</v>
+        <v>1.68</v>
       </c>
       <c r="BC7">
-        <v>6.6</v>
+        <v>1.67</v>
       </c>
       <c r="BD7">
-        <v>7.6</v>
+        <v>1.68</v>
       </c>
       <c r="BE7">
-        <v>8.199999999999999</v>
+        <v>1.7</v>
       </c>
       <c r="BF7">
-        <v>20</v>
+        <v>5.2</v>
       </c>
       <c r="BG7">
-        <v>8.199999999999999</v>
+        <v>1.66</v>
       </c>
       <c r="BH7">
-        <v>2.94</v>
+        <v>1000</v>
       </c>
       <c r="BI7">
-        <v>2.26</v>
+        <v>1.04</v>
       </c>
       <c r="BJ7">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="BK7">
-        <v>4.3</v>
+        <v>1.04</v>
       </c>
       <c r="BL7">
         <v>1000</v>
       </c>
       <c r="BM7">
-        <v>6</v>
+        <v>1.04</v>
       </c>
       <c r="BN7">
-        <v>4.8</v>
+        <v>1000</v>
       </c>
       <c r="BO7">
-        <v>3.4</v>
+        <v>1.04</v>
       </c>
       <c r="BP7">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="BQ7">
-        <v>4.6</v>
+        <v>1.04</v>
       </c>
       <c r="BR7">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="BS7">
-        <v>5.5</v>
+        <v>1.04</v>
       </c>
       <c r="BT7">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="BU7">
-        <v>3.85</v>
+        <v>1.04</v>
       </c>
       <c r="BV7">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="BW7">
-        <v>5.7</v>
+        <v>1.04</v>
       </c>
       <c r="BX7">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="BY7">
-        <v>5.8</v>
+        <v>1.04</v>
       </c>
       <c r="BZ7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA7">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="CB7" t="s">
-        <v>143</v>
+        <v>129</v>
       </c>
     </row>
     <row r="8" spans="1:80">
@@ -2479,1002 +2437,1002 @@
         <v>85</v>
       </c>
       <c r="B8" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C8" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="D8" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="E8" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="F8">
-        <v>1.58</v>
+        <v>1.05</v>
       </c>
       <c r="G8">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="H8">
-        <v>4.7</v>
+        <v>5.4</v>
       </c>
       <c r="I8">
-        <v>5.6</v>
+        <v>870</v>
       </c>
       <c r="J8">
-        <v>4.9</v>
+        <v>3.8</v>
       </c>
       <c r="K8">
-        <v>5.7</v>
+        <v>500</v>
       </c>
       <c r="L8">
         <v>1.01</v>
       </c>
       <c r="M8">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="N8">
-        <v>7.6</v>
+        <v>1.1</v>
       </c>
       <c r="O8">
+        <v>1.01</v>
+      </c>
+      <c r="P8">
+        <v>1.25</v>
+      </c>
+      <c r="Q8">
+        <v>1.01</v>
+      </c>
+      <c r="R8">
+        <v>1.18</v>
+      </c>
+      <c r="S8">
+        <v>1.05</v>
+      </c>
+      <c r="T8">
         <v>1.11</v>
       </c>
-      <c r="P8">
-        <v>3.4</v>
-      </c>
-      <c r="Q8">
-        <v>1.33</v>
-      </c>
-      <c r="R8">
-        <v>2.02</v>
-      </c>
-      <c r="S8">
-        <v>1.82</v>
-      </c>
-      <c r="T8">
-        <v>1.46</v>
-      </c>
       <c r="U8">
-        <v>2.82</v>
+        <v>1.11</v>
       </c>
       <c r="V8">
-        <v>1.21</v>
+        <v>1.01</v>
       </c>
       <c r="W8">
-        <v>2.44</v>
+        <v>1.01</v>
       </c>
       <c r="X8">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="Y8">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="Z8">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AA8">
-        <v>700</v>
+        <v>1000</v>
       </c>
       <c r="AB8">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AC8">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AD8">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AE8">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AF8">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AG8">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AH8">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AI8">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AJ8">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AK8">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AL8">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AM8">
+        <v>1000</v>
+      </c>
+      <c r="AN8">
         <v>55</v>
       </c>
-      <c r="AN8">
-        <v>4.8</v>
-      </c>
       <c r="AO8">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AP8">
-        <v>32</v>
+        <v>1.01</v>
       </c>
       <c r="AQ8">
-        <v>18</v>
+        <v>2.5</v>
       </c>
       <c r="AR8">
-        <v>9</v>
+        <v>2.5</v>
       </c>
       <c r="AS8">
-        <v>8.199999999999999</v>
+        <v>2.5</v>
       </c>
       <c r="AT8">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="AU8">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AV8">
-        <v>17</v>
+        <v>2.5</v>
       </c>
       <c r="AW8">
-        <v>7.6</v>
+        <v>2.5</v>
       </c>
       <c r="AX8">
-        <v>14.5</v>
+        <v>1.01</v>
       </c>
       <c r="AY8">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AZ8">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA8">
-        <v>9</v>
+        <v>2.5</v>
       </c>
       <c r="BB8">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="BC8">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="BD8">
-        <v>18</v>
+        <v>1.01</v>
       </c>
       <c r="BE8">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="BF8">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="BG8">
-        <v>6.6</v>
+        <v>1.55</v>
       </c>
       <c r="BH8">
-        <v>6.8</v>
+        <v>1000</v>
       </c>
       <c r="BI8">
-        <v>4.7</v>
+        <v>1.04</v>
       </c>
       <c r="BJ8">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="BK8">
-        <v>3.5</v>
+        <v>1.04</v>
       </c>
       <c r="BL8">
         <v>1000</v>
       </c>
       <c r="BM8">
-        <v>5</v>
+        <v>1.04</v>
       </c>
       <c r="BN8">
-        <v>6</v>
+        <v>1000</v>
       </c>
       <c r="BO8">
-        <v>4.2</v>
+        <v>1.04</v>
       </c>
       <c r="BP8">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ8">
-        <v>3.7</v>
+        <v>1.04</v>
       </c>
       <c r="BR8">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="BS8">
-        <v>4.2</v>
+        <v>1.04</v>
       </c>
       <c r="BT8">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="BU8">
-        <v>3.65</v>
+        <v>1.04</v>
       </c>
       <c r="BV8">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="BW8">
-        <v>4.7</v>
+        <v>1.04</v>
       </c>
       <c r="BX8">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BY8">
-        <v>4.7</v>
+        <v>1.04</v>
       </c>
       <c r="BZ8">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="CA8">
-        <v>3.5</v>
+        <v>1.04</v>
       </c>
       <c r="CB8" t="s">
-        <v>143</v>
+        <v>129</v>
       </c>
     </row>
     <row r="9" spans="1:80">
       <c r="A9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B9" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C9" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="D9" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="E9" t="s">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="F9">
-        <v>2.56</v>
+        <v>1.3</v>
       </c>
       <c r="G9">
-        <v>2.8</v>
+        <v>600</v>
       </c>
       <c r="H9">
-        <v>2.88</v>
+        <v>2.4</v>
       </c>
       <c r="I9">
-        <v>3.3</v>
+        <v>870</v>
       </c>
       <c r="J9">
-        <v>2.88</v>
+        <v>2.32</v>
       </c>
       <c r="K9">
-        <v>3.7</v>
+        <v>950</v>
       </c>
       <c r="L9">
-        <v>1.41</v>
+        <v>1.01</v>
       </c>
       <c r="M9">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="N9">
-        <v>3.35</v>
+        <v>1.1</v>
       </c>
       <c r="O9">
-        <v>1.33</v>
+        <v>1.01</v>
       </c>
       <c r="P9">
-        <v>1.81</v>
+        <v>1.24</v>
       </c>
       <c r="Q9">
-        <v>2.02</v>
+        <v>1.01</v>
       </c>
       <c r="R9">
-        <v>1.31</v>
+        <v>1.18</v>
       </c>
       <c r="S9">
-        <v>3.6</v>
+        <v>1.01</v>
       </c>
       <c r="T9">
-        <v>1.76</v>
+        <v>1.11</v>
       </c>
       <c r="U9">
-        <v>2.06</v>
+        <v>1.11</v>
       </c>
       <c r="V9">
-        <v>1.46</v>
+        <v>1.01</v>
       </c>
       <c r="W9">
-        <v>1.56</v>
+        <v>1.01</v>
       </c>
       <c r="X9">
-        <v>15.5</v>
+        <v>500</v>
       </c>
       <c r="Y9">
-        <v>14</v>
+        <v>500</v>
       </c>
       <c r="Z9">
-        <v>25</v>
+        <v>500</v>
       </c>
       <c r="AA9">
-        <v>60</v>
+        <v>500</v>
       </c>
       <c r="AB9">
-        <v>12.5</v>
+        <v>500</v>
       </c>
       <c r="AC9">
-        <v>8.199999999999999</v>
+        <v>500</v>
       </c>
       <c r="AD9">
-        <v>16</v>
+        <v>500</v>
       </c>
       <c r="AE9">
-        <v>42</v>
+        <v>500</v>
       </c>
       <c r="AF9">
-        <v>18.5</v>
+        <v>500</v>
       </c>
       <c r="AG9">
-        <v>13</v>
+        <v>500</v>
       </c>
       <c r="AH9">
-        <v>19</v>
+        <v>500</v>
       </c>
       <c r="AI9">
-        <v>55</v>
+        <v>500</v>
       </c>
       <c r="AJ9">
-        <v>46</v>
+        <v>500</v>
       </c>
       <c r="AK9">
-        <v>36</v>
+        <v>500</v>
       </c>
       <c r="AL9">
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="AM9">
-        <v>110</v>
+        <v>500</v>
       </c>
       <c r="AN9">
-        <v>30</v>
+        <v>500</v>
       </c>
       <c r="AO9">
-        <v>36</v>
+        <v>500</v>
       </c>
       <c r="AP9">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AQ9">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AR9">
-        <v>17.5</v>
+        <v>1.01</v>
       </c>
       <c r="AS9">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="AT9">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="AU9">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="AV9">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AW9">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="AX9">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="AY9">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AZ9">
-        <v>14.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA9">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="BB9">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="BC9">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="BD9">
-        <v>24</v>
+        <v>1.01</v>
       </c>
       <c r="BE9">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="BF9">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BG9">
-        <v>9.800000000000001</v>
+        <v>1.55</v>
       </c>
       <c r="BH9">
-        <v>3.8</v>
+        <v>1000</v>
       </c>
       <c r="BI9">
-        <v>2.64</v>
+        <v>1.01</v>
       </c>
       <c r="BJ9">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="BK9">
-        <v>3.4</v>
+        <v>1.01</v>
       </c>
       <c r="BL9">
         <v>1000</v>
       </c>
       <c r="BM9">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="BN9">
-        <v>6.6</v>
+        <v>1000</v>
       </c>
       <c r="BO9">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="BP9">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="BQ9">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="BR9">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="BS9">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="BT9">
-        <v>7.2</v>
+        <v>1000</v>
       </c>
       <c r="BU9">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="BV9">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="BW9">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="BX9">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="BY9">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="BZ9">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="CA9">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="CB9" t="s">
-        <v>143</v>
+        <v>129</v>
       </c>
     </row>
     <row r="10" spans="1:80">
       <c r="A10" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="B10" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C10" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="D10" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="E10" t="s">
-        <v>132</v>
+        <v>122</v>
       </c>
       <c r="F10">
-        <v>2.64</v>
+        <v>2.28</v>
       </c>
       <c r="G10">
-        <v>2.84</v>
+        <v>2.44</v>
       </c>
       <c r="H10">
-        <v>2.76</v>
+        <v>3.2</v>
       </c>
       <c r="I10">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="J10">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="K10">
         <v>3.65</v>
       </c>
       <c r="L10">
-        <v>1.34</v>
+        <v>1.41</v>
       </c>
       <c r="M10">
         <v>1.07</v>
       </c>
       <c r="N10">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="O10">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="P10">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="Q10">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="R10">
         <v>1.33</v>
       </c>
       <c r="S10">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="T10">
-        <v>1.77</v>
+        <v>1.87</v>
       </c>
       <c r="U10">
-        <v>2.1</v>
+        <v>1.11</v>
       </c>
       <c r="V10">
-        <v>1.5</v>
+        <v>1.01</v>
       </c>
       <c r="W10">
-        <v>1.54</v>
+        <v>1.01</v>
       </c>
       <c r="X10">
-        <v>16.5</v>
+        <v>970</v>
       </c>
       <c r="Y10">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="Z10">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="AA10">
-        <v>55</v>
+        <v>900</v>
       </c>
       <c r="AB10">
-        <v>12.5</v>
+        <v>970</v>
       </c>
       <c r="AC10">
-        <v>8.199999999999999</v>
+        <v>42</v>
       </c>
       <c r="AD10">
-        <v>16</v>
+        <v>970</v>
       </c>
       <c r="AE10">
-        <v>50</v>
+        <v>110</v>
       </c>
       <c r="AF10">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AG10">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AH10">
-        <v>18</v>
+        <v>970</v>
       </c>
       <c r="AI10">
-        <v>150</v>
+        <v>130</v>
       </c>
       <c r="AJ10">
-        <v>44</v>
+        <v>900</v>
       </c>
       <c r="AK10">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AL10">
-        <v>55</v>
+        <v>110</v>
       </c>
       <c r="AM10">
         <v>580</v>
       </c>
       <c r="AN10">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AO10">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AP10">
-        <v>11.5</v>
+        <v>1.36</v>
       </c>
       <c r="AQ10">
-        <v>9.800000000000001</v>
+        <v>1.43</v>
       </c>
       <c r="AR10">
-        <v>16.5</v>
+        <v>1.39</v>
       </c>
       <c r="AS10">
-        <v>5.4</v>
+        <v>1.42</v>
       </c>
       <c r="AT10">
-        <v>9.6</v>
+        <v>1.34</v>
       </c>
       <c r="AU10">
-        <v>6.8</v>
+        <v>1.3</v>
       </c>
       <c r="AV10">
-        <v>11</v>
+        <v>1.37</v>
       </c>
       <c r="AW10">
-        <v>16</v>
+        <v>1.42</v>
       </c>
       <c r="AX10">
-        <v>15</v>
+        <v>1.43</v>
       </c>
       <c r="AY10">
-        <v>10.5</v>
+        <v>1.43</v>
       </c>
       <c r="AZ10">
-        <v>14.5</v>
+        <v>1.36</v>
       </c>
       <c r="BA10">
-        <v>5.4</v>
+        <v>1.42</v>
       </c>
       <c r="BB10">
-        <v>16.5</v>
+        <v>1.43</v>
       </c>
       <c r="BC10">
-        <v>15</v>
+        <v>1.41</v>
       </c>
       <c r="BD10">
-        <v>22</v>
+        <v>1.42</v>
       </c>
       <c r="BE10">
-        <v>5.7</v>
+        <v>1.43</v>
       </c>
       <c r="BF10">
-        <v>21</v>
+        <v>1.55</v>
       </c>
       <c r="BG10">
-        <v>6.2</v>
+        <v>1.55</v>
       </c>
       <c r="BH10">
-        <v>3.45</v>
+        <v>1000</v>
       </c>
       <c r="BI10">
-        <v>2.98</v>
+        <v>1.04</v>
       </c>
       <c r="BJ10">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="BK10">
-        <v>5</v>
+        <v>1.04</v>
       </c>
       <c r="BL10">
         <v>1000</v>
       </c>
       <c r="BM10">
-        <v>9.6</v>
+        <v>1.04</v>
       </c>
       <c r="BN10">
-        <v>5.9</v>
+        <v>1000</v>
       </c>
       <c r="BO10">
-        <v>4.3</v>
+        <v>1.04</v>
       </c>
       <c r="BP10">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="BQ10">
-        <v>7</v>
+        <v>1.04</v>
       </c>
       <c r="BR10">
         <v>1000</v>
       </c>
       <c r="BS10">
-        <v>8</v>
+        <v>1.04</v>
       </c>
       <c r="BT10">
-        <v>6.2</v>
+        <v>1000</v>
       </c>
       <c r="BU10">
-        <v>4.5</v>
+        <v>1.04</v>
       </c>
       <c r="BV10">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="BW10">
-        <v>7.2</v>
+        <v>1.04</v>
       </c>
       <c r="BX10">
         <v>1000</v>
       </c>
       <c r="BY10">
-        <v>8.199999999999999</v>
+        <v>1.04</v>
       </c>
       <c r="BZ10">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="CA10">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="CB10" t="s">
-        <v>143</v>
+        <v>129</v>
       </c>
     </row>
     <row r="11" spans="1:80">
       <c r="A11" t="s">
+        <v>81</v>
+      </c>
+      <c r="B11" t="s">
         <v>87</v>
       </c>
-      <c r="B11" t="s">
-        <v>89</v>
-      </c>
       <c r="C11" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="D11" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="E11" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="F11">
-        <v>2.28</v>
+        <v>1.83</v>
       </c>
       <c r="G11">
-        <v>2.42</v>
+        <v>1.93</v>
       </c>
       <c r="H11">
-        <v>3.45</v>
+        <v>4.7</v>
       </c>
       <c r="I11">
-        <v>3.65</v>
+        <v>6.4</v>
       </c>
       <c r="J11">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K11">
         <v>3.65</v>
       </c>
       <c r="L11">
-        <v>1.01</v>
+        <v>1.52</v>
       </c>
       <c r="M11">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="N11">
-        <v>3.7</v>
+        <v>2.88</v>
       </c>
       <c r="O11">
-        <v>1.31</v>
+        <v>1.47</v>
       </c>
       <c r="P11">
-        <v>1.91</v>
+        <v>1.62</v>
       </c>
       <c r="Q11">
-        <v>1.92</v>
+        <v>2.42</v>
       </c>
       <c r="R11">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="S11">
-        <v>3.35</v>
+        <v>4.7</v>
       </c>
       <c r="T11">
-        <v>1.74</v>
+        <v>1.11</v>
       </c>
       <c r="U11">
-        <v>2.18</v>
+        <v>1.11</v>
       </c>
       <c r="V11">
-        <v>1.38</v>
+        <v>1.01</v>
       </c>
       <c r="W11">
-        <v>1.71</v>
+        <v>1.01</v>
       </c>
       <c r="X11">
-        <v>15</v>
+        <v>970</v>
       </c>
       <c r="Y11">
-        <v>14</v>
+        <v>970</v>
       </c>
       <c r="Z11">
-        <v>26</v>
+        <v>120</v>
       </c>
       <c r="AA11">
-        <v>75</v>
+        <v>900</v>
       </c>
       <c r="AB11">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AC11">
-        <v>9.6</v>
+        <v>42</v>
       </c>
       <c r="AD11">
-        <v>15</v>
+        <v>970</v>
       </c>
       <c r="AE11">
-        <v>48</v>
+        <v>260</v>
       </c>
       <c r="AF11">
-        <v>15.5</v>
+        <v>970</v>
       </c>
       <c r="AG11">
-        <v>13.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AH11">
-        <v>17</v>
+        <v>950</v>
       </c>
       <c r="AI11">
-        <v>60</v>
+        <v>700</v>
       </c>
       <c r="AJ11">
-        <v>38</v>
+        <v>900</v>
       </c>
       <c r="AK11">
-        <v>32</v>
+        <v>100</v>
       </c>
       <c r="AL11">
-        <v>46</v>
+        <v>450</v>
       </c>
       <c r="AM11">
-        <v>110</v>
+        <v>580</v>
       </c>
       <c r="AN11">
-        <v>23</v>
+        <v>970</v>
       </c>
       <c r="AO11">
-        <v>46</v>
+        <v>700</v>
       </c>
       <c r="AP11">
-        <v>12.5</v>
+        <v>1.67</v>
       </c>
       <c r="AQ11">
-        <v>11.5</v>
+        <v>1.73</v>
       </c>
       <c r="AR11">
-        <v>21</v>
+        <v>1.83</v>
       </c>
       <c r="AS11">
-        <v>5.5</v>
+        <v>1.85</v>
       </c>
       <c r="AT11">
-        <v>9</v>
+        <v>1.86</v>
       </c>
       <c r="AU11">
-        <v>7</v>
+        <v>1.64</v>
       </c>
       <c r="AV11">
-        <v>12.5</v>
+        <v>1.78</v>
       </c>
       <c r="AW11">
-        <v>5.3</v>
+        <v>1.85</v>
       </c>
       <c r="AX11">
-        <v>13</v>
+        <v>5.1</v>
       </c>
       <c r="AY11">
-        <v>9.800000000000001</v>
+        <v>1.55</v>
       </c>
       <c r="AZ11">
-        <v>14.5</v>
+        <v>1.8</v>
       </c>
       <c r="BA11">
-        <v>5.3</v>
+        <v>1.85</v>
       </c>
       <c r="BB11">
-        <v>14.5</v>
+        <v>1.8</v>
       </c>
       <c r="BC11">
-        <v>21</v>
+        <v>1.81</v>
       </c>
       <c r="BD11">
-        <v>5.2</v>
+        <v>1.83</v>
       </c>
       <c r="BE11">
-        <v>5.6</v>
+        <v>1.85</v>
       </c>
       <c r="BF11">
-        <v>13.5</v>
+        <v>4.3</v>
       </c>
       <c r="BG11">
-        <v>6.8</v>
+        <v>1.85</v>
       </c>
       <c r="BH11">
         <v>1000</v>
       </c>
       <c r="BI11">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ11">
         <v>1000</v>
       </c>
       <c r="BK11">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL11">
         <v>1000</v>
       </c>
       <c r="BM11">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN11">
         <v>1000</v>
       </c>
       <c r="BO11">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP11">
         <v>1000</v>
       </c>
       <c r="BQ11">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR11">
         <v>1000</v>
       </c>
       <c r="BS11">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT11">
         <v>1000</v>
       </c>
       <c r="BU11">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV11">
         <v>1000</v>
       </c>
       <c r="BW11">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX11">
         <v>1000</v>
       </c>
       <c r="BY11">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA11">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="CB11" t="s">
-        <v>143</v>
+        <v>129</v>
       </c>
     </row>
     <row r="12" spans="1:80">
       <c r="A12" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B12" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C12" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="D12" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="E12" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="F12">
-        <v>1.05</v>
+        <v>4</v>
       </c>
       <c r="G12">
-        <v>1.64</v>
+        <v>100</v>
       </c>
       <c r="H12">
-        <v>5.4</v>
+        <v>1.47</v>
       </c>
       <c r="I12">
-        <v>990</v>
+        <v>2.04</v>
       </c>
       <c r="J12">
-        <v>3.8</v>
+        <v>2.7</v>
       </c>
       <c r="K12">
-        <v>500</v>
+        <v>44</v>
       </c>
       <c r="L12">
         <v>1.01</v>
@@ -3483,22 +3441,22 @@
         <v>1.01</v>
       </c>
       <c r="N12">
-        <v>1.32</v>
+        <v>1.1</v>
       </c>
       <c r="O12">
-        <v>1.28</v>
+        <v>1.09</v>
       </c>
       <c r="P12">
         <v>1.25</v>
       </c>
       <c r="Q12">
-        <v>1.28</v>
+        <v>1.86</v>
       </c>
       <c r="R12">
         <v>1.18</v>
       </c>
       <c r="S12">
-        <v>1.27</v>
+        <v>1.05</v>
       </c>
       <c r="T12">
         <v>1.11</v>
@@ -3510,43 +3468,43 @@
         <v>1.01</v>
       </c>
       <c r="W12">
-        <v>2.52</v>
+        <v>1.01</v>
       </c>
       <c r="X12">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="Y12">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="Z12">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AA12">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AB12">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AC12">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AD12">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AE12">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AF12">
-        <v>1000</v>
+        <v>570</v>
       </c>
       <c r="AG12">
-        <v>1000</v>
+        <v>330</v>
       </c>
       <c r="AH12">
-        <v>1000</v>
+        <v>380</v>
       </c>
       <c r="AI12">
-        <v>1000</v>
+        <v>770</v>
       </c>
       <c r="AJ12">
         <v>1000</v>
@@ -3561,64 +3519,64 @@
         <v>1000</v>
       </c>
       <c r="AN12">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AO12">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AP12">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="AQ12">
-        <v>2.5</v>
+        <v>2.94</v>
       </c>
       <c r="AR12">
-        <v>2.5</v>
+        <v>1.47</v>
       </c>
       <c r="AS12">
-        <v>2.5</v>
+        <v>9</v>
       </c>
       <c r="AT12">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="AU12">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AV12">
-        <v>2.5</v>
+        <v>8</v>
       </c>
       <c r="AW12">
-        <v>2.5</v>
+        <v>13.5</v>
       </c>
       <c r="AX12">
-        <v>1.01</v>
+        <v>24</v>
       </c>
       <c r="AY12">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="AZ12">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="BA12">
-        <v>2.5</v>
+        <v>34</v>
       </c>
       <c r="BB12">
-        <v>1.01</v>
+        <v>1.65</v>
       </c>
       <c r="BC12">
-        <v>1.01</v>
+        <v>1.65</v>
       </c>
       <c r="BD12">
-        <v>1.01</v>
+        <v>1.65</v>
       </c>
       <c r="BE12">
-        <v>1.01</v>
+        <v>1.65</v>
       </c>
       <c r="BF12">
-        <v>1.01</v>
+        <v>1.65</v>
       </c>
       <c r="BG12">
-        <v>1.55</v>
+        <v>6.4</v>
       </c>
       <c r="BH12">
         <v>1000</v>
@@ -3675,846 +3633,846 @@
         <v>1.01</v>
       </c>
       <c r="BZ12">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA12">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="CB12" t="s">
-        <v>143</v>
+        <v>129</v>
       </c>
     </row>
     <row r="13" spans="1:80">
       <c r="A13" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B13" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C13" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="D13" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="E13" t="s">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="F13">
-        <v>1.3</v>
+        <v>2.44</v>
       </c>
       <c r="G13">
-        <v>110</v>
+        <v>2.52</v>
       </c>
       <c r="H13">
-        <v>2.4</v>
+        <v>3.6</v>
       </c>
       <c r="I13">
-        <v>990</v>
+        <v>3.75</v>
       </c>
       <c r="J13">
-        <v>2.32</v>
+        <v>3.05</v>
       </c>
       <c r="K13">
-        <v>950</v>
+        <v>3.15</v>
       </c>
       <c r="L13">
-        <v>1.01</v>
+        <v>1.59</v>
       </c>
       <c r="M13">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="N13">
-        <v>1.26</v>
+        <v>2.68</v>
       </c>
       <c r="O13">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="P13">
-        <v>1.25</v>
+        <v>1.54</v>
       </c>
       <c r="Q13">
-        <v>2.5</v>
+        <v>2.74</v>
       </c>
       <c r="R13">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="S13">
-        <v>3.85</v>
+        <v>5.7</v>
       </c>
       <c r="T13">
-        <v>1.11</v>
+        <v>2.16</v>
       </c>
       <c r="U13">
-        <v>1.11</v>
+        <v>1.72</v>
       </c>
       <c r="V13">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="W13">
-        <v>1.17</v>
+        <v>1.01</v>
       </c>
       <c r="X13">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="Y13">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="Z13">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AA13">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AB13">
-        <v>500</v>
+        <v>8</v>
       </c>
       <c r="AC13">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="AD13">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AE13">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AF13">
-        <v>500</v>
+        <v>14</v>
       </c>
       <c r="AG13">
-        <v>500</v>
+        <v>15</v>
       </c>
       <c r="AH13">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AI13">
-        <v>1000</v>
+        <v>220</v>
       </c>
       <c r="AJ13">
-        <v>500</v>
+        <v>44</v>
       </c>
       <c r="AK13">
-        <v>500</v>
+        <v>42</v>
       </c>
       <c r="AL13">
-        <v>500</v>
+        <v>140</v>
       </c>
       <c r="AM13">
         <v>1000</v>
       </c>
       <c r="AN13">
-        <v>500</v>
+        <v>46</v>
       </c>
       <c r="AO13">
-        <v>1000</v>
+        <v>220</v>
       </c>
       <c r="AP13">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AQ13">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR13">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="AS13">
-        <v>1.01</v>
+        <v>32</v>
       </c>
       <c r="AT13">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AU13">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AV13">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="AW13">
-        <v>1.01</v>
+        <v>29</v>
       </c>
       <c r="AX13">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AY13">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AZ13">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="BA13">
-        <v>1.01</v>
+        <v>36</v>
       </c>
       <c r="BB13">
-        <v>1.01</v>
+        <v>22</v>
       </c>
       <c r="BC13">
-        <v>1.01</v>
+        <v>22</v>
       </c>
       <c r="BD13">
-        <v>1.01</v>
+        <v>32</v>
       </c>
       <c r="BE13">
-        <v>1.01</v>
+        <v>70</v>
       </c>
       <c r="BF13">
-        <v>1.01</v>
+        <v>22</v>
       </c>
       <c r="BG13">
-        <v>1.55</v>
+        <v>34</v>
       </c>
       <c r="BH13">
         <v>1000</v>
       </c>
       <c r="BI13">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ13">
         <v>1000</v>
       </c>
       <c r="BK13">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL13">
         <v>1000</v>
       </c>
       <c r="BM13">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN13">
         <v>1000</v>
       </c>
       <c r="BO13">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP13">
         <v>1000</v>
       </c>
       <c r="BQ13">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR13">
         <v>1000</v>
       </c>
       <c r="BS13">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT13">
         <v>1000</v>
       </c>
       <c r="BU13">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV13">
         <v>1000</v>
       </c>
       <c r="BW13">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX13">
         <v>1000</v>
       </c>
       <c r="BY13">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ13">
         <v>1000</v>
       </c>
       <c r="CA13">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB13" t="s">
-        <v>143</v>
+        <v>129</v>
       </c>
     </row>
     <row r="14" spans="1:80">
       <c r="A14" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B14" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C14" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="D14" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="E14" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="F14">
-        <v>2.26</v>
+        <v>1.85</v>
       </c>
       <c r="G14">
-        <v>2.46</v>
+        <v>2</v>
       </c>
       <c r="H14">
-        <v>3.25</v>
+        <v>4.4</v>
       </c>
       <c r="I14">
-        <v>3.6</v>
+        <v>5.9</v>
       </c>
       <c r="J14">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="K14">
-        <v>3.7</v>
+        <v>3.95</v>
       </c>
       <c r="L14">
-        <v>1.18</v>
+        <v>1.46</v>
       </c>
       <c r="M14">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="N14">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="O14">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="P14">
+        <v>1.74</v>
+      </c>
+      <c r="Q14">
+        <v>2.16</v>
+      </c>
+      <c r="R14">
+        <v>1.27</v>
+      </c>
+      <c r="S14">
+        <v>3.95</v>
+      </c>
+      <c r="T14">
+        <v>1.11</v>
+      </c>
+      <c r="U14">
+        <v>1.11</v>
+      </c>
+      <c r="V14">
+        <v>1.01</v>
+      </c>
+      <c r="W14">
+        <v>1.01</v>
+      </c>
+      <c r="X14">
+        <v>500</v>
+      </c>
+      <c r="Y14">
+        <v>970</v>
+      </c>
+      <c r="Z14">
+        <v>500</v>
+      </c>
+      <c r="AA14">
+        <v>900</v>
+      </c>
+      <c r="AB14">
+        <v>970</v>
+      </c>
+      <c r="AC14">
+        <v>42</v>
+      </c>
+      <c r="AD14">
+        <v>950</v>
+      </c>
+      <c r="AE14">
+        <v>500</v>
+      </c>
+      <c r="AF14">
+        <v>970</v>
+      </c>
+      <c r="AG14">
+        <v>500</v>
+      </c>
+      <c r="AH14">
+        <v>950</v>
+      </c>
+      <c r="AI14">
+        <v>500</v>
+      </c>
+      <c r="AJ14">
+        <v>500</v>
+      </c>
+      <c r="AK14">
+        <v>500</v>
+      </c>
+      <c r="AL14">
+        <v>500</v>
+      </c>
+      <c r="AM14">
+        <v>580</v>
+      </c>
+      <c r="AN14">
+        <v>65</v>
+      </c>
+      <c r="AO14">
+        <v>300</v>
+      </c>
+      <c r="AP14">
+        <v>2.5</v>
+      </c>
+      <c r="AQ14">
+        <v>1.75</v>
+      </c>
+      <c r="AR14">
+        <v>1.85</v>
+      </c>
+      <c r="AS14">
+        <v>1.88</v>
+      </c>
+      <c r="AT14">
+        <v>4.2</v>
+      </c>
+      <c r="AU14">
+        <v>4.4</v>
+      </c>
+      <c r="AV14">
+        <v>1.81</v>
+      </c>
+      <c r="AW14">
         <v>1.87</v>
       </c>
-      <c r="Q14">
-        <v>1.95</v>
-      </c>
-      <c r="R14">
-        <v>1.34</v>
-      </c>
-      <c r="S14">
-        <v>3.45</v>
-      </c>
-      <c r="T14">
+      <c r="AX14">
+        <v>2.5</v>
+      </c>
+      <c r="AY14">
+        <v>1.71</v>
+      </c>
+      <c r="AZ14">
+        <v>1.82</v>
+      </c>
+      <c r="BA14">
         <v>1.87</v>
       </c>
-      <c r="U14">
-        <v>2.12</v>
-      </c>
-      <c r="V14">
-        <v>1.38</v>
-      </c>
-      <c r="W14">
-        <v>1.68</v>
-      </c>
-      <c r="X14">
-        <v>14.5</v>
-      </c>
-      <c r="Y14">
-        <v>15.5</v>
-      </c>
-      <c r="Z14">
-        <v>25</v>
-      </c>
-      <c r="AA14">
-        <v>65</v>
-      </c>
-      <c r="AB14">
-        <v>10.5</v>
-      </c>
-      <c r="AC14">
-        <v>8.4</v>
-      </c>
-      <c r="AD14">
-        <v>15</v>
-      </c>
-      <c r="AE14">
-        <v>42</v>
-      </c>
-      <c r="AF14">
-        <v>16</v>
-      </c>
-      <c r="AG14">
-        <v>14</v>
-      </c>
-      <c r="AH14">
-        <v>18.5</v>
-      </c>
-      <c r="AI14">
-        <v>55</v>
-      </c>
-      <c r="AJ14">
-        <v>34</v>
-      </c>
-      <c r="AK14">
-        <v>27</v>
-      </c>
-      <c r="AL14">
-        <v>42</v>
-      </c>
-      <c r="AM14">
-        <v>120</v>
-      </c>
-      <c r="AN14">
-        <v>24</v>
-      </c>
-      <c r="AO14">
-        <v>42</v>
-      </c>
-      <c r="AP14">
-        <v>12</v>
-      </c>
-      <c r="AQ14">
-        <v>11</v>
-      </c>
-      <c r="AR14">
-        <v>20</v>
-      </c>
-      <c r="AS14">
-        <v>6.4</v>
-      </c>
-      <c r="AT14">
-        <v>8.6</v>
-      </c>
-      <c r="AU14">
-        <v>6.8</v>
-      </c>
-      <c r="AV14">
-        <v>12</v>
-      </c>
-      <c r="AW14">
-        <v>6.2</v>
-      </c>
-      <c r="AX14">
-        <v>13</v>
-      </c>
-      <c r="AY14">
-        <v>9.6</v>
-      </c>
-      <c r="AZ14">
-        <v>14.5</v>
-      </c>
-      <c r="BA14">
-        <v>6.4</v>
-      </c>
       <c r="BB14">
-        <v>6</v>
+        <v>1.84</v>
       </c>
       <c r="BC14">
-        <v>21</v>
+        <v>1.83</v>
       </c>
       <c r="BD14">
-        <v>32</v>
+        <v>1.86</v>
       </c>
       <c r="BE14">
-        <v>6.8</v>
+        <v>1.88</v>
       </c>
       <c r="BF14">
-        <v>16.5</v>
+        <v>4.4</v>
       </c>
       <c r="BG14">
-        <v>6.2</v>
+        <v>1.87</v>
       </c>
       <c r="BH14">
-        <v>3.5</v>
+        <v>1000</v>
       </c>
       <c r="BI14">
-        <v>2.7</v>
+        <v>1.04</v>
       </c>
       <c r="BJ14">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="BK14">
-        <v>5.2</v>
+        <v>1.04</v>
       </c>
       <c r="BL14">
         <v>1000</v>
       </c>
       <c r="BM14">
-        <v>10</v>
+        <v>1.04</v>
       </c>
       <c r="BN14">
-        <v>5.4</v>
+        <v>1000</v>
       </c>
       <c r="BO14">
-        <v>3.6</v>
+        <v>1.04</v>
       </c>
       <c r="BP14">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="BQ14">
-        <v>6.8</v>
+        <v>1.04</v>
       </c>
       <c r="BR14">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BS14">
-        <v>8</v>
+        <v>1.04</v>
       </c>
       <c r="BT14">
-        <v>6.8</v>
+        <v>1000</v>
       </c>
       <c r="BU14">
-        <v>4.9</v>
+        <v>1.04</v>
       </c>
       <c r="BV14">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="BW14">
-        <v>7.8</v>
+        <v>1.04</v>
       </c>
       <c r="BX14">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="BY14">
-        <v>8.6</v>
+        <v>1.04</v>
       </c>
       <c r="BZ14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA14">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="CB14" t="s">
-        <v>143</v>
+        <v>129</v>
       </c>
     </row>
     <row r="15" spans="1:80">
       <c r="A15" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="B15" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C15" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="D15" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="E15" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="F15">
-        <v>1.83</v>
+        <v>1.2</v>
       </c>
       <c r="G15">
-        <v>1.94</v>
+        <v>600</v>
       </c>
       <c r="H15">
-        <v>5.2</v>
+        <v>1.04</v>
       </c>
       <c r="I15">
-        <v>5.7</v>
+        <v>870</v>
       </c>
       <c r="J15">
-        <v>3.4</v>
+        <v>1.2</v>
       </c>
       <c r="K15">
-        <v>3.65</v>
+        <v>950</v>
       </c>
       <c r="L15">
-        <v>1.52</v>
+        <v>1.28</v>
       </c>
       <c r="M15">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="N15">
-        <v>2.88</v>
+        <v>1.36</v>
       </c>
       <c r="O15">
-        <v>1.47</v>
+        <v>1.01</v>
       </c>
       <c r="P15">
-        <v>1.62</v>
+        <v>1.25</v>
       </c>
       <c r="Q15">
-        <v>2.4</v>
+        <v>1.01</v>
       </c>
       <c r="R15">
-        <v>1.23</v>
+        <v>1.13</v>
       </c>
       <c r="S15">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="T15">
-        <v>2.12</v>
+        <v>1.93</v>
       </c>
       <c r="U15">
-        <v>1.78</v>
+        <v>1.32</v>
       </c>
       <c r="V15">
-        <v>1.21</v>
+        <v>1.01</v>
       </c>
       <c r="W15">
-        <v>2.06</v>
+        <v>1.01</v>
       </c>
       <c r="X15">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="Y15">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="Z15">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AA15">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="AB15">
-        <v>6.8</v>
+        <v>1000</v>
       </c>
       <c r="AC15">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="AD15">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AE15">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AF15">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AG15">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AH15">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AI15">
-        <v>700</v>
+        <v>1000</v>
       </c>
       <c r="AJ15">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AK15">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AL15">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AM15">
-        <v>580</v>
+        <v>1000</v>
       </c>
       <c r="AN15">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AO15">
-        <v>700</v>
+        <v>1000</v>
       </c>
       <c r="AP15">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="AQ15">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="AR15">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="AS15">
-        <v>14.5</v>
+        <v>1.01</v>
       </c>
       <c r="AT15">
-        <v>5.9</v>
+        <v>1.01</v>
       </c>
       <c r="AU15">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="AV15">
-        <v>19</v>
+        <v>1.01</v>
       </c>
       <c r="AW15">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="AX15">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AY15">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AZ15">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BA15">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="BB15">
-        <v>18</v>
+        <v>1.01</v>
       </c>
       <c r="BC15">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BD15">
-        <v>30</v>
+        <v>1.01</v>
       </c>
       <c r="BE15">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="BF15">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="BG15">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="BH15">
-        <v>2.9</v>
+        <v>1000</v>
       </c>
       <c r="BI15">
-        <v>2.62</v>
+        <v>1.04</v>
       </c>
       <c r="BJ15">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="BK15">
-        <v>8.800000000000001</v>
+        <v>1.04</v>
       </c>
       <c r="BL15">
         <v>1000</v>
       </c>
       <c r="BM15">
-        <v>13.5</v>
+        <v>1.04</v>
       </c>
       <c r="BN15">
-        <v>4.3</v>
+        <v>1000</v>
       </c>
       <c r="BO15">
-        <v>3.8</v>
+        <v>1.04</v>
       </c>
       <c r="BP15">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ15">
-        <v>7.2</v>
+        <v>1.04</v>
       </c>
       <c r="BR15">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="BS15">
-        <v>10.5</v>
+        <v>1.04</v>
       </c>
       <c r="BT15">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="BU15">
-        <v>5.5</v>
+        <v>1.04</v>
       </c>
       <c r="BV15">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="BW15">
-        <v>11.5</v>
+        <v>1.04</v>
       </c>
       <c r="BX15">
         <v>1000</v>
       </c>
       <c r="BY15">
-        <v>12</v>
+        <v>1.04</v>
       </c>
       <c r="BZ15">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="CA15">
-        <v>10</v>
+        <v>1.04</v>
       </c>
       <c r="CB15" t="s">
-        <v>143</v>
+        <v>129</v>
       </c>
     </row>
     <row r="16" spans="1:80">
       <c r="A16" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="B16" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C16" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D16" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="E16" t="s">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="F16">
-        <v>6.8</v>
+        <v>3.3</v>
       </c>
       <c r="G16">
-        <v>100</v>
+        <v>3.7</v>
       </c>
       <c r="H16">
-        <v>1.48</v>
+        <v>2.08</v>
       </c>
       <c r="I16">
-        <v>1.49</v>
+        <v>2.24</v>
       </c>
       <c r="J16">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="K16">
-        <v>5.7</v>
+        <v>4</v>
       </c>
       <c r="L16">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="M16">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="N16">
-        <v>1.24</v>
+        <v>4.9</v>
       </c>
       <c r="O16">
-        <v>1.09</v>
+        <v>1.21</v>
       </c>
       <c r="P16">
-        <v>1.24</v>
+        <v>2.34</v>
       </c>
       <c r="Q16">
-        <v>1.92</v>
+        <v>1.66</v>
       </c>
       <c r="R16">
-        <v>1.18</v>
+        <v>1.53</v>
       </c>
       <c r="S16">
-        <v>1.92</v>
+        <v>2.66</v>
       </c>
       <c r="T16">
-        <v>1.11</v>
+        <v>1.56</v>
       </c>
       <c r="U16">
         <v>1.11</v>
       </c>
       <c r="V16">
-        <v>3</v>
+        <v>1.01</v>
       </c>
       <c r="W16">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="X16">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="Y16">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="Z16">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AA16">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AB16">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AC16">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AD16">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AE16">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AF16">
-        <v>470</v>
+        <v>1000</v>
       </c>
       <c r="AG16">
-        <v>280</v>
+        <v>1000</v>
       </c>
       <c r="AH16">
-        <v>340</v>
+        <v>1000</v>
       </c>
       <c r="AI16">
-        <v>700</v>
+        <v>1000</v>
       </c>
       <c r="AJ16">
         <v>1000</v>
@@ -4532,49 +4490,49 @@
         <v>1000</v>
       </c>
       <c r="AO16">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AP16">
-        <v>3.7</v>
+        <v>1.01</v>
       </c>
       <c r="AQ16">
-        <v>2.76</v>
+        <v>1.01</v>
       </c>
       <c r="AR16">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="AS16">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="AT16">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="AU16">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="AV16">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="AW16">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="AX16">
-        <v>26</v>
+        <v>1.01</v>
       </c>
       <c r="AY16">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="AZ16">
-        <v>15.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA16">
-        <v>29</v>
+        <v>1.01</v>
       </c>
       <c r="BB16">
         <v>1.01</v>
       </c>
       <c r="BC16">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD16">
         <v>1.01</v>
@@ -4586,61 +4544,61 @@
         <v>1.01</v>
       </c>
       <c r="BG16">
-        <v>5.6</v>
+        <v>1.01</v>
       </c>
       <c r="BH16">
         <v>1000</v>
       </c>
       <c r="BI16">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ16">
         <v>1000</v>
       </c>
       <c r="BK16">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL16">
         <v>1000</v>
       </c>
       <c r="BM16">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN16">
         <v>1000</v>
       </c>
       <c r="BO16">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP16">
         <v>1000</v>
       </c>
       <c r="BQ16">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR16">
         <v>1000</v>
       </c>
       <c r="BS16">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT16">
         <v>1000</v>
       </c>
       <c r="BU16">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV16">
         <v>1000</v>
       </c>
       <c r="BW16">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX16">
         <v>1000</v>
       </c>
       <c r="BY16">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ16">
         <v>0</v>
@@ -4649,975 +4607,7 @@
         <v>0</v>
       </c>
       <c r="CB16" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="17" spans="1:80">
-      <c r="A17" t="s">
-        <v>80</v>
-      </c>
-      <c r="B17" t="s">
-        <v>89</v>
-      </c>
-      <c r="C17" t="s">
-        <v>101</v>
-      </c>
-      <c r="D17" t="s">
-        <v>120</v>
-      </c>
-      <c r="E17" t="s">
-        <v>139</v>
-      </c>
-      <c r="F17">
-        <v>2.42</v>
-      </c>
-      <c r="G17">
-        <v>2.5</v>
-      </c>
-      <c r="H17">
-        <v>3.6</v>
-      </c>
-      <c r="I17">
-        <v>3.8</v>
-      </c>
-      <c r="J17">
-        <v>3.05</v>
-      </c>
-      <c r="K17">
-        <v>3.15</v>
-      </c>
-      <c r="L17">
-        <v>1.58</v>
-      </c>
-      <c r="M17">
-        <v>1.13</v>
-      </c>
-      <c r="N17">
-        <v>2.64</v>
-      </c>
-      <c r="O17">
-        <v>1.56</v>
-      </c>
-      <c r="P17">
-        <v>1.54</v>
-      </c>
-      <c r="Q17">
-        <v>2.68</v>
-      </c>
-      <c r="R17">
-        <v>1.19</v>
-      </c>
-      <c r="S17">
-        <v>5.7</v>
-      </c>
-      <c r="T17">
-        <v>2.16</v>
-      </c>
-      <c r="U17">
-        <v>1.79</v>
-      </c>
-      <c r="V17">
-        <v>1.36</v>
-      </c>
-      <c r="W17">
-        <v>1.66</v>
-      </c>
-      <c r="X17">
-        <v>9</v>
-      </c>
-      <c r="Y17">
-        <v>10</v>
-      </c>
-      <c r="Z17">
-        <v>24</v>
-      </c>
-      <c r="AA17">
-        <v>95</v>
-      </c>
-      <c r="AB17">
-        <v>7.6</v>
-      </c>
-      <c r="AC17">
-        <v>7.2</v>
-      </c>
-      <c r="AD17">
-        <v>17.5</v>
-      </c>
-      <c r="AE17">
-        <v>75</v>
-      </c>
-      <c r="AF17">
-        <v>16</v>
-      </c>
-      <c r="AG17">
-        <v>12.5</v>
-      </c>
-      <c r="AH17">
-        <v>26</v>
-      </c>
-      <c r="AI17">
-        <v>220</v>
-      </c>
-      <c r="AJ17">
-        <v>44</v>
-      </c>
-      <c r="AK17">
-        <v>40</v>
-      </c>
-      <c r="AL17">
-        <v>140</v>
-      </c>
-      <c r="AM17">
-        <v>1000</v>
-      </c>
-      <c r="AN17">
-        <v>42</v>
-      </c>
-      <c r="AO17">
-        <v>220</v>
-      </c>
-      <c r="AP17">
-        <v>7.8</v>
-      </c>
-      <c r="AQ17">
-        <v>9</v>
-      </c>
-      <c r="AR17">
-        <v>16</v>
-      </c>
-      <c r="AS17">
-        <v>32</v>
-      </c>
-      <c r="AT17">
-        <v>6.8</v>
-      </c>
-      <c r="AU17">
-        <v>6.6</v>
-      </c>
-      <c r="AV17">
-        <v>14.5</v>
-      </c>
-      <c r="AW17">
-        <v>29</v>
-      </c>
-      <c r="AX17">
-        <v>12</v>
-      </c>
-      <c r="AY17">
-        <v>11.5</v>
-      </c>
-      <c r="AZ17">
-        <v>21</v>
-      </c>
-      <c r="BA17">
-        <v>36</v>
-      </c>
-      <c r="BB17">
-        <v>32</v>
-      </c>
-      <c r="BC17">
-        <v>22</v>
-      </c>
-      <c r="BD17">
-        <v>32</v>
-      </c>
-      <c r="BE17">
-        <v>70</v>
-      </c>
-      <c r="BF17">
-        <v>30</v>
-      </c>
-      <c r="BG17">
-        <v>34</v>
-      </c>
-      <c r="BH17">
-        <v>3.15</v>
-      </c>
-      <c r="BI17">
-        <v>2.24</v>
-      </c>
-      <c r="BJ17">
-        <v>13.5</v>
-      </c>
-      <c r="BK17">
-        <v>3.95</v>
-      </c>
-      <c r="BL17">
-        <v>1000</v>
-      </c>
-      <c r="BM17">
-        <v>5.5</v>
-      </c>
-      <c r="BN17">
-        <v>6</v>
-      </c>
-      <c r="BO17">
-        <v>3.9</v>
-      </c>
-      <c r="BP17">
-        <v>26</v>
-      </c>
-      <c r="BQ17">
-        <v>4.6</v>
-      </c>
-      <c r="BR17">
-        <v>55</v>
-      </c>
-      <c r="BS17">
-        <v>5.1</v>
-      </c>
-      <c r="BT17">
-        <v>6.6</v>
-      </c>
-      <c r="BU17">
-        <v>5</v>
-      </c>
-      <c r="BV17">
-        <v>44</v>
-      </c>
-      <c r="BW17">
-        <v>5</v>
-      </c>
-      <c r="BX17">
-        <v>70</v>
-      </c>
-      <c r="BY17">
-        <v>5.2</v>
-      </c>
-      <c r="BZ17">
-        <v>60</v>
-      </c>
-      <c r="CA17">
-        <v>5.1</v>
-      </c>
-      <c r="CB17" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="18" spans="1:80">
-      <c r="A18" t="s">
-        <v>86</v>
-      </c>
-      <c r="B18" t="s">
-        <v>89</v>
-      </c>
-      <c r="C18" t="s">
-        <v>102</v>
-      </c>
-      <c r="D18" t="s">
-        <v>121</v>
-      </c>
-      <c r="E18" t="s">
-        <v>140</v>
-      </c>
-      <c r="F18">
-        <v>1.8</v>
-      </c>
-      <c r="G18">
-        <v>2.06</v>
-      </c>
-      <c r="H18">
-        <v>4.2</v>
-      </c>
-      <c r="I18">
-        <v>7</v>
-      </c>
-      <c r="J18">
-        <v>3</v>
-      </c>
-      <c r="K18">
-        <v>3.85</v>
-      </c>
-      <c r="L18">
-        <v>1.35</v>
-      </c>
-      <c r="M18">
-        <v>1.05</v>
-      </c>
-      <c r="N18">
-        <v>2.86</v>
-      </c>
-      <c r="O18">
-        <v>1.39</v>
-      </c>
-      <c r="P18">
-        <v>1.64</v>
-      </c>
-      <c r="Q18">
-        <v>2.02</v>
-      </c>
-      <c r="R18">
-        <v>1.18</v>
-      </c>
-      <c r="S18">
-        <v>2.56</v>
-      </c>
-      <c r="T18">
-        <v>1.11</v>
-      </c>
-      <c r="U18">
-        <v>1.81</v>
-      </c>
-      <c r="V18">
-        <v>1.2</v>
-      </c>
-      <c r="W18">
-        <v>1.94</v>
-      </c>
-      <c r="X18">
-        <v>500</v>
-      </c>
-      <c r="Y18">
-        <v>950</v>
-      </c>
-      <c r="Z18">
-        <v>500</v>
-      </c>
-      <c r="AA18">
-        <v>900</v>
-      </c>
-      <c r="AB18">
-        <v>970</v>
-      </c>
-      <c r="AC18">
-        <v>42</v>
-      </c>
-      <c r="AD18">
-        <v>950</v>
-      </c>
-      <c r="AE18">
-        <v>500</v>
-      </c>
-      <c r="AF18">
-        <v>500</v>
-      </c>
-      <c r="AG18">
-        <v>500</v>
-      </c>
-      <c r="AH18">
-        <v>950</v>
-      </c>
-      <c r="AI18">
-        <v>500</v>
-      </c>
-      <c r="AJ18">
-        <v>900</v>
-      </c>
-      <c r="AK18">
-        <v>500</v>
-      </c>
-      <c r="AL18">
-        <v>500</v>
-      </c>
-      <c r="AM18">
-        <v>580</v>
-      </c>
-      <c r="AN18">
-        <v>500</v>
-      </c>
-      <c r="AO18">
-        <v>1000</v>
-      </c>
-      <c r="AP18">
-        <v>7.8</v>
-      </c>
-      <c r="AQ18">
-        <v>1.72</v>
-      </c>
-      <c r="AR18">
-        <v>1.82</v>
-      </c>
-      <c r="AS18">
-        <v>1.84</v>
-      </c>
-      <c r="AT18">
-        <v>4.2</v>
-      </c>
-      <c r="AU18">
-        <v>4.4</v>
-      </c>
-      <c r="AV18">
-        <v>1.78</v>
-      </c>
-      <c r="AW18">
-        <v>1.84</v>
-      </c>
-      <c r="AX18">
-        <v>5.6</v>
-      </c>
-      <c r="AY18">
-        <v>6.2</v>
-      </c>
-      <c r="AZ18">
-        <v>1.79</v>
-      </c>
-      <c r="BA18">
-        <v>1.84</v>
-      </c>
-      <c r="BB18">
-        <v>1.81</v>
-      </c>
-      <c r="BC18">
-        <v>1.8</v>
-      </c>
-      <c r="BD18">
-        <v>1.83</v>
-      </c>
-      <c r="BE18">
-        <v>1.84</v>
-      </c>
-      <c r="BF18">
-        <v>4.4</v>
-      </c>
-      <c r="BG18">
-        <v>1.85</v>
-      </c>
-      <c r="BH18">
-        <v>1000</v>
-      </c>
-      <c r="BI18">
-        <v>1.04</v>
-      </c>
-      <c r="BJ18">
-        <v>1000</v>
-      </c>
-      <c r="BK18">
-        <v>1.04</v>
-      </c>
-      <c r="BL18">
-        <v>1000</v>
-      </c>
-      <c r="BM18">
-        <v>1.04</v>
-      </c>
-      <c r="BN18">
-        <v>1000</v>
-      </c>
-      <c r="BO18">
-        <v>1.04</v>
-      </c>
-      <c r="BP18">
-        <v>1000</v>
-      </c>
-      <c r="BQ18">
-        <v>1.04</v>
-      </c>
-      <c r="BR18">
-        <v>1000</v>
-      </c>
-      <c r="BS18">
-        <v>1.04</v>
-      </c>
-      <c r="BT18">
-        <v>1000</v>
-      </c>
-      <c r="BU18">
-        <v>1.04</v>
-      </c>
-      <c r="BV18">
-        <v>1000</v>
-      </c>
-      <c r="BW18">
-        <v>1.04</v>
-      </c>
-      <c r="BX18">
-        <v>1000</v>
-      </c>
-      <c r="BY18">
-        <v>1.04</v>
-      </c>
-      <c r="BZ18">
-        <v>1000</v>
-      </c>
-      <c r="CA18">
-        <v>1.04</v>
-      </c>
-      <c r="CB18" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="19" spans="1:80">
-      <c r="A19" t="s">
-        <v>84</v>
-      </c>
-      <c r="B19" t="s">
-        <v>89</v>
-      </c>
-      <c r="C19" t="s">
-        <v>103</v>
-      </c>
-      <c r="D19" t="s">
-        <v>122</v>
-      </c>
-      <c r="E19" t="s">
-        <v>141</v>
-      </c>
-      <c r="F19">
-        <v>1.95</v>
-      </c>
-      <c r="G19">
-        <v>2.2</v>
-      </c>
-      <c r="H19">
-        <v>1.9</v>
-      </c>
-      <c r="I19">
-        <v>870</v>
-      </c>
-      <c r="J19">
-        <v>1.1</v>
-      </c>
-      <c r="K19">
-        <v>950</v>
-      </c>
-      <c r="L19">
-        <v>1.28</v>
-      </c>
-      <c r="M19">
-        <v>1.01</v>
-      </c>
-      <c r="N19">
-        <v>1.33</v>
-      </c>
-      <c r="O19">
-        <v>1.57</v>
-      </c>
-      <c r="P19">
-        <v>1.33</v>
-      </c>
-      <c r="Q19">
-        <v>1.57</v>
-      </c>
-      <c r="R19">
-        <v>1.13</v>
-      </c>
-      <c r="S19">
-        <v>1.05</v>
-      </c>
-      <c r="T19">
-        <v>1.93</v>
-      </c>
-      <c r="U19">
-        <v>1.32</v>
-      </c>
-      <c r="V19">
-        <v>1.21</v>
-      </c>
-      <c r="W19">
-        <v>1.84</v>
-      </c>
-      <c r="X19">
-        <v>1000</v>
-      </c>
-      <c r="Y19">
-        <v>1000</v>
-      </c>
-      <c r="Z19">
-        <v>1000</v>
-      </c>
-      <c r="AA19">
-        <v>1000</v>
-      </c>
-      <c r="AB19">
-        <v>7.8</v>
-      </c>
-      <c r="AC19">
-        <v>1000</v>
-      </c>
-      <c r="AD19">
-        <v>950</v>
-      </c>
-      <c r="AE19">
-        <v>1000</v>
-      </c>
-      <c r="AF19">
-        <v>970</v>
-      </c>
-      <c r="AG19">
-        <v>17</v>
-      </c>
-      <c r="AH19">
-        <v>950</v>
-      </c>
-      <c r="AI19">
-        <v>1000</v>
-      </c>
-      <c r="AJ19">
-        <v>1000</v>
-      </c>
-      <c r="AK19">
-        <v>1000</v>
-      </c>
-      <c r="AL19">
-        <v>1000</v>
-      </c>
-      <c r="AM19">
-        <v>1000</v>
-      </c>
-      <c r="AN19">
-        <v>1000</v>
-      </c>
-      <c r="AO19">
-        <v>1000</v>
-      </c>
-      <c r="AP19">
-        <v>1.34</v>
-      </c>
-      <c r="AQ19">
-        <v>1.34</v>
-      </c>
-      <c r="AR19">
-        <v>1.35</v>
-      </c>
-      <c r="AS19">
-        <v>1.35</v>
-      </c>
-      <c r="AT19">
-        <v>4.3</v>
-      </c>
-      <c r="AU19">
-        <v>1.34</v>
-      </c>
-      <c r="AV19">
-        <v>5.6</v>
-      </c>
-      <c r="AW19">
-        <v>1.35</v>
-      </c>
-      <c r="AX19">
-        <v>5.4</v>
-      </c>
-      <c r="AY19">
-        <v>6.6</v>
-      </c>
-      <c r="AZ19">
-        <v>1.31</v>
-      </c>
-      <c r="BA19">
-        <v>1.35</v>
-      </c>
-      <c r="BB19">
-        <v>1.35</v>
-      </c>
-      <c r="BC19">
-        <v>1.35</v>
-      </c>
-      <c r="BD19">
-        <v>1.35</v>
-      </c>
-      <c r="BE19">
-        <v>1.35</v>
-      </c>
-      <c r="BF19">
-        <v>1.35</v>
-      </c>
-      <c r="BG19">
-        <v>1.35</v>
-      </c>
-      <c r="BH19">
-        <v>1000</v>
-      </c>
-      <c r="BI19">
-        <v>1.04</v>
-      </c>
-      <c r="BJ19">
-        <v>1000</v>
-      </c>
-      <c r="BK19">
-        <v>1.04</v>
-      </c>
-      <c r="BL19">
-        <v>1000</v>
-      </c>
-      <c r="BM19">
-        <v>1.04</v>
-      </c>
-      <c r="BN19">
-        <v>1000</v>
-      </c>
-      <c r="BO19">
-        <v>1.04</v>
-      </c>
-      <c r="BP19">
-        <v>1000</v>
-      </c>
-      <c r="BQ19">
-        <v>1.04</v>
-      </c>
-      <c r="BR19">
-        <v>1000</v>
-      </c>
-      <c r="BS19">
-        <v>1.04</v>
-      </c>
-      <c r="BT19">
-        <v>1000</v>
-      </c>
-      <c r="BU19">
-        <v>1.04</v>
-      </c>
-      <c r="BV19">
-        <v>1000</v>
-      </c>
-      <c r="BW19">
-        <v>1.04</v>
-      </c>
-      <c r="BX19">
-        <v>1000</v>
-      </c>
-      <c r="BY19">
-        <v>1.04</v>
-      </c>
-      <c r="BZ19">
-        <v>1000</v>
-      </c>
-      <c r="CA19">
-        <v>1.04</v>
-      </c>
-      <c r="CB19" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="20" spans="1:80">
-      <c r="A20" t="s">
-        <v>83</v>
-      </c>
-      <c r="B20" t="s">
-        <v>89</v>
-      </c>
-      <c r="C20" t="s">
-        <v>104</v>
-      </c>
-      <c r="D20" t="s">
-        <v>123</v>
-      </c>
-      <c r="E20" t="s">
-        <v>142</v>
-      </c>
-      <c r="F20">
-        <v>3.15</v>
-      </c>
-      <c r="G20">
-        <v>3.75</v>
-      </c>
-      <c r="H20">
-        <v>2.06</v>
-      </c>
-      <c r="I20">
-        <v>2.3</v>
-      </c>
-      <c r="J20">
-        <v>3.65</v>
-      </c>
-      <c r="K20">
-        <v>4.1</v>
-      </c>
-      <c r="L20">
-        <v>1.01</v>
-      </c>
-      <c r="M20">
-        <v>1.01</v>
-      </c>
-      <c r="N20">
-        <v>4.8</v>
-      </c>
-      <c r="O20">
-        <v>1.19</v>
-      </c>
-      <c r="P20">
-        <v>2.3</v>
-      </c>
-      <c r="Q20">
-        <v>1.59</v>
-      </c>
-      <c r="R20">
-        <v>1.53</v>
-      </c>
-      <c r="S20">
-        <v>2.48</v>
-      </c>
-      <c r="T20">
-        <v>1.55</v>
-      </c>
-      <c r="U20">
-        <v>2.38</v>
-      </c>
-      <c r="V20">
-        <v>1.76</v>
-      </c>
-      <c r="W20">
-        <v>1.37</v>
-      </c>
-      <c r="X20">
-        <v>25</v>
-      </c>
-      <c r="Y20">
-        <v>16</v>
-      </c>
-      <c r="Z20">
-        <v>19.5</v>
-      </c>
-      <c r="AA20">
-        <v>28</v>
-      </c>
-      <c r="AB20">
-        <v>18.5</v>
-      </c>
-      <c r="AC20">
-        <v>11.5</v>
-      </c>
-      <c r="AD20">
-        <v>12.5</v>
-      </c>
-      <c r="AE20">
-        <v>25</v>
-      </c>
-      <c r="AF20">
-        <v>29</v>
-      </c>
-      <c r="AG20">
-        <v>18</v>
-      </c>
-      <c r="AH20">
-        <v>16.5</v>
-      </c>
-      <c r="AI20">
-        <v>32</v>
-      </c>
-      <c r="AJ20">
-        <v>65</v>
-      </c>
-      <c r="AK20">
-        <v>38</v>
-      </c>
-      <c r="AL20">
-        <v>44</v>
-      </c>
-      <c r="AM20">
-        <v>75</v>
-      </c>
-      <c r="AN20">
-        <v>30</v>
-      </c>
-      <c r="AO20">
-        <v>13</v>
-      </c>
-      <c r="AP20">
-        <v>18.5</v>
-      </c>
-      <c r="AQ20">
-        <v>11</v>
-      </c>
-      <c r="AR20">
-        <v>13</v>
-      </c>
-      <c r="AS20">
-        <v>4.6</v>
-      </c>
-      <c r="AT20">
-        <v>14.5</v>
-      </c>
-      <c r="AU20">
-        <v>8</v>
-      </c>
-      <c r="AV20">
-        <v>9.4</v>
-      </c>
-      <c r="AW20">
-        <v>17</v>
-      </c>
-      <c r="AX20">
-        <v>6.2</v>
-      </c>
-      <c r="AY20">
-        <v>12</v>
-      </c>
-      <c r="AZ20">
-        <v>12.5</v>
-      </c>
-      <c r="BA20">
-        <v>10.5</v>
-      </c>
-      <c r="BB20">
-        <v>5.1</v>
-      </c>
-      <c r="BC20">
-        <v>19.5</v>
-      </c>
-      <c r="BD20">
-        <v>22</v>
-      </c>
-      <c r="BE20">
-        <v>29</v>
-      </c>
-      <c r="BF20">
-        <v>17.5</v>
-      </c>
-      <c r="BG20">
-        <v>8.4</v>
-      </c>
-      <c r="BH20">
-        <v>4.9</v>
-      </c>
-      <c r="BI20">
-        <v>3.3</v>
-      </c>
-      <c r="BJ20">
-        <v>10.5</v>
-      </c>
-      <c r="BK20">
-        <v>3.25</v>
-      </c>
-      <c r="BL20">
-        <v>95</v>
-      </c>
-      <c r="BM20">
-        <v>4.4</v>
-      </c>
-      <c r="BN20">
-        <v>8.4</v>
-      </c>
-      <c r="BO20">
-        <v>5.2</v>
-      </c>
-      <c r="BP20">
-        <v>29</v>
-      </c>
-      <c r="BQ20">
-        <v>4</v>
-      </c>
-      <c r="BR20">
-        <v>36</v>
-      </c>
-      <c r="BS20">
-        <v>4.1</v>
-      </c>
-      <c r="BT20">
-        <v>6.4</v>
-      </c>
-      <c r="BU20">
-        <v>4.1</v>
-      </c>
-      <c r="BV20">
-        <v>17.5</v>
-      </c>
-      <c r="BW20">
-        <v>3.7</v>
-      </c>
-      <c r="BX20">
-        <v>28</v>
-      </c>
-      <c r="BY20">
-        <v>4</v>
-      </c>
-      <c r="BZ20">
-        <v>0</v>
-      </c>
-      <c r="CA20">
-        <v>0</v>
-      </c>
-      <c r="CB20" t="s">
-        <v>143</v>
+        <v>129</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-06.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-06.xlsx
@@ -403,7 +403,7 @@
     <t>Always Ready</t>
   </si>
   <si>
-    <t>2026-08-06 01:35:02</t>
+    <t>2026-08-06 03:47:07</t>
   </si>
 </sst>
 </file>
@@ -997,13 +997,13 @@
         <v>114</v>
       </c>
       <c r="F2">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="G2">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="H2">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="I2">
         <v>4</v>
@@ -1012,13 +1012,13 @@
         <v>3.9</v>
       </c>
       <c r="K2">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L2">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="M2">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N2">
         <v>4.8</v>
@@ -1027,43 +1027,43 @@
         <v>1.22</v>
       </c>
       <c r="P2">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="Q2">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="R2">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="S2">
-        <v>2.72</v>
+        <v>2.66</v>
       </c>
       <c r="T2">
         <v>1.65</v>
       </c>
       <c r="U2">
-        <v>1.11</v>
+        <v>2.34</v>
       </c>
       <c r="V2">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="W2">
-        <v>1.01</v>
+        <v>1.89</v>
       </c>
       <c r="X2">
         <v>21</v>
       </c>
       <c r="Y2">
-        <v>65</v>
+        <v>22</v>
       </c>
       <c r="Z2">
-        <v>65</v>
+        <v>32</v>
       </c>
       <c r="AA2">
-        <v>160</v>
+        <v>80</v>
       </c>
       <c r="AB2">
-        <v>970</v>
+        <v>12.5</v>
       </c>
       <c r="AC2">
         <v>10</v>
@@ -1075,37 +1075,37 @@
         <v>42</v>
       </c>
       <c r="AF2">
-        <v>970</v>
+        <v>16.5</v>
       </c>
       <c r="AG2">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="AH2">
         <v>17</v>
       </c>
       <c r="AI2">
-        <v>95</v>
+        <v>46</v>
       </c>
       <c r="AJ2">
-        <v>900</v>
+        <v>25</v>
       </c>
       <c r="AK2">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AL2">
-        <v>70</v>
+        <v>29</v>
       </c>
       <c r="AM2">
         <v>75</v>
       </c>
       <c r="AN2">
-        <v>85</v>
+        <v>11.5</v>
       </c>
       <c r="AO2">
-        <v>220</v>
+        <v>34</v>
       </c>
       <c r="AP2">
-        <v>4.1</v>
+        <v>14.5</v>
       </c>
       <c r="AQ2">
         <v>16</v>
@@ -1114,7 +1114,7 @@
         <v>25</v>
       </c>
       <c r="AS2">
-        <v>9.4</v>
+        <v>20</v>
       </c>
       <c r="AT2">
         <v>10.5</v>
@@ -1123,10 +1123,10 @@
         <v>4.9</v>
       </c>
       <c r="AV2">
-        <v>14</v>
+        <v>7.6</v>
       </c>
       <c r="AW2">
-        <v>14.5</v>
+        <v>7.8</v>
       </c>
       <c r="AX2">
         <v>12.5</v>
@@ -1150,64 +1150,64 @@
         <v>24</v>
       </c>
       <c r="BE2">
-        <v>4.8</v>
+        <v>9</v>
       </c>
       <c r="BF2">
         <v>9.6</v>
       </c>
       <c r="BG2">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="BH2">
-        <v>1000</v>
+        <v>4.6</v>
       </c>
       <c r="BI2">
         <v>1.01</v>
       </c>
       <c r="BJ2">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BK2">
         <v>1.01</v>
       </c>
       <c r="BL2">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="BM2">
         <v>1.01</v>
       </c>
       <c r="BN2">
-        <v>1000</v>
+        <v>5.4</v>
       </c>
       <c r="BO2">
         <v>1.01</v>
       </c>
       <c r="BP2">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="BQ2">
         <v>1.01</v>
       </c>
       <c r="BR2">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="BS2">
         <v>1.01</v>
       </c>
       <c r="BT2">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="BU2">
         <v>1.01</v>
       </c>
       <c r="BV2">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="BW2">
         <v>1.01</v>
       </c>
       <c r="BX2">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BY2">
         <v>1.01</v>
@@ -1239,19 +1239,19 @@
         <v>115</v>
       </c>
       <c r="F3">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="G3">
-        <v>1.96</v>
+        <v>1.93</v>
       </c>
       <c r="H3">
-        <v>4.9</v>
+        <v>5.5</v>
       </c>
       <c r="I3">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="J3">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="K3">
         <v>3.55</v>
@@ -1260,199 +1260,199 @@
         <v>1.59</v>
       </c>
       <c r="M3">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="N3">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="O3">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="P3">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="Q3">
-        <v>2.74</v>
+        <v>2.68</v>
       </c>
       <c r="R3">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="S3">
         <v>5.5</v>
       </c>
       <c r="T3">
-        <v>1.11</v>
+        <v>2.24</v>
       </c>
       <c r="U3">
-        <v>1.11</v>
+        <v>1.69</v>
       </c>
       <c r="V3">
-        <v>1.01</v>
+        <v>1.2</v>
       </c>
       <c r="W3">
-        <v>1.01</v>
+        <v>2.08</v>
       </c>
       <c r="X3">
-        <v>970</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Y3">
-        <v>970</v>
+        <v>14.5</v>
       </c>
       <c r="Z3">
-        <v>120</v>
+        <v>46</v>
       </c>
       <c r="AA3">
         <v>900</v>
       </c>
       <c r="AB3">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="AC3">
-        <v>42</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD3">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AE3">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AF3">
-        <v>970</v>
+        <v>10.5</v>
       </c>
       <c r="AG3">
         <v>9.4</v>
       </c>
       <c r="AH3">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AI3">
         <v>700</v>
       </c>
       <c r="AJ3">
-        <v>900</v>
+        <v>24</v>
       </c>
       <c r="AK3">
+        <v>28</v>
+      </c>
+      <c r="AL3">
         <v>75</v>
-      </c>
-      <c r="AL3">
-        <v>170</v>
       </c>
       <c r="AM3">
         <v>500</v>
       </c>
       <c r="AN3">
-        <v>60</v>
+        <v>24</v>
       </c>
       <c r="AO3">
         <v>700</v>
       </c>
       <c r="AP3">
-        <v>1.48</v>
+        <v>7.6</v>
       </c>
       <c r="AQ3">
-        <v>1.53</v>
+        <v>10.5</v>
       </c>
       <c r="AR3">
-        <v>1.61</v>
+        <v>32</v>
       </c>
       <c r="AS3">
-        <v>1.63</v>
+        <v>10.5</v>
       </c>
       <c r="AT3">
-        <v>1.63</v>
+        <v>5.6</v>
       </c>
       <c r="AU3">
-        <v>1.46</v>
+        <v>7</v>
       </c>
       <c r="AV3">
-        <v>1.63</v>
+        <v>20</v>
       </c>
       <c r="AW3">
-        <v>1.63</v>
+        <v>11</v>
       </c>
       <c r="AX3">
-        <v>1.5</v>
+        <v>8.4</v>
       </c>
       <c r="AY3">
         <v>9.199999999999999</v>
       </c>
       <c r="AZ3">
-        <v>1.63</v>
+        <v>18.5</v>
       </c>
       <c r="BA3">
-        <v>1.63</v>
+        <v>11</v>
       </c>
       <c r="BB3">
-        <v>1.63</v>
+        <v>16.5</v>
       </c>
       <c r="BC3">
-        <v>1.59</v>
+        <v>20</v>
       </c>
       <c r="BD3">
-        <v>1.61</v>
+        <v>10</v>
       </c>
       <c r="BE3">
-        <v>1.62</v>
+        <v>11</v>
       </c>
       <c r="BF3">
-        <v>1.59</v>
+        <v>19</v>
       </c>
       <c r="BG3">
-        <v>1.63</v>
+        <v>11</v>
       </c>
       <c r="BH3">
-        <v>1000</v>
+        <v>2.98</v>
       </c>
       <c r="BI3">
-        <v>1.04</v>
+        <v>2.28</v>
       </c>
       <c r="BJ3">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="BK3">
-        <v>1.04</v>
+        <v>4.3</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>1.04</v>
+        <v>6</v>
       </c>
       <c r="BN3">
-        <v>1000</v>
+        <v>4.8</v>
       </c>
       <c r="BO3">
-        <v>1.04</v>
+        <v>3.4</v>
       </c>
       <c r="BP3">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="BQ3">
-        <v>1.04</v>
+        <v>4.6</v>
       </c>
       <c r="BR3">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="BS3">
-        <v>1.04</v>
+        <v>5.5</v>
       </c>
       <c r="BT3">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="BU3">
-        <v>1.04</v>
+        <v>3.85</v>
       </c>
       <c r="BV3">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="BW3">
-        <v>1.04</v>
+        <v>5.8</v>
       </c>
       <c r="BX3">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="BY3">
-        <v>1.04</v>
+        <v>5.9</v>
       </c>
       <c r="BZ3">
         <v>0</v>
@@ -1481,25 +1481,25 @@
         <v>116</v>
       </c>
       <c r="F4">
+        <v>1.55</v>
+      </c>
+      <c r="G4">
         <v>1.6</v>
       </c>
-      <c r="G4">
-        <v>1.65</v>
-      </c>
       <c r="H4">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="I4">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="J4">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="K4">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="L4">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="M4">
         <v>1.01</v>
@@ -1508,199 +1508,199 @@
         <v>8</v>
       </c>
       <c r="O4">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="P4">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="Q4">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="R4">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="S4">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="T4">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="U4">
-        <v>2.16</v>
+        <v>2.8</v>
       </c>
       <c r="V4">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="W4">
-        <v>1.01</v>
+        <v>2.64</v>
       </c>
       <c r="X4">
-        <v>950</v>
+        <v>55</v>
       </c>
       <c r="Y4">
-        <v>950</v>
+        <v>48</v>
       </c>
       <c r="Z4">
-        <v>230</v>
+        <v>80</v>
       </c>
       <c r="AA4">
         <v>700</v>
       </c>
       <c r="AB4">
-        <v>970</v>
+        <v>21</v>
       </c>
       <c r="AC4">
-        <v>970</v>
+        <v>16</v>
       </c>
       <c r="AD4">
-        <v>950</v>
+        <v>25</v>
       </c>
       <c r="AE4">
-        <v>200</v>
+        <v>70</v>
       </c>
       <c r="AF4">
-        <v>970</v>
+        <v>17.5</v>
       </c>
       <c r="AG4">
-        <v>970</v>
+        <v>12.5</v>
       </c>
       <c r="AH4">
-        <v>970</v>
+        <v>18</v>
       </c>
       <c r="AI4">
-        <v>150</v>
+        <v>50</v>
       </c>
       <c r="AJ4">
-        <v>65</v>
+        <v>19.5</v>
       </c>
       <c r="AK4">
-        <v>970</v>
+        <v>15.5</v>
       </c>
       <c r="AL4">
-        <v>44</v>
+        <v>23</v>
       </c>
       <c r="AM4">
-        <v>580</v>
+        <v>60</v>
       </c>
       <c r="AN4">
-        <v>29</v>
+        <v>4.5</v>
       </c>
       <c r="AO4">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AP4">
-        <v>1.84</v>
+        <v>36</v>
       </c>
       <c r="AQ4">
-        <v>1.83</v>
+        <v>24</v>
       </c>
       <c r="AR4">
-        <v>1.85</v>
+        <v>23</v>
       </c>
       <c r="AS4">
-        <v>1.87</v>
+        <v>7.6</v>
       </c>
       <c r="AT4">
-        <v>1.81</v>
+        <v>15</v>
       </c>
       <c r="AU4">
-        <v>1.69</v>
+        <v>12.5</v>
       </c>
       <c r="AV4">
-        <v>1.79</v>
+        <v>20</v>
       </c>
       <c r="AW4">
-        <v>1.84</v>
+        <v>7.2</v>
       </c>
       <c r="AX4">
-        <v>1.77</v>
+        <v>14</v>
       </c>
       <c r="AY4">
-        <v>1.68</v>
+        <v>10</v>
       </c>
       <c r="AZ4">
-        <v>1.72</v>
+        <v>14.5</v>
       </c>
       <c r="BA4">
-        <v>1.83</v>
+        <v>6.8</v>
       </c>
       <c r="BB4">
-        <v>1.77</v>
+        <v>15</v>
       </c>
       <c r="BC4">
-        <v>1.74</v>
+        <v>12.5</v>
       </c>
       <c r="BD4">
-        <v>1.78</v>
+        <v>18</v>
       </c>
       <c r="BE4">
-        <v>1.85</v>
+        <v>7</v>
       </c>
       <c r="BF4">
-        <v>1.66</v>
+        <v>3.75</v>
       </c>
       <c r="BG4">
-        <v>4.9</v>
+        <v>6.4</v>
       </c>
       <c r="BH4">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="BI4">
-        <v>1.04</v>
+        <v>4.7</v>
       </c>
       <c r="BJ4">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BK4">
-        <v>1.04</v>
+        <v>3.6</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>1.04</v>
+        <v>5</v>
       </c>
       <c r="BN4">
-        <v>1000</v>
+        <v>5.8</v>
       </c>
       <c r="BO4">
-        <v>1.04</v>
+        <v>4.1</v>
       </c>
       <c r="BP4">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BQ4">
-        <v>1.04</v>
+        <v>3.65</v>
       </c>
       <c r="BR4">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="BS4">
-        <v>1.04</v>
+        <v>4.2</v>
       </c>
       <c r="BT4">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BU4">
-        <v>1.04</v>
+        <v>3.7</v>
       </c>
       <c r="BV4">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BW4">
-        <v>1.04</v>
+        <v>4.8</v>
       </c>
       <c r="BX4">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BY4">
-        <v>1.04</v>
+        <v>4.7</v>
       </c>
       <c r="BZ4">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="CA4">
-        <v>1.04</v>
+        <v>3.5</v>
       </c>
       <c r="CB4" t="s">
         <v>129</v>
@@ -1723,7 +1723,7 @@
         <v>117</v>
       </c>
       <c r="F5">
-        <v>2.56</v>
+        <v>2.7</v>
       </c>
       <c r="G5">
         <v>2.88</v>
@@ -1732,217 +1732,217 @@
         <v>2.82</v>
       </c>
       <c r="I5">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="J5">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="K5">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="L5">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="M5">
         <v>1.08</v>
       </c>
       <c r="N5">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="O5">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="P5">
-        <v>1.81</v>
+        <v>1.78</v>
       </c>
       <c r="Q5">
-        <v>2.04</v>
+        <v>2.12</v>
       </c>
       <c r="R5">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="S5">
-        <v>3.6</v>
+        <v>3.85</v>
       </c>
       <c r="T5">
-        <v>1.11</v>
+        <v>1.8</v>
       </c>
       <c r="U5">
-        <v>1.96</v>
+        <v>2.02</v>
       </c>
       <c r="V5">
-        <v>1.01</v>
+        <v>1.46</v>
       </c>
       <c r="W5">
-        <v>1.01</v>
+        <v>1.53</v>
       </c>
       <c r="X5">
-        <v>970</v>
+        <v>15</v>
       </c>
       <c r="Y5">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="Z5">
+        <v>24</v>
+      </c>
+      <c r="AA5">
+        <v>60</v>
+      </c>
+      <c r="AB5">
+        <v>12.5</v>
+      </c>
+      <c r="AC5">
+        <v>7.8</v>
+      </c>
+      <c r="AD5">
+        <v>16</v>
+      </c>
+      <c r="AE5">
+        <v>44</v>
+      </c>
+      <c r="AF5">
+        <v>19</v>
+      </c>
+      <c r="AG5">
+        <v>15.5</v>
+      </c>
+      <c r="AH5">
+        <v>22</v>
+      </c>
+      <c r="AI5">
+        <v>60</v>
+      </c>
+      <c r="AJ5">
+        <v>55</v>
+      </c>
+      <c r="AK5">
+        <v>40</v>
+      </c>
+      <c r="AL5">
+        <v>60</v>
+      </c>
+      <c r="AM5">
+        <v>450</v>
+      </c>
+      <c r="AN5">
+        <v>38</v>
+      </c>
+      <c r="AO5">
         <v>42</v>
       </c>
-      <c r="AA5">
-        <v>900</v>
-      </c>
-      <c r="AB5">
-        <v>970</v>
-      </c>
-      <c r="AC5">
-        <v>42</v>
-      </c>
-      <c r="AD5">
-        <v>1000</v>
-      </c>
-      <c r="AE5">
-        <v>230</v>
-      </c>
-      <c r="AF5">
-        <v>1000</v>
-      </c>
-      <c r="AG5">
-        <v>970</v>
-      </c>
-      <c r="AH5">
-        <v>970</v>
-      </c>
-      <c r="AI5">
-        <v>370</v>
-      </c>
-      <c r="AJ5">
-        <v>900</v>
-      </c>
-      <c r="AK5">
-        <v>80</v>
-      </c>
-      <c r="AL5">
-        <v>290</v>
-      </c>
-      <c r="AM5">
-        <v>580</v>
-      </c>
-      <c r="AN5">
-        <v>1000</v>
-      </c>
-      <c r="AO5">
-        <v>150</v>
-      </c>
       <c r="AP5">
-        <v>1.37</v>
+        <v>6.2</v>
       </c>
       <c r="AQ5">
-        <v>1.45</v>
+        <v>6.2</v>
       </c>
       <c r="AR5">
-        <v>1.41</v>
+        <v>4.1</v>
       </c>
       <c r="AS5">
-        <v>1.44</v>
+        <v>4.6</v>
       </c>
       <c r="AT5">
-        <v>4.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU5">
         <v>4.4</v>
       </c>
       <c r="AV5">
-        <v>1.45</v>
+        <v>3.8</v>
       </c>
       <c r="AW5">
-        <v>1.43</v>
+        <v>4.5</v>
       </c>
       <c r="AX5">
-        <v>1.45</v>
+        <v>3.95</v>
       </c>
       <c r="AY5">
-        <v>1.37</v>
+        <v>6.4</v>
       </c>
       <c r="AZ5">
-        <v>1.42</v>
+        <v>12</v>
       </c>
       <c r="BA5">
-        <v>1.44</v>
+        <v>4.6</v>
       </c>
       <c r="BB5">
-        <v>1.44</v>
+        <v>4.6</v>
       </c>
       <c r="BC5">
-        <v>1.43</v>
+        <v>4.4</v>
       </c>
       <c r="BD5">
-        <v>1.44</v>
+        <v>4.6</v>
       </c>
       <c r="BE5">
-        <v>1.45</v>
+        <v>4.8</v>
       </c>
       <c r="BF5">
         <v>5</v>
       </c>
       <c r="BG5">
-        <v>1.55</v>
+        <v>4.5</v>
       </c>
       <c r="BH5">
-        <v>1000</v>
+        <v>3.65</v>
       </c>
       <c r="BI5">
-        <v>1.04</v>
+        <v>2.56</v>
       </c>
       <c r="BJ5">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BK5">
-        <v>1.04</v>
+        <v>3.55</v>
       </c>
       <c r="BL5">
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>1.04</v>
+        <v>4.9</v>
       </c>
       <c r="BN5">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="BO5">
-        <v>1.04</v>
+        <v>2.92</v>
       </c>
       <c r="BP5">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BQ5">
-        <v>1.04</v>
+        <v>4.1</v>
       </c>
       <c r="BR5">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="BS5">
-        <v>1.04</v>
+        <v>4.5</v>
       </c>
       <c r="BT5">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="BU5">
-        <v>1.04</v>
+        <v>2.96</v>
       </c>
       <c r="BV5">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="BW5">
-        <v>1.04</v>
+        <v>4.3</v>
       </c>
       <c r="BX5">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="BY5">
-        <v>1.04</v>
+        <v>4.6</v>
       </c>
       <c r="BZ5">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="CA5">
-        <v>1.04</v>
+        <v>4.4</v>
       </c>
       <c r="CB5" t="s">
         <v>129</v>
@@ -1968,31 +1968,31 @@
         <v>2.28</v>
       </c>
       <c r="G6">
-        <v>2.46</v>
+        <v>2.36</v>
       </c>
       <c r="H6">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="I6">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="J6">
-        <v>3.15</v>
+        <v>3.4</v>
       </c>
       <c r="K6">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="L6">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="M6">
         <v>1.07</v>
       </c>
       <c r="N6">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="O6">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="P6">
         <v>1.96</v>
@@ -2007,175 +2007,175 @@
         <v>3.3</v>
       </c>
       <c r="T6">
-        <v>1.11</v>
+        <v>1.73</v>
       </c>
       <c r="U6">
-        <v>1.11</v>
+        <v>2.18</v>
       </c>
       <c r="V6">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="W6">
-        <v>1.01</v>
+        <v>1.73</v>
       </c>
       <c r="X6">
-        <v>970</v>
+        <v>15</v>
       </c>
       <c r="Y6">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="Z6">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AA6">
-        <v>900</v>
+        <v>75</v>
       </c>
       <c r="AB6">
-        <v>970</v>
+        <v>12.5</v>
       </c>
       <c r="AC6">
-        <v>970</v>
+        <v>9.6</v>
       </c>
       <c r="AD6">
-        <v>970</v>
+        <v>15.5</v>
       </c>
       <c r="AE6">
-        <v>120</v>
+        <v>50</v>
       </c>
       <c r="AF6">
-        <v>970</v>
+        <v>18.5</v>
       </c>
       <c r="AG6">
-        <v>970</v>
+        <v>13.5</v>
       </c>
       <c r="AH6">
-        <v>970</v>
+        <v>21</v>
       </c>
       <c r="AI6">
-        <v>250</v>
+        <v>60</v>
       </c>
       <c r="AJ6">
-        <v>900</v>
+        <v>38</v>
       </c>
       <c r="AK6">
-        <v>75</v>
+        <v>30</v>
       </c>
       <c r="AL6">
-        <v>100</v>
+        <v>46</v>
       </c>
       <c r="AM6">
-        <v>580</v>
+        <v>110</v>
       </c>
       <c r="AN6">
-        <v>55</v>
+        <v>18.5</v>
       </c>
       <c r="AO6">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="AP6">
-        <v>1.56</v>
+        <v>13</v>
       </c>
       <c r="AQ6">
-        <v>1.66</v>
+        <v>12</v>
       </c>
       <c r="AR6">
-        <v>1.66</v>
+        <v>21</v>
       </c>
       <c r="AS6">
-        <v>1.64</v>
+        <v>5.1</v>
       </c>
       <c r="AT6">
-        <v>1.54</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU6">
-        <v>4.4</v>
+        <v>7.2</v>
       </c>
       <c r="AV6">
-        <v>1.55</v>
+        <v>13</v>
       </c>
       <c r="AW6">
-        <v>1.63</v>
+        <v>4.9</v>
       </c>
       <c r="AX6">
-        <v>1.57</v>
+        <v>13</v>
       </c>
       <c r="AY6">
-        <v>1.59</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ6">
-        <v>1.56</v>
+        <v>14.5</v>
       </c>
       <c r="BA6">
-        <v>1.64</v>
+        <v>5</v>
       </c>
       <c r="BB6">
-        <v>1.63</v>
+        <v>14.5</v>
       </c>
       <c r="BC6">
-        <v>1.62</v>
+        <v>21</v>
       </c>
       <c r="BD6">
-        <v>1.63</v>
+        <v>4.8</v>
       </c>
       <c r="BE6">
-        <v>1.65</v>
+        <v>5.2</v>
       </c>
       <c r="BF6">
-        <v>4.4</v>
+        <v>16</v>
       </c>
       <c r="BG6">
-        <v>1.61</v>
+        <v>6.8</v>
       </c>
       <c r="BH6">
-        <v>1000</v>
+        <v>4.1</v>
       </c>
       <c r="BI6">
-        <v>1.01</v>
+        <v>2.78</v>
       </c>
       <c r="BJ6">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BK6">
         <v>1.01</v>
       </c>
       <c r="BL6">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="BM6">
         <v>1.01</v>
       </c>
       <c r="BN6">
-        <v>1000</v>
+        <v>5.3</v>
       </c>
       <c r="BO6">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BP6">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="BQ6">
         <v>1.01</v>
       </c>
       <c r="BR6">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BS6">
         <v>1.01</v>
       </c>
       <c r="BT6">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="BU6">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BV6">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BW6">
         <v>1.01</v>
       </c>
       <c r="BX6">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="BY6">
         <v>1.01</v>
@@ -2213,22 +2213,22 @@
         <v>2.88</v>
       </c>
       <c r="H7">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="I7">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="J7">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="K7">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="L7">
         <v>1.42</v>
       </c>
       <c r="M7">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N7">
         <v>3.55</v>
@@ -2243,67 +2243,67 @@
         <v>2</v>
       </c>
       <c r="R7">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="S7">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="T7">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="U7">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="V7">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="W7">
-        <v>1.01</v>
+        <v>1.53</v>
       </c>
       <c r="X7">
-        <v>970</v>
+        <v>14.5</v>
       </c>
       <c r="Y7">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="Z7">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="AA7">
-        <v>900</v>
+        <v>120</v>
       </c>
       <c r="AB7">
-        <v>970</v>
+        <v>11.5</v>
       </c>
       <c r="AC7">
-        <v>42</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD7">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AE7">
-        <v>90</v>
+        <v>46</v>
       </c>
       <c r="AF7">
-        <v>970</v>
+        <v>19</v>
       </c>
       <c r="AG7">
-        <v>970</v>
+        <v>13</v>
       </c>
       <c r="AH7">
+        <v>18</v>
+      </c>
+      <c r="AI7">
         <v>60</v>
       </c>
-      <c r="AI7">
-        <v>150</v>
-      </c>
       <c r="AJ7">
-        <v>900</v>
+        <v>44</v>
       </c>
       <c r="AK7">
-        <v>80</v>
+        <v>34</v>
       </c>
       <c r="AL7">
-        <v>150</v>
+        <v>46</v>
       </c>
       <c r="AM7">
         <v>580</v>
@@ -2312,121 +2312,121 @@
         <v>46</v>
       </c>
       <c r="AO7">
-        <v>55</v>
+        <v>32</v>
       </c>
       <c r="AP7">
-        <v>1.61</v>
+        <v>5.6</v>
       </c>
       <c r="AQ7">
-        <v>1.7</v>
+        <v>6.2</v>
       </c>
       <c r="AR7">
-        <v>1.63</v>
+        <v>6.2</v>
       </c>
       <c r="AS7">
-        <v>1.68</v>
+        <v>7.6</v>
       </c>
       <c r="AT7">
-        <v>1.58</v>
+        <v>5.8</v>
       </c>
       <c r="AU7">
         <v>4.4</v>
       </c>
       <c r="AV7">
-        <v>1.7</v>
+        <v>5.4</v>
       </c>
       <c r="AW7">
-        <v>1.67</v>
+        <v>7.2</v>
       </c>
       <c r="AX7">
-        <v>1.62</v>
+        <v>6</v>
       </c>
       <c r="AY7">
-        <v>1.59</v>
+        <v>5.3</v>
       </c>
       <c r="AZ7">
-        <v>1.6</v>
+        <v>10.5</v>
       </c>
       <c r="BA7">
-        <v>1.68</v>
+        <v>7.6</v>
       </c>
       <c r="BB7">
-        <v>1.68</v>
+        <v>7.4</v>
       </c>
       <c r="BC7">
-        <v>1.67</v>
+        <v>7.2</v>
       </c>
       <c r="BD7">
-        <v>1.68</v>
+        <v>7.6</v>
       </c>
       <c r="BE7">
-        <v>1.7</v>
+        <v>29</v>
       </c>
       <c r="BF7">
-        <v>5.2</v>
+        <v>6.8</v>
       </c>
       <c r="BG7">
-        <v>1.66</v>
+        <v>7</v>
       </c>
       <c r="BH7">
-        <v>1000</v>
+        <v>3.45</v>
       </c>
       <c r="BI7">
-        <v>1.04</v>
+        <v>2.66</v>
       </c>
       <c r="BJ7">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK7">
-        <v>1.04</v>
+        <v>5</v>
       </c>
       <c r="BL7">
         <v>1000</v>
       </c>
       <c r="BM7">
-        <v>1.04</v>
+        <v>2.54</v>
       </c>
       <c r="BN7">
-        <v>1000</v>
+        <v>5.9</v>
       </c>
       <c r="BO7">
-        <v>1.04</v>
+        <v>3.75</v>
       </c>
       <c r="BP7">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="BQ7">
-        <v>1.04</v>
+        <v>7</v>
       </c>
       <c r="BR7">
         <v>1000</v>
       </c>
       <c r="BS7">
-        <v>1.04</v>
+        <v>8</v>
       </c>
       <c r="BT7">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="BU7">
-        <v>1.04</v>
+        <v>3.9</v>
       </c>
       <c r="BV7">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="BW7">
-        <v>1.04</v>
+        <v>7.2</v>
       </c>
       <c r="BX7">
         <v>1000</v>
       </c>
       <c r="BY7">
-        <v>1.04</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ7">
         <v>1000</v>
       </c>
       <c r="CA7">
-        <v>1.04</v>
+        <v>7.6</v>
       </c>
       <c r="CB7" t="s">
         <v>129</v>
@@ -2458,7 +2458,7 @@
         <v>5.4</v>
       </c>
       <c r="I8">
-        <v>870</v>
+        <v>990</v>
       </c>
       <c r="J8">
         <v>3.8</v>
@@ -2473,10 +2473,10 @@
         <v>1.01</v>
       </c>
       <c r="N8">
-        <v>1.1</v>
+        <v>1.31</v>
       </c>
       <c r="O8">
-        <v>1.01</v>
+        <v>1.28</v>
       </c>
       <c r="P8">
         <v>1.25</v>
@@ -2488,7 +2488,7 @@
         <v>1.18</v>
       </c>
       <c r="S8">
-        <v>1.05</v>
+        <v>2.88</v>
       </c>
       <c r="T8">
         <v>1.11</v>
@@ -2500,7 +2500,7 @@
         <v>1.01</v>
       </c>
       <c r="W8">
-        <v>1.01</v>
+        <v>2.52</v>
       </c>
       <c r="X8">
         <v>1000</v>
@@ -2694,13 +2694,13 @@
         <v>1.3</v>
       </c>
       <c r="G9">
-        <v>600</v>
+        <v>110</v>
       </c>
       <c r="H9">
         <v>2.4</v>
       </c>
       <c r="I9">
-        <v>870</v>
+        <v>990</v>
       </c>
       <c r="J9">
         <v>2.32</v>
@@ -2715,22 +2715,22 @@
         <v>1.01</v>
       </c>
       <c r="N9">
-        <v>1.1</v>
+        <v>1.25</v>
       </c>
       <c r="O9">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="P9">
         <v>1.24</v>
       </c>
       <c r="Q9">
-        <v>1.01</v>
+        <v>2.52</v>
       </c>
       <c r="R9">
         <v>1.18</v>
       </c>
       <c r="S9">
-        <v>1.01</v>
+        <v>2.52</v>
       </c>
       <c r="T9">
         <v>1.11</v>
@@ -2739,10 +2739,10 @@
         <v>1.11</v>
       </c>
       <c r="V9">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="W9">
-        <v>1.01</v>
+        <v>1.18</v>
       </c>
       <c r="X9">
         <v>500</v>
@@ -2936,217 +2936,217 @@
         <v>2.28</v>
       </c>
       <c r="G10">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="H10">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="I10">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="J10">
         <v>3.4</v>
       </c>
       <c r="K10">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="L10">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="M10">
         <v>1.07</v>
       </c>
       <c r="N10">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="O10">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="P10">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="Q10">
         <v>2</v>
       </c>
       <c r="R10">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="S10">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="T10">
         <v>1.87</v>
       </c>
       <c r="U10">
-        <v>1.11</v>
+        <v>2.08</v>
       </c>
       <c r="V10">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="W10">
-        <v>1.01</v>
+        <v>1.7</v>
       </c>
       <c r="X10">
-        <v>970</v>
+        <v>15</v>
       </c>
       <c r="Y10">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="Z10">
-        <v>48</v>
+        <v>25</v>
       </c>
       <c r="AA10">
-        <v>900</v>
+        <v>65</v>
       </c>
       <c r="AB10">
-        <v>970</v>
+        <v>11</v>
       </c>
       <c r="AC10">
+        <v>8.4</v>
+      </c>
+      <c r="AD10">
+        <v>15</v>
+      </c>
+      <c r="AE10">
         <v>42</v>
       </c>
-      <c r="AD10">
-        <v>970</v>
-      </c>
-      <c r="AE10">
-        <v>110</v>
-      </c>
       <c r="AF10">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AG10">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AH10">
-        <v>970</v>
+        <v>18.5</v>
       </c>
       <c r="AI10">
-        <v>130</v>
+        <v>55</v>
       </c>
       <c r="AJ10">
-        <v>900</v>
+        <v>34</v>
       </c>
       <c r="AK10">
-        <v>75</v>
+        <v>27</v>
       </c>
       <c r="AL10">
-        <v>110</v>
+        <v>42</v>
       </c>
       <c r="AM10">
         <v>580</v>
       </c>
       <c r="AN10">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AO10">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AP10">
-        <v>1.36</v>
+        <v>10</v>
       </c>
       <c r="AQ10">
-        <v>1.43</v>
+        <v>10</v>
       </c>
       <c r="AR10">
-        <v>1.39</v>
+        <v>17</v>
       </c>
       <c r="AS10">
-        <v>1.42</v>
+        <v>6.2</v>
       </c>
       <c r="AT10">
-        <v>1.34</v>
+        <v>7.6</v>
       </c>
       <c r="AU10">
-        <v>1.3</v>
+        <v>6</v>
       </c>
       <c r="AV10">
-        <v>1.37</v>
+        <v>10.5</v>
       </c>
       <c r="AW10">
-        <v>1.42</v>
+        <v>5.9</v>
       </c>
       <c r="AX10">
-        <v>1.43</v>
+        <v>11</v>
       </c>
       <c r="AY10">
-        <v>1.43</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ10">
-        <v>1.36</v>
+        <v>12.5</v>
       </c>
       <c r="BA10">
-        <v>1.42</v>
+        <v>34</v>
       </c>
       <c r="BB10">
-        <v>1.43</v>
+        <v>5.7</v>
       </c>
       <c r="BC10">
-        <v>1.41</v>
+        <v>18.5</v>
       </c>
       <c r="BD10">
-        <v>1.42</v>
+        <v>5.9</v>
       </c>
       <c r="BE10">
-        <v>1.43</v>
+        <v>6.4</v>
       </c>
       <c r="BF10">
-        <v>1.55</v>
+        <v>17</v>
       </c>
       <c r="BG10">
-        <v>1.55</v>
+        <v>6</v>
       </c>
       <c r="BH10">
-        <v>1000</v>
+        <v>3.5</v>
       </c>
       <c r="BI10">
-        <v>1.04</v>
+        <v>2.7</v>
       </c>
       <c r="BJ10">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK10">
-        <v>1.04</v>
+        <v>5.1</v>
       </c>
       <c r="BL10">
         <v>1000</v>
       </c>
       <c r="BM10">
-        <v>1.04</v>
+        <v>10</v>
       </c>
       <c r="BN10">
-        <v>1000</v>
+        <v>5.4</v>
       </c>
       <c r="BO10">
-        <v>1.04</v>
+        <v>4</v>
       </c>
       <c r="BP10">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="BQ10">
-        <v>1.04</v>
+        <v>6.8</v>
       </c>
       <c r="BR10">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BS10">
-        <v>1.04</v>
+        <v>8</v>
       </c>
       <c r="BT10">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="BU10">
-        <v>1.04</v>
+        <v>4.9</v>
       </c>
       <c r="BV10">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="BW10">
-        <v>1.04</v>
+        <v>7.8</v>
       </c>
       <c r="BX10">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BY10">
-        <v>1.04</v>
+        <v>8.4</v>
       </c>
       <c r="BZ10">
         <v>0</v>
@@ -3175,19 +3175,19 @@
         <v>123</v>
       </c>
       <c r="F11">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="G11">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="H11">
-        <v>4.7</v>
+        <v>5.5</v>
       </c>
       <c r="I11">
         <v>6.4</v>
       </c>
       <c r="J11">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K11">
         <v>3.65</v>
@@ -3199,202 +3199,202 @@
         <v>1.1</v>
       </c>
       <c r="N11">
-        <v>2.88</v>
+        <v>2.96</v>
       </c>
       <c r="O11">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="P11">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="Q11">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="R11">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="S11">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="T11">
-        <v>1.11</v>
+        <v>2.1</v>
       </c>
       <c r="U11">
-        <v>1.11</v>
+        <v>1.79</v>
       </c>
       <c r="V11">
-        <v>1.01</v>
+        <v>1.2</v>
       </c>
       <c r="W11">
-        <v>1.01</v>
+        <v>2.14</v>
       </c>
       <c r="X11">
-        <v>970</v>
+        <v>10.5</v>
       </c>
       <c r="Y11">
-        <v>970</v>
+        <v>15.5</v>
       </c>
       <c r="Z11">
-        <v>120</v>
+        <v>46</v>
       </c>
       <c r="AA11">
         <v>900</v>
       </c>
       <c r="AB11">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="AC11">
-        <v>42</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD11">
-        <v>970</v>
+        <v>24</v>
       </c>
       <c r="AE11">
         <v>260</v>
       </c>
       <c r="AF11">
-        <v>970</v>
+        <v>10.5</v>
       </c>
       <c r="AG11">
         <v>9.199999999999999</v>
       </c>
       <c r="AH11">
-        <v>950</v>
+        <v>25</v>
       </c>
       <c r="AI11">
         <v>700</v>
       </c>
       <c r="AJ11">
-        <v>900</v>
+        <v>21</v>
       </c>
       <c r="AK11">
-        <v>100</v>
+        <v>24</v>
       </c>
       <c r="AL11">
-        <v>450</v>
+        <v>55</v>
       </c>
       <c r="AM11">
         <v>580</v>
       </c>
       <c r="AN11">
-        <v>970</v>
+        <v>18</v>
       </c>
       <c r="AO11">
         <v>700</v>
       </c>
       <c r="AP11">
-        <v>1.67</v>
+        <v>7.6</v>
       </c>
       <c r="AQ11">
-        <v>1.73</v>
+        <v>13</v>
       </c>
       <c r="AR11">
-        <v>1.83</v>
+        <v>32</v>
       </c>
       <c r="AS11">
-        <v>1.85</v>
+        <v>13</v>
       </c>
       <c r="AT11">
-        <v>1.86</v>
+        <v>6</v>
       </c>
       <c r="AU11">
-        <v>1.64</v>
+        <v>7</v>
       </c>
       <c r="AV11">
-        <v>1.78</v>
+        <v>20</v>
       </c>
       <c r="AW11">
-        <v>1.85</v>
+        <v>12.5</v>
       </c>
       <c r="AX11">
-        <v>5.1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY11">
-        <v>1.55</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ11">
-        <v>1.8</v>
+        <v>21</v>
       </c>
       <c r="BA11">
-        <v>1.85</v>
+        <v>12.5</v>
       </c>
       <c r="BB11">
-        <v>1.8</v>
+        <v>18</v>
       </c>
       <c r="BC11">
-        <v>1.81</v>
+        <v>21</v>
       </c>
       <c r="BD11">
-        <v>1.83</v>
+        <v>11</v>
       </c>
       <c r="BE11">
-        <v>1.85</v>
+        <v>13</v>
       </c>
       <c r="BF11">
-        <v>4.3</v>
+        <v>15</v>
       </c>
       <c r="BG11">
-        <v>1.85</v>
+        <v>13</v>
       </c>
       <c r="BH11">
-        <v>1000</v>
+        <v>2.96</v>
       </c>
       <c r="BI11">
-        <v>1.04</v>
+        <v>2.46</v>
       </c>
       <c r="BJ11">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BK11">
-        <v>1.04</v>
+        <v>6.6</v>
       </c>
       <c r="BL11">
         <v>1000</v>
       </c>
       <c r="BM11">
-        <v>1.04</v>
+        <v>14</v>
       </c>
       <c r="BN11">
-        <v>1000</v>
+        <v>4.2</v>
       </c>
       <c r="BO11">
-        <v>1.04</v>
+        <v>3.25</v>
       </c>
       <c r="BP11">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="BQ11">
-        <v>1.04</v>
+        <v>7</v>
       </c>
       <c r="BR11">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BS11">
-        <v>1.04</v>
+        <v>10.5</v>
       </c>
       <c r="BT11">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BU11">
-        <v>1.04</v>
+        <v>5.7</v>
       </c>
       <c r="BV11">
         <v>1000</v>
       </c>
       <c r="BW11">
-        <v>1.04</v>
+        <v>12</v>
       </c>
       <c r="BX11">
         <v>1000</v>
       </c>
       <c r="BY11">
-        <v>1.04</v>
+        <v>12.5</v>
       </c>
       <c r="BZ11">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="CA11">
-        <v>1.04</v>
+        <v>10</v>
       </c>
       <c r="CB11" t="s">
         <v>129</v>
@@ -3426,13 +3426,13 @@
         <v>1.47</v>
       </c>
       <c r="I12">
-        <v>2.04</v>
+        <v>1.59</v>
       </c>
       <c r="J12">
-        <v>2.7</v>
+        <v>3.25</v>
       </c>
       <c r="K12">
-        <v>44</v>
+        <v>19</v>
       </c>
       <c r="L12">
         <v>1.01</v>
@@ -3441,22 +3441,22 @@
         <v>1.01</v>
       </c>
       <c r="N12">
-        <v>1.1</v>
+        <v>1.26</v>
       </c>
       <c r="O12">
-        <v>1.09</v>
+        <v>1.41</v>
       </c>
       <c r="P12">
         <v>1.25</v>
       </c>
       <c r="Q12">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="R12">
         <v>1.18</v>
       </c>
       <c r="S12">
-        <v>1.05</v>
+        <v>1.99</v>
       </c>
       <c r="T12">
         <v>1.11</v>
@@ -3465,47 +3465,47 @@
         <v>1.11</v>
       </c>
       <c r="V12">
-        <v>1.01</v>
+        <v>2.58</v>
       </c>
       <c r="W12">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="X12">
         <v>16</v>
       </c>
       <c r="Y12">
-        <v>11</v>
+        <v>9.4</v>
       </c>
       <c r="Z12">
-        <v>13.5</v>
+        <v>10</v>
       </c>
       <c r="AA12">
+        <v>21</v>
+      </c>
+      <c r="AB12">
         <v>36</v>
       </c>
-      <c r="AB12">
-        <v>44</v>
-      </c>
       <c r="AC12">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AD12">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="AE12">
         <v>65</v>
       </c>
       <c r="AF12">
+        <v>380</v>
+      </c>
+      <c r="AG12">
+        <v>230</v>
+      </c>
+      <c r="AH12">
+        <v>270</v>
+      </c>
+      <c r="AI12">
         <v>570</v>
       </c>
-      <c r="AG12">
-        <v>330</v>
-      </c>
-      <c r="AH12">
-        <v>380</v>
-      </c>
-      <c r="AI12">
-        <v>770</v>
-      </c>
       <c r="AJ12">
         <v>1000</v>
       </c>
@@ -3522,7 +3522,7 @@
         <v>1000</v>
       </c>
       <c r="AO12">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="AP12">
         <v>3.9</v>
@@ -3531,16 +3531,16 @@
         <v>2.94</v>
       </c>
       <c r="AR12">
-        <v>1.47</v>
+        <v>1.62</v>
       </c>
       <c r="AS12">
         <v>9</v>
       </c>
       <c r="AT12">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="AU12">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="AV12">
         <v>8</v>
@@ -3549,31 +3549,31 @@
         <v>13.5</v>
       </c>
       <c r="AX12">
-        <v>24</v>
+        <v>1.92</v>
       </c>
       <c r="AY12">
-        <v>13.5</v>
+        <v>20</v>
       </c>
       <c r="AZ12">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="BA12">
         <v>34</v>
       </c>
       <c r="BB12">
-        <v>1.65</v>
+        <v>1.93</v>
       </c>
       <c r="BC12">
-        <v>1.65</v>
+        <v>1.93</v>
       </c>
       <c r="BD12">
-        <v>1.65</v>
+        <v>1.93</v>
       </c>
       <c r="BE12">
-        <v>1.65</v>
+        <v>1.93</v>
       </c>
       <c r="BF12">
-        <v>1.65</v>
+        <v>1.93</v>
       </c>
       <c r="BG12">
         <v>6.4</v>
@@ -3659,16 +3659,16 @@
         <v>125</v>
       </c>
       <c r="F13">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="G13">
         <v>2.52</v>
       </c>
       <c r="H13">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="I13">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="J13">
         <v>3.05</v>
@@ -3677,106 +3677,106 @@
         <v>3.15</v>
       </c>
       <c r="L13">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="M13">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="N13">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="O13">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="P13">
         <v>1.54</v>
       </c>
       <c r="Q13">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="R13">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="S13">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="T13">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="U13">
-        <v>1.72</v>
+        <v>1.78</v>
       </c>
       <c r="V13">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="W13">
-        <v>1.01</v>
+        <v>1.65</v>
       </c>
       <c r="X13">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="Y13">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z13">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AA13">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="AB13">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="AC13">
         <v>7.2</v>
       </c>
       <c r="AD13">
-        <v>19.5</v>
+        <v>17</v>
       </c>
       <c r="AE13">
-        <v>150</v>
+        <v>65</v>
       </c>
       <c r="AF13">
         <v>14</v>
       </c>
       <c r="AG13">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AH13">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AI13">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="AJ13">
+        <v>42</v>
+      </c>
+      <c r="AK13">
+        <v>40</v>
+      </c>
+      <c r="AL13">
+        <v>130</v>
+      </c>
+      <c r="AM13">
+        <v>990</v>
+      </c>
+      <c r="AN13">
         <v>44</v>
       </c>
-      <c r="AK13">
-        <v>42</v>
-      </c>
-      <c r="AL13">
-        <v>140</v>
-      </c>
-      <c r="AM13">
-        <v>1000</v>
-      </c>
-      <c r="AN13">
-        <v>46</v>
-      </c>
       <c r="AO13">
-        <v>220</v>
+        <v>85</v>
       </c>
       <c r="AP13">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AQ13">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AR13">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="AS13">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AT13">
         <v>6.8</v>
@@ -3788,97 +3788,97 @@
         <v>14.5</v>
       </c>
       <c r="AW13">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="AX13">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AY13">
         <v>11.5</v>
       </c>
       <c r="AZ13">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="BA13">
+        <v>70</v>
+      </c>
+      <c r="BB13">
+        <v>32</v>
+      </c>
+      <c r="BC13">
+        <v>30</v>
+      </c>
+      <c r="BD13">
+        <v>50</v>
+      </c>
+      <c r="BE13">
+        <v>75</v>
+      </c>
+      <c r="BF13">
+        <v>34</v>
+      </c>
+      <c r="BG13">
         <v>36</v>
       </c>
-      <c r="BB13">
-        <v>22</v>
-      </c>
-      <c r="BC13">
-        <v>22</v>
-      </c>
-      <c r="BD13">
-        <v>32</v>
-      </c>
-      <c r="BE13">
+      <c r="BH13">
+        <v>3.1</v>
+      </c>
+      <c r="BI13">
+        <v>2.24</v>
+      </c>
+      <c r="BJ13">
+        <v>11.5</v>
+      </c>
+      <c r="BK13">
+        <v>4.8</v>
+      </c>
+      <c r="BL13">
+        <v>1000</v>
+      </c>
+      <c r="BM13">
+        <v>8</v>
+      </c>
+      <c r="BN13">
+        <v>5.1</v>
+      </c>
+      <c r="BO13">
+        <v>3.95</v>
+      </c>
+      <c r="BP13">
+        <v>26</v>
+      </c>
+      <c r="BQ13">
+        <v>6.2</v>
+      </c>
+      <c r="BR13">
+        <v>55</v>
+      </c>
+      <c r="BS13">
+        <v>7</v>
+      </c>
+      <c r="BT13">
+        <v>6.6</v>
+      </c>
+      <c r="BU13">
+        <v>5</v>
+      </c>
+      <c r="BV13">
+        <v>42</v>
+      </c>
+      <c r="BW13">
+        <v>6.8</v>
+      </c>
+      <c r="BX13">
         <v>70</v>
       </c>
-      <c r="BF13">
-        <v>22</v>
-      </c>
-      <c r="BG13">
-        <v>34</v>
-      </c>
-      <c r="BH13">
-        <v>1000</v>
-      </c>
-      <c r="BI13">
-        <v>1.04</v>
-      </c>
-      <c r="BJ13">
-        <v>1000</v>
-      </c>
-      <c r="BK13">
-        <v>1.04</v>
-      </c>
-      <c r="BL13">
-        <v>1000</v>
-      </c>
-      <c r="BM13">
-        <v>1.04</v>
-      </c>
-      <c r="BN13">
-        <v>1000</v>
-      </c>
-      <c r="BO13">
-        <v>1.04</v>
-      </c>
-      <c r="BP13">
-        <v>1000</v>
-      </c>
-      <c r="BQ13">
-        <v>1.04</v>
-      </c>
-      <c r="BR13">
-        <v>1000</v>
-      </c>
-      <c r="BS13">
-        <v>1.04</v>
-      </c>
-      <c r="BT13">
-        <v>1000</v>
-      </c>
-      <c r="BU13">
-        <v>1.04</v>
-      </c>
-      <c r="BV13">
-        <v>1000</v>
-      </c>
-      <c r="BW13">
-        <v>1.04</v>
-      </c>
-      <c r="BX13">
-        <v>1000</v>
-      </c>
       <c r="BY13">
-        <v>1.04</v>
+        <v>7.2</v>
       </c>
       <c r="BZ13">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="CA13">
-        <v>1.04</v>
+        <v>7.2</v>
       </c>
       <c r="CB13" t="s">
         <v>129</v>
@@ -3901,226 +3901,226 @@
         <v>126</v>
       </c>
       <c r="F14">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="G14">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="H14">
         <v>4.4</v>
       </c>
       <c r="I14">
-        <v>5.9</v>
+        <v>5.4</v>
       </c>
       <c r="J14">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="K14">
-        <v>3.95</v>
+        <v>3.75</v>
       </c>
       <c r="L14">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="M14">
         <v>1.09</v>
       </c>
       <c r="N14">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="O14">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="P14">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="Q14">
-        <v>2.16</v>
+        <v>2.22</v>
       </c>
       <c r="R14">
         <v>1.27</v>
       </c>
       <c r="S14">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="T14">
-        <v>1.11</v>
+        <v>1.96</v>
       </c>
       <c r="U14">
-        <v>1.11</v>
+        <v>1.83</v>
       </c>
       <c r="V14">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="W14">
-        <v>1.01</v>
+        <v>1.99</v>
       </c>
       <c r="X14">
-        <v>500</v>
+        <v>14.5</v>
       </c>
       <c r="Y14">
-        <v>970</v>
+        <v>15</v>
       </c>
       <c r="Z14">
-        <v>500</v>
+        <v>38</v>
       </c>
       <c r="AA14">
         <v>900</v>
       </c>
       <c r="AB14">
-        <v>970</v>
+        <v>7.8</v>
       </c>
       <c r="AC14">
-        <v>42</v>
+        <v>8.6</v>
       </c>
       <c r="AD14">
-        <v>950</v>
+        <v>21</v>
       </c>
       <c r="AE14">
-        <v>500</v>
+        <v>90</v>
       </c>
       <c r="AF14">
-        <v>970</v>
+        <v>11.5</v>
       </c>
       <c r="AG14">
-        <v>500</v>
+        <v>11</v>
       </c>
       <c r="AH14">
-        <v>950</v>
+        <v>27</v>
       </c>
       <c r="AI14">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="AJ14">
-        <v>500</v>
+        <v>23</v>
       </c>
       <c r="AK14">
-        <v>500</v>
+        <v>24</v>
       </c>
       <c r="AL14">
-        <v>500</v>
+        <v>55</v>
       </c>
       <c r="AM14">
         <v>580</v>
       </c>
       <c r="AN14">
-        <v>65</v>
+        <v>18</v>
       </c>
       <c r="AO14">
-        <v>300</v>
+        <v>130</v>
       </c>
       <c r="AP14">
-        <v>2.5</v>
+        <v>5.6</v>
       </c>
       <c r="AQ14">
-        <v>1.75</v>
+        <v>5</v>
       </c>
       <c r="AR14">
-        <v>1.85</v>
+        <v>6.2</v>
       </c>
       <c r="AS14">
-        <v>1.88</v>
+        <v>7.2</v>
       </c>
       <c r="AT14">
-        <v>4.2</v>
+        <v>6.4</v>
       </c>
       <c r="AU14">
         <v>4.4</v>
       </c>
       <c r="AV14">
-        <v>1.81</v>
+        <v>5.5</v>
       </c>
       <c r="AW14">
-        <v>1.87</v>
+        <v>7</v>
       </c>
       <c r="AX14">
+        <v>5.6</v>
+      </c>
+      <c r="AY14">
+        <v>7.8</v>
+      </c>
+      <c r="AZ14">
+        <v>5.9</v>
+      </c>
+      <c r="BA14">
+        <v>7</v>
+      </c>
+      <c r="BB14">
+        <v>5.7</v>
+      </c>
+      <c r="BC14">
+        <v>5.7</v>
+      </c>
+      <c r="BD14">
+        <v>6.6</v>
+      </c>
+      <c r="BE14">
+        <v>7.2</v>
+      </c>
+      <c r="BF14">
+        <v>5.3</v>
+      </c>
+      <c r="BG14">
+        <v>7.2</v>
+      </c>
+      <c r="BH14">
+        <v>3.55</v>
+      </c>
+      <c r="BI14">
         <v>2.5</v>
       </c>
-      <c r="AY14">
-        <v>1.71</v>
-      </c>
-      <c r="AZ14">
-        <v>1.82</v>
-      </c>
-      <c r="BA14">
-        <v>1.87</v>
-      </c>
-      <c r="BB14">
-        <v>1.84</v>
-      </c>
-      <c r="BC14">
-        <v>1.83</v>
-      </c>
-      <c r="BD14">
-        <v>1.86</v>
-      </c>
-      <c r="BE14">
-        <v>1.88</v>
-      </c>
-      <c r="BF14">
+      <c r="BJ14">
+        <v>13</v>
+      </c>
+      <c r="BK14">
+        <v>3.6</v>
+      </c>
+      <c r="BL14">
+        <v>1000</v>
+      </c>
+      <c r="BM14">
+        <v>4.9</v>
+      </c>
+      <c r="BN14">
+        <v>5.2</v>
+      </c>
+      <c r="BO14">
+        <v>2.56</v>
+      </c>
+      <c r="BP14">
+        <v>17</v>
+      </c>
+      <c r="BQ14">
+        <v>3.9</v>
+      </c>
+      <c r="BR14">
+        <v>40</v>
+      </c>
+      <c r="BS14">
         <v>4.4</v>
       </c>
-      <c r="BG14">
-        <v>1.87</v>
-      </c>
-      <c r="BH14">
-        <v>1000</v>
-      </c>
-      <c r="BI14">
-        <v>1.04</v>
-      </c>
-      <c r="BJ14">
-        <v>1000</v>
-      </c>
-      <c r="BK14">
-        <v>1.04</v>
-      </c>
-      <c r="BL14">
-        <v>1000</v>
-      </c>
-      <c r="BM14">
-        <v>1.04</v>
-      </c>
-      <c r="BN14">
-        <v>1000</v>
-      </c>
-      <c r="BO14">
-        <v>1.04</v>
-      </c>
-      <c r="BP14">
-        <v>1000</v>
-      </c>
-      <c r="BQ14">
-        <v>1.04</v>
-      </c>
-      <c r="BR14">
-        <v>1000</v>
-      </c>
-      <c r="BS14">
-        <v>1.04</v>
-      </c>
       <c r="BT14">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="BU14">
-        <v>1.04</v>
+        <v>3.3</v>
       </c>
       <c r="BV14">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BW14">
-        <v>1.04</v>
+        <v>4.6</v>
       </c>
       <c r="BX14">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="BY14">
-        <v>1.04</v>
+        <v>4.7</v>
       </c>
       <c r="BZ14">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="CA14">
-        <v>1.04</v>
+        <v>4.4</v>
       </c>
       <c r="CB14" t="s">
         <v>129</v>
@@ -4143,7 +4143,7 @@
         <v>127</v>
       </c>
       <c r="F15">
-        <v>1.2</v>
+        <v>1.04</v>
       </c>
       <c r="G15">
         <v>600</v>
@@ -4155,7 +4155,7 @@
         <v>870</v>
       </c>
       <c r="J15">
-        <v>1.2</v>
+        <v>1.01</v>
       </c>
       <c r="K15">
         <v>950</v>
@@ -4164,10 +4164,10 @@
         <v>1.28</v>
       </c>
       <c r="M15">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="N15">
-        <v>1.36</v>
+        <v>1.02</v>
       </c>
       <c r="O15">
         <v>1.01</v>
@@ -4385,220 +4385,220 @@
         <v>128</v>
       </c>
       <c r="F16">
-        <v>3.3</v>
+        <v>2.92</v>
       </c>
       <c r="G16">
-        <v>3.7</v>
+        <v>3.35</v>
       </c>
       <c r="H16">
-        <v>2.08</v>
+        <v>2.38</v>
       </c>
       <c r="I16">
-        <v>2.24</v>
+        <v>2.62</v>
       </c>
       <c r="J16">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="K16">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="L16">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="M16">
         <v>1.04</v>
       </c>
       <c r="N16">
+        <v>5.2</v>
+      </c>
+      <c r="O16">
+        <v>1.19</v>
+      </c>
+      <c r="P16">
+        <v>2.42</v>
+      </c>
+      <c r="Q16">
+        <v>1.62</v>
+      </c>
+      <c r="R16">
+        <v>1.57</v>
+      </c>
+      <c r="S16">
+        <v>2.48</v>
+      </c>
+      <c r="T16">
+        <v>1.49</v>
+      </c>
+      <c r="U16">
+        <v>2.56</v>
+      </c>
+      <c r="V16">
+        <v>1.62</v>
+      </c>
+      <c r="W16">
+        <v>1.43</v>
+      </c>
+      <c r="X16">
+        <v>28</v>
+      </c>
+      <c r="Y16">
+        <v>18</v>
+      </c>
+      <c r="Z16">
+        <v>21</v>
+      </c>
+      <c r="AA16">
+        <v>36</v>
+      </c>
+      <c r="AB16">
+        <v>22</v>
+      </c>
+      <c r="AC16">
+        <v>10</v>
+      </c>
+      <c r="AD16">
+        <v>13</v>
+      </c>
+      <c r="AE16">
+        <v>25</v>
+      </c>
+      <c r="AF16">
+        <v>27</v>
+      </c>
+      <c r="AG16">
+        <v>15</v>
+      </c>
+      <c r="AH16">
+        <v>15</v>
+      </c>
+      <c r="AI16">
+        <v>32</v>
+      </c>
+      <c r="AJ16">
+        <v>60</v>
+      </c>
+      <c r="AK16">
+        <v>29</v>
+      </c>
+      <c r="AL16">
+        <v>34</v>
+      </c>
+      <c r="AM16">
+        <v>70</v>
+      </c>
+      <c r="AN16">
+        <v>18.5</v>
+      </c>
+      <c r="AO16">
+        <v>14</v>
+      </c>
+      <c r="AP16">
+        <v>5.5</v>
+      </c>
+      <c r="AQ16">
         <v>4.9</v>
       </c>
-      <c r="O16">
-        <v>1.21</v>
-      </c>
-      <c r="P16">
-        <v>2.34</v>
-      </c>
-      <c r="Q16">
-        <v>1.66</v>
-      </c>
-      <c r="R16">
-        <v>1.53</v>
-      </c>
-      <c r="S16">
-        <v>2.66</v>
-      </c>
-      <c r="T16">
-        <v>1.56</v>
-      </c>
-      <c r="U16">
-        <v>1.11</v>
-      </c>
-      <c r="V16">
-        <v>1.01</v>
-      </c>
-      <c r="W16">
-        <v>1.01</v>
-      </c>
-      <c r="X16">
-        <v>1000</v>
-      </c>
-      <c r="Y16">
-        <v>1000</v>
-      </c>
-      <c r="Z16">
-        <v>1000</v>
-      </c>
-      <c r="AA16">
-        <v>1000</v>
-      </c>
-      <c r="AB16">
-        <v>1000</v>
-      </c>
-      <c r="AC16">
-        <v>1000</v>
-      </c>
-      <c r="AD16">
-        <v>1000</v>
-      </c>
-      <c r="AE16">
-        <v>1000</v>
-      </c>
-      <c r="AF16">
-        <v>1000</v>
-      </c>
-      <c r="AG16">
-        <v>1000</v>
-      </c>
-      <c r="AH16">
-        <v>1000</v>
-      </c>
-      <c r="AI16">
-        <v>1000</v>
-      </c>
-      <c r="AJ16">
-        <v>1000</v>
-      </c>
-      <c r="AK16">
-        <v>1000</v>
-      </c>
-      <c r="AL16">
-        <v>1000</v>
-      </c>
-      <c r="AM16">
-        <v>1000</v>
-      </c>
-      <c r="AN16">
-        <v>1000</v>
-      </c>
-      <c r="AO16">
-        <v>1000</v>
-      </c>
-      <c r="AP16">
-        <v>1.01</v>
-      </c>
-      <c r="AQ16">
-        <v>1.01</v>
-      </c>
       <c r="AR16">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="AS16">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="AT16">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="AU16">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AV16">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AW16">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="AX16">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="AY16">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AZ16">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BA16">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BB16">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="BC16">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BD16">
-        <v>1.01</v>
+        <v>19.5</v>
       </c>
       <c r="BE16">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF16">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BG16">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BH16">
-        <v>1000</v>
+        <v>5.1</v>
       </c>
       <c r="BI16">
-        <v>1.04</v>
+        <v>2.56</v>
       </c>
       <c r="BJ16">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BK16">
-        <v>1.04</v>
+        <v>3.45</v>
       </c>
       <c r="BL16">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="BM16">
-        <v>1.04</v>
+        <v>4.8</v>
       </c>
       <c r="BN16">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="BO16">
-        <v>1.04</v>
+        <v>2.96</v>
       </c>
       <c r="BP16">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="BQ16">
-        <v>1.04</v>
+        <v>4.1</v>
       </c>
       <c r="BR16">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BS16">
-        <v>1.04</v>
+        <v>4.4</v>
       </c>
       <c r="BT16">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="BU16">
-        <v>1.04</v>
+        <v>3.9</v>
       </c>
       <c r="BV16">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="BW16">
-        <v>1.04</v>
+        <v>4</v>
       </c>
       <c r="BX16">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="BY16">
-        <v>1.04</v>
+        <v>4.3</v>
       </c>
       <c r="BZ16">
         <v>0</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-06.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-06.xlsx
@@ -403,7 +403,7 @@
     <t>Always Ready</t>
   </si>
   <si>
-    <t>2026-08-06 03:47:07</t>
+    <t>2026-08-06 05:55:28</t>
   </si>
 </sst>
 </file>
@@ -997,139 +997,139 @@
         <v>114</v>
       </c>
       <c r="F2">
-        <v>2.02</v>
+        <v>1.9</v>
       </c>
       <c r="G2">
-        <v>2.12</v>
+        <v>1.95</v>
       </c>
       <c r="H2">
-        <v>3.55</v>
+        <v>3.9</v>
       </c>
       <c r="I2">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="J2">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="K2">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="L2">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="M2">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N2">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
       <c r="O2">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="P2">
-        <v>2.3</v>
+        <v>2.52</v>
       </c>
       <c r="Q2">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="R2">
-        <v>1.5</v>
+        <v>1.61</v>
       </c>
       <c r="S2">
-        <v>2.66</v>
+        <v>2.56</v>
       </c>
       <c r="T2">
         <v>1.65</v>
       </c>
       <c r="U2">
-        <v>2.34</v>
+        <v>2.46</v>
       </c>
       <c r="V2">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="W2">
-        <v>1.89</v>
+        <v>2.04</v>
       </c>
       <c r="X2">
         <v>21</v>
       </c>
       <c r="Y2">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Z2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AA2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AB2">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AC2">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AD2">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AE2">
         <v>42</v>
       </c>
       <c r="AF2">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="AG2">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH2">
         <v>17</v>
       </c>
       <c r="AI2">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AJ2">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AK2">
+        <v>18</v>
+      </c>
+      <c r="AL2">
+        <v>27</v>
+      </c>
+      <c r="AM2">
+        <v>70</v>
+      </c>
+      <c r="AN2">
+        <v>9.4</v>
+      </c>
+      <c r="AO2">
+        <v>32</v>
+      </c>
+      <c r="AP2">
         <v>20</v>
       </c>
-      <c r="AL2">
-        <v>29</v>
-      </c>
-      <c r="AM2">
-        <v>75</v>
-      </c>
-      <c r="AN2">
-        <v>11.5</v>
-      </c>
-      <c r="AO2">
-        <v>34</v>
-      </c>
-      <c r="AP2">
-        <v>14.5</v>
-      </c>
       <c r="AQ2">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AR2">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="AS2">
-        <v>20</v>
+        <v>55</v>
       </c>
       <c r="AT2">
         <v>10.5</v>
       </c>
       <c r="AU2">
-        <v>4.9</v>
+        <v>8.4</v>
       </c>
       <c r="AV2">
-        <v>7.6</v>
+        <v>14</v>
       </c>
       <c r="AW2">
-        <v>7.8</v>
+        <v>29</v>
       </c>
       <c r="AX2">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AY2">
         <v>9.199999999999999</v>
@@ -1141,67 +1141,67 @@
         <v>36</v>
       </c>
       <c r="BB2">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="BC2">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BD2">
         <v>24</v>
       </c>
       <c r="BE2">
-        <v>9</v>
+        <v>55</v>
       </c>
       <c r="BF2">
-        <v>9.6</v>
+        <v>8</v>
       </c>
       <c r="BG2">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="BH2">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="BI2">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="BJ2">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BK2">
         <v>1.01</v>
       </c>
       <c r="BL2">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="BM2">
         <v>1.01</v>
       </c>
       <c r="BN2">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="BO2">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BP2">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="BQ2">
         <v>1.01</v>
       </c>
       <c r="BR2">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="BS2">
         <v>1.01</v>
       </c>
       <c r="BT2">
-        <v>7.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BU2">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BV2">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="BW2">
         <v>1.01</v>
@@ -1239,67 +1239,67 @@
         <v>115</v>
       </c>
       <c r="F3">
-        <v>1.84</v>
+        <v>1.72</v>
       </c>
       <c r="G3">
-        <v>1.93</v>
+        <v>1.81</v>
       </c>
       <c r="H3">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="I3">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="J3">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="K3">
-        <v>3.55</v>
+        <v>3.8</v>
       </c>
       <c r="L3">
-        <v>1.59</v>
+        <v>1.54</v>
       </c>
       <c r="M3">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="N3">
-        <v>2.62</v>
+        <v>2.8</v>
       </c>
       <c r="O3">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="P3">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="Q3">
-        <v>2.68</v>
+        <v>2.48</v>
       </c>
       <c r="R3">
+        <v>1.21</v>
+      </c>
+      <c r="S3">
+        <v>5.1</v>
+      </c>
+      <c r="T3">
+        <v>2.26</v>
+      </c>
+      <c r="U3">
+        <v>1.68</v>
+      </c>
+      <c r="V3">
         <v>1.18</v>
       </c>
-      <c r="S3">
-        <v>5.5</v>
-      </c>
-      <c r="T3">
-        <v>2.24</v>
-      </c>
-      <c r="U3">
-        <v>1.69</v>
-      </c>
-      <c r="V3">
-        <v>1.2</v>
-      </c>
       <c r="W3">
-        <v>2.08</v>
+        <v>2.22</v>
       </c>
       <c r="X3">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="Y3">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="Z3">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="AA3">
         <v>900</v>
@@ -1308,19 +1308,19 @@
         <v>6.4</v>
       </c>
       <c r="AC3">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AD3">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AE3">
-        <v>140</v>
+        <v>260</v>
       </c>
       <c r="AF3">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="AG3">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AH3">
         <v>29</v>
@@ -1329,130 +1329,130 @@
         <v>700</v>
       </c>
       <c r="AJ3">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="AK3">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AL3">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AM3">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN3">
-        <v>24</v>
+        <v>18.5</v>
       </c>
       <c r="AO3">
         <v>700</v>
       </c>
       <c r="AP3">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="AQ3">
-        <v>10.5</v>
+        <v>13</v>
       </c>
       <c r="AR3">
         <v>32</v>
       </c>
       <c r="AS3">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AT3">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="AU3">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AV3">
         <v>20</v>
       </c>
       <c r="AW3">
-        <v>11</v>
+        <v>55</v>
       </c>
       <c r="AX3">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="AY3">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ3">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="BA3">
-        <v>11</v>
+        <v>60</v>
       </c>
       <c r="BB3">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BC3">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BD3">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="BE3">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BF3">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="BG3">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BH3">
-        <v>2.98</v>
+        <v>3.15</v>
       </c>
       <c r="BI3">
-        <v>2.28</v>
+        <v>2.4</v>
       </c>
       <c r="BJ3">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BK3">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="BN3">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="BO3">
         <v>3.4</v>
       </c>
       <c r="BP3">
-        <v>17.5</v>
+        <v>15</v>
       </c>
       <c r="BQ3">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BR3">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="BS3">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="BT3">
         <v>10</v>
       </c>
       <c r="BU3">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="BV3">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="BW3">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="BX3">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="BY3">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="BZ3">
         <v>0</v>
@@ -1481,19 +1481,19 @@
         <v>116</v>
       </c>
       <c r="F4">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="G4">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="H4">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="I4">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="J4">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="K4">
         <v>5.9</v>
@@ -1505,34 +1505,34 @@
         <v>1.01</v>
       </c>
       <c r="N4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O4">
         <v>1.11</v>
       </c>
       <c r="P4">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="Q4">
         <v>1.33</v>
       </c>
       <c r="R4">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="S4">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="T4">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="U4">
         <v>2.8</v>
       </c>
       <c r="V4">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="W4">
-        <v>2.64</v>
+        <v>2.74</v>
       </c>
       <c r="X4">
         <v>55</v>
@@ -1547,7 +1547,7 @@
         <v>700</v>
       </c>
       <c r="AB4">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AC4">
         <v>16</v>
@@ -1559,7 +1559,7 @@
         <v>70</v>
       </c>
       <c r="AF4">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AG4">
         <v>12.5</v>
@@ -1571,37 +1571,37 @@
         <v>50</v>
       </c>
       <c r="AJ4">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AK4">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AL4">
         <v>23</v>
       </c>
       <c r="AM4">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AN4">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="AO4">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AP4">
         <v>36</v>
       </c>
       <c r="AQ4">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="AR4">
-        <v>23</v>
+        <v>50</v>
       </c>
       <c r="AS4">
-        <v>7.6</v>
+        <v>29</v>
       </c>
       <c r="AT4">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AU4">
         <v>12.5</v>
@@ -1610,7 +1610,7 @@
         <v>20</v>
       </c>
       <c r="AW4">
-        <v>7.2</v>
+        <v>42</v>
       </c>
       <c r="AX4">
         <v>14</v>
@@ -1622,10 +1622,10 @@
         <v>14.5</v>
       </c>
       <c r="BA4">
-        <v>6.8</v>
+        <v>27</v>
       </c>
       <c r="BB4">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BC4">
         <v>12.5</v>
@@ -1634,73 +1634,73 @@
         <v>18</v>
       </c>
       <c r="BE4">
+        <v>38</v>
+      </c>
+      <c r="BF4">
+        <v>3.65</v>
+      </c>
+      <c r="BG4">
+        <v>25</v>
+      </c>
+      <c r="BH4">
         <v>7</v>
       </c>
-      <c r="BF4">
-        <v>3.75</v>
-      </c>
-      <c r="BG4">
-        <v>6.4</v>
-      </c>
-      <c r="BH4">
-        <v>6.8</v>
-      </c>
       <c r="BI4">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BJ4">
         <v>10.5</v>
       </c>
       <c r="BK4">
-        <v>3.6</v>
+        <v>3.85</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="BN4">
         <v>5.8</v>
       </c>
       <c r="BO4">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="BP4">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BQ4">
-        <v>3.65</v>
+        <v>3.85</v>
       </c>
       <c r="BR4">
-        <v>18.5</v>
+        <v>16.5</v>
       </c>
       <c r="BS4">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="BT4">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BU4">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="BV4">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BW4">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="BX4">
         <v>36</v>
       </c>
       <c r="BY4">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="BZ4">
-        <v>9.6</v>
+        <v>8.4</v>
       </c>
       <c r="CA4">
-        <v>3.5</v>
+        <v>6.4</v>
       </c>
       <c r="CB4" t="s">
         <v>129</v>
@@ -1723,106 +1723,106 @@
         <v>117</v>
       </c>
       <c r="F5">
-        <v>2.7</v>
+        <v>2.78</v>
       </c>
       <c r="G5">
-        <v>2.88</v>
+        <v>3.05</v>
       </c>
       <c r="H5">
-        <v>2.82</v>
+        <v>2.92</v>
       </c>
       <c r="I5">
         <v>3.2</v>
       </c>
       <c r="J5">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="K5">
-        <v>3.45</v>
+        <v>3.2</v>
       </c>
       <c r="L5">
         <v>1.45</v>
       </c>
       <c r="M5">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N5">
         <v>3.35</v>
       </c>
       <c r="O5">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="P5">
         <v>1.78</v>
       </c>
       <c r="Q5">
+        <v>2.16</v>
+      </c>
+      <c r="R5">
+        <v>1.31</v>
+      </c>
+      <c r="S5">
+        <v>3.95</v>
+      </c>
+      <c r="T5">
+        <v>1.81</v>
+      </c>
+      <c r="U5">
         <v>2.12</v>
       </c>
-      <c r="R5">
-        <v>1.29</v>
-      </c>
-      <c r="S5">
-        <v>3.85</v>
-      </c>
-      <c r="T5">
-        <v>1.8</v>
-      </c>
-      <c r="U5">
-        <v>2.02</v>
-      </c>
       <c r="V5">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="W5">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="X5">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="Y5">
         <v>11.5</v>
       </c>
       <c r="Z5">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="AA5">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AB5">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AC5">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="AD5">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AE5">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AF5">
         <v>19</v>
       </c>
       <c r="AG5">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AH5">
-        <v>22</v>
+        <v>17.5</v>
       </c>
       <c r="AI5">
         <v>60</v>
       </c>
       <c r="AJ5">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="AK5">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AL5">
         <v>60</v>
       </c>
       <c r="AM5">
-        <v>450</v>
+        <v>130</v>
       </c>
       <c r="AN5">
         <v>38</v>
@@ -1831,118 +1831,118 @@
         <v>42</v>
       </c>
       <c r="AP5">
-        <v>6.2</v>
+        <v>9.6</v>
       </c>
       <c r="AQ5">
-        <v>6.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR5">
-        <v>4.1</v>
+        <v>16</v>
       </c>
       <c r="AS5">
-        <v>4.6</v>
+        <v>38</v>
       </c>
       <c r="AT5">
         <v>8.800000000000001</v>
       </c>
       <c r="AU5">
-        <v>4.4</v>
+        <v>6.2</v>
       </c>
       <c r="AV5">
-        <v>3.8</v>
+        <v>11</v>
       </c>
       <c r="AW5">
-        <v>4.5</v>
+        <v>25</v>
       </c>
       <c r="AX5">
-        <v>3.95</v>
+        <v>15</v>
       </c>
       <c r="AY5">
-        <v>6.4</v>
+        <v>10.5</v>
       </c>
       <c r="AZ5">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="BA5">
-        <v>4.6</v>
+        <v>29</v>
       </c>
       <c r="BB5">
-        <v>4.6</v>
+        <v>29</v>
       </c>
       <c r="BC5">
-        <v>4.4</v>
+        <v>16</v>
       </c>
       <c r="BD5">
-        <v>4.6</v>
+        <v>24</v>
       </c>
       <c r="BE5">
-        <v>4.8</v>
+        <v>70</v>
       </c>
       <c r="BF5">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="BG5">
-        <v>4.5</v>
+        <v>15</v>
       </c>
       <c r="BH5">
         <v>3.65</v>
       </c>
       <c r="BI5">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="BJ5">
         <v>12</v>
       </c>
       <c r="BK5">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="BL5">
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BN5">
         <v>6.8</v>
       </c>
       <c r="BO5">
-        <v>2.92</v>
+        <v>4.8</v>
       </c>
       <c r="BP5">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="BQ5">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BR5">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="BS5">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BT5">
         <v>7</v>
       </c>
       <c r="BU5">
-        <v>2.96</v>
+        <v>5.1</v>
       </c>
       <c r="BV5">
         <v>29</v>
       </c>
       <c r="BW5">
+        <v>4.2</v>
+      </c>
+      <c r="BX5">
+        <v>48</v>
+      </c>
+      <c r="BY5">
+        <v>4.5</v>
+      </c>
+      <c r="BZ5">
+        <v>36</v>
+      </c>
+      <c r="CA5">
         <v>4.3</v>
-      </c>
-      <c r="BX5">
-        <v>46</v>
-      </c>
-      <c r="BY5">
-        <v>4.6</v>
-      </c>
-      <c r="BZ5">
-        <v>34</v>
-      </c>
-      <c r="CA5">
-        <v>4.4</v>
       </c>
       <c r="CB5" t="s">
         <v>129</v>
@@ -1971,7 +1971,7 @@
         <v>2.36</v>
       </c>
       <c r="H6">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="I6">
         <v>3.75</v>
@@ -1983,43 +1983,43 @@
         <v>3.5</v>
       </c>
       <c r="L6">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="M6">
         <v>1.07</v>
       </c>
       <c r="N6">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="O6">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="P6">
         <v>1.96</v>
       </c>
       <c r="Q6">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="R6">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="S6">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="T6">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="U6">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="V6">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W6">
         <v>1.73</v>
       </c>
       <c r="X6">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="Y6">
         <v>14.5</v>
@@ -2031,10 +2031,10 @@
         <v>75</v>
       </c>
       <c r="AB6">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AC6">
-        <v>9.6</v>
+        <v>7.8</v>
       </c>
       <c r="AD6">
         <v>15.5</v>
@@ -2043,13 +2043,13 @@
         <v>50</v>
       </c>
       <c r="AF6">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AG6">
         <v>13.5</v>
       </c>
       <c r="AH6">
-        <v>21</v>
+        <v>17.5</v>
       </c>
       <c r="AI6">
         <v>60</v>
@@ -2061,7 +2061,7 @@
         <v>30</v>
       </c>
       <c r="AL6">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AM6">
         <v>110</v>
@@ -2073,7 +2073,7 @@
         <v>46</v>
       </c>
       <c r="AP6">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AQ6">
         <v>12</v>
@@ -2082,7 +2082,7 @@
         <v>21</v>
       </c>
       <c r="AS6">
-        <v>5.1</v>
+        <v>46</v>
       </c>
       <c r="AT6">
         <v>9.199999999999999</v>
@@ -2094,7 +2094,7 @@
         <v>13</v>
       </c>
       <c r="AW6">
-        <v>4.9</v>
+        <v>29</v>
       </c>
       <c r="AX6">
         <v>13</v>
@@ -2106,31 +2106,31 @@
         <v>14.5</v>
       </c>
       <c r="BA6">
-        <v>5</v>
+        <v>36</v>
       </c>
       <c r="BB6">
-        <v>14.5</v>
+        <v>22</v>
       </c>
       <c r="BC6">
         <v>21</v>
       </c>
       <c r="BD6">
-        <v>4.8</v>
+        <v>29</v>
       </c>
       <c r="BE6">
-        <v>5.2</v>
+        <v>65</v>
       </c>
       <c r="BF6">
         <v>16</v>
       </c>
       <c r="BG6">
-        <v>6.8</v>
+        <v>26</v>
       </c>
       <c r="BH6">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BI6">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="BJ6">
         <v>11.5</v>
@@ -2157,7 +2157,7 @@
         <v>1.01</v>
       </c>
       <c r="BR6">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BS6">
         <v>1.01</v>
@@ -2166,10 +2166,10 @@
         <v>7.8</v>
       </c>
       <c r="BU6">
-        <v>5</v>
+        <v>5.8</v>
       </c>
       <c r="BV6">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BW6">
         <v>1.01</v>
@@ -2207,196 +2207,196 @@
         <v>119</v>
       </c>
       <c r="F7">
-        <v>2.6</v>
+        <v>2.18</v>
       </c>
       <c r="G7">
-        <v>2.88</v>
+        <v>2.3</v>
       </c>
       <c r="H7">
-        <v>2.72</v>
+        <v>3.35</v>
       </c>
       <c r="I7">
-        <v>2.98</v>
+        <v>3.7</v>
       </c>
       <c r="J7">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="K7">
         <v>3.7</v>
       </c>
       <c r="L7">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="M7">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N7">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="O7">
         <v>1.33</v>
       </c>
       <c r="P7">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="Q7">
         <v>2</v>
       </c>
       <c r="R7">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="S7">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="T7">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="U7">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="V7">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="W7">
-        <v>1.53</v>
+        <v>1.76</v>
       </c>
       <c r="X7">
+        <v>15</v>
+      </c>
+      <c r="Y7">
+        <v>13.5</v>
+      </c>
+      <c r="Z7">
+        <v>25</v>
+      </c>
+      <c r="AA7">
+        <v>70</v>
+      </c>
+      <c r="AB7">
+        <v>10</v>
+      </c>
+      <c r="AC7">
+        <v>8.4</v>
+      </c>
+      <c r="AD7">
         <v>14.5</v>
       </c>
-      <c r="Y7">
-        <v>12</v>
-      </c>
-      <c r="Z7">
-        <v>20</v>
-      </c>
-      <c r="AA7">
-        <v>120</v>
-      </c>
-      <c r="AB7">
-        <v>11.5</v>
-      </c>
-      <c r="AC7">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AD7">
-        <v>13.5</v>
-      </c>
       <c r="AE7">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AF7">
+        <v>15</v>
+      </c>
+      <c r="AG7">
+        <v>11</v>
+      </c>
+      <c r="AH7">
         <v>19</v>
       </c>
-      <c r="AG7">
-        <v>13</v>
-      </c>
-      <c r="AH7">
-        <v>18</v>
-      </c>
       <c r="AI7">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AJ7">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="AK7">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="AL7">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="AM7">
         <v>580</v>
       </c>
       <c r="AN7">
-        <v>46</v>
+        <v>20</v>
       </c>
       <c r="AO7">
+        <v>44</v>
+      </c>
+      <c r="AP7">
+        <v>11.5</v>
+      </c>
+      <c r="AQ7">
+        <v>11</v>
+      </c>
+      <c r="AR7">
+        <v>20</v>
+      </c>
+      <c r="AS7">
+        <v>44</v>
+      </c>
+      <c r="AT7">
+        <v>8.6</v>
+      </c>
+      <c r="AU7">
+        <v>7.2</v>
+      </c>
+      <c r="AV7">
+        <v>13</v>
+      </c>
+      <c r="AW7">
+        <v>34</v>
+      </c>
+      <c r="AX7">
+        <v>12.5</v>
+      </c>
+      <c r="AY7">
+        <v>9.6</v>
+      </c>
+      <c r="AZ7">
+        <v>16</v>
+      </c>
+      <c r="BA7">
+        <v>42</v>
+      </c>
+      <c r="BB7">
+        <v>25</v>
+      </c>
+      <c r="BC7">
+        <v>21</v>
+      </c>
+      <c r="BD7">
         <v>32</v>
       </c>
-      <c r="AP7">
-        <v>5.6</v>
-      </c>
-      <c r="AQ7">
-        <v>6.2</v>
-      </c>
-      <c r="AR7">
-        <v>6.2</v>
-      </c>
-      <c r="AS7">
-        <v>7.6</v>
-      </c>
-      <c r="AT7">
-        <v>5.8</v>
-      </c>
-      <c r="AU7">
-        <v>4.4</v>
-      </c>
-      <c r="AV7">
-        <v>5.4</v>
-      </c>
-      <c r="AW7">
-        <v>7.2</v>
-      </c>
-      <c r="AX7">
-        <v>6</v>
-      </c>
-      <c r="AY7">
-        <v>5.3</v>
-      </c>
-      <c r="AZ7">
-        <v>10.5</v>
-      </c>
-      <c r="BA7">
-        <v>7.6</v>
-      </c>
-      <c r="BB7">
-        <v>7.4</v>
-      </c>
-      <c r="BC7">
-        <v>7.2</v>
-      </c>
-      <c r="BD7">
-        <v>7.6</v>
-      </c>
       <c r="BE7">
-        <v>29</v>
+        <v>75</v>
       </c>
       <c r="BF7">
-        <v>6.8</v>
+        <v>16.5</v>
       </c>
       <c r="BG7">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="BH7">
         <v>3.45</v>
       </c>
       <c r="BI7">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="BJ7">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BK7">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BL7">
         <v>1000</v>
       </c>
       <c r="BM7">
-        <v>2.54</v>
+        <v>10</v>
       </c>
       <c r="BN7">
-        <v>5.9</v>
+        <v>5.3</v>
       </c>
       <c r="BO7">
-        <v>3.75</v>
+        <v>4.4</v>
       </c>
       <c r="BP7">
-        <v>22</v>
+        <v>17.5</v>
       </c>
       <c r="BQ7">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="BR7">
         <v>1000</v>
@@ -2405,28 +2405,28 @@
         <v>8</v>
       </c>
       <c r="BT7">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="BU7">
-        <v>3.9</v>
+        <v>5.8</v>
       </c>
       <c r="BV7">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="BW7">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="BX7">
         <v>1000</v>
       </c>
       <c r="BY7">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BZ7">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="CA7">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="CB7" t="s">
         <v>129</v>
@@ -2449,226 +2449,226 @@
         <v>120</v>
       </c>
       <c r="F8">
+        <v>1.26</v>
+      </c>
+      <c r="G8">
+        <v>1.32</v>
+      </c>
+      <c r="H8">
+        <v>13.5</v>
+      </c>
+      <c r="I8">
+        <v>21</v>
+      </c>
+      <c r="J8">
+        <v>5.6</v>
+      </c>
+      <c r="K8">
+        <v>7.6</v>
+      </c>
+      <c r="L8">
+        <v>1.37</v>
+      </c>
+      <c r="M8">
+        <v>1.06</v>
+      </c>
+      <c r="N8">
+        <v>4.1</v>
+      </c>
+      <c r="O8">
+        <v>1.27</v>
+      </c>
+      <c r="P8">
+        <v>2.06</v>
+      </c>
+      <c r="Q8">
+        <v>1.8</v>
+      </c>
+      <c r="R8">
+        <v>1.41</v>
+      </c>
+      <c r="S8">
+        <v>3.05</v>
+      </c>
+      <c r="T8">
+        <v>2.5</v>
+      </c>
+      <c r="U8">
+        <v>1.49</v>
+      </c>
+      <c r="V8">
         <v>1.05</v>
       </c>
-      <c r="G8">
-        <v>1.64</v>
-      </c>
-      <c r="H8">
-        <v>5.4</v>
-      </c>
-      <c r="I8">
-        <v>990</v>
-      </c>
-      <c r="J8">
+      <c r="W8">
+        <v>4.1</v>
+      </c>
+      <c r="X8">
+        <v>18</v>
+      </c>
+      <c r="Y8">
+        <v>50</v>
+      </c>
+      <c r="Z8">
+        <v>200</v>
+      </c>
+      <c r="AA8">
+        <v>1000</v>
+      </c>
+      <c r="AB8">
+        <v>7.4</v>
+      </c>
+      <c r="AC8">
+        <v>16.5</v>
+      </c>
+      <c r="AD8">
+        <v>90</v>
+      </c>
+      <c r="AE8">
+        <v>470</v>
+      </c>
+      <c r="AF8">
+        <v>6.8</v>
+      </c>
+      <c r="AG8">
+        <v>12</v>
+      </c>
+      <c r="AH8">
+        <v>55</v>
+      </c>
+      <c r="AI8">
+        <v>350</v>
+      </c>
+      <c r="AJ8">
+        <v>9.4</v>
+      </c>
+      <c r="AK8">
+        <v>17</v>
+      </c>
+      <c r="AL8">
+        <v>75</v>
+      </c>
+      <c r="AM8">
+        <v>390</v>
+      </c>
+      <c r="AN8">
+        <v>6.2</v>
+      </c>
+      <c r="AO8">
+        <v>1000</v>
+      </c>
+      <c r="AP8">
+        <v>14.5</v>
+      </c>
+      <c r="AQ8">
+        <v>7.4</v>
+      </c>
+      <c r="AR8">
+        <v>8.4</v>
+      </c>
+      <c r="AS8">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AT8">
+        <v>4</v>
+      </c>
+      <c r="AU8">
+        <v>12</v>
+      </c>
+      <c r="AV8">
+        <v>7.8</v>
+      </c>
+      <c r="AW8">
+        <v>8.6</v>
+      </c>
+      <c r="AX8">
         <v>3.8</v>
       </c>
-      <c r="K8">
-        <v>500</v>
-      </c>
-      <c r="L8">
-        <v>1.01</v>
-      </c>
-      <c r="M8">
-        <v>1.01</v>
-      </c>
-      <c r="N8">
-        <v>1.31</v>
-      </c>
-      <c r="O8">
-        <v>1.28</v>
-      </c>
-      <c r="P8">
-        <v>1.25</v>
-      </c>
-      <c r="Q8">
-        <v>1.01</v>
-      </c>
-      <c r="R8">
-        <v>1.18</v>
-      </c>
-      <c r="S8">
-        <v>2.88</v>
-      </c>
-      <c r="T8">
-        <v>1.11</v>
-      </c>
-      <c r="U8">
-        <v>1.11</v>
-      </c>
-      <c r="V8">
-        <v>1.01</v>
-      </c>
-      <c r="W8">
-        <v>2.52</v>
-      </c>
-      <c r="X8">
-        <v>1000</v>
-      </c>
-      <c r="Y8">
-        <v>1000</v>
-      </c>
-      <c r="Z8">
-        <v>1000</v>
-      </c>
-      <c r="AA8">
-        <v>1000</v>
-      </c>
-      <c r="AB8">
-        <v>1000</v>
-      </c>
-      <c r="AC8">
-        <v>1000</v>
-      </c>
-      <c r="AD8">
-        <v>1000</v>
-      </c>
-      <c r="AE8">
-        <v>1000</v>
-      </c>
-      <c r="AF8">
-        <v>1000</v>
-      </c>
-      <c r="AG8">
-        <v>1000</v>
-      </c>
-      <c r="AH8">
-        <v>1000</v>
-      </c>
-      <c r="AI8">
-        <v>1000</v>
-      </c>
-      <c r="AJ8">
-        <v>1000</v>
-      </c>
-      <c r="AK8">
-        <v>1000</v>
-      </c>
-      <c r="AL8">
-        <v>1000</v>
-      </c>
-      <c r="AM8">
-        <v>1000</v>
-      </c>
-      <c r="AN8">
-        <v>55</v>
-      </c>
-      <c r="AO8">
-        <v>1000</v>
-      </c>
-      <c r="AP8">
-        <v>1.01</v>
-      </c>
-      <c r="AQ8">
-        <v>2.5</v>
-      </c>
-      <c r="AR8">
-        <v>2.5</v>
-      </c>
-      <c r="AS8">
-        <v>2.5</v>
-      </c>
-      <c r="AT8">
-        <v>1.01</v>
-      </c>
-      <c r="AU8">
-        <v>1.01</v>
-      </c>
-      <c r="AV8">
-        <v>2.5</v>
-      </c>
-      <c r="AW8">
-        <v>2.5</v>
-      </c>
-      <c r="AX8">
-        <v>1.01</v>
-      </c>
       <c r="AY8">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AZ8">
-        <v>1.01</v>
+        <v>32</v>
       </c>
       <c r="BA8">
-        <v>2.5</v>
+        <v>8.4</v>
       </c>
       <c r="BB8">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BC8">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="BD8">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BE8">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="BF8">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BG8">
-        <v>1.55</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH8">
-        <v>1000</v>
+        <v>4.3</v>
       </c>
       <c r="BI8">
-        <v>1.04</v>
+        <v>2.92</v>
       </c>
       <c r="BJ8">
         <v>1000</v>
       </c>
       <c r="BK8">
-        <v>1.04</v>
+        <v>2.28</v>
       </c>
       <c r="BL8">
         <v>1000</v>
       </c>
       <c r="BM8">
-        <v>1.04</v>
+        <v>2.28</v>
       </c>
       <c r="BN8">
-        <v>1000</v>
+        <v>3.9</v>
       </c>
       <c r="BO8">
-        <v>1.04</v>
+        <v>1.44</v>
       </c>
       <c r="BP8">
         <v>1000</v>
       </c>
       <c r="BQ8">
-        <v>1.04</v>
+        <v>2.28</v>
       </c>
       <c r="BR8">
         <v>1000</v>
       </c>
       <c r="BS8">
-        <v>1.04</v>
+        <v>2.28</v>
       </c>
       <c r="BT8">
         <v>1000</v>
       </c>
       <c r="BU8">
-        <v>1.04</v>
+        <v>2.28</v>
       </c>
       <c r="BV8">
         <v>1000</v>
       </c>
       <c r="BW8">
-        <v>1.04</v>
+        <v>2.28</v>
       </c>
       <c r="BX8">
         <v>1000</v>
       </c>
       <c r="BY8">
-        <v>1.04</v>
+        <v>2.26</v>
       </c>
       <c r="BZ8">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="CA8">
-        <v>1.04</v>
+        <v>2.02</v>
       </c>
       <c r="CB8" t="s">
         <v>129</v>
@@ -2691,226 +2691,226 @@
         <v>121</v>
       </c>
       <c r="F9">
-        <v>1.3</v>
+        <v>1.74</v>
       </c>
       <c r="G9">
-        <v>110</v>
+        <v>1.9</v>
       </c>
       <c r="H9">
-        <v>2.4</v>
+        <v>6</v>
       </c>
       <c r="I9">
-        <v>990</v>
+        <v>7.4</v>
       </c>
       <c r="J9">
+        <v>3.1</v>
+      </c>
+      <c r="K9">
+        <v>3.5</v>
+      </c>
+      <c r="L9">
+        <v>1.53</v>
+      </c>
+      <c r="M9">
+        <v>1.13</v>
+      </c>
+      <c r="N9">
         <v>2.32</v>
       </c>
-      <c r="K9">
-        <v>950</v>
-      </c>
-      <c r="L9">
-        <v>1.01</v>
-      </c>
-      <c r="M9">
-        <v>1.01</v>
-      </c>
-      <c r="N9">
-        <v>1.25</v>
-      </c>
       <c r="O9">
-        <v>1.13</v>
+        <v>1.62</v>
       </c>
       <c r="P9">
-        <v>1.24</v>
+        <v>1.42</v>
       </c>
       <c r="Q9">
-        <v>2.52</v>
+        <v>2.88</v>
       </c>
       <c r="R9">
         <v>1.18</v>
       </c>
       <c r="S9">
+        <v>6.2</v>
+      </c>
+      <c r="T9">
         <v>2.52</v>
       </c>
-      <c r="T9">
-        <v>1.11</v>
-      </c>
       <c r="U9">
-        <v>1.11</v>
+        <v>1.54</v>
       </c>
       <c r="V9">
-        <v>1.04</v>
+        <v>1.15</v>
       </c>
       <c r="W9">
-        <v>1.18</v>
+        <v>2.12</v>
       </c>
       <c r="X9">
-        <v>500</v>
+        <v>8</v>
       </c>
       <c r="Y9">
-        <v>500</v>
+        <v>17.5</v>
       </c>
       <c r="Z9">
-        <v>500</v>
+        <v>65</v>
       </c>
       <c r="AA9">
         <v>500</v>
       </c>
       <c r="AB9">
-        <v>500</v>
+        <v>5.6</v>
       </c>
       <c r="AC9">
-        <v>500</v>
+        <v>8.6</v>
       </c>
       <c r="AD9">
-        <v>500</v>
+        <v>38</v>
       </c>
       <c r="AE9">
         <v>500</v>
       </c>
       <c r="AF9">
-        <v>500</v>
+        <v>9.4</v>
       </c>
       <c r="AG9">
-        <v>500</v>
+        <v>12.5</v>
       </c>
       <c r="AH9">
-        <v>500</v>
+        <v>38</v>
       </c>
       <c r="AI9">
         <v>500</v>
       </c>
       <c r="AJ9">
-        <v>500</v>
+        <v>22</v>
       </c>
       <c r="AK9">
-        <v>500</v>
+        <v>32</v>
       </c>
       <c r="AL9">
-        <v>500</v>
+        <v>160</v>
       </c>
       <c r="AM9">
         <v>500</v>
       </c>
       <c r="AN9">
-        <v>500</v>
+        <v>26</v>
       </c>
       <c r="AO9">
-        <v>500</v>
+        <v>460</v>
       </c>
       <c r="AP9">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="AQ9">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AR9">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AS9">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="AT9">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AU9">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AV9">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="AW9">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="AX9">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AY9">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="AZ9">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BA9">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BB9">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="BC9">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BD9">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BE9">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BF9">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="BG9">
-        <v>1.55</v>
+        <v>7.8</v>
       </c>
       <c r="BH9">
-        <v>1000</v>
+        <v>2.62</v>
       </c>
       <c r="BI9">
-        <v>1.01</v>
+        <v>2.1</v>
       </c>
       <c r="BJ9">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="BK9">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BL9">
         <v>1000</v>
       </c>
       <c r="BM9">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BN9">
-        <v>1000</v>
+        <v>4.2</v>
       </c>
       <c r="BO9">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="BP9">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="BQ9">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BR9">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="BS9">
-        <v>1.01</v>
+        <v>32</v>
       </c>
       <c r="BT9">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BU9">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BV9">
         <v>1000</v>
       </c>
       <c r="BW9">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BX9">
         <v>1000</v>
       </c>
       <c r="BY9">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BZ9">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="CA9">
-        <v>1.01</v>
+        <v>32</v>
       </c>
       <c r="CB9" t="s">
         <v>129</v>
@@ -2933,22 +2933,22 @@
         <v>122</v>
       </c>
       <c r="F10">
-        <v>2.28</v>
+        <v>2.34</v>
       </c>
       <c r="G10">
-        <v>2.42</v>
+        <v>2.48</v>
       </c>
       <c r="H10">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="I10">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="J10">
         <v>3.4</v>
       </c>
       <c r="K10">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="L10">
         <v>1.42</v>
@@ -2957,64 +2957,64 @@
         <v>1.07</v>
       </c>
       <c r="N10">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="O10">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="P10">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="Q10">
         <v>2</v>
       </c>
       <c r="R10">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="S10">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="T10">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="U10">
         <v>2.08</v>
       </c>
       <c r="V10">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W10">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="X10">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="Y10">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="Z10">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AA10">
-        <v>65</v>
+        <v>160</v>
       </c>
       <c r="AB10">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AC10">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD10">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AE10">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AF10">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AG10">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AH10">
         <v>18.5</v>
@@ -3023,10 +3023,10 @@
         <v>55</v>
       </c>
       <c r="AJ10">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AK10">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AL10">
         <v>42</v>
@@ -3038,73 +3038,73 @@
         <v>25</v>
       </c>
       <c r="AO10">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AP10">
         <v>10</v>
       </c>
       <c r="AQ10">
+        <v>10.5</v>
+      </c>
+      <c r="AR10">
+        <v>16.5</v>
+      </c>
+      <c r="AS10">
+        <v>7.8</v>
+      </c>
+      <c r="AT10">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AU10">
+        <v>6.8</v>
+      </c>
+      <c r="AV10">
         <v>10</v>
       </c>
-      <c r="AR10">
-        <v>17</v>
-      </c>
-      <c r="AS10">
-        <v>6.2</v>
-      </c>
-      <c r="AT10">
-        <v>7.6</v>
-      </c>
-      <c r="AU10">
-        <v>6</v>
-      </c>
-      <c r="AV10">
-        <v>10.5</v>
-      </c>
       <c r="AW10">
-        <v>5.9</v>
+        <v>7.2</v>
       </c>
       <c r="AX10">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AY10">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ10">
         <v>12.5</v>
       </c>
       <c r="BA10">
-        <v>34</v>
+        <v>7.6</v>
       </c>
       <c r="BB10">
-        <v>5.7</v>
+        <v>7</v>
       </c>
       <c r="BC10">
+        <v>19.5</v>
+      </c>
+      <c r="BD10">
+        <v>7.2</v>
+      </c>
+      <c r="BE10">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BF10">
         <v>18.5</v>
       </c>
-      <c r="BD10">
-        <v>5.9</v>
-      </c>
-      <c r="BE10">
-        <v>6.4</v>
-      </c>
-      <c r="BF10">
-        <v>17</v>
-      </c>
       <c r="BG10">
-        <v>6</v>
+        <v>7.4</v>
       </c>
       <c r="BH10">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="BI10">
-        <v>2.7</v>
+        <v>2.64</v>
       </c>
       <c r="BJ10">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BK10">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BL10">
         <v>1000</v>
@@ -3113,31 +3113,31 @@
         <v>10</v>
       </c>
       <c r="BN10">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BO10">
         <v>4</v>
       </c>
       <c r="BP10">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="BQ10">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BR10">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BS10">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BT10">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BU10">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BV10">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BW10">
         <v>7.8</v>
@@ -3146,7 +3146,7 @@
         <v>40</v>
       </c>
       <c r="BY10">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BZ10">
         <v>0</v>
@@ -3175,19 +3175,19 @@
         <v>123</v>
       </c>
       <c r="F11">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="G11">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="H11">
-        <v>5.5</v>
+        <v>5.1</v>
       </c>
       <c r="I11">
-        <v>6.4</v>
+        <v>5.9</v>
       </c>
       <c r="J11">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="K11">
         <v>3.65</v>
@@ -3196,58 +3196,58 @@
         <v>1.52</v>
       </c>
       <c r="M11">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="N11">
-        <v>2.96</v>
+        <v>2.84</v>
       </c>
       <c r="O11">
-        <v>1.46</v>
+        <v>1.52</v>
       </c>
       <c r="P11">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="Q11">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="R11">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="S11">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="T11">
+        <v>2.12</v>
+      </c>
+      <c r="U11">
+        <v>1.77</v>
+      </c>
+      <c r="V11">
+        <v>1.21</v>
+      </c>
+      <c r="W11">
         <v>2.1</v>
       </c>
-      <c r="U11">
-        <v>1.79</v>
-      </c>
-      <c r="V11">
-        <v>1.2</v>
-      </c>
-      <c r="W11">
-        <v>2.14</v>
-      </c>
       <c r="X11">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Y11">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="Z11">
-        <v>46</v>
+        <v>100</v>
       </c>
       <c r="AA11">
         <v>900</v>
       </c>
       <c r="AB11">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AC11">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AD11">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AE11">
         <v>260</v>
@@ -3268,16 +3268,16 @@
         <v>21</v>
       </c>
       <c r="AK11">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AL11">
-        <v>55</v>
+        <v>120</v>
       </c>
       <c r="AM11">
         <v>580</v>
       </c>
       <c r="AN11">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="AO11">
         <v>700</v>
@@ -3286,13 +3286,13 @@
         <v>7.6</v>
       </c>
       <c r="AQ11">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AR11">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AS11">
-        <v>13</v>
+        <v>16.5</v>
       </c>
       <c r="AT11">
         <v>6</v>
@@ -3301,10 +3301,10 @@
         <v>7</v>
       </c>
       <c r="AV11">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AW11">
-        <v>12.5</v>
+        <v>15.5</v>
       </c>
       <c r="AX11">
         <v>8.800000000000001</v>
@@ -3316,7 +3316,7 @@
         <v>21</v>
       </c>
       <c r="BA11">
-        <v>12.5</v>
+        <v>15.5</v>
       </c>
       <c r="BB11">
         <v>18</v>
@@ -3325,55 +3325,55 @@
         <v>21</v>
       </c>
       <c r="BD11">
-        <v>11</v>
+        <v>13.5</v>
       </c>
       <c r="BE11">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="BF11">
         <v>15</v>
       </c>
       <c r="BG11">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="BH11">
-        <v>2.96</v>
+        <v>2.9</v>
       </c>
       <c r="BI11">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="BJ11">
         <v>12</v>
       </c>
       <c r="BK11">
-        <v>6.6</v>
+        <v>8.4</v>
       </c>
       <c r="BL11">
         <v>1000</v>
       </c>
       <c r="BM11">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BN11">
         <v>4.2</v>
       </c>
       <c r="BO11">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="BP11">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BQ11">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BR11">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BS11">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BT11">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BU11">
         <v>5.7</v>
@@ -3382,19 +3382,19 @@
         <v>1000</v>
       </c>
       <c r="BW11">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BX11">
         <v>1000</v>
       </c>
       <c r="BY11">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BZ11">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="CA11">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="CB11" t="s">
         <v>129</v>
@@ -3417,175 +3417,175 @@
         <v>124</v>
       </c>
       <c r="F12">
-        <v>4</v>
+        <v>6.4</v>
       </c>
       <c r="G12">
-        <v>100</v>
+        <v>10.5</v>
       </c>
       <c r="H12">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="I12">
-        <v>1.59</v>
+        <v>1.64</v>
       </c>
       <c r="J12">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="K12">
+        <v>4.5</v>
+      </c>
+      <c r="L12">
+        <v>1.5</v>
+      </c>
+      <c r="M12">
+        <v>1.1</v>
+      </c>
+      <c r="N12">
+        <v>2.74</v>
+      </c>
+      <c r="O12">
+        <v>1.46</v>
+      </c>
+      <c r="P12">
+        <v>1.55</v>
+      </c>
+      <c r="Q12">
+        <v>2.34</v>
+      </c>
+      <c r="R12">
+        <v>1.2</v>
+      </c>
+      <c r="S12">
+        <v>4.7</v>
+      </c>
+      <c r="T12">
+        <v>2.46</v>
+      </c>
+      <c r="U12">
+        <v>1.51</v>
+      </c>
+      <c r="V12">
+        <v>2.52</v>
+      </c>
+      <c r="W12">
+        <v>1.1</v>
+      </c>
+      <c r="X12">
+        <v>10.5</v>
+      </c>
+      <c r="Y12">
+        <v>6.2</v>
+      </c>
+      <c r="Z12">
+        <v>8</v>
+      </c>
+      <c r="AA12">
+        <v>15</v>
+      </c>
+      <c r="AB12">
+        <v>22</v>
+      </c>
+      <c r="AC12">
+        <v>10</v>
+      </c>
+      <c r="AD12">
+        <v>12</v>
+      </c>
+      <c r="AE12">
+        <v>24</v>
+      </c>
+      <c r="AF12">
+        <v>90</v>
+      </c>
+      <c r="AG12">
+        <v>42</v>
+      </c>
+      <c r="AH12">
+        <v>42</v>
+      </c>
+      <c r="AI12">
+        <v>75</v>
+      </c>
+      <c r="AJ12">
+        <v>520</v>
+      </c>
+      <c r="AK12">
+        <v>260</v>
+      </c>
+      <c r="AL12">
+        <v>260</v>
+      </c>
+      <c r="AM12">
+        <v>390</v>
+      </c>
+      <c r="AN12">
+        <v>580</v>
+      </c>
+      <c r="AO12">
+        <v>14</v>
+      </c>
+      <c r="AP12">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AQ12">
+        <v>4.9</v>
+      </c>
+      <c r="AR12">
+        <v>6.2</v>
+      </c>
+      <c r="AS12">
+        <v>11</v>
+      </c>
+      <c r="AT12">
+        <v>16.5</v>
+      </c>
+      <c r="AU12">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AV12">
+        <v>9.4</v>
+      </c>
+      <c r="AW12">
         <v>19</v>
       </c>
-      <c r="L12">
-        <v>1.01</v>
-      </c>
-      <c r="M12">
-        <v>1.01</v>
-      </c>
-      <c r="N12">
-        <v>1.26</v>
-      </c>
-      <c r="O12">
-        <v>1.41</v>
-      </c>
-      <c r="P12">
-        <v>1.25</v>
-      </c>
-      <c r="Q12">
-        <v>1.9</v>
-      </c>
-      <c r="R12">
-        <v>1.18</v>
-      </c>
-      <c r="S12">
-        <v>1.99</v>
-      </c>
-      <c r="T12">
-        <v>1.11</v>
-      </c>
-      <c r="U12">
-        <v>1.11</v>
-      </c>
-      <c r="V12">
-        <v>2.58</v>
-      </c>
-      <c r="W12">
-        <v>1.04</v>
-      </c>
-      <c r="X12">
+      <c r="AX12">
+        <v>38</v>
+      </c>
+      <c r="AY12">
+        <v>21</v>
+      </c>
+      <c r="AZ12">
+        <v>23</v>
+      </c>
+      <c r="BA12">
+        <v>29</v>
+      </c>
+      <c r="BB12">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BC12">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BD12">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BE12">
+        <v>8.4</v>
+      </c>
+      <c r="BF12">
+        <v>9</v>
+      </c>
+      <c r="BG12">
+        <v>10.5</v>
+      </c>
+      <c r="BH12">
+        <v>3.1</v>
+      </c>
+      <c r="BI12">
+        <v>2.44</v>
+      </c>
+      <c r="BJ12">
         <v>16</v>
-      </c>
-      <c r="Y12">
-        <v>9.4</v>
-      </c>
-      <c r="Z12">
-        <v>10</v>
-      </c>
-      <c r="AA12">
-        <v>21</v>
-      </c>
-      <c r="AB12">
-        <v>36</v>
-      </c>
-      <c r="AC12">
-        <v>20</v>
-      </c>
-      <c r="AD12">
-        <v>27</v>
-      </c>
-      <c r="AE12">
-        <v>65</v>
-      </c>
-      <c r="AF12">
-        <v>380</v>
-      </c>
-      <c r="AG12">
-        <v>230</v>
-      </c>
-      <c r="AH12">
-        <v>270</v>
-      </c>
-      <c r="AI12">
-        <v>570</v>
-      </c>
-      <c r="AJ12">
-        <v>1000</v>
-      </c>
-      <c r="AK12">
-        <v>1000</v>
-      </c>
-      <c r="AL12">
-        <v>1000</v>
-      </c>
-      <c r="AM12">
-        <v>1000</v>
-      </c>
-      <c r="AN12">
-        <v>1000</v>
-      </c>
-      <c r="AO12">
-        <v>40</v>
-      </c>
-      <c r="AP12">
-        <v>3.9</v>
-      </c>
-      <c r="AQ12">
-        <v>2.94</v>
-      </c>
-      <c r="AR12">
-        <v>1.62</v>
-      </c>
-      <c r="AS12">
-        <v>9</v>
-      </c>
-      <c r="AT12">
-        <v>13</v>
-      </c>
-      <c r="AU12">
-        <v>7.4</v>
-      </c>
-      <c r="AV12">
-        <v>8</v>
-      </c>
-      <c r="AW12">
-        <v>13.5</v>
-      </c>
-      <c r="AX12">
-        <v>1.92</v>
-      </c>
-      <c r="AY12">
-        <v>20</v>
-      </c>
-      <c r="AZ12">
-        <v>19</v>
-      </c>
-      <c r="BA12">
-        <v>34</v>
-      </c>
-      <c r="BB12">
-        <v>1.93</v>
-      </c>
-      <c r="BC12">
-        <v>1.93</v>
-      </c>
-      <c r="BD12">
-        <v>1.93</v>
-      </c>
-      <c r="BE12">
-        <v>1.93</v>
-      </c>
-      <c r="BF12">
-        <v>1.93</v>
-      </c>
-      <c r="BG12">
-        <v>6.4</v>
-      </c>
-      <c r="BH12">
-        <v>1000</v>
-      </c>
-      <c r="BI12">
-        <v>1.01</v>
-      </c>
-      <c r="BJ12">
-        <v>1000</v>
       </c>
       <c r="BK12">
         <v>1.01</v>
@@ -3597,7 +3597,7 @@
         <v>1.01</v>
       </c>
       <c r="BN12">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="BO12">
         <v>1.01</v>
@@ -3615,19 +3615,19 @@
         <v>1.01</v>
       </c>
       <c r="BT12">
-        <v>1000</v>
+        <v>3.75</v>
       </c>
       <c r="BU12">
-        <v>1.01</v>
+        <v>2.92</v>
       </c>
       <c r="BV12">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BW12">
         <v>1.01</v>
       </c>
       <c r="BX12">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="BY12">
         <v>1.01</v>
@@ -3665,7 +3665,7 @@
         <v>2.52</v>
       </c>
       <c r="H13">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="I13">
         <v>3.7</v>
@@ -3674,19 +3674,19 @@
         <v>3.05</v>
       </c>
       <c r="K13">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="L13">
         <v>1.6</v>
       </c>
       <c r="M13">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="N13">
         <v>2.7</v>
       </c>
       <c r="O13">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="P13">
         <v>1.54</v>
@@ -3695,7 +3695,7 @@
         <v>2.78</v>
       </c>
       <c r="R13">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="S13">
         <v>5.8</v>
@@ -3713,28 +3713,28 @@
         <v>1.65</v>
       </c>
       <c r="X13">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Y13">
         <v>9.800000000000001</v>
       </c>
       <c r="Z13">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AA13">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AB13">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AC13">
         <v>7.2</v>
       </c>
       <c r="AD13">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AE13">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AF13">
         <v>14</v>
@@ -3743,34 +3743,34 @@
         <v>13</v>
       </c>
       <c r="AH13">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AI13">
-        <v>210</v>
+        <v>90</v>
       </c>
       <c r="AJ13">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AK13">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AL13">
-        <v>130</v>
+        <v>70</v>
       </c>
       <c r="AM13">
         <v>990</v>
       </c>
       <c r="AN13">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AO13">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AP13">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AQ13">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR13">
         <v>20</v>
@@ -3779,16 +3779,16 @@
         <v>36</v>
       </c>
       <c r="AT13">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AU13">
         <v>6.6</v>
       </c>
       <c r="AV13">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AW13">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="AX13">
         <v>12.5</v>
@@ -3797,7 +3797,7 @@
         <v>11.5</v>
       </c>
       <c r="AZ13">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BA13">
         <v>70</v>
@@ -3806,10 +3806,10 @@
         <v>32</v>
       </c>
       <c r="BC13">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BD13">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BE13">
         <v>75</v>
@@ -3821,7 +3821,7 @@
         <v>36</v>
       </c>
       <c r="BH13">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="BI13">
         <v>2.24</v>
@@ -3830,13 +3830,13 @@
         <v>11.5</v>
       </c>
       <c r="BK13">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BL13">
         <v>1000</v>
       </c>
       <c r="BM13">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BN13">
         <v>5.1</v>
@@ -3848,13 +3848,13 @@
         <v>26</v>
       </c>
       <c r="BQ13">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BR13">
         <v>55</v>
       </c>
       <c r="BS13">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BT13">
         <v>6.6</v>
@@ -3866,19 +3866,19 @@
         <v>42</v>
       </c>
       <c r="BW13">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BX13">
         <v>70</v>
       </c>
       <c r="BY13">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BZ13">
         <v>65</v>
       </c>
       <c r="CA13">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="CB13" t="s">
         <v>129</v>
@@ -3901,22 +3901,22 @@
         <v>126</v>
       </c>
       <c r="F14">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="G14">
-        <v>2.02</v>
+        <v>1.88</v>
       </c>
       <c r="H14">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="I14">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="J14">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="K14">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="L14">
         <v>1.47</v>
@@ -3925,16 +3925,16 @@
         <v>1.09</v>
       </c>
       <c r="N14">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="O14">
         <v>1.4</v>
       </c>
       <c r="P14">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="Q14">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="R14">
         <v>1.27</v>
@@ -3943,25 +3943,25 @@
         <v>4.1</v>
       </c>
       <c r="T14">
-        <v>1.96</v>
+        <v>2.02</v>
       </c>
       <c r="U14">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="V14">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="W14">
-        <v>1.99</v>
+        <v>2.12</v>
       </c>
       <c r="X14">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="Y14">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="Z14">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="AA14">
         <v>900</v>
@@ -3970,25 +3970,25 @@
         <v>7.8</v>
       </c>
       <c r="AC14">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AD14">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AE14">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="AF14">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AG14">
         <v>11</v>
       </c>
       <c r="AH14">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="AI14">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="AJ14">
         <v>23</v>
@@ -4003,64 +4003,64 @@
         <v>580</v>
       </c>
       <c r="AN14">
+        <v>15.5</v>
+      </c>
+      <c r="AO14">
+        <v>160</v>
+      </c>
+      <c r="AP14">
+        <v>10</v>
+      </c>
+      <c r="AQ14">
+        <v>12</v>
+      </c>
+      <c r="AR14">
+        <v>15</v>
+      </c>
+      <c r="AS14">
+        <v>7</v>
+      </c>
+      <c r="AT14">
+        <v>6</v>
+      </c>
+      <c r="AU14">
+        <v>7.2</v>
+      </c>
+      <c r="AV14">
+        <v>16</v>
+      </c>
+      <c r="AW14">
+        <v>6.8</v>
+      </c>
+      <c r="AX14">
+        <v>8.4</v>
+      </c>
+      <c r="AY14">
+        <v>6.2</v>
+      </c>
+      <c r="AZ14">
+        <v>11.5</v>
+      </c>
+      <c r="BA14">
+        <v>6.8</v>
+      </c>
+      <c r="BB14">
+        <v>16</v>
+      </c>
+      <c r="BC14">
         <v>18</v>
       </c>
-      <c r="AO14">
-        <v>130</v>
-      </c>
-      <c r="AP14">
-        <v>5.6</v>
-      </c>
-      <c r="AQ14">
-        <v>5</v>
-      </c>
-      <c r="AR14">
-        <v>6.2</v>
-      </c>
-      <c r="AS14">
-        <v>7.2</v>
-      </c>
-      <c r="AT14">
-        <v>6.4</v>
-      </c>
-      <c r="AU14">
-        <v>4.4</v>
-      </c>
-      <c r="AV14">
-        <v>5.5</v>
-      </c>
-      <c r="AW14">
+      <c r="BD14">
+        <v>36</v>
+      </c>
+      <c r="BE14">
         <v>7</v>
       </c>
-      <c r="AX14">
-        <v>5.6</v>
-      </c>
-      <c r="AY14">
-        <v>7.8</v>
-      </c>
-      <c r="AZ14">
-        <v>5.9</v>
-      </c>
-      <c r="BA14">
-        <v>7</v>
-      </c>
-      <c r="BB14">
-        <v>5.7</v>
-      </c>
-      <c r="BC14">
-        <v>5.7</v>
-      </c>
-      <c r="BD14">
-        <v>6.6</v>
-      </c>
-      <c r="BE14">
-        <v>7.2</v>
-      </c>
       <c r="BF14">
-        <v>5.3</v>
+        <v>12.5</v>
       </c>
       <c r="BG14">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="BH14">
         <v>3.55</v>
@@ -4069,7 +4069,7 @@
         <v>2.5</v>
       </c>
       <c r="BJ14">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BK14">
         <v>3.6</v>
@@ -4078,19 +4078,19 @@
         <v>1000</v>
       </c>
       <c r="BM14">
+        <v>4.8</v>
+      </c>
+      <c r="BN14">
         <v>4.9</v>
       </c>
-      <c r="BN14">
-        <v>5.2</v>
-      </c>
       <c r="BO14">
-        <v>2.56</v>
+        <v>3.3</v>
       </c>
       <c r="BP14">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="BQ14">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="BR14">
         <v>40</v>
@@ -4099,28 +4099,28 @@
         <v>4.4</v>
       </c>
       <c r="BT14">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="BU14">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="BV14">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="BW14">
         <v>4.6</v>
       </c>
       <c r="BX14">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="BY14">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BZ14">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="CA14">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="CB14" t="s">
         <v>129</v>
@@ -4385,220 +4385,220 @@
         <v>128</v>
       </c>
       <c r="F16">
-        <v>2.92</v>
+        <v>2.74</v>
       </c>
       <c r="G16">
-        <v>3.35</v>
+        <v>2.96</v>
       </c>
       <c r="H16">
+        <v>2.64</v>
+      </c>
+      <c r="I16">
+        <v>2.82</v>
+      </c>
+      <c r="J16">
+        <v>3.4</v>
+      </c>
+      <c r="K16">
+        <v>3.85</v>
+      </c>
+      <c r="L16">
+        <v>1.31</v>
+      </c>
+      <c r="M16">
+        <v>1.05</v>
+      </c>
+      <c r="N16">
+        <v>5.1</v>
+      </c>
+      <c r="O16">
+        <v>1.2</v>
+      </c>
+      <c r="P16">
         <v>2.38</v>
       </c>
-      <c r="I16">
-        <v>2.62</v>
-      </c>
-      <c r="J16">
-        <v>3.5</v>
-      </c>
-      <c r="K16">
-        <v>3.9</v>
-      </c>
-      <c r="L16">
-        <v>1.29</v>
-      </c>
-      <c r="M16">
-        <v>1.04</v>
-      </c>
-      <c r="N16">
-        <v>5.2</v>
-      </c>
-      <c r="O16">
-        <v>1.19</v>
-      </c>
-      <c r="P16">
-        <v>2.42</v>
-      </c>
       <c r="Q16">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="R16">
         <v>1.57</v>
       </c>
       <c r="S16">
-        <v>2.48</v>
+        <v>2.58</v>
       </c>
       <c r="T16">
-        <v>1.49</v>
+        <v>1.54</v>
       </c>
       <c r="U16">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="V16">
-        <v>1.62</v>
+        <v>1.54</v>
       </c>
       <c r="W16">
-        <v>1.43</v>
+        <v>1.51</v>
       </c>
       <c r="X16">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="Y16">
+        <v>19.5</v>
+      </c>
+      <c r="Z16">
+        <v>25</v>
+      </c>
+      <c r="AA16">
+        <v>42</v>
+      </c>
+      <c r="AB16">
         <v>18</v>
       </c>
-      <c r="Z16">
-        <v>21</v>
-      </c>
-      <c r="AA16">
-        <v>36</v>
-      </c>
-      <c r="AB16">
-        <v>22</v>
-      </c>
       <c r="AC16">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD16">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AE16">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AF16">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="AG16">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="AH16">
         <v>15</v>
       </c>
       <c r="AI16">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AJ16">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="AK16">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="AL16">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AM16">
         <v>70</v>
       </c>
       <c r="AN16">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AO16">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="AP16">
-        <v>5.5</v>
+        <v>16.5</v>
       </c>
       <c r="AQ16">
-        <v>4.9</v>
+        <v>13</v>
       </c>
       <c r="AR16">
-        <v>5.1</v>
+        <v>16.5</v>
       </c>
       <c r="AS16">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="AT16">
-        <v>5.2</v>
+        <v>14.5</v>
       </c>
       <c r="AU16">
-        <v>4</v>
+        <v>7.4</v>
       </c>
       <c r="AV16">
-        <v>7.8</v>
+        <v>10.5</v>
       </c>
       <c r="AW16">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AX16">
-        <v>5.4</v>
+        <v>18</v>
       </c>
       <c r="AY16">
-        <v>4.7</v>
+        <v>10.5</v>
       </c>
       <c r="AZ16">
-        <v>4.7</v>
+        <v>12</v>
       </c>
       <c r="BA16">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="BB16">
-        <v>15.5</v>
+        <v>32</v>
       </c>
       <c r="BC16">
-        <v>10.5</v>
+        <v>20</v>
       </c>
       <c r="BD16">
-        <v>19.5</v>
+        <v>24</v>
       </c>
       <c r="BE16">
-        <v>9.199999999999999</v>
+        <v>6.4</v>
       </c>
       <c r="BF16">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="BG16">
-        <v>4.6</v>
+        <v>12.5</v>
       </c>
       <c r="BH16">
-        <v>5.1</v>
+        <v>4.8</v>
       </c>
       <c r="BI16">
-        <v>2.56</v>
+        <v>3.25</v>
       </c>
       <c r="BJ16">
         <v>10.5</v>
       </c>
       <c r="BK16">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="BL16">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="BM16">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="BN16">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BO16">
-        <v>2.96</v>
+        <v>4.6</v>
       </c>
       <c r="BP16">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BQ16">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BR16">
         <v>32</v>
       </c>
       <c r="BS16">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="BT16">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BU16">
-        <v>3.9</v>
+        <v>4.6</v>
       </c>
       <c r="BV16">
-        <v>19.5</v>
+        <v>22</v>
       </c>
       <c r="BW16">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="BX16">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="BY16">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BZ16">
         <v>0</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-06.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-06.xlsx
@@ -403,7 +403,7 @@
     <t>Always Ready</t>
   </si>
   <si>
-    <t>2026-08-06 05:55:28</t>
+    <t>2026-08-06 08:08:29</t>
   </si>
 </sst>
 </file>
@@ -997,16 +997,16 @@
         <v>114</v>
       </c>
       <c r="F2">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="G2">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="H2">
         <v>3.9</v>
       </c>
       <c r="I2">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="J2">
         <v>4.2</v>
@@ -1027,31 +1027,31 @@
         <v>1.2</v>
       </c>
       <c r="P2">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="Q2">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="R2">
-        <v>1.61</v>
+        <v>1.66</v>
       </c>
       <c r="S2">
-        <v>2.56</v>
+        <v>2.48</v>
       </c>
       <c r="T2">
-        <v>1.65</v>
+        <v>1.59</v>
       </c>
       <c r="U2">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="V2">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="W2">
         <v>2.04</v>
       </c>
       <c r="X2">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="Y2">
         <v>21</v>
@@ -1060,7 +1060,7 @@
         <v>34</v>
       </c>
       <c r="AA2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="AB2">
         <v>13</v>
@@ -1084,7 +1084,7 @@
         <v>17</v>
       </c>
       <c r="AI2">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="AJ2">
         <v>23</v>
@@ -1102,13 +1102,13 @@
         <v>9.4</v>
       </c>
       <c r="AO2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AP2">
         <v>20</v>
       </c>
       <c r="AQ2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AR2">
         <v>28</v>
@@ -1117,22 +1117,22 @@
         <v>55</v>
       </c>
       <c r="AT2">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AU2">
-        <v>8.4</v>
+        <v>7.2</v>
       </c>
       <c r="AV2">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AW2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AX2">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AY2">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AZ2">
         <v>14</v>
@@ -1144,7 +1144,7 @@
         <v>19.5</v>
       </c>
       <c r="BC2">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BD2">
         <v>24</v>
@@ -1153,10 +1153,10 @@
         <v>55</v>
       </c>
       <c r="BF2">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BG2">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BH2">
         <v>4.9</v>
@@ -1168,13 +1168,13 @@
         <v>10</v>
       </c>
       <c r="BK2">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="BL2">
         <v>90</v>
       </c>
       <c r="BM2">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BN2">
         <v>5.8</v>
@@ -1183,34 +1183,34 @@
         <v>4.1</v>
       </c>
       <c r="BP2">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BQ2">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BR2">
         <v>25</v>
       </c>
       <c r="BS2">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BT2">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="BU2">
         <v>6</v>
       </c>
       <c r="BV2">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="BW2">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BX2">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="BY2">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BZ2">
         <v>0</v>
@@ -1239,22 +1239,22 @@
         <v>115</v>
       </c>
       <c r="F3">
-        <v>1.72</v>
+        <v>1.79</v>
       </c>
       <c r="G3">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="H3">
-        <v>6</v>
+        <v>5.3</v>
       </c>
       <c r="I3">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="J3">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="K3">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="L3">
         <v>1.54</v>
@@ -1263,196 +1263,196 @@
         <v>1.11</v>
       </c>
       <c r="N3">
-        <v>2.8</v>
+        <v>2.86</v>
       </c>
       <c r="O3">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="P3">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="Q3">
-        <v>2.48</v>
+        <v>2.44</v>
       </c>
       <c r="R3">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="S3">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="T3">
-        <v>2.26</v>
+        <v>2.16</v>
       </c>
       <c r="U3">
-        <v>1.68</v>
+        <v>1.75</v>
       </c>
       <c r="V3">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="W3">
-        <v>2.22</v>
+        <v>2.16</v>
       </c>
       <c r="X3">
         <v>10.5</v>
       </c>
       <c r="Y3">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Z3">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="AA3">
         <v>900</v>
       </c>
       <c r="AB3">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AC3">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD3">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AE3">
         <v>260</v>
       </c>
       <c r="AF3">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="AG3">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AH3">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AI3">
         <v>700</v>
       </c>
       <c r="AJ3">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AK3">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AL3">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AM3">
         <v>580</v>
       </c>
       <c r="AN3">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="AO3">
-        <v>700</v>
+        <v>320</v>
       </c>
       <c r="AP3">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ3">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AR3">
         <v>32</v>
       </c>
       <c r="AS3">
+        <v>10.5</v>
+      </c>
+      <c r="AT3">
+        <v>5.8</v>
+      </c>
+      <c r="AU3">
+        <v>7</v>
+      </c>
+      <c r="AV3">
+        <v>19.5</v>
+      </c>
+      <c r="AW3">
+        <v>10</v>
+      </c>
+      <c r="AX3">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AY3">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ3">
         <v>12</v>
       </c>
-      <c r="AT3">
-        <v>5.5</v>
-      </c>
-      <c r="AU3">
-        <v>7.2</v>
-      </c>
-      <c r="AV3">
+      <c r="BA3">
+        <v>10</v>
+      </c>
+      <c r="BB3">
+        <v>18.5</v>
+      </c>
+      <c r="BC3">
         <v>20</v>
       </c>
-      <c r="AW3">
-        <v>55</v>
-      </c>
-      <c r="AX3">
-        <v>8</v>
-      </c>
-      <c r="AY3">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AZ3">
-        <v>21</v>
-      </c>
-      <c r="BA3">
-        <v>60</v>
-      </c>
-      <c r="BB3">
-        <v>16</v>
-      </c>
-      <c r="BC3">
-        <v>19</v>
-      </c>
       <c r="BD3">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="BE3">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="BF3">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BG3">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="BH3">
         <v>3.15</v>
       </c>
       <c r="BI3">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="BJ3">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="BK3">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="BN3">
+        <v>4.3</v>
+      </c>
+      <c r="BO3">
+        <v>3.65</v>
+      </c>
+      <c r="BP3">
+        <v>16</v>
+      </c>
+      <c r="BQ3">
+        <v>5.3</v>
+      </c>
+      <c r="BR3">
+        <v>38</v>
+      </c>
+      <c r="BS3">
+        <v>6.4</v>
+      </c>
+      <c r="BT3">
+        <v>10.5</v>
+      </c>
+      <c r="BU3">
         <v>4.5</v>
       </c>
-      <c r="BO3">
-        <v>3.4</v>
-      </c>
-      <c r="BP3">
-        <v>15</v>
-      </c>
-      <c r="BQ3">
-        <v>4.8</v>
-      </c>
-      <c r="BR3">
-        <v>42</v>
-      </c>
-      <c r="BS3">
-        <v>6</v>
-      </c>
-      <c r="BT3">
-        <v>10</v>
-      </c>
-      <c r="BU3">
-        <v>4.1</v>
-      </c>
       <c r="BV3">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="BW3">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="BX3">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="BY3">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="BZ3">
         <v>0</v>
@@ -1481,13 +1481,13 @@
         <v>116</v>
       </c>
       <c r="F4">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="G4">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="H4">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="I4">
         <v>6.2</v>
@@ -1505,37 +1505,37 @@
         <v>1.01</v>
       </c>
       <c r="N4">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="O4">
         <v>1.11</v>
       </c>
       <c r="P4">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="Q4">
         <v>1.33</v>
       </c>
       <c r="R4">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="S4">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="T4">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="U4">
         <v>2.8</v>
       </c>
       <c r="V4">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="W4">
-        <v>2.74</v>
+        <v>2.8</v>
       </c>
       <c r="X4">
-        <v>55</v>
+        <v>85</v>
       </c>
       <c r="Y4">
         <v>48</v>
@@ -1550,7 +1550,7 @@
         <v>19</v>
       </c>
       <c r="AC4">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AD4">
         <v>25</v>
@@ -1559,16 +1559,16 @@
         <v>70</v>
       </c>
       <c r="AF4">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AG4">
         <v>12.5</v>
       </c>
       <c r="AH4">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AI4">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AJ4">
         <v>18.5</v>
@@ -1589,25 +1589,25 @@
         <v>36</v>
       </c>
       <c r="AP4">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AQ4">
         <v>36</v>
       </c>
       <c r="AR4">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AS4">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="AT4">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AU4">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AV4">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AW4">
         <v>42</v>
@@ -1619,16 +1619,16 @@
         <v>10</v>
       </c>
       <c r="AZ4">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BA4">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="BB4">
         <v>15.5</v>
       </c>
       <c r="BC4">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BD4">
         <v>18</v>
@@ -1640,25 +1640,25 @@
         <v>3.65</v>
       </c>
       <c r="BG4">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BH4">
         <v>7</v>
       </c>
       <c r="BI4">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BJ4">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="BK4">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="BN4">
         <v>5.8</v>
@@ -1670,37 +1670,37 @@
         <v>10.5</v>
       </c>
       <c r="BQ4">
-        <v>3.85</v>
+        <v>6.8</v>
       </c>
       <c r="BR4">
         <v>16.5</v>
       </c>
       <c r="BS4">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="BT4">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BU4">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="BV4">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="BW4">
-        <v>5.3</v>
+        <v>5.9</v>
       </c>
       <c r="BX4">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BY4">
-        <v>5.2</v>
+        <v>5.8</v>
       </c>
       <c r="BZ4">
         <v>8.4</v>
       </c>
       <c r="CA4">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="CB4" t="s">
         <v>129</v>
@@ -1723,13 +1723,13 @@
         <v>117</v>
       </c>
       <c r="F5">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="G5">
-        <v>3.05</v>
+        <v>2.96</v>
       </c>
       <c r="H5">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="I5">
         <v>3.2</v>
@@ -1747,34 +1747,34 @@
         <v>1.09</v>
       </c>
       <c r="N5">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="O5">
         <v>1.37</v>
       </c>
       <c r="P5">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="Q5">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="R5">
         <v>1.31</v>
       </c>
       <c r="S5">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="T5">
         <v>1.81</v>
       </c>
       <c r="U5">
-        <v>2.12</v>
+        <v>2.04</v>
       </c>
       <c r="V5">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="W5">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="X5">
         <v>13</v>
@@ -1795,7 +1795,7 @@
         <v>7.4</v>
       </c>
       <c r="AD5">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AE5">
         <v>38</v>
@@ -1807,7 +1807,7 @@
         <v>15</v>
       </c>
       <c r="AH5">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AI5">
         <v>60</v>
@@ -1831,16 +1831,16 @@
         <v>42</v>
       </c>
       <c r="AP5">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AQ5">
         <v>9.6</v>
       </c>
-      <c r="AQ5">
-        <v>8.800000000000001</v>
-      </c>
       <c r="AR5">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AS5">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AT5">
         <v>8.800000000000001</v>
@@ -1861,28 +1861,28 @@
         <v>10.5</v>
       </c>
       <c r="AZ5">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="BA5">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="BB5">
         <v>29</v>
       </c>
       <c r="BC5">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="BD5">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="BE5">
         <v>70</v>
       </c>
       <c r="BF5">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="BG5">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="BH5">
         <v>3.65</v>
@@ -1894,13 +1894,13 @@
         <v>12</v>
       </c>
       <c r="BK5">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="BL5">
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="BN5">
         <v>6.8</v>
@@ -1912,37 +1912,37 @@
         <v>27</v>
       </c>
       <c r="BQ5">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="BR5">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="BS5">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BT5">
         <v>7</v>
       </c>
       <c r="BU5">
-        <v>5.1</v>
+        <v>4.5</v>
       </c>
       <c r="BV5">
         <v>29</v>
       </c>
       <c r="BW5">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BX5">
         <v>48</v>
       </c>
       <c r="BY5">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="BZ5">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="CA5">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="CB5" t="s">
         <v>129</v>
@@ -1965,22 +1965,22 @@
         <v>118</v>
       </c>
       <c r="F6">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="G6">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="H6">
+        <v>3.5</v>
+      </c>
+      <c r="I6">
+        <v>3.65</v>
+      </c>
+      <c r="J6">
+        <v>3.5</v>
+      </c>
+      <c r="K6">
         <v>3.55</v>
-      </c>
-      <c r="I6">
-        <v>3.75</v>
-      </c>
-      <c r="J6">
-        <v>3.4</v>
-      </c>
-      <c r="K6">
-        <v>3.5</v>
       </c>
       <c r="L6">
         <v>1.41</v>
@@ -1989,43 +1989,43 @@
         <v>1.07</v>
       </c>
       <c r="N6">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="O6">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="P6">
-        <v>1.96</v>
+        <v>1.99</v>
       </c>
       <c r="Q6">
-        <v>1.98</v>
+        <v>1.94</v>
       </c>
       <c r="R6">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="S6">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="T6">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="U6">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="V6">
         <v>1.37</v>
       </c>
       <c r="W6">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="X6">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="Y6">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="Z6">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AA6">
         <v>75</v>
@@ -2034,7 +2034,7 @@
         <v>12</v>
       </c>
       <c r="AC6">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD6">
         <v>15.5</v>
@@ -2043,16 +2043,16 @@
         <v>50</v>
       </c>
       <c r="AF6">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AG6">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="AH6">
         <v>17.5</v>
       </c>
       <c r="AI6">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AJ6">
         <v>38</v>
@@ -2061,16 +2061,16 @@
         <v>30</v>
       </c>
       <c r="AL6">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="AM6">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AN6">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AO6">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AP6">
         <v>12.5</v>
@@ -2115,16 +2115,16 @@
         <v>21</v>
       </c>
       <c r="BD6">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="BE6">
         <v>65</v>
       </c>
       <c r="BF6">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BG6">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="BH6">
         <v>4</v>
@@ -2136,13 +2136,13 @@
         <v>11.5</v>
       </c>
       <c r="BK6">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BL6">
         <v>140</v>
       </c>
       <c r="BM6">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BN6">
         <v>5.3</v>
@@ -2154,13 +2154,13 @@
         <v>21</v>
       </c>
       <c r="BQ6">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BR6">
         <v>38</v>
       </c>
       <c r="BS6">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BT6">
         <v>7.8</v>
@@ -2172,13 +2172,13 @@
         <v>34</v>
       </c>
       <c r="BW6">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BX6">
         <v>46</v>
       </c>
       <c r="BY6">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BZ6">
         <v>0</v>
@@ -2207,226 +2207,226 @@
         <v>119</v>
       </c>
       <c r="F7">
-        <v>2.18</v>
+        <v>2.34</v>
       </c>
       <c r="G7">
-        <v>2.3</v>
+        <v>2.48</v>
       </c>
       <c r="H7">
-        <v>3.35</v>
+        <v>3.1</v>
       </c>
       <c r="I7">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="J7">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K7">
         <v>3.7</v>
       </c>
       <c r="L7">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="M7">
         <v>1.07</v>
       </c>
       <c r="N7">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="O7">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="P7">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="Q7">
         <v>2</v>
       </c>
       <c r="R7">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="S7">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="T7">
         <v>1.81</v>
       </c>
       <c r="U7">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="V7">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="W7">
-        <v>1.76</v>
+        <v>1.68</v>
       </c>
       <c r="X7">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="Y7">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="Z7">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AA7">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AB7">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AC7">
         <v>8.4</v>
       </c>
       <c r="AD7">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AE7">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AF7">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="AG7">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AH7">
         <v>19</v>
       </c>
       <c r="AI7">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AJ7">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AK7">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AL7">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AM7">
-        <v>580</v>
+        <v>110</v>
       </c>
       <c r="AN7">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AO7">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AP7">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AQ7">
         <v>11</v>
       </c>
       <c r="AR7">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AS7">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AT7">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AU7">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AV7">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AW7">
+        <v>30</v>
+      </c>
+      <c r="AX7">
+        <v>13.5</v>
+      </c>
+      <c r="AY7">
+        <v>10</v>
+      </c>
+      <c r="AZ7">
+        <v>15.5</v>
+      </c>
+      <c r="BA7">
+        <v>40</v>
+      </c>
+      <c r="BB7">
+        <v>29</v>
+      </c>
+      <c r="BC7">
+        <v>23</v>
+      </c>
+      <c r="BD7">
         <v>34</v>
       </c>
-      <c r="AX7">
-        <v>12.5</v>
-      </c>
-      <c r="AY7">
-        <v>9.6</v>
-      </c>
-      <c r="AZ7">
-        <v>16</v>
-      </c>
-      <c r="BA7">
-        <v>42</v>
-      </c>
-      <c r="BB7">
-        <v>25</v>
-      </c>
-      <c r="BC7">
-        <v>21</v>
-      </c>
-      <c r="BD7">
-        <v>32</v>
-      </c>
       <c r="BE7">
-        <v>75</v>
+        <v>11.5</v>
       </c>
       <c r="BF7">
-        <v>16.5</v>
+        <v>19</v>
       </c>
       <c r="BG7">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="BH7">
         <v>3.45</v>
       </c>
       <c r="BI7">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="BJ7">
         <v>10</v>
       </c>
       <c r="BK7">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BL7">
         <v>1000</v>
       </c>
       <c r="BM7">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BN7">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="BO7">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="BP7">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="BQ7">
         <v>6.6</v>
       </c>
       <c r="BR7">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BS7">
         <v>8</v>
       </c>
       <c r="BT7">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="BU7">
-        <v>5.8</v>
+        <v>5.4</v>
       </c>
       <c r="BV7">
         <v>1000</v>
       </c>
       <c r="BW7">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="BX7">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BY7">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ7">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="CA7">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="CB7" t="s">
         <v>129</v>
@@ -2452,25 +2452,25 @@
         <v>1.26</v>
       </c>
       <c r="G8">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="H8">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="I8">
         <v>21</v>
       </c>
       <c r="J8">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="K8">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="L8">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="M8">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N8">
         <v>4.1</v>
@@ -2485,7 +2485,7 @@
         <v>1.8</v>
       </c>
       <c r="R8">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="S8">
         <v>3.05</v>
@@ -2494,22 +2494,22 @@
         <v>2.5</v>
       </c>
       <c r="U8">
-        <v>1.49</v>
+        <v>1.57</v>
       </c>
       <c r="V8">
         <v>1.05</v>
       </c>
       <c r="W8">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="X8">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="Y8">
-        <v>50</v>
+        <v>950</v>
       </c>
       <c r="Z8">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="AA8">
         <v>1000</v>
@@ -2521,76 +2521,76 @@
         <v>16.5</v>
       </c>
       <c r="AD8">
-        <v>90</v>
+        <v>160</v>
       </c>
       <c r="AE8">
-        <v>470</v>
+        <v>450</v>
       </c>
       <c r="AF8">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AG8">
         <v>12</v>
       </c>
       <c r="AH8">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AI8">
-        <v>350</v>
+        <v>330</v>
       </c>
       <c r="AJ8">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AK8">
         <v>17</v>
       </c>
       <c r="AL8">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AM8">
-        <v>390</v>
+        <v>350</v>
       </c>
       <c r="AN8">
-        <v>6.2</v>
+        <v>5.7</v>
       </c>
       <c r="AO8">
         <v>1000</v>
       </c>
       <c r="AP8">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AQ8">
         <v>7.4</v>
       </c>
       <c r="AR8">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AS8">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AT8">
-        <v>4</v>
+        <v>6.2</v>
       </c>
       <c r="AU8">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AV8">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AW8">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AX8">
-        <v>3.8</v>
+        <v>6</v>
       </c>
       <c r="AY8">
         <v>10</v>
       </c>
       <c r="AZ8">
-        <v>32</v>
+        <v>7.6</v>
       </c>
       <c r="BA8">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB8">
         <v>8</v>
@@ -2599,76 +2599,76 @@
         <v>14</v>
       </c>
       <c r="BD8">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BE8">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BF8">
+        <v>4.9</v>
+      </c>
+      <c r="BG8">
+        <v>9</v>
+      </c>
+      <c r="BH8">
+        <v>4.4</v>
+      </c>
+      <c r="BI8">
+        <v>3</v>
+      </c>
+      <c r="BJ8">
+        <v>17.5</v>
+      </c>
+      <c r="BK8">
+        <v>3.9</v>
+      </c>
+      <c r="BL8">
+        <v>1000</v>
+      </c>
+      <c r="BM8">
+        <v>4.9</v>
+      </c>
+      <c r="BN8">
+        <v>4</v>
+      </c>
+      <c r="BO8">
+        <v>2.76</v>
+      </c>
+      <c r="BP8">
         <v>8.6</v>
       </c>
-      <c r="BF8">
-        <v>5.2</v>
-      </c>
-      <c r="BG8">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BH8">
-        <v>4.3</v>
-      </c>
-      <c r="BI8">
-        <v>2.92</v>
-      </c>
-      <c r="BJ8">
-        <v>1000</v>
-      </c>
-      <c r="BK8">
-        <v>2.28</v>
-      </c>
-      <c r="BL8">
-        <v>1000</v>
-      </c>
-      <c r="BM8">
-        <v>2.28</v>
-      </c>
-      <c r="BN8">
-        <v>3.9</v>
-      </c>
-      <c r="BO8">
-        <v>1.44</v>
-      </c>
-      <c r="BP8">
-        <v>1000</v>
-      </c>
       <c r="BQ8">
-        <v>2.28</v>
+        <v>5.4</v>
       </c>
       <c r="BR8">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BS8">
-        <v>2.28</v>
+        <v>4.4</v>
       </c>
       <c r="BT8">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="BU8">
-        <v>2.28</v>
+        <v>4</v>
       </c>
       <c r="BV8">
         <v>1000</v>
       </c>
       <c r="BW8">
-        <v>2.28</v>
+        <v>4.9</v>
       </c>
       <c r="BX8">
         <v>1000</v>
       </c>
       <c r="BY8">
-        <v>2.26</v>
+        <v>4.9</v>
       </c>
       <c r="BZ8">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="CA8">
-        <v>2.02</v>
+        <v>3.85</v>
       </c>
       <c r="CB8" t="s">
         <v>129</v>
@@ -2691,40 +2691,40 @@
         <v>121</v>
       </c>
       <c r="F9">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="G9">
-        <v>1.9</v>
+        <v>1.83</v>
       </c>
       <c r="H9">
         <v>6</v>
       </c>
       <c r="I9">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="J9">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="K9">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="L9">
-        <v>1.53</v>
+        <v>1.59</v>
       </c>
       <c r="M9">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="N9">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="O9">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="P9">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="Q9">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="R9">
         <v>1.18</v>
@@ -2733,37 +2733,37 @@
         <v>6.2</v>
       </c>
       <c r="T9">
-        <v>2.52</v>
+        <v>2.46</v>
       </c>
       <c r="U9">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="V9">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="W9">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="X9">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Y9">
-        <v>17.5</v>
+        <v>15</v>
       </c>
       <c r="Z9">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AA9">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="AB9">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="AC9">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD9">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="AE9">
         <v>500</v>
@@ -2772,103 +2772,103 @@
         <v>9.4</v>
       </c>
       <c r="AG9">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH9">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AI9">
         <v>500</v>
       </c>
       <c r="AJ9">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AK9">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AL9">
-        <v>160</v>
+        <v>190</v>
       </c>
       <c r="AM9">
         <v>500</v>
       </c>
       <c r="AN9">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AO9">
-        <v>460</v>
+        <v>410</v>
       </c>
       <c r="AP9">
-        <v>5.7</v>
+        <v>6.8</v>
       </c>
       <c r="AQ9">
+        <v>12</v>
+      </c>
+      <c r="AR9">
+        <v>38</v>
+      </c>
+      <c r="AS9">
         <v>10</v>
       </c>
-      <c r="AR9">
+      <c r="AT9">
+        <v>4.9</v>
+      </c>
+      <c r="AU9">
         <v>7</v>
       </c>
-      <c r="AS9">
-        <v>7.6</v>
-      </c>
-      <c r="AT9">
-        <v>4.1</v>
-      </c>
-      <c r="AU9">
-        <v>6</v>
-      </c>
       <c r="AV9">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="AW9">
-        <v>7.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AX9">
-        <v>6.6</v>
+        <v>8</v>
       </c>
       <c r="AY9">
-        <v>8.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ9">
-        <v>6.4</v>
+        <v>15</v>
       </c>
       <c r="BA9">
-        <v>7.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BB9">
-        <v>15</v>
+        <v>17.5</v>
       </c>
       <c r="BC9">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="BD9">
-        <v>7.2</v>
+        <v>9.4</v>
       </c>
       <c r="BE9">
-        <v>7.8</v>
+        <v>10</v>
       </c>
       <c r="BF9">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="BG9">
-        <v>7.8</v>
+        <v>10</v>
       </c>
       <c r="BH9">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="BI9">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="BJ9">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BK9">
-        <v>10</v>
+        <v>6.2</v>
       </c>
       <c r="BL9">
         <v>1000</v>
       </c>
       <c r="BM9">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="BN9">
         <v>4.2</v>
@@ -2880,37 +2880,37 @@
         <v>15.5</v>
       </c>
       <c r="BQ9">
-        <v>10.5</v>
+        <v>6.4</v>
       </c>
       <c r="BR9">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="BS9">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="BT9">
         <v>10.5</v>
       </c>
       <c r="BU9">
-        <v>7.2</v>
+        <v>5.4</v>
       </c>
       <c r="BV9">
         <v>1000</v>
       </c>
       <c r="BW9">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="BX9">
         <v>1000</v>
       </c>
       <c r="BY9">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="BZ9">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="CA9">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="CB9" t="s">
         <v>129</v>
@@ -2936,10 +2936,10 @@
         <v>2.34</v>
       </c>
       <c r="G10">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="H10">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="I10">
         <v>3.4</v>
@@ -2948,25 +2948,25 @@
         <v>3.4</v>
       </c>
       <c r="K10">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="L10">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="M10">
         <v>1.07</v>
       </c>
       <c r="N10">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="O10">
         <v>1.34</v>
       </c>
       <c r="P10">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="Q10">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="R10">
         <v>1.33</v>
@@ -2975,7 +2975,7 @@
         <v>3.6</v>
       </c>
       <c r="T10">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="U10">
         <v>2.08</v>
@@ -2996,7 +2996,7 @@
         <v>24</v>
       </c>
       <c r="AA10">
-        <v>160</v>
+        <v>75</v>
       </c>
       <c r="AB10">
         <v>10.5</v>
@@ -3041,16 +3041,16 @@
         <v>46</v>
       </c>
       <c r="AP10">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ10">
         <v>10.5</v>
       </c>
       <c r="AR10">
-        <v>16.5</v>
+        <v>19</v>
       </c>
       <c r="AS10">
-        <v>7.8</v>
+        <v>42</v>
       </c>
       <c r="AT10">
         <v>8.800000000000001</v>
@@ -3059,40 +3059,40 @@
         <v>6.8</v>
       </c>
       <c r="AV10">
+        <v>12</v>
+      </c>
+      <c r="AW10">
+        <v>27</v>
+      </c>
+      <c r="AX10">
+        <v>13</v>
+      </c>
+      <c r="AY10">
         <v>10</v>
       </c>
-      <c r="AW10">
-        <v>7.2</v>
-      </c>
-      <c r="AX10">
-        <v>11.5</v>
-      </c>
-      <c r="AY10">
-        <v>9.800000000000001</v>
-      </c>
       <c r="AZ10">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="BA10">
-        <v>7.6</v>
+        <v>34</v>
       </c>
       <c r="BB10">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="BC10">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BD10">
-        <v>7.2</v>
+        <v>29</v>
       </c>
       <c r="BE10">
-        <v>8.199999999999999</v>
+        <v>70</v>
       </c>
       <c r="BF10">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BG10">
-        <v>7.4</v>
+        <v>23</v>
       </c>
       <c r="BH10">
         <v>3.4</v>
@@ -3178,22 +3178,22 @@
         <v>1.82</v>
       </c>
       <c r="G11">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="H11">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="I11">
         <v>5.9</v>
       </c>
       <c r="J11">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="K11">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="L11">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="M11">
         <v>1.11</v>
@@ -3202,28 +3202,28 @@
         <v>2.84</v>
       </c>
       <c r="O11">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="P11">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="Q11">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="R11">
         <v>1.22</v>
       </c>
       <c r="S11">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="T11">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="U11">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="V11">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="W11">
         <v>2.1</v>
@@ -3235,7 +3235,7 @@
         <v>14.5</v>
       </c>
       <c r="Z11">
-        <v>100</v>
+        <v>48</v>
       </c>
       <c r="AA11">
         <v>900</v>
@@ -3244,7 +3244,7 @@
         <v>6.8</v>
       </c>
       <c r="AC11">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD11">
         <v>23</v>
@@ -3253,16 +3253,16 @@
         <v>260</v>
       </c>
       <c r="AF11">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AG11">
         <v>9.199999999999999</v>
       </c>
       <c r="AH11">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AI11">
-        <v>700</v>
+        <v>540</v>
       </c>
       <c r="AJ11">
         <v>21</v>
@@ -3271,28 +3271,28 @@
         <v>25</v>
       </c>
       <c r="AL11">
-        <v>120</v>
+        <v>65</v>
       </c>
       <c r="AM11">
         <v>580</v>
       </c>
       <c r="AN11">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AO11">
         <v>700</v>
       </c>
       <c r="AP11">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="AQ11">
         <v>12.5</v>
       </c>
       <c r="AR11">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AS11">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AT11">
         <v>6</v>
@@ -3304,43 +3304,43 @@
         <v>19.5</v>
       </c>
       <c r="AW11">
-        <v>15.5</v>
+        <v>55</v>
       </c>
       <c r="AX11">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AY11">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AZ11">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BA11">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BB11">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BC11">
         <v>21</v>
       </c>
       <c r="BD11">
-        <v>13.5</v>
+        <v>32</v>
       </c>
       <c r="BE11">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BF11">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="BG11">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BH11">
         <v>2.9</v>
       </c>
       <c r="BI11">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="BJ11">
         <v>12</v>
@@ -3352,13 +3352,13 @@
         <v>1000</v>
       </c>
       <c r="BM11">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BN11">
         <v>4.2</v>
       </c>
       <c r="BO11">
-        <v>3.3</v>
+        <v>3.75</v>
       </c>
       <c r="BP11">
         <v>14</v>
@@ -3367,7 +3367,7 @@
         <v>7.4</v>
       </c>
       <c r="BR11">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="BS11">
         <v>11</v>
@@ -3376,7 +3376,7 @@
         <v>9</v>
       </c>
       <c r="BU11">
-        <v>5.7</v>
+        <v>6.8</v>
       </c>
       <c r="BV11">
         <v>1000</v>
@@ -3417,220 +3417,220 @@
         <v>124</v>
       </c>
       <c r="F12">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="G12">
-        <v>10.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="H12">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="I12">
-        <v>1.64</v>
+        <v>1.69</v>
       </c>
       <c r="J12">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="K12">
-        <v>4.5</v>
+        <v>3.9</v>
       </c>
       <c r="L12">
         <v>1.5</v>
       </c>
       <c r="M12">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="N12">
-        <v>2.74</v>
+        <v>2.66</v>
       </c>
       <c r="O12">
         <v>1.46</v>
       </c>
       <c r="P12">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="Q12">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="R12">
         <v>1.2</v>
       </c>
       <c r="S12">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="T12">
+        <v>2.32</v>
+      </c>
+      <c r="U12">
+        <v>1.63</v>
+      </c>
+      <c r="V12">
         <v>2.46</v>
       </c>
-      <c r="U12">
-        <v>1.51</v>
-      </c>
-      <c r="V12">
-        <v>2.52</v>
-      </c>
       <c r="W12">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="X12">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="Y12">
         <v>6.2</v>
       </c>
       <c r="Z12">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="AA12">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AB12">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="AC12">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AD12">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AE12">
         <v>24</v>
       </c>
       <c r="AF12">
-        <v>90</v>
+        <v>65</v>
       </c>
       <c r="AG12">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="AH12">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AI12">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AJ12">
-        <v>520</v>
+        <v>370</v>
       </c>
       <c r="AK12">
-        <v>260</v>
+        <v>180</v>
       </c>
       <c r="AL12">
-        <v>260</v>
+        <v>220</v>
       </c>
       <c r="AM12">
-        <v>390</v>
+        <v>580</v>
       </c>
       <c r="AN12">
-        <v>580</v>
+        <v>310</v>
       </c>
       <c r="AO12">
-        <v>14</v>
+        <v>16.5</v>
       </c>
       <c r="AP12">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AQ12">
+        <v>5.3</v>
+      </c>
+      <c r="AR12">
+        <v>6.6</v>
+      </c>
+      <c r="AS12">
+        <v>13</v>
+      </c>
+      <c r="AT12">
+        <v>14.5</v>
+      </c>
+      <c r="AU12">
+        <v>8.4</v>
+      </c>
+      <c r="AV12">
+        <v>9.6</v>
+      </c>
+      <c r="AW12">
+        <v>18.5</v>
+      </c>
+      <c r="AX12">
+        <v>48</v>
+      </c>
+      <c r="AY12">
+        <v>23</v>
+      </c>
+      <c r="AZ12">
+        <v>25</v>
+      </c>
+      <c r="BA12">
+        <v>48</v>
+      </c>
+      <c r="BB12">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BC12">
+        <v>9</v>
+      </c>
+      <c r="BD12">
+        <v>8</v>
+      </c>
+      <c r="BE12">
         <v>8.199999999999999</v>
       </c>
-      <c r="AQ12">
-        <v>4.9</v>
-      </c>
-      <c r="AR12">
-        <v>6.2</v>
-      </c>
-      <c r="AS12">
-        <v>11</v>
-      </c>
-      <c r="AT12">
-        <v>16.5</v>
-      </c>
-      <c r="AU12">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AV12">
-        <v>9.4</v>
-      </c>
-      <c r="AW12">
-        <v>19</v>
-      </c>
-      <c r="AX12">
-        <v>38</v>
-      </c>
-      <c r="AY12">
-        <v>21</v>
-      </c>
-      <c r="AZ12">
-        <v>23</v>
-      </c>
-      <c r="BA12">
-        <v>29</v>
-      </c>
-      <c r="BB12">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BC12">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BD12">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BE12">
-        <v>8.4</v>
-      </c>
       <c r="BF12">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG12">
-        <v>10.5</v>
+        <v>6</v>
       </c>
       <c r="BH12">
         <v>3.1</v>
       </c>
       <c r="BI12">
-        <v>2.44</v>
+        <v>2.56</v>
       </c>
       <c r="BJ12">
-        <v>16</v>
+        <v>13.5</v>
       </c>
       <c r="BK12">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BL12">
         <v>1000</v>
       </c>
       <c r="BM12">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BN12">
-        <v>14.5</v>
+        <v>12</v>
       </c>
       <c r="BO12">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BP12">
         <v>1000</v>
       </c>
       <c r="BQ12">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BR12">
         <v>1000</v>
       </c>
       <c r="BS12">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BT12">
-        <v>3.75</v>
+        <v>4.1</v>
       </c>
       <c r="BU12">
-        <v>2.92</v>
+        <v>3.25</v>
       </c>
       <c r="BV12">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="BW12">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BX12">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BY12">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BZ12">
         <v>0</v>
@@ -3659,16 +3659,16 @@
         <v>125</v>
       </c>
       <c r="F13">
-        <v>2.46</v>
+        <v>2.56</v>
       </c>
       <c r="G13">
-        <v>2.52</v>
+        <v>2.6</v>
       </c>
       <c r="H13">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="I13">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="J13">
         <v>3.05</v>
@@ -3677,46 +3677,46 @@
         <v>3.1</v>
       </c>
       <c r="L13">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="M13">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="N13">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="O13">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="P13">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="Q13">
-        <v>2.78</v>
+        <v>2.84</v>
       </c>
       <c r="R13">
         <v>1.19</v>
       </c>
       <c r="S13">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="T13">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="U13">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="V13">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="W13">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="X13">
         <v>8.199999999999999</v>
       </c>
       <c r="Y13">
-        <v>9.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="Z13">
         <v>22</v>
@@ -3725,13 +3725,13 @@
         <v>80</v>
       </c>
       <c r="AB13">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="AC13">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AD13">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AE13">
         <v>60</v>
@@ -3740,16 +3740,16 @@
         <v>14</v>
       </c>
       <c r="AG13">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AH13">
         <v>25</v>
       </c>
       <c r="AI13">
-        <v>90</v>
+        <v>210</v>
       </c>
       <c r="AJ13">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AK13">
         <v>36</v>
@@ -3761,40 +3761,40 @@
         <v>990</v>
       </c>
       <c r="AN13">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AO13">
         <v>80</v>
       </c>
       <c r="AP13">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AQ13">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AR13">
         <v>20</v>
       </c>
       <c r="AS13">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="AT13">
         <v>7</v>
       </c>
       <c r="AU13">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AV13">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AW13">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AX13">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AY13">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AZ13">
         <v>22</v>
@@ -3803,10 +3803,10 @@
         <v>70</v>
       </c>
       <c r="BB13">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BC13">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BD13">
         <v>55</v>
@@ -3815,70 +3815,70 @@
         <v>75</v>
       </c>
       <c r="BF13">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BG13">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="BH13">
         <v>3.05</v>
       </c>
       <c r="BI13">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="BJ13">
         <v>11.5</v>
       </c>
       <c r="BK13">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BL13">
         <v>1000</v>
       </c>
       <c r="BM13">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN13">
         <v>5.1</v>
       </c>
       <c r="BO13">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BP13">
         <v>26</v>
       </c>
       <c r="BQ13">
+        <v>6.6</v>
+      </c>
+      <c r="BR13">
+        <v>60</v>
+      </c>
+      <c r="BS13">
+        <v>7.8</v>
+      </c>
+      <c r="BT13">
         <v>6.4</v>
-      </c>
-      <c r="BR13">
-        <v>55</v>
-      </c>
-      <c r="BS13">
-        <v>7.4</v>
-      </c>
-      <c r="BT13">
-        <v>6.6</v>
       </c>
       <c r="BU13">
         <v>5</v>
       </c>
       <c r="BV13">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="BW13">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BX13">
         <v>70</v>
       </c>
       <c r="BY13">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BZ13">
         <v>65</v>
       </c>
       <c r="CA13">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="CB13" t="s">
         <v>129</v>
@@ -3901,25 +3901,25 @@
         <v>126</v>
       </c>
       <c r="F14">
-        <v>1.8</v>
+        <v>1.71</v>
       </c>
       <c r="G14">
-        <v>1.88</v>
+        <v>1.77</v>
       </c>
       <c r="H14">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="I14">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="J14">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="K14">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="L14">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="M14">
         <v>1.09</v>
@@ -3931,28 +3931,28 @@
         <v>1.4</v>
       </c>
       <c r="P14">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="Q14">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="R14">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="S14">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="T14">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="U14">
         <v>1.79</v>
       </c>
       <c r="V14">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="W14">
-        <v>2.12</v>
+        <v>2.26</v>
       </c>
       <c r="X14">
         <v>12.5</v>
@@ -3961,25 +3961,25 @@
         <v>16.5</v>
       </c>
       <c r="Z14">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="AA14">
         <v>900</v>
       </c>
       <c r="AB14">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="AC14">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD14">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AE14">
         <v>110</v>
       </c>
       <c r="AF14">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AG14">
         <v>11</v>
@@ -3991,7 +3991,7 @@
         <v>120</v>
       </c>
       <c r="AJ14">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="AK14">
         <v>24</v>
@@ -4000,73 +4000,73 @@
         <v>55</v>
       </c>
       <c r="AM14">
-        <v>580</v>
+        <v>500</v>
       </c>
       <c r="AN14">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="AO14">
-        <v>160</v>
+        <v>600</v>
       </c>
       <c r="AP14">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AQ14">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AR14">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="AS14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AT14">
         <v>6</v>
       </c>
       <c r="AU14">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AV14">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="AW14">
-        <v>6.8</v>
+        <v>50</v>
       </c>
       <c r="AX14">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY14">
-        <v>6.2</v>
+        <v>9</v>
       </c>
       <c r="AZ14">
-        <v>11.5</v>
+        <v>18</v>
       </c>
       <c r="BA14">
-        <v>6.8</v>
+        <v>55</v>
       </c>
       <c r="BB14">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BC14">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BD14">
         <v>36</v>
       </c>
       <c r="BE14">
-        <v>7</v>
+        <v>8.4</v>
       </c>
       <c r="BF14">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BG14">
-        <v>6.8</v>
+        <v>8.4</v>
       </c>
       <c r="BH14">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="BI14">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="BJ14">
         <v>13.5</v>
@@ -4084,40 +4084,40 @@
         <v>4.9</v>
       </c>
       <c r="BO14">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="BP14">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="BQ14">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="BR14">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BS14">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BT14">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BU14">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="BV14">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="BW14">
         <v>4.6</v>
       </c>
       <c r="BX14">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="BY14">
         <v>4.6</v>
       </c>
       <c r="BZ14">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="CA14">
         <v>4.3</v>
@@ -4394,13 +4394,13 @@
         <v>2.64</v>
       </c>
       <c r="I16">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="J16">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K16">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="L16">
         <v>1.31</v>
@@ -4424,7 +4424,7 @@
         <v>1.57</v>
       </c>
       <c r="S16">
-        <v>2.58</v>
+        <v>2.54</v>
       </c>
       <c r="T16">
         <v>1.54</v>
@@ -4433,7 +4433,7 @@
         <v>2.5</v>
       </c>
       <c r="V16">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="W16">
         <v>1.51</v>
@@ -4442,49 +4442,49 @@
         <v>25</v>
       </c>
       <c r="Y16">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="Z16">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="AA16">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="AB16">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AC16">
         <v>9.199999999999999</v>
       </c>
       <c r="AD16">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="AE16">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AF16">
         <v>23</v>
       </c>
       <c r="AG16">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="AH16">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AI16">
+        <v>36</v>
+      </c>
+      <c r="AJ16">
+        <v>50</v>
+      </c>
+      <c r="AK16">
+        <v>32</v>
+      </c>
+      <c r="AL16">
         <v>34</v>
       </c>
-      <c r="AJ16">
-        <v>44</v>
-      </c>
-      <c r="AK16">
-        <v>26</v>
-      </c>
-      <c r="AL16">
-        <v>38</v>
-      </c>
       <c r="AM16">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AN16">
         <v>17.5</v>
@@ -4499,10 +4499,10 @@
         <v>13</v>
       </c>
       <c r="AR16">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="AS16">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="AT16">
         <v>14.5</v>
@@ -4514,7 +4514,7 @@
         <v>10.5</v>
       </c>
       <c r="AW16">
-        <v>18</v>
+        <v>4.7</v>
       </c>
       <c r="AX16">
         <v>18</v>
@@ -4526,7 +4526,7 @@
         <v>12</v>
       </c>
       <c r="BA16">
-        <v>5.9</v>
+        <v>4.9</v>
       </c>
       <c r="BB16">
         <v>32</v>
@@ -4535,10 +4535,10 @@
         <v>20</v>
       </c>
       <c r="BD16">
-        <v>24</v>
+        <v>4.8</v>
       </c>
       <c r="BE16">
-        <v>6.4</v>
+        <v>38</v>
       </c>
       <c r="BF16">
         <v>12</v>
@@ -4550,55 +4550,55 @@
         <v>4.8</v>
       </c>
       <c r="BI16">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="BJ16">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="BK16">
-        <v>3.3</v>
+        <v>5.7</v>
       </c>
       <c r="BL16">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="BM16">
-        <v>4.6</v>
+        <v>6.4</v>
       </c>
       <c r="BN16">
-        <v>7.2</v>
+        <v>6.4</v>
       </c>
       <c r="BO16">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="BP16">
-        <v>23</v>
+        <v>19.5</v>
       </c>
       <c r="BQ16">
-        <v>4</v>
+        <v>5.1</v>
       </c>
       <c r="BR16">
         <v>32</v>
       </c>
       <c r="BS16">
-        <v>4.2</v>
+        <v>5.7</v>
       </c>
       <c r="BT16">
-        <v>7.2</v>
+        <v>6.4</v>
       </c>
       <c r="BU16">
-        <v>4.6</v>
+        <v>5.2</v>
       </c>
       <c r="BV16">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="BW16">
-        <v>3.95</v>
+        <v>5.1</v>
       </c>
       <c r="BX16">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BY16">
-        <v>4.2</v>
+        <v>5.7</v>
       </c>
       <c r="BZ16">
         <v>0</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-06.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-06.xlsx
@@ -403,7 +403,7 @@
     <t>Always Ready</t>
   </si>
   <si>
-    <t>2026-08-06 08:08:29</t>
+    <t>2026-08-06 10:22:45</t>
   </si>
 </sst>
 </file>
@@ -997,64 +997,64 @@
         <v>114</v>
       </c>
       <c r="F2">
-        <v>1.89</v>
+        <v>1.95</v>
       </c>
       <c r="G2">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="H2">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="I2">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="J2">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="K2">
         <v>4.3</v>
       </c>
       <c r="L2">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="M2">
         <v>1.04</v>
       </c>
       <c r="N2">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="O2">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="P2">
+        <v>2.54</v>
+      </c>
+      <c r="Q2">
+        <v>1.6</v>
+      </c>
+      <c r="R2">
+        <v>1.6</v>
+      </c>
+      <c r="S2">
         <v>2.5</v>
       </c>
-      <c r="Q2">
-        <v>1.62</v>
-      </c>
-      <c r="R2">
-        <v>1.66</v>
-      </c>
-      <c r="S2">
-        <v>2.48</v>
-      </c>
       <c r="T2">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="U2">
         <v>2.5</v>
       </c>
       <c r="V2">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="W2">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="X2">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Y2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Z2">
         <v>34</v>
@@ -1063,7 +1063,7 @@
         <v>85</v>
       </c>
       <c r="AB2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AC2">
         <v>9.6</v>
@@ -1075,19 +1075,19 @@
         <v>42</v>
       </c>
       <c r="AF2">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AG2">
         <v>10.5</v>
       </c>
       <c r="AH2">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AI2">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AJ2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AK2">
         <v>18</v>
@@ -1096,43 +1096,43 @@
         <v>27</v>
       </c>
       <c r="AM2">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AN2">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AO2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AP2">
         <v>20</v>
       </c>
       <c r="AQ2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AR2">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AS2">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AT2">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AU2">
-        <v>7.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV2">
         <v>15</v>
       </c>
       <c r="AW2">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AX2">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AY2">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="AZ2">
         <v>14</v>
@@ -1141,76 +1141,76 @@
         <v>36</v>
       </c>
       <c r="BB2">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="BC2">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BD2">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BE2">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="BF2">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG2">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="BH2">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BI2">
-        <v>3.5</v>
+        <v>2.72</v>
       </c>
       <c r="BJ2">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BK2">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="BL2">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="BM2">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="BN2">
         <v>5.8</v>
       </c>
       <c r="BO2">
-        <v>4.1</v>
+        <v>2.94</v>
       </c>
       <c r="BP2">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BQ2">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="BR2">
         <v>25</v>
       </c>
       <c r="BS2">
+        <v>4.8</v>
+      </c>
+      <c r="BT2">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BU2">
+        <v>3.55</v>
+      </c>
+      <c r="BV2">
+        <v>32</v>
+      </c>
+      <c r="BW2">
+        <v>5</v>
+      </c>
+      <c r="BX2">
+        <v>38</v>
+      </c>
+      <c r="BY2">
         <v>5.1</v>
-      </c>
-      <c r="BT2">
-        <v>8</v>
-      </c>
-      <c r="BU2">
-        <v>6</v>
-      </c>
-      <c r="BV2">
-        <v>29</v>
-      </c>
-      <c r="BW2">
-        <v>5.2</v>
-      </c>
-      <c r="BX2">
-        <v>34</v>
-      </c>
-      <c r="BY2">
-        <v>5.4</v>
       </c>
       <c r="BZ2">
         <v>0</v>
@@ -1239,25 +1239,25 @@
         <v>115</v>
       </c>
       <c r="F3">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="G3">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="H3">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="I3">
         <v>6.4</v>
       </c>
       <c r="J3">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="K3">
         <v>3.65</v>
       </c>
       <c r="L3">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="M3">
         <v>1.11</v>
@@ -1269,22 +1269,22 @@
         <v>1.48</v>
       </c>
       <c r="P3">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="Q3">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="R3">
         <v>1.22</v>
       </c>
       <c r="S3">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="T3">
         <v>2.16</v>
       </c>
       <c r="U3">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="V3">
         <v>1.19</v>
@@ -1296,25 +1296,25 @@
         <v>10.5</v>
       </c>
       <c r="Y3">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="Z3">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AA3">
         <v>900</v>
       </c>
       <c r="AB3">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="AC3">
-        <v>8.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="AD3">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AE3">
-        <v>260</v>
+        <v>130</v>
       </c>
       <c r="AF3">
         <v>10.5</v>
@@ -1326,7 +1326,7 @@
         <v>28</v>
       </c>
       <c r="AI3">
-        <v>700</v>
+        <v>170</v>
       </c>
       <c r="AJ3">
         <v>22</v>
@@ -1335,7 +1335,7 @@
         <v>26</v>
       </c>
       <c r="AL3">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AM3">
         <v>580</v>
@@ -1344,115 +1344,115 @@
         <v>19.5</v>
       </c>
       <c r="AO3">
-        <v>320</v>
+        <v>300</v>
       </c>
       <c r="AP3">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AQ3">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AR3">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="AS3">
-        <v>10.5</v>
+        <v>17.5</v>
       </c>
       <c r="AT3">
-        <v>5.8</v>
+        <v>5.1</v>
       </c>
       <c r="AU3">
-        <v>7</v>
+        <v>6.2</v>
       </c>
       <c r="AV3">
-        <v>19.5</v>
+        <v>17</v>
       </c>
       <c r="AW3">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="AX3">
-        <v>8.800000000000001</v>
+        <v>7.2</v>
       </c>
       <c r="AY3">
-        <v>9.199999999999999</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AZ3">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="BA3">
-        <v>10</v>
+        <v>55</v>
       </c>
       <c r="BB3">
-        <v>18.5</v>
+        <v>14.5</v>
       </c>
       <c r="BC3">
-        <v>20</v>
+        <v>16.5</v>
       </c>
       <c r="BD3">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="BE3">
-        <v>10.5</v>
+        <v>28</v>
       </c>
       <c r="BF3">
-        <v>15.5</v>
+        <v>13</v>
       </c>
       <c r="BG3">
-        <v>10.5</v>
+        <v>14</v>
       </c>
       <c r="BH3">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="BI3">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="BJ3">
         <v>12.5</v>
       </c>
       <c r="BK3">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BN3">
         <v>4.3</v>
       </c>
       <c r="BO3">
-        <v>3.65</v>
+        <v>3</v>
       </c>
       <c r="BP3">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BQ3">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BR3">
         <v>38</v>
       </c>
       <c r="BS3">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BT3">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="BU3">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BV3">
         <v>65</v>
       </c>
       <c r="BW3">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BX3">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="BY3">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BZ3">
         <v>0</v>
@@ -1484,7 +1484,7 @@
         <v>1.51</v>
       </c>
       <c r="G4">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="H4">
         <v>5.7</v>
@@ -1502,13 +1502,13 @@
         <v>1.19</v>
       </c>
       <c r="M4">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N4">
         <v>9.199999999999999</v>
       </c>
       <c r="O4">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="P4">
         <v>3.75</v>
@@ -1517,13 +1517,13 @@
         <v>1.33</v>
       </c>
       <c r="R4">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="S4">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="T4">
-        <v>1.49</v>
+        <v>1.46</v>
       </c>
       <c r="U4">
         <v>2.8</v>
@@ -1532,40 +1532,40 @@
         <v>1.19</v>
       </c>
       <c r="W4">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="X4">
+        <v>55</v>
+      </c>
+      <c r="Y4">
+        <v>55</v>
+      </c>
+      <c r="Z4">
         <v>85</v>
-      </c>
-      <c r="Y4">
-        <v>48</v>
-      </c>
-      <c r="Z4">
-        <v>80</v>
       </c>
       <c r="AA4">
         <v>700</v>
       </c>
       <c r="AB4">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AC4">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AD4">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AE4">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="AF4">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AG4">
         <v>12.5</v>
       </c>
       <c r="AH4">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AI4">
         <v>55</v>
@@ -1577,130 +1577,130 @@
         <v>15</v>
       </c>
       <c r="AL4">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AM4">
         <v>65</v>
       </c>
       <c r="AN4">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="AO4">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AP4">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="AQ4">
-        <v>36</v>
+        <v>19.5</v>
       </c>
       <c r="AR4">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="AS4">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="AT4">
         <v>15.5</v>
       </c>
       <c r="AU4">
-        <v>13</v>
+        <v>10.5</v>
       </c>
       <c r="AV4">
         <v>21</v>
       </c>
       <c r="AW4">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AX4">
+        <v>11.5</v>
+      </c>
+      <c r="AY4">
+        <v>8.6</v>
+      </c>
+      <c r="AZ4">
         <v>14</v>
       </c>
-      <c r="AY4">
+      <c r="BA4">
+        <v>29</v>
+      </c>
+      <c r="BB4">
+        <v>12</v>
+      </c>
+      <c r="BC4">
         <v>10</v>
       </c>
-      <c r="AZ4">
-        <v>15</v>
-      </c>
-      <c r="BA4">
-        <v>32</v>
-      </c>
-      <c r="BB4">
-        <v>15.5</v>
-      </c>
-      <c r="BC4">
-        <v>12</v>
-      </c>
       <c r="BD4">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BE4">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="BF4">
-        <v>3.65</v>
+        <v>3.3</v>
       </c>
       <c r="BG4">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="BH4">
         <v>7</v>
       </c>
       <c r="BI4">
-        <v>4.8</v>
+        <v>3.35</v>
       </c>
       <c r="BJ4">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="BK4">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="BL4">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="BM4">
-        <v>6.2</v>
+        <v>5.8</v>
       </c>
       <c r="BN4">
-        <v>5.8</v>
+        <v>5.4</v>
       </c>
       <c r="BO4">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="BP4">
         <v>10.5</v>
       </c>
       <c r="BQ4">
-        <v>6.8</v>
+        <v>3.95</v>
       </c>
       <c r="BR4">
         <v>16.5</v>
       </c>
       <c r="BS4">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="BT4">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BU4">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="BV4">
         <v>38</v>
       </c>
       <c r="BW4">
-        <v>5.9</v>
+        <v>5.4</v>
       </c>
       <c r="BX4">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="BY4">
-        <v>5.8</v>
+        <v>5.3</v>
       </c>
       <c r="BZ4">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="CA4">
-        <v>6.8</v>
+        <v>3.8</v>
       </c>
       <c r="CB4" t="s">
         <v>129</v>
@@ -1723,16 +1723,16 @@
         <v>117</v>
       </c>
       <c r="F5">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="G5">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="H5">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="I5">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="J5">
         <v>3</v>
@@ -1747,76 +1747,76 @@
         <v>1.09</v>
       </c>
       <c r="N5">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="O5">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="P5">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="Q5">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="R5">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="S5">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="T5">
         <v>1.81</v>
       </c>
       <c r="U5">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="V5">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="W5">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="X5">
+        <v>14</v>
+      </c>
+      <c r="Y5">
         <v>13</v>
       </c>
-      <c r="Y5">
-        <v>11.5</v>
-      </c>
       <c r="Z5">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="AA5">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AB5">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AC5">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AD5">
         <v>14.5</v>
       </c>
       <c r="AE5">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="AF5">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AG5">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AH5">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AI5">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AJ5">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="AK5">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="AL5">
         <v>60</v>
@@ -1825,67 +1825,67 @@
         <v>130</v>
       </c>
       <c r="AN5">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AO5">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AP5">
+        <v>6.2</v>
+      </c>
+      <c r="AQ5">
+        <v>6.2</v>
+      </c>
+      <c r="AR5">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AS5">
+        <v>4.6</v>
+      </c>
+      <c r="AT5">
+        <v>4.9</v>
+      </c>
+      <c r="AU5">
+        <v>6</v>
+      </c>
+      <c r="AV5">
+        <v>6</v>
+      </c>
+      <c r="AW5">
+        <v>4.7</v>
+      </c>
+      <c r="AX5">
+        <v>6.4</v>
+      </c>
+      <c r="AY5">
+        <v>6.4</v>
+      </c>
+      <c r="AZ5">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BA5">
+        <v>4.7</v>
+      </c>
+      <c r="BB5">
+        <v>4.8</v>
+      </c>
+      <c r="BC5">
+        <v>7.4</v>
+      </c>
+      <c r="BD5">
+        <v>4.8</v>
+      </c>
+      <c r="BE5">
+        <v>4.8</v>
+      </c>
+      <c r="BF5">
+        <v>5</v>
+      </c>
+      <c r="BG5">
         <v>9.800000000000001</v>
       </c>
-      <c r="AQ5">
-        <v>9.6</v>
-      </c>
-      <c r="AR5">
-        <v>16.5</v>
-      </c>
-      <c r="AS5">
-        <v>34</v>
-      </c>
-      <c r="AT5">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AU5">
-        <v>6.2</v>
-      </c>
-      <c r="AV5">
-        <v>11</v>
-      </c>
-      <c r="AW5">
-        <v>25</v>
-      </c>
-      <c r="AX5">
-        <v>15</v>
-      </c>
-      <c r="AY5">
-        <v>10.5</v>
-      </c>
-      <c r="AZ5">
-        <v>14.5</v>
-      </c>
-      <c r="BA5">
-        <v>40</v>
-      </c>
-      <c r="BB5">
-        <v>29</v>
-      </c>
-      <c r="BC5">
-        <v>24</v>
-      </c>
-      <c r="BD5">
-        <v>38</v>
-      </c>
-      <c r="BE5">
-        <v>70</v>
-      </c>
-      <c r="BF5">
-        <v>23</v>
-      </c>
-      <c r="BG5">
-        <v>23</v>
-      </c>
       <c r="BH5">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="BI5">
         <v>2.54</v>
@@ -1894,55 +1894,55 @@
         <v>12</v>
       </c>
       <c r="BK5">
-        <v>3.4</v>
+        <v>3.85</v>
       </c>
       <c r="BL5">
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>4.6</v>
+        <v>5.5</v>
       </c>
       <c r="BN5">
-        <v>6.8</v>
+        <v>5.9</v>
       </c>
       <c r="BO5">
-        <v>4.8</v>
+        <v>2.9</v>
       </c>
       <c r="BP5">
         <v>27</v>
       </c>
       <c r="BQ5">
-        <v>4</v>
+        <v>4.7</v>
       </c>
       <c r="BR5">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="BS5">
-        <v>4.3</v>
+        <v>4.9</v>
       </c>
       <c r="BT5">
         <v>7</v>
       </c>
       <c r="BU5">
-        <v>4.5</v>
+        <v>3.1</v>
       </c>
       <c r="BV5">
         <v>29</v>
       </c>
       <c r="BW5">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="BX5">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="BY5">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="BZ5">
         <v>40</v>
       </c>
       <c r="CA5">
-        <v>4.2</v>
+        <v>4.9</v>
       </c>
       <c r="CB5" t="s">
         <v>129</v>
@@ -1965,22 +1965,22 @@
         <v>118</v>
       </c>
       <c r="F6">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="G6">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="H6">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="I6">
         <v>3.65</v>
       </c>
       <c r="J6">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="K6">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="L6">
         <v>1.41</v>
@@ -1989,22 +1989,22 @@
         <v>1.07</v>
       </c>
       <c r="N6">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="O6">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="P6">
         <v>1.99</v>
       </c>
       <c r="Q6">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="R6">
         <v>1.4</v>
       </c>
       <c r="S6">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="T6">
         <v>1.72</v>
@@ -2016,7 +2016,7 @@
         <v>1.37</v>
       </c>
       <c r="W6">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="X6">
         <v>15.5</v>
@@ -2025,7 +2025,7 @@
         <v>15</v>
       </c>
       <c r="Z6">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AA6">
         <v>75</v>
@@ -2034,19 +2034,19 @@
         <v>12</v>
       </c>
       <c r="AC6">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AD6">
-        <v>15.5</v>
+        <v>18</v>
       </c>
       <c r="AE6">
         <v>50</v>
       </c>
       <c r="AF6">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="AG6">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AH6">
         <v>17.5</v>
@@ -2058,16 +2058,16 @@
         <v>38</v>
       </c>
       <c r="AK6">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="AL6">
         <v>36</v>
       </c>
       <c r="AM6">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="AN6">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AO6">
         <v>42</v>
@@ -2076,109 +2076,109 @@
         <v>12.5</v>
       </c>
       <c r="AQ6">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AR6">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AS6">
         <v>46</v>
       </c>
       <c r="AT6">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AU6">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AV6">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AW6">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AX6">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AY6">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AZ6">
         <v>14.5</v>
       </c>
       <c r="BA6">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BB6">
         <v>22</v>
       </c>
       <c r="BC6">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="BD6">
         <v>27</v>
       </c>
       <c r="BE6">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="BF6">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BG6">
         <v>24</v>
       </c>
       <c r="BH6">
-        <v>4</v>
+        <v>3.45</v>
       </c>
       <c r="BI6">
-        <v>2.74</v>
+        <v>3.1</v>
       </c>
       <c r="BJ6">
-        <v>11.5</v>
+        <v>9.4</v>
       </c>
       <c r="BK6">
-        <v>7</v>
+        <v>5.1</v>
       </c>
       <c r="BL6">
         <v>140</v>
       </c>
       <c r="BM6">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BN6">
         <v>5.2</v>
       </c>
-      <c r="BN6">
-        <v>5.3</v>
-      </c>
       <c r="BO6">
-        <v>4</v>
+        <v>4.7</v>
       </c>
       <c r="BP6">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="BQ6">
-        <v>4.3</v>
+        <v>6.8</v>
       </c>
       <c r="BR6">
         <v>38</v>
       </c>
       <c r="BS6">
-        <v>4.7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT6">
-        <v>7.8</v>
+        <v>6.6</v>
       </c>
       <c r="BU6">
-        <v>5.8</v>
+        <v>4.9</v>
       </c>
       <c r="BV6">
         <v>34</v>
       </c>
       <c r="BW6">
-        <v>4.6</v>
+        <v>8</v>
       </c>
       <c r="BX6">
         <v>46</v>
       </c>
       <c r="BY6">
-        <v>4.8</v>
+        <v>8.6</v>
       </c>
       <c r="BZ6">
         <v>0</v>
@@ -2207,43 +2207,43 @@
         <v>119</v>
       </c>
       <c r="F7">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="G7">
         <v>2.48</v>
       </c>
       <c r="H7">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="I7">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="J7">
+        <v>3.5</v>
+      </c>
+      <c r="K7">
+        <v>3.75</v>
+      </c>
+      <c r="L7">
+        <v>1.43</v>
+      </c>
+      <c r="M7">
+        <v>1.08</v>
+      </c>
+      <c r="N7">
         <v>3.55</v>
-      </c>
-      <c r="K7">
-        <v>3.7</v>
-      </c>
-      <c r="L7">
-        <v>1.42</v>
-      </c>
-      <c r="M7">
-        <v>1.07</v>
-      </c>
-      <c r="N7">
-        <v>3.6</v>
       </c>
       <c r="O7">
         <v>1.34</v>
       </c>
       <c r="P7">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="Q7">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="R7">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="S7">
         <v>3.6</v>
@@ -2261,16 +2261,16 @@
         <v>1.68</v>
       </c>
       <c r="X7">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="Y7">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="Z7">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AA7">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AB7">
         <v>10.5</v>
@@ -2282,10 +2282,10 @@
         <v>14</v>
       </c>
       <c r="AE7">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AF7">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AG7">
         <v>12</v>
@@ -2294,13 +2294,13 @@
         <v>19</v>
       </c>
       <c r="AI7">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AJ7">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AK7">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AL7">
         <v>42</v>
@@ -2309,13 +2309,13 @@
         <v>110</v>
       </c>
       <c r="AN7">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AO7">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="AP7">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AQ7">
         <v>11</v>
@@ -2324,7 +2324,7 @@
         <v>19.5</v>
       </c>
       <c r="AS7">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AT7">
         <v>9</v>
@@ -2333,13 +2333,13 @@
         <v>7</v>
       </c>
       <c r="AV7">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AW7">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AX7">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AY7">
         <v>10</v>
@@ -2348,7 +2348,7 @@
         <v>15.5</v>
       </c>
       <c r="BA7">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="BB7">
         <v>29</v>
@@ -2360,73 +2360,73 @@
         <v>34</v>
       </c>
       <c r="BE7">
-        <v>11.5</v>
+        <v>75</v>
       </c>
       <c r="BF7">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="BG7">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="BH7">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="BI7">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="BJ7">
         <v>10</v>
       </c>
       <c r="BK7">
-        <v>5.1</v>
+        <v>4.8</v>
       </c>
       <c r="BL7">
         <v>1000</v>
       </c>
       <c r="BM7">
-        <v>9.6</v>
+        <v>2.5</v>
       </c>
       <c r="BN7">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BO7">
-        <v>4.1</v>
+        <v>3.45</v>
       </c>
       <c r="BP7">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BQ7">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="BR7">
         <v>34</v>
       </c>
       <c r="BS7">
-        <v>8</v>
+        <v>7.2</v>
       </c>
       <c r="BT7">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BU7">
-        <v>5.4</v>
+        <v>4</v>
       </c>
       <c r="BV7">
         <v>1000</v>
       </c>
       <c r="BW7">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="BX7">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BY7">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="BZ7">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="CA7">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="CB7" t="s">
         <v>129</v>
@@ -2449,52 +2449,52 @@
         <v>120</v>
       </c>
       <c r="F8">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="G8">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="H8">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="I8">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J8">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="K8">
         <v>7</v>
       </c>
       <c r="L8">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="M8">
         <v>1.05</v>
       </c>
       <c r="N8">
-        <v>4.1</v>
+        <v>3.55</v>
       </c>
       <c r="O8">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="P8">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="Q8">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="R8">
         <v>1.4</v>
       </c>
       <c r="S8">
-        <v>3.05</v>
+        <v>2.9</v>
       </c>
       <c r="T8">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="U8">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="V8">
         <v>1.05</v>
@@ -2503,52 +2503,52 @@
         <v>4.2</v>
       </c>
       <c r="X8">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="Y8">
-        <v>950</v>
+        <v>55</v>
       </c>
       <c r="Z8">
-        <v>190</v>
+        <v>220</v>
       </c>
       <c r="AA8">
         <v>1000</v>
       </c>
       <c r="AB8">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AC8">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="AD8">
         <v>160</v>
       </c>
       <c r="AE8">
-        <v>450</v>
+        <v>520</v>
       </c>
       <c r="AF8">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AG8">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AH8">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="AI8">
-        <v>330</v>
+        <v>380</v>
       </c>
       <c r="AJ8">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AK8">
         <v>17</v>
       </c>
       <c r="AL8">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="AM8">
-        <v>350</v>
+        <v>400</v>
       </c>
       <c r="AN8">
         <v>5.7</v>
@@ -2557,76 +2557,76 @@
         <v>1000</v>
       </c>
       <c r="AP8">
-        <v>15</v>
+        <v>5.7</v>
       </c>
       <c r="AQ8">
+        <v>7</v>
+      </c>
+      <c r="AR8">
+        <v>7.8</v>
+      </c>
+      <c r="AS8">
+        <v>8</v>
+      </c>
+      <c r="AT8">
+        <v>3.9</v>
+      </c>
+      <c r="AU8">
+        <v>5.6</v>
+      </c>
+      <c r="AV8">
         <v>7.4</v>
       </c>
-      <c r="AR8">
-        <v>8.6</v>
-      </c>
-      <c r="AS8">
-        <v>9</v>
-      </c>
-      <c r="AT8">
-        <v>6.2</v>
-      </c>
-      <c r="AU8">
-        <v>11.5</v>
-      </c>
-      <c r="AV8">
+      <c r="AW8">
         <v>8</v>
       </c>
-      <c r="AW8">
-        <v>9</v>
-      </c>
       <c r="AX8">
-        <v>6</v>
+        <v>3.75</v>
       </c>
       <c r="AY8">
-        <v>10</v>
+        <v>5.5</v>
       </c>
       <c r="AZ8">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="BA8">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="BB8">
+        <v>4.4</v>
+      </c>
+      <c r="BC8">
+        <v>5.5</v>
+      </c>
+      <c r="BD8">
+        <v>7.2</v>
+      </c>
+      <c r="BE8">
         <v>8</v>
       </c>
-      <c r="BC8">
-        <v>14</v>
-      </c>
-      <c r="BD8">
+      <c r="BF8">
+        <v>3.35</v>
+      </c>
+      <c r="BG8">
         <v>8</v>
       </c>
-      <c r="BE8">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BF8">
-        <v>4.9</v>
-      </c>
-      <c r="BG8">
-        <v>9</v>
-      </c>
       <c r="BH8">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BI8">
         <v>3</v>
       </c>
       <c r="BJ8">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BK8">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="BL8">
         <v>1000</v>
       </c>
       <c r="BM8">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BN8">
         <v>4</v>
@@ -2638,13 +2638,13 @@
         <v>8.6</v>
       </c>
       <c r="BQ8">
-        <v>5.4</v>
+        <v>3.1</v>
       </c>
       <c r="BR8">
         <v>36</v>
       </c>
       <c r="BS8">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BT8">
         <v>21</v>
@@ -2656,19 +2656,19 @@
         <v>1000</v>
       </c>
       <c r="BW8">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BX8">
         <v>1000</v>
       </c>
       <c r="BY8">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BZ8">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="CA8">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="CB8" t="s">
         <v>129</v>
@@ -2691,10 +2691,10 @@
         <v>121</v>
       </c>
       <c r="F9">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="G9">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="H9">
         <v>6</v>
@@ -2709,34 +2709,34 @@
         <v>3.55</v>
       </c>
       <c r="L9">
-        <v>1.59</v>
+        <v>1.53</v>
       </c>
       <c r="M9">
         <v>1.14</v>
       </c>
       <c r="N9">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="O9">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="P9">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="Q9">
-        <v>2.84</v>
+        <v>2.62</v>
       </c>
       <c r="R9">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="S9">
-        <v>6.2</v>
+        <v>1.05</v>
       </c>
       <c r="T9">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="U9">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="V9">
         <v>1.17</v>
@@ -2745,22 +2745,22 @@
         <v>2.2</v>
       </c>
       <c r="X9">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="Y9">
         <v>15</v>
       </c>
       <c r="Z9">
-        <v>55</v>
+        <v>150</v>
       </c>
       <c r="AA9">
         <v>900</v>
       </c>
       <c r="AB9">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="AC9">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AD9">
         <v>32</v>
@@ -2769,10 +2769,10 @@
         <v>500</v>
       </c>
       <c r="AF9">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AG9">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AH9">
         <v>36</v>
@@ -2781,85 +2781,85 @@
         <v>500</v>
       </c>
       <c r="AJ9">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AK9">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AL9">
-        <v>190</v>
+        <v>85</v>
       </c>
       <c r="AM9">
         <v>500</v>
       </c>
       <c r="AN9">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AO9">
-        <v>410</v>
+        <v>460</v>
       </c>
       <c r="AP9">
+        <v>4.2</v>
+      </c>
+      <c r="AQ9">
+        <v>5.8</v>
+      </c>
+      <c r="AR9">
+        <v>8</v>
+      </c>
+      <c r="AS9">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AT9">
+        <v>3.6</v>
+      </c>
+      <c r="AU9">
+        <v>4.5</v>
+      </c>
+      <c r="AV9">
+        <v>7.2</v>
+      </c>
+      <c r="AW9">
+        <v>9</v>
+      </c>
+      <c r="AX9">
+        <v>4.7</v>
+      </c>
+      <c r="AY9">
+        <v>5.4</v>
+      </c>
+      <c r="AZ9">
+        <v>7.4</v>
+      </c>
+      <c r="BA9">
+        <v>9</v>
+      </c>
+      <c r="BB9">
+        <v>6.6</v>
+      </c>
+      <c r="BC9">
+        <v>7.2</v>
+      </c>
+      <c r="BD9">
+        <v>8.4</v>
+      </c>
+      <c r="BE9">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BF9">
         <v>6.8</v>
       </c>
-      <c r="AQ9">
-        <v>12</v>
-      </c>
-      <c r="AR9">
-        <v>38</v>
-      </c>
-      <c r="AS9">
-        <v>10</v>
-      </c>
-      <c r="AT9">
-        <v>4.9</v>
-      </c>
-      <c r="AU9">
-        <v>7</v>
-      </c>
-      <c r="AV9">
-        <v>8</v>
-      </c>
-      <c r="AW9">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AX9">
-        <v>8</v>
-      </c>
-      <c r="AY9">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AZ9">
-        <v>15</v>
-      </c>
-      <c r="BA9">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BB9">
-        <v>17.5</v>
-      </c>
-      <c r="BC9">
-        <v>13</v>
-      </c>
-      <c r="BD9">
-        <v>9.4</v>
-      </c>
-      <c r="BE9">
-        <v>10</v>
-      </c>
-      <c r="BF9">
-        <v>20</v>
-      </c>
       <c r="BG9">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH9">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="BI9">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="BJ9">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BK9">
         <v>6.2</v>
@@ -2868,13 +2868,13 @@
         <v>1000</v>
       </c>
       <c r="BM9">
-        <v>11</v>
+        <v>2.1</v>
       </c>
       <c r="BN9">
         <v>4.2</v>
       </c>
       <c r="BO9">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="BP9">
         <v>15.5</v>
@@ -2883,10 +2883,10 @@
         <v>6.4</v>
       </c>
       <c r="BR9">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="BS9">
-        <v>9</v>
+        <v>2.04</v>
       </c>
       <c r="BT9">
         <v>10.5</v>
@@ -2898,19 +2898,19 @@
         <v>1000</v>
       </c>
       <c r="BW9">
-        <v>10</v>
+        <v>2.06</v>
       </c>
       <c r="BX9">
         <v>1000</v>
       </c>
       <c r="BY9">
-        <v>10</v>
+        <v>2.08</v>
       </c>
       <c r="BZ9">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="CA9">
-        <v>9</v>
+        <v>2.04</v>
       </c>
       <c r="CB9" t="s">
         <v>129</v>
@@ -2933,10 +2933,10 @@
         <v>122</v>
       </c>
       <c r="F10">
-        <v>2.34</v>
+        <v>2.42</v>
       </c>
       <c r="G10">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="H10">
         <v>3.2</v>
@@ -2951,127 +2951,127 @@
         <v>3.55</v>
       </c>
       <c r="L10">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="M10">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N10">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="O10">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="P10">
-        <v>1.88</v>
+        <v>1.84</v>
       </c>
       <c r="Q10">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="R10">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="S10">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="T10">
         <v>1.87</v>
       </c>
       <c r="U10">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="V10">
         <v>1.41</v>
       </c>
       <c r="W10">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="X10">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="Y10">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Z10">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AA10">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="AB10">
         <v>10.5</v>
       </c>
       <c r="AC10">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AD10">
         <v>14.5</v>
       </c>
       <c r="AE10">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AF10">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AG10">
         <v>12.5</v>
       </c>
       <c r="AH10">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AI10">
         <v>55</v>
       </c>
       <c r="AJ10">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AK10">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AL10">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="AM10">
         <v>580</v>
       </c>
       <c r="AN10">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AO10">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="AP10">
-        <v>11</v>
+        <v>9.6</v>
       </c>
       <c r="AQ10">
+        <v>10</v>
+      </c>
+      <c r="AR10">
+        <v>17</v>
+      </c>
+      <c r="AS10">
+        <v>40</v>
+      </c>
+      <c r="AT10">
+        <v>7.6</v>
+      </c>
+      <c r="AU10">
+        <v>5.8</v>
+      </c>
+      <c r="AV10">
         <v>10.5</v>
-      </c>
-      <c r="AR10">
-        <v>19</v>
-      </c>
-      <c r="AS10">
-        <v>42</v>
-      </c>
-      <c r="AT10">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AU10">
-        <v>6.8</v>
-      </c>
-      <c r="AV10">
-        <v>12</v>
       </c>
       <c r="AW10">
         <v>27</v>
       </c>
       <c r="AX10">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AY10">
-        <v>10</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ10">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BA10">
         <v>34</v>
@@ -3080,28 +3080,28 @@
         <v>23</v>
       </c>
       <c r="BC10">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BD10">
         <v>29</v>
       </c>
       <c r="BE10">
-        <v>70</v>
+        <v>28</v>
       </c>
       <c r="BF10">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="BG10">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BH10">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="BI10">
-        <v>2.64</v>
+        <v>2.58</v>
       </c>
       <c r="BJ10">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BK10">
         <v>5.2</v>
@@ -3110,43 +3110,43 @@
         <v>1000</v>
       </c>
       <c r="BM10">
-        <v>10</v>
+        <v>2.48</v>
       </c>
       <c r="BN10">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BO10">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="BP10">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="BQ10">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BR10">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BS10">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="BT10">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BU10">
-        <v>4.8</v>
+        <v>3.95</v>
       </c>
       <c r="BV10">
         <v>27</v>
       </c>
       <c r="BW10">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="BX10">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BY10">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ10">
         <v>0</v>
@@ -3175,52 +3175,52 @@
         <v>123</v>
       </c>
       <c r="F11">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="G11">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="H11">
         <v>5.2</v>
       </c>
       <c r="I11">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="J11">
         <v>3.35</v>
       </c>
       <c r="K11">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="L11">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="M11">
         <v>1.11</v>
       </c>
       <c r="N11">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="O11">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="P11">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="Q11">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="R11">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="S11">
         <v>4.9</v>
       </c>
       <c r="T11">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="U11">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="V11">
         <v>1.2</v>
@@ -3229,10 +3229,10 @@
         <v>2.1</v>
       </c>
       <c r="X11">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="Y11">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="Z11">
         <v>48</v>
@@ -3244,7 +3244,7 @@
         <v>6.8</v>
       </c>
       <c r="AC11">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AD11">
         <v>23</v>
@@ -3253,148 +3253,148 @@
         <v>260</v>
       </c>
       <c r="AF11">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AG11">
         <v>9.199999999999999</v>
       </c>
       <c r="AH11">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AI11">
         <v>540</v>
       </c>
       <c r="AJ11">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AK11">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AL11">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AM11">
         <v>580</v>
       </c>
       <c r="AN11">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AO11">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="AP11">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AQ11">
         <v>12.5</v>
       </c>
       <c r="AR11">
+        <v>24</v>
+      </c>
+      <c r="AS11">
+        <v>36</v>
+      </c>
+      <c r="AT11">
+        <v>4.9</v>
+      </c>
+      <c r="AU11">
+        <v>6.6</v>
+      </c>
+      <c r="AV11">
+        <v>17</v>
+      </c>
+      <c r="AW11">
         <v>29</v>
       </c>
-      <c r="AS11">
-        <v>17</v>
-      </c>
-      <c r="AT11">
-        <v>6</v>
-      </c>
-      <c r="AU11">
-        <v>7</v>
-      </c>
-      <c r="AV11">
-        <v>19.5</v>
-      </c>
-      <c r="AW11">
-        <v>55</v>
-      </c>
       <c r="AX11">
-        <v>9</v>
+        <v>7.8</v>
       </c>
       <c r="AY11">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="AZ11">
-        <v>22</v>
+        <v>15.5</v>
       </c>
       <c r="BA11">
-        <v>16</v>
+        <v>11.5</v>
       </c>
       <c r="BB11">
-        <v>18.5</v>
+        <v>15</v>
       </c>
       <c r="BC11">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="BD11">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BE11">
-        <v>17.5</v>
+        <v>12</v>
       </c>
       <c r="BF11">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="BG11">
-        <v>17.5</v>
+        <v>12</v>
       </c>
       <c r="BH11">
         <v>2.9</v>
       </c>
       <c r="BI11">
-        <v>2.46</v>
+        <v>2.38</v>
       </c>
       <c r="BJ11">
         <v>12</v>
       </c>
       <c r="BK11">
-        <v>8.4</v>
+        <v>6.4</v>
       </c>
       <c r="BL11">
         <v>1000</v>
       </c>
       <c r="BM11">
-        <v>15</v>
+        <v>2.36</v>
       </c>
       <c r="BN11">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BO11">
-        <v>3.75</v>
+        <v>3.25</v>
       </c>
       <c r="BP11">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BQ11">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="BR11">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BS11">
-        <v>11</v>
+        <v>2.24</v>
       </c>
       <c r="BT11">
         <v>9</v>
       </c>
       <c r="BU11">
-        <v>6.8</v>
+        <v>5.4</v>
       </c>
       <c r="BV11">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BW11">
-        <v>12.5</v>
+        <v>2.3</v>
       </c>
       <c r="BX11">
         <v>1000</v>
       </c>
       <c r="BY11">
-        <v>13</v>
+        <v>2.32</v>
       </c>
       <c r="BZ11">
         <v>36</v>
       </c>
       <c r="CA11">
-        <v>11</v>
+        <v>2.24</v>
       </c>
       <c r="CB11" t="s">
         <v>129</v>
@@ -3420,22 +3420,22 @@
         <v>6.2</v>
       </c>
       <c r="G12">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="H12">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="I12">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="J12">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="K12">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="L12">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="M12">
         <v>1.09</v>
@@ -3444,40 +3444,40 @@
         <v>2.66</v>
       </c>
       <c r="O12">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="P12">
         <v>1.56</v>
       </c>
       <c r="Q12">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="R12">
         <v>1.2</v>
       </c>
       <c r="S12">
-        <v>4.8</v>
+        <v>1.05</v>
       </c>
       <c r="T12">
-        <v>2.32</v>
+        <v>2.42</v>
       </c>
       <c r="U12">
-        <v>1.63</v>
+        <v>1.55</v>
       </c>
       <c r="V12">
         <v>2.46</v>
       </c>
       <c r="W12">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="X12">
         <v>11</v>
       </c>
       <c r="Y12">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="Z12">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AA12">
         <v>17</v>
@@ -3486,7 +3486,7 @@
         <v>18</v>
       </c>
       <c r="AC12">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AD12">
         <v>11</v>
@@ -3507,37 +3507,37 @@
         <v>70</v>
       </c>
       <c r="AJ12">
-        <v>370</v>
+        <v>900</v>
       </c>
       <c r="AK12">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="AL12">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="AM12">
         <v>580</v>
       </c>
       <c r="AN12">
-        <v>310</v>
+        <v>410</v>
       </c>
       <c r="AO12">
         <v>16.5</v>
       </c>
       <c r="AP12">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ12">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="AR12">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AS12">
-        <v>13</v>
+        <v>7.8</v>
       </c>
       <c r="AT12">
-        <v>14.5</v>
+        <v>6</v>
       </c>
       <c r="AU12">
         <v>8.4</v>
@@ -3546,91 +3546,91 @@
         <v>9.6</v>
       </c>
       <c r="AW12">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AX12">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="AY12">
-        <v>23</v>
+        <v>6.8</v>
       </c>
       <c r="AZ12">
         <v>25</v>
       </c>
       <c r="BA12">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="BB12">
-        <v>8.800000000000001</v>
+        <v>7.4</v>
       </c>
       <c r="BC12">
-        <v>9</v>
+        <v>7.2</v>
       </c>
       <c r="BD12">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE12">
-        <v>8.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="BF12">
-        <v>8.800000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="BG12">
-        <v>6</v>
+        <v>11.5</v>
       </c>
       <c r="BH12">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="BI12">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="BJ12">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="BK12">
-        <v>5.2</v>
+        <v>4.8</v>
       </c>
       <c r="BL12">
         <v>1000</v>
       </c>
       <c r="BM12">
-        <v>8.199999999999999</v>
+        <v>7</v>
       </c>
       <c r="BN12">
         <v>12</v>
       </c>
       <c r="BO12">
-        <v>5.3</v>
+        <v>4.8</v>
       </c>
       <c r="BP12">
         <v>1000</v>
       </c>
       <c r="BQ12">
-        <v>7.8</v>
+        <v>6.6</v>
       </c>
       <c r="BR12">
         <v>1000</v>
       </c>
       <c r="BS12">
-        <v>7.8</v>
+        <v>6.8</v>
       </c>
       <c r="BT12">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BU12">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="BV12">
         <v>12.5</v>
       </c>
       <c r="BW12">
-        <v>5.1</v>
+        <v>4.8</v>
       </c>
       <c r="BX12">
         <v>40</v>
       </c>
       <c r="BY12">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BZ12">
         <v>0</v>
@@ -3659,64 +3659,64 @@
         <v>125</v>
       </c>
       <c r="F13">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="G13">
         <v>2.6</v>
       </c>
       <c r="H13">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="I13">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="J13">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="K13">
         <v>3.1</v>
       </c>
       <c r="L13">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="M13">
         <v>1.14</v>
       </c>
       <c r="N13">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="O13">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="P13">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="Q13">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="R13">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="S13">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="T13">
         <v>2.22</v>
       </c>
       <c r="U13">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="V13">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="W13">
         <v>1.62</v>
       </c>
       <c r="X13">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="Y13">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z13">
         <v>22</v>
@@ -3725,13 +3725,13 @@
         <v>80</v>
       </c>
       <c r="AB13">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="AC13">
         <v>7</v>
       </c>
       <c r="AD13">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AE13">
         <v>60</v>
@@ -3746,49 +3746,49 @@
         <v>25</v>
       </c>
       <c r="AI13">
-        <v>210</v>
+        <v>90</v>
       </c>
       <c r="AJ13">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AK13">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AL13">
         <v>70</v>
       </c>
       <c r="AM13">
-        <v>990</v>
+        <v>500</v>
       </c>
       <c r="AN13">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AO13">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AP13">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AQ13">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AR13">
         <v>20</v>
       </c>
       <c r="AS13">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AT13">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AU13">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AV13">
         <v>14.5</v>
       </c>
       <c r="AW13">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AX13">
         <v>13</v>
@@ -3800,46 +3800,46 @@
         <v>22</v>
       </c>
       <c r="BA13">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="BB13">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BC13">
         <v>34</v>
       </c>
       <c r="BD13">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="BE13">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="BF13">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BG13">
-        <v>48</v>
+        <v>70</v>
       </c>
       <c r="BH13">
-        <v>3.05</v>
+        <v>2.96</v>
       </c>
       <c r="BI13">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="BJ13">
         <v>11.5</v>
       </c>
       <c r="BK13">
-        <v>5.1</v>
+        <v>8.4</v>
       </c>
       <c r="BL13">
         <v>1000</v>
       </c>
       <c r="BM13">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN13">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BO13">
         <v>4</v>
@@ -3848,13 +3848,13 @@
         <v>26</v>
       </c>
       <c r="BQ13">
-        <v>6.6</v>
+        <v>16</v>
       </c>
       <c r="BR13">
         <v>60</v>
       </c>
       <c r="BS13">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT13">
         <v>6.4</v>
@@ -3866,19 +3866,19 @@
         <v>36</v>
       </c>
       <c r="BW13">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BX13">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="BY13">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ13">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="CA13">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CB13" t="s">
         <v>129</v>
@@ -3901,226 +3901,226 @@
         <v>126</v>
       </c>
       <c r="F14">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="G14">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="H14">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="I14">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="J14">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="K14">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="L14">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="M14">
         <v>1.09</v>
       </c>
       <c r="N14">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="O14">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="P14">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="Q14">
-        <v>2.18</v>
+        <v>2.28</v>
       </c>
       <c r="R14">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="S14">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="T14">
-        <v>2.06</v>
+        <v>2.16</v>
       </c>
       <c r="U14">
-        <v>1.79</v>
+        <v>1.68</v>
       </c>
       <c r="V14">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="W14">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="X14">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="Y14">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="Z14">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AA14">
         <v>900</v>
       </c>
       <c r="AB14">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="AC14">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD14">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="AE14">
-        <v>110</v>
+        <v>160</v>
       </c>
       <c r="AF14">
-        <v>11</v>
+        <v>9.4</v>
       </c>
       <c r="AG14">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AH14">
         <v>34</v>
       </c>
       <c r="AI14">
-        <v>120</v>
+        <v>160</v>
       </c>
       <c r="AJ14">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AK14">
+        <v>23</v>
+      </c>
+      <c r="AL14">
+        <v>65</v>
+      </c>
+      <c r="AM14">
+        <v>580</v>
+      </c>
+      <c r="AN14">
+        <v>16</v>
+      </c>
+      <c r="AO14">
+        <v>260</v>
+      </c>
+      <c r="AP14">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AQ14">
+        <v>13.5</v>
+      </c>
+      <c r="AR14">
+        <v>22</v>
+      </c>
+      <c r="AS14">
+        <v>8.6</v>
+      </c>
+      <c r="AT14">
+        <v>5.4</v>
+      </c>
+      <c r="AU14">
+        <v>6.8</v>
+      </c>
+      <c r="AV14">
+        <v>17</v>
+      </c>
+      <c r="AW14">
+        <v>38</v>
+      </c>
+      <c r="AX14">
+        <v>7.2</v>
+      </c>
+      <c r="AY14">
+        <v>7.6</v>
+      </c>
+      <c r="AZ14">
+        <v>13</v>
+      </c>
+      <c r="BA14">
+        <v>28</v>
+      </c>
+      <c r="BB14">
+        <v>12.5</v>
+      </c>
+      <c r="BC14">
+        <v>16.5</v>
+      </c>
+      <c r="BD14">
         <v>24</v>
       </c>
-      <c r="AL14">
-        <v>55</v>
-      </c>
-      <c r="AM14">
-        <v>500</v>
-      </c>
-      <c r="AN14">
-        <v>14</v>
-      </c>
-      <c r="AO14">
-        <v>600</v>
-      </c>
-      <c r="AP14">
-        <v>9.6</v>
-      </c>
-      <c r="AQ14">
-        <v>14</v>
-      </c>
-      <c r="AR14">
-        <v>30</v>
-      </c>
-      <c r="AS14">
-        <v>8</v>
-      </c>
-      <c r="AT14">
-        <v>6</v>
-      </c>
-      <c r="AU14">
-        <v>7.4</v>
-      </c>
-      <c r="AV14">
-        <v>20</v>
-      </c>
-      <c r="AW14">
-        <v>50</v>
-      </c>
-      <c r="AX14">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AY14">
-        <v>9</v>
-      </c>
-      <c r="AZ14">
-        <v>18</v>
-      </c>
-      <c r="BA14">
-        <v>55</v>
-      </c>
-      <c r="BB14">
-        <v>15.5</v>
-      </c>
-      <c r="BC14">
-        <v>17.5</v>
-      </c>
-      <c r="BD14">
-        <v>36</v>
-      </c>
       <c r="BE14">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BF14">
+        <v>11.5</v>
+      </c>
+      <c r="BG14">
+        <v>7.6</v>
+      </c>
+      <c r="BH14">
+        <v>3.35</v>
+      </c>
+      <c r="BI14">
+        <v>2.38</v>
+      </c>
+      <c r="BJ14">
+        <v>14.5</v>
+      </c>
+      <c r="BK14">
+        <v>3.7</v>
+      </c>
+      <c r="BL14">
+        <v>1000</v>
+      </c>
+      <c r="BM14">
+        <v>4.9</v>
+      </c>
+      <c r="BN14">
+        <v>4.8</v>
+      </c>
+      <c r="BO14">
+        <v>2.44</v>
+      </c>
+      <c r="BP14">
+        <v>15</v>
+      </c>
+      <c r="BQ14">
+        <v>3.7</v>
+      </c>
+      <c r="BR14">
+        <v>44</v>
+      </c>
+      <c r="BS14">
+        <v>4.4</v>
+      </c>
+      <c r="BT14">
         <v>12</v>
       </c>
-      <c r="BG14">
-        <v>8.4</v>
-      </c>
-      <c r="BH14">
-        <v>3.6</v>
-      </c>
-      <c r="BI14">
-        <v>2.52</v>
-      </c>
-      <c r="BJ14">
-        <v>13.5</v>
-      </c>
-      <c r="BK14">
-        <v>3.6</v>
-      </c>
-      <c r="BL14">
-        <v>1000</v>
-      </c>
-      <c r="BM14">
-        <v>4.8</v>
-      </c>
-      <c r="BN14">
-        <v>4.9</v>
-      </c>
-      <c r="BO14">
-        <v>3.25</v>
-      </c>
-      <c r="BP14">
-        <v>14.5</v>
-      </c>
-      <c r="BQ14">
-        <v>3.65</v>
-      </c>
-      <c r="BR14">
+      <c r="BU14">
+        <v>3.5</v>
+      </c>
+      <c r="BV14">
+        <v>90</v>
+      </c>
+      <c r="BW14">
+        <v>4.7</v>
+      </c>
+      <c r="BX14">
+        <v>100</v>
+      </c>
+      <c r="BY14">
+        <v>4.7</v>
+      </c>
+      <c r="BZ14">
         <v>38</v>
       </c>
-      <c r="BS14">
-        <v>4.3</v>
-      </c>
-      <c r="BT14">
-        <v>11.5</v>
-      </c>
-      <c r="BU14">
-        <v>3.45</v>
-      </c>
-      <c r="BV14">
-        <v>75</v>
-      </c>
-      <c r="BW14">
-        <v>4.6</v>
-      </c>
-      <c r="BX14">
-        <v>85</v>
-      </c>
-      <c r="BY14">
-        <v>4.6</v>
-      </c>
-      <c r="BZ14">
-        <v>34</v>
-      </c>
       <c r="CA14">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="CB14" t="s">
         <v>129</v>
@@ -4385,220 +4385,220 @@
         <v>128</v>
       </c>
       <c r="F16">
-        <v>2.74</v>
+        <v>2.58</v>
       </c>
       <c r="G16">
-        <v>2.96</v>
+        <v>2.68</v>
       </c>
       <c r="H16">
-        <v>2.64</v>
+        <v>2.78</v>
       </c>
       <c r="I16">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="J16">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="K16">
-        <v>3.75</v>
+        <v>3.95</v>
       </c>
       <c r="L16">
         <v>1.31</v>
       </c>
       <c r="M16">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N16">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="O16">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="P16">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="Q16">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="R16">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="S16">
-        <v>2.54</v>
+        <v>2.66</v>
       </c>
       <c r="T16">
+        <v>1.61</v>
+      </c>
+      <c r="U16">
+        <v>2.56</v>
+      </c>
+      <c r="V16">
         <v>1.54</v>
       </c>
-      <c r="U16">
-        <v>2.5</v>
-      </c>
-      <c r="V16">
-        <v>1.55</v>
-      </c>
       <c r="W16">
-        <v>1.51</v>
+        <v>1.59</v>
       </c>
       <c r="X16">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="Y16">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="Z16">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AA16">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AB16">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="AC16">
         <v>9.199999999999999</v>
       </c>
       <c r="AD16">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="AE16">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AF16">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AG16">
-        <v>15.5</v>
+        <v>13</v>
       </c>
       <c r="AH16">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AI16">
         <v>36</v>
       </c>
       <c r="AJ16">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="AK16">
+        <v>24</v>
+      </c>
+      <c r="AL16">
         <v>32</v>
       </c>
-      <c r="AL16">
-        <v>34</v>
-      </c>
       <c r="AM16">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AN16">
-        <v>17.5</v>
+        <v>14</v>
       </c>
       <c r="AO16">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AP16">
+        <v>15.5</v>
+      </c>
+      <c r="AQ16">
+        <v>12</v>
+      </c>
+      <c r="AR16">
+        <v>17</v>
+      </c>
+      <c r="AS16">
+        <v>19</v>
+      </c>
+      <c r="AT16">
+        <v>11.5</v>
+      </c>
+      <c r="AU16">
+        <v>6.4</v>
+      </c>
+      <c r="AV16">
+        <v>9.6</v>
+      </c>
+      <c r="AW16">
+        <v>20</v>
+      </c>
+      <c r="AX16">
         <v>16.5</v>
       </c>
-      <c r="AQ16">
-        <v>13</v>
-      </c>
-      <c r="AR16">
-        <v>14.5</v>
-      </c>
-      <c r="AS16">
-        <v>26</v>
-      </c>
-      <c r="AT16">
-        <v>14.5</v>
-      </c>
-      <c r="AU16">
-        <v>7.4</v>
-      </c>
-      <c r="AV16">
-        <v>10.5</v>
-      </c>
-      <c r="AW16">
-        <v>4.7</v>
-      </c>
-      <c r="AX16">
-        <v>18</v>
-      </c>
       <c r="AY16">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="AZ16">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BA16">
-        <v>4.9</v>
+        <v>17</v>
       </c>
       <c r="BB16">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="BC16">
         <v>20</v>
       </c>
       <c r="BD16">
-        <v>4.8</v>
+        <v>16.5</v>
       </c>
       <c r="BE16">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BF16">
+        <v>11.5</v>
+      </c>
+      <c r="BG16">
         <v>12</v>
       </c>
-      <c r="BG16">
-        <v>12.5</v>
-      </c>
       <c r="BH16">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BI16">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="BJ16">
         <v>9</v>
       </c>
       <c r="BK16">
+        <v>4.4</v>
+      </c>
+      <c r="BL16">
+        <v>95</v>
+      </c>
+      <c r="BM16">
+        <v>7.8</v>
+      </c>
+      <c r="BN16">
+        <v>6</v>
+      </c>
+      <c r="BO16">
+        <v>3.5</v>
+      </c>
+      <c r="BP16">
+        <v>17.5</v>
+      </c>
+      <c r="BQ16">
         <v>5.7</v>
       </c>
-      <c r="BL16">
-        <v>100</v>
-      </c>
-      <c r="BM16">
+      <c r="BR16">
+        <v>26</v>
+      </c>
+      <c r="BS16">
         <v>6.4</v>
       </c>
-      <c r="BN16">
-        <v>6.4</v>
-      </c>
-      <c r="BO16">
-        <v>5.1</v>
-      </c>
-      <c r="BP16">
-        <v>19.5</v>
-      </c>
-      <c r="BQ16">
-        <v>5.1</v>
-      </c>
-      <c r="BR16">
-        <v>32</v>
-      </c>
-      <c r="BS16">
-        <v>5.7</v>
-      </c>
       <c r="BT16">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BU16">
-        <v>5.2</v>
+        <v>3.7</v>
       </c>
       <c r="BV16">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="BW16">
-        <v>5.1</v>
+        <v>6</v>
       </c>
       <c r="BX16">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="BY16">
-        <v>5.7</v>
+        <v>6.6</v>
       </c>
       <c r="BZ16">
         <v>0</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-06.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-06.xlsx
@@ -403,7 +403,7 @@
     <t>Always Ready</t>
   </si>
   <si>
-    <t>2026-08-06 10:22:45</t>
+    <t>2026-08-06 12:40:03</t>
   </si>
 </sst>
 </file>
@@ -997,94 +997,94 @@
         <v>114</v>
       </c>
       <c r="F2">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="G2">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="H2">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="I2">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="J2">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K2">
         <v>4.3</v>
       </c>
       <c r="L2">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="M2">
         <v>1.04</v>
       </c>
       <c r="N2">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="O2">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="P2">
-        <v>2.54</v>
+        <v>2.66</v>
       </c>
       <c r="Q2">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="R2">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="S2">
-        <v>2.5</v>
+        <v>2.42</v>
       </c>
       <c r="T2">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="U2">
-        <v>2.5</v>
+        <v>2.58</v>
       </c>
       <c r="V2">
         <v>1.32</v>
       </c>
       <c r="W2">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="X2">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="Y2">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Z2">
         <v>34</v>
       </c>
       <c r="AA2">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AB2">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AC2">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="AD2">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AE2">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AF2">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AG2">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AH2">
         <v>16</v>
       </c>
       <c r="AI2">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AJ2">
         <v>24</v>
@@ -1093,19 +1093,19 @@
         <v>18</v>
       </c>
       <c r="AL2">
+        <v>26</v>
+      </c>
+      <c r="AM2">
+        <v>60</v>
+      </c>
+      <c r="AN2">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AO2">
         <v>27</v>
       </c>
-      <c r="AM2">
-        <v>65</v>
-      </c>
-      <c r="AN2">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AO2">
-        <v>36</v>
-      </c>
       <c r="AP2">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AQ2">
         <v>19</v>
@@ -1114,22 +1114,22 @@
         <v>30</v>
       </c>
       <c r="AS2">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AT2">
-        <v>10.5</v>
+        <v>13</v>
       </c>
       <c r="AU2">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AV2">
         <v>15</v>
       </c>
       <c r="AW2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AX2">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AY2">
         <v>9.6</v>
@@ -1138,79 +1138,79 @@
         <v>14</v>
       </c>
       <c r="BA2">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BB2">
         <v>21</v>
       </c>
       <c r="BC2">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BD2">
+        <v>22</v>
+      </c>
+      <c r="BE2">
+        <v>48</v>
+      </c>
+      <c r="BF2">
+        <v>7.8</v>
+      </c>
+      <c r="BG2">
         <v>23</v>
       </c>
-      <c r="BE2">
-        <v>46</v>
-      </c>
-      <c r="BF2">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BG2">
-        <v>19</v>
-      </c>
       <c r="BH2">
-        <v>5</v>
+        <v>1000</v>
       </c>
       <c r="BI2">
-        <v>2.72</v>
+        <v>1.01</v>
       </c>
       <c r="BJ2">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="BK2">
-        <v>3.6</v>
+        <v>1.01</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>5.5</v>
+        <v>1.01</v>
       </c>
       <c r="BN2">
-        <v>5.8</v>
+        <v>1000</v>
       </c>
       <c r="BO2">
-        <v>2.94</v>
+        <v>1.01</v>
       </c>
       <c r="BP2">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ2">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="BR2">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="BS2">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="BT2">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="BU2">
-        <v>3.55</v>
+        <v>1.01</v>
       </c>
       <c r="BV2">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BW2">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="BX2">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="BY2">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="BZ2">
         <v>0</v>
@@ -1242,91 +1242,91 @@
         <v>1.8</v>
       </c>
       <c r="G3">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="H3">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="I3">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="J3">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K3">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="L3">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="M3">
         <v>1.11</v>
       </c>
       <c r="N3">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="O3">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="P3">
         <v>1.63</v>
       </c>
       <c r="Q3">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="R3">
         <v>1.22</v>
       </c>
       <c r="S3">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="T3">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="U3">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="V3">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="W3">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="X3">
         <v>10.5</v>
       </c>
       <c r="Y3">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="Z3">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AA3">
         <v>900</v>
       </c>
       <c r="AB3">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="AC3">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD3">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AE3">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AF3">
         <v>10.5</v>
       </c>
       <c r="AG3">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AH3">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AI3">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="AJ3">
         <v>22</v>
@@ -1344,115 +1344,115 @@
         <v>19.5</v>
       </c>
       <c r="AO3">
-        <v>300</v>
+        <v>270</v>
       </c>
       <c r="AP3">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ3">
         <v>12.5</v>
       </c>
       <c r="AR3">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="AS3">
-        <v>17.5</v>
+        <v>85</v>
       </c>
       <c r="AT3">
-        <v>5.1</v>
+        <v>5.8</v>
       </c>
       <c r="AU3">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="AV3">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AW3">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AX3">
-        <v>7.2</v>
+        <v>8.6</v>
       </c>
       <c r="AY3">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AZ3">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="BA3">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="BB3">
-        <v>14.5</v>
+        <v>18</v>
       </c>
       <c r="BC3">
-        <v>16.5</v>
+        <v>21</v>
       </c>
       <c r="BD3">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="BE3">
-        <v>28</v>
+        <v>90</v>
       </c>
       <c r="BF3">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BG3">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BH3">
-        <v>3.2</v>
+        <v>1000</v>
       </c>
       <c r="BI3">
-        <v>2.42</v>
+        <v>1.04</v>
       </c>
       <c r="BJ3">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="BK3">
-        <v>5</v>
+        <v>1.04</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>8</v>
+        <v>1.04</v>
       </c>
       <c r="BN3">
-        <v>4.3</v>
+        <v>1000</v>
       </c>
       <c r="BO3">
-        <v>3</v>
+        <v>1.04</v>
       </c>
       <c r="BP3">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ3">
-        <v>5.4</v>
+        <v>1.04</v>
       </c>
       <c r="BR3">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="BS3">
-        <v>6.8</v>
+        <v>1.04</v>
       </c>
       <c r="BT3">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="BU3">
-        <v>4.4</v>
+        <v>1.04</v>
       </c>
       <c r="BV3">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="BW3">
-        <v>7.4</v>
+        <v>1.04</v>
       </c>
       <c r="BX3">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="BY3">
-        <v>7.6</v>
+        <v>1.04</v>
       </c>
       <c r="BZ3">
         <v>0</v>
@@ -1484,25 +1484,25 @@
         <v>1.51</v>
       </c>
       <c r="G4">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="H4">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="I4">
         <v>6.2</v>
       </c>
       <c r="J4">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="K4">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="L4">
         <v>1.19</v>
       </c>
       <c r="M4">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="N4">
         <v>9.199999999999999</v>
@@ -1523,7 +1523,7 @@
         <v>1.82</v>
       </c>
       <c r="T4">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="U4">
         <v>2.8</v>
@@ -1532,13 +1532,13 @@
         <v>1.19</v>
       </c>
       <c r="W4">
-        <v>2.84</v>
+        <v>2.78</v>
       </c>
       <c r="X4">
         <v>55</v>
       </c>
       <c r="Y4">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="Z4">
         <v>85</v>
@@ -1556,7 +1556,7 @@
         <v>26</v>
       </c>
       <c r="AE4">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AF4">
         <v>17</v>
@@ -1586,121 +1586,121 @@
         <v>4.3</v>
       </c>
       <c r="AO4">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AP4">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="AQ4">
-        <v>19.5</v>
+        <v>36</v>
       </c>
       <c r="AR4">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="AS4">
-        <v>29</v>
+        <v>9.4</v>
       </c>
       <c r="AT4">
         <v>15.5</v>
       </c>
       <c r="AU4">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="AV4">
         <v>21</v>
       </c>
       <c r="AW4">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AX4">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="AY4">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="AZ4">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BA4">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="BB4">
+        <v>15</v>
+      </c>
+      <c r="BC4">
         <v>12</v>
       </c>
-      <c r="BC4">
-        <v>10</v>
-      </c>
       <c r="BD4">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BE4">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="BF4">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="BG4">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="BH4">
-        <v>7</v>
+        <v>1000</v>
       </c>
       <c r="BI4">
-        <v>3.35</v>
+        <v>1.04</v>
       </c>
       <c r="BJ4">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="BK4">
-        <v>3.95</v>
+        <v>1.04</v>
       </c>
       <c r="BL4">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="BM4">
-        <v>5.8</v>
+        <v>1.04</v>
       </c>
       <c r="BN4">
-        <v>5.4</v>
+        <v>1000</v>
       </c>
       <c r="BO4">
-        <v>4.1</v>
+        <v>1.04</v>
       </c>
       <c r="BP4">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ4">
-        <v>3.95</v>
+        <v>1.04</v>
       </c>
       <c r="BR4">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="BS4">
-        <v>4.6</v>
+        <v>1.04</v>
       </c>
       <c r="BT4">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="BU4">
-        <v>4.1</v>
+        <v>1.04</v>
       </c>
       <c r="BV4">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="BW4">
-        <v>5.4</v>
+        <v>1.04</v>
       </c>
       <c r="BX4">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="BY4">
-        <v>5.3</v>
+        <v>1.04</v>
       </c>
       <c r="BZ4">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="CA4">
-        <v>3.8</v>
+        <v>1.04</v>
       </c>
       <c r="CB4" t="s">
         <v>129</v>
@@ -1723,25 +1723,25 @@
         <v>117</v>
       </c>
       <c r="F5">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="G5">
+        <v>3</v>
+      </c>
+      <c r="H5">
+        <v>2.94</v>
+      </c>
+      <c r="I5">
+        <v>3.2</v>
+      </c>
+      <c r="J5">
         <v>2.92</v>
       </c>
-      <c r="H5">
-        <v>3</v>
-      </c>
-      <c r="I5">
-        <v>3.1</v>
-      </c>
-      <c r="J5">
-        <v>3</v>
-      </c>
       <c r="K5">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="L5">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="M5">
         <v>1.09</v>
@@ -1750,7 +1750,7 @@
         <v>3.35</v>
       </c>
       <c r="O5">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="P5">
         <v>1.78</v>
@@ -1759,37 +1759,37 @@
         <v>2.12</v>
       </c>
       <c r="R5">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="S5">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="T5">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="U5">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="V5">
         <v>1.47</v>
       </c>
       <c r="W5">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="X5">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="Y5">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Z5">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AA5">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AB5">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AC5">
         <v>7.6</v>
@@ -1798,25 +1798,25 @@
         <v>14.5</v>
       </c>
       <c r="AE5">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="AF5">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AG5">
         <v>14</v>
       </c>
       <c r="AH5">
-        <v>21</v>
+        <v>17.5</v>
       </c>
       <c r="AI5">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AJ5">
         <v>55</v>
       </c>
       <c r="AK5">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AL5">
         <v>60</v>
@@ -1825,64 +1825,64 @@
         <v>130</v>
       </c>
       <c r="AN5">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="AO5">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AP5">
-        <v>6.2</v>
+        <v>9</v>
       </c>
       <c r="AQ5">
-        <v>6.2</v>
+        <v>9.6</v>
       </c>
       <c r="AR5">
+        <v>15.5</v>
+      </c>
+      <c r="AS5">
+        <v>32</v>
+      </c>
+      <c r="AT5">
         <v>8.800000000000001</v>
-      </c>
-      <c r="AS5">
-        <v>4.6</v>
-      </c>
-      <c r="AT5">
-        <v>4.9</v>
       </c>
       <c r="AU5">
         <v>6</v>
       </c>
       <c r="AV5">
-        <v>6</v>
+        <v>9.6</v>
       </c>
       <c r="AW5">
-        <v>4.7</v>
+        <v>25</v>
       </c>
       <c r="AX5">
-        <v>6.4</v>
+        <v>15.5</v>
       </c>
       <c r="AY5">
-        <v>6.4</v>
+        <v>9.6</v>
       </c>
       <c r="AZ5">
-        <v>8.199999999999999</v>
+        <v>13</v>
       </c>
       <c r="BA5">
-        <v>4.7</v>
+        <v>34</v>
       </c>
       <c r="BB5">
-        <v>4.8</v>
+        <v>29</v>
       </c>
       <c r="BC5">
-        <v>7.4</v>
+        <v>25</v>
       </c>
       <c r="BD5">
-        <v>4.8</v>
+        <v>36</v>
       </c>
       <c r="BE5">
-        <v>4.8</v>
+        <v>29</v>
       </c>
       <c r="BF5">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="BG5">
-        <v>9.800000000000001</v>
+        <v>13.5</v>
       </c>
       <c r="BH5">
         <v>3.6</v>
@@ -1894,55 +1894,55 @@
         <v>12</v>
       </c>
       <c r="BK5">
-        <v>3.85</v>
+        <v>3.55</v>
       </c>
       <c r="BL5">
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>5.5</v>
+        <v>4.8</v>
       </c>
       <c r="BN5">
-        <v>5.9</v>
+        <v>7</v>
       </c>
       <c r="BO5">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="BP5">
+        <v>28</v>
+      </c>
+      <c r="BQ5">
+        <v>4.2</v>
+      </c>
+      <c r="BR5">
+        <v>48</v>
+      </c>
+      <c r="BS5">
+        <v>4.5</v>
+      </c>
+      <c r="BT5">
+        <v>6.6</v>
+      </c>
+      <c r="BU5">
+        <v>2.84</v>
+      </c>
+      <c r="BV5">
         <v>27</v>
       </c>
-      <c r="BQ5">
-        <v>4.7</v>
-      </c>
-      <c r="BR5">
-        <v>40</v>
-      </c>
-      <c r="BS5">
-        <v>4.9</v>
-      </c>
-      <c r="BT5">
-        <v>7</v>
-      </c>
-      <c r="BU5">
-        <v>3.1</v>
-      </c>
-      <c r="BV5">
-        <v>29</v>
-      </c>
       <c r="BW5">
-        <v>4.7</v>
+        <v>4.2</v>
       </c>
       <c r="BX5">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="BY5">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="BZ5">
         <v>40</v>
       </c>
       <c r="CA5">
-        <v>4.9</v>
+        <v>4.4</v>
       </c>
       <c r="CB5" t="s">
         <v>129</v>
@@ -1968,28 +1968,28 @@
         <v>2.3</v>
       </c>
       <c r="G6">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="H6">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="I6">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="J6">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="K6">
         <v>3.45</v>
       </c>
       <c r="L6">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="M6">
         <v>1.07</v>
       </c>
       <c r="N6">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="O6">
         <v>1.31</v>
@@ -1998,88 +1998,88 @@
         <v>1.99</v>
       </c>
       <c r="Q6">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="R6">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="S6">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="T6">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="U6">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="V6">
         <v>1.37</v>
       </c>
       <c r="W6">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="X6">
+        <v>15</v>
+      </c>
+      <c r="Y6">
+        <v>14.5</v>
+      </c>
+      <c r="Z6">
+        <v>27</v>
+      </c>
+      <c r="AA6">
+        <v>80</v>
+      </c>
+      <c r="AB6">
+        <v>10.5</v>
+      </c>
+      <c r="AC6">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD6">
         <v>15.5</v>
       </c>
-      <c r="Y6">
-        <v>15</v>
-      </c>
-      <c r="Z6">
+      <c r="AE6">
+        <v>55</v>
+      </c>
+      <c r="AF6">
+        <v>15.5</v>
+      </c>
+      <c r="AG6">
+        <v>11.5</v>
+      </c>
+      <c r="AH6">
+        <v>16.5</v>
+      </c>
+      <c r="AI6">
+        <v>65</v>
+      </c>
+      <c r="AJ6">
+        <v>32</v>
+      </c>
+      <c r="AK6">
         <v>25</v>
-      </c>
-      <c r="AA6">
-        <v>75</v>
-      </c>
-      <c r="AB6">
-        <v>12</v>
-      </c>
-      <c r="AC6">
-        <v>8</v>
-      </c>
-      <c r="AD6">
-        <v>18</v>
-      </c>
-      <c r="AE6">
-        <v>50</v>
-      </c>
-      <c r="AF6">
-        <v>16</v>
-      </c>
-      <c r="AG6">
-        <v>13</v>
-      </c>
-      <c r="AH6">
-        <v>17.5</v>
-      </c>
-      <c r="AI6">
-        <v>55</v>
-      </c>
-      <c r="AJ6">
-        <v>38</v>
-      </c>
-      <c r="AK6">
-        <v>26</v>
       </c>
       <c r="AL6">
         <v>36</v>
       </c>
       <c r="AM6">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AN6">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="AO6">
         <v>42</v>
       </c>
       <c r="AP6">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AQ6">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AR6">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AS6">
         <v>46</v>
@@ -2094,10 +2094,10 @@
         <v>13.5</v>
       </c>
       <c r="AW6">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AX6">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AY6">
         <v>10</v>
@@ -2112,7 +2112,7 @@
         <v>22</v>
       </c>
       <c r="BC6">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="BD6">
         <v>27</v>
@@ -2121,64 +2121,64 @@
         <v>60</v>
       </c>
       <c r="BF6">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="BG6">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BH6">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="BI6">
-        <v>3.1</v>
+        <v>2.76</v>
       </c>
       <c r="BJ6">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BK6">
-        <v>5.1</v>
+        <v>4.2</v>
       </c>
       <c r="BL6">
         <v>140</v>
       </c>
       <c r="BM6">
-        <v>9.800000000000001</v>
+        <v>6.4</v>
       </c>
       <c r="BN6">
-        <v>5.2</v>
+        <v>6.2</v>
       </c>
       <c r="BO6">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BP6">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BQ6">
-        <v>6.8</v>
+        <v>5</v>
       </c>
       <c r="BR6">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="BS6">
-        <v>8.199999999999999</v>
+        <v>5.6</v>
       </c>
       <c r="BT6">
-        <v>6.6</v>
+        <v>8</v>
       </c>
       <c r="BU6">
-        <v>4.9</v>
+        <v>5.9</v>
       </c>
       <c r="BV6">
         <v>34</v>
       </c>
       <c r="BW6">
-        <v>8</v>
+        <v>5.5</v>
       </c>
       <c r="BX6">
         <v>46</v>
       </c>
       <c r="BY6">
-        <v>8.6</v>
+        <v>5.9</v>
       </c>
       <c r="BZ6">
         <v>0</v>
@@ -2207,73 +2207,73 @@
         <v>119</v>
       </c>
       <c r="F7">
+        <v>2.28</v>
+      </c>
+      <c r="G7">
         <v>2.36</v>
       </c>
-      <c r="G7">
-        <v>2.48</v>
-      </c>
       <c r="H7">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="I7">
         <v>3.35</v>
       </c>
       <c r="J7">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="K7">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="L7">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="M7">
         <v>1.08</v>
       </c>
       <c r="N7">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="O7">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="P7">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="Q7">
         <v>2.02</v>
       </c>
       <c r="R7">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="S7">
         <v>3.6</v>
       </c>
       <c r="T7">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="U7">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="V7">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="W7">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="X7">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="Y7">
         <v>13</v>
       </c>
       <c r="Z7">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AA7">
         <v>65</v>
       </c>
       <c r="AB7">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AC7">
         <v>8.4</v>
@@ -2282,13 +2282,13 @@
         <v>14</v>
       </c>
       <c r="AE7">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AF7">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AG7">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AH7">
         <v>19</v>
@@ -2297,10 +2297,10 @@
         <v>55</v>
       </c>
       <c r="AJ7">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AK7">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AL7">
         <v>42</v>
@@ -2309,52 +2309,52 @@
         <v>110</v>
       </c>
       <c r="AN7">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AO7">
         <v>42</v>
       </c>
       <c r="AP7">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ7">
         <v>11</v>
       </c>
       <c r="AR7">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AS7">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AT7">
         <v>9</v>
       </c>
       <c r="AU7">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AV7">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AW7">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="AX7">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AY7">
         <v>10</v>
       </c>
       <c r="AZ7">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="BA7">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="BB7">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="BC7">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BD7">
         <v>34</v>
@@ -2363,13 +2363,13 @@
         <v>75</v>
       </c>
       <c r="BF7">
-        <v>15</v>
+        <v>17.5</v>
       </c>
       <c r="BG7">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="BH7">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="BI7">
         <v>2.68</v>
@@ -2378,55 +2378,55 @@
         <v>10</v>
       </c>
       <c r="BK7">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="BL7">
         <v>1000</v>
       </c>
       <c r="BM7">
-        <v>2.5</v>
+        <v>10</v>
       </c>
       <c r="BN7">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="BO7">
-        <v>3.45</v>
+        <v>3.95</v>
       </c>
       <c r="BP7">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="BQ7">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BR7">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BS7">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT7">
         <v>7</v>
       </c>
       <c r="BU7">
-        <v>4</v>
+        <v>5.1</v>
       </c>
       <c r="BV7">
         <v>1000</v>
       </c>
       <c r="BW7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BX7">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="BY7">
-        <v>7.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ7">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="CA7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="CB7" t="s">
         <v>129</v>
@@ -2449,67 +2449,67 @@
         <v>120</v>
       </c>
       <c r="F8">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="G8">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="H8">
-        <v>13</v>
+        <v>15.5</v>
       </c>
       <c r="I8">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J8">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="K8">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="L8">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="M8">
         <v>1.05</v>
       </c>
       <c r="N8">
-        <v>3.55</v>
+        <v>4.2</v>
       </c>
       <c r="O8">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="P8">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="Q8">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="R8">
         <v>1.4</v>
       </c>
       <c r="S8">
-        <v>2.9</v>
+        <v>3.05</v>
       </c>
       <c r="T8">
-        <v>2.52</v>
+        <v>2.46</v>
       </c>
       <c r="U8">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="V8">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="W8">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="X8">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="Y8">
         <v>55</v>
       </c>
       <c r="Z8">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="AA8">
         <v>1000</v>
@@ -2518,13 +2518,13 @@
         <v>7.6</v>
       </c>
       <c r="AC8">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AD8">
-        <v>160</v>
+        <v>75</v>
       </c>
       <c r="AE8">
-        <v>520</v>
+        <v>460</v>
       </c>
       <c r="AF8">
         <v>7</v>
@@ -2533,10 +2533,10 @@
         <v>12.5</v>
       </c>
       <c r="AH8">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AI8">
-        <v>380</v>
+        <v>340</v>
       </c>
       <c r="AJ8">
         <v>9.199999999999999</v>
@@ -2545,130 +2545,130 @@
         <v>17</v>
       </c>
       <c r="AL8">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AM8">
-        <v>400</v>
+        <v>370</v>
       </c>
       <c r="AN8">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="AO8">
         <v>1000</v>
       </c>
       <c r="AP8">
-        <v>5.7</v>
+        <v>15.5</v>
       </c>
       <c r="AQ8">
-        <v>7</v>
+        <v>19.5</v>
       </c>
       <c r="AR8">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AS8">
+        <v>9.6</v>
+      </c>
+      <c r="AT8">
+        <v>6.2</v>
+      </c>
+      <c r="AU8">
+        <v>12</v>
+      </c>
+      <c r="AV8">
+        <v>27</v>
+      </c>
+      <c r="AW8">
+        <v>9.6</v>
+      </c>
+      <c r="AX8">
+        <v>5.9</v>
+      </c>
+      <c r="AY8">
+        <v>10</v>
+      </c>
+      <c r="AZ8">
+        <v>8.4</v>
+      </c>
+      <c r="BA8">
+        <v>9.6</v>
+      </c>
+      <c r="BB8">
         <v>7.8</v>
       </c>
-      <c r="AS8">
-        <v>8</v>
-      </c>
-      <c r="AT8">
-        <v>3.9</v>
-      </c>
-      <c r="AU8">
-        <v>5.6</v>
-      </c>
-      <c r="AV8">
-        <v>7.4</v>
-      </c>
-      <c r="AW8">
-        <v>8</v>
-      </c>
-      <c r="AX8">
-        <v>3.75</v>
-      </c>
-      <c r="AY8">
-        <v>5.5</v>
-      </c>
-      <c r="AZ8">
-        <v>7.2</v>
-      </c>
-      <c r="BA8">
-        <v>8</v>
-      </c>
-      <c r="BB8">
-        <v>4.4</v>
-      </c>
       <c r="BC8">
-        <v>5.5</v>
+        <v>13.5</v>
       </c>
       <c r="BD8">
-        <v>7.2</v>
+        <v>25</v>
       </c>
       <c r="BE8">
-        <v>8</v>
+        <v>9.6</v>
       </c>
       <c r="BF8">
-        <v>3.35</v>
+        <v>4.8</v>
       </c>
       <c r="BG8">
-        <v>8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH8">
-        <v>4.5</v>
+        <v>1000</v>
       </c>
       <c r="BI8">
-        <v>3</v>
+        <v>1.04</v>
       </c>
       <c r="BJ8">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="BK8">
-        <v>3.85</v>
+        <v>1.04</v>
       </c>
       <c r="BL8">
         <v>1000</v>
       </c>
       <c r="BM8">
-        <v>4.8</v>
+        <v>1.04</v>
       </c>
       <c r="BN8">
-        <v>4</v>
+        <v>1000</v>
       </c>
       <c r="BO8">
-        <v>2.76</v>
+        <v>1.04</v>
       </c>
       <c r="BP8">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="BQ8">
-        <v>3.1</v>
+        <v>1.04</v>
       </c>
       <c r="BR8">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="BS8">
-        <v>4.3</v>
+        <v>1.04</v>
       </c>
       <c r="BT8">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="BU8">
-        <v>4</v>
+        <v>1.04</v>
       </c>
       <c r="BV8">
         <v>1000</v>
       </c>
       <c r="BW8">
-        <v>4.8</v>
+        <v>1.04</v>
       </c>
       <c r="BX8">
         <v>1000</v>
       </c>
       <c r="BY8">
-        <v>4.8</v>
+        <v>1.04</v>
       </c>
       <c r="BZ8">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="CA8">
-        <v>3.7</v>
+        <v>1.04</v>
       </c>
       <c r="CB8" t="s">
         <v>129</v>
@@ -2691,88 +2691,88 @@
         <v>121</v>
       </c>
       <c r="F9">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="G9">
-        <v>1.82</v>
+        <v>1.88</v>
       </c>
       <c r="H9">
         <v>6</v>
       </c>
       <c r="I9">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="J9">
+        <v>3.1</v>
+      </c>
+      <c r="K9">
         <v>3.5</v>
       </c>
-      <c r="K9">
-        <v>3.55</v>
-      </c>
       <c r="L9">
-        <v>1.53</v>
+        <v>1.66</v>
       </c>
       <c r="M9">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="N9">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="O9">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="P9">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="Q9">
-        <v>2.62</v>
+        <v>2.92</v>
       </c>
       <c r="R9">
         <v>1.17</v>
       </c>
       <c r="S9">
-        <v>1.05</v>
+        <v>6.2</v>
       </c>
       <c r="T9">
         <v>2.5</v>
       </c>
       <c r="U9">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="V9">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="W9">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="X9">
         <v>7.8</v>
       </c>
       <c r="Y9">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="Z9">
-        <v>150</v>
+        <v>55</v>
       </c>
       <c r="AA9">
         <v>900</v>
       </c>
       <c r="AB9">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="AC9">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD9">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AE9">
         <v>500</v>
       </c>
       <c r="AF9">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AG9">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH9">
         <v>36</v>
@@ -2787,7 +2787,7 @@
         <v>32</v>
       </c>
       <c r="AL9">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AM9">
         <v>500</v>
@@ -2796,70 +2796,70 @@
         <v>26</v>
       </c>
       <c r="AO9">
-        <v>460</v>
+        <v>410</v>
       </c>
       <c r="AP9">
-        <v>4.2</v>
+        <v>6.6</v>
       </c>
       <c r="AQ9">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="AR9">
+        <v>9</v>
+      </c>
+      <c r="AS9">
+        <v>10</v>
+      </c>
+      <c r="AT9">
+        <v>4.8</v>
+      </c>
+      <c r="AU9">
+        <v>7</v>
+      </c>
+      <c r="AV9">
         <v>8</v>
       </c>
-      <c r="AS9">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AT9">
-        <v>3.6</v>
-      </c>
-      <c r="AU9">
-        <v>4.5</v>
-      </c>
-      <c r="AV9">
-        <v>7.2</v>
-      </c>
       <c r="AW9">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AX9">
-        <v>4.7</v>
+        <v>8</v>
       </c>
       <c r="AY9">
-        <v>5.4</v>
+        <v>10</v>
       </c>
       <c r="AZ9">
-        <v>7.4</v>
+        <v>15</v>
       </c>
       <c r="BA9">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BB9">
-        <v>6.6</v>
+        <v>18</v>
       </c>
       <c r="BC9">
-        <v>7.2</v>
+        <v>13</v>
       </c>
       <c r="BD9">
-        <v>8.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BE9">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="BF9">
-        <v>6.8</v>
+        <v>21</v>
       </c>
       <c r="BG9">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="BH9">
-        <v>2.62</v>
+        <v>2.52</v>
       </c>
       <c r="BI9">
-        <v>2.12</v>
+        <v>2.06</v>
       </c>
       <c r="BJ9">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BK9">
         <v>6.2</v>
@@ -2868,49 +2868,49 @@
         <v>1000</v>
       </c>
       <c r="BM9">
-        <v>2.1</v>
+        <v>10.5</v>
       </c>
       <c r="BN9">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="BO9">
-        <v>3.05</v>
+        <v>3.45</v>
       </c>
       <c r="BP9">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="BQ9">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BR9">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BS9">
-        <v>2.04</v>
+        <v>9.4</v>
       </c>
       <c r="BT9">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="BU9">
-        <v>5.4</v>
+        <v>5.1</v>
       </c>
       <c r="BV9">
         <v>1000</v>
       </c>
       <c r="BW9">
-        <v>2.06</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BX9">
         <v>1000</v>
       </c>
       <c r="BY9">
-        <v>2.08</v>
+        <v>10</v>
       </c>
       <c r="BZ9">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="CA9">
-        <v>2.04</v>
+        <v>9.4</v>
       </c>
       <c r="CB9" t="s">
         <v>129</v>
@@ -2933,16 +2933,16 @@
         <v>122</v>
       </c>
       <c r="F10">
-        <v>2.42</v>
+        <v>2.34</v>
       </c>
       <c r="G10">
         <v>2.5</v>
       </c>
       <c r="H10">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="I10">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="J10">
         <v>3.4</v>
@@ -2957,10 +2957,10 @@
         <v>1.08</v>
       </c>
       <c r="N10">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="O10">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="P10">
         <v>1.84</v>
@@ -2969,22 +2969,22 @@
         <v>2.06</v>
       </c>
       <c r="R10">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="S10">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="T10">
         <v>1.87</v>
       </c>
       <c r="U10">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="V10">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="W10">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="X10">
         <v>13.5</v>
@@ -2996,10 +2996,10 @@
         <v>23</v>
       </c>
       <c r="AA10">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="AB10">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AC10">
         <v>8</v>
@@ -3011,7 +3011,7 @@
         <v>42</v>
       </c>
       <c r="AF10">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AG10">
         <v>12.5</v>
@@ -3023,58 +3023,58 @@
         <v>55</v>
       </c>
       <c r="AJ10">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AK10">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AL10">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AM10">
         <v>580</v>
       </c>
       <c r="AN10">
+        <v>25</v>
+      </c>
+      <c r="AO10">
+        <v>42</v>
+      </c>
+      <c r="AP10">
+        <v>11</v>
+      </c>
+      <c r="AQ10">
+        <v>9.6</v>
+      </c>
+      <c r="AR10">
+        <v>17.5</v>
+      </c>
+      <c r="AS10">
         <v>27</v>
       </c>
-      <c r="AO10">
-        <v>40</v>
-      </c>
-      <c r="AP10">
-        <v>9.6</v>
-      </c>
-      <c r="AQ10">
-        <v>10</v>
-      </c>
-      <c r="AR10">
-        <v>17</v>
-      </c>
-      <c r="AS10">
-        <v>40</v>
-      </c>
       <c r="AT10">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU10">
         <v>5.8</v>
       </c>
       <c r="AV10">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AW10">
         <v>27</v>
       </c>
       <c r="AX10">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="AY10">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AZ10">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="BA10">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="BB10">
         <v>23</v>
@@ -3083,70 +3083,70 @@
         <v>20</v>
       </c>
       <c r="BD10">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BE10">
-        <v>28</v>
+        <v>75</v>
       </c>
       <c r="BF10">
-        <v>16</v>
+        <v>19.5</v>
       </c>
       <c r="BG10">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BH10">
-        <v>3.35</v>
+        <v>1000</v>
       </c>
       <c r="BI10">
-        <v>2.58</v>
+        <v>1.04</v>
       </c>
       <c r="BJ10">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="BK10">
-        <v>5.2</v>
+        <v>1.04</v>
       </c>
       <c r="BL10">
         <v>1000</v>
       </c>
       <c r="BM10">
-        <v>2.48</v>
+        <v>1.04</v>
       </c>
       <c r="BN10">
-        <v>5.6</v>
+        <v>1000</v>
       </c>
       <c r="BO10">
-        <v>3.6</v>
+        <v>1.04</v>
       </c>
       <c r="BP10">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="BQ10">
-        <v>6.8</v>
+        <v>1.04</v>
       </c>
       <c r="BR10">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="BS10">
-        <v>8</v>
+        <v>1.04</v>
       </c>
       <c r="BT10">
-        <v>6.4</v>
+        <v>1000</v>
       </c>
       <c r="BU10">
-        <v>3.95</v>
+        <v>1.04</v>
       </c>
       <c r="BV10">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="BW10">
-        <v>7.4</v>
+        <v>1.04</v>
       </c>
       <c r="BX10">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="BY10">
-        <v>8.199999999999999</v>
+        <v>1.04</v>
       </c>
       <c r="BZ10">
         <v>0</v>
@@ -3175,67 +3175,67 @@
         <v>123</v>
       </c>
       <c r="F11">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="G11">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="H11">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="I11">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="J11">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K11">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="L11">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="M11">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="N11">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="O11">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="P11">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="Q11">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="R11">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="S11">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="T11">
         <v>2.14</v>
       </c>
       <c r="U11">
-        <v>1.74</v>
+        <v>1.77</v>
       </c>
       <c r="V11">
         <v>1.2</v>
       </c>
       <c r="W11">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="X11">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="Y11">
         <v>15</v>
       </c>
       <c r="Z11">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AA11">
         <v>900</v>
@@ -3244,7 +3244,7 @@
         <v>6.8</v>
       </c>
       <c r="AC11">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD11">
         <v>23</v>
@@ -3253,22 +3253,22 @@
         <v>260</v>
       </c>
       <c r="AF11">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AG11">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AH11">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AI11">
-        <v>540</v>
+        <v>260</v>
       </c>
       <c r="AJ11">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AK11">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AL11">
         <v>60</v>
@@ -3277,124 +3277,124 @@
         <v>580</v>
       </c>
       <c r="AN11">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AO11">
-        <v>600</v>
+        <v>240</v>
       </c>
       <c r="AP11">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ11">
         <v>12.5</v>
       </c>
       <c r="AR11">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="AS11">
-        <v>36</v>
+        <v>85</v>
       </c>
       <c r="AT11">
-        <v>4.9</v>
+        <v>5.8</v>
       </c>
       <c r="AU11">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="AV11">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AW11">
-        <v>29</v>
+        <v>55</v>
       </c>
       <c r="AX11">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="AY11">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="AZ11">
-        <v>15.5</v>
+        <v>22</v>
       </c>
       <c r="BA11">
-        <v>11.5</v>
+        <v>60</v>
       </c>
       <c r="BB11">
+        <v>14.5</v>
+      </c>
+      <c r="BC11">
+        <v>17.5</v>
+      </c>
+      <c r="BD11">
+        <v>32</v>
+      </c>
+      <c r="BE11">
+        <v>65</v>
+      </c>
+      <c r="BF11">
+        <v>14</v>
+      </c>
+      <c r="BG11">
         <v>15</v>
-      </c>
-      <c r="BC11">
-        <v>18</v>
-      </c>
-      <c r="BD11">
-        <v>34</v>
-      </c>
-      <c r="BE11">
-        <v>12</v>
-      </c>
-      <c r="BF11">
-        <v>15</v>
-      </c>
-      <c r="BG11">
-        <v>12</v>
       </c>
       <c r="BH11">
         <v>2.9</v>
       </c>
       <c r="BI11">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="BJ11">
         <v>12</v>
       </c>
       <c r="BK11">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BL11">
         <v>1000</v>
       </c>
       <c r="BM11">
-        <v>2.36</v>
+        <v>13.5</v>
       </c>
       <c r="BN11">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BO11">
         <v>3.25</v>
       </c>
       <c r="BP11">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BQ11">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BR11">
         <v>38</v>
       </c>
       <c r="BS11">
-        <v>2.24</v>
+        <v>10.5</v>
       </c>
       <c r="BT11">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BU11">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BV11">
         <v>65</v>
       </c>
       <c r="BW11">
-        <v>2.3</v>
+        <v>12</v>
       </c>
       <c r="BX11">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="BY11">
-        <v>2.32</v>
+        <v>12.5</v>
       </c>
       <c r="BZ11">
         <v>36</v>
       </c>
       <c r="CA11">
-        <v>2.24</v>
+        <v>10.5</v>
       </c>
       <c r="CB11" t="s">
         <v>129</v>
@@ -3417,88 +3417,88 @@
         <v>124</v>
       </c>
       <c r="F12">
-        <v>6.2</v>
+        <v>4.8</v>
       </c>
       <c r="G12">
-        <v>7.8</v>
+        <v>5.9</v>
       </c>
       <c r="H12">
-        <v>1.61</v>
+        <v>1.72</v>
       </c>
       <c r="I12">
-        <v>1.68</v>
+        <v>1.83</v>
       </c>
       <c r="J12">
-        <v>3.9</v>
+        <v>3.65</v>
       </c>
       <c r="K12">
         <v>4.1</v>
       </c>
       <c r="L12">
-        <v>1.46</v>
+        <v>1.54</v>
       </c>
       <c r="M12">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="N12">
-        <v>2.66</v>
+        <v>2.52</v>
       </c>
       <c r="O12">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="P12">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="Q12">
-        <v>2.4</v>
+        <v>2.54</v>
       </c>
       <c r="R12">
+        <v>1.18</v>
+      </c>
+      <c r="S12">
+        <v>5.5</v>
+      </c>
+      <c r="T12">
+        <v>2.32</v>
+      </c>
+      <c r="U12">
+        <v>1.63</v>
+      </c>
+      <c r="V12">
+        <v>2.2</v>
+      </c>
+      <c r="W12">
         <v>1.2</v>
       </c>
-      <c r="S12">
-        <v>1.05</v>
-      </c>
-      <c r="T12">
-        <v>2.42</v>
-      </c>
-      <c r="U12">
-        <v>1.55</v>
-      </c>
-      <c r="V12">
-        <v>2.46</v>
-      </c>
-      <c r="W12">
-        <v>1.15</v>
-      </c>
       <c r="X12">
-        <v>11</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Y12">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="Z12">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AA12">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="AB12">
-        <v>18</v>
+        <v>13.5</v>
       </c>
       <c r="AC12">
-        <v>11.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD12">
         <v>11</v>
       </c>
       <c r="AE12">
+        <v>27</v>
+      </c>
+      <c r="AF12">
+        <v>44</v>
+      </c>
+      <c r="AG12">
         <v>24</v>
-      </c>
-      <c r="AF12">
-        <v>65</v>
-      </c>
-      <c r="AG12">
-        <v>32</v>
       </c>
       <c r="AH12">
         <v>38</v>
@@ -3510,127 +3510,127 @@
         <v>900</v>
       </c>
       <c r="AK12">
-        <v>190</v>
+        <v>150</v>
       </c>
       <c r="AL12">
-        <v>230</v>
+        <v>700</v>
       </c>
       <c r="AM12">
-        <v>580</v>
+        <v>280</v>
       </c>
       <c r="AN12">
-        <v>410</v>
+        <v>270</v>
       </c>
       <c r="AO12">
-        <v>16.5</v>
+        <v>26</v>
       </c>
       <c r="AP12">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="AQ12">
-        <v>5.5</v>
+        <v>4.6</v>
       </c>
       <c r="AR12">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="AS12">
         <v>7.8</v>
       </c>
       <c r="AT12">
-        <v>6</v>
+        <v>11.5</v>
       </c>
       <c r="AU12">
-        <v>8.4</v>
+        <v>7.6</v>
       </c>
       <c r="AV12">
         <v>9.6</v>
       </c>
       <c r="AW12">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="AX12">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="AY12">
-        <v>6.8</v>
+        <v>17.5</v>
       </c>
       <c r="AZ12">
-        <v>25</v>
+        <v>15.5</v>
       </c>
       <c r="BA12">
-        <v>27</v>
+        <v>9.4</v>
       </c>
       <c r="BB12">
+        <v>9.6</v>
+      </c>
+      <c r="BC12">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BD12">
+        <v>10</v>
+      </c>
+      <c r="BE12">
+        <v>9.6</v>
+      </c>
+      <c r="BF12">
+        <v>9.6</v>
+      </c>
+      <c r="BG12">
         <v>7.4</v>
       </c>
-      <c r="BC12">
-        <v>7.2</v>
-      </c>
-      <c r="BD12">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BE12">
-        <v>7.4</v>
-      </c>
-      <c r="BF12">
-        <v>7.8</v>
-      </c>
-      <c r="BG12">
-        <v>11.5</v>
-      </c>
       <c r="BH12">
-        <v>3.2</v>
+        <v>1000</v>
       </c>
       <c r="BI12">
-        <v>2.54</v>
+        <v>2.32</v>
       </c>
       <c r="BJ12">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="BK12">
-        <v>4.8</v>
+        <v>1.14</v>
       </c>
       <c r="BL12">
         <v>1000</v>
       </c>
       <c r="BM12">
-        <v>7</v>
+        <v>1.14</v>
       </c>
       <c r="BN12">
-        <v>12</v>
+        <v>9.6</v>
       </c>
       <c r="BO12">
-        <v>4.8</v>
+        <v>1.02</v>
       </c>
       <c r="BP12">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="BQ12">
-        <v>6.6</v>
+        <v>1.12</v>
       </c>
       <c r="BR12">
         <v>1000</v>
       </c>
       <c r="BS12">
-        <v>6.8</v>
+        <v>1.14</v>
       </c>
       <c r="BT12">
-        <v>4.2</v>
+        <v>1000</v>
       </c>
       <c r="BU12">
-        <v>3.35</v>
+        <v>3.65</v>
       </c>
       <c r="BV12">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="BW12">
-        <v>4.8</v>
+        <v>1.14</v>
       </c>
       <c r="BX12">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="BY12">
-        <v>6</v>
+        <v>1.14</v>
       </c>
       <c r="BZ12">
         <v>0</v>
@@ -3662,7 +3662,7 @@
         <v>2.54</v>
       </c>
       <c r="G13">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="H13">
         <v>3.5</v>
@@ -3671,7 +3671,7 @@
         <v>3.6</v>
       </c>
       <c r="J13">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="K13">
         <v>3.1</v>
@@ -3683,7 +3683,7 @@
         <v>1.14</v>
       </c>
       <c r="N13">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="O13">
         <v>1.6</v>
@@ -3692,25 +3692,25 @@
         <v>1.52</v>
       </c>
       <c r="Q13">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="R13">
         <v>1.18</v>
       </c>
       <c r="S13">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="T13">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="U13">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="V13">
         <v>1.38</v>
       </c>
       <c r="W13">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="X13">
         <v>8</v>
@@ -3740,16 +3740,16 @@
         <v>14</v>
       </c>
       <c r="AG13">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AH13">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AI13">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AJ13">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AK13">
         <v>38</v>
@@ -3761,7 +3761,7 @@
         <v>500</v>
       </c>
       <c r="AN13">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AO13">
         <v>85</v>
@@ -3770,13 +3770,13 @@
         <v>7.4</v>
       </c>
       <c r="AQ13">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AR13">
         <v>20</v>
       </c>
       <c r="AS13">
-        <v>65</v>
+        <v>36</v>
       </c>
       <c r="AT13">
         <v>6.8</v>
@@ -3785,7 +3785,7 @@
         <v>6.6</v>
       </c>
       <c r="AV13">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AW13">
         <v>50</v>
@@ -3800,10 +3800,10 @@
         <v>22</v>
       </c>
       <c r="BA13">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="BB13">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BC13">
         <v>34</v>
@@ -3812,73 +3812,73 @@
         <v>60</v>
       </c>
       <c r="BE13">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="BF13">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BG13">
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="BH13">
-        <v>2.96</v>
+        <v>3.05</v>
       </c>
       <c r="BI13">
-        <v>2.26</v>
+        <v>2.18</v>
       </c>
       <c r="BJ13">
-        <v>11.5</v>
+        <v>14</v>
       </c>
       <c r="BK13">
-        <v>8.4</v>
+        <v>7.4</v>
       </c>
       <c r="BL13">
-        <v>1000</v>
+        <v>270</v>
       </c>
       <c r="BM13">
-        <v>9.199999999999999</v>
+        <v>5.6</v>
       </c>
       <c r="BN13">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="BO13">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="BP13">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="BQ13">
-        <v>16</v>
+        <v>4.5</v>
       </c>
       <c r="BR13">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="BS13">
-        <v>8.199999999999999</v>
+        <v>5.1</v>
       </c>
       <c r="BT13">
-        <v>6.4</v>
+        <v>7.8</v>
       </c>
       <c r="BU13">
-        <v>5</v>
+        <v>5.8</v>
       </c>
       <c r="BV13">
         <v>36</v>
       </c>
       <c r="BW13">
-        <v>7.6</v>
+        <v>4.9</v>
       </c>
       <c r="BX13">
         <v>60</v>
       </c>
       <c r="BY13">
-        <v>8.199999999999999</v>
+        <v>5.2</v>
       </c>
       <c r="BZ13">
         <v>55</v>
       </c>
       <c r="CA13">
-        <v>8.199999999999999</v>
+        <v>5.2</v>
       </c>
       <c r="CB13" t="s">
         <v>129</v>
@@ -3901,16 +3901,16 @@
         <v>126</v>
       </c>
       <c r="F14">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="G14">
         <v>1.8</v>
       </c>
       <c r="H14">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="I14">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="J14">
         <v>3.55</v>
@@ -3919,7 +3919,7 @@
         <v>3.9</v>
       </c>
       <c r="L14">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="M14">
         <v>1.09</v>
@@ -3931,160 +3931,160 @@
         <v>1.42</v>
       </c>
       <c r="P14">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="Q14">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="R14">
         <v>1.26</v>
       </c>
       <c r="S14">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="T14">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="U14">
-        <v>1.68</v>
+        <v>1.76</v>
       </c>
       <c r="V14">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="W14">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="X14">
         <v>11.5</v>
       </c>
       <c r="Y14">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="Z14">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AA14">
         <v>900</v>
       </c>
       <c r="AB14">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AC14">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AD14">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="AE14">
-        <v>160</v>
+        <v>120</v>
       </c>
       <c r="AF14">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AG14">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AH14">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="AI14">
-        <v>160</v>
+        <v>130</v>
       </c>
       <c r="AJ14">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AK14">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AL14">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AM14">
         <v>580</v>
       </c>
       <c r="AN14">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AO14">
-        <v>260</v>
+        <v>220</v>
       </c>
       <c r="AP14">
-        <v>8.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ14">
         <v>13.5</v>
       </c>
       <c r="AR14">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="AS14">
-        <v>8.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT14">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="AU14">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="AV14">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AW14">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="AX14">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY14">
-        <v>7.6</v>
+        <v>9</v>
       </c>
       <c r="AZ14">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="BA14">
         <v>28</v>
       </c>
       <c r="BB14">
-        <v>12.5</v>
+        <v>15.5</v>
       </c>
       <c r="BC14">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="BD14">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="BE14">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="BF14">
         <v>11.5</v>
       </c>
       <c r="BG14">
-        <v>7.6</v>
+        <v>9.6</v>
       </c>
       <c r="BH14">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="BI14">
-        <v>2.38</v>
+        <v>2.46</v>
       </c>
       <c r="BJ14">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BK14">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="BL14">
         <v>1000</v>
       </c>
       <c r="BM14">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BN14">
         <v>4.8</v>
       </c>
       <c r="BO14">
-        <v>2.44</v>
+        <v>3.2</v>
       </c>
       <c r="BP14">
         <v>15</v>
@@ -4093,34 +4093,34 @@
         <v>3.7</v>
       </c>
       <c r="BR14">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="BS14">
         <v>4.4</v>
       </c>
       <c r="BT14">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BU14">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="BV14">
+        <v>80</v>
+      </c>
+      <c r="BW14">
+        <v>4.6</v>
+      </c>
+      <c r="BX14">
         <v>90</v>
-      </c>
-      <c r="BW14">
-        <v>4.7</v>
-      </c>
-      <c r="BX14">
-        <v>100</v>
       </c>
       <c r="BY14">
         <v>4.7</v>
       </c>
       <c r="BZ14">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="CA14">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="CB14" t="s">
         <v>129</v>
@@ -4385,19 +4385,19 @@
         <v>128</v>
       </c>
       <c r="F16">
-        <v>2.58</v>
+        <v>2.5</v>
       </c>
       <c r="G16">
-        <v>2.68</v>
+        <v>2.62</v>
       </c>
       <c r="H16">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="I16">
-        <v>2.84</v>
+        <v>2.94</v>
       </c>
       <c r="J16">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="K16">
         <v>3.95</v>
@@ -4409,40 +4409,40 @@
         <v>1.04</v>
       </c>
       <c r="N16">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="O16">
         <v>1.21</v>
       </c>
       <c r="P16">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="Q16">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="R16">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="S16">
-        <v>2.66</v>
+        <v>2.58</v>
       </c>
       <c r="T16">
         <v>1.61</v>
       </c>
       <c r="U16">
-        <v>2.56</v>
+        <v>2.3</v>
       </c>
       <c r="V16">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="W16">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="X16">
         <v>21</v>
       </c>
       <c r="Y16">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="Z16">
         <v>23</v>
@@ -4451,31 +4451,31 @@
         <v>46</v>
       </c>
       <c r="AB16">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AC16">
         <v>9.199999999999999</v>
       </c>
       <c r="AD16">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AE16">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AF16">
         <v>21</v>
       </c>
       <c r="AG16">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AH16">
         <v>15</v>
       </c>
       <c r="AI16">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AJ16">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AK16">
         <v>24</v>
@@ -4484,121 +4484,121 @@
         <v>32</v>
       </c>
       <c r="AM16">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="AN16">
+        <v>15</v>
+      </c>
+      <c r="AO16">
+        <v>19</v>
+      </c>
+      <c r="AP16">
+        <v>18</v>
+      </c>
+      <c r="AQ16">
+        <v>14.5</v>
+      </c>
+      <c r="AR16">
+        <v>19.5</v>
+      </c>
+      <c r="AS16">
+        <v>36</v>
+      </c>
+      <c r="AT16">
         <v>14</v>
       </c>
-      <c r="AO16">
-        <v>21</v>
-      </c>
-      <c r="AP16">
-        <v>15.5</v>
-      </c>
-      <c r="AQ16">
+      <c r="AU16">
+        <v>7.8</v>
+      </c>
+      <c r="AV16">
+        <v>11.5</v>
+      </c>
+      <c r="AW16">
+        <v>24</v>
+      </c>
+      <c r="AX16">
+        <v>17</v>
+      </c>
+      <c r="AY16">
+        <v>10.5</v>
+      </c>
+      <c r="AZ16">
         <v>12</v>
       </c>
-      <c r="AR16">
-        <v>17</v>
-      </c>
-      <c r="AS16">
-        <v>19</v>
-      </c>
-      <c r="AT16">
-        <v>11.5</v>
-      </c>
-      <c r="AU16">
-        <v>6.4</v>
-      </c>
-      <c r="AV16">
-        <v>9.6</v>
-      </c>
-      <c r="AW16">
-        <v>20</v>
-      </c>
-      <c r="AX16">
-        <v>16.5</v>
-      </c>
-      <c r="AY16">
-        <v>9.4</v>
-      </c>
-      <c r="AZ16">
-        <v>11.5</v>
-      </c>
       <c r="BA16">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="BB16">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="BC16">
         <v>20</v>
       </c>
       <c r="BD16">
-        <v>16.5</v>
+        <v>25</v>
       </c>
       <c r="BE16">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="BF16">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="BG16">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="BH16">
-        <v>4.7</v>
+        <v>1000</v>
       </c>
       <c r="BI16">
-        <v>3</v>
+        <v>1.04</v>
       </c>
       <c r="BJ16">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="BK16">
-        <v>4.4</v>
+        <v>1.04</v>
       </c>
       <c r="BL16">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="BM16">
-        <v>7.8</v>
+        <v>1.04</v>
       </c>
       <c r="BN16">
-        <v>6</v>
+        <v>1000</v>
       </c>
       <c r="BO16">
-        <v>3.5</v>
+        <v>1.04</v>
       </c>
       <c r="BP16">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ16">
-        <v>5.7</v>
+        <v>1.04</v>
       </c>
       <c r="BR16">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="BS16">
-        <v>6.4</v>
+        <v>1.04</v>
       </c>
       <c r="BT16">
-        <v>6.6</v>
+        <v>1000</v>
       </c>
       <c r="BU16">
-        <v>3.7</v>
+        <v>1.04</v>
       </c>
       <c r="BV16">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="BW16">
-        <v>6</v>
+        <v>1.04</v>
       </c>
       <c r="BX16">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="BY16">
-        <v>6.6</v>
+        <v>1.04</v>
       </c>
       <c r="BZ16">
         <v>0</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-06.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-06.xlsx
@@ -403,7 +403,7 @@
     <t>Always Ready</t>
   </si>
   <si>
-    <t>2026-08-06 12:40:03</t>
+    <t>2026-08-06 14:58:38</t>
   </si>
 </sst>
 </file>
@@ -997,16 +997,16 @@
         <v>114</v>
       </c>
       <c r="F2">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="G2">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="H2">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="I2">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="J2">
         <v>4.1</v>
@@ -1015,43 +1015,43 @@
         <v>4.3</v>
       </c>
       <c r="L2">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="M2">
         <v>1.04</v>
       </c>
       <c r="N2">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="O2">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="P2">
-        <v>2.66</v>
+        <v>2.74</v>
       </c>
       <c r="Q2">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="R2">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="S2">
-        <v>2.42</v>
+        <v>2.3</v>
       </c>
       <c r="T2">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="U2">
-        <v>2.58</v>
+        <v>2.64</v>
       </c>
       <c r="V2">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="W2">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="X2">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="Y2">
         <v>23</v>
@@ -1063,31 +1063,31 @@
         <v>80</v>
       </c>
       <c r="AB2">
-        <v>15</v>
+        <v>18.5</v>
       </c>
       <c r="AC2">
         <v>10.5</v>
       </c>
       <c r="AD2">
+        <v>19</v>
+      </c>
+      <c r="AE2">
+        <v>38</v>
+      </c>
+      <c r="AF2">
         <v>17</v>
       </c>
-      <c r="AE2">
-        <v>40</v>
-      </c>
-      <c r="AF2">
-        <v>16.5</v>
-      </c>
       <c r="AG2">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AH2">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AI2">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AJ2">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="AK2">
         <v>18</v>
@@ -1102,7 +1102,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AO2">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AP2">
         <v>22</v>
@@ -1111,7 +1111,7 @@
         <v>19</v>
       </c>
       <c r="AR2">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AS2">
         <v>55</v>
@@ -1120,13 +1120,13 @@
         <v>13</v>
       </c>
       <c r="AU2">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV2">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AW2">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AX2">
         <v>14</v>
@@ -1135,10 +1135,10 @@
         <v>9.6</v>
       </c>
       <c r="AZ2">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="BA2">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BB2">
         <v>21</v>
@@ -1150,67 +1150,67 @@
         <v>22</v>
       </c>
       <c r="BE2">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="BF2">
         <v>7.8</v>
       </c>
       <c r="BG2">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="BH2">
-        <v>1000</v>
+        <v>5.7</v>
       </c>
       <c r="BI2">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BJ2">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="BK2">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BN2">
-        <v>1000</v>
+        <v>5.9</v>
       </c>
       <c r="BO2">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BP2">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BQ2">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BR2">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="BS2">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="BT2">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BU2">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BV2">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="BW2">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BX2">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="BY2">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BZ2">
         <v>0</v>
@@ -1239,16 +1239,16 @@
         <v>115</v>
       </c>
       <c r="F3">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="G3">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="H3">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="I3">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="J3">
         <v>3.4</v>
@@ -1263,16 +1263,16 @@
         <v>1.11</v>
       </c>
       <c r="N3">
-        <v>2.84</v>
+        <v>2.92</v>
       </c>
       <c r="O3">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="P3">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="Q3">
-        <v>2.46</v>
+        <v>2.42</v>
       </c>
       <c r="R3">
         <v>1.22</v>
@@ -1281,16 +1281,16 @@
         <v>5</v>
       </c>
       <c r="T3">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="U3">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="V3">
         <v>1.2</v>
       </c>
       <c r="W3">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="X3">
         <v>10.5</v>
@@ -1305,7 +1305,7 @@
         <v>900</v>
       </c>
       <c r="AB3">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="AC3">
         <v>8.199999999999999</v>
@@ -1320,13 +1320,13 @@
         <v>10.5</v>
       </c>
       <c r="AG3">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AH3">
         <v>27</v>
       </c>
       <c r="AI3">
-        <v>160</v>
+        <v>190</v>
       </c>
       <c r="AJ3">
         <v>22</v>
@@ -1344,22 +1344,22 @@
         <v>19.5</v>
       </c>
       <c r="AO3">
-        <v>270</v>
+        <v>200</v>
       </c>
       <c r="AP3">
         <v>8.800000000000001</v>
       </c>
       <c r="AQ3">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AR3">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AS3">
-        <v>85</v>
+        <v>12</v>
       </c>
       <c r="AT3">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="AU3">
         <v>7.2</v>
@@ -1368,91 +1368,91 @@
         <v>20</v>
       </c>
       <c r="AW3">
-        <v>55</v>
+        <v>11.5</v>
       </c>
       <c r="AX3">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY3">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ3">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BA3">
-        <v>60</v>
+        <v>10.5</v>
       </c>
       <c r="BB3">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BC3">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BD3">
         <v>38</v>
       </c>
       <c r="BE3">
-        <v>90</v>
+        <v>13</v>
       </c>
       <c r="BF3">
-        <v>13.5</v>
+        <v>8.4</v>
       </c>
       <c r="BG3">
-        <v>13.5</v>
+        <v>10</v>
       </c>
       <c r="BH3">
-        <v>1000</v>
+        <v>3.2</v>
       </c>
       <c r="BI3">
-        <v>1.04</v>
+        <v>2.58</v>
       </c>
       <c r="BJ3">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BK3">
-        <v>1.04</v>
+        <v>4.2</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>1.04</v>
+        <v>6.2</v>
       </c>
       <c r="BN3">
-        <v>1000</v>
+        <v>4.7</v>
       </c>
       <c r="BO3">
-        <v>1.04</v>
+        <v>3.7</v>
       </c>
       <c r="BP3">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="BQ3">
-        <v>1.04</v>
+        <v>4.6</v>
       </c>
       <c r="BR3">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="BS3">
-        <v>1.04</v>
+        <v>5.6</v>
       </c>
       <c r="BT3">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="BU3">
-        <v>1.04</v>
+        <v>3.9</v>
       </c>
       <c r="BV3">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="BW3">
-        <v>1.04</v>
+        <v>5.9</v>
       </c>
       <c r="BX3">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="BY3">
-        <v>1.04</v>
+        <v>6</v>
       </c>
       <c r="BZ3">
         <v>0</v>
@@ -1481,22 +1481,22 @@
         <v>116</v>
       </c>
       <c r="F4">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="G4">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="H4">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="I4">
         <v>6.2</v>
       </c>
       <c r="J4">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="K4">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="L4">
         <v>1.19</v>
@@ -1505,52 +1505,52 @@
         <v>1.01</v>
       </c>
       <c r="N4">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="O4">
         <v>1.1</v>
       </c>
       <c r="P4">
-        <v>3.75</v>
+        <v>4.1</v>
       </c>
       <c r="Q4">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="R4">
-        <v>2.14</v>
+        <v>2.24</v>
       </c>
       <c r="S4">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="T4">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="U4">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="V4">
         <v>1.19</v>
       </c>
       <c r="W4">
-        <v>2.78</v>
+        <v>2.84</v>
       </c>
       <c r="X4">
+        <v>60</v>
+      </c>
+      <c r="Y4">
         <v>55</v>
       </c>
-      <c r="Y4">
-        <v>48</v>
-      </c>
       <c r="Z4">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AA4">
         <v>700</v>
       </c>
       <c r="AB4">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="AC4">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AD4">
         <v>26</v>
@@ -1559,7 +1559,7 @@
         <v>75</v>
       </c>
       <c r="AF4">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AG4">
         <v>12.5</v>
@@ -1568,7 +1568,7 @@
         <v>18</v>
       </c>
       <c r="AI4">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="AJ4">
         <v>18.5</v>
@@ -1583,7 +1583,7 @@
         <v>65</v>
       </c>
       <c r="AN4">
-        <v>4.3</v>
+        <v>3.85</v>
       </c>
       <c r="AO4">
         <v>36</v>
@@ -1595,25 +1595,25 @@
         <v>36</v>
       </c>
       <c r="AR4">
-        <v>50</v>
+        <v>28</v>
       </c>
       <c r="AS4">
-        <v>9.4</v>
+        <v>11</v>
       </c>
       <c r="AT4">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AU4">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AV4">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AW4">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="AX4">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AY4">
         <v>10</v>
@@ -1625,82 +1625,82 @@
         <v>36</v>
       </c>
       <c r="BB4">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BC4">
         <v>12</v>
       </c>
       <c r="BD4">
-        <v>17</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BE4">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="BF4">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="BG4">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="BH4">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="BI4">
-        <v>1.04</v>
+        <v>5.3</v>
       </c>
       <c r="BJ4">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BK4">
-        <v>1.04</v>
+        <v>7.2</v>
       </c>
       <c r="BL4">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BM4">
-        <v>1.04</v>
+        <v>7.8</v>
       </c>
       <c r="BN4">
-        <v>1000</v>
+        <v>5.4</v>
       </c>
       <c r="BO4">
-        <v>1.04</v>
+        <v>4.5</v>
       </c>
       <c r="BP4">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="BQ4">
-        <v>1.04</v>
+        <v>7</v>
       </c>
       <c r="BR4">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="BS4">
-        <v>1.04</v>
+        <v>6</v>
       </c>
       <c r="BT4">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BU4">
-        <v>1.04</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BV4">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BW4">
-        <v>1.04</v>
+        <v>7.2</v>
       </c>
       <c r="BX4">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BY4">
-        <v>1.04</v>
+        <v>7</v>
       </c>
       <c r="BZ4">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CA4">
-        <v>1.04</v>
+        <v>6.8</v>
       </c>
       <c r="CB4" t="s">
         <v>129</v>
@@ -1723,22 +1723,22 @@
         <v>117</v>
       </c>
       <c r="F5">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="G5">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="H5">
         <v>2.94</v>
       </c>
       <c r="I5">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="J5">
-        <v>2.92</v>
+        <v>3.05</v>
       </c>
       <c r="K5">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="L5">
         <v>1.46</v>
@@ -1747,28 +1747,28 @@
         <v>1.09</v>
       </c>
       <c r="N5">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
       <c r="O5">
         <v>1.37</v>
       </c>
       <c r="P5">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="Q5">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="R5">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="S5">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="T5">
         <v>1.82</v>
       </c>
       <c r="U5">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="V5">
         <v>1.47</v>
@@ -1780,31 +1780,31 @@
         <v>12</v>
       </c>
       <c r="Y5">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="Z5">
         <v>21</v>
       </c>
       <c r="AA5">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AB5">
         <v>11</v>
       </c>
       <c r="AC5">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AD5">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AE5">
         <v>38</v>
       </c>
       <c r="AF5">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AG5">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AH5">
         <v>17.5</v>
@@ -1813,10 +1813,10 @@
         <v>60</v>
       </c>
       <c r="AJ5">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AK5">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AL5">
         <v>60</v>
@@ -1825,46 +1825,46 @@
         <v>130</v>
       </c>
       <c r="AN5">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AO5">
         <v>38</v>
       </c>
       <c r="AP5">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ5">
         <v>9.6</v>
       </c>
       <c r="AR5">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AS5">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="AT5">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AU5">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AV5">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="AW5">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AX5">
         <v>15.5</v>
       </c>
       <c r="AY5">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="AZ5">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="BA5">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BB5">
         <v>29</v>
@@ -1873,76 +1873,76 @@
         <v>25</v>
       </c>
       <c r="BD5">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BE5">
-        <v>29</v>
+        <v>70</v>
       </c>
       <c r="BF5">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="BG5">
-        <v>13.5</v>
+        <v>23</v>
       </c>
       <c r="BH5">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="BI5">
-        <v>2.54</v>
+        <v>2.8</v>
       </c>
       <c r="BJ5">
         <v>12</v>
       </c>
       <c r="BK5">
-        <v>3.55</v>
+        <v>8</v>
       </c>
       <c r="BL5">
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>4.8</v>
+        <v>5.6</v>
       </c>
       <c r="BN5">
+        <v>6.8</v>
+      </c>
+      <c r="BO5">
+        <v>4.9</v>
+      </c>
+      <c r="BP5">
+        <v>27</v>
+      </c>
+      <c r="BQ5">
+        <v>5.1</v>
+      </c>
+      <c r="BR5">
+        <v>40</v>
+      </c>
+      <c r="BS5">
+        <v>5.4</v>
+      </c>
+      <c r="BT5">
         <v>7</v>
       </c>
-      <c r="BO5">
-        <v>2.92</v>
-      </c>
-      <c r="BP5">
-        <v>28</v>
-      </c>
-      <c r="BQ5">
-        <v>4.2</v>
-      </c>
-      <c r="BR5">
-        <v>48</v>
-      </c>
-      <c r="BS5">
-        <v>4.5</v>
-      </c>
-      <c r="BT5">
-        <v>6.6</v>
-      </c>
       <c r="BU5">
-        <v>2.84</v>
+        <v>5</v>
       </c>
       <c r="BV5">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="BW5">
-        <v>4.2</v>
+        <v>5.2</v>
       </c>
       <c r="BX5">
         <v>46</v>
       </c>
       <c r="BY5">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="BZ5">
         <v>40</v>
       </c>
       <c r="CA5">
-        <v>4.4</v>
+        <v>5.1</v>
       </c>
       <c r="CB5" t="s">
         <v>129</v>
@@ -1965,16 +1965,16 @@
         <v>118</v>
       </c>
       <c r="F6">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="G6">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="H6">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="I6">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="J6">
         <v>3.35</v>
@@ -1989,73 +1989,73 @@
         <v>1.07</v>
       </c>
       <c r="N6">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="O6">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="P6">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="Q6">
-        <v>1.94</v>
+        <v>1.9</v>
       </c>
       <c r="R6">
+        <v>1.4</v>
+      </c>
+      <c r="S6">
+        <v>3.2</v>
+      </c>
+      <c r="T6">
+        <v>1.75</v>
+      </c>
+      <c r="U6">
+        <v>2.24</v>
+      </c>
+      <c r="V6">
         <v>1.39</v>
       </c>
-      <c r="S6">
-        <v>3.35</v>
-      </c>
-      <c r="T6">
-        <v>1.71</v>
-      </c>
-      <c r="U6">
-        <v>2.2</v>
-      </c>
-      <c r="V6">
-        <v>1.37</v>
-      </c>
       <c r="W6">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="X6">
         <v>15</v>
       </c>
       <c r="Y6">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="Z6">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AA6">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="AB6">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AC6">
         <v>8.199999999999999</v>
       </c>
       <c r="AD6">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AE6">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="AF6">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AG6">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AH6">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AI6">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="AJ6">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AK6">
         <v>25</v>
@@ -2067,10 +2067,10 @@
         <v>85</v>
       </c>
       <c r="AN6">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AO6">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="AP6">
         <v>13</v>
@@ -2079,22 +2079,22 @@
         <v>13</v>
       </c>
       <c r="AR6">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AS6">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AT6">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AU6">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AV6">
         <v>13.5</v>
       </c>
       <c r="AW6">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="AX6">
         <v>13</v>
@@ -2103,49 +2103,49 @@
         <v>10</v>
       </c>
       <c r="AZ6">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BA6">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="BB6">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="BC6">
         <v>21</v>
       </c>
       <c r="BD6">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="BE6">
         <v>60</v>
       </c>
       <c r="BF6">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BG6">
         <v>25</v>
       </c>
       <c r="BH6">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="BI6">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="BJ6">
         <v>9.6</v>
       </c>
       <c r="BK6">
-        <v>4.2</v>
+        <v>5.2</v>
       </c>
       <c r="BL6">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="BM6">
-        <v>6.4</v>
+        <v>10</v>
       </c>
       <c r="BN6">
-        <v>6.2</v>
+        <v>5.2</v>
       </c>
       <c r="BO6">
         <v>4.6</v>
@@ -2154,31 +2154,31 @@
         <v>19.5</v>
       </c>
       <c r="BQ6">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="BR6">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BS6">
-        <v>5.6</v>
+        <v>8.4</v>
       </c>
       <c r="BT6">
-        <v>8</v>
+        <v>6.8</v>
       </c>
       <c r="BU6">
-        <v>5.9</v>
+        <v>4.4</v>
       </c>
       <c r="BV6">
         <v>34</v>
       </c>
       <c r="BW6">
-        <v>5.5</v>
+        <v>8</v>
       </c>
       <c r="BX6">
         <v>46</v>
       </c>
       <c r="BY6">
-        <v>5.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ6">
         <v>0</v>
@@ -2207,70 +2207,70 @@
         <v>119</v>
       </c>
       <c r="F7">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="G7">
-        <v>2.36</v>
+        <v>2.3</v>
       </c>
       <c r="H7">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="I7">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="J7">
         <v>3.6</v>
       </c>
       <c r="K7">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="L7">
         <v>1.42</v>
       </c>
       <c r="M7">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N7">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="O7">
         <v>1.33</v>
       </c>
       <c r="P7">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="Q7">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="R7">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="S7">
         <v>3.6</v>
       </c>
       <c r="T7">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="U7">
         <v>2.08</v>
       </c>
       <c r="V7">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="W7">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="X7">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="Y7">
         <v>13</v>
       </c>
       <c r="Z7">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AA7">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AB7">
         <v>10</v>
@@ -2279,13 +2279,13 @@
         <v>8.4</v>
       </c>
       <c r="AD7">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AE7">
         <v>44</v>
       </c>
       <c r="AF7">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AG7">
         <v>11.5</v>
@@ -2297,10 +2297,10 @@
         <v>55</v>
       </c>
       <c r="AJ7">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AK7">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AL7">
         <v>42</v>
@@ -2309,10 +2309,10 @@
         <v>110</v>
       </c>
       <c r="AN7">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AO7">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AP7">
         <v>12</v>
@@ -2321,10 +2321,10 @@
         <v>11</v>
       </c>
       <c r="AR7">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AS7">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AT7">
         <v>9</v>
@@ -2336,10 +2336,10 @@
         <v>12.5</v>
       </c>
       <c r="AW7">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AX7">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AY7">
         <v>10</v>
@@ -2351,28 +2351,28 @@
         <v>42</v>
       </c>
       <c r="BB7">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BC7">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BD7">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BE7">
         <v>75</v>
       </c>
       <c r="BF7">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="BG7">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="BH7">
         <v>3.45</v>
       </c>
       <c r="BI7">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="BJ7">
         <v>10</v>
@@ -2387,46 +2387,46 @@
         <v>10</v>
       </c>
       <c r="BN7">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BO7">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="BP7">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BQ7">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BR7">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BS7">
         <v>8.199999999999999</v>
       </c>
       <c r="BT7">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BU7">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BV7">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BW7">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX7">
         <v>1000</v>
       </c>
       <c r="BY7">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BZ7">
         <v>1000</v>
       </c>
       <c r="CA7">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="CB7" t="s">
         <v>129</v>
@@ -2449,226 +2449,226 @@
         <v>120</v>
       </c>
       <c r="F8">
-        <v>1.26</v>
+        <v>1.19</v>
       </c>
       <c r="G8">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="H8">
-        <v>15.5</v>
+        <v>19.5</v>
       </c>
       <c r="I8">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J8">
+        <v>7.4</v>
+      </c>
+      <c r="K8">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="L8">
+        <v>1.2</v>
+      </c>
+      <c r="M8">
+        <v>1.03</v>
+      </c>
+      <c r="N8">
         <v>5.8</v>
       </c>
-      <c r="K8">
-        <v>6.8</v>
-      </c>
-      <c r="L8">
-        <v>1.37</v>
-      </c>
-      <c r="M8">
-        <v>1.05</v>
-      </c>
-      <c r="N8">
-        <v>4.2</v>
-      </c>
       <c r="O8">
-        <v>1.27</v>
+        <v>1.18</v>
       </c>
       <c r="P8">
-        <v>2.08</v>
+        <v>2.66</v>
       </c>
       <c r="Q8">
-        <v>1.8</v>
+        <v>1.54</v>
       </c>
       <c r="R8">
-        <v>1.4</v>
+        <v>1.66</v>
       </c>
       <c r="S8">
-        <v>3.05</v>
+        <v>2.38</v>
       </c>
       <c r="T8">
-        <v>2.46</v>
+        <v>2.34</v>
       </c>
       <c r="U8">
-        <v>1.56</v>
+        <v>1.63</v>
       </c>
       <c r="V8">
         <v>1.04</v>
       </c>
       <c r="W8">
-        <v>4.3</v>
+        <v>5.3</v>
       </c>
       <c r="X8">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="Y8">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="Z8">
-        <v>210</v>
+        <v>290</v>
       </c>
       <c r="AA8">
         <v>1000</v>
       </c>
       <c r="AB8">
-        <v>7.6</v>
+        <v>13</v>
       </c>
       <c r="AC8">
-        <v>17.5</v>
+        <v>21</v>
       </c>
       <c r="AD8">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="AE8">
-        <v>460</v>
+        <v>490</v>
       </c>
       <c r="AF8">
-        <v>7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AG8">
-        <v>12.5</v>
+        <v>15.5</v>
       </c>
       <c r="AH8">
         <v>55</v>
       </c>
       <c r="AI8">
-        <v>340</v>
+        <v>330</v>
       </c>
       <c r="AJ8">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AK8">
-        <v>17</v>
+        <v>14.5</v>
       </c>
       <c r="AL8">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AM8">
-        <v>370</v>
+        <v>330</v>
       </c>
       <c r="AN8">
-        <v>5.5</v>
+        <v>4.1</v>
       </c>
       <c r="AO8">
         <v>1000</v>
       </c>
       <c r="AP8">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AQ8">
+        <v>25</v>
+      </c>
+      <c r="AR8">
+        <v>6.2</v>
+      </c>
+      <c r="AS8">
+        <v>6.4</v>
+      </c>
+      <c r="AT8">
+        <v>9</v>
+      </c>
+      <c r="AU8">
         <v>15.5</v>
       </c>
-      <c r="AQ8">
-        <v>19.5</v>
-      </c>
-      <c r="AR8">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AS8">
-        <v>9.6</v>
-      </c>
-      <c r="AT8">
+      <c r="AV8">
+        <v>6</v>
+      </c>
+      <c r="AW8">
+        <v>6.4</v>
+      </c>
+      <c r="AX8">
+        <v>6.8</v>
+      </c>
+      <c r="AY8">
+        <v>11</v>
+      </c>
+      <c r="AZ8">
+        <v>6</v>
+      </c>
+      <c r="BA8">
         <v>6.2</v>
       </c>
-      <c r="AU8">
-        <v>12</v>
-      </c>
-      <c r="AV8">
-        <v>27</v>
-      </c>
-      <c r="AW8">
-        <v>9.6</v>
-      </c>
-      <c r="AX8">
-        <v>5.9</v>
-      </c>
-      <c r="AY8">
-        <v>10</v>
-      </c>
-      <c r="AZ8">
-        <v>8.4</v>
-      </c>
-      <c r="BA8">
-        <v>9.6</v>
-      </c>
       <c r="BB8">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="BC8">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="BD8">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="BE8">
-        <v>9.6</v>
+        <v>6.2</v>
       </c>
       <c r="BF8">
-        <v>4.8</v>
+        <v>3.25</v>
       </c>
       <c r="BG8">
-        <v>9.800000000000001</v>
+        <v>6.8</v>
       </c>
       <c r="BH8">
         <v>1000</v>
       </c>
       <c r="BI8">
-        <v>1.04</v>
+        <v>4.3</v>
       </c>
       <c r="BJ8">
         <v>1000</v>
       </c>
       <c r="BK8">
-        <v>1.04</v>
+        <v>1.47</v>
       </c>
       <c r="BL8">
         <v>1000</v>
       </c>
       <c r="BM8">
-        <v>1.04</v>
+        <v>1.47</v>
       </c>
       <c r="BN8">
         <v>1000</v>
       </c>
       <c r="BO8">
-        <v>1.04</v>
+        <v>3.45</v>
       </c>
       <c r="BP8">
-        <v>1000</v>
+        <v>5</v>
       </c>
       <c r="BQ8">
-        <v>1.04</v>
+        <v>3.95</v>
       </c>
       <c r="BR8">
         <v>1000</v>
       </c>
       <c r="BS8">
-        <v>1.04</v>
+        <v>1.47</v>
       </c>
       <c r="BT8">
         <v>1000</v>
       </c>
       <c r="BU8">
-        <v>1.04</v>
+        <v>1.47</v>
       </c>
       <c r="BV8">
         <v>1000</v>
       </c>
       <c r="BW8">
-        <v>1.04</v>
+        <v>1.47</v>
       </c>
       <c r="BX8">
         <v>1000</v>
       </c>
       <c r="BY8">
-        <v>1.04</v>
+        <v>4</v>
       </c>
       <c r="BZ8">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CA8">
-        <v>1.04</v>
+        <v>2</v>
       </c>
       <c r="CB8" t="s">
         <v>129</v>
@@ -2691,10 +2691,10 @@
         <v>121</v>
       </c>
       <c r="F9">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="G9">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="H9">
         <v>6</v>
@@ -2703,10 +2703,10 @@
         <v>7.2</v>
       </c>
       <c r="J9">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="K9">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="L9">
         <v>1.66</v>
@@ -2715,28 +2715,28 @@
         <v>1.15</v>
       </c>
       <c r="N9">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="O9">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="P9">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="Q9">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="R9">
         <v>1.17</v>
       </c>
       <c r="S9">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="T9">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="U9">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="V9">
         <v>1.16</v>
@@ -2769,10 +2769,10 @@
         <v>500</v>
       </c>
       <c r="AF9">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AG9">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AH9">
         <v>36</v>
@@ -2802,13 +2802,13 @@
         <v>6.6</v>
       </c>
       <c r="AQ9">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AR9">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AS9">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT9">
         <v>4.8</v>
@@ -2817,22 +2817,22 @@
         <v>7</v>
       </c>
       <c r="AV9">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="AW9">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AX9">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY9">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AZ9">
         <v>15</v>
       </c>
       <c r="BA9">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BB9">
         <v>18</v>
@@ -2841,19 +2841,19 @@
         <v>13</v>
       </c>
       <c r="BD9">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE9">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BF9">
         <v>21</v>
       </c>
       <c r="BG9">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BH9">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="BI9">
         <v>2.06</v>
@@ -2868,13 +2868,13 @@
         <v>1000</v>
       </c>
       <c r="BM9">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BN9">
         <v>4.6</v>
       </c>
       <c r="BO9">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="BP9">
         <v>17</v>
@@ -2886,31 +2886,31 @@
         <v>55</v>
       </c>
       <c r="BS9">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BT9">
         <v>9.4</v>
       </c>
       <c r="BU9">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BV9">
         <v>1000</v>
       </c>
       <c r="BW9">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BX9">
         <v>1000</v>
       </c>
       <c r="BY9">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BZ9">
         <v>55</v>
       </c>
       <c r="CA9">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="CB9" t="s">
         <v>129</v>
@@ -2933,10 +2933,10 @@
         <v>122</v>
       </c>
       <c r="F10">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="G10">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="H10">
         <v>3.25</v>
@@ -2948,7 +2948,7 @@
         <v>3.4</v>
       </c>
       <c r="K10">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="L10">
         <v>1.44</v>
@@ -2963,7 +2963,7 @@
         <v>1.35</v>
       </c>
       <c r="P10">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="Q10">
         <v>2.06</v>
@@ -2972,7 +2972,7 @@
         <v>1.32</v>
       </c>
       <c r="S10">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="T10">
         <v>1.87</v>
@@ -2984,7 +2984,7 @@
         <v>1.4</v>
       </c>
       <c r="W10">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="X10">
         <v>13.5</v>
@@ -2999,7 +2999,7 @@
         <v>75</v>
       </c>
       <c r="AB10">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC10">
         <v>8</v>
@@ -3044,25 +3044,25 @@
         <v>11</v>
       </c>
       <c r="AQ10">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="AR10">
         <v>17.5</v>
       </c>
       <c r="AS10">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="AT10">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AU10">
-        <v>5.8</v>
+        <v>6.8</v>
       </c>
       <c r="AV10">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AW10">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AX10">
         <v>13.5</v>
@@ -3074,13 +3074,13 @@
         <v>15.5</v>
       </c>
       <c r="BA10">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="BB10">
         <v>23</v>
       </c>
       <c r="BC10">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BD10">
         <v>30</v>
@@ -3095,58 +3095,58 @@
         <v>25</v>
       </c>
       <c r="BH10">
-        <v>1000</v>
+        <v>3.35</v>
       </c>
       <c r="BI10">
-        <v>1.04</v>
+        <v>2.6</v>
       </c>
       <c r="BJ10">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BK10">
-        <v>1.04</v>
+        <v>5.2</v>
       </c>
       <c r="BL10">
         <v>1000</v>
       </c>
       <c r="BM10">
-        <v>1.04</v>
+        <v>9.6</v>
       </c>
       <c r="BN10">
-        <v>1000</v>
+        <v>5.5</v>
       </c>
       <c r="BO10">
-        <v>1.04</v>
+        <v>4</v>
       </c>
       <c r="BP10">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="BQ10">
-        <v>1.04</v>
+        <v>6.6</v>
       </c>
       <c r="BR10">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BS10">
-        <v>1.04</v>
+        <v>8</v>
       </c>
       <c r="BT10">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="BU10">
-        <v>1.04</v>
+        <v>4.8</v>
       </c>
       <c r="BV10">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="BW10">
-        <v>1.04</v>
+        <v>7.4</v>
       </c>
       <c r="BX10">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="BY10">
-        <v>1.04</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ10">
         <v>0</v>
@@ -3184,13 +3184,13 @@
         <v>5.4</v>
       </c>
       <c r="I11">
-        <v>6.2</v>
+        <v>5.8</v>
       </c>
       <c r="J11">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K11">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="L11">
         <v>1.53</v>
@@ -3205,7 +3205,7 @@
         <v>1.5</v>
       </c>
       <c r="P11">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="Q11">
         <v>2.46</v>
@@ -3217,16 +3217,16 @@
         <v>5</v>
       </c>
       <c r="T11">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="U11">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="V11">
         <v>1.2</v>
       </c>
       <c r="W11">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="X11">
         <v>10.5</v>
@@ -3235,7 +3235,7 @@
         <v>15</v>
       </c>
       <c r="Z11">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AA11">
         <v>900</v>
@@ -3277,10 +3277,10 @@
         <v>580</v>
       </c>
       <c r="AN11">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AO11">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="AP11">
         <v>8.800000000000001</v>
@@ -3289,7 +3289,7 @@
         <v>12.5</v>
       </c>
       <c r="AR11">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="AS11">
         <v>85</v>
@@ -3310,7 +3310,7 @@
         <v>8.6</v>
       </c>
       <c r="AY11">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AZ11">
         <v>22</v>
@@ -3319,25 +3319,25 @@
         <v>60</v>
       </c>
       <c r="BB11">
-        <v>14.5</v>
+        <v>17</v>
       </c>
       <c r="BC11">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="BD11">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BE11">
         <v>65</v>
       </c>
       <c r="BF11">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="BG11">
         <v>15</v>
       </c>
       <c r="BH11">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="BI11">
         <v>2.42</v>
@@ -3352,13 +3352,13 @@
         <v>1000</v>
       </c>
       <c r="BM11">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BN11">
         <v>4.2</v>
       </c>
       <c r="BO11">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="BP11">
         <v>14</v>
@@ -3376,7 +3376,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BU11">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BV11">
         <v>65</v>
@@ -3417,76 +3417,76 @@
         <v>124</v>
       </c>
       <c r="F12">
-        <v>4.8</v>
+        <v>5.7</v>
       </c>
       <c r="G12">
-        <v>5.9</v>
+        <v>6.8</v>
       </c>
       <c r="H12">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="I12">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="J12">
         <v>3.65</v>
       </c>
       <c r="K12">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L12">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="M12">
         <v>1.11</v>
       </c>
       <c r="N12">
-        <v>2.52</v>
+        <v>2.62</v>
       </c>
       <c r="O12">
         <v>1.53</v>
       </c>
       <c r="P12">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="Q12">
-        <v>2.54</v>
+        <v>2.6</v>
       </c>
       <c r="R12">
         <v>1.18</v>
       </c>
       <c r="S12">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="T12">
-        <v>2.32</v>
+        <v>2.4</v>
       </c>
       <c r="U12">
-        <v>1.63</v>
+        <v>1.57</v>
       </c>
       <c r="V12">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="W12">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="X12">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="Y12">
-        <v>6.2</v>
+        <v>5.7</v>
       </c>
       <c r="Z12">
+        <v>12</v>
+      </c>
+      <c r="AA12">
+        <v>20</v>
+      </c>
+      <c r="AB12">
+        <v>15</v>
+      </c>
+      <c r="AC12">
         <v>10</v>
-      </c>
-      <c r="AA12">
-        <v>24</v>
-      </c>
-      <c r="AB12">
-        <v>13.5</v>
-      </c>
-      <c r="AC12">
-        <v>9.800000000000001</v>
       </c>
       <c r="AD12">
         <v>11</v>
@@ -3495,10 +3495,10 @@
         <v>27</v>
       </c>
       <c r="AF12">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="AG12">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AH12">
         <v>38</v>
@@ -3507,130 +3507,130 @@
         <v>70</v>
       </c>
       <c r="AJ12">
-        <v>900</v>
+        <v>250</v>
       </c>
       <c r="AK12">
         <v>150</v>
       </c>
       <c r="AL12">
-        <v>700</v>
+        <v>180</v>
       </c>
       <c r="AM12">
-        <v>280</v>
+        <v>330</v>
       </c>
       <c r="AN12">
         <v>270</v>
       </c>
       <c r="AO12">
-        <v>26</v>
+        <v>50</v>
       </c>
       <c r="AP12">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ12">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AR12">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="AS12">
-        <v>7.8</v>
+        <v>16.5</v>
       </c>
       <c r="AT12">
         <v>11.5</v>
       </c>
       <c r="AU12">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AV12">
         <v>9.6</v>
       </c>
       <c r="AW12">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AX12">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AY12">
-        <v>17.5</v>
+        <v>21</v>
       </c>
       <c r="AZ12">
-        <v>15.5</v>
+        <v>25</v>
       </c>
       <c r="BA12">
-        <v>9.4</v>
+        <v>38</v>
       </c>
       <c r="BB12">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="BC12">
+        <v>10.5</v>
+      </c>
+      <c r="BD12">
+        <v>65</v>
+      </c>
+      <c r="BE12">
+        <v>11</v>
+      </c>
+      <c r="BF12">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BG12">
+        <v>16.5</v>
+      </c>
+      <c r="BH12">
+        <v>2.86</v>
+      </c>
+      <c r="BI12">
+        <v>2.42</v>
+      </c>
+      <c r="BJ12">
+        <v>13.5</v>
+      </c>
+      <c r="BK12">
+        <v>5.6</v>
+      </c>
+      <c r="BL12">
+        <v>1000</v>
+      </c>
+      <c r="BM12">
         <v>9.199999999999999</v>
       </c>
-      <c r="BD12">
+      <c r="BN12">
         <v>10</v>
       </c>
-      <c r="BE12">
-        <v>9.6</v>
-      </c>
-      <c r="BF12">
-        <v>9.6</v>
-      </c>
-      <c r="BG12">
-        <v>7.4</v>
-      </c>
-      <c r="BH12">
-        <v>1000</v>
-      </c>
-      <c r="BI12">
-        <v>2.32</v>
-      </c>
-      <c r="BJ12">
-        <v>1000</v>
-      </c>
-      <c r="BK12">
-        <v>1.14</v>
-      </c>
-      <c r="BL12">
-        <v>1000</v>
-      </c>
-      <c r="BM12">
-        <v>1.14</v>
-      </c>
-      <c r="BN12">
-        <v>9.6</v>
-      </c>
       <c r="BO12">
-        <v>1.02</v>
+        <v>5</v>
       </c>
       <c r="BP12">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="BQ12">
-        <v>1.12</v>
+        <v>8.4</v>
       </c>
       <c r="BR12">
         <v>1000</v>
       </c>
       <c r="BS12">
-        <v>1.14</v>
+        <v>8.6</v>
       </c>
       <c r="BT12">
-        <v>1000</v>
+        <v>4.3</v>
       </c>
       <c r="BU12">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="BV12">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="BW12">
-        <v>1.14</v>
+        <v>5.8</v>
       </c>
       <c r="BX12">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="BY12">
-        <v>1.14</v>
+        <v>7.8</v>
       </c>
       <c r="BZ12">
         <v>0</v>
@@ -3659,16 +3659,16 @@
         <v>125</v>
       </c>
       <c r="F13">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="G13">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="H13">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="I13">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="J13">
         <v>3.05</v>
@@ -3701,7 +3701,7 @@
         <v>6</v>
       </c>
       <c r="T13">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="U13">
         <v>1.77</v>
@@ -3710,13 +3710,13 @@
         <v>1.38</v>
       </c>
       <c r="W13">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="X13">
         <v>8</v>
       </c>
       <c r="Y13">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="Z13">
         <v>22</v>
@@ -3731,7 +3731,7 @@
         <v>7</v>
       </c>
       <c r="AD13">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AE13">
         <v>60</v>
@@ -3749,7 +3749,7 @@
         <v>85</v>
       </c>
       <c r="AJ13">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AK13">
         <v>38</v>
@@ -3764,13 +3764,13 @@
         <v>42</v>
       </c>
       <c r="AO13">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AP13">
         <v>7.4</v>
       </c>
       <c r="AQ13">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR13">
         <v>20</v>
@@ -3791,10 +3791,10 @@
         <v>50</v>
       </c>
       <c r="AX13">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AY13">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AZ13">
         <v>22</v>
@@ -3812,16 +3812,16 @@
         <v>60</v>
       </c>
       <c r="BE13">
-        <v>75</v>
+        <v>95</v>
       </c>
       <c r="BF13">
         <v>36</v>
       </c>
       <c r="BG13">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="BH13">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="BI13">
         <v>2.18</v>
@@ -3830,28 +3830,28 @@
         <v>14</v>
       </c>
       <c r="BK13">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="BL13">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="BM13">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BN13">
         <v>6</v>
       </c>
       <c r="BO13">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BP13">
         <v>22</v>
       </c>
       <c r="BQ13">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BR13">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="BS13">
         <v>5.1</v>
@@ -3860,19 +3860,19 @@
         <v>7.8</v>
       </c>
       <c r="BU13">
-        <v>5.8</v>
+        <v>5</v>
       </c>
       <c r="BV13">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="BW13">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BX13">
         <v>60</v>
       </c>
       <c r="BY13">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BZ13">
         <v>55</v>
@@ -3901,22 +3901,22 @@
         <v>126</v>
       </c>
       <c r="F14">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="G14">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="H14">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="I14">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="J14">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="K14">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="L14">
         <v>1.48</v>
@@ -3928,10 +3928,10 @@
         <v>3.15</v>
       </c>
       <c r="O14">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="P14">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="Q14">
         <v>2.24</v>
@@ -3943,22 +3943,22 @@
         <v>4.3</v>
       </c>
       <c r="T14">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="U14">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="V14">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="W14">
-        <v>2.24</v>
+        <v>2.32</v>
       </c>
       <c r="X14">
         <v>11.5</v>
       </c>
       <c r="Y14">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="Z14">
         <v>55</v>
@@ -3973,13 +3973,13 @@
         <v>8.6</v>
       </c>
       <c r="AD14">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="AE14">
         <v>120</v>
       </c>
       <c r="AF14">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AG14">
         <v>11</v>
@@ -3991,10 +3991,10 @@
         <v>130</v>
       </c>
       <c r="AJ14">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AK14">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AL14">
         <v>60</v>
@@ -4003,7 +4003,7 @@
         <v>580</v>
       </c>
       <c r="AN14">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AO14">
         <v>220</v>
@@ -4012,13 +4012,13 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AQ14">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AR14">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AS14">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AT14">
         <v>6</v>
@@ -4030,10 +4030,10 @@
         <v>20</v>
       </c>
       <c r="AW14">
-        <v>50</v>
+        <v>29</v>
       </c>
       <c r="AX14">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AY14">
         <v>9</v>
@@ -4042,37 +4042,37 @@
         <v>21</v>
       </c>
       <c r="BA14">
-        <v>28</v>
+        <v>55</v>
       </c>
       <c r="BB14">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BC14">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="BD14">
         <v>29</v>
       </c>
       <c r="BE14">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BF14">
         <v>11.5</v>
       </c>
       <c r="BG14">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BH14">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="BI14">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="BJ14">
         <v>14</v>
       </c>
       <c r="BK14">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="BL14">
         <v>1000</v>
@@ -4096,7 +4096,7 @@
         <v>40</v>
       </c>
       <c r="BS14">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BT14">
         <v>11.5</v>
@@ -4114,10 +4114,10 @@
         <v>90</v>
       </c>
       <c r="BY14">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BZ14">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="CA14">
         <v>4.3</v>
@@ -4385,22 +4385,22 @@
         <v>128</v>
       </c>
       <c r="F16">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="G16">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="H16">
-        <v>2.8</v>
+        <v>2.86</v>
       </c>
       <c r="I16">
-        <v>2.94</v>
+        <v>3.05</v>
       </c>
       <c r="J16">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="K16">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="L16">
         <v>1.31</v>
@@ -4412,31 +4412,31 @@
         <v>5.2</v>
       </c>
       <c r="O16">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="P16">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="Q16">
         <v>1.68</v>
       </c>
       <c r="R16">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="S16">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="T16">
         <v>1.61</v>
       </c>
       <c r="U16">
-        <v>2.3</v>
+        <v>2.54</v>
       </c>
       <c r="V16">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="W16">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="X16">
         <v>21</v>
@@ -4475,7 +4475,7 @@
         <v>34</v>
       </c>
       <c r="AJ16">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AK16">
         <v>24</v>
@@ -4484,13 +4484,13 @@
         <v>32</v>
       </c>
       <c r="AM16">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AN16">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AO16">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AP16">
         <v>18</v>
@@ -4502,10 +4502,10 @@
         <v>19.5</v>
       </c>
       <c r="AS16">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AT16">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AU16">
         <v>7.8</v>
@@ -4517,7 +4517,7 @@
         <v>24</v>
       </c>
       <c r="AX16">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AY16">
         <v>10.5</v>
@@ -4538,67 +4538,67 @@
         <v>25</v>
       </c>
       <c r="BE16">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="BF16">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BG16">
         <v>16</v>
       </c>
       <c r="BH16">
-        <v>1000</v>
+        <v>4.9</v>
       </c>
       <c r="BI16">
-        <v>1.04</v>
+        <v>3.25</v>
       </c>
       <c r="BJ16">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="BK16">
-        <v>1.04</v>
+        <v>5.4</v>
       </c>
       <c r="BL16">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="BM16">
-        <v>1.04</v>
+        <v>7.4</v>
       </c>
       <c r="BN16">
-        <v>1000</v>
+        <v>6</v>
       </c>
       <c r="BO16">
-        <v>1.04</v>
+        <v>5</v>
       </c>
       <c r="BP16">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="BQ16">
-        <v>1.04</v>
+        <v>5.5</v>
       </c>
       <c r="BR16">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="BS16">
-        <v>1.04</v>
+        <v>6</v>
       </c>
       <c r="BT16">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="BU16">
-        <v>1.04</v>
+        <v>5.4</v>
       </c>
       <c r="BV16">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="BW16">
-        <v>1.04</v>
+        <v>5.8</v>
       </c>
       <c r="BX16">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="BY16">
-        <v>1.04</v>
+        <v>6.2</v>
       </c>
       <c r="BZ16">
         <v>0</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-06.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-06.xlsx
@@ -403,7 +403,7 @@
     <t>Always Ready</t>
   </si>
   <si>
-    <t>2026-08-06 14:58:38</t>
+    <t>2026-08-06 17:18:17</t>
   </si>
 </sst>
 </file>
@@ -997,220 +997,220 @@
         <v>114</v>
       </c>
       <c r="F2">
-        <v>1.96</v>
+        <v>2.36</v>
       </c>
       <c r="G2">
-        <v>2.02</v>
+        <v>2.46</v>
       </c>
       <c r="H2">
         <v>3.7</v>
       </c>
       <c r="I2">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="J2">
+        <v>3.1</v>
+      </c>
+      <c r="K2">
+        <v>3.25</v>
+      </c>
+      <c r="L2">
+        <v>0</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>7.8</v>
+      </c>
+      <c r="O2">
+        <v>1.13</v>
+      </c>
+      <c r="P2">
+        <v>2.48</v>
+      </c>
+      <c r="Q2">
+        <v>1.59</v>
+      </c>
+      <c r="R2">
+        <v>1.44</v>
+      </c>
+      <c r="S2">
+        <v>2.96</v>
+      </c>
+      <c r="T2">
+        <v>1.19</v>
+      </c>
+      <c r="U2">
+        <v>5.4</v>
+      </c>
+      <c r="V2">
+        <v>1.33</v>
+      </c>
+      <c r="W2">
+        <v>1.7</v>
+      </c>
+      <c r="X2">
+        <v>1000</v>
+      </c>
+      <c r="Y2">
+        <v>9</v>
+      </c>
+      <c r="Z2">
+        <v>28</v>
+      </c>
+      <c r="AA2">
+        <v>170</v>
+      </c>
+      <c r="AB2">
+        <v>1000</v>
+      </c>
+      <c r="AC2">
+        <v>4.7</v>
+      </c>
+      <c r="AD2">
+        <v>16</v>
+      </c>
+      <c r="AE2">
+        <v>110</v>
+      </c>
+      <c r="AF2">
+        <v>1000</v>
+      </c>
+      <c r="AG2">
+        <v>4.9</v>
+      </c>
+      <c r="AH2">
+        <v>14.5</v>
+      </c>
+      <c r="AI2">
+        <v>140</v>
+      </c>
+      <c r="AJ2">
+        <v>1000</v>
+      </c>
+      <c r="AK2">
+        <v>12</v>
+      </c>
+      <c r="AL2">
+        <v>28</v>
+      </c>
+      <c r="AM2">
+        <v>220</v>
+      </c>
+      <c r="AN2">
+        <v>16</v>
+      </c>
+      <c r="AO2">
+        <v>300</v>
+      </c>
+      <c r="AP2">
+        <v>11</v>
+      </c>
+      <c r="AQ2">
+        <v>7.8</v>
+      </c>
+      <c r="AR2">
+        <v>21</v>
+      </c>
+      <c r="AS2">
+        <v>10</v>
+      </c>
+      <c r="AT2">
+        <v>11</v>
+      </c>
+      <c r="AU2">
         <v>4.1</v>
       </c>
-      <c r="K2">
-        <v>4.3</v>
-      </c>
-      <c r="L2">
-        <v>1.26</v>
-      </c>
-      <c r="M2">
-        <v>1.04</v>
-      </c>
-      <c r="N2">
-        <v>6.2</v>
-      </c>
-      <c r="O2">
-        <v>1.17</v>
-      </c>
-      <c r="P2">
-        <v>2.74</v>
-      </c>
-      <c r="Q2">
-        <v>1.53</v>
-      </c>
-      <c r="R2">
-        <v>1.71</v>
-      </c>
-      <c r="S2">
-        <v>2.3</v>
-      </c>
-      <c r="T2">
-        <v>1.53</v>
-      </c>
-      <c r="U2">
-        <v>2.64</v>
-      </c>
-      <c r="V2">
-        <v>1.34</v>
-      </c>
-      <c r="W2">
-        <v>1.98</v>
-      </c>
-      <c r="X2">
-        <v>32</v>
-      </c>
-      <c r="Y2">
-        <v>23</v>
-      </c>
-      <c r="Z2">
-        <v>34</v>
-      </c>
-      <c r="AA2">
-        <v>80</v>
-      </c>
-      <c r="AB2">
-        <v>18.5</v>
-      </c>
-      <c r="AC2">
-        <v>10.5</v>
-      </c>
-      <c r="AD2">
-        <v>19</v>
-      </c>
-      <c r="AE2">
-        <v>38</v>
-      </c>
-      <c r="AF2">
-        <v>17</v>
-      </c>
-      <c r="AG2">
-        <v>11.5</v>
-      </c>
-      <c r="AH2">
-        <v>17</v>
-      </c>
-      <c r="AI2">
-        <v>38</v>
-      </c>
-      <c r="AJ2">
-        <v>28</v>
-      </c>
-      <c r="AK2">
-        <v>18</v>
-      </c>
-      <c r="AL2">
-        <v>26</v>
-      </c>
-      <c r="AM2">
-        <v>60</v>
-      </c>
-      <c r="AN2">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AO2">
-        <v>25</v>
-      </c>
-      <c r="AP2">
-        <v>22</v>
-      </c>
-      <c r="AQ2">
-        <v>19</v>
-      </c>
-      <c r="AR2">
-        <v>29</v>
-      </c>
-      <c r="AS2">
-        <v>55</v>
-      </c>
-      <c r="AT2">
+      <c r="AV2">
         <v>13</v>
       </c>
-      <c r="AU2">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AV2">
-        <v>14.5</v>
-      </c>
       <c r="AW2">
-        <v>32</v>
+        <v>65</v>
       </c>
       <c r="AX2">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AY2">
-        <v>9.6</v>
+        <v>4.4</v>
       </c>
       <c r="AZ2">
         <v>12.5</v>
       </c>
       <c r="BA2">
-        <v>32</v>
+        <v>75</v>
       </c>
       <c r="BB2">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="BC2">
-        <v>15.5</v>
+        <v>10</v>
       </c>
       <c r="BD2">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="BE2">
-        <v>30</v>
+        <v>65</v>
       </c>
       <c r="BF2">
-        <v>7.8</v>
+        <v>12</v>
       </c>
       <c r="BG2">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="BH2">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="BI2">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="BJ2">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="BK2">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="BL2">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM2">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="BN2">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="BO2">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="BP2">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="BQ2">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="BR2">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="BS2">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="BT2">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="BU2">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="BV2">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="BW2">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="BX2">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="BY2">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="BZ2">
         <v>0</v>
@@ -1239,220 +1239,220 @@
         <v>115</v>
       </c>
       <c r="F3">
-        <v>1.81</v>
+        <v>1.99</v>
       </c>
       <c r="G3">
-        <v>1.88</v>
+        <v>2.06</v>
       </c>
       <c r="H3">
-        <v>5.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I3">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="J3">
-        <v>3.4</v>
+        <v>2.56</v>
       </c>
       <c r="K3">
+        <v>2.64</v>
+      </c>
+      <c r="L3">
+        <v>0</v>
+      </c>
+      <c r="M3">
+        <v>1.35</v>
+      </c>
+      <c r="N3">
+        <v>1.57</v>
+      </c>
+      <c r="O3">
+        <v>2.6</v>
+      </c>
+      <c r="P3">
+        <v>1.15</v>
+      </c>
+      <c r="Q3">
+        <v>6.8</v>
+      </c>
+      <c r="R3">
+        <v>1.03</v>
+      </c>
+      <c r="S3">
+        <v>24</v>
+      </c>
+      <c r="T3">
+        <v>4.9</v>
+      </c>
+      <c r="U3">
+        <v>1.22</v>
+      </c>
+      <c r="V3">
+        <v>1.12</v>
+      </c>
+      <c r="W3">
+        <v>1.96</v>
+      </c>
+      <c r="X3">
         <v>3.7</v>
       </c>
-      <c r="L3">
-        <v>1.55</v>
-      </c>
-      <c r="M3">
-        <v>1.11</v>
-      </c>
-      <c r="N3">
-        <v>2.92</v>
-      </c>
-      <c r="O3">
-        <v>1.48</v>
-      </c>
-      <c r="P3">
-        <v>1.65</v>
-      </c>
-      <c r="Q3">
-        <v>2.42</v>
-      </c>
-      <c r="R3">
-        <v>1.22</v>
-      </c>
-      <c r="S3">
-        <v>5</v>
-      </c>
-      <c r="T3">
-        <v>2.16</v>
-      </c>
-      <c r="U3">
-        <v>1.75</v>
-      </c>
-      <c r="V3">
-        <v>1.2</v>
-      </c>
-      <c r="W3">
-        <v>2.12</v>
-      </c>
-      <c r="X3">
+      <c r="Y3">
+        <v>28</v>
+      </c>
+      <c r="Z3">
+        <v>90</v>
+      </c>
+      <c r="AA3">
+        <v>1000</v>
+      </c>
+      <c r="AB3">
+        <v>3.9</v>
+      </c>
+      <c r="AC3">
         <v>10.5</v>
       </c>
-      <c r="Y3">
-        <v>15</v>
-      </c>
-      <c r="Z3">
-        <v>46</v>
-      </c>
-      <c r="AA3">
-        <v>900</v>
-      </c>
-      <c r="AB3">
+      <c r="AD3">
+        <v>85</v>
+      </c>
+      <c r="AE3">
+        <v>1000</v>
+      </c>
+      <c r="AF3">
+        <v>9</v>
+      </c>
+      <c r="AG3">
+        <v>25</v>
+      </c>
+      <c r="AH3">
+        <v>150</v>
+      </c>
+      <c r="AI3">
+        <v>1000</v>
+      </c>
+      <c r="AJ3">
+        <v>1000</v>
+      </c>
+      <c r="AK3">
+        <v>1000</v>
+      </c>
+      <c r="AL3">
+        <v>1000</v>
+      </c>
+      <c r="AM3">
+        <v>1000</v>
+      </c>
+      <c r="AN3">
+        <v>110</v>
+      </c>
+      <c r="AO3">
+        <v>1000</v>
+      </c>
+      <c r="AP3">
+        <v>3.5</v>
+      </c>
+      <c r="AQ3">
+        <v>10.5</v>
+      </c>
+      <c r="AR3">
+        <v>8.6</v>
+      </c>
+      <c r="AS3">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AT3">
+        <v>3.55</v>
+      </c>
+      <c r="AU3">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AV3">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AW3">
+        <v>9.4</v>
+      </c>
+      <c r="AX3">
         <v>7.4</v>
       </c>
-      <c r="AC3">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AD3">
-        <v>24</v>
-      </c>
-      <c r="AE3">
-        <v>120</v>
-      </c>
-      <c r="AF3">
-        <v>10.5</v>
-      </c>
-      <c r="AG3">
-        <v>9</v>
-      </c>
-      <c r="AH3">
-        <v>27</v>
-      </c>
-      <c r="AI3">
-        <v>190</v>
-      </c>
-      <c r="AJ3">
-        <v>22</v>
-      </c>
-      <c r="AK3">
+      <c r="AY3">
+        <v>7.6</v>
+      </c>
+      <c r="AZ3">
+        <v>80</v>
+      </c>
+      <c r="BA3">
+        <v>29</v>
+      </c>
+      <c r="BB3">
         <v>26</v>
       </c>
-      <c r="AL3">
-        <v>60</v>
-      </c>
-      <c r="AM3">
-        <v>580</v>
-      </c>
-      <c r="AN3">
-        <v>19.5</v>
-      </c>
-      <c r="AO3">
-        <v>200</v>
-      </c>
-      <c r="AP3">
+      <c r="BC3">
+        <v>65</v>
+      </c>
+      <c r="BD3">
+        <v>6.4</v>
+      </c>
+      <c r="BE3">
         <v>8.800000000000001</v>
       </c>
-      <c r="AQ3">
-        <v>13</v>
-      </c>
-      <c r="AR3">
-        <v>32</v>
-      </c>
-      <c r="AS3">
-        <v>12</v>
-      </c>
-      <c r="AT3">
-        <v>5.9</v>
-      </c>
-      <c r="AU3">
-        <v>7.2</v>
-      </c>
-      <c r="AV3">
-        <v>20</v>
-      </c>
-      <c r="AW3">
-        <v>11.5</v>
-      </c>
-      <c r="AX3">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AY3">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AZ3">
-        <v>22</v>
-      </c>
-      <c r="BA3">
-        <v>10.5</v>
-      </c>
-      <c r="BB3">
-        <v>18.5</v>
-      </c>
-      <c r="BC3">
-        <v>22</v>
-      </c>
-      <c r="BD3">
-        <v>38</v>
-      </c>
-      <c r="BE3">
-        <v>13</v>
-      </c>
       <c r="BF3">
-        <v>8.4</v>
+        <v>65</v>
       </c>
       <c r="BG3">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="BH3">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="BI3">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="BJ3">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="BK3">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="BL3">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM3">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="BN3">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="BO3">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="BP3">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="BQ3">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="BR3">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="BS3">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="BT3">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="BU3">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="BV3">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="BW3">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="BX3">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="BY3">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="BZ3">
         <v>0</v>
@@ -1481,226 +1481,226 @@
         <v>116</v>
       </c>
       <c r="F4">
-        <v>1.5</v>
+        <v>1.19</v>
       </c>
       <c r="G4">
-        <v>1.54</v>
+        <v>1.21</v>
       </c>
       <c r="H4">
-        <v>5.6</v>
+        <v>23</v>
       </c>
       <c r="I4">
-        <v>6.2</v>
+        <v>28</v>
       </c>
       <c r="J4">
-        <v>5.5</v>
+        <v>7.6</v>
       </c>
       <c r="K4">
-        <v>6.2</v>
+        <v>8.4</v>
       </c>
       <c r="L4">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="M4">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="N4">
-        <v>9.800000000000001</v>
+        <v>7.2</v>
       </c>
       <c r="O4">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="P4">
-        <v>4.1</v>
+        <v>2.46</v>
       </c>
       <c r="Q4">
-        <v>1.3</v>
+        <v>1.62</v>
       </c>
       <c r="R4">
-        <v>2.24</v>
+        <v>1.48</v>
       </c>
       <c r="S4">
-        <v>1.75</v>
+        <v>3</v>
       </c>
       <c r="T4">
-        <v>1.48</v>
+        <v>2.14</v>
       </c>
       <c r="U4">
-        <v>2.88</v>
+        <v>1.79</v>
       </c>
       <c r="V4">
-        <v>1.19</v>
+        <v>1.03</v>
       </c>
       <c r="W4">
-        <v>2.84</v>
+        <v>5.7</v>
       </c>
       <c r="X4">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="Y4">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="Z4">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AA4">
-        <v>700</v>
+        <v>1000</v>
       </c>
       <c r="AB4">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="AC4">
-        <v>17</v>
+        <v>12.5</v>
       </c>
       <c r="AD4">
-        <v>26</v>
+        <v>50</v>
       </c>
       <c r="AE4">
-        <v>75</v>
+        <v>240</v>
       </c>
       <c r="AF4">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="AG4">
-        <v>12.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AH4">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="AI4">
-        <v>46</v>
+        <v>180</v>
       </c>
       <c r="AJ4">
-        <v>18.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AK4">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="AL4">
-        <v>22</v>
+        <v>50</v>
       </c>
       <c r="AM4">
-        <v>65</v>
+        <v>260</v>
       </c>
       <c r="AN4">
-        <v>3.85</v>
+        <v>6.6</v>
       </c>
       <c r="AO4">
-        <v>36</v>
+        <v>460</v>
       </c>
       <c r="AP4">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="AQ4">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="AR4">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="AS4">
+        <v>14</v>
+      </c>
+      <c r="AT4">
+        <v>7.2</v>
+      </c>
+      <c r="AU4">
         <v>11</v>
       </c>
-      <c r="AT4">
-        <v>16.5</v>
-      </c>
-      <c r="AU4">
+      <c r="AV4">
+        <v>34</v>
+      </c>
+      <c r="AW4">
+        <v>13</v>
+      </c>
+      <c r="AX4">
+        <v>5.3</v>
+      </c>
+      <c r="AY4">
+        <v>8</v>
+      </c>
+      <c r="AZ4">
+        <v>25</v>
+      </c>
+      <c r="BA4">
+        <v>13</v>
+      </c>
+      <c r="BB4">
+        <v>7</v>
+      </c>
+      <c r="BC4">
+        <v>11.5</v>
+      </c>
+      <c r="BD4">
+        <v>11</v>
+      </c>
+      <c r="BE4">
+        <v>13</v>
+      </c>
+      <c r="BF4">
+        <v>5.9</v>
+      </c>
+      <c r="BG4">
         <v>13.5</v>
       </c>
-      <c r="AV4">
-        <v>19.5</v>
-      </c>
-      <c r="AW4">
-        <v>25</v>
-      </c>
-      <c r="AX4">
-        <v>14.5</v>
-      </c>
-      <c r="AY4">
-        <v>10</v>
-      </c>
-      <c r="AZ4">
-        <v>15</v>
-      </c>
-      <c r="BA4">
-        <v>36</v>
-      </c>
-      <c r="BB4">
-        <v>15.5</v>
-      </c>
-      <c r="BC4">
-        <v>12</v>
-      </c>
-      <c r="BD4">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BE4">
-        <v>32</v>
-      </c>
-      <c r="BF4">
-        <v>3.55</v>
-      </c>
-      <c r="BG4">
-        <v>24</v>
-      </c>
       <c r="BH4">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="BI4">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="BJ4">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="BK4">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="BL4">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="BM4">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="BN4">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="BO4">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="BP4">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="BQ4">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="BR4">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="BS4">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="BT4">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="BU4">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="BV4">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="BW4">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="BX4">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="BY4">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="BZ4">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="CA4">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="CB4" t="s">
         <v>129</v>
@@ -1723,226 +1723,226 @@
         <v>117</v>
       </c>
       <c r="F5">
-        <v>2.82</v>
+        <v>3.35</v>
       </c>
       <c r="G5">
+        <v>3.5</v>
+      </c>
+      <c r="H5">
         <v>2.96</v>
       </c>
-      <c r="H5">
-        <v>2.94</v>
-      </c>
       <c r="I5">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="J5">
-        <v>3.05</v>
+        <v>2.6</v>
       </c>
       <c r="K5">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
       <c r="L5">
-        <v>1.46</v>
+        <v>6.8</v>
       </c>
       <c r="M5">
+        <v>1.25</v>
+      </c>
+      <c r="N5">
+        <v>1.99</v>
+      </c>
+      <c r="O5">
+        <v>1.96</v>
+      </c>
+      <c r="P5">
+        <v>1.28</v>
+      </c>
+      <c r="Q5">
+        <v>4.2</v>
+      </c>
+      <c r="R5">
         <v>1.09</v>
       </c>
-      <c r="N5">
-        <v>3.6</v>
-      </c>
-      <c r="O5">
-        <v>1.37</v>
-      </c>
-      <c r="P5">
-        <v>1.79</v>
-      </c>
-      <c r="Q5">
-        <v>2.14</v>
-      </c>
-      <c r="R5">
-        <v>1.31</v>
-      </c>
       <c r="S5">
-        <v>3.9</v>
+        <v>11</v>
       </c>
       <c r="T5">
-        <v>1.82</v>
+        <v>2.84</v>
       </c>
       <c r="U5">
-        <v>2.06</v>
+        <v>1.51</v>
       </c>
       <c r="V5">
         <v>1.47</v>
       </c>
       <c r="W5">
-        <v>1.51</v>
+        <v>1.4</v>
       </c>
       <c r="X5">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="Y5">
-        <v>11.5</v>
+        <v>6.4</v>
       </c>
       <c r="Z5">
-        <v>21</v>
+        <v>16.5</v>
       </c>
       <c r="AA5">
+        <v>70</v>
+      </c>
+      <c r="AB5">
+        <v>7.2</v>
+      </c>
+      <c r="AC5">
+        <v>7.2</v>
+      </c>
+      <c r="AD5">
+        <v>20</v>
+      </c>
+      <c r="AE5">
+        <v>85</v>
+      </c>
+      <c r="AF5">
+        <v>19.5</v>
+      </c>
+      <c r="AG5">
+        <v>22</v>
+      </c>
+      <c r="AH5">
+        <v>46</v>
+      </c>
+      <c r="AI5">
+        <v>1000</v>
+      </c>
+      <c r="AJ5">
+        <v>95</v>
+      </c>
+      <c r="AK5">
+        <v>120</v>
+      </c>
+      <c r="AL5">
+        <v>270</v>
+      </c>
+      <c r="AM5">
+        <v>1000</v>
+      </c>
+      <c r="AN5">
+        <v>190</v>
+      </c>
+      <c r="AO5">
+        <v>130</v>
+      </c>
+      <c r="AP5">
+        <v>4.6</v>
+      </c>
+      <c r="AQ5">
+        <v>5.9</v>
+      </c>
+      <c r="AR5">
+        <v>14.5</v>
+      </c>
+      <c r="AS5">
+        <v>46</v>
+      </c>
+      <c r="AT5">
+        <v>6.6</v>
+      </c>
+      <c r="AU5">
+        <v>6.6</v>
+      </c>
+      <c r="AV5">
+        <v>16.5</v>
+      </c>
+      <c r="AW5">
         <v>60</v>
       </c>
-      <c r="AB5">
-        <v>11</v>
-      </c>
-      <c r="AC5">
-        <v>7.4</v>
-      </c>
-      <c r="AD5">
-        <v>14</v>
-      </c>
-      <c r="AE5">
+      <c r="AX5">
+        <v>17.5</v>
+      </c>
+      <c r="AY5">
+        <v>18</v>
+      </c>
+      <c r="AZ5">
         <v>38</v>
       </c>
-      <c r="AF5">
-        <v>19</v>
-      </c>
-      <c r="AG5">
-        <v>13.5</v>
-      </c>
-      <c r="AH5">
-        <v>17.5</v>
-      </c>
-      <c r="AI5">
-        <v>60</v>
-      </c>
-      <c r="AJ5">
-        <v>50</v>
-      </c>
-      <c r="AK5">
-        <v>36</v>
-      </c>
-      <c r="AL5">
-        <v>60</v>
-      </c>
-      <c r="AM5">
+      <c r="BA5">
+        <v>140</v>
+      </c>
+      <c r="BB5">
+        <v>65</v>
+      </c>
+      <c r="BC5">
+        <v>70</v>
+      </c>
+      <c r="BD5">
+        <v>160</v>
+      </c>
+      <c r="BE5">
+        <v>360</v>
+      </c>
+      <c r="BF5">
         <v>130</v>
       </c>
-      <c r="AN5">
-        <v>40</v>
-      </c>
-      <c r="AO5">
-        <v>38</v>
-      </c>
-      <c r="AP5">
-        <v>10</v>
-      </c>
-      <c r="AQ5">
-        <v>9.6</v>
-      </c>
-      <c r="AR5">
-        <v>16.5</v>
-      </c>
-      <c r="AS5">
-        <v>38</v>
-      </c>
-      <c r="AT5">
-        <v>9.4</v>
-      </c>
-      <c r="AU5">
-        <v>6.2</v>
-      </c>
-      <c r="AV5">
-        <v>11</v>
-      </c>
-      <c r="AW5">
-        <v>26</v>
-      </c>
-      <c r="AX5">
-        <v>15.5</v>
-      </c>
-      <c r="AY5">
-        <v>11</v>
-      </c>
-      <c r="AZ5">
-        <v>14.5</v>
-      </c>
-      <c r="BA5">
-        <v>36</v>
-      </c>
-      <c r="BB5">
-        <v>29</v>
-      </c>
-      <c r="BC5">
-        <v>25</v>
-      </c>
-      <c r="BD5">
-        <v>38</v>
-      </c>
-      <c r="BE5">
-        <v>70</v>
-      </c>
-      <c r="BF5">
-        <v>23</v>
-      </c>
       <c r="BG5">
-        <v>23</v>
+        <v>85</v>
       </c>
       <c r="BH5">
-        <v>3.25</v>
+        <v>1.26</v>
       </c>
       <c r="BI5">
-        <v>2.8</v>
+        <v>1.21</v>
       </c>
       <c r="BJ5">
-        <v>12</v>
+        <v>950</v>
       </c>
       <c r="BK5">
-        <v>8</v>
+        <v>4.9</v>
       </c>
       <c r="BL5">
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>5.6</v>
+        <v>4.9</v>
       </c>
       <c r="BN5">
-        <v>6.8</v>
+        <v>800</v>
       </c>
       <c r="BO5">
+        <v>7.2</v>
+      </c>
+      <c r="BP5">
+        <v>1000</v>
+      </c>
+      <c r="BQ5">
         <v>4.9</v>
       </c>
-      <c r="BP5">
-        <v>27</v>
-      </c>
-      <c r="BQ5">
-        <v>5.1</v>
-      </c>
       <c r="BR5">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="BS5">
-        <v>5.4</v>
+        <v>4.9</v>
       </c>
       <c r="BT5">
-        <v>7</v>
+        <v>800</v>
       </c>
       <c r="BU5">
-        <v>5</v>
+        <v>7.2</v>
       </c>
       <c r="BV5">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="BW5">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
       <c r="BX5">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="BY5">
-        <v>5.5</v>
+        <v>4.9</v>
       </c>
       <c r="BZ5">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="CA5">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="CB5" t="s">
         <v>129</v>
@@ -1965,220 +1965,220 @@
         <v>118</v>
       </c>
       <c r="F6">
-        <v>2.36</v>
+        <v>2.22</v>
       </c>
       <c r="G6">
-        <v>2.4</v>
+        <v>2.28</v>
       </c>
       <c r="H6">
-        <v>3.45</v>
+        <v>3.7</v>
       </c>
       <c r="I6">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="J6">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K6">
         <v>3.45</v>
       </c>
       <c r="L6">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="M6">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="N6">
-        <v>4.1</v>
+        <v>3.45</v>
       </c>
       <c r="O6">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="P6">
-        <v>2.02</v>
+        <v>1.82</v>
       </c>
       <c r="Q6">
-        <v>1.9</v>
+        <v>2.12</v>
       </c>
       <c r="R6">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="S6">
-        <v>3.2</v>
+        <v>3.85</v>
       </c>
       <c r="T6">
-        <v>1.75</v>
+        <v>1.87</v>
       </c>
       <c r="U6">
-        <v>2.24</v>
+        <v>2.04</v>
       </c>
       <c r="V6">
-        <v>1.39</v>
+        <v>1.34</v>
       </c>
       <c r="W6">
-        <v>1.72</v>
+        <v>1.79</v>
       </c>
       <c r="X6">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="Y6">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="Z6">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AA6">
+        <v>80</v>
+      </c>
+      <c r="AB6">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AC6">
+        <v>7.6</v>
+      </c>
+      <c r="AD6">
+        <v>16</v>
+      </c>
+      <c r="AE6">
+        <v>55</v>
+      </c>
+      <c r="AF6">
+        <v>14.5</v>
+      </c>
+      <c r="AG6">
+        <v>11.5</v>
+      </c>
+      <c r="AH6">
+        <v>18.5</v>
+      </c>
+      <c r="AI6">
         <v>70</v>
       </c>
-      <c r="AB6">
-        <v>11</v>
-      </c>
-      <c r="AC6">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AD6">
-        <v>15</v>
-      </c>
-      <c r="AE6">
-        <v>40</v>
-      </c>
-      <c r="AF6">
-        <v>15</v>
-      </c>
-      <c r="AG6">
-        <v>11</v>
-      </c>
-      <c r="AH6">
-        <v>17.5</v>
-      </c>
-      <c r="AI6">
-        <v>46</v>
-      </c>
       <c r="AJ6">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AK6">
         <v>25</v>
       </c>
       <c r="AL6">
+        <v>55</v>
+      </c>
+      <c r="AM6">
+        <v>120</v>
+      </c>
+      <c r="AN6">
+        <v>24</v>
+      </c>
+      <c r="AO6">
+        <v>1000</v>
+      </c>
+      <c r="AP6">
+        <v>11.5</v>
+      </c>
+      <c r="AQ6">
+        <v>11.5</v>
+      </c>
+      <c r="AR6">
+        <v>20</v>
+      </c>
+      <c r="AS6">
+        <v>55</v>
+      </c>
+      <c r="AT6">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AU6">
+        <v>7</v>
+      </c>
+      <c r="AV6">
+        <v>13</v>
+      </c>
+      <c r="AW6">
+        <v>30</v>
+      </c>
+      <c r="AX6">
+        <v>11.5</v>
+      </c>
+      <c r="AY6">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ6">
+        <v>16</v>
+      </c>
+      <c r="BA6">
+        <v>46</v>
+      </c>
+      <c r="BB6">
+        <v>25</v>
+      </c>
+      <c r="BC6">
+        <v>22</v>
+      </c>
+      <c r="BD6">
+        <v>28</v>
+      </c>
+      <c r="BE6">
+        <v>75</v>
+      </c>
+      <c r="BF6">
+        <v>16.5</v>
+      </c>
+      <c r="BG6">
+        <v>38</v>
+      </c>
+      <c r="BH6">
+        <v>2.84</v>
+      </c>
+      <c r="BI6">
+        <v>2.62</v>
+      </c>
+      <c r="BJ6">
+        <v>11.5</v>
+      </c>
+      <c r="BK6">
+        <v>10</v>
+      </c>
+      <c r="BL6">
+        <v>160</v>
+      </c>
+      <c r="BM6">
+        <v>140</v>
+      </c>
+      <c r="BN6">
+        <v>5</v>
+      </c>
+      <c r="BO6">
+        <v>4.4</v>
+      </c>
+      <c r="BP6">
+        <v>23</v>
+      </c>
+      <c r="BQ6">
+        <v>17</v>
+      </c>
+      <c r="BR6">
+        <v>46</v>
+      </c>
+      <c r="BS6">
         <v>36</v>
-      </c>
-      <c r="AM6">
-        <v>85</v>
-      </c>
-      <c r="AN6">
-        <v>17.5</v>
-      </c>
-      <c r="AO6">
-        <v>36</v>
-      </c>
-      <c r="AP6">
-        <v>13</v>
-      </c>
-      <c r="AQ6">
-        <v>13</v>
-      </c>
-      <c r="AR6">
-        <v>22</v>
-      </c>
-      <c r="AS6">
-        <v>48</v>
-      </c>
-      <c r="AT6">
-        <v>10</v>
-      </c>
-      <c r="AU6">
-        <v>7.2</v>
-      </c>
-      <c r="AV6">
-        <v>13.5</v>
-      </c>
-      <c r="AW6">
-        <v>34</v>
-      </c>
-      <c r="AX6">
-        <v>13</v>
-      </c>
-      <c r="AY6">
-        <v>10</v>
-      </c>
-      <c r="AZ6">
-        <v>15</v>
-      </c>
-      <c r="BA6">
-        <v>40</v>
-      </c>
-      <c r="BB6">
-        <v>27</v>
-      </c>
-      <c r="BC6">
-        <v>21</v>
-      </c>
-      <c r="BD6">
-        <v>30</v>
-      </c>
-      <c r="BE6">
-        <v>60</v>
-      </c>
-      <c r="BF6">
-        <v>14.5</v>
-      </c>
-      <c r="BG6">
-        <v>25</v>
-      </c>
-      <c r="BH6">
-        <v>3.45</v>
-      </c>
-      <c r="BI6">
-        <v>2.74</v>
-      </c>
-      <c r="BJ6">
-        <v>9.6</v>
-      </c>
-      <c r="BK6">
-        <v>5.2</v>
-      </c>
-      <c r="BL6">
-        <v>1000</v>
-      </c>
-      <c r="BM6">
-        <v>10</v>
-      </c>
-      <c r="BN6">
-        <v>5.2</v>
-      </c>
-      <c r="BO6">
-        <v>4.6</v>
-      </c>
-      <c r="BP6">
-        <v>19.5</v>
-      </c>
-      <c r="BQ6">
-        <v>7</v>
-      </c>
-      <c r="BR6">
-        <v>36</v>
-      </c>
-      <c r="BS6">
-        <v>8.4</v>
       </c>
       <c r="BT6">
         <v>6.8</v>
       </c>
       <c r="BU6">
-        <v>4.4</v>
+        <v>5.7</v>
       </c>
       <c r="BV6">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="BW6">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="BX6">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="BY6">
-        <v>8.800000000000001</v>
+        <v>50</v>
       </c>
       <c r="BZ6">
         <v>0</v>
@@ -2207,226 +2207,226 @@
         <v>119</v>
       </c>
       <c r="F7">
-        <v>2.2</v>
+        <v>2.62</v>
       </c>
       <c r="G7">
-        <v>2.3</v>
+        <v>2.72</v>
       </c>
       <c r="H7">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="I7">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="J7">
-        <v>3.6</v>
+        <v>2.96</v>
       </c>
       <c r="K7">
-        <v>3.85</v>
+        <v>3.15</v>
       </c>
       <c r="L7">
-        <v>1.42</v>
+        <v>1.01</v>
       </c>
       <c r="M7">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="N7">
-        <v>3.65</v>
+        <v>2.46</v>
       </c>
       <c r="O7">
-        <v>1.33</v>
+        <v>1.64</v>
       </c>
       <c r="P7">
-        <v>1.9</v>
+        <v>1.49</v>
       </c>
       <c r="Q7">
-        <v>2</v>
+        <v>2.88</v>
       </c>
       <c r="R7">
-        <v>1.34</v>
+        <v>1.16</v>
       </c>
       <c r="S7">
-        <v>3.6</v>
+        <v>6.6</v>
       </c>
       <c r="T7">
-        <v>1.81</v>
+        <v>1.05</v>
       </c>
       <c r="U7">
-        <v>2.08</v>
+        <v>1.01</v>
       </c>
       <c r="V7">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="W7">
-        <v>1.76</v>
+        <v>1.1</v>
       </c>
       <c r="X7">
-        <v>14.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Y7">
-        <v>13</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z7">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AA7">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="AB7">
-        <v>10</v>
+        <v>7.6</v>
       </c>
       <c r="AC7">
+        <v>7.2</v>
+      </c>
+      <c r="AD7">
+        <v>16</v>
+      </c>
+      <c r="AE7">
+        <v>65</v>
+      </c>
+      <c r="AF7">
+        <v>16.5</v>
+      </c>
+      <c r="AG7">
+        <v>13.5</v>
+      </c>
+      <c r="AH7">
+        <v>32</v>
+      </c>
+      <c r="AI7">
+        <v>120</v>
+      </c>
+      <c r="AJ7">
+        <v>46</v>
+      </c>
+      <c r="AK7">
+        <v>44</v>
+      </c>
+      <c r="AL7">
+        <v>95</v>
+      </c>
+      <c r="AM7">
+        <v>280</v>
+      </c>
+      <c r="AN7">
+        <v>60</v>
+      </c>
+      <c r="AO7">
+        <v>85</v>
+      </c>
+      <c r="AP7">
+        <v>6.8</v>
+      </c>
+      <c r="AQ7">
         <v>8.4</v>
       </c>
-      <c r="AD7">
-        <v>14.5</v>
-      </c>
-      <c r="AE7">
-        <v>44</v>
-      </c>
-      <c r="AF7">
-        <v>14.5</v>
-      </c>
-      <c r="AG7">
-        <v>11.5</v>
-      </c>
-      <c r="AH7">
-        <v>19</v>
-      </c>
-      <c r="AI7">
-        <v>55</v>
-      </c>
-      <c r="AJ7">
-        <v>30</v>
-      </c>
-      <c r="AK7">
-        <v>25</v>
-      </c>
-      <c r="AL7">
-        <v>42</v>
-      </c>
-      <c r="AM7">
-        <v>110</v>
-      </c>
-      <c r="AN7">
-        <v>19</v>
-      </c>
-      <c r="AO7">
-        <v>44</v>
-      </c>
-      <c r="AP7">
-        <v>12</v>
-      </c>
-      <c r="AQ7">
-        <v>11</v>
-      </c>
       <c r="AR7">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="AS7">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AT7">
-        <v>9</v>
+        <v>6.6</v>
       </c>
       <c r="AU7">
-        <v>7.2</v>
+        <v>6.2</v>
       </c>
       <c r="AV7">
         <v>12.5</v>
       </c>
       <c r="AW7">
+        <v>42</v>
+      </c>
+      <c r="AX7">
+        <v>13</v>
+      </c>
+      <c r="AY7">
+        <v>11</v>
+      </c>
+      <c r="AZ7">
+        <v>20</v>
+      </c>
+      <c r="BA7">
+        <v>65</v>
+      </c>
+      <c r="BB7">
         <v>34</v>
       </c>
-      <c r="AX7">
+      <c r="BC7">
+        <v>34</v>
+      </c>
+      <c r="BD7">
+        <v>60</v>
+      </c>
+      <c r="BE7">
+        <v>180</v>
+      </c>
+      <c r="BF7">
+        <v>36</v>
+      </c>
+      <c r="BG7">
+        <v>55</v>
+      </c>
+      <c r="BH7">
+        <v>2.2</v>
+      </c>
+      <c r="BI7">
+        <v>2.04</v>
+      </c>
+      <c r="BJ7">
+        <v>15.5</v>
+      </c>
+      <c r="BK7">
+        <v>13</v>
+      </c>
+      <c r="BL7">
+        <v>960</v>
+      </c>
+      <c r="BM7">
         <v>12.5</v>
       </c>
-      <c r="AY7">
-        <v>10</v>
-      </c>
-      <c r="AZ7">
-        <v>16.5</v>
-      </c>
-      <c r="BA7">
-        <v>42</v>
-      </c>
-      <c r="BB7">
+      <c r="BN7">
+        <v>5.5</v>
+      </c>
+      <c r="BO7">
+        <v>4.7</v>
+      </c>
+      <c r="BP7">
+        <v>34</v>
+      </c>
+      <c r="BQ7">
         <v>26</v>
       </c>
-      <c r="BC7">
-        <v>21</v>
-      </c>
-      <c r="BD7">
-        <v>32</v>
-      </c>
-      <c r="BE7">
+      <c r="BR7">
+        <v>860</v>
+      </c>
+      <c r="BS7">
+        <v>60</v>
+      </c>
+      <c r="BT7">
+        <v>6.6</v>
+      </c>
+      <c r="BU7">
+        <v>5.7</v>
+      </c>
+      <c r="BV7">
+        <v>55</v>
+      </c>
+      <c r="BW7">
+        <v>34</v>
+      </c>
+      <c r="BX7">
+        <v>940</v>
+      </c>
+      <c r="BY7">
         <v>75</v>
       </c>
-      <c r="BF7">
-        <v>16.5</v>
-      </c>
-      <c r="BG7">
-        <v>34</v>
-      </c>
-      <c r="BH7">
-        <v>3.45</v>
-      </c>
-      <c r="BI7">
-        <v>2.7</v>
-      </c>
-      <c r="BJ7">
-        <v>10</v>
-      </c>
-      <c r="BK7">
-        <v>5.2</v>
-      </c>
-      <c r="BL7">
-        <v>1000</v>
-      </c>
-      <c r="BM7">
-        <v>10</v>
-      </c>
-      <c r="BN7">
-        <v>5.2</v>
-      </c>
-      <c r="BO7">
-        <v>3.9</v>
-      </c>
-      <c r="BP7">
-        <v>17</v>
-      </c>
-      <c r="BQ7">
-        <v>6.6</v>
-      </c>
-      <c r="BR7">
-        <v>32</v>
-      </c>
-      <c r="BS7">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BT7">
-        <v>7.2</v>
-      </c>
-      <c r="BU7">
-        <v>5.2</v>
-      </c>
-      <c r="BV7">
-        <v>32</v>
-      </c>
-      <c r="BW7">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BX7">
-        <v>1000</v>
-      </c>
-      <c r="BY7">
-        <v>8.6</v>
-      </c>
       <c r="BZ7">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="CA7">
-        <v>7.8</v>
+        <v>70</v>
       </c>
       <c r="CB7" t="s">
         <v>129</v>
@@ -2449,67 +2449,67 @@
         <v>120</v>
       </c>
       <c r="F8">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="G8">
+        <v>1.25</v>
+      </c>
+      <c r="H8">
+        <v>15</v>
+      </c>
+      <c r="I8">
+        <v>21</v>
+      </c>
+      <c r="J8">
+        <v>6.4</v>
+      </c>
+      <c r="K8">
+        <v>8.6</v>
+      </c>
+      <c r="L8">
         <v>1.23</v>
-      </c>
-      <c r="H8">
-        <v>19.5</v>
-      </c>
-      <c r="I8">
-        <v>23</v>
-      </c>
-      <c r="J8">
-        <v>7.4</v>
-      </c>
-      <c r="K8">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="L8">
-        <v>1.2</v>
       </c>
       <c r="M8">
         <v>1.03</v>
       </c>
       <c r="N8">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="O8">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="P8">
-        <v>2.66</v>
+        <v>2.52</v>
       </c>
       <c r="Q8">
-        <v>1.54</v>
+        <v>1.59</v>
       </c>
       <c r="R8">
-        <v>1.66</v>
+        <v>1.59</v>
       </c>
       <c r="S8">
+        <v>2.5</v>
+      </c>
+      <c r="T8">
         <v>2.38</v>
       </c>
-      <c r="T8">
-        <v>2.34</v>
-      </c>
       <c r="U8">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="V8">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="W8">
-        <v>5.3</v>
+        <v>4.8</v>
       </c>
       <c r="X8">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="Y8">
-        <v>75</v>
+        <v>120</v>
       </c>
       <c r="Z8">
-        <v>290</v>
+        <v>240</v>
       </c>
       <c r="AA8">
         <v>1000</v>
@@ -2518,40 +2518,40 @@
         <v>13</v>
       </c>
       <c r="AC8">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AD8">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AE8">
-        <v>490</v>
+        <v>440</v>
       </c>
       <c r="AF8">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AG8">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="AH8">
         <v>55</v>
       </c>
       <c r="AI8">
-        <v>330</v>
+        <v>300</v>
       </c>
       <c r="AJ8">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AK8">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AL8">
         <v>65</v>
       </c>
       <c r="AM8">
-        <v>330</v>
+        <v>300</v>
       </c>
       <c r="AN8">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="AO8">
         <v>1000</v>
@@ -2569,106 +2569,106 @@
         <v>6.4</v>
       </c>
       <c r="AT8">
-        <v>9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU8">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AV8">
-        <v>6</v>
+        <v>27</v>
       </c>
       <c r="AW8">
         <v>6.4</v>
       </c>
       <c r="AX8">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AY8">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AZ8">
-        <v>6</v>
+        <v>19.5</v>
       </c>
       <c r="BA8">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BB8">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BC8">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BD8">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="BE8">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="BF8">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="BG8">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="BH8">
-        <v>1000</v>
+        <v>5.5</v>
       </c>
       <c r="BI8">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BJ8">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="BK8">
-        <v>1.47</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BL8">
         <v>1000</v>
       </c>
       <c r="BM8">
-        <v>1.47</v>
+        <v>6.6</v>
       </c>
       <c r="BN8">
-        <v>1000</v>
+        <v>4.5</v>
       </c>
       <c r="BO8">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="BP8">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="BQ8">
-        <v>3.95</v>
+        <v>4.5</v>
       </c>
       <c r="BR8">
-        <v>1000</v>
+        <v>980</v>
       </c>
       <c r="BS8">
-        <v>1.47</v>
+        <v>7.6</v>
       </c>
       <c r="BT8">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="BU8">
-        <v>1.47</v>
+        <v>7.8</v>
       </c>
       <c r="BV8">
         <v>1000</v>
       </c>
       <c r="BW8">
-        <v>1.47</v>
+        <v>6.6</v>
       </c>
       <c r="BX8">
         <v>1000</v>
       </c>
       <c r="BY8">
-        <v>4</v>
+        <v>6.6</v>
       </c>
       <c r="BZ8">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="CA8">
-        <v>2</v>
+        <v>5.1</v>
       </c>
       <c r="CB8" t="s">
         <v>129</v>
@@ -2691,58 +2691,58 @@
         <v>121</v>
       </c>
       <c r="F9">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="G9">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="H9">
         <v>6</v>
       </c>
       <c r="I9">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="J9">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="K9">
         <v>3.45</v>
       </c>
       <c r="L9">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="M9">
         <v>1.15</v>
       </c>
       <c r="N9">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="O9">
         <v>1.64</v>
       </c>
       <c r="P9">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="Q9">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="R9">
         <v>1.17</v>
       </c>
       <c r="S9">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="T9">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="U9">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="V9">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="W9">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="X9">
         <v>7.8</v>
@@ -2751,7 +2751,7 @@
         <v>14.5</v>
       </c>
       <c r="Z9">
-        <v>55</v>
+        <v>150</v>
       </c>
       <c r="AA9">
         <v>900</v>
@@ -2763,16 +2763,16 @@
         <v>8.4</v>
       </c>
       <c r="AD9">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AE9">
         <v>500</v>
       </c>
       <c r="AF9">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AG9">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AH9">
         <v>36</v>
@@ -2784,7 +2784,7 @@
         <v>22</v>
       </c>
       <c r="AK9">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AL9">
         <v>90</v>
@@ -2793,124 +2793,124 @@
         <v>500</v>
       </c>
       <c r="AN9">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AO9">
         <v>410</v>
       </c>
       <c r="AP9">
+        <v>6.8</v>
+      </c>
+      <c r="AQ9">
         <v>6.6</v>
       </c>
-      <c r="AQ9">
-        <v>6</v>
-      </c>
       <c r="AR9">
-        <v>8.6</v>
+        <v>9.6</v>
       </c>
       <c r="AS9">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="AT9">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AU9">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AV9">
-        <v>7.6</v>
+        <v>13</v>
       </c>
       <c r="AW9">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="AX9">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AY9">
         <v>10.5</v>
       </c>
       <c r="AZ9">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="BA9">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="BB9">
         <v>18</v>
       </c>
       <c r="BC9">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BD9">
-        <v>9.199999999999999</v>
+        <v>30</v>
       </c>
       <c r="BE9">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="BF9">
         <v>21</v>
       </c>
       <c r="BG9">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="BH9">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="BI9">
-        <v>2.06</v>
+        <v>2.3</v>
       </c>
       <c r="BJ9">
         <v>14</v>
       </c>
       <c r="BK9">
-        <v>6.2</v>
+        <v>7.4</v>
       </c>
       <c r="BL9">
         <v>1000</v>
       </c>
       <c r="BM9">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="BN9">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
       <c r="BO9">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="BP9">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="BQ9">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="BR9">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="BS9">
-        <v>9.6</v>
+        <v>12</v>
       </c>
       <c r="BT9">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BU9">
-        <v>5.2</v>
+        <v>6.4</v>
       </c>
       <c r="BV9">
         <v>1000</v>
       </c>
       <c r="BW9">
-        <v>10</v>
+        <v>13.5</v>
       </c>
       <c r="BX9">
         <v>1000</v>
       </c>
       <c r="BY9">
-        <v>10.5</v>
+        <v>14</v>
       </c>
       <c r="BZ9">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="CA9">
-        <v>9.6</v>
+        <v>12</v>
       </c>
       <c r="CB9" t="s">
         <v>129</v>
@@ -2933,10 +2933,10 @@
         <v>122</v>
       </c>
       <c r="F10">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="G10">
-        <v>2.48</v>
+        <v>2.44</v>
       </c>
       <c r="H10">
         <v>3.25</v>
@@ -2945,61 +2945,61 @@
         <v>3.45</v>
       </c>
       <c r="J10">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K10">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="L10">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="M10">
         <v>1.08</v>
       </c>
       <c r="N10">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="O10">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="P10">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="Q10">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="R10">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="S10">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="T10">
-        <v>1.87</v>
+        <v>1.79</v>
       </c>
       <c r="U10">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="V10">
         <v>1.4</v>
       </c>
       <c r="W10">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="X10">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="Y10">
         <v>12.5</v>
       </c>
       <c r="Z10">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AA10">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AB10">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AC10">
         <v>8</v>
@@ -3008,34 +3008,34 @@
         <v>14.5</v>
       </c>
       <c r="AE10">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="AF10">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AG10">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH10">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AI10">
         <v>55</v>
       </c>
       <c r="AJ10">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AK10">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AL10">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AM10">
         <v>580</v>
       </c>
       <c r="AN10">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AO10">
         <v>42</v>
@@ -3047,22 +3047,22 @@
         <v>10.5</v>
       </c>
       <c r="AR10">
+        <v>10</v>
+      </c>
+      <c r="AS10">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AT10">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AU10">
+        <v>7</v>
+      </c>
+      <c r="AV10">
+        <v>12.5</v>
+      </c>
+      <c r="AW10">
         <v>17.5</v>
-      </c>
-      <c r="AS10">
-        <v>36</v>
-      </c>
-      <c r="AT10">
-        <v>8.6</v>
-      </c>
-      <c r="AU10">
-        <v>6.8</v>
-      </c>
-      <c r="AV10">
-        <v>12</v>
-      </c>
-      <c r="AW10">
-        <v>28</v>
       </c>
       <c r="AX10">
         <v>13.5</v>
@@ -3074,40 +3074,40 @@
         <v>15.5</v>
       </c>
       <c r="BA10">
-        <v>30</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BB10">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="BC10">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="BD10">
-        <v>30</v>
+        <v>18.5</v>
       </c>
       <c r="BE10">
-        <v>75</v>
+        <v>10.5</v>
       </c>
       <c r="BF10">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="BG10">
-        <v>25</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH10">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="BI10">
-        <v>2.6</v>
+        <v>2.66</v>
       </c>
       <c r="BJ10">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BK10">
-        <v>5.2</v>
+        <v>7</v>
       </c>
       <c r="BL10">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="BM10">
         <v>9.6</v>
@@ -3119,31 +3119,31 @@
         <v>4</v>
       </c>
       <c r="BP10">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BQ10">
         <v>6.6</v>
       </c>
       <c r="BR10">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BS10">
         <v>8</v>
       </c>
       <c r="BT10">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BU10">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BV10">
         <v>28</v>
       </c>
       <c r="BW10">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BX10">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BY10">
         <v>8.199999999999999</v>
@@ -3175,67 +3175,67 @@
         <v>123</v>
       </c>
       <c r="F11">
-        <v>1.8</v>
+        <v>1.69</v>
       </c>
       <c r="G11">
-        <v>1.87</v>
+        <v>1.74</v>
       </c>
       <c r="H11">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="I11">
-        <v>5.8</v>
+        <v>6.6</v>
       </c>
       <c r="J11">
-        <v>3.45</v>
+        <v>3.75</v>
       </c>
       <c r="K11">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="L11">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="M11">
         <v>1.1</v>
       </c>
       <c r="N11">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="O11">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="P11">
-        <v>1.64</v>
+        <v>1.68</v>
       </c>
       <c r="Q11">
-        <v>2.46</v>
+        <v>2.34</v>
       </c>
       <c r="R11">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="S11">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="T11">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="U11">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="V11">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="W11">
-        <v>2.14</v>
+        <v>2.34</v>
       </c>
       <c r="X11">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="Y11">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Z11">
-        <v>46</v>
+        <v>120</v>
       </c>
       <c r="AA11">
         <v>900</v>
@@ -3244,157 +3244,157 @@
         <v>6.8</v>
       </c>
       <c r="AC11">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD11">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AE11">
-        <v>260</v>
+        <v>130</v>
       </c>
       <c r="AF11">
-        <v>10</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AG11">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AH11">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="AI11">
-        <v>260</v>
+        <v>700</v>
       </c>
       <c r="AJ11">
-        <v>21</v>
+        <v>17.5</v>
       </c>
       <c r="AK11">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AL11">
         <v>60</v>
       </c>
       <c r="AM11">
-        <v>580</v>
+        <v>500</v>
       </c>
       <c r="AN11">
-        <v>19</v>
+        <v>15.5</v>
       </c>
       <c r="AO11">
-        <v>230</v>
+        <v>280</v>
       </c>
       <c r="AP11">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AQ11">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="AR11">
         <v>36</v>
       </c>
       <c r="AS11">
-        <v>85</v>
+        <v>21</v>
       </c>
       <c r="AT11">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="AU11">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="AV11">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AW11">
-        <v>55</v>
+        <v>19</v>
       </c>
       <c r="AX11">
+        <v>7.8</v>
+      </c>
+      <c r="AY11">
         <v>8.6</v>
       </c>
-      <c r="AY11">
-        <v>8.199999999999999</v>
-      </c>
       <c r="AZ11">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="BA11">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="BB11">
+        <v>15.5</v>
+      </c>
+      <c r="BC11">
+        <v>19</v>
+      </c>
+      <c r="BD11">
+        <v>40</v>
+      </c>
+      <c r="BE11">
+        <v>19.5</v>
+      </c>
+      <c r="BF11">
+        <v>13.5</v>
+      </c>
+      <c r="BG11">
         <v>17</v>
       </c>
-      <c r="BC11">
-        <v>20</v>
-      </c>
-      <c r="BD11">
-        <v>34</v>
-      </c>
-      <c r="BE11">
-        <v>65</v>
-      </c>
-      <c r="BF11">
-        <v>15.5</v>
-      </c>
-      <c r="BG11">
-        <v>15</v>
-      </c>
       <c r="BH11">
-        <v>2.88</v>
+        <v>1000</v>
       </c>
       <c r="BI11">
-        <v>2.42</v>
+        <v>2.54</v>
       </c>
       <c r="BJ11">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="BK11">
-        <v>6.6</v>
+        <v>2.84</v>
       </c>
       <c r="BL11">
         <v>1000</v>
       </c>
       <c r="BM11">
-        <v>14</v>
+        <v>1.17</v>
       </c>
       <c r="BN11">
-        <v>4.2</v>
+        <v>1000</v>
       </c>
       <c r="BO11">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="BP11">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="BQ11">
-        <v>7.2</v>
+        <v>2.76</v>
       </c>
       <c r="BR11">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="BS11">
-        <v>10.5</v>
+        <v>1.17</v>
       </c>
       <c r="BT11">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="BU11">
-        <v>5.7</v>
+        <v>2.28</v>
       </c>
       <c r="BV11">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="BW11">
-        <v>12</v>
+        <v>1.17</v>
       </c>
       <c r="BX11">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="BY11">
-        <v>12.5</v>
+        <v>1.17</v>
       </c>
       <c r="BZ11">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="CA11">
-        <v>10.5</v>
+        <v>1.17</v>
       </c>
       <c r="CB11" t="s">
         <v>129</v>
@@ -3417,67 +3417,67 @@
         <v>124</v>
       </c>
       <c r="F12">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="G12">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="H12">
         <v>1.73</v>
       </c>
       <c r="I12">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="J12">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="K12">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="L12">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="M12">
         <v>1.11</v>
       </c>
       <c r="N12">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="O12">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="P12">
-        <v>1.54</v>
+        <v>1.51</v>
       </c>
       <c r="Q12">
-        <v>2.6</v>
+        <v>2.66</v>
       </c>
       <c r="R12">
         <v>1.18</v>
       </c>
       <c r="S12">
+        <v>5.8</v>
+      </c>
+      <c r="T12">
+        <v>2.44</v>
+      </c>
+      <c r="U12">
+        <v>1.61</v>
+      </c>
+      <c r="V12">
+        <v>2.28</v>
+      </c>
+      <c r="W12">
+        <v>1.18</v>
+      </c>
+      <c r="X12">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="Y12">
         <v>5.6</v>
       </c>
-      <c r="T12">
-        <v>2.4</v>
-      </c>
-      <c r="U12">
-        <v>1.57</v>
-      </c>
-      <c r="V12">
-        <v>2.24</v>
-      </c>
-      <c r="W12">
-        <v>1.19</v>
-      </c>
-      <c r="X12">
-        <v>10.5</v>
-      </c>
-      <c r="Y12">
-        <v>5.7</v>
-      </c>
       <c r="Z12">
-        <v>12</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AA12">
         <v>20</v>
@@ -3486,7 +3486,7 @@
         <v>15</v>
       </c>
       <c r="AC12">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AD12">
         <v>11</v>
@@ -3495,7 +3495,7 @@
         <v>27</v>
       </c>
       <c r="AF12">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AG12">
         <v>27</v>
@@ -3507,7 +3507,7 @@
         <v>70</v>
       </c>
       <c r="AJ12">
-        <v>250</v>
+        <v>900</v>
       </c>
       <c r="AK12">
         <v>150</v>
@@ -3516,121 +3516,121 @@
         <v>180</v>
       </c>
       <c r="AM12">
-        <v>330</v>
+        <v>580</v>
       </c>
       <c r="AN12">
-        <v>270</v>
+        <v>280</v>
       </c>
       <c r="AO12">
-        <v>50</v>
+        <v>22</v>
       </c>
       <c r="AP12">
         <v>8.199999999999999</v>
       </c>
       <c r="AQ12">
-        <v>4.7</v>
+        <v>5.4</v>
       </c>
       <c r="AR12">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AS12">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AT12">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AU12">
         <v>8</v>
       </c>
       <c r="AV12">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AW12">
         <v>21</v>
       </c>
       <c r="AX12">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="AY12">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AZ12">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="BA12">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="BB12">
-        <v>11</v>
+        <v>14.5</v>
       </c>
       <c r="BC12">
-        <v>10.5</v>
+        <v>75</v>
       </c>
       <c r="BD12">
-        <v>65</v>
+        <v>16.5</v>
       </c>
       <c r="BE12">
-        <v>11</v>
+        <v>17.5</v>
       </c>
       <c r="BF12">
-        <v>9.800000000000001</v>
+        <v>15</v>
       </c>
       <c r="BG12">
         <v>16.5</v>
       </c>
       <c r="BH12">
-        <v>2.86</v>
+        <v>2.8</v>
       </c>
       <c r="BI12">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="BJ12">
         <v>13.5</v>
       </c>
       <c r="BK12">
-        <v>5.6</v>
+        <v>10.5</v>
       </c>
       <c r="BL12">
         <v>1000</v>
       </c>
       <c r="BM12">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="BN12">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BO12">
-        <v>5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BP12">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="BQ12">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="BR12">
         <v>1000</v>
       </c>
       <c r="BS12">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BT12">
+        <v>4.2</v>
+      </c>
+      <c r="BU12">
+        <v>3.6</v>
+      </c>
+      <c r="BV12">
+        <v>14.5</v>
+      </c>
+      <c r="BW12">
+        <v>10.5</v>
+      </c>
+      <c r="BX12">
+        <v>42</v>
+      </c>
+      <c r="BY12">
         <v>8.6</v>
-      </c>
-      <c r="BT12">
-        <v>4.3</v>
-      </c>
-      <c r="BU12">
-        <v>3.5</v>
-      </c>
-      <c r="BV12">
-        <v>15</v>
-      </c>
-      <c r="BW12">
-        <v>5.8</v>
-      </c>
-      <c r="BX12">
-        <v>44</v>
-      </c>
-      <c r="BY12">
-        <v>7.8</v>
       </c>
       <c r="BZ12">
         <v>0</v>
@@ -3659,94 +3659,94 @@
         <v>125</v>
       </c>
       <c r="F13">
-        <v>2.52</v>
+        <v>2.46</v>
       </c>
       <c r="G13">
+        <v>2.5</v>
+      </c>
+      <c r="H13">
+        <v>3.7</v>
+      </c>
+      <c r="I13">
+        <v>3.75</v>
+      </c>
+      <c r="J13">
+        <v>3</v>
+      </c>
+      <c r="K13">
+        <v>3.05</v>
+      </c>
+      <c r="L13">
+        <v>1.66</v>
+      </c>
+      <c r="M13">
+        <v>1.15</v>
+      </c>
+      <c r="N13">
         <v>2.56</v>
       </c>
-      <c r="H13">
-        <v>3.55</v>
-      </c>
-      <c r="I13">
-        <v>3.65</v>
-      </c>
-      <c r="J13">
-        <v>3.05</v>
-      </c>
-      <c r="K13">
-        <v>3.1</v>
-      </c>
-      <c r="L13">
+      <c r="O13">
         <v>1.62</v>
       </c>
-      <c r="M13">
-        <v>1.14</v>
-      </c>
-      <c r="N13">
-        <v>2.6</v>
-      </c>
-      <c r="O13">
-        <v>1.6</v>
-      </c>
       <c r="P13">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="Q13">
-        <v>2.84</v>
+        <v>2.9</v>
       </c>
       <c r="R13">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="S13">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="T13">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="U13">
-        <v>1.77</v>
+        <v>1.74</v>
       </c>
       <c r="V13">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="W13">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="X13">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="Y13">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="Z13">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AA13">
         <v>80</v>
       </c>
       <c r="AB13">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="AC13">
         <v>7</v>
       </c>
       <c r="AD13">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AE13">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AF13">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AG13">
         <v>13</v>
       </c>
       <c r="AH13">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AI13">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="AJ13">
         <v>38</v>
@@ -3758,13 +3758,13 @@
         <v>70</v>
       </c>
       <c r="AM13">
-        <v>500</v>
+        <v>220</v>
       </c>
       <c r="AN13">
         <v>42</v>
       </c>
       <c r="AO13">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AP13">
         <v>7.4</v>
@@ -3773,10 +3773,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AR13">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AS13">
-        <v>36</v>
+        <v>70</v>
       </c>
       <c r="AT13">
         <v>6.8</v>
@@ -3785,10 +3785,10 @@
         <v>6.6</v>
       </c>
       <c r="AV13">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AW13">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AX13">
         <v>12.5</v>
@@ -3800,7 +3800,7 @@
         <v>22</v>
       </c>
       <c r="BA13">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="BB13">
         <v>34</v>
@@ -3818,67 +3818,67 @@
         <v>36</v>
       </c>
       <c r="BG13">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="BH13">
-        <v>3</v>
+        <v>2.78</v>
       </c>
       <c r="BI13">
-        <v>2.18</v>
+        <v>2.42</v>
       </c>
       <c r="BJ13">
         <v>14</v>
       </c>
       <c r="BK13">
-        <v>8.4</v>
+        <v>10</v>
       </c>
       <c r="BL13">
         <v>260</v>
       </c>
       <c r="BM13">
-        <v>5.7</v>
+        <v>30</v>
       </c>
       <c r="BN13">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BO13">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="BP13">
         <v>22</v>
       </c>
       <c r="BQ13">
-        <v>4.6</v>
+        <v>5.2</v>
       </c>
       <c r="BR13">
         <v>46</v>
       </c>
       <c r="BS13">
-        <v>5.1</v>
+        <v>6</v>
       </c>
       <c r="BT13">
-        <v>7.8</v>
+        <v>6.8</v>
       </c>
       <c r="BU13">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BV13">
         <v>42</v>
       </c>
       <c r="BW13">
-        <v>5.1</v>
+        <v>5.9</v>
       </c>
       <c r="BX13">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="BY13">
-        <v>5.3</v>
+        <v>6.2</v>
       </c>
       <c r="BZ13">
         <v>55</v>
       </c>
       <c r="CA13">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="CB13" t="s">
         <v>129</v>
@@ -3901,121 +3901,121 @@
         <v>126</v>
       </c>
       <c r="F14">
+        <v>1.62</v>
+      </c>
+      <c r="G14">
         <v>1.7</v>
       </c>
-      <c r="G14">
-        <v>1.75</v>
-      </c>
       <c r="H14">
-        <v>5.7</v>
+        <v>6.6</v>
       </c>
       <c r="I14">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="J14">
         <v>3.65</v>
       </c>
       <c r="K14">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="L14">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="M14">
         <v>1.09</v>
       </c>
       <c r="N14">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="O14">
         <v>1.41</v>
       </c>
       <c r="P14">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="Q14">
-        <v>2.24</v>
+        <v>2.18</v>
       </c>
       <c r="R14">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="S14">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="T14">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="U14">
-        <v>1.79</v>
+        <v>1.74</v>
       </c>
       <c r="V14">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="W14">
-        <v>2.32</v>
+        <v>2.42</v>
       </c>
       <c r="X14">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="Y14">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="Z14">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AA14">
         <v>900</v>
       </c>
       <c r="AB14">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AC14">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AD14">
         <v>28</v>
       </c>
       <c r="AE14">
-        <v>120</v>
+        <v>200</v>
       </c>
       <c r="AF14">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="AG14">
         <v>11</v>
       </c>
       <c r="AH14">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AI14">
-        <v>130</v>
+        <v>500</v>
       </c>
       <c r="AJ14">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="AK14">
         <v>21</v>
       </c>
       <c r="AL14">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AM14">
         <v>580</v>
       </c>
       <c r="AN14">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AO14">
-        <v>220</v>
+        <v>330</v>
       </c>
       <c r="AP14">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AQ14">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="AR14">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AS14">
         <v>10</v>
@@ -4024,40 +4024,40 @@
         <v>6</v>
       </c>
       <c r="AU14">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AV14">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AW14">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="AX14">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="AY14">
         <v>9</v>
       </c>
       <c r="AZ14">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BA14">
-        <v>55</v>
+        <v>23</v>
       </c>
       <c r="BB14">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="BC14">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BD14">
         <v>29</v>
       </c>
       <c r="BE14">
+        <v>10</v>
+      </c>
+      <c r="BF14">
         <v>10.5</v>
-      </c>
-      <c r="BF14">
-        <v>11.5</v>
       </c>
       <c r="BG14">
         <v>10</v>
@@ -4066,61 +4066,61 @@
         <v>3.55</v>
       </c>
       <c r="BI14">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="BJ14">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BK14">
-        <v>3.6</v>
+        <v>4.5</v>
       </c>
       <c r="BL14">
         <v>1000</v>
       </c>
       <c r="BM14">
-        <v>4.8</v>
+        <v>6.6</v>
       </c>
       <c r="BN14">
-        <v>4.8</v>
+        <v>4.1</v>
       </c>
       <c r="BO14">
-        <v>3.2</v>
+        <v>3.55</v>
       </c>
       <c r="BP14">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="BQ14">
-        <v>3.7</v>
+        <v>4.5</v>
       </c>
       <c r="BR14">
         <v>40</v>
       </c>
       <c r="BS14">
-        <v>4.3</v>
+        <v>5.8</v>
       </c>
       <c r="BT14">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="BU14">
-        <v>3.45</v>
+        <v>4.1</v>
       </c>
       <c r="BV14">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="BW14">
-        <v>4.6</v>
+        <v>6.2</v>
       </c>
       <c r="BX14">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="BY14">
-        <v>4.6</v>
+        <v>6.4</v>
       </c>
       <c r="BZ14">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="CA14">
-        <v>4.3</v>
+        <v>5.5</v>
       </c>
       <c r="CB14" t="s">
         <v>129</v>
@@ -4385,22 +4385,22 @@
         <v>128</v>
       </c>
       <c r="F16">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="G16">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="H16">
-        <v>2.86</v>
+        <v>2.82</v>
       </c>
       <c r="I16">
-        <v>3.05</v>
+        <v>2.98</v>
       </c>
       <c r="J16">
         <v>3.6</v>
       </c>
       <c r="K16">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="L16">
         <v>1.31</v>
@@ -4412,7 +4412,7 @@
         <v>5.2</v>
       </c>
       <c r="O16">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="P16">
         <v>2.38</v>
@@ -4421,7 +4421,7 @@
         <v>1.68</v>
       </c>
       <c r="R16">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="S16">
         <v>2.6</v>
@@ -4430,19 +4430,19 @@
         <v>1.61</v>
       </c>
       <c r="U16">
-        <v>2.54</v>
+        <v>2.32</v>
       </c>
       <c r="V16">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="W16">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="X16">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="Y16">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="Z16">
         <v>23</v>
@@ -4451,10 +4451,10 @@
         <v>46</v>
       </c>
       <c r="AB16">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AC16">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD16">
         <v>13.5</v>
@@ -4475,7 +4475,7 @@
         <v>34</v>
       </c>
       <c r="AJ16">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AK16">
         <v>24</v>
@@ -4484,10 +4484,10 @@
         <v>32</v>
       </c>
       <c r="AM16">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AN16">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AO16">
         <v>19.5</v>
@@ -4505,10 +4505,10 @@
         <v>38</v>
       </c>
       <c r="AT16">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AU16">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AV16">
         <v>11.5</v>
@@ -4517,13 +4517,13 @@
         <v>24</v>
       </c>
       <c r="AX16">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AY16">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AZ16">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BA16">
         <v>29</v>
@@ -4538,67 +4538,67 @@
         <v>25</v>
       </c>
       <c r="BE16">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="BF16">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BG16">
         <v>16</v>
       </c>
       <c r="BH16">
-        <v>4.9</v>
+        <v>1000</v>
       </c>
       <c r="BI16">
-        <v>3.25</v>
+        <v>1.04</v>
       </c>
       <c r="BJ16">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="BK16">
-        <v>5.4</v>
+        <v>1.04</v>
       </c>
       <c r="BL16">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="BM16">
-        <v>7.4</v>
+        <v>1.04</v>
       </c>
       <c r="BN16">
-        <v>6</v>
+        <v>1000</v>
       </c>
       <c r="BO16">
-        <v>5</v>
+        <v>1.04</v>
       </c>
       <c r="BP16">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ16">
-        <v>5.5</v>
+        <v>1.04</v>
       </c>
       <c r="BR16">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="BS16">
-        <v>6</v>
+        <v>1.04</v>
       </c>
       <c r="BT16">
-        <v>6.6</v>
+        <v>1000</v>
       </c>
       <c r="BU16">
-        <v>5.4</v>
+        <v>1.04</v>
       </c>
       <c r="BV16">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="BW16">
-        <v>5.8</v>
+        <v>1.04</v>
       </c>
       <c r="BX16">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="BY16">
-        <v>6.2</v>
+        <v>1.04</v>
       </c>
       <c r="BZ16">
         <v>0</v>
